--- a/benchmarking/results/results.xlsx
+++ b/benchmarking/results/results.xlsx
@@ -5,12 +5,12 @@
   <workbookPr hidePivotFieldList="1" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/deborahdore/Documents/political-debates-graph-analysis/benchmarking/search_for_best_combination/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/deborahdore/Documents/political-debates-graph-analysis/benchmarking/results/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{063555A2-2350-1A4B-BBB0-774FF3BC1890}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA9310B9-64F5-6341-A559-2DE829997205}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4280" yWindow="500" windowWidth="46920" windowHeight="26600" xr2:uid="{E2EDC037-19C4-FE46-A599-BB595128A04F}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="21600" xr2:uid="{E2EDC037-19C4-FE46-A599-BB595128A04F}"/>
   </bookViews>
   <sheets>
     <sheet name="Results BASIC" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="470" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="470" uniqueCount="87">
   <si>
     <t>MODEL'S TYPE</t>
   </si>
@@ -213,9 +213,6 @@
   </si>
   <si>
     <t>RELATION CLASSIFICATION F1-MACRO</t>
-  </si>
-  <si>
-    <t>RELATION CLASSIFICATION  F1-MACRO</t>
   </si>
   <si>
     <t>EXPLAINATION EXPERIMENT</t>
@@ -311,6 +308,12 @@
   </si>
   <si>
     <t>experiment with basic sampler and downsampling the major class</t>
+  </si>
+  <si>
+    <t>TRIPLE CLASSIFICATION F1-WEIGHTED</t>
+  </si>
+  <si>
+    <t>RELATION CLASSIFICATION  F1-WEIGHTED</t>
   </si>
 </sst>
 </file>
@@ -471,7 +474,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="82">
+  <cellXfs count="80">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -647,6 +650,18 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -656,27 +671,30 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -693,27 +711,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1080,10 +1077,10 @@
         <v>55</v>
       </c>
       <c r="I1" s="12" t="s">
-        <v>56</v>
+        <v>85</v>
       </c>
       <c r="J1" s="12" t="s">
-        <v>58</v>
+        <v>86</v>
       </c>
       <c r="K1" s="7" t="s">
         <v>14</v>
@@ -1097,21 +1094,31 @@
       <c r="B2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="64" t="s">
+      <c r="C2" s="68" t="s">
         <v>41</v>
       </c>
-      <c r="D2" s="63" t="s">
+      <c r="D2" s="67" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="63" t="s">
+      <c r="E2" s="67" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="75"/>
-      <c r="G2" s="75"/>
-      <c r="H2" s="75"/>
-      <c r="I2" s="75"/>
-      <c r="J2" s="75"/>
-      <c r="K2" s="66" t="s">
+      <c r="F2" s="11">
+        <v>7.5551294300000002E-2</v>
+      </c>
+      <c r="G2" s="11">
+        <v>2.2051773000000001E-3</v>
+      </c>
+      <c r="H2" s="11">
+        <v>0.44467881110000002</v>
+      </c>
+      <c r="I2" s="11">
+        <v>0.57438833690000002</v>
+      </c>
+      <c r="J2" s="11">
+        <v>0.56363568119999996</v>
+      </c>
+      <c r="K2" s="70" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1122,15 +1129,25 @@
       <c r="B3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="60"/>
-      <c r="D3" s="61"/>
-      <c r="E3" s="61"/>
-      <c r="F3" s="75"/>
-      <c r="G3" s="75"/>
-      <c r="H3" s="75"/>
-      <c r="I3" s="75"/>
-      <c r="J3" s="75"/>
-      <c r="K3" s="67"/>
+      <c r="C3" s="64"/>
+      <c r="D3" s="65"/>
+      <c r="E3" s="65"/>
+      <c r="F3" s="11">
+        <v>3.9117929099999997E-2</v>
+      </c>
+      <c r="G3" s="11">
+        <v>9.5877280000000004E-4</v>
+      </c>
+      <c r="H3" s="11">
+        <v>0.38044103550000002</v>
+      </c>
+      <c r="I3" s="11">
+        <v>0.53542729820000001</v>
+      </c>
+      <c r="J3" s="11">
+        <v>0.52549201359999997</v>
+      </c>
+      <c r="K3" s="71"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
@@ -1139,22 +1156,25 @@
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="60"/>
-      <c r="D4" s="61"/>
-      <c r="E4" s="61"/>
-      <c r="F4" s="75"/>
-      <c r="G4" s="75"/>
-      <c r="H4" s="75"/>
-      <c r="I4" s="75"/>
-      <c r="J4" s="75"/>
-      <c r="K4" s="67"/>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="F5" s="75"/>
-      <c r="G5" s="75"/>
-      <c r="H5" s="75"/>
-      <c r="I5" s="75"/>
-      <c r="J5" s="75"/>
+      <c r="C4" s="64"/>
+      <c r="D4" s="65"/>
+      <c r="E4" s="65"/>
+      <c r="F4" s="11">
+        <v>2.1093001000000002E-3</v>
+      </c>
+      <c r="G4" s="11">
+        <v>3.8350910000000001E-4</v>
+      </c>
+      <c r="H4" s="11">
+        <v>0.43509108340000002</v>
+      </c>
+      <c r="I4" s="11">
+        <v>0.58024751610000003</v>
+      </c>
+      <c r="J4" s="11">
+        <v>0.4978749918</v>
+      </c>
+      <c r="K4" s="71"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
@@ -1163,21 +1183,31 @@
       <c r="B6" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="60" t="s">
+      <c r="C6" s="64" t="s">
         <v>42</v>
       </c>
-      <c r="D6" s="61" t="s">
+      <c r="D6" s="65" t="s">
         <v>10</v>
       </c>
-      <c r="E6" s="61" t="s">
+      <c r="E6" s="65" t="s">
         <v>13</v>
       </c>
-      <c r="F6" s="75"/>
-      <c r="G6" s="75"/>
-      <c r="H6" s="75"/>
-      <c r="I6" s="75"/>
-      <c r="J6" s="75"/>
-      <c r="K6" s="67" t="s">
+      <c r="F6" s="11">
+        <v>3.9950182000000001E-2</v>
+      </c>
+      <c r="G6" s="11">
+        <v>1.3412531E-3</v>
+      </c>
+      <c r="H6" s="11">
+        <v>0.36232994829999998</v>
+      </c>
+      <c r="I6" s="11">
+        <v>0.53999942830000003</v>
+      </c>
+      <c r="J6" s="11">
+        <v>0.54077441869999998</v>
+      </c>
+      <c r="K6" s="71" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1188,15 +1218,25 @@
       <c r="B7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="60"/>
-      <c r="D7" s="61"/>
-      <c r="E7" s="61"/>
-      <c r="F7" s="75"/>
-      <c r="G7" s="75"/>
-      <c r="H7" s="75"/>
-      <c r="I7" s="75"/>
-      <c r="J7" s="75"/>
-      <c r="K7" s="67"/>
+      <c r="C7" s="64"/>
+      <c r="D7" s="65"/>
+      <c r="E7" s="65"/>
+      <c r="F7" s="11">
+        <v>3.2094270899999999E-2</v>
+      </c>
+      <c r="G7" s="11">
+        <v>2.5867023999999999E-3</v>
+      </c>
+      <c r="H7" s="11">
+        <v>0.35351599919999999</v>
+      </c>
+      <c r="I7" s="11">
+        <v>0.5349605033</v>
+      </c>
+      <c r="J7" s="11">
+        <v>0.53556060419999996</v>
+      </c>
+      <c r="K7" s="71"/>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
@@ -1205,44 +1245,40 @@
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="60"/>
-      <c r="D8" s="61"/>
-      <c r="E8" s="61"/>
-      <c r="F8" s="75"/>
-      <c r="G8" s="75"/>
-      <c r="H8" s="75"/>
-      <c r="I8" s="75"/>
-      <c r="J8" s="75"/>
-      <c r="K8" s="67"/>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="F9" s="75"/>
-      <c r="G9" s="75"/>
-      <c r="H9" s="75"/>
-      <c r="I9" s="75"/>
-      <c r="J9" s="75"/>
-    </row>
-    <row r="10" spans="1:12" s="80" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="77" t="s">
+      <c r="C8" s="64"/>
+      <c r="D8" s="65"/>
+      <c r="E8" s="65"/>
+      <c r="F8" s="11">
+        <v>2.8741139999999998E-4</v>
+      </c>
+      <c r="G8" s="11">
+        <v>1.2454492999999999E-3</v>
+      </c>
+      <c r="H8" s="11">
+        <v>0.4696301974</v>
+      </c>
+      <c r="I8" s="11">
+        <v>0.56417524429999999</v>
+      </c>
+      <c r="J8" s="11">
+        <v>0.518358965</v>
+      </c>
+      <c r="K8" s="71"/>
+    </row>
+    <row r="10" spans="1:12" s="59" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="66" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="77"/>
-      <c r="C10" s="77"/>
-      <c r="D10" s="77"/>
-      <c r="E10" s="78"/>
-      <c r="F10" s="79"/>
-      <c r="G10" s="79"/>
-      <c r="H10" s="79"/>
-      <c r="I10" s="79"/>
-      <c r="J10" s="79"/>
-      <c r="K10" s="78"/>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="F11" s="75"/>
-      <c r="G11" s="75"/>
-      <c r="H11" s="75"/>
-      <c r="I11" s="75"/>
-      <c r="J11" s="75"/>
+      <c r="B10" s="66"/>
+      <c r="C10" s="66"/>
+      <c r="D10" s="66"/>
+      <c r="E10" s="60"/>
+      <c r="F10" s="61"/>
+      <c r="G10" s="61"/>
+      <c r="H10" s="61"/>
+      <c r="I10" s="61"/>
+      <c r="J10" s="61"/>
+      <c r="K10" s="60"/>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
@@ -1251,21 +1287,31 @@
       <c r="B12" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C12" s="60" t="s">
+      <c r="C12" s="64" t="s">
         <v>43</v>
       </c>
-      <c r="D12" s="61" t="s">
+      <c r="D12" s="65" t="s">
         <v>11</v>
       </c>
-      <c r="E12" s="61" t="s">
+      <c r="E12" s="65" t="s">
         <v>17</v>
       </c>
-      <c r="F12" s="75"/>
-      <c r="G12" s="75"/>
-      <c r="H12" s="75"/>
-      <c r="I12" s="75"/>
-      <c r="J12" s="75"/>
-      <c r="K12" s="67" t="s">
+      <c r="F12" s="11">
+        <v>0.11278433860000001</v>
+      </c>
+      <c r="G12" s="11">
+        <v>5.3816279600000003E-2</v>
+      </c>
+      <c r="H12" s="11">
+        <v>0.51319648090000003</v>
+      </c>
+      <c r="I12" s="11">
+        <v>0.67925847319999999</v>
+      </c>
+      <c r="J12" s="11">
+        <v>0.7111340854</v>
+      </c>
+      <c r="K12" s="71" t="s">
         <v>18</v>
       </c>
     </row>
@@ -1276,15 +1322,25 @@
       <c r="B13" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C13" s="60"/>
-      <c r="D13" s="61"/>
-      <c r="E13" s="61"/>
-      <c r="F13" s="75"/>
-      <c r="G13" s="75"/>
-      <c r="H13" s="75"/>
-      <c r="I13" s="75"/>
-      <c r="J13" s="75"/>
-      <c r="K13" s="67"/>
+      <c r="C13" s="64"/>
+      <c r="D13" s="65"/>
+      <c r="E13" s="65"/>
+      <c r="F13" s="11">
+        <v>1.0937623800000001E-2</v>
+      </c>
+      <c r="G13" s="11">
+        <v>0</v>
+      </c>
+      <c r="H13" s="11">
+        <v>0.33597527150000001</v>
+      </c>
+      <c r="I13" s="11">
+        <v>0.48911294719999998</v>
+      </c>
+      <c r="J13" s="11">
+        <v>0.54478313199999995</v>
+      </c>
+      <c r="K13" s="71"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
@@ -1293,22 +1349,25 @@
       <c r="B14" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C14" s="60"/>
-      <c r="D14" s="61"/>
-      <c r="E14" s="61"/>
-      <c r="F14" s="75"/>
-      <c r="G14" s="75"/>
-      <c r="H14" s="75"/>
-      <c r="I14" s="75"/>
-      <c r="J14" s="75"/>
-      <c r="K14" s="67"/>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="F15" s="75"/>
-      <c r="G15" s="75"/>
-      <c r="H15" s="75"/>
-      <c r="I15" s="75"/>
-      <c r="J15" s="75"/>
+      <c r="C14" s="64"/>
+      <c r="D14" s="65"/>
+      <c r="E14" s="65"/>
+      <c r="F14" s="11">
+        <v>2.377744E-4</v>
+      </c>
+      <c r="G14" s="11">
+        <v>6.7369420000000003E-4</v>
+      </c>
+      <c r="H14" s="11">
+        <v>0.99643338349999999</v>
+      </c>
+      <c r="I14" s="11">
+        <v>0.4136900905</v>
+      </c>
+      <c r="J14" s="11">
+        <v>0.60797287919999998</v>
+      </c>
+      <c r="K14" s="71"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
@@ -1317,21 +1376,16 @@
       <c r="B16" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C16" s="60" t="s">
+      <c r="C16" s="64" t="s">
         <v>44</v>
       </c>
-      <c r="D16" s="61" t="s">
+      <c r="D16" s="65" t="s">
         <v>19</v>
       </c>
-      <c r="E16" s="61" t="s">
+      <c r="E16" s="65" t="s">
         <v>27</v>
       </c>
-      <c r="F16" s="75"/>
-      <c r="G16" s="75"/>
-      <c r="H16" s="75"/>
-      <c r="I16" s="75"/>
-      <c r="J16" s="75"/>
-      <c r="K16" s="67" t="s">
+      <c r="K16" s="71" t="s">
         <v>36</v>
       </c>
     </row>
@@ -1342,15 +1396,10 @@
       <c r="B17" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C17" s="60"/>
-      <c r="D17" s="61"/>
-      <c r="E17" s="61"/>
-      <c r="F17" s="75"/>
-      <c r="G17" s="75"/>
-      <c r="H17" s="75"/>
-      <c r="I17" s="75"/>
-      <c r="J17" s="75"/>
-      <c r="K17" s="67"/>
+      <c r="C17" s="64"/>
+      <c r="D17" s="65"/>
+      <c r="E17" s="65"/>
+      <c r="K17" s="71"/>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
@@ -1359,22 +1408,10 @@
       <c r="B18" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C18" s="60"/>
-      <c r="D18" s="61"/>
-      <c r="E18" s="61"/>
-      <c r="F18" s="75"/>
-      <c r="G18" s="75"/>
-      <c r="H18" s="75"/>
-      <c r="I18" s="75"/>
-      <c r="J18" s="75"/>
-      <c r="K18" s="67"/>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="F19" s="75"/>
-      <c r="G19" s="75"/>
-      <c r="H19" s="75"/>
-      <c r="I19" s="75"/>
-      <c r="J19" s="75"/>
+      <c r="C18" s="64"/>
+      <c r="D18" s="65"/>
+      <c r="E18" s="65"/>
+      <c r="K18" s="71"/>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
@@ -1383,21 +1420,31 @@
       <c r="B20" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C20" s="60" t="s">
+      <c r="C20" s="64" t="s">
         <v>45</v>
       </c>
-      <c r="D20" s="61" t="s">
+      <c r="D20" s="65" t="s">
         <v>20</v>
       </c>
-      <c r="E20" s="61" t="s">
+      <c r="E20" s="65" t="s">
         <v>28</v>
       </c>
-      <c r="F20" s="75"/>
-      <c r="G20" s="75"/>
-      <c r="H20" s="75"/>
-      <c r="I20" s="75"/>
-      <c r="J20" s="75"/>
-      <c r="K20" s="67" t="s">
+      <c r="F20" s="11">
+        <v>0.39523043940000002</v>
+      </c>
+      <c r="G20" s="11">
+        <v>3.3092175799999998E-2</v>
+      </c>
+      <c r="H20" s="11">
+        <v>0.68837084670000004</v>
+      </c>
+      <c r="I20" s="11">
+        <v>0.86719286390000005</v>
+      </c>
+      <c r="J20" s="11">
+        <v>0.42558258160000001</v>
+      </c>
+      <c r="K20" s="71" t="s">
         <v>35</v>
       </c>
     </row>
@@ -1408,15 +1455,25 @@
       <c r="B21" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C21" s="60"/>
-      <c r="D21" s="61"/>
-      <c r="E21" s="61"/>
-      <c r="F21" s="75"/>
-      <c r="G21" s="75"/>
-      <c r="H21" s="75"/>
-      <c r="I21" s="75"/>
-      <c r="J21" s="75"/>
-      <c r="K21" s="67"/>
+      <c r="C21" s="64"/>
+      <c r="D21" s="65"/>
+      <c r="E21" s="65"/>
+      <c r="F21" s="11">
+        <v>0.36964094320000002</v>
+      </c>
+      <c r="G21" s="11">
+        <v>1.3397640000000001E-4</v>
+      </c>
+      <c r="H21" s="11">
+        <v>0.63594140759999995</v>
+      </c>
+      <c r="I21" s="11">
+        <v>0.85885026710000001</v>
+      </c>
+      <c r="J21" s="11">
+        <v>0.7749568309</v>
+      </c>
+      <c r="K21" s="71"/>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
@@ -1425,22 +1482,25 @@
       <c r="B22" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C22" s="60"/>
-      <c r="D22" s="61"/>
-      <c r="E22" s="61"/>
-      <c r="F22" s="75"/>
-      <c r="G22" s="75"/>
-      <c r="H22" s="75"/>
-      <c r="I22" s="75"/>
-      <c r="J22" s="75"/>
-      <c r="K22" s="67"/>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="F23" s="75"/>
-      <c r="G23" s="75"/>
-      <c r="H23" s="75"/>
-      <c r="I23" s="75"/>
-      <c r="J23" s="75"/>
+      <c r="C22" s="64"/>
+      <c r="D22" s="65"/>
+      <c r="E22" s="65"/>
+      <c r="F22" s="11">
+        <v>1.786352E-4</v>
+      </c>
+      <c r="G22" s="11">
+        <v>0.18283315459999999</v>
+      </c>
+      <c r="H22" s="11">
+        <v>4.60878885E-2</v>
+      </c>
+      <c r="I22" s="11">
+        <v>0.55591291340000004</v>
+      </c>
+      <c r="J22" s="11">
+        <v>0.35294220799999998</v>
+      </c>
+      <c r="K22" s="71"/>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
@@ -1449,20 +1509,30 @@
       <c r="B24" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C24" s="60" t="s">
+      <c r="C24" s="64" t="s">
         <v>46</v>
       </c>
-      <c r="D24" s="61" t="s">
+      <c r="D24" s="65" t="s">
         <v>21</v>
       </c>
-      <c r="E24" s="61" t="s">
+      <c r="E24" s="65" t="s">
         <v>32</v>
       </c>
-      <c r="F24" s="75"/>
-      <c r="G24" s="75"/>
-      <c r="H24" s="75"/>
-      <c r="I24" s="75"/>
-      <c r="J24" s="75"/>
+      <c r="F24" s="11">
+        <v>0.29124472569999998</v>
+      </c>
+      <c r="G24" s="11">
+        <v>0.21207805900000001</v>
+      </c>
+      <c r="H24" s="11">
+        <v>0.74541139239999998</v>
+      </c>
+      <c r="I24" s="11">
+        <v>0.84871145309999996</v>
+      </c>
+      <c r="J24" s="11">
+        <v>0.80021173410000002</v>
+      </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
@@ -1471,14 +1541,24 @@
       <c r="B25" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C25" s="60"/>
-      <c r="D25" s="61"/>
-      <c r="E25" s="61"/>
-      <c r="F25" s="75"/>
-      <c r="G25" s="75"/>
-      <c r="H25" s="75"/>
-      <c r="I25" s="75"/>
-      <c r="J25" s="75"/>
+      <c r="C25" s="64"/>
+      <c r="D25" s="65"/>
+      <c r="E25" s="65"/>
+      <c r="F25" s="11">
+        <v>2.2257384000000002E-2</v>
+      </c>
+      <c r="G25" s="11">
+        <v>2.6371309999999998E-4</v>
+      </c>
+      <c r="H25" s="11">
+        <v>0.36339662449999999</v>
+      </c>
+      <c r="I25" s="11">
+        <v>0.57537618469999996</v>
+      </c>
+      <c r="J25" s="11">
+        <v>0.63357712190000004</v>
+      </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
@@ -1487,21 +1567,24 @@
       <c r="B26" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C26" s="60"/>
-      <c r="D26" s="61"/>
-      <c r="E26" s="61"/>
-      <c r="F26" s="75"/>
-      <c r="G26" s="75"/>
-      <c r="H26" s="75"/>
-      <c r="I26" s="75"/>
-      <c r="J26" s="75"/>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="F27" s="75"/>
-      <c r="G27" s="75"/>
-      <c r="H27" s="75"/>
-      <c r="I27" s="75"/>
-      <c r="J27" s="75"/>
+      <c r="C26" s="64"/>
+      <c r="D26" s="65"/>
+      <c r="E26" s="65"/>
+      <c r="F26" s="11">
+        <v>3.9556960000000001E-4</v>
+      </c>
+      <c r="G26" s="11">
+        <v>2.6371309999999998E-4</v>
+      </c>
+      <c r="H26" s="11">
+        <v>1</v>
+      </c>
+      <c r="I26" s="11">
+        <v>0.79791006350000004</v>
+      </c>
+      <c r="J26" s="11">
+        <v>0.27747491489999998</v>
+      </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
@@ -1510,20 +1593,30 @@
       <c r="B28" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C28" s="60" t="s">
+      <c r="C28" s="64" t="s">
         <v>47</v>
       </c>
-      <c r="D28" s="61" t="s">
+      <c r="D28" s="65" t="s">
         <v>22</v>
       </c>
-      <c r="E28" s="61" t="s">
+      <c r="E28" s="65" t="s">
         <v>33</v>
       </c>
-      <c r="F28" s="75"/>
-      <c r="G28" s="75"/>
-      <c r="H28" s="75"/>
-      <c r="I28" s="75"/>
-      <c r="J28" s="75"/>
+      <c r="F28" s="11">
+        <v>0.35495752229999999</v>
+      </c>
+      <c r="G28" s="11">
+        <v>0.21803419730000001</v>
+      </c>
+      <c r="H28" s="11">
+        <v>0.44531670070000001</v>
+      </c>
+      <c r="I28" s="11">
+        <v>0.7989096738</v>
+      </c>
+      <c r="J28" s="11">
+        <v>0.60950750590000002</v>
+      </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
@@ -1532,14 +1625,24 @@
       <c r="B29" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C29" s="60"/>
-      <c r="D29" s="61"/>
-      <c r="E29" s="61"/>
-      <c r="F29" s="75"/>
-      <c r="G29" s="75"/>
-      <c r="H29" s="75"/>
-      <c r="I29" s="75"/>
-      <c r="J29" s="75"/>
+      <c r="C29" s="64"/>
+      <c r="D29" s="65"/>
+      <c r="E29" s="65"/>
+      <c r="F29" s="11">
+        <v>1.8442843300000001E-2</v>
+      </c>
+      <c r="G29" s="11">
+        <v>5.37692E-5</v>
+      </c>
+      <c r="H29" s="11">
+        <v>0.35874825249999998</v>
+      </c>
+      <c r="I29" s="11">
+        <v>0.59498168819999997</v>
+      </c>
+      <c r="J29" s="11">
+        <v>0.62220035299999998</v>
+      </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
@@ -1548,21 +1651,24 @@
       <c r="B30" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C30" s="60"/>
-      <c r="D30" s="61"/>
-      <c r="E30" s="61"/>
-      <c r="F30" s="75"/>
-      <c r="G30" s="75"/>
-      <c r="H30" s="75"/>
-      <c r="I30" s="75"/>
-      <c r="J30" s="75"/>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="F31" s="75"/>
-      <c r="G31" s="75"/>
-      <c r="H31" s="75"/>
-      <c r="I31" s="75"/>
-      <c r="J31" s="75"/>
+      <c r="C30" s="64"/>
+      <c r="D30" s="65"/>
+      <c r="E30" s="65"/>
+      <c r="F30" s="11">
+        <v>6.9899990000000004E-4</v>
+      </c>
+      <c r="G30" s="11">
+        <v>2.6884609999999997E-4</v>
+      </c>
+      <c r="H30" s="11">
+        <v>1</v>
+      </c>
+      <c r="I30" s="11">
+        <v>0.76702944120000005</v>
+      </c>
+      <c r="J30" s="11">
+        <v>0.27796758100000002</v>
+      </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
@@ -1571,20 +1677,30 @@
       <c r="B32" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C32" s="60" t="s">
+      <c r="C32" s="64" t="s">
         <v>48</v>
       </c>
-      <c r="D32" s="61" t="s">
+      <c r="D32" s="65" t="s">
         <v>23</v>
       </c>
-      <c r="E32" s="61" t="s">
+      <c r="E32" s="65" t="s">
         <v>29</v>
       </c>
-      <c r="F32" s="75"/>
-      <c r="G32" s="75"/>
-      <c r="H32" s="75"/>
-      <c r="I32" s="75"/>
-      <c r="J32" s="75"/>
+      <c r="F32" s="11">
+        <v>0.29222857140000003</v>
+      </c>
+      <c r="G32" s="11">
+        <v>6.5342857200000007E-2</v>
+      </c>
+      <c r="H32" s="11">
+        <v>0.52434285709999995</v>
+      </c>
+      <c r="I32" s="11">
+        <v>0.88386083839999996</v>
+      </c>
+      <c r="J32" s="11">
+        <v>0.51603915860000005</v>
+      </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
@@ -1593,14 +1709,24 @@
       <c r="B33" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C33" s="60"/>
-      <c r="D33" s="61"/>
-      <c r="E33" s="61"/>
-      <c r="F33" s="75"/>
-      <c r="G33" s="75"/>
-      <c r="H33" s="75"/>
-      <c r="I33" s="75"/>
-      <c r="J33" s="75"/>
+      <c r="C33" s="64"/>
+      <c r="D33" s="65"/>
+      <c r="E33" s="65"/>
+      <c r="F33" s="11">
+        <v>4.8571429999999999E-4</v>
+      </c>
+      <c r="G33" s="11">
+        <v>7.7142849999999995E-4</v>
+      </c>
+      <c r="H33" s="11">
+        <v>7.5257142900000004E-2</v>
+      </c>
+      <c r="I33" s="11">
+        <v>0.51078131569999996</v>
+      </c>
+      <c r="J33" s="11">
+        <v>0.56004145900000002</v>
+      </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
@@ -1609,21 +1735,24 @@
       <c r="B34" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C34" s="60"/>
-      <c r="D34" s="61"/>
-      <c r="E34" s="61"/>
-      <c r="F34" s="75"/>
-      <c r="G34" s="75"/>
-      <c r="H34" s="75"/>
-      <c r="I34" s="75"/>
-      <c r="J34" s="75"/>
-    </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="F35" s="75"/>
-      <c r="G35" s="75"/>
-      <c r="H35" s="75"/>
-      <c r="I35" s="75"/>
-      <c r="J35" s="75"/>
+      <c r="C34" s="64"/>
+      <c r="D34" s="65"/>
+      <c r="E34" s="65"/>
+      <c r="F34" s="11">
+        <v>8.5714299999999993E-5</v>
+      </c>
+      <c r="G34" s="11">
+        <v>2.857143E-4</v>
+      </c>
+      <c r="H34" s="11">
+        <v>1</v>
+      </c>
+      <c r="I34" s="11">
+        <v>0.7444025527</v>
+      </c>
+      <c r="J34" s="11">
+        <v>0.28967926030000002</v>
+      </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
@@ -1632,20 +1761,30 @@
       <c r="B36" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C36" s="60" t="s">
+      <c r="C36" s="64" t="s">
         <v>49</v>
       </c>
-      <c r="D36" s="61" t="s">
+      <c r="D36" s="65" t="s">
         <v>24</v>
       </c>
-      <c r="E36" s="61" t="s">
+      <c r="E36" s="65" t="s">
         <v>34</v>
       </c>
-      <c r="F36" s="75"/>
-      <c r="G36" s="75"/>
-      <c r="H36" s="75"/>
-      <c r="I36" s="75"/>
-      <c r="J36" s="75"/>
+      <c r="F36" s="11">
+        <v>0.2590513612</v>
+      </c>
+      <c r="G36" s="11">
+        <v>0.19550138319999999</v>
+      </c>
+      <c r="H36" s="11">
+        <v>0.49388556989999999</v>
+      </c>
+      <c r="I36" s="11">
+        <v>0.81622520009999999</v>
+      </c>
+      <c r="J36" s="11">
+        <v>0.68215240119999998</v>
+      </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
@@ -1654,14 +1793,24 @@
       <c r="B37" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C37" s="60"/>
-      <c r="D37" s="61"/>
-      <c r="E37" s="61"/>
-      <c r="F37" s="75"/>
-      <c r="G37" s="75"/>
-      <c r="H37" s="75"/>
-      <c r="I37" s="75"/>
-      <c r="J37" s="75"/>
+      <c r="C37" s="64"/>
+      <c r="D37" s="65"/>
+      <c r="E37" s="65"/>
+      <c r="F37" s="11">
+        <v>0.12567659680000001</v>
+      </c>
+      <c r="G37" s="11">
+        <v>8.0189299999999995E-5</v>
+      </c>
+      <c r="H37" s="11">
+        <v>0.55410769419999995</v>
+      </c>
+      <c r="I37" s="11">
+        <v>0.69175754229999997</v>
+      </c>
+      <c r="J37" s="11">
+        <v>0.83367986199999999</v>
+      </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
@@ -1670,43 +1819,39 @@
       <c r="B38" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C38" s="60"/>
-      <c r="D38" s="61"/>
-      <c r="E38" s="61"/>
-      <c r="F38" s="75"/>
-      <c r="G38" s="75"/>
-      <c r="H38" s="75"/>
-      <c r="I38" s="75"/>
-      <c r="J38" s="75"/>
-    </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="F39" s="75"/>
-      <c r="G39" s="75"/>
-      <c r="H39" s="75"/>
-      <c r="I39" s="75"/>
-      <c r="J39" s="75"/>
-    </row>
-    <row r="40" spans="1:11" s="80" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="77" t="s">
+      <c r="C38" s="64"/>
+      <c r="D38" s="65"/>
+      <c r="E38" s="65"/>
+      <c r="F38" s="11">
+        <v>5.4127739999999998E-4</v>
+      </c>
+      <c r="G38" s="11">
+        <v>2.0047310000000001E-4</v>
+      </c>
+      <c r="H38" s="11">
+        <v>1</v>
+      </c>
+      <c r="I38" s="11">
+        <v>0.83321648010000005</v>
+      </c>
+      <c r="J38" s="11">
+        <v>0.24805656309999999</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" s="59" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="66" t="s">
         <v>38</v>
       </c>
-      <c r="B40" s="77"/>
-      <c r="C40" s="77"/>
-      <c r="D40" s="77"/>
-      <c r="E40" s="78"/>
-      <c r="F40" s="79"/>
-      <c r="G40" s="79"/>
-      <c r="H40" s="79"/>
-      <c r="I40" s="79"/>
-      <c r="J40" s="79"/>
-      <c r="K40" s="78"/>
-    </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="F41" s="75"/>
-      <c r="G41" s="75"/>
-      <c r="H41" s="75"/>
-      <c r="I41" s="75"/>
-      <c r="J41" s="75"/>
+      <c r="B40" s="66"/>
+      <c r="C40" s="66"/>
+      <c r="D40" s="66"/>
+      <c r="E40" s="60"/>
+      <c r="F40" s="61"/>
+      <c r="G40" s="61"/>
+      <c r="H40" s="61"/>
+      <c r="I40" s="61"/>
+      <c r="J40" s="61"/>
+      <c r="K40" s="60"/>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
@@ -1715,21 +1860,31 @@
       <c r="B42" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C42" s="60" t="s">
+      <c r="C42" s="64" t="s">
         <v>50</v>
       </c>
-      <c r="D42" s="61" t="s">
+      <c r="D42" s="65" t="s">
         <v>25</v>
       </c>
-      <c r="E42" s="61" t="s">
+      <c r="E42" s="65" t="s">
         <v>27</v>
       </c>
-      <c r="F42" s="75"/>
-      <c r="G42" s="75"/>
-      <c r="H42" s="75"/>
-      <c r="I42" s="75"/>
-      <c r="J42" s="75"/>
-      <c r="K42" s="67" t="s">
+      <c r="F42" s="11">
+        <v>0.28531987060000003</v>
+      </c>
+      <c r="G42" s="11">
+        <v>0.20485919380000001</v>
+      </c>
+      <c r="H42" s="11">
+        <v>0.46154452950000002</v>
+      </c>
+      <c r="I42" s="11">
+        <v>0.74200403739999998</v>
+      </c>
+      <c r="J42" s="11">
+        <v>0.57024913060000004</v>
+      </c>
+      <c r="K42" s="71" t="s">
         <v>30</v>
       </c>
     </row>
@@ -1740,15 +1895,25 @@
       <c r="B43" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C43" s="60"/>
-      <c r="D43" s="61"/>
-      <c r="E43" s="61"/>
-      <c r="F43" s="75"/>
-      <c r="G43" s="75"/>
-      <c r="H43" s="75"/>
-      <c r="I43" s="75"/>
-      <c r="J43" s="75"/>
-      <c r="K43" s="67"/>
+      <c r="C43" s="64"/>
+      <c r="D43" s="65"/>
+      <c r="E43" s="65"/>
+      <c r="F43" s="11">
+        <v>0.15768715</v>
+      </c>
+      <c r="G43" s="11">
+        <v>3.9441499999999998E-5</v>
+      </c>
+      <c r="H43" s="11">
+        <v>0.52638636900000002</v>
+      </c>
+      <c r="I43" s="11">
+        <v>0.69545189539999996</v>
+      </c>
+      <c r="J43" s="11">
+        <v>0.7451035896</v>
+      </c>
+      <c r="K43" s="71"/>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
@@ -1757,22 +1922,25 @@
       <c r="B44" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C44" s="60"/>
-      <c r="D44" s="61"/>
-      <c r="E44" s="61"/>
-      <c r="F44" s="75"/>
-      <c r="G44" s="75"/>
-      <c r="H44" s="75"/>
-      <c r="I44" s="75"/>
-      <c r="J44" s="75"/>
-      <c r="K44" s="67"/>
-    </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="F45" s="75"/>
-      <c r="G45" s="75"/>
-      <c r="H45" s="75"/>
-      <c r="I45" s="75"/>
-      <c r="J45" s="75"/>
+      <c r="C44" s="64"/>
+      <c r="D44" s="65"/>
+      <c r="E44" s="65"/>
+      <c r="F44" s="11">
+        <v>1.5776599999999999E-4</v>
+      </c>
+      <c r="G44" s="11">
+        <v>3.9441509999999999E-4</v>
+      </c>
+      <c r="H44" s="11">
+        <v>1</v>
+      </c>
+      <c r="I44" s="11">
+        <v>0.76069328420000004</v>
+      </c>
+      <c r="J44" s="11">
+        <v>0.35300280709999998</v>
+      </c>
+      <c r="K44" s="71"/>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
@@ -1781,21 +1949,31 @@
       <c r="B46" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C46" s="60" t="s">
+      <c r="C46" s="64" t="s">
         <v>51</v>
       </c>
-      <c r="D46" s="61" t="s">
+      <c r="D46" s="65" t="s">
         <v>26</v>
       </c>
-      <c r="E46" s="61" t="s">
+      <c r="E46" s="65" t="s">
         <v>28</v>
       </c>
-      <c r="F46" s="75"/>
-      <c r="G46" s="75"/>
-      <c r="H46" s="75"/>
-      <c r="I46" s="75"/>
-      <c r="J46" s="75"/>
-      <c r="K46" s="67" t="s">
+      <c r="F46" s="11">
+        <v>0.35679343540000003</v>
+      </c>
+      <c r="G46" s="11">
+        <v>1.6174846E-3</v>
+      </c>
+      <c r="H46" s="11">
+        <v>0.69543948239999998</v>
+      </c>
+      <c r="I46" s="11">
+        <v>0.76689637619999995</v>
+      </c>
+      <c r="J46" s="11">
+        <v>0.47753796059999998</v>
+      </c>
+      <c r="K46" s="71" t="s">
         <v>31</v>
       </c>
     </row>
@@ -1806,15 +1984,25 @@
       <c r="B47" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C47" s="60"/>
-      <c r="D47" s="61"/>
-      <c r="E47" s="61"/>
-      <c r="F47" s="75"/>
-      <c r="G47" s="75"/>
-      <c r="H47" s="75"/>
-      <c r="I47" s="75"/>
-      <c r="J47" s="75"/>
-      <c r="K47" s="67"/>
+      <c r="C47" s="64"/>
+      <c r="D47" s="65"/>
+      <c r="E47" s="65"/>
+      <c r="F47" s="11">
+        <v>0.28846457310000001</v>
+      </c>
+      <c r="G47" s="11">
+        <v>3.9450850000000002E-4</v>
+      </c>
+      <c r="H47" s="11">
+        <v>0.62947767080000006</v>
+      </c>
+      <c r="I47" s="11">
+        <v>0.73420197409999999</v>
+      </c>
+      <c r="J47" s="11">
+        <v>0.69566912999999997</v>
+      </c>
+      <c r="K47" s="71"/>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
@@ -1823,22 +2011,25 @@
       <c r="B48" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C48" s="60"/>
-      <c r="D48" s="61"/>
-      <c r="E48" s="61"/>
-      <c r="F48" s="75"/>
-      <c r="G48" s="75"/>
-      <c r="H48" s="75"/>
-      <c r="I48" s="75"/>
-      <c r="J48" s="75"/>
-      <c r="K48" s="67"/>
-    </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="F49" s="75"/>
-      <c r="G49" s="75"/>
-      <c r="H49" s="75"/>
-      <c r="I49" s="75"/>
-      <c r="J49" s="75"/>
+      <c r="C48" s="64"/>
+      <c r="D48" s="65"/>
+      <c r="E48" s="65"/>
+      <c r="F48" s="11">
+        <v>2.7615590000000002E-4</v>
+      </c>
+      <c r="G48" s="11">
+        <v>5.2075113999999999E-3</v>
+      </c>
+      <c r="H48" s="11">
+        <v>0.59902161909999996</v>
+      </c>
+      <c r="I48" s="11">
+        <v>0.69778750060000005</v>
+      </c>
+      <c r="J48" s="11">
+        <v>0.40179085320000002</v>
+      </c>
+      <c r="K48" s="71"/>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
@@ -1847,20 +2038,30 @@
       <c r="B50" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C50" s="60" t="s">
+      <c r="C50" s="64" t="s">
         <v>52</v>
       </c>
-      <c r="D50" s="61" t="s">
+      <c r="D50" s="65" t="s">
         <v>39</v>
       </c>
-      <c r="E50" s="61" t="s">
+      <c r="E50" s="65" t="s">
         <v>29</v>
       </c>
-      <c r="F50" s="75"/>
-      <c r="G50" s="75"/>
-      <c r="H50" s="75"/>
-      <c r="I50" s="75"/>
-      <c r="J50" s="75"/>
+      <c r="F50" s="11">
+        <v>0.2336330221</v>
+      </c>
+      <c r="G50" s="11">
+        <v>0.14819690050000001</v>
+      </c>
+      <c r="H50" s="11">
+        <v>0.66992847209999995</v>
+      </c>
+      <c r="I50" s="11">
+        <v>0.84746806279999998</v>
+      </c>
+      <c r="J50" s="11">
+        <v>0.67688287540000003</v>
+      </c>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A51" s="1" t="s">
@@ -1869,14 +2070,24 @@
       <c r="B51" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C51" s="60"/>
-      <c r="D51" s="61"/>
-      <c r="E51" s="61"/>
-      <c r="F51" s="75"/>
-      <c r="G51" s="75"/>
-      <c r="H51" s="75"/>
-      <c r="I51" s="75"/>
-      <c r="J51" s="75"/>
+      <c r="C51" s="64"/>
+      <c r="D51" s="65"/>
+      <c r="E51" s="65"/>
+      <c r="F51" s="11">
+        <v>3.5391416699999997E-2</v>
+      </c>
+      <c r="G51" s="11">
+        <v>2.4836090000000002E-4</v>
+      </c>
+      <c r="H51" s="11">
+        <v>0.54530101330000003</v>
+      </c>
+      <c r="I51" s="11">
+        <v>0.70820905810000001</v>
+      </c>
+      <c r="J51" s="11">
+        <v>0.77551452759999995</v>
+      </c>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
@@ -1885,72 +2096,82 @@
       <c r="B52" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C52" s="60"/>
-      <c r="D52" s="61"/>
-      <c r="E52" s="61"/>
-      <c r="F52" s="75"/>
-      <c r="G52" s="75"/>
-      <c r="H52" s="75"/>
-      <c r="I52" s="75"/>
-      <c r="J52" s="75"/>
+      <c r="C52" s="64"/>
+      <c r="D52" s="65"/>
+      <c r="E52" s="65"/>
+      <c r="F52" s="11">
+        <v>9.9344299999999997E-5</v>
+      </c>
+      <c r="G52" s="11">
+        <v>1.4901650000000001E-4</v>
+      </c>
+      <c r="H52" s="11">
+        <v>8.3945957000000002E-3</v>
+      </c>
+      <c r="I52" s="11">
+        <v>0.1434131324</v>
+      </c>
+      <c r="J52" s="11">
+        <v>0.69463278129999995</v>
+      </c>
     </row>
     <row r="55" spans="1:11" s="42" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="59" t="s">
-        <v>60</v>
-      </c>
-      <c r="B55" s="59"/>
-      <c r="C55" s="59"/>
-      <c r="D55" s="59"/>
+      <c r="A55" s="63" t="s">
+        <v>59</v>
+      </c>
+      <c r="B55" s="63"/>
+      <c r="C55" s="63"/>
+      <c r="D55" s="63"/>
       <c r="E55" s="39"/>
       <c r="F55" s="40">
         <f>MAX(F2:F52)</f>
-        <v>0</v>
+        <v>0.39523043940000002</v>
       </c>
       <c r="G55" s="40">
         <f>MAX(G2:G52)</f>
-        <v>0</v>
+        <v>0.21803419730000001</v>
       </c>
       <c r="H55" s="40">
         <f>MAX(H2:H52)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I55" s="40">
         <f>MAX(I2:I52)</f>
-        <v>0</v>
+        <v>0.88386083839999996</v>
       </c>
       <c r="J55" s="40">
         <f>MAX(J2:J52)</f>
-        <v>0</v>
+        <v>0.83367986199999999</v>
       </c>
       <c r="K55" s="41"/>
     </row>
     <row r="56" spans="1:11" s="46" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="65" t="s">
-        <v>61</v>
-      </c>
-      <c r="B56" s="65"/>
-      <c r="C56" s="65"/>
-      <c r="D56" s="65"/>
+      <c r="A56" s="69" t="s">
+        <v>60</v>
+      </c>
+      <c r="B56" s="69"/>
+      <c r="C56" s="69"/>
+      <c r="D56" s="69"/>
       <c r="E56" s="43"/>
-      <c r="F56" s="44" t="e">
+      <c r="F56" s="44">
         <f>AVERAGE(F2:F52)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G56" s="44" t="e">
+        <v>0.11521239868787879</v>
+      </c>
+      <c r="G56" s="44">
         <f>AVERAGE(G2:G52)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H56" s="44" t="e">
+        <v>4.0409736993939391E-2</v>
+      </c>
+      <c r="H56" s="44">
         <f>AVERAGE(H2:H52)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I56" s="44" t="e">
+        <v>0.55629249514242429</v>
+      </c>
+      <c r="I56" s="44">
         <f>AVERAGE(I2:I52)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="J56" s="44" t="e">
+        <v>0.67128798901212117</v>
+      </c>
+      <c r="J56" s="44">
         <f>AVERAGE(J2:J52)</f>
-        <v>#DIV/0!</v>
+        <v>0.55575878672727275</v>
       </c>
       <c r="K56" s="45"/>
     </row>
@@ -2070,21 +2291,20 @@
       <c r="B2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="64" t="s">
+      <c r="C2" s="68" t="s">
         <v>41</v>
       </c>
-      <c r="D2" s="63" t="s">
+      <c r="D2" s="67" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="63" t="s">
+      <c r="E2" s="67" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="75"/>
-      <c r="G2" s="75"/>
-      <c r="H2" s="75"/>
-      <c r="I2" s="75"/>
-      <c r="J2" s="75"/>
-      <c r="K2" s="66" t="s">
+      <c r="G2" s="11"/>
+      <c r="H2" s="11"/>
+      <c r="I2" s="11"/>
+      <c r="J2" s="11"/>
+      <c r="K2" s="70" t="s">
         <v>15</v>
       </c>
     </row>
@@ -2095,15 +2315,14 @@
       <c r="B3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="60"/>
-      <c r="D3" s="61"/>
-      <c r="E3" s="61"/>
-      <c r="F3" s="75"/>
-      <c r="G3" s="75"/>
-      <c r="H3" s="75"/>
-      <c r="I3" s="75"/>
-      <c r="J3" s="75"/>
-      <c r="K3" s="67"/>
+      <c r="C3" s="64"/>
+      <c r="D3" s="65"/>
+      <c r="E3" s="65"/>
+      <c r="G3" s="11"/>
+      <c r="H3" s="11"/>
+      <c r="I3" s="11"/>
+      <c r="J3" s="11"/>
+      <c r="K3" s="71"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
@@ -2112,22 +2331,20 @@
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="60"/>
-      <c r="D4" s="61"/>
-      <c r="E4" s="61"/>
-      <c r="F4" s="75"/>
-      <c r="G4" s="75"/>
-      <c r="H4" s="75"/>
-      <c r="I4" s="75"/>
-      <c r="J4" s="75"/>
-      <c r="K4" s="67"/>
+      <c r="C4" s="64"/>
+      <c r="D4" s="65"/>
+      <c r="E4" s="65"/>
+      <c r="G4" s="11"/>
+      <c r="H4" s="11"/>
+      <c r="I4" s="11"/>
+      <c r="J4" s="11"/>
+      <c r="K4" s="71"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="F5" s="75"/>
-      <c r="G5" s="75"/>
-      <c r="H5" s="75"/>
-      <c r="I5" s="75"/>
-      <c r="J5" s="75"/>
+      <c r="G5" s="11"/>
+      <c r="H5" s="11"/>
+      <c r="I5" s="11"/>
+      <c r="J5" s="11"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
@@ -2136,21 +2353,20 @@
       <c r="B6" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="60" t="s">
+      <c r="C6" s="64" t="s">
         <v>42</v>
       </c>
-      <c r="D6" s="61" t="s">
+      <c r="D6" s="65" t="s">
         <v>10</v>
       </c>
-      <c r="E6" s="61" t="s">
+      <c r="E6" s="65" t="s">
         <v>13</v>
       </c>
-      <c r="F6" s="75"/>
-      <c r="G6" s="75"/>
-      <c r="H6" s="75"/>
-      <c r="I6" s="75"/>
-      <c r="J6" s="75"/>
-      <c r="K6" s="67" t="s">
+      <c r="G6" s="11"/>
+      <c r="H6" s="11"/>
+      <c r="I6" s="11"/>
+      <c r="J6" s="11"/>
+      <c r="K6" s="71" t="s">
         <v>16</v>
       </c>
     </row>
@@ -2161,15 +2377,14 @@
       <c r="B7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="60"/>
-      <c r="D7" s="61"/>
-      <c r="E7" s="61"/>
-      <c r="F7" s="75"/>
-      <c r="G7" s="75"/>
-      <c r="H7" s="75"/>
-      <c r="I7" s="75"/>
-      <c r="J7" s="75"/>
-      <c r="K7" s="67"/>
+      <c r="C7" s="64"/>
+      <c r="D7" s="65"/>
+      <c r="E7" s="65"/>
+      <c r="G7" s="11"/>
+      <c r="H7" s="11"/>
+      <c r="I7" s="11"/>
+      <c r="J7" s="11"/>
+      <c r="K7" s="71"/>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
@@ -2178,44 +2393,41 @@
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="60"/>
-      <c r="D8" s="61"/>
-      <c r="E8" s="61"/>
-      <c r="F8" s="75"/>
-      <c r="G8" s="75"/>
-      <c r="H8" s="75"/>
-      <c r="I8" s="75"/>
-      <c r="J8" s="75"/>
-      <c r="K8" s="67"/>
+      <c r="C8" s="64"/>
+      <c r="D8" s="65"/>
+      <c r="E8" s="65"/>
+      <c r="G8" s="11"/>
+      <c r="H8" s="11"/>
+      <c r="I8" s="11"/>
+      <c r="J8" s="11"/>
+      <c r="K8" s="71"/>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="F9" s="75"/>
-      <c r="G9" s="75"/>
-      <c r="H9" s="75"/>
-      <c r="I9" s="75"/>
-      <c r="J9" s="75"/>
-    </row>
-    <row r="10" spans="1:12" s="80" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="77" t="s">
+      <c r="G9" s="11"/>
+      <c r="H9" s="11"/>
+      <c r="I9" s="11"/>
+      <c r="J9" s="11"/>
+    </row>
+    <row r="10" spans="1:12" s="59" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="66" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="77"/>
-      <c r="C10" s="77"/>
-      <c r="D10" s="77"/>
-      <c r="E10" s="78"/>
-      <c r="F10" s="79"/>
-      <c r="G10" s="79"/>
-      <c r="H10" s="79"/>
-      <c r="I10" s="79"/>
-      <c r="J10" s="79"/>
-      <c r="K10" s="78"/>
+      <c r="B10" s="66"/>
+      <c r="C10" s="66"/>
+      <c r="D10" s="66"/>
+      <c r="E10" s="60"/>
+      <c r="F10" s="61"/>
+      <c r="G10" s="61"/>
+      <c r="H10" s="61"/>
+      <c r="I10" s="61"/>
+      <c r="J10" s="61"/>
+      <c r="K10" s="60"/>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="F11" s="75"/>
-      <c r="G11" s="75"/>
-      <c r="H11" s="75"/>
-      <c r="I11" s="75"/>
-      <c r="J11" s="75"/>
+      <c r="G11" s="11"/>
+      <c r="H11" s="11"/>
+      <c r="I11" s="11"/>
+      <c r="J11" s="11"/>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
@@ -2224,21 +2436,20 @@
       <c r="B12" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C12" s="60" t="s">
+      <c r="C12" s="64" t="s">
         <v>43</v>
       </c>
-      <c r="D12" s="61" t="s">
+      <c r="D12" s="65" t="s">
         <v>11</v>
       </c>
-      <c r="E12" s="61" t="s">
+      <c r="E12" s="65" t="s">
         <v>17</v>
       </c>
-      <c r="F12" s="75"/>
-      <c r="G12" s="75"/>
-      <c r="H12" s="75"/>
-      <c r="I12" s="75"/>
-      <c r="J12" s="75"/>
-      <c r="K12" s="67" t="s">
+      <c r="G12" s="11"/>
+      <c r="H12" s="11"/>
+      <c r="I12" s="11"/>
+      <c r="J12" s="11"/>
+      <c r="K12" s="71" t="s">
         <v>18</v>
       </c>
     </row>
@@ -2249,15 +2460,14 @@
       <c r="B13" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C13" s="60"/>
-      <c r="D13" s="61"/>
-      <c r="E13" s="61"/>
-      <c r="F13" s="75"/>
-      <c r="G13" s="75"/>
-      <c r="H13" s="75"/>
-      <c r="I13" s="75"/>
-      <c r="J13" s="75"/>
-      <c r="K13" s="67"/>
+      <c r="C13" s="64"/>
+      <c r="D13" s="65"/>
+      <c r="E13" s="65"/>
+      <c r="G13" s="11"/>
+      <c r="H13" s="11"/>
+      <c r="I13" s="11"/>
+      <c r="J13" s="11"/>
+      <c r="K13" s="71"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
@@ -2266,22 +2476,20 @@
       <c r="B14" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C14" s="60"/>
-      <c r="D14" s="61"/>
-      <c r="E14" s="61"/>
-      <c r="F14" s="75"/>
-      <c r="G14" s="75"/>
-      <c r="H14" s="75"/>
-      <c r="I14" s="75"/>
-      <c r="J14" s="75"/>
-      <c r="K14" s="67"/>
+      <c r="C14" s="64"/>
+      <c r="D14" s="65"/>
+      <c r="E14" s="65"/>
+      <c r="G14" s="11"/>
+      <c r="H14" s="11"/>
+      <c r="I14" s="11"/>
+      <c r="J14" s="11"/>
+      <c r="K14" s="71"/>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="F15" s="75"/>
-      <c r="G15" s="75"/>
-      <c r="H15" s="75"/>
-      <c r="I15" s="75"/>
-      <c r="J15" s="75"/>
+      <c r="G15" s="11"/>
+      <c r="H15" s="11"/>
+      <c r="I15" s="11"/>
+      <c r="J15" s="11"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
@@ -2290,21 +2498,20 @@
       <c r="B16" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C16" s="60" t="s">
+      <c r="C16" s="64" t="s">
         <v>44</v>
       </c>
-      <c r="D16" s="61" t="s">
+      <c r="D16" s="65" t="s">
         <v>19</v>
       </c>
-      <c r="E16" s="61" t="s">
+      <c r="E16" s="65" t="s">
         <v>27</v>
       </c>
-      <c r="F16" s="75"/>
-      <c r="G16" s="75"/>
-      <c r="H16" s="75"/>
-      <c r="I16" s="75"/>
-      <c r="J16" s="75"/>
-      <c r="K16" s="67" t="s">
+      <c r="G16" s="11"/>
+      <c r="H16" s="11"/>
+      <c r="I16" s="11"/>
+      <c r="J16" s="11"/>
+      <c r="K16" s="71" t="s">
         <v>36</v>
       </c>
     </row>
@@ -2315,15 +2522,14 @@
       <c r="B17" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C17" s="60"/>
-      <c r="D17" s="61"/>
-      <c r="E17" s="61"/>
-      <c r="F17" s="75"/>
-      <c r="G17" s="75"/>
-      <c r="H17" s="75"/>
-      <c r="I17" s="75"/>
-      <c r="J17" s="75"/>
-      <c r="K17" s="67"/>
+      <c r="C17" s="64"/>
+      <c r="D17" s="65"/>
+      <c r="E17" s="65"/>
+      <c r="G17" s="11"/>
+      <c r="H17" s="11"/>
+      <c r="I17" s="11"/>
+      <c r="J17" s="11"/>
+      <c r="K17" s="71"/>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
@@ -2332,22 +2538,20 @@
       <c r="B18" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C18" s="60"/>
-      <c r="D18" s="61"/>
-      <c r="E18" s="61"/>
-      <c r="F18" s="75"/>
-      <c r="G18" s="75"/>
-      <c r="H18" s="75"/>
-      <c r="I18" s="75"/>
-      <c r="J18" s="75"/>
-      <c r="K18" s="67"/>
+      <c r="C18" s="64"/>
+      <c r="D18" s="65"/>
+      <c r="E18" s="65"/>
+      <c r="G18" s="11"/>
+      <c r="H18" s="11"/>
+      <c r="I18" s="11"/>
+      <c r="J18" s="11"/>
+      <c r="K18" s="71"/>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="F19" s="75"/>
-      <c r="G19" s="75"/>
-      <c r="H19" s="75"/>
-      <c r="I19" s="75"/>
-      <c r="J19" s="75"/>
+      <c r="G19" s="11"/>
+      <c r="H19" s="11"/>
+      <c r="I19" s="11"/>
+      <c r="J19" s="11"/>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
@@ -2356,21 +2560,20 @@
       <c r="B20" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C20" s="60" t="s">
+      <c r="C20" s="64" t="s">
         <v>45</v>
       </c>
-      <c r="D20" s="61" t="s">
+      <c r="D20" s="65" t="s">
         <v>20</v>
       </c>
-      <c r="E20" s="61" t="s">
+      <c r="E20" s="65" t="s">
         <v>28</v>
       </c>
-      <c r="F20" s="75"/>
-      <c r="G20" s="75"/>
-      <c r="H20" s="75"/>
-      <c r="I20" s="75"/>
-      <c r="J20" s="75"/>
-      <c r="K20" s="67" t="s">
+      <c r="G20" s="11"/>
+      <c r="H20" s="11"/>
+      <c r="I20" s="11"/>
+      <c r="J20" s="11"/>
+      <c r="K20" s="71" t="s">
         <v>35</v>
       </c>
     </row>
@@ -2381,15 +2584,14 @@
       <c r="B21" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C21" s="60"/>
-      <c r="D21" s="61"/>
-      <c r="E21" s="61"/>
-      <c r="F21" s="75"/>
-      <c r="G21" s="75"/>
-      <c r="H21" s="75"/>
-      <c r="I21" s="75"/>
-      <c r="J21" s="75"/>
-      <c r="K21" s="67"/>
+      <c r="C21" s="64"/>
+      <c r="D21" s="65"/>
+      <c r="E21" s="65"/>
+      <c r="G21" s="11"/>
+      <c r="H21" s="11"/>
+      <c r="I21" s="11"/>
+      <c r="J21" s="11"/>
+      <c r="K21" s="71"/>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
@@ -2398,22 +2600,20 @@
       <c r="B22" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C22" s="60"/>
-      <c r="D22" s="61"/>
-      <c r="E22" s="61"/>
-      <c r="F22" s="75"/>
-      <c r="G22" s="75"/>
-      <c r="H22" s="75"/>
-      <c r="I22" s="75"/>
-      <c r="J22" s="75"/>
-      <c r="K22" s="67"/>
+      <c r="C22" s="64"/>
+      <c r="D22" s="65"/>
+      <c r="E22" s="65"/>
+      <c r="G22" s="11"/>
+      <c r="H22" s="11"/>
+      <c r="I22" s="11"/>
+      <c r="J22" s="11"/>
+      <c r="K22" s="71"/>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="F23" s="75"/>
-      <c r="G23" s="75"/>
-      <c r="H23" s="75"/>
-      <c r="I23" s="75"/>
-      <c r="J23" s="75"/>
+      <c r="G23" s="11"/>
+      <c r="H23" s="11"/>
+      <c r="I23" s="11"/>
+      <c r="J23" s="11"/>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
@@ -2422,20 +2622,19 @@
       <c r="B24" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C24" s="60" t="s">
+      <c r="C24" s="64" t="s">
         <v>46</v>
       </c>
-      <c r="D24" s="61" t="s">
+      <c r="D24" s="65" t="s">
         <v>21</v>
       </c>
-      <c r="E24" s="61" t="s">
+      <c r="E24" s="65" t="s">
         <v>32</v>
       </c>
-      <c r="F24" s="75"/>
-      <c r="G24" s="75"/>
-      <c r="H24" s="75"/>
-      <c r="I24" s="75"/>
-      <c r="J24" s="75"/>
+      <c r="G24" s="11"/>
+      <c r="H24" s="11"/>
+      <c r="I24" s="11"/>
+      <c r="J24" s="11"/>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
@@ -2444,14 +2643,13 @@
       <c r="B25" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C25" s="60"/>
-      <c r="D25" s="61"/>
-      <c r="E25" s="61"/>
-      <c r="F25" s="75"/>
-      <c r="G25" s="75"/>
-      <c r="H25" s="75"/>
-      <c r="I25" s="75"/>
-      <c r="J25" s="75"/>
+      <c r="C25" s="64"/>
+      <c r="D25" s="65"/>
+      <c r="E25" s="65"/>
+      <c r="G25" s="11"/>
+      <c r="H25" s="11"/>
+      <c r="I25" s="11"/>
+      <c r="J25" s="11"/>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
@@ -2460,21 +2658,19 @@
       <c r="B26" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C26" s="60"/>
-      <c r="D26" s="61"/>
-      <c r="E26" s="61"/>
-      <c r="F26" s="75"/>
-      <c r="G26" s="75"/>
-      <c r="H26" s="75"/>
-      <c r="I26" s="75"/>
-      <c r="J26" s="75"/>
+      <c r="C26" s="64"/>
+      <c r="D26" s="65"/>
+      <c r="E26" s="65"/>
+      <c r="G26" s="11"/>
+      <c r="H26" s="11"/>
+      <c r="I26" s="11"/>
+      <c r="J26" s="11"/>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="F27" s="75"/>
-      <c r="G27" s="75"/>
-      <c r="H27" s="75"/>
-      <c r="I27" s="75"/>
-      <c r="J27" s="75"/>
+      <c r="G27" s="11"/>
+      <c r="H27" s="11"/>
+      <c r="I27" s="11"/>
+      <c r="J27" s="11"/>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
@@ -2483,20 +2679,19 @@
       <c r="B28" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C28" s="60" t="s">
+      <c r="C28" s="64" t="s">
         <v>47</v>
       </c>
-      <c r="D28" s="61" t="s">
+      <c r="D28" s="65" t="s">
         <v>22</v>
       </c>
-      <c r="E28" s="61" t="s">
+      <c r="E28" s="65" t="s">
         <v>33</v>
       </c>
-      <c r="F28" s="75"/>
-      <c r="G28" s="75"/>
-      <c r="H28" s="75"/>
-      <c r="I28" s="75"/>
-      <c r="J28" s="75"/>
+      <c r="G28" s="11"/>
+      <c r="H28" s="11"/>
+      <c r="I28" s="11"/>
+      <c r="J28" s="11"/>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
@@ -2505,14 +2700,13 @@
       <c r="B29" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C29" s="60"/>
-      <c r="D29" s="61"/>
-      <c r="E29" s="61"/>
-      <c r="F29" s="75"/>
-      <c r="G29" s="75"/>
-      <c r="H29" s="75"/>
-      <c r="I29" s="75"/>
-      <c r="J29" s="75"/>
+      <c r="C29" s="64"/>
+      <c r="D29" s="65"/>
+      <c r="E29" s="65"/>
+      <c r="G29" s="11"/>
+      <c r="H29" s="11"/>
+      <c r="I29" s="11"/>
+      <c r="J29" s="11"/>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
@@ -2521,21 +2715,19 @@
       <c r="B30" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C30" s="60"/>
-      <c r="D30" s="61"/>
-      <c r="E30" s="61"/>
-      <c r="F30" s="75"/>
-      <c r="G30" s="75"/>
-      <c r="H30" s="75"/>
-      <c r="I30" s="75"/>
-      <c r="J30" s="75"/>
+      <c r="C30" s="64"/>
+      <c r="D30" s="65"/>
+      <c r="E30" s="65"/>
+      <c r="G30" s="11"/>
+      <c r="H30" s="11"/>
+      <c r="I30" s="11"/>
+      <c r="J30" s="11"/>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="F31" s="75"/>
-      <c r="G31" s="75"/>
-      <c r="H31" s="75"/>
-      <c r="I31" s="75"/>
-      <c r="J31" s="75"/>
+      <c r="G31" s="11"/>
+      <c r="H31" s="11"/>
+      <c r="I31" s="11"/>
+      <c r="J31" s="11"/>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
@@ -2544,20 +2736,19 @@
       <c r="B32" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C32" s="60" t="s">
+      <c r="C32" s="64" t="s">
         <v>48</v>
       </c>
-      <c r="D32" s="61" t="s">
+      <c r="D32" s="65" t="s">
         <v>23</v>
       </c>
-      <c r="E32" s="61" t="s">
+      <c r="E32" s="65" t="s">
         <v>29</v>
       </c>
-      <c r="F32" s="75"/>
-      <c r="G32" s="75"/>
-      <c r="H32" s="75"/>
-      <c r="I32" s="75"/>
-      <c r="J32" s="75"/>
+      <c r="G32" s="11"/>
+      <c r="H32" s="11"/>
+      <c r="I32" s="11"/>
+      <c r="J32" s="11"/>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
@@ -2566,14 +2757,13 @@
       <c r="B33" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C33" s="60"/>
-      <c r="D33" s="61"/>
-      <c r="E33" s="61"/>
-      <c r="F33" s="75"/>
-      <c r="G33" s="75"/>
-      <c r="H33" s="75"/>
-      <c r="I33" s="75"/>
-      <c r="J33" s="75"/>
+      <c r="C33" s="64"/>
+      <c r="D33" s="65"/>
+      <c r="E33" s="65"/>
+      <c r="G33" s="11"/>
+      <c r="H33" s="11"/>
+      <c r="I33" s="11"/>
+      <c r="J33" s="11"/>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
@@ -2582,21 +2772,19 @@
       <c r="B34" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C34" s="60"/>
-      <c r="D34" s="61"/>
-      <c r="E34" s="61"/>
-      <c r="F34" s="75"/>
-      <c r="G34" s="75"/>
-      <c r="H34" s="75"/>
-      <c r="I34" s="75"/>
-      <c r="J34" s="75"/>
+      <c r="C34" s="64"/>
+      <c r="D34" s="65"/>
+      <c r="E34" s="65"/>
+      <c r="G34" s="11"/>
+      <c r="H34" s="11"/>
+      <c r="I34" s="11"/>
+      <c r="J34" s="11"/>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="F35" s="75"/>
-      <c r="G35" s="75"/>
-      <c r="H35" s="75"/>
-      <c r="I35" s="75"/>
-      <c r="J35" s="75"/>
+      <c r="G35" s="11"/>
+      <c r="H35" s="11"/>
+      <c r="I35" s="11"/>
+      <c r="J35" s="11"/>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
@@ -2605,20 +2793,19 @@
       <c r="B36" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C36" s="60" t="s">
+      <c r="C36" s="64" t="s">
         <v>49</v>
       </c>
-      <c r="D36" s="61" t="s">
+      <c r="D36" s="65" t="s">
         <v>24</v>
       </c>
-      <c r="E36" s="61" t="s">
+      <c r="E36" s="65" t="s">
         <v>34</v>
       </c>
-      <c r="F36" s="75"/>
-      <c r="G36" s="75"/>
-      <c r="H36" s="75"/>
-      <c r="I36" s="75"/>
-      <c r="J36" s="75"/>
+      <c r="G36" s="11"/>
+      <c r="H36" s="11"/>
+      <c r="I36" s="11"/>
+      <c r="J36" s="11"/>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
@@ -2627,14 +2814,13 @@
       <c r="B37" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C37" s="60"/>
-      <c r="D37" s="61"/>
-      <c r="E37" s="61"/>
-      <c r="F37" s="75"/>
-      <c r="G37" s="75"/>
-      <c r="H37" s="75"/>
-      <c r="I37" s="75"/>
-      <c r="J37" s="75"/>
+      <c r="C37" s="64"/>
+      <c r="D37" s="65"/>
+      <c r="E37" s="65"/>
+      <c r="G37" s="11"/>
+      <c r="H37" s="11"/>
+      <c r="I37" s="11"/>
+      <c r="J37" s="11"/>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
@@ -2643,43 +2829,40 @@
       <c r="B38" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C38" s="60"/>
-      <c r="D38" s="61"/>
-      <c r="E38" s="61"/>
-      <c r="F38" s="75"/>
-      <c r="G38" s="75"/>
-      <c r="H38" s="75"/>
-      <c r="I38" s="75"/>
-      <c r="J38" s="75"/>
+      <c r="C38" s="64"/>
+      <c r="D38" s="65"/>
+      <c r="E38" s="65"/>
+      <c r="G38" s="11"/>
+      <c r="H38" s="11"/>
+      <c r="I38" s="11"/>
+      <c r="J38" s="11"/>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="F39" s="75"/>
-      <c r="G39" s="75"/>
-      <c r="H39" s="75"/>
-      <c r="I39" s="75"/>
-      <c r="J39" s="75"/>
-    </row>
-    <row r="40" spans="1:11" s="80" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="77" t="s">
+      <c r="G39" s="11"/>
+      <c r="H39" s="11"/>
+      <c r="I39" s="11"/>
+      <c r="J39" s="11"/>
+    </row>
+    <row r="40" spans="1:11" s="59" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="66" t="s">
         <v>38</v>
       </c>
-      <c r="B40" s="77"/>
-      <c r="C40" s="77"/>
-      <c r="D40" s="77"/>
-      <c r="E40" s="78"/>
-      <c r="F40" s="79"/>
-      <c r="G40" s="79"/>
-      <c r="H40" s="79"/>
-      <c r="I40" s="79"/>
-      <c r="J40" s="79"/>
-      <c r="K40" s="78"/>
+      <c r="B40" s="66"/>
+      <c r="C40" s="66"/>
+      <c r="D40" s="66"/>
+      <c r="E40" s="60"/>
+      <c r="F40" s="61"/>
+      <c r="G40" s="61"/>
+      <c r="H40" s="61"/>
+      <c r="I40" s="61"/>
+      <c r="J40" s="61"/>
+      <c r="K40" s="60"/>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="F41" s="75"/>
-      <c r="G41" s="75"/>
-      <c r="H41" s="75"/>
-      <c r="I41" s="75"/>
-      <c r="J41" s="75"/>
+      <c r="G41" s="11"/>
+      <c r="H41" s="11"/>
+      <c r="I41" s="11"/>
+      <c r="J41" s="11"/>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
@@ -2688,21 +2871,20 @@
       <c r="B42" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C42" s="60" t="s">
+      <c r="C42" s="64" t="s">
         <v>50</v>
       </c>
-      <c r="D42" s="61" t="s">
+      <c r="D42" s="65" t="s">
         <v>25</v>
       </c>
-      <c r="E42" s="61" t="s">
+      <c r="E42" s="65" t="s">
         <v>27</v>
       </c>
-      <c r="F42" s="75"/>
-      <c r="G42" s="75"/>
-      <c r="H42" s="75"/>
-      <c r="I42" s="75"/>
-      <c r="J42" s="75"/>
-      <c r="K42" s="67" t="s">
+      <c r="G42" s="11"/>
+      <c r="H42" s="11"/>
+      <c r="I42" s="11"/>
+      <c r="J42" s="11"/>
+      <c r="K42" s="71" t="s">
         <v>30</v>
       </c>
     </row>
@@ -2713,15 +2895,14 @@
       <c r="B43" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C43" s="60"/>
-      <c r="D43" s="61"/>
-      <c r="E43" s="61"/>
-      <c r="F43" s="75"/>
-      <c r="G43" s="75"/>
-      <c r="H43" s="75"/>
-      <c r="I43" s="75"/>
-      <c r="J43" s="75"/>
-      <c r="K43" s="67"/>
+      <c r="C43" s="64"/>
+      <c r="D43" s="65"/>
+      <c r="E43" s="65"/>
+      <c r="G43" s="11"/>
+      <c r="H43" s="11"/>
+      <c r="I43" s="11"/>
+      <c r="J43" s="11"/>
+      <c r="K43" s="71"/>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
@@ -2730,22 +2911,20 @@
       <c r="B44" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C44" s="60"/>
-      <c r="D44" s="61"/>
-      <c r="E44" s="61"/>
-      <c r="F44" s="75"/>
-      <c r="G44" s="75"/>
-      <c r="H44" s="75"/>
-      <c r="I44" s="75"/>
-      <c r="J44" s="75"/>
-      <c r="K44" s="67"/>
+      <c r="C44" s="64"/>
+      <c r="D44" s="65"/>
+      <c r="E44" s="65"/>
+      <c r="G44" s="11"/>
+      <c r="H44" s="11"/>
+      <c r="I44" s="11"/>
+      <c r="J44" s="11"/>
+      <c r="K44" s="71"/>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="F45" s="75"/>
-      <c r="G45" s="75"/>
-      <c r="H45" s="75"/>
-      <c r="I45" s="75"/>
-      <c r="J45" s="75"/>
+      <c r="G45" s="11"/>
+      <c r="H45" s="11"/>
+      <c r="I45" s="11"/>
+      <c r="J45" s="11"/>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
@@ -2754,21 +2933,20 @@
       <c r="B46" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C46" s="60" t="s">
+      <c r="C46" s="64" t="s">
         <v>51</v>
       </c>
-      <c r="D46" s="61" t="s">
+      <c r="D46" s="65" t="s">
         <v>26</v>
       </c>
-      <c r="E46" s="61" t="s">
+      <c r="E46" s="65" t="s">
         <v>28</v>
       </c>
-      <c r="F46" s="75"/>
-      <c r="G46" s="75"/>
-      <c r="H46" s="75"/>
-      <c r="I46" s="75"/>
-      <c r="J46" s="75"/>
-      <c r="K46" s="67" t="s">
+      <c r="G46" s="11"/>
+      <c r="H46" s="11"/>
+      <c r="I46" s="11"/>
+      <c r="J46" s="11"/>
+      <c r="K46" s="71" t="s">
         <v>31</v>
       </c>
     </row>
@@ -2779,15 +2957,14 @@
       <c r="B47" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C47" s="60"/>
-      <c r="D47" s="61"/>
-      <c r="E47" s="61"/>
-      <c r="F47" s="75"/>
-      <c r="G47" s="75"/>
-      <c r="H47" s="75"/>
-      <c r="I47" s="75"/>
-      <c r="J47" s="75"/>
-      <c r="K47" s="67"/>
+      <c r="C47" s="64"/>
+      <c r="D47" s="65"/>
+      <c r="E47" s="65"/>
+      <c r="G47" s="11"/>
+      <c r="H47" s="11"/>
+      <c r="I47" s="11"/>
+      <c r="J47" s="11"/>
+      <c r="K47" s="71"/>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
@@ -2796,22 +2973,20 @@
       <c r="B48" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C48" s="60"/>
-      <c r="D48" s="61"/>
-      <c r="E48" s="61"/>
-      <c r="F48" s="75"/>
-      <c r="G48" s="75"/>
-      <c r="H48" s="75"/>
-      <c r="I48" s="75"/>
-      <c r="J48" s="75"/>
-      <c r="K48" s="67"/>
+      <c r="C48" s="64"/>
+      <c r="D48" s="65"/>
+      <c r="E48" s="65"/>
+      <c r="G48" s="11"/>
+      <c r="H48" s="11"/>
+      <c r="I48" s="11"/>
+      <c r="J48" s="11"/>
+      <c r="K48" s="71"/>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="F49" s="75"/>
-      <c r="G49" s="75"/>
-      <c r="H49" s="75"/>
-      <c r="I49" s="75"/>
-      <c r="J49" s="75"/>
+      <c r="G49" s="11"/>
+      <c r="H49" s="11"/>
+      <c r="I49" s="11"/>
+      <c r="J49" s="11"/>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
@@ -2820,20 +2995,19 @@
       <c r="B50" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C50" s="60" t="s">
+      <c r="C50" s="64" t="s">
         <v>52</v>
       </c>
-      <c r="D50" s="61" t="s">
+      <c r="D50" s="65" t="s">
         <v>39</v>
       </c>
-      <c r="E50" s="61" t="s">
+      <c r="E50" s="65" t="s">
         <v>29</v>
       </c>
-      <c r="F50" s="75"/>
-      <c r="G50" s="75"/>
-      <c r="H50" s="75"/>
-      <c r="I50" s="75"/>
-      <c r="J50" s="75"/>
+      <c r="G50" s="11"/>
+      <c r="H50" s="11"/>
+      <c r="I50" s="11"/>
+      <c r="J50" s="11"/>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A51" s="1" t="s">
@@ -2842,14 +3016,13 @@
       <c r="B51" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C51" s="60"/>
-      <c r="D51" s="61"/>
-      <c r="E51" s="61"/>
-      <c r="F51" s="75"/>
-      <c r="G51" s="75"/>
-      <c r="H51" s="75"/>
-      <c r="I51" s="75"/>
-      <c r="J51" s="75"/>
+      <c r="C51" s="64"/>
+      <c r="D51" s="65"/>
+      <c r="E51" s="65"/>
+      <c r="G51" s="11"/>
+      <c r="H51" s="11"/>
+      <c r="I51" s="11"/>
+      <c r="J51" s="11"/>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
@@ -2858,14 +3031,13 @@
       <c r="B52" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C52" s="60"/>
-      <c r="D52" s="61"/>
-      <c r="E52" s="61"/>
-      <c r="F52" s="75"/>
-      <c r="G52" s="75"/>
-      <c r="H52" s="75"/>
-      <c r="I52" s="75"/>
-      <c r="J52" s="75"/>
+      <c r="C52" s="64"/>
+      <c r="D52" s="65"/>
+      <c r="E52" s="65"/>
+      <c r="G52" s="11"/>
+      <c r="H52" s="11"/>
+      <c r="I52" s="11"/>
+      <c r="J52" s="11"/>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.2">
       <c r="G53" s="11"/>
@@ -2880,12 +3052,12 @@
       <c r="J54" s="11"/>
     </row>
     <row r="55" spans="1:11" s="42" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="59" t="s">
-        <v>60</v>
-      </c>
-      <c r="B55" s="59"/>
-      <c r="C55" s="59"/>
-      <c r="D55" s="59"/>
+      <c r="A55" s="63" t="s">
+        <v>59</v>
+      </c>
+      <c r="B55" s="63"/>
+      <c r="C55" s="63"/>
+      <c r="D55" s="63"/>
       <c r="E55" s="39"/>
       <c r="F55" s="40">
         <f>MAX(F2:F52)</f>
@@ -2910,12 +3082,12 @@
       <c r="K55" s="41"/>
     </row>
     <row r="56" spans="1:11" s="46" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="65" t="s">
-        <v>61</v>
-      </c>
-      <c r="B56" s="65"/>
-      <c r="C56" s="65"/>
-      <c r="D56" s="65"/>
+      <c r="A56" s="69" t="s">
+        <v>60</v>
+      </c>
+      <c r="B56" s="69"/>
+      <c r="C56" s="69"/>
+      <c r="D56" s="69"/>
       <c r="E56" s="43"/>
       <c r="F56" s="44" t="e">
         <f>AVERAGE(F2:F52)</f>
@@ -3048,13 +3220,13 @@
         <v>57</v>
       </c>
       <c r="K1" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="L1" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="L1" s="12" t="s">
+      <c r="M1" s="12" t="s">
         <v>63</v>
-      </c>
-      <c r="M1" s="12" t="s">
-        <v>64</v>
       </c>
       <c r="N1" s="7" t="s">
         <v>14</v>
@@ -3068,20 +3240,15 @@
       <c r="B2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="64" t="s">
+      <c r="C2" s="68" t="s">
         <v>41</v>
       </c>
-      <c r="D2" s="63" t="s">
+      <c r="D2" s="67" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="63" t="s">
+      <c r="E2" s="67" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="75"/>
-      <c r="G2" s="75"/>
-      <c r="H2" s="75"/>
-      <c r="I2" s="75"/>
-      <c r="J2" s="75"/>
       <c r="K2" s="11">
         <f>SUM(F2*1/3,G2*1/3,I2*1/3)</f>
         <v>0</v>
@@ -3094,7 +3261,7 @@
         <f>SUM(F2*1/5,G2*1/5,H2*1/5,I2*1/5,J2*1/5)</f>
         <v>0</v>
       </c>
-      <c r="N2" s="66" t="s">
+      <c r="N2" s="70" t="s">
         <v>15</v>
       </c>
     </row>
@@ -3105,14 +3272,9 @@
       <c r="B3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="60"/>
-      <c r="D3" s="61"/>
-      <c r="E3" s="61"/>
-      <c r="F3" s="75"/>
-      <c r="G3" s="75"/>
-      <c r="H3" s="75"/>
-      <c r="I3" s="75"/>
-      <c r="J3" s="75"/>
+      <c r="C3" s="64"/>
+      <c r="D3" s="65"/>
+      <c r="E3" s="65"/>
       <c r="K3" s="11">
         <f>SUM(F3*1/3,G3*1/3,I3*1/3)</f>
         <v>0</v>
@@ -3125,7 +3287,7 @@
         <f>SUM(F3*1/5,G3*1/5,H3*1/5,I3*1/5,J3*1/5)</f>
         <v>0</v>
       </c>
-      <c r="N3" s="67"/>
+      <c r="N3" s="71"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
@@ -3134,14 +3296,9 @@
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="60"/>
-      <c r="D4" s="61"/>
-      <c r="E4" s="61"/>
-      <c r="F4" s="75"/>
-      <c r="G4" s="75"/>
-      <c r="H4" s="75"/>
-      <c r="I4" s="75"/>
-      <c r="J4" s="75"/>
+      <c r="C4" s="64"/>
+      <c r="D4" s="65"/>
+      <c r="E4" s="65"/>
       <c r="K4" s="11">
         <f>SUM(F4*1/3,G4*1/3,I4*1/3)</f>
         <v>0</v>
@@ -3154,14 +3311,7 @@
         <f>SUM(F4*1/5,G4*1/5,H4*1/5,I4*1/5,J4*1/5)</f>
         <v>0</v>
       </c>
-      <c r="N4" s="67"/>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="F5" s="75"/>
-      <c r="G5" s="75"/>
-      <c r="H5" s="75"/>
-      <c r="I5" s="75"/>
-      <c r="J5" s="75"/>
+      <c r="N4" s="71"/>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
@@ -3170,20 +3320,15 @@
       <c r="B6" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="60" t="s">
+      <c r="C6" s="64" t="s">
         <v>42</v>
       </c>
-      <c r="D6" s="61" t="s">
+      <c r="D6" s="65" t="s">
         <v>10</v>
       </c>
-      <c r="E6" s="61" t="s">
+      <c r="E6" s="65" t="s">
         <v>13</v>
       </c>
-      <c r="F6" s="75"/>
-      <c r="G6" s="75"/>
-      <c r="H6" s="75"/>
-      <c r="I6" s="75"/>
-      <c r="J6" s="75"/>
       <c r="K6" s="11">
         <f>SUM(F6*1/3,G6*1/3,I6*1/3)</f>
         <v>0</v>
@@ -3196,7 +3341,7 @@
         <f>SUM(F6*1/5,G6*1/5,H6*1/5,I6*1/5,J6*1/5)</f>
         <v>0</v>
       </c>
-      <c r="N6" s="67" t="s">
+      <c r="N6" s="71" t="s">
         <v>16</v>
       </c>
     </row>
@@ -3207,14 +3352,9 @@
       <c r="B7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="60"/>
-      <c r="D7" s="61"/>
-      <c r="E7" s="61"/>
-      <c r="F7" s="75"/>
-      <c r="G7" s="75"/>
-      <c r="H7" s="75"/>
-      <c r="I7" s="75"/>
-      <c r="J7" s="75"/>
+      <c r="C7" s="64"/>
+      <c r="D7" s="65"/>
+      <c r="E7" s="65"/>
       <c r="K7" s="11">
         <f>SUM(F7*1/3,G7*1/3,I7*1/3)</f>
         <v>0</v>
@@ -3227,7 +3367,7 @@
         <f>SUM(F7*1/5,G7*1/5,H7*1/5,I7*1/5,J7*1/5)</f>
         <v>0</v>
       </c>
-      <c r="N7" s="67"/>
+      <c r="N7" s="71"/>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
@@ -3236,14 +3376,9 @@
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="60"/>
-      <c r="D8" s="61"/>
-      <c r="E8" s="61"/>
-      <c r="F8" s="75"/>
-      <c r="G8" s="75"/>
-      <c r="H8" s="75"/>
-      <c r="I8" s="75"/>
-      <c r="J8" s="75"/>
+      <c r="C8" s="64"/>
+      <c r="D8" s="65"/>
+      <c r="E8" s="65"/>
       <c r="K8" s="11">
         <f>SUM(F8*1/3,G8*1/3,I8*1/3)</f>
         <v>0</v>
@@ -3256,15 +3391,15 @@
         <f>SUM(F8*1/5,G8*1/5,H8*1/5,I8*1/5,J8*1/5)</f>
         <v>0</v>
       </c>
-      <c r="N8" s="67"/>
+      <c r="N8" s="71"/>
     </row>
     <row r="10" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="62" t="s">
+      <c r="A10" s="73" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="62"/>
-      <c r="C10" s="62"/>
-      <c r="D10" s="62"/>
+      <c r="B10" s="73"/>
+      <c r="C10" s="73"/>
+      <c r="D10" s="73"/>
       <c r="E10" s="5"/>
       <c r="F10" s="13"/>
       <c r="G10" s="13"/>
@@ -3283,33 +3418,28 @@
       <c r="B12" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C12" s="60" t="s">
+      <c r="C12" s="64" t="s">
         <v>43</v>
       </c>
-      <c r="D12" s="61" t="s">
+      <c r="D12" s="65" t="s">
         <v>11</v>
       </c>
-      <c r="E12" s="61" t="s">
+      <c r="E12" s="65" t="s">
         <v>17</v>
       </c>
-      <c r="F12" s="75"/>
-      <c r="G12" s="75"/>
-      <c r="H12" s="75"/>
-      <c r="I12" s="75"/>
-      <c r="J12" s="75"/>
-      <c r="K12" s="75">
+      <c r="K12" s="11">
         <f>SUM(F12*1/3,G12*1/3,I12*1/3)</f>
         <v>0</v>
       </c>
-      <c r="L12" s="75">
+      <c r="L12" s="11">
         <f>SUM(H12*1/2,J12*1/2)</f>
         <v>0</v>
       </c>
-      <c r="M12" s="75">
+      <c r="M12" s="11">
         <f>SUM(F12*1/5,G12*1/5,H12*1/5,I12*1/5,J12*1/5)</f>
         <v>0</v>
       </c>
-      <c r="N12" s="67" t="s">
+      <c r="N12" s="71" t="s">
         <v>18</v>
       </c>
     </row>
@@ -3320,27 +3450,22 @@
       <c r="B13" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C13" s="60"/>
-      <c r="D13" s="61"/>
-      <c r="E13" s="61"/>
-      <c r="F13" s="75"/>
-      <c r="G13" s="75"/>
-      <c r="H13" s="75"/>
-      <c r="I13" s="75"/>
-      <c r="J13" s="75"/>
-      <c r="K13" s="75">
+      <c r="C13" s="64"/>
+      <c r="D13" s="65"/>
+      <c r="E13" s="65"/>
+      <c r="K13" s="11">
         <f>SUM(F13*1/3,G13*1/3,I13*1/3)</f>
         <v>0</v>
       </c>
-      <c r="L13" s="75">
+      <c r="L13" s="11">
         <f>SUM(H13*1/2,J13*1/2)</f>
         <v>0</v>
       </c>
-      <c r="M13" s="75">
+      <c r="M13" s="11">
         <f>SUM(F13*1/5,G13*1/5,H13*1/5,I13*1/5,J13*1/5)</f>
         <v>0</v>
       </c>
-      <c r="N13" s="67"/>
+      <c r="N13" s="71"/>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
@@ -3349,37 +3474,22 @@
       <c r="B14" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C14" s="60"/>
-      <c r="D14" s="61"/>
-      <c r="E14" s="61"/>
-      <c r="F14" s="75"/>
-      <c r="G14" s="75"/>
-      <c r="H14" s="75"/>
-      <c r="I14" s="75"/>
-      <c r="J14" s="75"/>
-      <c r="K14" s="75">
+      <c r="C14" s="64"/>
+      <c r="D14" s="65"/>
+      <c r="E14" s="65"/>
+      <c r="K14" s="11">
         <f>SUM(F14*1/3,G14*1/3,I14*1/3)</f>
         <v>0</v>
       </c>
-      <c r="L14" s="75">
+      <c r="L14" s="11">
         <f>SUM(H14*1/2,J14*1/2)</f>
         <v>0</v>
       </c>
-      <c r="M14" s="75">
+      <c r="M14" s="11">
         <f>SUM(F14*1/5,G14*1/5,H14*1/5,I14*1/5,J14*1/5)</f>
         <v>0</v>
       </c>
-      <c r="N14" s="67"/>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="F15" s="75"/>
-      <c r="G15" s="75"/>
-      <c r="H15" s="75"/>
-      <c r="I15" s="75"/>
-      <c r="J15" s="75"/>
-      <c r="K15" s="75"/>
-      <c r="L15" s="75"/>
-      <c r="M15" s="75"/>
+      <c r="N14" s="71"/>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
@@ -3388,33 +3498,28 @@
       <c r="B16" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C16" s="60" t="s">
+      <c r="C16" s="64" t="s">
         <v>44</v>
       </c>
-      <c r="D16" s="61" t="s">
+      <c r="D16" s="65" t="s">
         <v>19</v>
       </c>
-      <c r="E16" s="61" t="s">
+      <c r="E16" s="65" t="s">
         <v>27</v>
       </c>
-      <c r="F16" s="75"/>
-      <c r="G16" s="75"/>
-      <c r="H16" s="75"/>
-      <c r="I16" s="75"/>
-      <c r="J16" s="75"/>
-      <c r="K16" s="75">
+      <c r="K16" s="11">
         <f>SUM(F16*1/3,G16*1/3,I16*1/3)</f>
         <v>0</v>
       </c>
-      <c r="L16" s="75">
+      <c r="L16" s="11">
         <f>SUM(H16*1/2,J16*1/2)</f>
         <v>0</v>
       </c>
-      <c r="M16" s="75">
+      <c r="M16" s="11">
         <f>SUM(F16*1/5,G16*1/5,H16*1/5,I16*1/5,J16*1/5)</f>
         <v>0</v>
       </c>
-      <c r="N16" s="67" t="s">
+      <c r="N16" s="71" t="s">
         <v>36</v>
       </c>
     </row>
@@ -3425,27 +3530,22 @@
       <c r="B17" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C17" s="60"/>
-      <c r="D17" s="61"/>
-      <c r="E17" s="61"/>
-      <c r="F17" s="75"/>
-      <c r="G17" s="75"/>
-      <c r="H17" s="75"/>
-      <c r="I17" s="75"/>
-      <c r="J17" s="75"/>
-      <c r="K17" s="75">
+      <c r="C17" s="64"/>
+      <c r="D17" s="65"/>
+      <c r="E17" s="65"/>
+      <c r="K17" s="11">
         <f>SUM(F17*1/3,G17*1/3,I17*1/3)</f>
         <v>0</v>
       </c>
-      <c r="L17" s="75">
+      <c r="L17" s="11">
         <f>SUM(H17*1/2,J17*1/2)</f>
         <v>0</v>
       </c>
-      <c r="M17" s="75">
+      <c r="M17" s="11">
         <f>SUM(F17*1/5,G17*1/5,H17*1/5,I17*1/5,J17*1/5)</f>
         <v>0</v>
       </c>
-      <c r="N17" s="67"/>
+      <c r="N17" s="71"/>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
@@ -3454,37 +3554,22 @@
       <c r="B18" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C18" s="60"/>
-      <c r="D18" s="61"/>
-      <c r="E18" s="61"/>
-      <c r="F18" s="75"/>
-      <c r="G18" s="75"/>
-      <c r="H18" s="75"/>
-      <c r="I18" s="75"/>
-      <c r="J18" s="75"/>
-      <c r="K18" s="75">
+      <c r="C18" s="64"/>
+      <c r="D18" s="65"/>
+      <c r="E18" s="65"/>
+      <c r="K18" s="11">
         <f>SUM(F18*1/3,G18*1/3,I18*1/3)</f>
         <v>0</v>
       </c>
-      <c r="L18" s="76">
+      <c r="L18" s="54">
         <f>SUM(H18*1/2,J18*1/2)</f>
         <v>0</v>
       </c>
-      <c r="M18" s="75">
+      <c r="M18" s="11">
         <f>SUM(F18*1/5,G18*1/5,H18*1/5,I18*1/5,J18*1/5)</f>
         <v>0</v>
       </c>
-      <c r="N18" s="67"/>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="F19" s="75"/>
-      <c r="G19" s="75"/>
-      <c r="H19" s="75"/>
-      <c r="I19" s="75"/>
-      <c r="J19" s="75"/>
-      <c r="K19" s="75"/>
-      <c r="L19" s="75"/>
-      <c r="M19" s="75"/>
+      <c r="N18" s="71"/>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
@@ -3493,33 +3578,28 @@
       <c r="B20" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C20" s="60" t="s">
+      <c r="C20" s="64" t="s">
         <v>45</v>
       </c>
-      <c r="D20" s="61" t="s">
+      <c r="D20" s="65" t="s">
         <v>20</v>
       </c>
-      <c r="E20" s="61" t="s">
+      <c r="E20" s="65" t="s">
         <v>28</v>
       </c>
-      <c r="F20" s="75"/>
-      <c r="G20" s="75"/>
-      <c r="H20" s="75"/>
-      <c r="I20" s="75"/>
-      <c r="J20" s="75"/>
-      <c r="K20" s="75">
+      <c r="K20" s="11">
         <f>SUM(F20*1/3,G20*1/3,I20*1/3)</f>
         <v>0</v>
       </c>
-      <c r="L20" s="75">
+      <c r="L20" s="11">
         <f>SUM(H20*1/2,J20*1/2)</f>
         <v>0</v>
       </c>
-      <c r="M20" s="75">
+      <c r="M20" s="11">
         <f>SUM(F20*1/5,G20*1/5,H20*1/5,I20*1/5,J20*1/5)</f>
         <v>0</v>
       </c>
-      <c r="N20" s="67" t="s">
+      <c r="N20" s="71" t="s">
         <v>35</v>
       </c>
     </row>
@@ -3530,27 +3610,22 @@
       <c r="B21" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C21" s="60"/>
-      <c r="D21" s="61"/>
-      <c r="E21" s="61"/>
-      <c r="F21" s="75"/>
-      <c r="G21" s="75"/>
-      <c r="H21" s="75"/>
-      <c r="I21" s="75"/>
-      <c r="J21" s="75"/>
-      <c r="K21" s="75">
+      <c r="C21" s="64"/>
+      <c r="D21" s="65"/>
+      <c r="E21" s="65"/>
+      <c r="K21" s="11">
         <f>SUM(F21*1/3,G21*1/3,I21*1/3)</f>
         <v>0</v>
       </c>
-      <c r="L21" s="75">
+      <c r="L21" s="11">
         <f>SUM(H21*1/2,J21*1/2)</f>
         <v>0</v>
       </c>
-      <c r="M21" s="76">
+      <c r="M21" s="54">
         <f>SUM(F21*1/5,G21*1/5,H21*1/5,I21*1/5,J21*1/5)</f>
         <v>0</v>
       </c>
-      <c r="N21" s="67"/>
+      <c r="N21" s="71"/>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
@@ -3559,37 +3634,22 @@
       <c r="B22" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C22" s="60"/>
-      <c r="D22" s="61"/>
-      <c r="E22" s="61"/>
-      <c r="F22" s="75"/>
-      <c r="G22" s="75"/>
-      <c r="H22" s="75"/>
-      <c r="I22" s="75"/>
-      <c r="J22" s="75"/>
-      <c r="K22" s="75">
+      <c r="C22" s="64"/>
+      <c r="D22" s="65"/>
+      <c r="E22" s="65"/>
+      <c r="K22" s="11">
         <f>SUM(F22*1/3,G22*1/3,I22*1/3)</f>
         <v>0</v>
       </c>
-      <c r="L22" s="75">
+      <c r="L22" s="11">
         <f>SUM(H22*1/2,J22*1/2)</f>
         <v>0</v>
       </c>
-      <c r="M22" s="75">
+      <c r="M22" s="11">
         <f>SUM(F22*1/5,G22*1/5,H22*1/5,I22*1/5,J22*1/5)</f>
         <v>0</v>
       </c>
-      <c r="N22" s="67"/>
-    </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="F23" s="75"/>
-      <c r="G23" s="75"/>
-      <c r="H23" s="75"/>
-      <c r="I23" s="75"/>
-      <c r="J23" s="75"/>
-      <c r="K23" s="75"/>
-      <c r="L23" s="75"/>
-      <c r="M23" s="75"/>
+      <c r="N22" s="71"/>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
@@ -3598,29 +3658,24 @@
       <c r="B24" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C24" s="60" t="s">
+      <c r="C24" s="64" t="s">
         <v>46</v>
       </c>
-      <c r="D24" s="61" t="s">
+      <c r="D24" s="65" t="s">
         <v>21</v>
       </c>
-      <c r="E24" s="61" t="s">
+      <c r="E24" s="65" t="s">
         <v>32</v>
       </c>
-      <c r="F24" s="75"/>
-      <c r="G24" s="75"/>
-      <c r="H24" s="75"/>
-      <c r="I24" s="75"/>
-      <c r="J24" s="75"/>
-      <c r="K24" s="75">
+      <c r="K24" s="11">
         <f>SUM(F24*1/3,G24*1/3,I24*1/3)</f>
         <v>0</v>
       </c>
-      <c r="L24" s="75">
+      <c r="L24" s="11">
         <f>SUM(H24*1/2,J24*1/2)</f>
         <v>0</v>
       </c>
-      <c r="M24" s="75">
+      <c r="M24" s="11">
         <f>SUM(F24*1/5,G24*1/5,H24*1/5,I24*1/5,J24*1/5)</f>
         <v>0</v>
       </c>
@@ -3632,23 +3687,18 @@
       <c r="B25" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C25" s="60"/>
-      <c r="D25" s="61"/>
-      <c r="E25" s="61"/>
-      <c r="F25" s="75"/>
-      <c r="G25" s="75"/>
-      <c r="H25" s="75"/>
-      <c r="I25" s="75"/>
-      <c r="J25" s="75"/>
-      <c r="K25" s="75">
+      <c r="C25" s="64"/>
+      <c r="D25" s="65"/>
+      <c r="E25" s="65"/>
+      <c r="K25" s="11">
         <f>SUM(F25*1/3,G25*1/3,I25*1/3)</f>
         <v>0</v>
       </c>
-      <c r="L25" s="75">
+      <c r="L25" s="11">
         <f>SUM(H25*1/2,J25*1/2)</f>
         <v>0</v>
       </c>
-      <c r="M25" s="75">
+      <c r="M25" s="11">
         <f>SUM(F25*1/5,G25*1/5,H25*1/5,I25*1/5,J25*1/5)</f>
         <v>0</v>
       </c>
@@ -3660,36 +3710,21 @@
       <c r="B26" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C26" s="60"/>
-      <c r="D26" s="61"/>
-      <c r="E26" s="61"/>
-      <c r="F26" s="75"/>
-      <c r="G26" s="75"/>
-      <c r="H26" s="75"/>
-      <c r="I26" s="75"/>
-      <c r="J26" s="75"/>
-      <c r="K26" s="75">
+      <c r="C26" s="64"/>
+      <c r="D26" s="65"/>
+      <c r="E26" s="65"/>
+      <c r="K26" s="11">
         <f>SUM(F26*1/3,G26*1/3,I26*1/3)</f>
         <v>0</v>
       </c>
-      <c r="L26" s="75">
+      <c r="L26" s="11">
         <f>SUM(H26*1/2,J26*1/2)</f>
         <v>0</v>
       </c>
-      <c r="M26" s="75">
+      <c r="M26" s="11">
         <f>SUM(F26*1/5,G26*1/5,H26*1/5,I26*1/5,J26*1/5)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="F27" s="75"/>
-      <c r="G27" s="75"/>
-      <c r="H27" s="75"/>
-      <c r="I27" s="75"/>
-      <c r="J27" s="75"/>
-      <c r="K27" s="75"/>
-      <c r="L27" s="75"/>
-      <c r="M27" s="75"/>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
@@ -3698,29 +3733,24 @@
       <c r="B28" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C28" s="60" t="s">
+      <c r="C28" s="64" t="s">
         <v>47</v>
       </c>
-      <c r="D28" s="61" t="s">
+      <c r="D28" s="65" t="s">
         <v>22</v>
       </c>
-      <c r="E28" s="61" t="s">
+      <c r="E28" s="65" t="s">
         <v>33</v>
       </c>
-      <c r="F28" s="75"/>
-      <c r="G28" s="75"/>
-      <c r="H28" s="75"/>
-      <c r="I28" s="75"/>
-      <c r="J28" s="75"/>
-      <c r="K28" s="75">
+      <c r="K28" s="11">
         <f>SUM(F28*1/3,G28*1/3,I28*1/3)</f>
         <v>0</v>
       </c>
-      <c r="L28" s="75">
+      <c r="L28" s="11">
         <f>SUM(H28*1/2,J28*1/2)</f>
         <v>0</v>
       </c>
-      <c r="M28" s="75">
+      <c r="M28" s="11">
         <f>SUM(F28*1/5,G28*1/5,H28*1/5,I28*1/5,J28*1/5)</f>
         <v>0</v>
       </c>
@@ -3732,23 +3762,18 @@
       <c r="B29" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C29" s="60"/>
-      <c r="D29" s="61"/>
-      <c r="E29" s="61"/>
-      <c r="F29" s="75"/>
-      <c r="G29" s="75"/>
-      <c r="H29" s="75"/>
-      <c r="I29" s="75"/>
-      <c r="J29" s="75"/>
-      <c r="K29" s="75">
+      <c r="C29" s="64"/>
+      <c r="D29" s="65"/>
+      <c r="E29" s="65"/>
+      <c r="K29" s="11">
         <f>SUM(F29*1/3,G29*1/3,I29*1/3)</f>
         <v>0</v>
       </c>
-      <c r="L29" s="75">
+      <c r="L29" s="11">
         <f>SUM(H29*1/2,J29*1/2)</f>
         <v>0</v>
       </c>
-      <c r="M29" s="75">
+      <c r="M29" s="11">
         <f>SUM(F29*1/5,G29*1/5,H29*1/5,I29*1/5,J29*1/5)</f>
         <v>0</v>
       </c>
@@ -3760,36 +3785,21 @@
       <c r="B30" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C30" s="60"/>
-      <c r="D30" s="61"/>
-      <c r="E30" s="61"/>
-      <c r="F30" s="75"/>
-      <c r="G30" s="75"/>
-      <c r="H30" s="75"/>
-      <c r="I30" s="75"/>
-      <c r="J30" s="75"/>
-      <c r="K30" s="75">
+      <c r="C30" s="64"/>
+      <c r="D30" s="65"/>
+      <c r="E30" s="65"/>
+      <c r="K30" s="11">
         <f>SUM(F30*1/3,G30*1/3,I30*1/3)</f>
         <v>0</v>
       </c>
-      <c r="L30" s="75">
+      <c r="L30" s="11">
         <f>SUM(H30*1/2,J30*1/2)</f>
         <v>0</v>
       </c>
-      <c r="M30" s="75">
+      <c r="M30" s="11">
         <f>SUM(F30*1/5,G30*1/5,H30*1/5,I30*1/5,J30*1/5)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="F31" s="75"/>
-      <c r="G31" s="75"/>
-      <c r="H31" s="75"/>
-      <c r="I31" s="75"/>
-      <c r="J31" s="75"/>
-      <c r="K31" s="75"/>
-      <c r="L31" s="75"/>
-      <c r="M31" s="75"/>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
@@ -3798,29 +3808,24 @@
       <c r="B32" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C32" s="60" t="s">
+      <c r="C32" s="64" t="s">
         <v>48</v>
       </c>
-      <c r="D32" s="61" t="s">
+      <c r="D32" s="65" t="s">
         <v>23</v>
       </c>
-      <c r="E32" s="61" t="s">
+      <c r="E32" s="65" t="s">
         <v>29</v>
       </c>
-      <c r="F32" s="75"/>
-      <c r="G32" s="75"/>
-      <c r="H32" s="75"/>
-      <c r="I32" s="75"/>
-      <c r="J32" s="75"/>
-      <c r="K32" s="75">
+      <c r="K32" s="11">
         <f>SUM(F32*1/3,G32*1/3,I32*1/3)</f>
         <v>0</v>
       </c>
-      <c r="L32" s="75">
+      <c r="L32" s="11">
         <f>SUM(H32*1/2,J32*1/2)</f>
         <v>0</v>
       </c>
-      <c r="M32" s="75">
+      <c r="M32" s="11">
         <f>SUM(F32*1/5,G32*1/5,H32*1/5,I32*1/5,J32*1/5)</f>
         <v>0</v>
       </c>
@@ -3832,23 +3837,18 @@
       <c r="B33" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C33" s="60"/>
-      <c r="D33" s="61"/>
-      <c r="E33" s="61"/>
-      <c r="F33" s="75"/>
-      <c r="G33" s="75"/>
-      <c r="H33" s="75"/>
-      <c r="I33" s="75"/>
-      <c r="J33" s="75"/>
-      <c r="K33" s="76">
+      <c r="C33" s="64"/>
+      <c r="D33" s="65"/>
+      <c r="E33" s="65"/>
+      <c r="K33" s="54">
         <f>SUM(F33*1/3,G33*1/3,I33*1/3)</f>
         <v>0</v>
       </c>
-      <c r="L33" s="75">
+      <c r="L33" s="11">
         <f>SUM(H33*1/2,J33*1/2)</f>
         <v>0</v>
       </c>
-      <c r="M33" s="75">
+      <c r="M33" s="11">
         <f>SUM(F33*1/5,G33*1/5,H33*1/5,I33*1/5,J33*1/5)</f>
         <v>0</v>
       </c>
@@ -3860,36 +3860,21 @@
       <c r="B34" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C34" s="60"/>
-      <c r="D34" s="61"/>
-      <c r="E34" s="61"/>
-      <c r="F34" s="75"/>
-      <c r="G34" s="75"/>
-      <c r="H34" s="75"/>
-      <c r="I34" s="75"/>
-      <c r="J34" s="75"/>
-      <c r="K34" s="75">
+      <c r="C34" s="64"/>
+      <c r="D34" s="65"/>
+      <c r="E34" s="65"/>
+      <c r="K34" s="11">
         <f>SUM(F34*1/3,G34*1/3,I34*1/3)</f>
         <v>0</v>
       </c>
-      <c r="L34" s="75">
+      <c r="L34" s="11">
         <f>SUM(H34*1/2,J34*1/2)</f>
         <v>0</v>
       </c>
-      <c r="M34" s="75">
+      <c r="M34" s="11">
         <f>SUM(F34*1/5,G34*1/5,H34*1/5,I34*1/5,J34*1/5)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="F35" s="75"/>
-      <c r="G35" s="75"/>
-      <c r="H35" s="75"/>
-      <c r="I35" s="75"/>
-      <c r="J35" s="75"/>
-      <c r="K35" s="75"/>
-      <c r="L35" s="75"/>
-      <c r="M35" s="75"/>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
@@ -3898,29 +3883,24 @@
       <c r="B36" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C36" s="60" t="s">
+      <c r="C36" s="64" t="s">
         <v>49</v>
       </c>
-      <c r="D36" s="61" t="s">
+      <c r="D36" s="65" t="s">
         <v>24</v>
       </c>
-      <c r="E36" s="61" t="s">
+      <c r="E36" s="65" t="s">
         <v>34</v>
       </c>
-      <c r="F36" s="75"/>
-      <c r="G36" s="75"/>
-      <c r="H36" s="75"/>
-      <c r="I36" s="75"/>
-      <c r="J36" s="75"/>
-      <c r="K36" s="75">
+      <c r="K36" s="11">
         <f>SUM(F36*1/3,G36*1/3,I36*1/3)</f>
         <v>0</v>
       </c>
-      <c r="L36" s="75">
+      <c r="L36" s="11">
         <f>SUM(H36*1/2,J36*1/2)</f>
         <v>0</v>
       </c>
-      <c r="M36" s="75">
+      <c r="M36" s="11">
         <f>SUM(F36*1/5,G36*1/5,H36*1/5,I36*1/5,J36*1/5)</f>
         <v>0</v>
       </c>
@@ -3932,23 +3912,18 @@
       <c r="B37" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C37" s="60"/>
-      <c r="D37" s="61"/>
-      <c r="E37" s="61"/>
-      <c r="F37" s="75"/>
-      <c r="G37" s="75"/>
-      <c r="H37" s="75"/>
-      <c r="I37" s="75"/>
-      <c r="J37" s="75"/>
-      <c r="K37" s="75">
+      <c r="C37" s="64"/>
+      <c r="D37" s="65"/>
+      <c r="E37" s="65"/>
+      <c r="K37" s="11">
         <f>SUM(F37*1/3,G37*1/3,I37*1/3)</f>
         <v>0</v>
       </c>
-      <c r="L37" s="75">
+      <c r="L37" s="11">
         <f>SUM(H37*1/2,J37*1/2)</f>
         <v>0</v>
       </c>
-      <c r="M37" s="75">
+      <c r="M37" s="11">
         <f>SUM(F37*1/5,G37*1/5,H37*1/5,I37*1/5,J37*1/5)</f>
         <v>0</v>
       </c>
@@ -3960,44 +3935,29 @@
       <c r="B38" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C38" s="60"/>
-      <c r="D38" s="61"/>
-      <c r="E38" s="61"/>
-      <c r="F38" s="75"/>
-      <c r="G38" s="75"/>
-      <c r="H38" s="75"/>
-      <c r="I38" s="75"/>
-      <c r="J38" s="75"/>
-      <c r="K38" s="75">
+      <c r="C38" s="64"/>
+      <c r="D38" s="65"/>
+      <c r="E38" s="65"/>
+      <c r="K38" s="11">
         <f>SUM(F38*1/3,G38*1/3,I38*1/3)</f>
         <v>0</v>
       </c>
-      <c r="L38" s="75">
+      <c r="L38" s="11">
         <f>SUM(H38*1/2,J38*1/2)</f>
         <v>0</v>
       </c>
-      <c r="M38" s="75">
+      <c r="M38" s="11">
         <f>SUM(F38*1/5,G38*1/5,H38*1/5,I38*1/5,J38*1/5)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="F39" s="75"/>
-      <c r="G39" s="75"/>
-      <c r="H39" s="75"/>
-      <c r="I39" s="75"/>
-      <c r="J39" s="75"/>
-      <c r="K39" s="75"/>
-      <c r="L39" s="75"/>
-      <c r="M39" s="75"/>
-    </row>
     <row r="40" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="62" t="s">
+      <c r="A40" s="73" t="s">
         <v>38</v>
       </c>
-      <c r="B40" s="62"/>
-      <c r="C40" s="62"/>
-      <c r="D40" s="62"/>
+      <c r="B40" s="73"/>
+      <c r="C40" s="73"/>
+      <c r="D40" s="73"/>
       <c r="E40" s="5"/>
       <c r="F40" s="13"/>
       <c r="G40" s="13"/>
@@ -4016,20 +3976,15 @@
       <c r="B42" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C42" s="60" t="s">
+      <c r="C42" s="64" t="s">
         <v>50</v>
       </c>
-      <c r="D42" s="61" t="s">
+      <c r="D42" s="65" t="s">
         <v>25</v>
       </c>
-      <c r="E42" s="61" t="s">
+      <c r="E42" s="65" t="s">
         <v>27</v>
       </c>
-      <c r="F42" s="75"/>
-      <c r="G42" s="75"/>
-      <c r="H42" s="75"/>
-      <c r="I42" s="75"/>
-      <c r="J42" s="75"/>
       <c r="K42" s="11">
         <f>SUM(F42*1/3,G42*1/3,I42*1/3)</f>
         <v>0</v>
@@ -4042,7 +3997,7 @@
         <f>SUM(F42*1/5,G42*1/5,H42*1/5,I42*1/5,J42*1/5)</f>
         <v>0</v>
       </c>
-      <c r="N42" s="67" t="s">
+      <c r="N42" s="71" t="s">
         <v>30</v>
       </c>
     </row>
@@ -4053,14 +4008,9 @@
       <c r="B43" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C43" s="60"/>
-      <c r="D43" s="61"/>
-      <c r="E43" s="61"/>
-      <c r="F43" s="75"/>
-      <c r="G43" s="75"/>
-      <c r="H43" s="75"/>
-      <c r="I43" s="75"/>
-      <c r="J43" s="75"/>
+      <c r="C43" s="64"/>
+      <c r="D43" s="65"/>
+      <c r="E43" s="65"/>
       <c r="K43" s="11">
         <f>SUM(F43*1/3,G43*1/3,I43*1/3)</f>
         <v>0</v>
@@ -4073,7 +4023,7 @@
         <f>SUM(F43*1/5,G43*1/5,H43*1/5,I43*1/5,J43*1/5)</f>
         <v>0</v>
       </c>
-      <c r="N43" s="67"/>
+      <c r="N43" s="71"/>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
@@ -4082,14 +4032,10 @@
       <c r="B44" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C44" s="60"/>
-      <c r="D44" s="61"/>
-      <c r="E44" s="61"/>
-      <c r="F44" s="81"/>
-      <c r="G44" s="75"/>
-      <c r="H44" s="75"/>
-      <c r="I44" s="75"/>
-      <c r="J44" s="75"/>
+      <c r="C44" s="64"/>
+      <c r="D44" s="65"/>
+      <c r="E44" s="65"/>
+      <c r="F44" s="62"/>
       <c r="K44" s="11">
         <f>SUM(F44*1/3,G44*1/3,I44*1/3)</f>
         <v>0</v>
@@ -4102,14 +4048,7 @@
         <f>SUM(F44*1/5,G44*1/5,H44*1/5,I44*1/5,J44*1/5)</f>
         <v>0</v>
       </c>
-      <c r="N44" s="67"/>
-    </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="F45" s="75"/>
-      <c r="G45" s="75"/>
-      <c r="H45" s="75"/>
-      <c r="I45" s="75"/>
-      <c r="J45" s="75"/>
+      <c r="N44" s="71"/>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
@@ -4118,20 +4057,15 @@
       <c r="B46" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C46" s="60" t="s">
+      <c r="C46" s="64" t="s">
         <v>51</v>
       </c>
-      <c r="D46" s="61" t="s">
+      <c r="D46" s="65" t="s">
         <v>26</v>
       </c>
-      <c r="E46" s="61" t="s">
+      <c r="E46" s="65" t="s">
         <v>28</v>
       </c>
-      <c r="F46" s="75"/>
-      <c r="G46" s="75"/>
-      <c r="H46" s="75"/>
-      <c r="I46" s="75"/>
-      <c r="J46" s="75"/>
       <c r="K46" s="11">
         <f>SUM(F46*1/3,G46*1/3,I46*1/3)</f>
         <v>0</v>
@@ -4144,7 +4078,7 @@
         <f>SUM(F46*1/5,G46*1/5,H46*1/5,I46*1/5,J46*1/5)</f>
         <v>0</v>
       </c>
-      <c r="N46" s="67" t="s">
+      <c r="N46" s="71" t="s">
         <v>31</v>
       </c>
     </row>
@@ -4155,14 +4089,9 @@
       <c r="B47" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C47" s="60"/>
-      <c r="D47" s="61"/>
-      <c r="E47" s="61"/>
-      <c r="F47" s="75"/>
-      <c r="G47" s="75"/>
-      <c r="H47" s="75"/>
-      <c r="I47" s="75"/>
-      <c r="J47" s="75"/>
+      <c r="C47" s="64"/>
+      <c r="D47" s="65"/>
+      <c r="E47" s="65"/>
       <c r="K47" s="11">
         <f>SUM(F47*1/3,G47*1/3,I47*1/3)</f>
         <v>0</v>
@@ -4175,7 +4104,7 @@
         <f>SUM(F47*1/5,G47*1/5,H47*1/5,I47*1/5,J47*1/5)</f>
         <v>0</v>
       </c>
-      <c r="N47" s="67"/>
+      <c r="N47" s="71"/>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
@@ -4184,14 +4113,9 @@
       <c r="B48" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C48" s="60"/>
-      <c r="D48" s="61"/>
-      <c r="E48" s="61"/>
-      <c r="F48" s="75"/>
-      <c r="G48" s="75"/>
-      <c r="H48" s="75"/>
-      <c r="I48" s="75"/>
-      <c r="J48" s="75"/>
+      <c r="C48" s="64"/>
+      <c r="D48" s="65"/>
+      <c r="E48" s="65"/>
       <c r="K48" s="11">
         <f>SUM(F48*1/3,G48*1/3,I48*1/3)</f>
         <v>0</v>
@@ -4204,14 +4128,7 @@
         <f>SUM(F48*1/5,G48*1/5,H48*1/5,I48*1/5,J48*1/5)</f>
         <v>0</v>
       </c>
-      <c r="N48" s="67"/>
-    </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="F49" s="75"/>
-      <c r="G49" s="75"/>
-      <c r="H49" s="75"/>
-      <c r="I49" s="75"/>
-      <c r="J49" s="75"/>
+      <c r="N48" s="71"/>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
@@ -4220,20 +4137,15 @@
       <c r="B50" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C50" s="60" t="s">
+      <c r="C50" s="64" t="s">
         <v>52</v>
       </c>
-      <c r="D50" s="61" t="s">
+      <c r="D50" s="65" t="s">
         <v>39</v>
       </c>
-      <c r="E50" s="61" t="s">
+      <c r="E50" s="65" t="s">
         <v>29</v>
       </c>
-      <c r="F50" s="75"/>
-      <c r="G50" s="75"/>
-      <c r="H50" s="75"/>
-      <c r="I50" s="75"/>
-      <c r="J50" s="75"/>
       <c r="K50" s="11">
         <f>SUM(F50*1/3,G50*1/3,I50*1/3)</f>
         <v>0</v>
@@ -4254,14 +4166,9 @@
       <c r="B51" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C51" s="60"/>
-      <c r="D51" s="61"/>
-      <c r="E51" s="61"/>
-      <c r="F51" s="75"/>
-      <c r="G51" s="75"/>
-      <c r="H51" s="75"/>
-      <c r="I51" s="75"/>
-      <c r="J51" s="75"/>
+      <c r="C51" s="64"/>
+      <c r="D51" s="65"/>
+      <c r="E51" s="65"/>
       <c r="K51" s="11">
         <f>SUM(F51*1/3,G51*1/3,I51*1/3)</f>
         <v>0</v>
@@ -4282,14 +4189,10 @@
       <c r="B52" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C52" s="60"/>
-      <c r="D52" s="61"/>
-      <c r="E52" s="61"/>
-      <c r="F52" s="81"/>
-      <c r="G52" s="75"/>
-      <c r="H52" s="75"/>
-      <c r="I52" s="75"/>
-      <c r="J52" s="75"/>
+      <c r="C52" s="64"/>
+      <c r="D52" s="65"/>
+      <c r="E52" s="65"/>
+      <c r="F52" s="62"/>
       <c r="K52" s="11">
         <f>SUM(F52*1/3,G52*1/3,I52*1/3)</f>
         <v>0</v>
@@ -4304,12 +4207,12 @@
       </c>
     </row>
     <row r="55" spans="1:14" s="14" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="68" t="s">
-        <v>60</v>
-      </c>
-      <c r="B55" s="68"/>
-      <c r="C55" s="68"/>
-      <c r="D55" s="68"/>
+      <c r="A55" s="72" t="s">
+        <v>59</v>
+      </c>
+      <c r="B55" s="72"/>
+      <c r="C55" s="72"/>
+      <c r="D55" s="72"/>
       <c r="E55" s="15"/>
       <c r="F55" s="16">
         <f t="shared" ref="F55:M55" si="0">MAX(F2:F52)</f>
@@ -4346,12 +4249,12 @@
       <c r="N55" s="17"/>
     </row>
     <row r="56" spans="1:14" s="18" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="69" t="s">
-        <v>61</v>
-      </c>
-      <c r="B56" s="69"/>
-      <c r="C56" s="69"/>
-      <c r="D56" s="69"/>
+      <c r="A56" s="74" t="s">
+        <v>60</v>
+      </c>
+      <c r="B56" s="74"/>
+      <c r="C56" s="74"/>
+      <c r="D56" s="74"/>
       <c r="E56" s="19"/>
       <c r="F56" s="20" t="e">
         <f t="shared" ref="F56:M56" si="1">AVERAGE(F2:F52)</f>
@@ -4388,13 +4291,13 @@
       <c r="N56" s="21"/>
     </row>
     <row r="58" spans="1:14" s="22" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="72" t="s">
-        <v>68</v>
-      </c>
-      <c r="B58" s="72"/>
-      <c r="C58" s="72"/>
-      <c r="D58" s="72"/>
-      <c r="E58" s="72"/>
+      <c r="A58" s="77" t="s">
+        <v>67</v>
+      </c>
+      <c r="B58" s="77"/>
+      <c r="C58" s="77"/>
+      <c r="D58" s="77"/>
+      <c r="E58" s="77"/>
       <c r="F58" s="29">
         <f>SUM(F55*(1/3),  G55*(1/3), I55*(1/3))</f>
         <v>0</v>
@@ -4409,13 +4312,13 @@
       <c r="N58" s="24"/>
     </row>
     <row r="59" spans="1:14" s="27" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="73" t="s">
-        <v>69</v>
-      </c>
-      <c r="B59" s="73"/>
-      <c r="C59" s="73"/>
-      <c r="D59" s="73"/>
-      <c r="E59" s="73"/>
+      <c r="A59" s="78" t="s">
+        <v>68</v>
+      </c>
+      <c r="B59" s="78"/>
+      <c r="C59" s="78"/>
+      <c r="D59" s="78"/>
+      <c r="E59" s="78"/>
       <c r="F59" s="28">
         <f>SUM(H55*(1/2),  J55*(1/2))</f>
         <v>0</v>
@@ -4430,13 +4333,13 @@
       <c r="N59" s="26"/>
     </row>
     <row r="60" spans="1:14" s="33" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="74" t="s">
-        <v>70</v>
-      </c>
-      <c r="B60" s="74"/>
-      <c r="C60" s="74"/>
-      <c r="D60" s="74"/>
-      <c r="E60" s="74"/>
+      <c r="A60" s="79" t="s">
+        <v>69</v>
+      </c>
+      <c r="B60" s="79"/>
+      <c r="C60" s="79"/>
+      <c r="D60" s="79"/>
+      <c r="E60" s="79"/>
       <c r="F60" s="30">
         <f>SUM(F55*1/5, G55*1/5, H55*1/5, I55*1/5,J55*1/5)</f>
         <v>0</v>
@@ -4451,12 +4354,12 @@
       <c r="N60" s="32"/>
     </row>
     <row r="62" spans="1:14" s="37" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="70" t="s">
-        <v>65</v>
-      </c>
-      <c r="B62" s="70"/>
-      <c r="C62" s="70"/>
-      <c r="D62" s="70"/>
+      <c r="A62" s="75" t="s">
+        <v>64</v>
+      </c>
+      <c r="B62" s="75"/>
+      <c r="C62" s="75"/>
+      <c r="D62" s="75"/>
       <c r="E62" s="34"/>
       <c r="F62" s="35"/>
       <c r="G62" s="35"/>
@@ -4469,12 +4372,12 @@
       <c r="N62" s="36"/>
     </row>
     <row r="63" spans="1:14" s="37" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A63" s="70" t="s">
-        <v>66</v>
-      </c>
-      <c r="B63" s="71"/>
-      <c r="C63" s="71"/>
-      <c r="D63" s="71"/>
+      <c r="A63" s="75" t="s">
+        <v>65</v>
+      </c>
+      <c r="B63" s="76"/>
+      <c r="C63" s="76"/>
+      <c r="D63" s="76"/>
       <c r="E63" s="38"/>
       <c r="F63" s="35"/>
       <c r="G63" s="35"/>
@@ -4487,12 +4390,12 @@
       <c r="N63" s="36"/>
     </row>
     <row r="64" spans="1:14" s="37" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="70" t="s">
-        <v>67</v>
-      </c>
-      <c r="B64" s="71"/>
-      <c r="C64" s="71"/>
-      <c r="D64" s="71"/>
+      <c r="A64" s="75" t="s">
+        <v>66</v>
+      </c>
+      <c r="B64" s="76"/>
+      <c r="C64" s="76"/>
+      <c r="D64" s="76"/>
       <c r="E64" s="38"/>
       <c r="F64" s="35"/>
       <c r="G64" s="35"/>
@@ -4595,7 +4498,7 @@
         <v>40</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E1" s="12" t="s">
         <v>53</v>
@@ -4613,13 +4516,13 @@
         <v>57</v>
       </c>
       <c r="J1" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="K1" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="K1" s="12" t="s">
+      <c r="L1" s="12" t="s">
         <v>63</v>
-      </c>
-      <c r="L1" s="12" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="2" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.2">
@@ -4639,17 +4542,17 @@
       <c r="N2" s="9"/>
     </row>
     <row r="3" spans="1:14" s="47" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="69" t="s">
-        <v>75</v>
-      </c>
-      <c r="B3" s="69"/>
-      <c r="C3" s="69"/>
-      <c r="D3" s="69"/>
-      <c r="E3" s="69"/>
-      <c r="F3" s="69"/>
-      <c r="G3" s="69"/>
-      <c r="H3" s="69"/>
-      <c r="I3" s="69"/>
+      <c r="A3" s="74" t="s">
+        <v>74</v>
+      </c>
+      <c r="B3" s="74"/>
+      <c r="C3" s="74"/>
+      <c r="D3" s="74"/>
+      <c r="E3" s="74"/>
+      <c r="F3" s="74"/>
+      <c r="G3" s="74"/>
+      <c r="H3" s="74"/>
+      <c r="I3" s="74"/>
       <c r="J3" s="49"/>
       <c r="K3" s="56"/>
       <c r="L3" s="56"/>
@@ -4675,17 +4578,12 @@
       <c r="B5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="67" t="s">
+      <c r="C5" s="71" t="s">
+        <v>70</v>
+      </c>
+      <c r="D5" s="71" t="s">
         <v>71</v>
       </c>
-      <c r="D5" s="67" t="s">
-        <v>72</v>
-      </c>
-      <c r="E5" s="75"/>
-      <c r="F5" s="75"/>
-      <c r="G5" s="75"/>
-      <c r="H5" s="75"/>
-      <c r="I5" s="75"/>
       <c r="J5" s="11">
         <f>SUM(E5*1/3,F5*1/3,H5*1/3)</f>
         <v>0</v>
@@ -4706,13 +4604,8 @@
       <c r="B6" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="67"/>
-      <c r="D6" s="67"/>
-      <c r="E6" s="75"/>
-      <c r="F6" s="75"/>
-      <c r="G6" s="75"/>
-      <c r="H6" s="75"/>
-      <c r="I6" s="75"/>
+      <c r="C6" s="71"/>
+      <c r="D6" s="71"/>
       <c r="J6" s="11">
         <f>SUM(E6*1/3,F6*1/3,H6*1/3)</f>
         <v>0</v>
@@ -4733,13 +4626,8 @@
       <c r="B7" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="67"/>
-      <c r="D7" s="67"/>
-      <c r="E7" s="75"/>
-      <c r="F7" s="75"/>
-      <c r="G7" s="75"/>
-      <c r="H7" s="75"/>
-      <c r="I7" s="75"/>
+      <c r="C7" s="71"/>
+      <c r="D7" s="71"/>
       <c r="J7" s="11">
         <f>SUM(E7*1/3,F7*1/3,H7*1/3)</f>
         <v>0</v>
@@ -4752,13 +4640,6 @@
         <f>SUM(E7*1/5,F7*1/5,G7*1/5,H7*1/5,I7*1/5)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="E8" s="75"/>
-      <c r="F8" s="75"/>
-      <c r="G8" s="75"/>
-      <c r="H8" s="75"/>
-      <c r="I8" s="75"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
@@ -4767,17 +4648,12 @@
       <c r="B9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="67" t="s">
+      <c r="C9" s="71" t="s">
+        <v>72</v>
+      </c>
+      <c r="D9" s="71" t="s">
         <v>73</v>
       </c>
-      <c r="D9" s="67" t="s">
-        <v>74</v>
-      </c>
-      <c r="E9" s="75"/>
-      <c r="F9" s="75"/>
-      <c r="G9" s="75"/>
-      <c r="H9" s="75"/>
-      <c r="I9" s="75"/>
       <c r="J9" s="11">
         <f>SUM(E9*1/3,F9*1/3,H9*1/3)</f>
         <v>0</v>
@@ -4798,13 +4674,8 @@
       <c r="B10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="67"/>
-      <c r="D10" s="67"/>
-      <c r="E10" s="75"/>
-      <c r="F10" s="75"/>
-      <c r="G10" s="75"/>
-      <c r="H10" s="75"/>
-      <c r="I10" s="75"/>
+      <c r="C10" s="71"/>
+      <c r="D10" s="71"/>
       <c r="J10" s="11">
         <f>SUM(E10*1/3,F10*1/3,H10*1/3)</f>
         <v>0</v>
@@ -4825,13 +4696,8 @@
       <c r="B11" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C11" s="67"/>
-      <c r="D11" s="67"/>
-      <c r="E11" s="75"/>
-      <c r="F11" s="75"/>
-      <c r="G11" s="75"/>
-      <c r="H11" s="75"/>
-      <c r="I11" s="75"/>
+      <c r="C11" s="71"/>
+      <c r="D11" s="71"/>
       <c r="J11" s="11">
         <f>SUM(E11*1/3,F11*1/3,H11*1/3)</f>
         <v>0</v>
@@ -4844,13 +4710,6 @@
         <f>SUM(E11*1/5,F11*1/5,G11*1/5,H11*1/5,I11*1/5)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="E12" s="75"/>
-      <c r="F12" s="75"/>
-      <c r="G12" s="75"/>
-      <c r="H12" s="75"/>
-      <c r="I12" s="75"/>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
@@ -4859,17 +4718,12 @@
       <c r="B13" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C13" s="67" t="s">
-        <v>78</v>
-      </c>
-      <c r="D13" s="67" t="s">
-        <v>85</v>
-      </c>
-      <c r="E13" s="75"/>
-      <c r="F13" s="75"/>
-      <c r="G13" s="75"/>
-      <c r="H13" s="75"/>
-      <c r="I13" s="75"/>
+      <c r="C13" s="71" t="s">
+        <v>77</v>
+      </c>
+      <c r="D13" s="71" t="s">
+        <v>84</v>
+      </c>
       <c r="J13" s="11">
         <f>SUM(E13*1/3,F13*1/3,H13*1/3)</f>
         <v>0</v>
@@ -4890,13 +4744,8 @@
       <c r="B14" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C14" s="67"/>
-      <c r="D14" s="67"/>
-      <c r="E14" s="75"/>
-      <c r="F14" s="75"/>
-      <c r="G14" s="75"/>
-      <c r="H14" s="75"/>
-      <c r="I14" s="75"/>
+      <c r="C14" s="71"/>
+      <c r="D14" s="71"/>
       <c r="J14" s="11">
         <f>SUM(E14*1/3,F14*1/3,H14*1/3)</f>
         <v>0</v>
@@ -4917,13 +4766,8 @@
       <c r="B15" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C15" s="67"/>
-      <c r="D15" s="67"/>
-      <c r="E15" s="75"/>
-      <c r="F15" s="75"/>
-      <c r="G15" s="75"/>
-      <c r="H15" s="75"/>
-      <c r="I15" s="75"/>
+      <c r="C15" s="71"/>
+      <c r="D15" s="71"/>
       <c r="J15" s="11">
         <f>SUM(E15*1/3,F15*1/3,H15*1/3)</f>
         <v>0</v>
@@ -4936,13 +4780,6 @@
         <f>SUM(E15*1/5,F15*1/5,G15*1/5,H15*1/5,I15*1/5)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="E16" s="75"/>
-      <c r="F16" s="75"/>
-      <c r="G16" s="75"/>
-      <c r="H16" s="75"/>
-      <c r="I16" s="75"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
@@ -4951,17 +4788,12 @@
       <c r="B17" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C17" s="67" t="s">
-        <v>84</v>
-      </c>
-      <c r="D17" s="67" t="s">
+      <c r="C17" s="71" t="s">
         <v>83</v>
       </c>
-      <c r="E17" s="75"/>
-      <c r="F17" s="75"/>
-      <c r="G17" s="75"/>
-      <c r="H17" s="75"/>
-      <c r="I17" s="75"/>
+      <c r="D17" s="71" t="s">
+        <v>82</v>
+      </c>
       <c r="J17" s="11">
         <f>SUM(E17*1/3,F17*1/3,H17*1/3)</f>
         <v>0</v>
@@ -4982,13 +4814,8 @@
       <c r="B18" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C18" s="67"/>
-      <c r="D18" s="67"/>
-      <c r="E18" s="75"/>
-      <c r="F18" s="75"/>
-      <c r="G18" s="75"/>
-      <c r="H18" s="75"/>
-      <c r="I18" s="75"/>
+      <c r="C18" s="71"/>
+      <c r="D18" s="71"/>
       <c r="J18" s="11">
         <f>SUM(E18*1/3,F18*1/3,H18*1/3)</f>
         <v>0</v>
@@ -5009,13 +4836,8 @@
       <c r="B19" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C19" s="67"/>
-      <c r="D19" s="67"/>
-      <c r="E19" s="75"/>
-      <c r="F19" s="75"/>
-      <c r="G19" s="75"/>
-      <c r="H19" s="75"/>
-      <c r="I19" s="75"/>
+      <c r="C19" s="71"/>
+      <c r="D19" s="71"/>
       <c r="J19" s="11">
         <f>SUM(E19*1/3,F19*1/3,H19*1/3)</f>
         <v>0</v>
@@ -5031,11 +4853,6 @@
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C20" s="50"/>
-      <c r="E20" s="75"/>
-      <c r="F20" s="75"/>
-      <c r="G20" s="75"/>
-      <c r="H20" s="75"/>
-      <c r="I20" s="75"/>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
@@ -5044,17 +4861,12 @@
       <c r="B21" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C21" s="67" t="s">
+      <c r="C21" s="71" t="s">
+        <v>75</v>
+      </c>
+      <c r="D21" s="71" t="s">
         <v>76</v>
       </c>
-      <c r="D21" s="67" t="s">
-        <v>77</v>
-      </c>
-      <c r="E21" s="75"/>
-      <c r="F21" s="75"/>
-      <c r="G21" s="75"/>
-      <c r="H21" s="75"/>
-      <c r="I21" s="75"/>
       <c r="J21" s="11">
         <f>SUM(E21*1/3,F21*1/3,H21*1/3)</f>
         <v>0</v>
@@ -5075,13 +4887,8 @@
       <c r="B22" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C22" s="67"/>
-      <c r="D22" s="67"/>
-      <c r="E22" s="75"/>
-      <c r="F22" s="75"/>
-      <c r="G22" s="75"/>
-      <c r="H22" s="75"/>
-      <c r="I22" s="75"/>
+      <c r="C22" s="71"/>
+      <c r="D22" s="71"/>
       <c r="J22" s="11">
         <f>SUM(E22*1/3,F22*1/3,H22*1/3)</f>
         <v>0</v>
@@ -5102,13 +4909,8 @@
       <c r="B23" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C23" s="67"/>
-      <c r="D23" s="67"/>
-      <c r="E23" s="75"/>
-      <c r="F23" s="75"/>
-      <c r="G23" s="75"/>
-      <c r="H23" s="75"/>
-      <c r="I23" s="75"/>
+      <c r="C23" s="71"/>
+      <c r="D23" s="71"/>
       <c r="J23" s="11">
         <f>SUM(E23*1/3,F23*1/3,H23*1/3)</f>
         <v>0</v>
@@ -5121,13 +4923,6 @@
         <f>SUM(E23*1/5,F23*1/5,G23*1/5,H23*1/5,I23*1/5)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="E24" s="75"/>
-      <c r="F24" s="75"/>
-      <c r="G24" s="75"/>
-      <c r="H24" s="75"/>
-      <c r="I24" s="75"/>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
@@ -5136,17 +4931,12 @@
       <c r="B25" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C25" s="67" t="s">
-        <v>81</v>
-      </c>
-      <c r="D25" s="67" t="s">
-        <v>79</v>
-      </c>
-      <c r="E25" s="75"/>
-      <c r="F25" s="75"/>
-      <c r="G25" s="75"/>
-      <c r="H25" s="75"/>
-      <c r="I25" s="75"/>
+      <c r="C25" s="71" t="s">
+        <v>80</v>
+      </c>
+      <c r="D25" s="71" t="s">
+        <v>78</v>
+      </c>
       <c r="J25" s="11">
         <f>SUM(E25*1/3,F25*1/3,H25*1/3)</f>
         <v>0</v>
@@ -5167,13 +4957,8 @@
       <c r="B26" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C26" s="67"/>
-      <c r="D26" s="67"/>
-      <c r="E26" s="75"/>
-      <c r="F26" s="75"/>
-      <c r="G26" s="75"/>
-      <c r="H26" s="75"/>
-      <c r="I26" s="75"/>
+      <c r="C26" s="71"/>
+      <c r="D26" s="71"/>
       <c r="J26" s="11">
         <f>SUM(E26*1/3,F26*1/3,H26*1/3)</f>
         <v>0</v>
@@ -5194,13 +4979,8 @@
       <c r="B27" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C27" s="67"/>
-      <c r="D27" s="67"/>
-      <c r="E27" s="75"/>
-      <c r="F27" s="75"/>
-      <c r="G27" s="75"/>
-      <c r="H27" s="75"/>
-      <c r="I27" s="75"/>
+      <c r="C27" s="71"/>
+      <c r="D27" s="71"/>
       <c r="J27" s="11">
         <f>SUM(E27*1/3,F27*1/3,H27*1/3)</f>
         <v>0</v>
@@ -5213,13 +4993,6 @@
         <f>SUM(E27*1/5,F27*1/5,G27*1/5,H27*1/5,I27*1/5)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="E28" s="75"/>
-      <c r="F28" s="75"/>
-      <c r="G28" s="75"/>
-      <c r="H28" s="75"/>
-      <c r="I28" s="75"/>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
@@ -5228,17 +5001,12 @@
       <c r="B29" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C29" s="67" t="s">
-        <v>82</v>
-      </c>
-      <c r="D29" s="67" t="s">
-        <v>80</v>
-      </c>
-      <c r="E29" s="75"/>
-      <c r="F29" s="75"/>
-      <c r="G29" s="75"/>
-      <c r="H29" s="75"/>
-      <c r="I29" s="75"/>
+      <c r="C29" s="71" t="s">
+        <v>81</v>
+      </c>
+      <c r="D29" s="71" t="s">
+        <v>79</v>
+      </c>
       <c r="J29" s="11">
         <f>SUM(E29*1/3,F29*1/3,H29*1/3)</f>
         <v>0</v>
@@ -5259,13 +5027,8 @@
       <c r="B30" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C30" s="67"/>
-      <c r="D30" s="67"/>
-      <c r="E30" s="75"/>
-      <c r="F30" s="75"/>
-      <c r="G30" s="75"/>
-      <c r="H30" s="75"/>
-      <c r="I30" s="75"/>
+      <c r="C30" s="71"/>
+      <c r="D30" s="71"/>
       <c r="J30" s="11">
         <f>SUM(E30*1/3,F30*1/3,H30*1/3)</f>
         <v>0</v>
@@ -5286,13 +5049,8 @@
       <c r="B31" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C31" s="67"/>
-      <c r="D31" s="67"/>
-      <c r="E31" s="75"/>
-      <c r="F31" s="75"/>
-      <c r="G31" s="75"/>
-      <c r="H31" s="75"/>
-      <c r="I31" s="75"/>
+      <c r="C31" s="71"/>
+      <c r="D31" s="71"/>
       <c r="J31" s="11">
         <f>SUM(E31*1/3,F31*1/3,H31*1/3)</f>
         <v>0</v>
@@ -5306,92 +5064,85 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="E32" s="75"/>
-      <c r="F32" s="75"/>
-      <c r="G32" s="75"/>
-      <c r="H32" s="75"/>
-      <c r="I32" s="75"/>
-    </row>
     <row r="34" spans="1:14" s="14" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="68" t="s">
-        <v>60</v>
-      </c>
-      <c r="B34" s="68"/>
-      <c r="C34" s="68"/>
-      <c r="D34" s="68"/>
+      <c r="A34" s="72" t="s">
+        <v>59</v>
+      </c>
+      <c r="B34" s="72"/>
+      <c r="C34" s="72"/>
+      <c r="D34" s="72"/>
       <c r="E34" s="16">
-        <f>MAX(E4:E32)</f>
+        <f t="shared" ref="E34:L34" si="0">MAX(E4:E32)</f>
         <v>0</v>
       </c>
       <c r="F34" s="16">
-        <f>MAX(F4:F32)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="G34" s="16">
-        <f>MAX(G4:G32)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H34" s="16">
-        <f>MAX(H4:H32)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="I34" s="16">
-        <f>MAX(I4:I32)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J34" s="16">
-        <f>MAX(J4:J32)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K34" s="16">
-        <f>MAX(K4:K32)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="L34" s="16">
-        <f>MAX(L4:L32)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="M34" s="16"/>
       <c r="N34" s="17"/>
     </row>
     <row r="35" spans="1:14" s="52" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="72" t="s">
-        <v>61</v>
-      </c>
-      <c r="B35" s="72"/>
-      <c r="C35" s="72"/>
-      <c r="D35" s="72"/>
+      <c r="A35" s="77" t="s">
+        <v>60</v>
+      </c>
+      <c r="B35" s="77"/>
+      <c r="C35" s="77"/>
+      <c r="D35" s="77"/>
       <c r="E35" s="29" t="e">
-        <f>AVERAGE(E5:E32)</f>
+        <f t="shared" ref="E35:L35" si="1">AVERAGE(E5:E32)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="F35" s="29" t="e">
-        <f>AVERAGE(F5:F32)</f>
+        <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G35" s="29" t="e">
-        <f>AVERAGE(G5:G32)</f>
+        <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H35" s="29" t="e">
-        <f>AVERAGE(H5:H32)</f>
+        <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I35" s="29" t="e">
-        <f>AVERAGE(I5:I32)</f>
+        <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
       <c r="J35" s="29">
-        <f>AVERAGE(J5:J32)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="K35" s="29">
-        <f>AVERAGE(K5:K32)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L35" s="29">
-        <f>AVERAGE(L5:L32)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="M35" s="29"/>

--- a/benchmarking/results/results.xlsx
+++ b/benchmarking/results/results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/deborahdore/Documents/political-debates-graph-analysis/benchmarking/results/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA9310B9-64F5-6341-A559-2DE829997205}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EF89D27-955F-D842-BBC2-48AFB651C750}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="21600" xr2:uid="{E2EDC037-19C4-FE46-A599-BB595128A04F}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="21600" activeTab="1" xr2:uid="{E2EDC037-19C4-FE46-A599-BB595128A04F}"/>
   </bookViews>
   <sheets>
     <sheet name="Results BASIC" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="470" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="470" uniqueCount="86">
   <si>
     <t>MODEL'S TYPE</t>
   </si>
@@ -310,10 +310,7 @@
     <t>experiment with basic sampler and downsampling the major class</t>
   </si>
   <si>
-    <t>TRIPLE CLASSIFICATION F1-WEIGHTED</t>
-  </si>
-  <si>
-    <t>RELATION CLASSIFICATION  F1-WEIGHTED</t>
+    <t>RELATION CLASSIFICATION  F1-MACRO</t>
   </si>
 </sst>
 </file>
@@ -662,55 +659,55 @@
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1077,10 +1074,10 @@
         <v>55</v>
       </c>
       <c r="I1" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="J1" s="12" t="s">
         <v>85</v>
-      </c>
-      <c r="J1" s="12" t="s">
-        <v>86</v>
       </c>
       <c r="K1" s="7" t="s">
         <v>14</v>
@@ -1094,7 +1091,7 @@
       <c r="B2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="68" t="s">
+      <c r="C2" s="70" t="s">
         <v>41</v>
       </c>
       <c r="D2" s="67" t="s">
@@ -1113,12 +1110,12 @@
         <v>0.44467881110000002</v>
       </c>
       <c r="I2" s="11">
-        <v>0.57438833690000002</v>
+        <v>0.54650166659999999</v>
       </c>
       <c r="J2" s="11">
-        <v>0.56363568119999996</v>
-      </c>
-      <c r="K2" s="70" t="s">
+        <v>0.52440008120000003</v>
+      </c>
+      <c r="K2" s="65" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1129,9 +1126,9 @@
       <c r="B3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="64"/>
-      <c r="D3" s="65"/>
-      <c r="E3" s="65"/>
+      <c r="C3" s="68"/>
+      <c r="D3" s="64"/>
+      <c r="E3" s="64"/>
       <c r="F3" s="11">
         <v>3.9117929099999997E-2</v>
       </c>
@@ -1142,12 +1139,12 @@
         <v>0.38044103550000002</v>
       </c>
       <c r="I3" s="11">
-        <v>0.53542729820000001</v>
+        <v>0.51528577320000002</v>
       </c>
       <c r="J3" s="11">
-        <v>0.52549201359999997</v>
-      </c>
-      <c r="K3" s="71"/>
+        <v>0.4957882649</v>
+      </c>
+      <c r="K3" s="66"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
@@ -1156,9 +1153,9 @@
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="64"/>
-      <c r="D4" s="65"/>
-      <c r="E4" s="65"/>
+      <c r="C4" s="68"/>
+      <c r="D4" s="64"/>
+      <c r="E4" s="64"/>
       <c r="F4" s="11">
         <v>2.1093001000000002E-3</v>
       </c>
@@ -1169,12 +1166,12 @@
         <v>0.43509108340000002</v>
       </c>
       <c r="I4" s="11">
-        <v>0.58024751610000003</v>
+        <v>0.56100031829999997</v>
       </c>
       <c r="J4" s="11">
-        <v>0.4978749918</v>
-      </c>
-      <c r="K4" s="71"/>
+        <v>0.4776301698</v>
+      </c>
+      <c r="K4" s="66"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
@@ -1183,13 +1180,13 @@
       <c r="B6" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="64" t="s">
+      <c r="C6" s="68" t="s">
         <v>42</v>
       </c>
-      <c r="D6" s="65" t="s">
+      <c r="D6" s="64" t="s">
         <v>10</v>
       </c>
-      <c r="E6" s="65" t="s">
+      <c r="E6" s="64" t="s">
         <v>13</v>
       </c>
       <c r="F6" s="11">
@@ -1202,12 +1199,12 @@
         <v>0.36232994829999998</v>
       </c>
       <c r="I6" s="11">
-        <v>0.53999942830000003</v>
+        <v>0.52680552849999995</v>
       </c>
       <c r="J6" s="11">
-        <v>0.54077441869999998</v>
-      </c>
-      <c r="K6" s="71" t="s">
+        <v>0.51801477490000003</v>
+      </c>
+      <c r="K6" s="66" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1218,9 +1215,9 @@
       <c r="B7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="64"/>
-      <c r="D7" s="65"/>
-      <c r="E7" s="65"/>
+      <c r="C7" s="68"/>
+      <c r="D7" s="64"/>
+      <c r="E7" s="64"/>
       <c r="F7" s="11">
         <v>3.2094270899999999E-2</v>
       </c>
@@ -1231,12 +1228,12 @@
         <v>0.35351599919999999</v>
       </c>
       <c r="I7" s="11">
-        <v>0.5349605033</v>
+        <v>0.51165179900000002</v>
       </c>
       <c r="J7" s="11">
-        <v>0.53556060419999996</v>
-      </c>
-      <c r="K7" s="71"/>
+        <v>0.50083099880000004</v>
+      </c>
+      <c r="K7" s="66"/>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
@@ -1245,9 +1242,9 @@
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="64"/>
-      <c r="D8" s="65"/>
-      <c r="E8" s="65"/>
+      <c r="C8" s="68"/>
+      <c r="D8" s="64"/>
+      <c r="E8" s="64"/>
       <c r="F8" s="11">
         <v>2.8741139999999998E-4</v>
       </c>
@@ -1258,20 +1255,20 @@
         <v>0.4696301974</v>
       </c>
       <c r="I8" s="11">
-        <v>0.56417524429999999</v>
+        <v>0.54079702780000005</v>
       </c>
       <c r="J8" s="11">
-        <v>0.518358965</v>
-      </c>
-      <c r="K8" s="71"/>
+        <v>0.4887305689</v>
+      </c>
+      <c r="K8" s="66"/>
     </row>
     <row r="10" spans="1:12" s="59" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="66" t="s">
+      <c r="A10" s="69" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="66"/>
-      <c r="C10" s="66"/>
-      <c r="D10" s="66"/>
+      <c r="B10" s="69"/>
+      <c r="C10" s="69"/>
+      <c r="D10" s="69"/>
       <c r="E10" s="60"/>
       <c r="F10" s="61"/>
       <c r="G10" s="61"/>
@@ -1287,13 +1284,13 @@
       <c r="B12" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C12" s="64" t="s">
+      <c r="C12" s="68" t="s">
         <v>43</v>
       </c>
-      <c r="D12" s="65" t="s">
+      <c r="D12" s="64" t="s">
         <v>11</v>
       </c>
-      <c r="E12" s="65" t="s">
+      <c r="E12" s="64" t="s">
         <v>17</v>
       </c>
       <c r="F12" s="11">
@@ -1306,12 +1303,12 @@
         <v>0.51319648090000003</v>
       </c>
       <c r="I12" s="11">
-        <v>0.67925847319999999</v>
+        <v>0.66492071900000005</v>
       </c>
       <c r="J12" s="11">
-        <v>0.7111340854</v>
-      </c>
-      <c r="K12" s="71" t="s">
+        <v>0.65087326729999995</v>
+      </c>
+      <c r="K12" s="66" t="s">
         <v>18</v>
       </c>
     </row>
@@ -1322,9 +1319,9 @@
       <c r="B13" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C13" s="64"/>
-      <c r="D13" s="65"/>
-      <c r="E13" s="65"/>
+      <c r="C13" s="68"/>
+      <c r="D13" s="64"/>
+      <c r="E13" s="64"/>
       <c r="F13" s="11">
         <v>1.0937623800000001E-2</v>
       </c>
@@ -1335,12 +1332,12 @@
         <v>0.33597527150000001</v>
       </c>
       <c r="I13" s="11">
-        <v>0.48911294719999998</v>
+        <v>0.48085677599999999</v>
       </c>
       <c r="J13" s="11">
-        <v>0.54478313199999995</v>
-      </c>
-      <c r="K13" s="71"/>
+        <v>0.48031703009999999</v>
+      </c>
+      <c r="K13" s="66"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
@@ -1349,9 +1346,9 @@
       <c r="B14" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C14" s="64"/>
-      <c r="D14" s="65"/>
-      <c r="E14" s="65"/>
+      <c r="C14" s="68"/>
+      <c r="D14" s="64"/>
+      <c r="E14" s="64"/>
       <c r="F14" s="11">
         <v>2.377744E-4</v>
       </c>
@@ -1362,12 +1359,12 @@
         <v>0.99643338349999999</v>
       </c>
       <c r="I14" s="11">
-        <v>0.4136900905</v>
+        <v>0.38529727969999999</v>
       </c>
       <c r="J14" s="11">
-        <v>0.60797287919999998</v>
-      </c>
-      <c r="K14" s="71"/>
+        <v>0.49770047779999999</v>
+      </c>
+      <c r="K14" s="66"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
@@ -1376,16 +1373,16 @@
       <c r="B16" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C16" s="64" t="s">
+      <c r="C16" s="68" t="s">
         <v>44</v>
       </c>
-      <c r="D16" s="65" t="s">
+      <c r="D16" s="64" t="s">
         <v>19</v>
       </c>
-      <c r="E16" s="65" t="s">
+      <c r="E16" s="64" t="s">
         <v>27</v>
       </c>
-      <c r="K16" s="71" t="s">
+      <c r="K16" s="66" t="s">
         <v>36</v>
       </c>
     </row>
@@ -1396,10 +1393,10 @@
       <c r="B17" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C17" s="64"/>
-      <c r="D17" s="65"/>
-      <c r="E17" s="65"/>
-      <c r="K17" s="71"/>
+      <c r="C17" s="68"/>
+      <c r="D17" s="64"/>
+      <c r="E17" s="64"/>
+      <c r="K17" s="66"/>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
@@ -1408,10 +1405,10 @@
       <c r="B18" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C18" s="64"/>
-      <c r="D18" s="65"/>
-      <c r="E18" s="65"/>
-      <c r="K18" s="71"/>
+      <c r="C18" s="68"/>
+      <c r="D18" s="64"/>
+      <c r="E18" s="64"/>
+      <c r="K18" s="66"/>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
@@ -1420,13 +1417,13 @@
       <c r="B20" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C20" s="64" t="s">
+      <c r="C20" s="68" t="s">
         <v>45</v>
       </c>
-      <c r="D20" s="65" t="s">
+      <c r="D20" s="64" t="s">
         <v>20</v>
       </c>
-      <c r="E20" s="65" t="s">
+      <c r="E20" s="64" t="s">
         <v>28</v>
       </c>
       <c r="F20" s="11">
@@ -1444,7 +1441,7 @@
       <c r="J20" s="11">
         <v>0.42558258160000001</v>
       </c>
-      <c r="K20" s="71" t="s">
+      <c r="K20" s="66" t="s">
         <v>35</v>
       </c>
     </row>
@@ -1455,9 +1452,9 @@
       <c r="B21" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C21" s="64"/>
-      <c r="D21" s="65"/>
-      <c r="E21" s="65"/>
+      <c r="C21" s="68"/>
+      <c r="D21" s="64"/>
+      <c r="E21" s="64"/>
       <c r="F21" s="11">
         <v>0.36964094320000002</v>
       </c>
@@ -1468,12 +1465,12 @@
         <v>0.63594140759999995</v>
       </c>
       <c r="I21" s="11">
-        <v>0.85885026710000001</v>
+        <v>0.84374597640000004</v>
       </c>
       <c r="J21" s="11">
-        <v>0.7749568309</v>
-      </c>
-      <c r="K21" s="71"/>
+        <v>0.71370811339999995</v>
+      </c>
+      <c r="K21" s="66"/>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
@@ -1482,9 +1479,9 @@
       <c r="B22" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C22" s="64"/>
-      <c r="D22" s="65"/>
-      <c r="E22" s="65"/>
+      <c r="C22" s="68"/>
+      <c r="D22" s="64"/>
+      <c r="E22" s="64"/>
       <c r="F22" s="11">
         <v>1.786352E-4</v>
       </c>
@@ -1495,12 +1492,12 @@
         <v>4.60878885E-2</v>
       </c>
       <c r="I22" s="11">
-        <v>0.55591291340000004</v>
+        <v>0.55456118539999999</v>
       </c>
       <c r="J22" s="11">
-        <v>0.35294220799999998</v>
-      </c>
-      <c r="K22" s="71"/>
+        <v>0.35677707139999998</v>
+      </c>
+      <c r="K22" s="66"/>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
@@ -1509,13 +1506,13 @@
       <c r="B24" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C24" s="64" t="s">
+      <c r="C24" s="68" t="s">
         <v>46</v>
       </c>
-      <c r="D24" s="65" t="s">
+      <c r="D24" s="64" t="s">
         <v>21</v>
       </c>
-      <c r="E24" s="65" t="s">
+      <c r="E24" s="64" t="s">
         <v>32</v>
       </c>
       <c r="F24" s="11">
@@ -1528,10 +1525,10 @@
         <v>0.74541139239999998</v>
       </c>
       <c r="I24" s="11">
-        <v>0.84871145309999996</v>
+        <v>0.84123693610000005</v>
       </c>
       <c r="J24" s="11">
-        <v>0.80021173410000002</v>
+        <v>0.70529922560000002</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.2">
@@ -1541,9 +1538,9 @@
       <c r="B25" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C25" s="64"/>
-      <c r="D25" s="65"/>
-      <c r="E25" s="65"/>
+      <c r="C25" s="68"/>
+      <c r="D25" s="64"/>
+      <c r="E25" s="64"/>
       <c r="F25" s="11">
         <v>2.2257384000000002E-2</v>
       </c>
@@ -1554,10 +1551,10 @@
         <v>0.36339662449999999</v>
       </c>
       <c r="I25" s="11">
-        <v>0.57537618469999996</v>
+        <v>0.56503944530000005</v>
       </c>
       <c r="J25" s="11">
-        <v>0.63357712190000004</v>
+        <v>0.50280775200000005</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.2">
@@ -1567,9 +1564,9 @@
       <c r="B26" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C26" s="64"/>
-      <c r="D26" s="65"/>
-      <c r="E26" s="65"/>
+      <c r="C26" s="68"/>
+      <c r="D26" s="64"/>
+      <c r="E26" s="64"/>
       <c r="F26" s="11">
         <v>3.9556960000000001E-4</v>
       </c>
@@ -1580,10 +1577,10 @@
         <v>1</v>
       </c>
       <c r="I26" s="11">
-        <v>0.79791006350000004</v>
+        <v>0.78779105299999996</v>
       </c>
       <c r="J26" s="11">
-        <v>0.27747491489999998</v>
+        <v>0.27760191880000001</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.2">
@@ -1593,13 +1590,13 @@
       <c r="B28" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C28" s="64" t="s">
+      <c r="C28" s="68" t="s">
         <v>47</v>
       </c>
-      <c r="D28" s="65" t="s">
+      <c r="D28" s="64" t="s">
         <v>22</v>
       </c>
-      <c r="E28" s="65" t="s">
+      <c r="E28" s="64" t="s">
         <v>33</v>
       </c>
       <c r="F28" s="11">
@@ -1612,10 +1609,10 @@
         <v>0.44531670070000001</v>
       </c>
       <c r="I28" s="11">
-        <v>0.7989096738</v>
+        <v>0.79220231240000005</v>
       </c>
       <c r="J28" s="11">
-        <v>0.60950750590000002</v>
+        <v>0.53978133429999997</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.2">
@@ -1625,9 +1622,9 @@
       <c r="B29" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C29" s="64"/>
-      <c r="D29" s="65"/>
-      <c r="E29" s="65"/>
+      <c r="C29" s="68"/>
+      <c r="D29" s="64"/>
+      <c r="E29" s="64"/>
       <c r="F29" s="11">
         <v>1.8442843300000001E-2</v>
       </c>
@@ -1638,10 +1635,10 @@
         <v>0.35874825249999998</v>
       </c>
       <c r="I29" s="11">
-        <v>0.59498168819999997</v>
+        <v>0.58555127210000002</v>
       </c>
       <c r="J29" s="11">
-        <v>0.62220035299999998</v>
+        <v>0.52262452000000004</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.2">
@@ -1651,9 +1648,9 @@
       <c r="B30" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C30" s="64"/>
-      <c r="D30" s="65"/>
-      <c r="E30" s="65"/>
+      <c r="C30" s="68"/>
+      <c r="D30" s="64"/>
+      <c r="E30" s="64"/>
       <c r="F30" s="11">
         <v>6.9899990000000004E-4</v>
       </c>
@@ -1664,10 +1661,10 @@
         <v>1</v>
       </c>
       <c r="I30" s="11">
-        <v>0.76702944120000005</v>
+        <v>0.75475396159999997</v>
       </c>
       <c r="J30" s="11">
-        <v>0.27796758100000002</v>
+        <v>0.29488310699999998</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.2">
@@ -1677,13 +1674,13 @@
       <c r="B32" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C32" s="64" t="s">
+      <c r="C32" s="68" t="s">
         <v>48</v>
       </c>
-      <c r="D32" s="65" t="s">
+      <c r="D32" s="64" t="s">
         <v>23</v>
       </c>
-      <c r="E32" s="65" t="s">
+      <c r="E32" s="64" t="s">
         <v>29</v>
       </c>
       <c r="F32" s="11">
@@ -1696,10 +1693,10 @@
         <v>0.52434285709999995</v>
       </c>
       <c r="I32" s="11">
-        <v>0.88386083839999996</v>
+        <v>0.87609028769999997</v>
       </c>
       <c r="J32" s="11">
-        <v>0.51603915860000005</v>
+        <v>0.45148898980000002</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.2">
@@ -1709,9 +1706,9 @@
       <c r="B33" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C33" s="64"/>
-      <c r="D33" s="65"/>
-      <c r="E33" s="65"/>
+      <c r="C33" s="68"/>
+      <c r="D33" s="64"/>
+      <c r="E33" s="64"/>
       <c r="F33" s="11">
         <v>4.8571429999999999E-4</v>
       </c>
@@ -1722,10 +1719,10 @@
         <v>7.5257142900000004E-2</v>
       </c>
       <c r="I33" s="11">
-        <v>0.51078131569999996</v>
+        <v>0.49477284040000002</v>
       </c>
       <c r="J33" s="11">
-        <v>0.56004145900000002</v>
+        <v>0.43843272950000001</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.2">
@@ -1735,9 +1732,9 @@
       <c r="B34" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C34" s="64"/>
-      <c r="D34" s="65"/>
-      <c r="E34" s="65"/>
+      <c r="C34" s="68"/>
+      <c r="D34" s="64"/>
+      <c r="E34" s="64"/>
       <c r="F34" s="11">
         <v>8.5714299999999993E-5</v>
       </c>
@@ -1748,10 +1745,10 @@
         <v>1</v>
       </c>
       <c r="I34" s="11">
-        <v>0.7444025527</v>
+        <v>0.7350538727</v>
       </c>
       <c r="J34" s="11">
-        <v>0.28967926030000002</v>
+        <v>0.28468339840000001</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.2">
@@ -1761,13 +1758,13 @@
       <c r="B36" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C36" s="64" t="s">
+      <c r="C36" s="68" t="s">
         <v>49</v>
       </c>
-      <c r="D36" s="65" t="s">
+      <c r="D36" s="64" t="s">
         <v>24</v>
       </c>
-      <c r="E36" s="65" t="s">
+      <c r="E36" s="64" t="s">
         <v>34</v>
       </c>
       <c r="F36" s="11">
@@ -1780,10 +1777,10 @@
         <v>0.49388556989999999</v>
       </c>
       <c r="I36" s="11">
-        <v>0.81622520009999999</v>
+        <v>0.79988943899999998</v>
       </c>
       <c r="J36" s="11">
-        <v>0.68215240119999998</v>
+        <v>0.56712002669999995</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.2">
@@ -1793,9 +1790,9 @@
       <c r="B37" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C37" s="64"/>
-      <c r="D37" s="65"/>
-      <c r="E37" s="65"/>
+      <c r="C37" s="68"/>
+      <c r="D37" s="64"/>
+      <c r="E37" s="64"/>
       <c r="F37" s="11">
         <v>0.12567659680000001</v>
       </c>
@@ -1806,10 +1803,10 @@
         <v>0.55410769419999995</v>
       </c>
       <c r="I37" s="11">
-        <v>0.69175754229999997</v>
+        <v>0.68580146590000002</v>
       </c>
       <c r="J37" s="11">
-        <v>0.83367986199999999</v>
+        <v>0.68997979440000001</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.2">
@@ -1819,9 +1816,9 @@
       <c r="B38" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C38" s="64"/>
-      <c r="D38" s="65"/>
-      <c r="E38" s="65"/>
+      <c r="C38" s="68"/>
+      <c r="D38" s="64"/>
+      <c r="E38" s="64"/>
       <c r="F38" s="11">
         <v>5.4127739999999998E-4</v>
       </c>
@@ -1832,19 +1829,19 @@
         <v>1</v>
       </c>
       <c r="I38" s="11">
-        <v>0.83321648010000005</v>
+        <v>0.82154033039999996</v>
       </c>
       <c r="J38" s="11">
-        <v>0.24805656309999999</v>
+        <v>0.24669741079999999</v>
       </c>
     </row>
     <row r="40" spans="1:11" s="59" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="66" t="s">
+      <c r="A40" s="69" t="s">
         <v>38</v>
       </c>
-      <c r="B40" s="66"/>
-      <c r="C40" s="66"/>
-      <c r="D40" s="66"/>
+      <c r="B40" s="69"/>
+      <c r="C40" s="69"/>
+      <c r="D40" s="69"/>
       <c r="E40" s="60"/>
       <c r="F40" s="61"/>
       <c r="G40" s="61"/>
@@ -1860,13 +1857,13 @@
       <c r="B42" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C42" s="64" t="s">
+      <c r="C42" s="68" t="s">
         <v>50</v>
       </c>
-      <c r="D42" s="65" t="s">
+      <c r="D42" s="64" t="s">
         <v>25</v>
       </c>
-      <c r="E42" s="65" t="s">
+      <c r="E42" s="64" t="s">
         <v>27</v>
       </c>
       <c r="F42" s="11">
@@ -1879,12 +1876,12 @@
         <v>0.46154452950000002</v>
       </c>
       <c r="I42" s="11">
-        <v>0.74200403739999998</v>
+        <v>0.74483595489999999</v>
       </c>
       <c r="J42" s="11">
-        <v>0.57024913060000004</v>
-      </c>
-      <c r="K42" s="71" t="s">
+        <v>0.47978398890000001</v>
+      </c>
+      <c r="K42" s="66" t="s">
         <v>30</v>
       </c>
     </row>
@@ -1895,9 +1892,9 @@
       <c r="B43" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C43" s="64"/>
-      <c r="D43" s="65"/>
-      <c r="E43" s="65"/>
+      <c r="C43" s="68"/>
+      <c r="D43" s="64"/>
+      <c r="E43" s="64"/>
       <c r="F43" s="11">
         <v>0.15768715</v>
       </c>
@@ -1908,12 +1905,12 @@
         <v>0.52638636900000002</v>
       </c>
       <c r="I43" s="11">
-        <v>0.69545189539999996</v>
+        <v>0.69569912779999998</v>
       </c>
       <c r="J43" s="11">
-        <v>0.7451035896</v>
-      </c>
-      <c r="K43" s="71"/>
+        <v>0.64265883619999997</v>
+      </c>
+      <c r="K43" s="66"/>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
@@ -1922,9 +1919,9 @@
       <c r="B44" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C44" s="64"/>
-      <c r="D44" s="65"/>
-      <c r="E44" s="65"/>
+      <c r="C44" s="68"/>
+      <c r="D44" s="64"/>
+      <c r="E44" s="64"/>
       <c r="F44" s="11">
         <v>1.5776599999999999E-4</v>
       </c>
@@ -1935,12 +1932,12 @@
         <v>1</v>
       </c>
       <c r="I44" s="11">
-        <v>0.76069328420000004</v>
+        <v>0.75793743489999998</v>
       </c>
       <c r="J44" s="11">
-        <v>0.35300280709999998</v>
-      </c>
-      <c r="K44" s="71"/>
+        <v>0.33957444949999999</v>
+      </c>
+      <c r="K44" s="66"/>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
@@ -1949,13 +1946,13 @@
       <c r="B46" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C46" s="64" t="s">
+      <c r="C46" s="68" t="s">
         <v>51</v>
       </c>
-      <c r="D46" s="65" t="s">
+      <c r="D46" s="64" t="s">
         <v>26</v>
       </c>
-      <c r="E46" s="65" t="s">
+      <c r="E46" s="64" t="s">
         <v>28</v>
       </c>
       <c r="F46" s="11">
@@ -1968,12 +1965,12 @@
         <v>0.69543948239999998</v>
       </c>
       <c r="I46" s="11">
-        <v>0.76689637619999995</v>
+        <v>0.76948813009999995</v>
       </c>
       <c r="J46" s="11">
-        <v>0.47753796059999998</v>
-      </c>
-      <c r="K46" s="71" t="s">
+        <v>0.43650638670000003</v>
+      </c>
+      <c r="K46" s="66" t="s">
         <v>31</v>
       </c>
     </row>
@@ -1984,9 +1981,9 @@
       <c r="B47" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C47" s="64"/>
-      <c r="D47" s="65"/>
-      <c r="E47" s="65"/>
+      <c r="C47" s="68"/>
+      <c r="D47" s="64"/>
+      <c r="E47" s="64"/>
       <c r="F47" s="11">
         <v>0.28846457310000001</v>
       </c>
@@ -1997,12 +1994,12 @@
         <v>0.62947767080000006</v>
       </c>
       <c r="I47" s="11">
-        <v>0.73420197409999999</v>
+        <v>0.73463845350000001</v>
       </c>
       <c r="J47" s="11">
-        <v>0.69566912999999997</v>
-      </c>
-      <c r="K47" s="71"/>
+        <v>0.62979789600000002</v>
+      </c>
+      <c r="K47" s="66"/>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
@@ -2011,9 +2008,9 @@
       <c r="B48" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C48" s="64"/>
-      <c r="D48" s="65"/>
-      <c r="E48" s="65"/>
+      <c r="C48" s="68"/>
+      <c r="D48" s="64"/>
+      <c r="E48" s="64"/>
       <c r="F48" s="11">
         <v>2.7615590000000002E-4</v>
       </c>
@@ -2024,12 +2021,12 @@
         <v>0.59902161909999996</v>
       </c>
       <c r="I48" s="11">
-        <v>0.69778750060000005</v>
+        <v>0.69259024489999998</v>
       </c>
       <c r="J48" s="11">
-        <v>0.40179085320000002</v>
-      </c>
-      <c r="K48" s="71"/>
+        <v>0.39453545410000002</v>
+      </c>
+      <c r="K48" s="66"/>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
@@ -2038,13 +2035,13 @@
       <c r="B50" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C50" s="64" t="s">
+      <c r="C50" s="68" t="s">
         <v>52</v>
       </c>
-      <c r="D50" s="65" t="s">
+      <c r="D50" s="64" t="s">
         <v>39</v>
       </c>
-      <c r="E50" s="65" t="s">
+      <c r="E50" s="64" t="s">
         <v>29</v>
       </c>
       <c r="F50" s="11">
@@ -2057,10 +2054,10 @@
         <v>0.66992847209999995</v>
       </c>
       <c r="I50" s="11">
-        <v>0.84746806279999998</v>
+        <v>0.8383940621</v>
       </c>
       <c r="J50" s="11">
-        <v>0.67688287540000003</v>
+        <v>0.58076474560000002</v>
       </c>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.2">
@@ -2070,9 +2067,9 @@
       <c r="B51" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C51" s="64"/>
-      <c r="D51" s="65"/>
-      <c r="E51" s="65"/>
+      <c r="C51" s="68"/>
+      <c r="D51" s="64"/>
+      <c r="E51" s="64"/>
       <c r="F51" s="11">
         <v>3.5391416699999997E-2</v>
       </c>
@@ -2083,10 +2080,10 @@
         <v>0.54530101330000003</v>
       </c>
       <c r="I51" s="11">
-        <v>0.70820905810000001</v>
+        <v>0.68842329739999997</v>
       </c>
       <c r="J51" s="11">
-        <v>0.77551452759999995</v>
+        <v>0.64893773720000003</v>
       </c>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.2">
@@ -2096,9 +2093,9 @@
       <c r="B52" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C52" s="64"/>
-      <c r="D52" s="65"/>
-      <c r="E52" s="65"/>
+      <c r="C52" s="68"/>
+      <c r="D52" s="64"/>
+      <c r="E52" s="64"/>
       <c r="F52" s="11">
         <v>9.9344299999999997E-5</v>
       </c>
@@ -2109,19 +2106,19 @@
         <v>8.3945957000000002E-3</v>
       </c>
       <c r="I52" s="11">
-        <v>0.1434131324</v>
+        <v>0.14927075749999999</v>
       </c>
       <c r="J52" s="11">
-        <v>0.69463278129999995</v>
+        <v>0.49504548949999999</v>
       </c>
     </row>
     <row r="55" spans="1:11" s="42" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="63" t="s">
+      <c r="A55" s="71" t="s">
         <v>59</v>
       </c>
-      <c r="B55" s="63"/>
-      <c r="C55" s="63"/>
-      <c r="D55" s="63"/>
+      <c r="B55" s="71"/>
+      <c r="C55" s="71"/>
+      <c r="D55" s="71"/>
       <c r="E55" s="39"/>
       <c r="F55" s="40">
         <f>MAX(F2:F52)</f>
@@ -2137,21 +2134,21 @@
       </c>
       <c r="I55" s="40">
         <f>MAX(I2:I52)</f>
-        <v>0.88386083839999996</v>
+        <v>0.87609028769999997</v>
       </c>
       <c r="J55" s="40">
         <f>MAX(J2:J52)</f>
-        <v>0.83367986199999999</v>
+        <v>0.71370811339999995</v>
       </c>
       <c r="K55" s="41"/>
     </row>
     <row r="56" spans="1:11" s="46" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="69" t="s">
+      <c r="A56" s="63" t="s">
         <v>60</v>
       </c>
-      <c r="B56" s="69"/>
-      <c r="C56" s="69"/>
-      <c r="D56" s="69"/>
+      <c r="B56" s="63"/>
+      <c r="C56" s="63"/>
+      <c r="D56" s="63"/>
       <c r="E56" s="43"/>
       <c r="F56" s="44">
         <f>AVERAGE(F2:F52)</f>
@@ -2167,16 +2164,47 @@
       </c>
       <c r="I56" s="44">
         <f>AVERAGE(I2:I52)</f>
-        <v>0.67128798901212117</v>
+        <v>0.66089750283333337</v>
       </c>
       <c r="J56" s="44">
         <f>AVERAGE(J2:J52)</f>
-        <v>0.55575878672727275</v>
+        <v>0.49391995730606059</v>
       </c>
       <c r="K56" s="45"/>
     </row>
   </sheetData>
   <mergeCells count="47">
+    <mergeCell ref="A55:D55"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="C12:C14"/>
+    <mergeCell ref="C16:C18"/>
+    <mergeCell ref="C20:C22"/>
+    <mergeCell ref="C24:C26"/>
+    <mergeCell ref="C50:C52"/>
+    <mergeCell ref="D24:D26"/>
+    <mergeCell ref="D28:D30"/>
+    <mergeCell ref="D32:D34"/>
+    <mergeCell ref="D36:D38"/>
+    <mergeCell ref="D42:D44"/>
+    <mergeCell ref="D46:D48"/>
+    <mergeCell ref="D50:D52"/>
+    <mergeCell ref="A40:D40"/>
+    <mergeCell ref="D2:D4"/>
+    <mergeCell ref="D6:D8"/>
+    <mergeCell ref="D12:D14"/>
+    <mergeCell ref="D16:D18"/>
+    <mergeCell ref="D20:D22"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="C2:C4"/>
+    <mergeCell ref="E12:E14"/>
+    <mergeCell ref="E16:E18"/>
+    <mergeCell ref="E20:E22"/>
+    <mergeCell ref="C42:C44"/>
+    <mergeCell ref="C46:C48"/>
+    <mergeCell ref="C28:C30"/>
+    <mergeCell ref="C32:C34"/>
+    <mergeCell ref="C36:C38"/>
+    <mergeCell ref="E46:E48"/>
     <mergeCell ref="A56:D56"/>
     <mergeCell ref="E50:E52"/>
     <mergeCell ref="K2:K4"/>
@@ -2193,37 +2221,6 @@
     <mergeCell ref="E42:E44"/>
     <mergeCell ref="E2:E4"/>
     <mergeCell ref="E6:E8"/>
-    <mergeCell ref="E12:E14"/>
-    <mergeCell ref="E16:E18"/>
-    <mergeCell ref="E20:E22"/>
-    <mergeCell ref="C42:C44"/>
-    <mergeCell ref="C46:C48"/>
-    <mergeCell ref="C28:C30"/>
-    <mergeCell ref="C32:C34"/>
-    <mergeCell ref="C36:C38"/>
-    <mergeCell ref="E46:E48"/>
-    <mergeCell ref="D2:D4"/>
-    <mergeCell ref="D6:D8"/>
-    <mergeCell ref="D12:D14"/>
-    <mergeCell ref="D16:D18"/>
-    <mergeCell ref="D20:D22"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="C2:C4"/>
-    <mergeCell ref="A55:D55"/>
-    <mergeCell ref="C6:C8"/>
-    <mergeCell ref="C12:C14"/>
-    <mergeCell ref="C16:C18"/>
-    <mergeCell ref="C20:C22"/>
-    <mergeCell ref="C24:C26"/>
-    <mergeCell ref="C50:C52"/>
-    <mergeCell ref="D24:D26"/>
-    <mergeCell ref="D28:D30"/>
-    <mergeCell ref="D32:D34"/>
-    <mergeCell ref="D36:D38"/>
-    <mergeCell ref="D42:D44"/>
-    <mergeCell ref="D46:D48"/>
-    <mergeCell ref="D50:D52"/>
-    <mergeCell ref="A40:D40"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2291,7 +2288,7 @@
       <c r="B2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="68" t="s">
+      <c r="C2" s="70" t="s">
         <v>41</v>
       </c>
       <c r="D2" s="67" t="s">
@@ -2300,11 +2297,22 @@
       <c r="E2" s="67" t="s">
         <v>13</v>
       </c>
-      <c r="G2" s="11"/>
-      <c r="H2" s="11"/>
-      <c r="I2" s="11"/>
-      <c r="J2" s="11"/>
-      <c r="K2" s="70" t="s">
+      <c r="F2" s="11">
+        <v>7.4400767000000007E-2</v>
+      </c>
+      <c r="G2" s="11">
+        <v>1.8216682999999999E-3</v>
+      </c>
+      <c r="H2" s="11">
+        <v>0.3535953979</v>
+      </c>
+      <c r="I2" s="11">
+        <v>0.52455385129999998</v>
+      </c>
+      <c r="J2" s="11">
+        <v>0.5008326072</v>
+      </c>
+      <c r="K2" s="65" t="s">
         <v>15</v>
       </c>
     </row>
@@ -2315,14 +2323,25 @@
       <c r="B3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="64"/>
-      <c r="D3" s="65"/>
-      <c r="E3" s="65"/>
-      <c r="G3" s="11"/>
-      <c r="H3" s="11"/>
-      <c r="I3" s="11"/>
-      <c r="J3" s="11"/>
-      <c r="K3" s="71"/>
+      <c r="C3" s="68"/>
+      <c r="D3" s="64"/>
+      <c r="E3" s="64"/>
+      <c r="F3" s="11">
+        <v>2.8763183099999999E-2</v>
+      </c>
+      <c r="G3" s="11">
+        <v>1.0546500999999999E-3</v>
+      </c>
+      <c r="H3" s="11">
+        <v>0.3340364334</v>
+      </c>
+      <c r="I3" s="11">
+        <v>0.51946074129999997</v>
+      </c>
+      <c r="J3" s="11">
+        <v>0.49456959480000001</v>
+      </c>
+      <c r="K3" s="66"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
@@ -2331,14 +2350,25 @@
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="64"/>
-      <c r="D4" s="65"/>
-      <c r="E4" s="65"/>
-      <c r="G4" s="11"/>
-      <c r="H4" s="11"/>
-      <c r="I4" s="11"/>
-      <c r="J4" s="11"/>
-      <c r="K4" s="71"/>
+      <c r="C4" s="68"/>
+      <c r="D4" s="64"/>
+      <c r="E4" s="64"/>
+      <c r="F4" s="11">
+        <v>5.7526370000000003E-4</v>
+      </c>
+      <c r="G4" s="11">
+        <v>4.7938640000000002E-4</v>
+      </c>
+      <c r="H4" s="11">
+        <v>0.39041227229999997</v>
+      </c>
+      <c r="I4" s="11">
+        <v>0.54885855390000005</v>
+      </c>
+      <c r="J4" s="11">
+        <v>0.46208879800000002</v>
+      </c>
+      <c r="K4" s="66"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="G5" s="11"/>
@@ -2353,20 +2383,31 @@
       <c r="B6" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="64" t="s">
+      <c r="C6" s="68" t="s">
         <v>42</v>
       </c>
-      <c r="D6" s="65" t="s">
+      <c r="D6" s="64" t="s">
         <v>10</v>
       </c>
-      <c r="E6" s="65" t="s">
+      <c r="E6" s="64" t="s">
         <v>13</v>
       </c>
-      <c r="G6" s="11"/>
-      <c r="H6" s="11"/>
-      <c r="I6" s="11"/>
-      <c r="J6" s="11"/>
-      <c r="K6" s="71" t="s">
+      <c r="F6" s="11">
+        <v>4.5985821000000003E-2</v>
+      </c>
+      <c r="G6" s="11">
+        <v>5.0776010999999998E-3</v>
+      </c>
+      <c r="H6" s="11">
+        <v>0.3447020502</v>
+      </c>
+      <c r="I6" s="11">
+        <v>0.51933168490000003</v>
+      </c>
+      <c r="J6" s="11">
+        <v>0.50993042769999997</v>
+      </c>
+      <c r="K6" s="66" t="s">
         <v>16</v>
       </c>
     </row>
@@ -2377,14 +2418,25 @@
       <c r="B7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="64"/>
-      <c r="D7" s="65"/>
-      <c r="E7" s="65"/>
-      <c r="G7" s="11"/>
-      <c r="H7" s="11"/>
-      <c r="I7" s="11"/>
-      <c r="J7" s="11"/>
-      <c r="K7" s="71"/>
+      <c r="C7" s="68"/>
+      <c r="D7" s="64"/>
+      <c r="E7" s="64"/>
+      <c r="F7" s="11">
+        <v>3.3435524000000001E-2</v>
+      </c>
+      <c r="G7" s="11">
+        <v>2.3950948999999998E-3</v>
+      </c>
+      <c r="H7" s="11">
+        <v>0.35504885990000001</v>
+      </c>
+      <c r="I7" s="11">
+        <v>0.49892429649999998</v>
+      </c>
+      <c r="J7" s="11">
+        <v>0.50392556320000004</v>
+      </c>
+      <c r="K7" s="66"/>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
@@ -2393,14 +2445,25 @@
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="64"/>
-      <c r="D8" s="65"/>
-      <c r="E8" s="65"/>
-      <c r="G8" s="11"/>
-      <c r="H8" s="11"/>
-      <c r="I8" s="11"/>
-      <c r="J8" s="11"/>
-      <c r="K8" s="71"/>
+      <c r="C8" s="68"/>
+      <c r="D8" s="64"/>
+      <c r="E8" s="64"/>
+      <c r="F8" s="11">
+        <v>3.8321520000000002E-4</v>
+      </c>
+      <c r="G8" s="11">
+        <v>2.0118796E-3</v>
+      </c>
+      <c r="H8" s="11">
+        <v>0.35294117650000001</v>
+      </c>
+      <c r="I8" s="11">
+        <v>0.50147258729999999</v>
+      </c>
+      <c r="J8" s="11">
+        <v>0.47738500210000001</v>
+      </c>
+      <c r="K8" s="66"/>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="G9" s="11"/>
@@ -2409,12 +2472,12 @@
       <c r="J9" s="11"/>
     </row>
     <row r="10" spans="1:12" s="59" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="66" t="s">
+      <c r="A10" s="69" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="66"/>
-      <c r="C10" s="66"/>
-      <c r="D10" s="66"/>
+      <c r="B10" s="69"/>
+      <c r="C10" s="69"/>
+      <c r="D10" s="69"/>
       <c r="E10" s="60"/>
       <c r="F10" s="61"/>
       <c r="G10" s="61"/>
@@ -2436,20 +2499,31 @@
       <c r="B12" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C12" s="64" t="s">
+      <c r="C12" s="68" t="s">
         <v>43</v>
       </c>
-      <c r="D12" s="65" t="s">
+      <c r="D12" s="64" t="s">
         <v>11</v>
       </c>
-      <c r="E12" s="65" t="s">
+      <c r="E12" s="64" t="s">
         <v>17</v>
       </c>
-      <c r="G12" s="11"/>
-      <c r="H12" s="11"/>
-      <c r="I12" s="11"/>
-      <c r="J12" s="11"/>
-      <c r="K12" s="71" t="s">
+      <c r="F12" s="11">
+        <v>4.82262704E-2</v>
+      </c>
+      <c r="G12" s="11">
+        <v>1.5340365000000001E-3</v>
+      </c>
+      <c r="H12" s="11">
+        <v>0.33844678810000001</v>
+      </c>
+      <c r="I12" s="11">
+        <v>0.55116861910000003</v>
+      </c>
+      <c r="J12" s="11">
+        <v>0.4966675035</v>
+      </c>
+      <c r="K12" s="66" t="s">
         <v>18</v>
       </c>
     </row>
@@ -2460,14 +2534,25 @@
       <c r="B13" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C13" s="64"/>
-      <c r="D13" s="65"/>
-      <c r="E13" s="65"/>
-      <c r="G13" s="11"/>
-      <c r="H13" s="11"/>
-      <c r="I13" s="11"/>
-      <c r="J13" s="11"/>
-      <c r="K13" s="71"/>
+      <c r="C13" s="68"/>
+      <c r="D13" s="64"/>
+      <c r="E13" s="64"/>
+      <c r="F13" s="11">
+        <v>2.876318E-4</v>
+      </c>
+      <c r="G13" s="11">
+        <v>2.5886864999999999E-3</v>
+      </c>
+      <c r="H13" s="11">
+        <v>0.25503355700000002</v>
+      </c>
+      <c r="I13" s="11">
+        <v>0.48627450519999998</v>
+      </c>
+      <c r="J13" s="11">
+        <v>0.48225264400000001</v>
+      </c>
+      <c r="K13" s="66"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
@@ -2476,14 +2561,25 @@
       <c r="B14" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C14" s="64"/>
-      <c r="D14" s="65"/>
-      <c r="E14" s="65"/>
-      <c r="G14" s="11"/>
-      <c r="H14" s="11"/>
-      <c r="I14" s="11"/>
-      <c r="J14" s="11"/>
-      <c r="K14" s="71"/>
+      <c r="C14" s="68"/>
+      <c r="D14" s="64"/>
+      <c r="E14" s="64"/>
+      <c r="F14" s="11">
+        <v>6.7114089999999996E-4</v>
+      </c>
+      <c r="G14" s="11">
+        <v>9.5877280000000004E-4</v>
+      </c>
+      <c r="H14" s="11">
+        <v>0.17948226270000001</v>
+      </c>
+      <c r="I14" s="11">
+        <v>0.47313867139999999</v>
+      </c>
+      <c r="J14" s="11">
+        <v>0.43776818420000002</v>
+      </c>
+      <c r="K14" s="66"/>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="G15" s="11"/>
@@ -2498,20 +2594,31 @@
       <c r="B16" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C16" s="64" t="s">
+      <c r="C16" s="68" t="s">
         <v>44</v>
       </c>
-      <c r="D16" s="65" t="s">
+      <c r="D16" s="64" t="s">
         <v>19</v>
       </c>
-      <c r="E16" s="65" t="s">
+      <c r="E16" s="64" t="s">
         <v>27</v>
       </c>
-      <c r="G16" s="11"/>
-      <c r="H16" s="11"/>
-      <c r="I16" s="11"/>
-      <c r="J16" s="11"/>
-      <c r="K16" s="71" t="s">
+      <c r="F16" s="11">
+        <v>3.4036433400000003E-2</v>
+      </c>
+      <c r="G16" s="11">
+        <v>1.8120805300000001E-2</v>
+      </c>
+      <c r="H16" s="11">
+        <v>0.37296260790000002</v>
+      </c>
+      <c r="I16" s="11">
+        <v>0.82428061320000001</v>
+      </c>
+      <c r="J16" s="11">
+        <v>0.44130707470000002</v>
+      </c>
+      <c r="K16" s="66" t="s">
         <v>36</v>
       </c>
     </row>
@@ -2522,14 +2629,25 @@
       <c r="B17" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C17" s="64"/>
-      <c r="D17" s="65"/>
-      <c r="E17" s="65"/>
-      <c r="G17" s="11"/>
-      <c r="H17" s="11"/>
-      <c r="I17" s="11"/>
-      <c r="J17" s="11"/>
-      <c r="K17" s="71"/>
+      <c r="C17" s="68"/>
+      <c r="D17" s="64"/>
+      <c r="E17" s="64"/>
+      <c r="F17" s="11">
+        <v>7.7660593999999998E-3</v>
+      </c>
+      <c r="G17" s="11">
+        <v>5.0814956999999999E-3</v>
+      </c>
+      <c r="H17" s="11">
+        <v>0.36222435279999998</v>
+      </c>
+      <c r="I17" s="11">
+        <v>0.64209529909999996</v>
+      </c>
+      <c r="J17" s="11">
+        <v>0.46778393010000002</v>
+      </c>
+      <c r="K17" s="66"/>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
@@ -2538,14 +2656,25 @@
       <c r="B18" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C18" s="64"/>
-      <c r="D18" s="65"/>
-      <c r="E18" s="65"/>
-      <c r="G18" s="11"/>
-      <c r="H18" s="11"/>
-      <c r="I18" s="11"/>
-      <c r="J18" s="11"/>
-      <c r="K18" s="71"/>
+      <c r="C18" s="68"/>
+      <c r="D18" s="64"/>
+      <c r="E18" s="64"/>
+      <c r="F18" s="11">
+        <v>2.876318E-4</v>
+      </c>
+      <c r="G18" s="11">
+        <v>9.5877281E-4</v>
+      </c>
+      <c r="H18" s="11">
+        <v>1</v>
+      </c>
+      <c r="I18" s="11">
+        <v>0.50192787270000006</v>
+      </c>
+      <c r="J18" s="11">
+        <v>0.46815617929999997</v>
+      </c>
+      <c r="K18" s="66"/>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.2">
       <c r="G19" s="11"/>
@@ -2560,20 +2689,31 @@
       <c r="B20" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C20" s="64" t="s">
+      <c r="C20" s="68" t="s">
         <v>45</v>
       </c>
-      <c r="D20" s="65" t="s">
+      <c r="D20" s="64" t="s">
         <v>20</v>
       </c>
-      <c r="E20" s="65" t="s">
+      <c r="E20" s="64" t="s">
         <v>28</v>
       </c>
-      <c r="G20" s="11"/>
-      <c r="H20" s="11"/>
-      <c r="I20" s="11"/>
-      <c r="J20" s="11"/>
-      <c r="K20" s="71" t="s">
+      <c r="F20" s="11">
+        <v>5.7238734399999998E-2</v>
+      </c>
+      <c r="G20" s="11">
+        <v>1.3422817999999999E-3</v>
+      </c>
+      <c r="H20" s="11">
+        <v>0.3856184084</v>
+      </c>
+      <c r="I20" s="11">
+        <v>0.84574131559999999</v>
+      </c>
+      <c r="J20" s="11">
+        <v>0.4434595543</v>
+      </c>
+      <c r="K20" s="66" t="s">
         <v>35</v>
       </c>
     </row>
@@ -2584,14 +2724,25 @@
       <c r="B21" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C21" s="64"/>
-      <c r="D21" s="65"/>
-      <c r="E21" s="65"/>
-      <c r="G21" s="11"/>
-      <c r="H21" s="11"/>
-      <c r="I21" s="11"/>
-      <c r="J21" s="11"/>
-      <c r="K21" s="71"/>
+      <c r="C21" s="68"/>
+      <c r="D21" s="64"/>
+      <c r="E21" s="64"/>
+      <c r="F21" s="11">
+        <v>5.11025887E-2</v>
+      </c>
+      <c r="G21" s="11">
+        <v>8.6289548999999993E-3</v>
+      </c>
+      <c r="H21" s="11">
+        <v>0.38446788110000002</v>
+      </c>
+      <c r="I21" s="11">
+        <v>0.70028981489999997</v>
+      </c>
+      <c r="J21" s="11">
+        <v>0.46092753450000001</v>
+      </c>
+      <c r="K21" s="66"/>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
@@ -2600,14 +2751,25 @@
       <c r="B22" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C22" s="64"/>
-      <c r="D22" s="65"/>
-      <c r="E22" s="65"/>
-      <c r="G22" s="11"/>
-      <c r="H22" s="11"/>
-      <c r="I22" s="11"/>
-      <c r="J22" s="11"/>
-      <c r="K22" s="71"/>
+      <c r="C22" s="68"/>
+      <c r="D22" s="64"/>
+      <c r="E22" s="64"/>
+      <c r="F22" s="11">
+        <v>0</v>
+      </c>
+      <c r="G22" s="11">
+        <v>1.2464046E-3</v>
+      </c>
+      <c r="H22" s="11">
+        <v>0.1394055609</v>
+      </c>
+      <c r="I22" s="11">
+        <v>0.50123826859999998</v>
+      </c>
+      <c r="J22" s="11">
+        <v>0.4740446935</v>
+      </c>
+      <c r="K22" s="66"/>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.2">
       <c r="G23" s="11"/>
@@ -2622,19 +2784,30 @@
       <c r="B24" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C24" s="64" t="s">
+      <c r="C24" s="68" t="s">
         <v>46</v>
       </c>
-      <c r="D24" s="65" t="s">
+      <c r="D24" s="64" t="s">
         <v>21</v>
       </c>
-      <c r="E24" s="65" t="s">
+      <c r="E24" s="64" t="s">
         <v>32</v>
       </c>
-      <c r="G24" s="11"/>
-      <c r="H24" s="11"/>
-      <c r="I24" s="11"/>
-      <c r="J24" s="11"/>
+      <c r="F24" s="11">
+        <v>2.3585810200000001E-2</v>
+      </c>
+      <c r="G24" s="11">
+        <v>3.8350911000000001E-3</v>
+      </c>
+      <c r="H24" s="11">
+        <v>0.44256951100000003</v>
+      </c>
+      <c r="I24" s="11">
+        <v>0.78002278650000001</v>
+      </c>
+      <c r="J24" s="11">
+        <v>0.43125917699999999</v>
+      </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
@@ -2643,13 +2816,24 @@
       <c r="B25" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C25" s="64"/>
-      <c r="D25" s="65"/>
-      <c r="E25" s="65"/>
-      <c r="G25" s="11"/>
-      <c r="H25" s="11"/>
-      <c r="I25" s="11"/>
-      <c r="J25" s="11"/>
+      <c r="C25" s="68"/>
+      <c r="D25" s="64"/>
+      <c r="E25" s="64"/>
+      <c r="F25" s="11">
+        <v>3.0584851400000002E-2</v>
+      </c>
+      <c r="G25" s="11">
+        <v>2.6845636999999999E-3</v>
+      </c>
+      <c r="H25" s="11">
+        <v>0.4122722915</v>
+      </c>
+      <c r="I25" s="11">
+        <v>0.77689365480000006</v>
+      </c>
+      <c r="J25" s="11">
+        <v>0.44582553250000001</v>
+      </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
@@ -2658,13 +2842,24 @@
       <c r="B26" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C26" s="64"/>
-      <c r="D26" s="65"/>
-      <c r="E26" s="65"/>
-      <c r="G26" s="11"/>
-      <c r="H26" s="11"/>
-      <c r="I26" s="11"/>
-      <c r="J26" s="11"/>
+      <c r="C26" s="68"/>
+      <c r="D26" s="64"/>
+      <c r="E26" s="64"/>
+      <c r="F26" s="11">
+        <v>6.7114089999999996E-4</v>
+      </c>
+      <c r="G26" s="11">
+        <v>1.5340364E-3</v>
+      </c>
+      <c r="H26" s="11">
+        <v>0.14400767019999999</v>
+      </c>
+      <c r="I26" s="11">
+        <v>0.48521459810000001</v>
+      </c>
+      <c r="J26" s="11">
+        <v>0.46724980519999998</v>
+      </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.2">
       <c r="G27" s="11"/>
@@ -2679,19 +2874,30 @@
       <c r="B28" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C28" s="64" t="s">
+      <c r="C28" s="68" t="s">
         <v>47</v>
       </c>
-      <c r="D28" s="65" t="s">
+      <c r="D28" s="64" t="s">
         <v>22</v>
       </c>
-      <c r="E28" s="65" t="s">
+      <c r="E28" s="64" t="s">
         <v>33</v>
       </c>
-      <c r="G28" s="11"/>
-      <c r="H28" s="11"/>
-      <c r="I28" s="11"/>
-      <c r="J28" s="11"/>
+      <c r="F28" s="11">
+        <v>3.2885905999999999E-2</v>
+      </c>
+      <c r="G28" s="11">
+        <v>6.2320229999999997E-3</v>
+      </c>
+      <c r="H28" s="11">
+        <v>0.50393096839999996</v>
+      </c>
+      <c r="I28" s="11">
+        <v>0.77736178700000003</v>
+      </c>
+      <c r="J28" s="11">
+        <v>0.43943819899999997</v>
+      </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
@@ -2700,13 +2906,24 @@
       <c r="B29" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C29" s="64"/>
-      <c r="D29" s="65"/>
-      <c r="E29" s="65"/>
-      <c r="G29" s="11"/>
-      <c r="H29" s="11"/>
-      <c r="I29" s="11"/>
-      <c r="J29" s="11"/>
+      <c r="C29" s="68"/>
+      <c r="D29" s="64"/>
+      <c r="E29" s="64"/>
+      <c r="F29" s="11">
+        <v>1.42857143E-2</v>
+      </c>
+      <c r="G29" s="11">
+        <v>6.5196548E-3</v>
+      </c>
+      <c r="H29" s="11">
+        <v>0.41303930970000002</v>
+      </c>
+      <c r="I29" s="11">
+        <v>0.6898911875</v>
+      </c>
+      <c r="J29" s="11">
+        <v>0.46205572309999998</v>
+      </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
@@ -2715,13 +2932,24 @@
       <c r="B30" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C30" s="64"/>
-      <c r="D30" s="65"/>
-      <c r="E30" s="65"/>
-      <c r="G30" s="11"/>
-      <c r="H30" s="11"/>
-      <c r="I30" s="11"/>
-      <c r="J30" s="11"/>
+      <c r="C30" s="68"/>
+      <c r="D30" s="64"/>
+      <c r="E30" s="64"/>
+      <c r="F30" s="11">
+        <v>3.8350910000000001E-4</v>
+      </c>
+      <c r="G30" s="11">
+        <v>1.4381591999999999E-3</v>
+      </c>
+      <c r="H30" s="11">
+        <v>9.7794822599999998E-2</v>
+      </c>
+      <c r="I30" s="11">
+        <v>0.45026455949999999</v>
+      </c>
+      <c r="J30" s="11">
+        <v>0.46414172419999999</v>
+      </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.2">
       <c r="G31" s="11"/>
@@ -2736,19 +2964,30 @@
       <c r="B32" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C32" s="64" t="s">
+      <c r="C32" s="68" t="s">
         <v>48</v>
       </c>
-      <c r="D32" s="65" t="s">
+      <c r="D32" s="64" t="s">
         <v>23</v>
       </c>
-      <c r="E32" s="65" t="s">
+      <c r="E32" s="64" t="s">
         <v>29</v>
       </c>
-      <c r="G32" s="11"/>
-      <c r="H32" s="11"/>
-      <c r="I32" s="11"/>
-      <c r="J32" s="11"/>
+      <c r="F32" s="11">
+        <v>5.7529773300000003E-2</v>
+      </c>
+      <c r="G32" s="11">
+        <v>6.7230119E-3</v>
+      </c>
+      <c r="H32" s="11">
+        <v>0.33499807910000001</v>
+      </c>
+      <c r="I32" s="11">
+        <v>0.89029599260000003</v>
+      </c>
+      <c r="J32" s="11">
+        <v>0.39083109230000002</v>
+      </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
@@ -2757,13 +2996,24 @@
       <c r="B33" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C33" s="64"/>
-      <c r="D33" s="65"/>
-      <c r="E33" s="65"/>
-      <c r="G33" s="11"/>
-      <c r="H33" s="11"/>
-      <c r="I33" s="11"/>
-      <c r="J33" s="11"/>
+      <c r="C33" s="68"/>
+      <c r="D33" s="64"/>
+      <c r="E33" s="64"/>
+      <c r="F33" s="11">
+        <v>6.9727237799999994E-2</v>
+      </c>
+      <c r="G33" s="11">
+        <v>8.6438724000000005E-3</v>
+      </c>
+      <c r="H33" s="11">
+        <v>0.34959661930000002</v>
+      </c>
+      <c r="I33" s="11">
+        <v>0.87258270429999996</v>
+      </c>
+      <c r="J33" s="11">
+        <v>0.37624693279999999</v>
+      </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
@@ -2772,13 +3022,24 @@
       <c r="B34" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C34" s="64"/>
-      <c r="D34" s="65"/>
-      <c r="E34" s="65"/>
-      <c r="G34" s="11"/>
-      <c r="H34" s="11"/>
-      <c r="I34" s="11"/>
-      <c r="J34" s="11"/>
+      <c r="C34" s="68"/>
+      <c r="D34" s="64"/>
+      <c r="E34" s="64"/>
+      <c r="F34" s="11">
+        <v>2.8812910000000001E-4</v>
+      </c>
+      <c r="G34" s="11">
+        <v>1.5366883999999999E-3</v>
+      </c>
+      <c r="H34" s="11">
+        <v>0.25201690360000001</v>
+      </c>
+      <c r="I34" s="11">
+        <v>0.47203997120000002</v>
+      </c>
+      <c r="J34" s="11">
+        <v>0.4837691543</v>
+      </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.2">
       <c r="G35" s="11"/>
@@ -2793,19 +3054,30 @@
       <c r="B36" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C36" s="64" t="s">
+      <c r="C36" s="68" t="s">
         <v>49</v>
       </c>
-      <c r="D36" s="65" t="s">
+      <c r="D36" s="64" t="s">
         <v>24</v>
       </c>
-      <c r="E36" s="65" t="s">
+      <c r="E36" s="64" t="s">
         <v>34</v>
       </c>
-      <c r="G36" s="11"/>
-      <c r="H36" s="11"/>
-      <c r="I36" s="11"/>
-      <c r="J36" s="11"/>
+      <c r="F36" s="11">
+        <v>4.46788111E-2</v>
+      </c>
+      <c r="G36" s="11">
+        <v>6.0402685000000003E-3</v>
+      </c>
+      <c r="H36" s="11">
+        <v>0.47727708530000001</v>
+      </c>
+      <c r="I36" s="11">
+        <v>0.81084688910000002</v>
+      </c>
+      <c r="J36" s="11">
+        <v>0.41388874180000002</v>
+      </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
@@ -2814,13 +3086,24 @@
       <c r="B37" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C37" s="64"/>
-      <c r="D37" s="65"/>
-      <c r="E37" s="65"/>
-      <c r="G37" s="11"/>
-      <c r="H37" s="11"/>
-      <c r="I37" s="11"/>
-      <c r="J37" s="11"/>
+      <c r="C37" s="68"/>
+      <c r="D37" s="64"/>
+      <c r="E37" s="64"/>
+      <c r="F37" s="11">
+        <v>1.4189837E-2</v>
+      </c>
+      <c r="G37" s="11">
+        <v>1.9367209900000001E-2</v>
+      </c>
+      <c r="H37" s="11">
+        <v>0.42243528279999998</v>
+      </c>
+      <c r="I37" s="11">
+        <v>0.80852306610000002</v>
+      </c>
+      <c r="J37" s="11">
+        <v>0.38425564280000002</v>
+      </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
@@ -2829,13 +3112,24 @@
       <c r="B38" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C38" s="64"/>
-      <c r="D38" s="65"/>
-      <c r="E38" s="65"/>
-      <c r="G38" s="11"/>
-      <c r="H38" s="11"/>
-      <c r="I38" s="11"/>
-      <c r="J38" s="11"/>
+      <c r="C38" s="68"/>
+      <c r="D38" s="64"/>
+      <c r="E38" s="64"/>
+      <c r="F38" s="11">
+        <v>2.876318E-4</v>
+      </c>
+      <c r="G38" s="11">
+        <v>1.4381591999999999E-3</v>
+      </c>
+      <c r="H38" s="11">
+        <v>9.8945350000000001E-2</v>
+      </c>
+      <c r="I38" s="11">
+        <v>0.45479480760000002</v>
+      </c>
+      <c r="J38" s="11">
+        <v>0.47442714809999997</v>
+      </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.2">
       <c r="G39" s="11"/>
@@ -2844,12 +3138,12 @@
       <c r="J39" s="11"/>
     </row>
     <row r="40" spans="1:11" s="59" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="66" t="s">
+      <c r="A40" s="69" t="s">
         <v>38</v>
       </c>
-      <c r="B40" s="66"/>
-      <c r="C40" s="66"/>
-      <c r="D40" s="66"/>
+      <c r="B40" s="69"/>
+      <c r="C40" s="69"/>
+      <c r="D40" s="69"/>
       <c r="E40" s="60"/>
       <c r="F40" s="61"/>
       <c r="G40" s="61"/>
@@ -2871,20 +3165,31 @@
       <c r="B42" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C42" s="64" t="s">
+      <c r="C42" s="68" t="s">
         <v>50</v>
       </c>
-      <c r="D42" s="65" t="s">
+      <c r="D42" s="64" t="s">
         <v>25</v>
       </c>
-      <c r="E42" s="65" t="s">
+      <c r="E42" s="64" t="s">
         <v>27</v>
       </c>
-      <c r="G42" s="11"/>
-      <c r="H42" s="11"/>
-      <c r="I42" s="11"/>
-      <c r="J42" s="11"/>
-      <c r="K42" s="71" t="s">
+      <c r="F42" s="11">
+        <v>1.7244682899999999E-2</v>
+      </c>
+      <c r="G42" s="11">
+        <v>5.1734049000000002E-3</v>
+      </c>
+      <c r="H42" s="11">
+        <v>0.35198313850000001</v>
+      </c>
+      <c r="I42" s="11">
+        <v>0.70341981239999996</v>
+      </c>
+      <c r="J42" s="11">
+        <v>0.4587482034</v>
+      </c>
+      <c r="K42" s="66" t="s">
         <v>30</v>
       </c>
     </row>
@@ -2895,14 +3200,25 @@
       <c r="B43" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C43" s="64"/>
-      <c r="D43" s="65"/>
-      <c r="E43" s="65"/>
-      <c r="G43" s="11"/>
-      <c r="H43" s="11"/>
-      <c r="I43" s="11"/>
-      <c r="J43" s="11"/>
-      <c r="K43" s="71"/>
+      <c r="C43" s="68"/>
+      <c r="D43" s="64"/>
+      <c r="E43" s="64"/>
+      <c r="F43" s="11">
+        <v>1.34125311E-2</v>
+      </c>
+      <c r="G43" s="11">
+        <v>2.0118796E-3</v>
+      </c>
+      <c r="H43" s="11">
+        <v>0.41138149070000002</v>
+      </c>
+      <c r="I43" s="11">
+        <v>0.6688536155</v>
+      </c>
+      <c r="J43" s="11">
+        <v>0.46907909489999999</v>
+      </c>
+      <c r="K43" s="66"/>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
@@ -2911,14 +3227,25 @@
       <c r="B44" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C44" s="64"/>
-      <c r="D44" s="65"/>
-      <c r="E44" s="65"/>
-      <c r="G44" s="11"/>
-      <c r="H44" s="11"/>
-      <c r="I44" s="11"/>
-      <c r="J44" s="11"/>
-      <c r="K44" s="71"/>
+      <c r="C44" s="68"/>
+      <c r="D44" s="64"/>
+      <c r="E44" s="64"/>
+      <c r="F44" s="11">
+        <v>8.6223409999999995E-4</v>
+      </c>
+      <c r="G44" s="11">
+        <v>2.5867024999999999E-3</v>
+      </c>
+      <c r="H44" s="11">
+        <v>0.4631155394</v>
+      </c>
+      <c r="I44" s="11">
+        <v>0.50944027609999998</v>
+      </c>
+      <c r="J44" s="11">
+        <v>0.49390839069999998</v>
+      </c>
+      <c r="K44" s="66"/>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.2">
       <c r="G45" s="11"/>
@@ -2933,20 +3260,31 @@
       <c r="B46" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C46" s="64" t="s">
+      <c r="C46" s="68" t="s">
         <v>51</v>
       </c>
-      <c r="D46" s="65" t="s">
+      <c r="D46" s="64" t="s">
         <v>26</v>
       </c>
-      <c r="E46" s="65" t="s">
+      <c r="E46" s="64" t="s">
         <v>28</v>
       </c>
-      <c r="G46" s="11"/>
-      <c r="H46" s="11"/>
-      <c r="I46" s="11"/>
-      <c r="J46" s="11"/>
-      <c r="K46" s="71" t="s">
+      <c r="F46" s="11">
+        <v>2.6920866099999999E-2</v>
+      </c>
+      <c r="G46" s="11">
+        <v>3.5447403999999999E-3</v>
+      </c>
+      <c r="H46" s="11">
+        <v>0.28434566010000001</v>
+      </c>
+      <c r="I46" s="11">
+        <v>0.75841570290000004</v>
+      </c>
+      <c r="J46" s="11">
+        <v>0.45388746419999998</v>
+      </c>
+      <c r="K46" s="66" t="s">
         <v>31</v>
       </c>
     </row>
@@ -2957,14 +3295,25 @@
       <c r="B47" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C47" s="64"/>
-      <c r="D47" s="65"/>
-      <c r="E47" s="65"/>
-      <c r="G47" s="11"/>
-      <c r="H47" s="11"/>
-      <c r="I47" s="11"/>
-      <c r="J47" s="11"/>
-      <c r="K47" s="71"/>
+      <c r="C47" s="68"/>
+      <c r="D47" s="64"/>
+      <c r="E47" s="64"/>
+      <c r="F47" s="11">
+        <v>4.3303314799999999E-2</v>
+      </c>
+      <c r="G47" s="11">
+        <v>5.7482276000000001E-3</v>
+      </c>
+      <c r="H47" s="11">
+        <v>0.38800536499999999</v>
+      </c>
+      <c r="I47" s="11">
+        <v>0.75218841530000002</v>
+      </c>
+      <c r="J47" s="11">
+        <v>0.45908136910000003</v>
+      </c>
+      <c r="K47" s="66"/>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
@@ -2973,14 +3322,25 @@
       <c r="B48" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C48" s="64"/>
-      <c r="D48" s="65"/>
-      <c r="E48" s="65"/>
-      <c r="G48" s="11"/>
-      <c r="H48" s="11"/>
-      <c r="I48" s="11"/>
-      <c r="J48" s="11"/>
-      <c r="K48" s="71"/>
+      <c r="C48" s="68"/>
+      <c r="D48" s="64"/>
+      <c r="E48" s="64"/>
+      <c r="F48" s="11">
+        <v>9.5803800000000006E-5</v>
+      </c>
+      <c r="G48" s="11">
+        <v>1.8202721E-3</v>
+      </c>
+      <c r="H48" s="11">
+        <v>0.99980839239999997</v>
+      </c>
+      <c r="I48" s="11">
+        <v>0.48246797149999998</v>
+      </c>
+      <c r="J48" s="11">
+        <v>0.478579698</v>
+      </c>
+      <c r="K48" s="66"/>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.2">
       <c r="G49" s="11"/>
@@ -2995,19 +3355,30 @@
       <c r="B50" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C50" s="64" t="s">
+      <c r="C50" s="68" t="s">
         <v>52</v>
       </c>
-      <c r="D50" s="65" t="s">
+      <c r="D50" s="64" t="s">
         <v>39</v>
       </c>
-      <c r="E50" s="65" t="s">
+      <c r="E50" s="64" t="s">
         <v>29</v>
       </c>
-      <c r="G50" s="11"/>
-      <c r="H50" s="11"/>
-      <c r="I50" s="11"/>
-      <c r="J50" s="11"/>
+      <c r="F50" s="11">
+        <v>3.1423644399999999E-2</v>
+      </c>
+      <c r="G50" s="11">
+        <v>4.5027783000000004E-3</v>
+      </c>
+      <c r="H50" s="11">
+        <v>0.31423644379999999</v>
+      </c>
+      <c r="I50" s="11">
+        <v>0.87912838900000001</v>
+      </c>
+      <c r="J50" s="11">
+        <v>0.37861748220000002</v>
+      </c>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A51" s="1" t="s">
@@ -3016,13 +3387,24 @@
       <c r="B51" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C51" s="64"/>
-      <c r="D51" s="65"/>
-      <c r="E51" s="65"/>
-      <c r="G51" s="11"/>
-      <c r="H51" s="11"/>
-      <c r="I51" s="11"/>
-      <c r="J51" s="11"/>
+      <c r="C51" s="68"/>
+      <c r="D51" s="64"/>
+      <c r="E51" s="64"/>
+      <c r="F51" s="11">
+        <v>8.8139489999999997E-3</v>
+      </c>
+      <c r="G51" s="11">
+        <v>2.3950948999999998E-3</v>
+      </c>
+      <c r="H51" s="11">
+        <v>0.36865299870000001</v>
+      </c>
+      <c r="I51" s="11">
+        <v>0.73505614159999999</v>
+      </c>
+      <c r="J51" s="11">
+        <v>0.438803202</v>
+      </c>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
@@ -3031,13 +3413,24 @@
       <c r="B52" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C52" s="64"/>
-      <c r="D52" s="65"/>
-      <c r="E52" s="65"/>
-      <c r="G52" s="11"/>
-      <c r="H52" s="11"/>
-      <c r="I52" s="11"/>
-      <c r="J52" s="11"/>
+      <c r="C52" s="68"/>
+      <c r="D52" s="64"/>
+      <c r="E52" s="64"/>
+      <c r="F52" s="11">
+        <v>1.9160760000000001E-4</v>
+      </c>
+      <c r="G52" s="11">
+        <v>1.9160759E-3</v>
+      </c>
+      <c r="H52" s="11">
+        <v>4.4261352699999999E-2</v>
+      </c>
+      <c r="I52" s="11">
+        <v>0.4812790361</v>
+      </c>
+      <c r="J52" s="11">
+        <v>0.47962761110000002</v>
+      </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.2">
       <c r="G53" s="11"/>
@@ -3052,67 +3445,98 @@
       <c r="J54" s="11"/>
     </row>
     <row r="55" spans="1:11" s="42" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="63" t="s">
+      <c r="A55" s="71" t="s">
         <v>59</v>
       </c>
-      <c r="B55" s="63"/>
-      <c r="C55" s="63"/>
-      <c r="D55" s="63"/>
+      <c r="B55" s="71"/>
+      <c r="C55" s="71"/>
+      <c r="D55" s="71"/>
       <c r="E55" s="39"/>
       <c r="F55" s="40">
         <f>MAX(F2:F52)</f>
-        <v>0</v>
+        <v>7.4400767000000007E-2</v>
       </c>
       <c r="G55" s="40">
         <f>MAX(G2:G52)</f>
-        <v>0</v>
+        <v>1.9367209900000001E-2</v>
       </c>
       <c r="H55" s="40">
         <f>MAX(H2:H52)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I55" s="40">
         <f>MAX(I2:I52)</f>
-        <v>0</v>
+        <v>0.89029599260000003</v>
       </c>
       <c r="J55" s="40">
         <f>MAX(J2:J52)</f>
-        <v>0</v>
+        <v>0.50993042769999997</v>
       </c>
       <c r="K55" s="41"/>
     </row>
     <row r="56" spans="1:11" s="46" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="69" t="s">
+      <c r="A56" s="63" t="s">
         <v>60</v>
       </c>
-      <c r="B56" s="69"/>
-      <c r="C56" s="69"/>
-      <c r="D56" s="69"/>
+      <c r="B56" s="63"/>
+      <c r="C56" s="63"/>
+      <c r="D56" s="63"/>
       <c r="E56" s="43"/>
-      <c r="F56" s="44" t="e">
+      <c r="F56" s="44">
         <f>AVERAGE(F2:F52)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G56" s="44" t="e">
+        <v>2.2625756961111115E-2</v>
+      </c>
+      <c r="G56" s="44">
         <f>AVERAGE(G2:G52)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H56" s="44" t="e">
+        <v>4.1386779447222218E-3</v>
+      </c>
+      <c r="H56" s="44">
         <f>AVERAGE(H2:H52)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I56" s="44" t="e">
+        <v>0.36452921899722224</v>
+      </c>
+      <c r="I56" s="44">
         <f>AVERAGE(I2:I52)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="J56" s="44" t="e">
+        <v>0.63549272388055567</v>
+      </c>
+      <c r="J56" s="44">
         <f>AVERAGE(J2:J52)</f>
-        <v>#DIV/0!</v>
+        <v>0.45735612999444442</v>
       </c>
       <c r="K56" s="45"/>
     </row>
   </sheetData>
   <mergeCells count="47">
+    <mergeCell ref="A55:D55"/>
+    <mergeCell ref="K42:K44"/>
+    <mergeCell ref="C46:C48"/>
+    <mergeCell ref="D46:D48"/>
+    <mergeCell ref="E46:E48"/>
+    <mergeCell ref="K46:K48"/>
+    <mergeCell ref="E50:E52"/>
+    <mergeCell ref="C36:C38"/>
+    <mergeCell ref="D36:D38"/>
+    <mergeCell ref="E36:E38"/>
+    <mergeCell ref="A40:D40"/>
+    <mergeCell ref="C42:C44"/>
+    <mergeCell ref="D42:D44"/>
+    <mergeCell ref="E42:E44"/>
+    <mergeCell ref="K12:K14"/>
+    <mergeCell ref="C20:C22"/>
+    <mergeCell ref="D20:D22"/>
+    <mergeCell ref="E20:E22"/>
+    <mergeCell ref="K20:K22"/>
+    <mergeCell ref="C16:C18"/>
+    <mergeCell ref="D16:D18"/>
+    <mergeCell ref="E16:E18"/>
+    <mergeCell ref="K16:K18"/>
+    <mergeCell ref="C2:C4"/>
+    <mergeCell ref="D2:D4"/>
+    <mergeCell ref="E2:E4"/>
+    <mergeCell ref="K2:K4"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="D6:D8"/>
+    <mergeCell ref="E6:E8"/>
+    <mergeCell ref="K6:K8"/>
     <mergeCell ref="A56:D56"/>
     <mergeCell ref="A10:D10"/>
     <mergeCell ref="C12:C14"/>
@@ -3129,37 +3553,6 @@
     <mergeCell ref="E32:E34"/>
     <mergeCell ref="C50:C52"/>
     <mergeCell ref="D50:D52"/>
-    <mergeCell ref="C2:C4"/>
-    <mergeCell ref="D2:D4"/>
-    <mergeCell ref="E2:E4"/>
-    <mergeCell ref="K2:K4"/>
-    <mergeCell ref="C6:C8"/>
-    <mergeCell ref="D6:D8"/>
-    <mergeCell ref="E6:E8"/>
-    <mergeCell ref="K6:K8"/>
-    <mergeCell ref="K12:K14"/>
-    <mergeCell ref="C20:C22"/>
-    <mergeCell ref="D20:D22"/>
-    <mergeCell ref="E20:E22"/>
-    <mergeCell ref="K20:K22"/>
-    <mergeCell ref="C16:C18"/>
-    <mergeCell ref="D16:D18"/>
-    <mergeCell ref="E16:E18"/>
-    <mergeCell ref="K16:K18"/>
-    <mergeCell ref="C36:C38"/>
-    <mergeCell ref="D36:D38"/>
-    <mergeCell ref="E36:E38"/>
-    <mergeCell ref="A40:D40"/>
-    <mergeCell ref="C42:C44"/>
-    <mergeCell ref="D42:D44"/>
-    <mergeCell ref="E42:E44"/>
-    <mergeCell ref="A55:D55"/>
-    <mergeCell ref="K42:K44"/>
-    <mergeCell ref="C46:C48"/>
-    <mergeCell ref="D46:D48"/>
-    <mergeCell ref="E46:E48"/>
-    <mergeCell ref="K46:K48"/>
-    <mergeCell ref="E50:E52"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -3240,7 +3633,7 @@
       <c r="B2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="68" t="s">
+      <c r="C2" s="70" t="s">
         <v>41</v>
       </c>
       <c r="D2" s="67" t="s">
@@ -3261,7 +3654,7 @@
         <f>SUM(F2*1/5,G2*1/5,H2*1/5,I2*1/5,J2*1/5)</f>
         <v>0</v>
       </c>
-      <c r="N2" s="70" t="s">
+      <c r="N2" s="65" t="s">
         <v>15</v>
       </c>
     </row>
@@ -3272,9 +3665,9 @@
       <c r="B3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="64"/>
-      <c r="D3" s="65"/>
-      <c r="E3" s="65"/>
+      <c r="C3" s="68"/>
+      <c r="D3" s="64"/>
+      <c r="E3" s="64"/>
       <c r="K3" s="11">
         <f>SUM(F3*1/3,G3*1/3,I3*1/3)</f>
         <v>0</v>
@@ -3287,7 +3680,7 @@
         <f>SUM(F3*1/5,G3*1/5,H3*1/5,I3*1/5,J3*1/5)</f>
         <v>0</v>
       </c>
-      <c r="N3" s="71"/>
+      <c r="N3" s="66"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
@@ -3296,9 +3689,9 @@
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="64"/>
-      <c r="D4" s="65"/>
-      <c r="E4" s="65"/>
+      <c r="C4" s="68"/>
+      <c r="D4" s="64"/>
+      <c r="E4" s="64"/>
       <c r="K4" s="11">
         <f>SUM(F4*1/3,G4*1/3,I4*1/3)</f>
         <v>0</v>
@@ -3311,7 +3704,7 @@
         <f>SUM(F4*1/5,G4*1/5,H4*1/5,I4*1/5,J4*1/5)</f>
         <v>0</v>
       </c>
-      <c r="N4" s="71"/>
+      <c r="N4" s="66"/>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
@@ -3320,13 +3713,13 @@
       <c r="B6" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="64" t="s">
+      <c r="C6" s="68" t="s">
         <v>42</v>
       </c>
-      <c r="D6" s="65" t="s">
+      <c r="D6" s="64" t="s">
         <v>10</v>
       </c>
-      <c r="E6" s="65" t="s">
+      <c r="E6" s="64" t="s">
         <v>13</v>
       </c>
       <c r="K6" s="11">
@@ -3341,7 +3734,7 @@
         <f>SUM(F6*1/5,G6*1/5,H6*1/5,I6*1/5,J6*1/5)</f>
         <v>0</v>
       </c>
-      <c r="N6" s="71" t="s">
+      <c r="N6" s="66" t="s">
         <v>16</v>
       </c>
     </row>
@@ -3352,9 +3745,9 @@
       <c r="B7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="64"/>
-      <c r="D7" s="65"/>
-      <c r="E7" s="65"/>
+      <c r="C7" s="68"/>
+      <c r="D7" s="64"/>
+      <c r="E7" s="64"/>
       <c r="K7" s="11">
         <f>SUM(F7*1/3,G7*1/3,I7*1/3)</f>
         <v>0</v>
@@ -3367,7 +3760,7 @@
         <f>SUM(F7*1/5,G7*1/5,H7*1/5,I7*1/5,J7*1/5)</f>
         <v>0</v>
       </c>
-      <c r="N7" s="71"/>
+      <c r="N7" s="66"/>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
@@ -3376,9 +3769,9 @@
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="64"/>
-      <c r="D8" s="65"/>
-      <c r="E8" s="65"/>
+      <c r="C8" s="68"/>
+      <c r="D8" s="64"/>
+      <c r="E8" s="64"/>
       <c r="K8" s="11">
         <f>SUM(F8*1/3,G8*1/3,I8*1/3)</f>
         <v>0</v>
@@ -3391,15 +3784,15 @@
         <f>SUM(F8*1/5,G8*1/5,H8*1/5,I8*1/5,J8*1/5)</f>
         <v>0</v>
       </c>
-      <c r="N8" s="71"/>
+      <c r="N8" s="66"/>
     </row>
     <row r="10" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="73" t="s">
+      <c r="A10" s="78" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="73"/>
-      <c r="C10" s="73"/>
-      <c r="D10" s="73"/>
+      <c r="B10" s="78"/>
+      <c r="C10" s="78"/>
+      <c r="D10" s="78"/>
       <c r="E10" s="5"/>
       <c r="F10" s="13"/>
       <c r="G10" s="13"/>
@@ -3418,13 +3811,13 @@
       <c r="B12" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C12" s="64" t="s">
+      <c r="C12" s="68" t="s">
         <v>43</v>
       </c>
-      <c r="D12" s="65" t="s">
+      <c r="D12" s="64" t="s">
         <v>11</v>
       </c>
-      <c r="E12" s="65" t="s">
+      <c r="E12" s="64" t="s">
         <v>17</v>
       </c>
       <c r="K12" s="11">
@@ -3439,7 +3832,7 @@
         <f>SUM(F12*1/5,G12*1/5,H12*1/5,I12*1/5,J12*1/5)</f>
         <v>0</v>
       </c>
-      <c r="N12" s="71" t="s">
+      <c r="N12" s="66" t="s">
         <v>18</v>
       </c>
     </row>
@@ -3450,9 +3843,9 @@
       <c r="B13" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C13" s="64"/>
-      <c r="D13" s="65"/>
-      <c r="E13" s="65"/>
+      <c r="C13" s="68"/>
+      <c r="D13" s="64"/>
+      <c r="E13" s="64"/>
       <c r="K13" s="11">
         <f>SUM(F13*1/3,G13*1/3,I13*1/3)</f>
         <v>0</v>
@@ -3465,7 +3858,7 @@
         <f>SUM(F13*1/5,G13*1/5,H13*1/5,I13*1/5,J13*1/5)</f>
         <v>0</v>
       </c>
-      <c r="N13" s="71"/>
+      <c r="N13" s="66"/>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
@@ -3474,9 +3867,9 @@
       <c r="B14" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C14" s="64"/>
-      <c r="D14" s="65"/>
-      <c r="E14" s="65"/>
+      <c r="C14" s="68"/>
+      <c r="D14" s="64"/>
+      <c r="E14" s="64"/>
       <c r="K14" s="11">
         <f>SUM(F14*1/3,G14*1/3,I14*1/3)</f>
         <v>0</v>
@@ -3489,7 +3882,7 @@
         <f>SUM(F14*1/5,G14*1/5,H14*1/5,I14*1/5,J14*1/5)</f>
         <v>0</v>
       </c>
-      <c r="N14" s="71"/>
+      <c r="N14" s="66"/>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
@@ -3498,13 +3891,13 @@
       <c r="B16" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C16" s="64" t="s">
+      <c r="C16" s="68" t="s">
         <v>44</v>
       </c>
-      <c r="D16" s="65" t="s">
+      <c r="D16" s="64" t="s">
         <v>19</v>
       </c>
-      <c r="E16" s="65" t="s">
+      <c r="E16" s="64" t="s">
         <v>27</v>
       </c>
       <c r="K16" s="11">
@@ -3519,7 +3912,7 @@
         <f>SUM(F16*1/5,G16*1/5,H16*1/5,I16*1/5,J16*1/5)</f>
         <v>0</v>
       </c>
-      <c r="N16" s="71" t="s">
+      <c r="N16" s="66" t="s">
         <v>36</v>
       </c>
     </row>
@@ -3530,9 +3923,9 @@
       <c r="B17" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C17" s="64"/>
-      <c r="D17" s="65"/>
-      <c r="E17" s="65"/>
+      <c r="C17" s="68"/>
+      <c r="D17" s="64"/>
+      <c r="E17" s="64"/>
       <c r="K17" s="11">
         <f>SUM(F17*1/3,G17*1/3,I17*1/3)</f>
         <v>0</v>
@@ -3545,7 +3938,7 @@
         <f>SUM(F17*1/5,G17*1/5,H17*1/5,I17*1/5,J17*1/5)</f>
         <v>0</v>
       </c>
-      <c r="N17" s="71"/>
+      <c r="N17" s="66"/>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
@@ -3554,9 +3947,9 @@
       <c r="B18" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C18" s="64"/>
-      <c r="D18" s="65"/>
-      <c r="E18" s="65"/>
+      <c r="C18" s="68"/>
+      <c r="D18" s="64"/>
+      <c r="E18" s="64"/>
       <c r="K18" s="11">
         <f>SUM(F18*1/3,G18*1/3,I18*1/3)</f>
         <v>0</v>
@@ -3569,7 +3962,7 @@
         <f>SUM(F18*1/5,G18*1/5,H18*1/5,I18*1/5,J18*1/5)</f>
         <v>0</v>
       </c>
-      <c r="N18" s="71"/>
+      <c r="N18" s="66"/>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
@@ -3578,13 +3971,13 @@
       <c r="B20" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C20" s="64" t="s">
+      <c r="C20" s="68" t="s">
         <v>45</v>
       </c>
-      <c r="D20" s="65" t="s">
+      <c r="D20" s="64" t="s">
         <v>20</v>
       </c>
-      <c r="E20" s="65" t="s">
+      <c r="E20" s="64" t="s">
         <v>28</v>
       </c>
       <c r="K20" s="11">
@@ -3599,7 +3992,7 @@
         <f>SUM(F20*1/5,G20*1/5,H20*1/5,I20*1/5,J20*1/5)</f>
         <v>0</v>
       </c>
-      <c r="N20" s="71" t="s">
+      <c r="N20" s="66" t="s">
         <v>35</v>
       </c>
     </row>
@@ -3610,9 +4003,9 @@
       <c r="B21" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C21" s="64"/>
-      <c r="D21" s="65"/>
-      <c r="E21" s="65"/>
+      <c r="C21" s="68"/>
+      <c r="D21" s="64"/>
+      <c r="E21" s="64"/>
       <c r="K21" s="11">
         <f>SUM(F21*1/3,G21*1/3,I21*1/3)</f>
         <v>0</v>
@@ -3625,7 +4018,7 @@
         <f>SUM(F21*1/5,G21*1/5,H21*1/5,I21*1/5,J21*1/5)</f>
         <v>0</v>
       </c>
-      <c r="N21" s="71"/>
+      <c r="N21" s="66"/>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
@@ -3634,9 +4027,9 @@
       <c r="B22" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C22" s="64"/>
-      <c r="D22" s="65"/>
-      <c r="E22" s="65"/>
+      <c r="C22" s="68"/>
+      <c r="D22" s="64"/>
+      <c r="E22" s="64"/>
       <c r="K22" s="11">
         <f>SUM(F22*1/3,G22*1/3,I22*1/3)</f>
         <v>0</v>
@@ -3649,7 +4042,7 @@
         <f>SUM(F22*1/5,G22*1/5,H22*1/5,I22*1/5,J22*1/5)</f>
         <v>0</v>
       </c>
-      <c r="N22" s="71"/>
+      <c r="N22" s="66"/>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
@@ -3658,13 +4051,13 @@
       <c r="B24" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C24" s="64" t="s">
+      <c r="C24" s="68" t="s">
         <v>46</v>
       </c>
-      <c r="D24" s="65" t="s">
+      <c r="D24" s="64" t="s">
         <v>21</v>
       </c>
-      <c r="E24" s="65" t="s">
+      <c r="E24" s="64" t="s">
         <v>32</v>
       </c>
       <c r="K24" s="11">
@@ -3687,9 +4080,9 @@
       <c r="B25" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C25" s="64"/>
-      <c r="D25" s="65"/>
-      <c r="E25" s="65"/>
+      <c r="C25" s="68"/>
+      <c r="D25" s="64"/>
+      <c r="E25" s="64"/>
       <c r="K25" s="11">
         <f>SUM(F25*1/3,G25*1/3,I25*1/3)</f>
         <v>0</v>
@@ -3710,9 +4103,9 @@
       <c r="B26" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C26" s="64"/>
-      <c r="D26" s="65"/>
-      <c r="E26" s="65"/>
+      <c r="C26" s="68"/>
+      <c r="D26" s="64"/>
+      <c r="E26" s="64"/>
       <c r="K26" s="11">
         <f>SUM(F26*1/3,G26*1/3,I26*1/3)</f>
         <v>0</v>
@@ -3733,13 +4126,13 @@
       <c r="B28" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C28" s="64" t="s">
+      <c r="C28" s="68" t="s">
         <v>47</v>
       </c>
-      <c r="D28" s="65" t="s">
+      <c r="D28" s="64" t="s">
         <v>22</v>
       </c>
-      <c r="E28" s="65" t="s">
+      <c r="E28" s="64" t="s">
         <v>33</v>
       </c>
       <c r="K28" s="11">
@@ -3762,9 +4155,9 @@
       <c r="B29" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C29" s="64"/>
-      <c r="D29" s="65"/>
-      <c r="E29" s="65"/>
+      <c r="C29" s="68"/>
+      <c r="D29" s="64"/>
+      <c r="E29" s="64"/>
       <c r="K29" s="11">
         <f>SUM(F29*1/3,G29*1/3,I29*1/3)</f>
         <v>0</v>
@@ -3785,9 +4178,9 @@
       <c r="B30" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C30" s="64"/>
-      <c r="D30" s="65"/>
-      <c r="E30" s="65"/>
+      <c r="C30" s="68"/>
+      <c r="D30" s="64"/>
+      <c r="E30" s="64"/>
       <c r="K30" s="11">
         <f>SUM(F30*1/3,G30*1/3,I30*1/3)</f>
         <v>0</v>
@@ -3808,13 +4201,13 @@
       <c r="B32" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C32" s="64" t="s">
+      <c r="C32" s="68" t="s">
         <v>48</v>
       </c>
-      <c r="D32" s="65" t="s">
+      <c r="D32" s="64" t="s">
         <v>23</v>
       </c>
-      <c r="E32" s="65" t="s">
+      <c r="E32" s="64" t="s">
         <v>29</v>
       </c>
       <c r="K32" s="11">
@@ -3837,9 +4230,9 @@
       <c r="B33" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C33" s="64"/>
-      <c r="D33" s="65"/>
-      <c r="E33" s="65"/>
+      <c r="C33" s="68"/>
+      <c r="D33" s="64"/>
+      <c r="E33" s="64"/>
       <c r="K33" s="54">
         <f>SUM(F33*1/3,G33*1/3,I33*1/3)</f>
         <v>0</v>
@@ -3860,9 +4253,9 @@
       <c r="B34" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C34" s="64"/>
-      <c r="D34" s="65"/>
-      <c r="E34" s="65"/>
+      <c r="C34" s="68"/>
+      <c r="D34" s="64"/>
+      <c r="E34" s="64"/>
       <c r="K34" s="11">
         <f>SUM(F34*1/3,G34*1/3,I34*1/3)</f>
         <v>0</v>
@@ -3883,13 +4276,13 @@
       <c r="B36" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C36" s="64" t="s">
+      <c r="C36" s="68" t="s">
         <v>49</v>
       </c>
-      <c r="D36" s="65" t="s">
+      <c r="D36" s="64" t="s">
         <v>24</v>
       </c>
-      <c r="E36" s="65" t="s">
+      <c r="E36" s="64" t="s">
         <v>34</v>
       </c>
       <c r="K36" s="11">
@@ -3912,9 +4305,9 @@
       <c r="B37" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C37" s="64"/>
-      <c r="D37" s="65"/>
-      <c r="E37" s="65"/>
+      <c r="C37" s="68"/>
+      <c r="D37" s="64"/>
+      <c r="E37" s="64"/>
       <c r="K37" s="11">
         <f>SUM(F37*1/3,G37*1/3,I37*1/3)</f>
         <v>0</v>
@@ -3935,9 +4328,9 @@
       <c r="B38" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C38" s="64"/>
-      <c r="D38" s="65"/>
-      <c r="E38" s="65"/>
+      <c r="C38" s="68"/>
+      <c r="D38" s="64"/>
+      <c r="E38" s="64"/>
       <c r="K38" s="11">
         <f>SUM(F38*1/3,G38*1/3,I38*1/3)</f>
         <v>0</v>
@@ -3952,12 +4345,12 @@
       </c>
     </row>
     <row r="40" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="73" t="s">
+      <c r="A40" s="78" t="s">
         <v>38</v>
       </c>
-      <c r="B40" s="73"/>
-      <c r="C40" s="73"/>
-      <c r="D40" s="73"/>
+      <c r="B40" s="78"/>
+      <c r="C40" s="78"/>
+      <c r="D40" s="78"/>
       <c r="E40" s="5"/>
       <c r="F40" s="13"/>
       <c r="G40" s="13"/>
@@ -3976,13 +4369,13 @@
       <c r="B42" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C42" s="64" t="s">
+      <c r="C42" s="68" t="s">
         <v>50</v>
       </c>
-      <c r="D42" s="65" t="s">
+      <c r="D42" s="64" t="s">
         <v>25</v>
       </c>
-      <c r="E42" s="65" t="s">
+      <c r="E42" s="64" t="s">
         <v>27</v>
       </c>
       <c r="K42" s="11">
@@ -3997,7 +4390,7 @@
         <f>SUM(F42*1/5,G42*1/5,H42*1/5,I42*1/5,J42*1/5)</f>
         <v>0</v>
       </c>
-      <c r="N42" s="71" t="s">
+      <c r="N42" s="66" t="s">
         <v>30</v>
       </c>
     </row>
@@ -4008,9 +4401,9 @@
       <c r="B43" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C43" s="64"/>
-      <c r="D43" s="65"/>
-      <c r="E43" s="65"/>
+      <c r="C43" s="68"/>
+      <c r="D43" s="64"/>
+      <c r="E43" s="64"/>
       <c r="K43" s="11">
         <f>SUM(F43*1/3,G43*1/3,I43*1/3)</f>
         <v>0</v>
@@ -4023,7 +4416,7 @@
         <f>SUM(F43*1/5,G43*1/5,H43*1/5,I43*1/5,J43*1/5)</f>
         <v>0</v>
       </c>
-      <c r="N43" s="71"/>
+      <c r="N43" s="66"/>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
@@ -4032,9 +4425,9 @@
       <c r="B44" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C44" s="64"/>
-      <c r="D44" s="65"/>
-      <c r="E44" s="65"/>
+      <c r="C44" s="68"/>
+      <c r="D44" s="64"/>
+      <c r="E44" s="64"/>
       <c r="F44" s="62"/>
       <c r="K44" s="11">
         <f>SUM(F44*1/3,G44*1/3,I44*1/3)</f>
@@ -4048,7 +4441,7 @@
         <f>SUM(F44*1/5,G44*1/5,H44*1/5,I44*1/5,J44*1/5)</f>
         <v>0</v>
       </c>
-      <c r="N44" s="71"/>
+      <c r="N44" s="66"/>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
@@ -4057,13 +4450,13 @@
       <c r="B46" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C46" s="64" t="s">
+      <c r="C46" s="68" t="s">
         <v>51</v>
       </c>
-      <c r="D46" s="65" t="s">
+      <c r="D46" s="64" t="s">
         <v>26</v>
       </c>
-      <c r="E46" s="65" t="s">
+      <c r="E46" s="64" t="s">
         <v>28</v>
       </c>
       <c r="K46" s="11">
@@ -4078,7 +4471,7 @@
         <f>SUM(F46*1/5,G46*1/5,H46*1/5,I46*1/5,J46*1/5)</f>
         <v>0</v>
       </c>
-      <c r="N46" s="71" t="s">
+      <c r="N46" s="66" t="s">
         <v>31</v>
       </c>
     </row>
@@ -4089,9 +4482,9 @@
       <c r="B47" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C47" s="64"/>
-      <c r="D47" s="65"/>
-      <c r="E47" s="65"/>
+      <c r="C47" s="68"/>
+      <c r="D47" s="64"/>
+      <c r="E47" s="64"/>
       <c r="K47" s="11">
         <f>SUM(F47*1/3,G47*1/3,I47*1/3)</f>
         <v>0</v>
@@ -4104,7 +4497,7 @@
         <f>SUM(F47*1/5,G47*1/5,H47*1/5,I47*1/5,J47*1/5)</f>
         <v>0</v>
       </c>
-      <c r="N47" s="71"/>
+      <c r="N47" s="66"/>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
@@ -4113,9 +4506,9 @@
       <c r="B48" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C48" s="64"/>
-      <c r="D48" s="65"/>
-      <c r="E48" s="65"/>
+      <c r="C48" s="68"/>
+      <c r="D48" s="64"/>
+      <c r="E48" s="64"/>
       <c r="K48" s="11">
         <f>SUM(F48*1/3,G48*1/3,I48*1/3)</f>
         <v>0</v>
@@ -4128,7 +4521,7 @@
         <f>SUM(F48*1/5,G48*1/5,H48*1/5,I48*1/5,J48*1/5)</f>
         <v>0</v>
       </c>
-      <c r="N48" s="71"/>
+      <c r="N48" s="66"/>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
@@ -4137,13 +4530,13 @@
       <c r="B50" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C50" s="64" t="s">
+      <c r="C50" s="68" t="s">
         <v>52</v>
       </c>
-      <c r="D50" s="65" t="s">
+      <c r="D50" s="64" t="s">
         <v>39</v>
       </c>
-      <c r="E50" s="65" t="s">
+      <c r="E50" s="64" t="s">
         <v>29</v>
       </c>
       <c r="K50" s="11">
@@ -4166,9 +4559,9 @@
       <c r="B51" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C51" s="64"/>
-      <c r="D51" s="65"/>
-      <c r="E51" s="65"/>
+      <c r="C51" s="68"/>
+      <c r="D51" s="64"/>
+      <c r="E51" s="64"/>
       <c r="K51" s="11">
         <f>SUM(F51*1/3,G51*1/3,I51*1/3)</f>
         <v>0</v>
@@ -4189,9 +4582,9 @@
       <c r="B52" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C52" s="64"/>
-      <c r="D52" s="65"/>
-      <c r="E52" s="65"/>
+      <c r="C52" s="68"/>
+      <c r="D52" s="64"/>
+      <c r="E52" s="64"/>
       <c r="F52" s="62"/>
       <c r="K52" s="11">
         <f>SUM(F52*1/3,G52*1/3,I52*1/3)</f>
@@ -4207,12 +4600,12 @@
       </c>
     </row>
     <row r="55" spans="1:14" s="14" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="72" t="s">
+      <c r="A55" s="79" t="s">
         <v>59</v>
       </c>
-      <c r="B55" s="72"/>
-      <c r="C55" s="72"/>
-      <c r="D55" s="72"/>
+      <c r="B55" s="79"/>
+      <c r="C55" s="79"/>
+      <c r="D55" s="79"/>
       <c r="E55" s="15"/>
       <c r="F55" s="16">
         <f t="shared" ref="F55:M55" si="0">MAX(F2:F52)</f>
@@ -4249,12 +4642,12 @@
       <c r="N55" s="17"/>
     </row>
     <row r="56" spans="1:14" s="18" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="74" t="s">
+      <c r="A56" s="77" t="s">
         <v>60</v>
       </c>
-      <c r="B56" s="74"/>
-      <c r="C56" s="74"/>
-      <c r="D56" s="74"/>
+      <c r="B56" s="77"/>
+      <c r="C56" s="77"/>
+      <c r="D56" s="77"/>
       <c r="E56" s="19"/>
       <c r="F56" s="20" t="e">
         <f t="shared" ref="F56:M56" si="1">AVERAGE(F2:F52)</f>
@@ -4291,13 +4684,13 @@
       <c r="N56" s="21"/>
     </row>
     <row r="58" spans="1:14" s="22" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="77" t="s">
+      <c r="A58" s="74" t="s">
         <v>67</v>
       </c>
-      <c r="B58" s="77"/>
-      <c r="C58" s="77"/>
-      <c r="D58" s="77"/>
-      <c r="E58" s="77"/>
+      <c r="B58" s="74"/>
+      <c r="C58" s="74"/>
+      <c r="D58" s="74"/>
+      <c r="E58" s="74"/>
       <c r="F58" s="29">
         <f>SUM(F55*(1/3),  G55*(1/3), I55*(1/3))</f>
         <v>0</v>
@@ -4312,13 +4705,13 @@
       <c r="N58" s="24"/>
     </row>
     <row r="59" spans="1:14" s="27" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="78" t="s">
+      <c r="A59" s="75" t="s">
         <v>68</v>
       </c>
-      <c r="B59" s="78"/>
-      <c r="C59" s="78"/>
-      <c r="D59" s="78"/>
-      <c r="E59" s="78"/>
+      <c r="B59" s="75"/>
+      <c r="C59" s="75"/>
+      <c r="D59" s="75"/>
+      <c r="E59" s="75"/>
       <c r="F59" s="28">
         <f>SUM(H55*(1/2),  J55*(1/2))</f>
         <v>0</v>
@@ -4333,13 +4726,13 @@
       <c r="N59" s="26"/>
     </row>
     <row r="60" spans="1:14" s="33" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="79" t="s">
+      <c r="A60" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="B60" s="79"/>
-      <c r="C60" s="79"/>
-      <c r="D60" s="79"/>
-      <c r="E60" s="79"/>
+      <c r="B60" s="76"/>
+      <c r="C60" s="76"/>
+      <c r="D60" s="76"/>
+      <c r="E60" s="76"/>
       <c r="F60" s="30">
         <f>SUM(F55*1/5, G55*1/5, H55*1/5, I55*1/5,J55*1/5)</f>
         <v>0</v>
@@ -4354,12 +4747,12 @@
       <c r="N60" s="32"/>
     </row>
     <row r="62" spans="1:14" s="37" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="75" t="s">
+      <c r="A62" s="72" t="s">
         <v>64</v>
       </c>
-      <c r="B62" s="75"/>
-      <c r="C62" s="75"/>
-      <c r="D62" s="75"/>
+      <c r="B62" s="72"/>
+      <c r="C62" s="72"/>
+      <c r="D62" s="72"/>
       <c r="E62" s="34"/>
       <c r="F62" s="35"/>
       <c r="G62" s="35"/>
@@ -4372,12 +4765,12 @@
       <c r="N62" s="36"/>
     </row>
     <row r="63" spans="1:14" s="37" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A63" s="75" t="s">
+      <c r="A63" s="72" t="s">
         <v>65</v>
       </c>
-      <c r="B63" s="76"/>
-      <c r="C63" s="76"/>
-      <c r="D63" s="76"/>
+      <c r="B63" s="73"/>
+      <c r="C63" s="73"/>
+      <c r="D63" s="73"/>
       <c r="E63" s="38"/>
       <c r="F63" s="35"/>
       <c r="G63" s="35"/>
@@ -4390,12 +4783,12 @@
       <c r="N63" s="36"/>
     </row>
     <row r="64" spans="1:14" s="37" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="75" t="s">
+      <c r="A64" s="72" t="s">
         <v>66</v>
       </c>
-      <c r="B64" s="76"/>
-      <c r="C64" s="76"/>
-      <c r="D64" s="76"/>
+      <c r="B64" s="73"/>
+      <c r="C64" s="73"/>
+      <c r="D64" s="73"/>
       <c r="E64" s="38"/>
       <c r="F64" s="35"/>
       <c r="G64" s="35"/>
@@ -4409,12 +4802,37 @@
     </row>
   </sheetData>
   <mergeCells count="53">
-    <mergeCell ref="A63:D63"/>
-    <mergeCell ref="A64:D64"/>
-    <mergeCell ref="A58:E58"/>
-    <mergeCell ref="A59:E59"/>
-    <mergeCell ref="A60:E60"/>
-    <mergeCell ref="A62:D62"/>
+    <mergeCell ref="A55:D55"/>
+    <mergeCell ref="N42:N44"/>
+    <mergeCell ref="C46:C48"/>
+    <mergeCell ref="D46:D48"/>
+    <mergeCell ref="E46:E48"/>
+    <mergeCell ref="N46:N48"/>
+    <mergeCell ref="E50:E52"/>
+    <mergeCell ref="C36:C38"/>
+    <mergeCell ref="D36:D38"/>
+    <mergeCell ref="E36:E38"/>
+    <mergeCell ref="A40:D40"/>
+    <mergeCell ref="C42:C44"/>
+    <mergeCell ref="D42:D44"/>
+    <mergeCell ref="E42:E44"/>
+    <mergeCell ref="N12:N14"/>
+    <mergeCell ref="C20:C22"/>
+    <mergeCell ref="D20:D22"/>
+    <mergeCell ref="E20:E22"/>
+    <mergeCell ref="N20:N22"/>
+    <mergeCell ref="C16:C18"/>
+    <mergeCell ref="D16:D18"/>
+    <mergeCell ref="E16:E18"/>
+    <mergeCell ref="N16:N18"/>
+    <mergeCell ref="C2:C4"/>
+    <mergeCell ref="D2:D4"/>
+    <mergeCell ref="E2:E4"/>
+    <mergeCell ref="N2:N4"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="D6:D8"/>
+    <mergeCell ref="E6:E8"/>
+    <mergeCell ref="N6:N8"/>
     <mergeCell ref="A56:D56"/>
     <mergeCell ref="A10:D10"/>
     <mergeCell ref="C12:C14"/>
@@ -4431,37 +4849,12 @@
     <mergeCell ref="E32:E34"/>
     <mergeCell ref="C50:C52"/>
     <mergeCell ref="D50:D52"/>
-    <mergeCell ref="C2:C4"/>
-    <mergeCell ref="D2:D4"/>
-    <mergeCell ref="E2:E4"/>
-    <mergeCell ref="N2:N4"/>
-    <mergeCell ref="C6:C8"/>
-    <mergeCell ref="D6:D8"/>
-    <mergeCell ref="E6:E8"/>
-    <mergeCell ref="N6:N8"/>
-    <mergeCell ref="N12:N14"/>
-    <mergeCell ref="C20:C22"/>
-    <mergeCell ref="D20:D22"/>
-    <mergeCell ref="E20:E22"/>
-    <mergeCell ref="N20:N22"/>
-    <mergeCell ref="C16:C18"/>
-    <mergeCell ref="D16:D18"/>
-    <mergeCell ref="E16:E18"/>
-    <mergeCell ref="N16:N18"/>
-    <mergeCell ref="C36:C38"/>
-    <mergeCell ref="D36:D38"/>
-    <mergeCell ref="E36:E38"/>
-    <mergeCell ref="A40:D40"/>
-    <mergeCell ref="C42:C44"/>
-    <mergeCell ref="D42:D44"/>
-    <mergeCell ref="E42:E44"/>
-    <mergeCell ref="A55:D55"/>
-    <mergeCell ref="N42:N44"/>
-    <mergeCell ref="C46:C48"/>
-    <mergeCell ref="D46:D48"/>
-    <mergeCell ref="E46:E48"/>
-    <mergeCell ref="N46:N48"/>
-    <mergeCell ref="E50:E52"/>
+    <mergeCell ref="A63:D63"/>
+    <mergeCell ref="A64:D64"/>
+    <mergeCell ref="A58:E58"/>
+    <mergeCell ref="A59:E59"/>
+    <mergeCell ref="A60:E60"/>
+    <mergeCell ref="A62:D62"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4542,17 +4935,17 @@
       <c r="N2" s="9"/>
     </row>
     <row r="3" spans="1:14" s="47" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="74" t="s">
+      <c r="A3" s="77" t="s">
         <v>74</v>
       </c>
-      <c r="B3" s="74"/>
-      <c r="C3" s="74"/>
-      <c r="D3" s="74"/>
-      <c r="E3" s="74"/>
-      <c r="F3" s="74"/>
-      <c r="G3" s="74"/>
-      <c r="H3" s="74"/>
-      <c r="I3" s="74"/>
+      <c r="B3" s="77"/>
+      <c r="C3" s="77"/>
+      <c r="D3" s="77"/>
+      <c r="E3" s="77"/>
+      <c r="F3" s="77"/>
+      <c r="G3" s="77"/>
+      <c r="H3" s="77"/>
+      <c r="I3" s="77"/>
       <c r="J3" s="49"/>
       <c r="K3" s="56"/>
       <c r="L3" s="56"/>
@@ -4578,10 +4971,10 @@
       <c r="B5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="71" t="s">
+      <c r="C5" s="66" t="s">
         <v>70</v>
       </c>
-      <c r="D5" s="71" t="s">
+      <c r="D5" s="66" t="s">
         <v>71</v>
       </c>
       <c r="J5" s="11">
@@ -4604,8 +4997,8 @@
       <c r="B6" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="71"/>
-      <c r="D6" s="71"/>
+      <c r="C6" s="66"/>
+      <c r="D6" s="66"/>
       <c r="J6" s="11">
         <f>SUM(E6*1/3,F6*1/3,H6*1/3)</f>
         <v>0</v>
@@ -4626,8 +5019,8 @@
       <c r="B7" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="71"/>
-      <c r="D7" s="71"/>
+      <c r="C7" s="66"/>
+      <c r="D7" s="66"/>
       <c r="J7" s="11">
         <f>SUM(E7*1/3,F7*1/3,H7*1/3)</f>
         <v>0</v>
@@ -4648,10 +5041,10 @@
       <c r="B9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="71" t="s">
+      <c r="C9" s="66" t="s">
         <v>72</v>
       </c>
-      <c r="D9" s="71" t="s">
+      <c r="D9" s="66" t="s">
         <v>73</v>
       </c>
       <c r="J9" s="11">
@@ -4674,8 +5067,8 @@
       <c r="B10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="71"/>
-      <c r="D10" s="71"/>
+      <c r="C10" s="66"/>
+      <c r="D10" s="66"/>
       <c r="J10" s="11">
         <f>SUM(E10*1/3,F10*1/3,H10*1/3)</f>
         <v>0</v>
@@ -4696,8 +5089,8 @@
       <c r="B11" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C11" s="71"/>
-      <c r="D11" s="71"/>
+      <c r="C11" s="66"/>
+      <c r="D11" s="66"/>
       <c r="J11" s="11">
         <f>SUM(E11*1/3,F11*1/3,H11*1/3)</f>
         <v>0</v>
@@ -4718,10 +5111,10 @@
       <c r="B13" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C13" s="71" t="s">
+      <c r="C13" s="66" t="s">
         <v>77</v>
       </c>
-      <c r="D13" s="71" t="s">
+      <c r="D13" s="66" t="s">
         <v>84</v>
       </c>
       <c r="J13" s="11">
@@ -4744,8 +5137,8 @@
       <c r="B14" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C14" s="71"/>
-      <c r="D14" s="71"/>
+      <c r="C14" s="66"/>
+      <c r="D14" s="66"/>
       <c r="J14" s="11">
         <f>SUM(E14*1/3,F14*1/3,H14*1/3)</f>
         <v>0</v>
@@ -4766,8 +5159,8 @@
       <c r="B15" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C15" s="71"/>
-      <c r="D15" s="71"/>
+      <c r="C15" s="66"/>
+      <c r="D15" s="66"/>
       <c r="J15" s="11">
         <f>SUM(E15*1/3,F15*1/3,H15*1/3)</f>
         <v>0</v>
@@ -4788,10 +5181,10 @@
       <c r="B17" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C17" s="71" t="s">
+      <c r="C17" s="66" t="s">
         <v>83</v>
       </c>
-      <c r="D17" s="71" t="s">
+      <c r="D17" s="66" t="s">
         <v>82</v>
       </c>
       <c r="J17" s="11">
@@ -4814,8 +5207,8 @@
       <c r="B18" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C18" s="71"/>
-      <c r="D18" s="71"/>
+      <c r="C18" s="66"/>
+      <c r="D18" s="66"/>
       <c r="J18" s="11">
         <f>SUM(E18*1/3,F18*1/3,H18*1/3)</f>
         <v>0</v>
@@ -4836,8 +5229,8 @@
       <c r="B19" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C19" s="71"/>
-      <c r="D19" s="71"/>
+      <c r="C19" s="66"/>
+      <c r="D19" s="66"/>
       <c r="J19" s="11">
         <f>SUM(E19*1/3,F19*1/3,H19*1/3)</f>
         <v>0</v>
@@ -4861,10 +5254,10 @@
       <c r="B21" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C21" s="71" t="s">
+      <c r="C21" s="66" t="s">
         <v>75</v>
       </c>
-      <c r="D21" s="71" t="s">
+      <c r="D21" s="66" t="s">
         <v>76</v>
       </c>
       <c r="J21" s="11">
@@ -4887,8 +5280,8 @@
       <c r="B22" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C22" s="71"/>
-      <c r="D22" s="71"/>
+      <c r="C22" s="66"/>
+      <c r="D22" s="66"/>
       <c r="J22" s="11">
         <f>SUM(E22*1/3,F22*1/3,H22*1/3)</f>
         <v>0</v>
@@ -4909,8 +5302,8 @@
       <c r="B23" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C23" s="71"/>
-      <c r="D23" s="71"/>
+      <c r="C23" s="66"/>
+      <c r="D23" s="66"/>
       <c r="J23" s="11">
         <f>SUM(E23*1/3,F23*1/3,H23*1/3)</f>
         <v>0</v>
@@ -4931,10 +5324,10 @@
       <c r="B25" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C25" s="71" t="s">
+      <c r="C25" s="66" t="s">
         <v>80</v>
       </c>
-      <c r="D25" s="71" t="s">
+      <c r="D25" s="66" t="s">
         <v>78</v>
       </c>
       <c r="J25" s="11">
@@ -4957,8 +5350,8 @@
       <c r="B26" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C26" s="71"/>
-      <c r="D26" s="71"/>
+      <c r="C26" s="66"/>
+      <c r="D26" s="66"/>
       <c r="J26" s="11">
         <f>SUM(E26*1/3,F26*1/3,H26*1/3)</f>
         <v>0</v>
@@ -4979,8 +5372,8 @@
       <c r="B27" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C27" s="71"/>
-      <c r="D27" s="71"/>
+      <c r="C27" s="66"/>
+      <c r="D27" s="66"/>
       <c r="J27" s="11">
         <f>SUM(E27*1/3,F27*1/3,H27*1/3)</f>
         <v>0</v>
@@ -5001,10 +5394,10 @@
       <c r="B29" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C29" s="71" t="s">
+      <c r="C29" s="66" t="s">
         <v>81</v>
       </c>
-      <c r="D29" s="71" t="s">
+      <c r="D29" s="66" t="s">
         <v>79</v>
       </c>
       <c r="J29" s="11">
@@ -5027,8 +5420,8 @@
       <c r="B30" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C30" s="71"/>
-      <c r="D30" s="71"/>
+      <c r="C30" s="66"/>
+      <c r="D30" s="66"/>
       <c r="J30" s="11">
         <f>SUM(E30*1/3,F30*1/3,H30*1/3)</f>
         <v>0</v>
@@ -5049,8 +5442,8 @@
       <c r="B31" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C31" s="71"/>
-      <c r="D31" s="71"/>
+      <c r="C31" s="66"/>
+      <c r="D31" s="66"/>
       <c r="J31" s="11">
         <f>SUM(E31*1/3,F31*1/3,H31*1/3)</f>
         <v>0</v>
@@ -5065,12 +5458,12 @@
       </c>
     </row>
     <row r="34" spans="1:14" s="14" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="72" t="s">
+      <c r="A34" s="79" t="s">
         <v>59</v>
       </c>
-      <c r="B34" s="72"/>
-      <c r="C34" s="72"/>
-      <c r="D34" s="72"/>
+      <c r="B34" s="79"/>
+      <c r="C34" s="79"/>
+      <c r="D34" s="79"/>
       <c r="E34" s="16">
         <f t="shared" ref="E34:L34" si="0">MAX(E4:E32)</f>
         <v>0</v>
@@ -5107,12 +5500,12 @@
       <c r="N34" s="17"/>
     </row>
     <row r="35" spans="1:14" s="52" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="77" t="s">
+      <c r="A35" s="74" t="s">
         <v>60</v>
       </c>
-      <c r="B35" s="77"/>
-      <c r="C35" s="77"/>
-      <c r="D35" s="77"/>
+      <c r="B35" s="74"/>
+      <c r="C35" s="74"/>
+      <c r="D35" s="74"/>
       <c r="E35" s="29" t="e">
         <f t="shared" ref="E35:L35" si="1">AVERAGE(E5:E32)</f>
         <v>#DIV/0!</v>
@@ -5150,12 +5543,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A34:D34"/>
-    <mergeCell ref="A35:D35"/>
-    <mergeCell ref="C13:C15"/>
-    <mergeCell ref="D13:D15"/>
-    <mergeCell ref="C29:C31"/>
-    <mergeCell ref="D29:D31"/>
     <mergeCell ref="A3:I3"/>
     <mergeCell ref="C21:C23"/>
     <mergeCell ref="D21:D23"/>
@@ -5167,6 +5554,12 @@
     <mergeCell ref="C9:C11"/>
     <mergeCell ref="D17:D19"/>
     <mergeCell ref="C17:C19"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="C13:C15"/>
+    <mergeCell ref="D13:D15"/>
+    <mergeCell ref="C29:C31"/>
+    <mergeCell ref="D29:D31"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/benchmarking/results/results.xlsx
+++ b/benchmarking/results/results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/deborahdore/Documents/political-debates-graph-analysis/benchmarking/results/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EF89D27-955F-D842-BBC2-48AFB651C750}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49C871E4-A1B9-7148-9667-3B4F4FE704E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="21600" activeTab="1" xr2:uid="{E2EDC037-19C4-FE46-A599-BB595128A04F}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="30240" windowHeight="18900" xr2:uid="{E2EDC037-19C4-FE46-A599-BB595128A04F}"/>
   </bookViews>
   <sheets>
     <sheet name="Results BASIC" sheetId="1" r:id="rId1"/>
@@ -233,15 +233,6 @@
     <t>WEIGHTED SUM OF ALL</t>
   </si>
   <si>
-    <t>BEST RESULT OF 1) text_speaker_year WITH DISTMULT</t>
-  </si>
-  <si>
-    <t>BEST RESULT OF 2) text_speaker WITH CONVE</t>
-  </si>
-  <si>
-    <t>BEST RESULT OF 3) text_year WITH DISTMULT</t>
-  </si>
-  <si>
     <t>1) WEIGHTED MEAN OF MAX LP, LD, TC:</t>
   </si>
   <si>
@@ -311,6 +302,15 @@
   </si>
   <si>
     <t>RELATION CLASSIFICATION  F1-MACRO</t>
+  </si>
+  <si>
+    <t>BEST RESULT OF 1) text_speaker_year</t>
+  </si>
+  <si>
+    <t>BEST RESULT OF 2) text_claim_year</t>
+  </si>
+  <si>
+    <t>BEST RESULT OF 3) text+claim_speaker_year</t>
   </si>
 </sst>
 </file>
@@ -1077,7 +1077,7 @@
         <v>56</v>
       </c>
       <c r="J1" s="12" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="K1" s="7" t="s">
         <v>14</v>
@@ -1382,6 +1382,21 @@
       <c r="E16" s="64" t="s">
         <v>27</v>
       </c>
+      <c r="F16" s="11">
+        <v>0.25311472569999999</v>
+      </c>
+      <c r="G16" s="11">
+        <v>0.14518082709999999</v>
+      </c>
+      <c r="H16" s="11">
+        <v>0.40370306280000001</v>
+      </c>
+      <c r="I16" s="11">
+        <v>0.79073086699999995</v>
+      </c>
+      <c r="J16" s="11">
+        <v>0.44106115289999998</v>
+      </c>
       <c r="K16" s="66" t="s">
         <v>36</v>
       </c>
@@ -1396,6 +1411,21 @@
       <c r="C17" s="68"/>
       <c r="D17" s="64"/>
       <c r="E17" s="64"/>
+      <c r="F17" s="11">
+        <v>6.6187922000000001E-3</v>
+      </c>
+      <c r="G17" s="11">
+        <v>4.326008E-4</v>
+      </c>
+      <c r="H17" s="11">
+        <v>0.40811559089999999</v>
+      </c>
+      <c r="I17" s="11">
+        <v>0.63536669859999995</v>
+      </c>
+      <c r="J17" s="11">
+        <v>0.48203358359999998</v>
+      </c>
       <c r="K17" s="66"/>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.2">
@@ -1408,6 +1438,21 @@
       <c r="C18" s="68"/>
       <c r="D18" s="64"/>
       <c r="E18" s="64"/>
+      <c r="F18" s="11">
+        <v>1.9467035999999999E-3</v>
+      </c>
+      <c r="G18" s="11">
+        <v>0.24390032880000001</v>
+      </c>
+      <c r="H18" s="11">
+        <v>0.37281536599999998</v>
+      </c>
+      <c r="I18" s="11">
+        <v>0.61435163960000005</v>
+      </c>
+      <c r="J18" s="11">
+        <v>0.31319458500000003</v>
+      </c>
       <c r="K18" s="66"/>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.2">
@@ -2126,7 +2171,7 @@
       </c>
       <c r="G55" s="40">
         <f>MAX(G2:G52)</f>
-        <v>0.21803419730000001</v>
+        <v>0.24390032880000001</v>
       </c>
       <c r="H55" s="40">
         <f>MAX(H2:H52)</f>
@@ -2152,23 +2197,23 @@
       <c r="E56" s="43"/>
       <c r="F56" s="44">
         <f>AVERAGE(F2:F52)</f>
-        <v>0.11521239868787879</v>
+        <v>0.11288026050555554</v>
       </c>
       <c r="G56" s="44">
         <f>AVERAGE(G2:G52)</f>
-        <v>4.0409736993939391E-2</v>
+        <v>4.7862085486111108E-2</v>
       </c>
       <c r="H56" s="44">
         <f>AVERAGE(H2:H52)</f>
-        <v>0.55629249514242429</v>
+        <v>0.54284128776111118</v>
       </c>
       <c r="I56" s="44">
         <f>AVERAGE(I2:I52)</f>
-        <v>0.66089750283333337</v>
+        <v>0.66250185551944452</v>
       </c>
       <c r="J56" s="44">
         <f>AVERAGE(J2:J52)</f>
-        <v>0.49391995730606059</v>
+        <v>0.48710133090555563</v>
       </c>
       <c r="K56" s="45"/>
     </row>
@@ -3642,17 +3687,32 @@
       <c r="E2" s="67" t="s">
         <v>13</v>
       </c>
+      <c r="F2" s="11">
+        <v>7.94822627E-2</v>
+      </c>
+      <c r="G2" s="11">
+        <v>2.7804410999999998E-3</v>
+      </c>
+      <c r="H2" s="11">
+        <v>0.30028763180000001</v>
+      </c>
+      <c r="I2" s="11">
+        <v>0.61040879550000005</v>
+      </c>
+      <c r="J2" s="11">
+        <v>0.46355931169999998</v>
+      </c>
       <c r="K2" s="11">
         <f>SUM(F2*1/3,G2*1/3,I2*1/3)</f>
-        <v>0</v>
+        <v>0.23089049976666667</v>
       </c>
       <c r="L2" s="11">
         <f>SUM(H2*1/2,J2*1/2)</f>
-        <v>0</v>
+        <v>0.38192347174999997</v>
       </c>
       <c r="M2" s="11">
         <f>SUM(F2*1/5,G2*1/5,H2*1/5,I2*1/5,J2*1/5)</f>
-        <v>0</v>
+        <v>0.29130368856</v>
       </c>
       <c r="N2" s="65" t="s">
         <v>15</v>
@@ -3668,17 +3728,32 @@
       <c r="C3" s="68"/>
       <c r="D3" s="64"/>
       <c r="E3" s="64"/>
+      <c r="F3" s="11">
+        <v>2.3969319E-3</v>
+      </c>
+      <c r="G3" s="11">
+        <v>1.8216682999999999E-3</v>
+      </c>
+      <c r="H3" s="11">
+        <v>0.32809204219999999</v>
+      </c>
+      <c r="I3" s="11">
+        <v>0.49360722829999998</v>
+      </c>
+      <c r="J3" s="11">
+        <v>0.48535807889999999</v>
+      </c>
       <c r="K3" s="11">
         <f>SUM(F3*1/3,G3*1/3,I3*1/3)</f>
-        <v>0</v>
+        <v>0.16594194283333333</v>
       </c>
       <c r="L3" s="11">
         <f>SUM(H3*1/2,J3*1/2)</f>
-        <v>0</v>
+        <v>0.40672506055000002</v>
       </c>
       <c r="M3" s="11">
         <f>SUM(F3*1/5,G3*1/5,H3*1/5,I3*1/5,J3*1/5)</f>
-        <v>0</v>
+        <v>0.26225518991999996</v>
       </c>
       <c r="N3" s="66"/>
     </row>
@@ -3692,17 +3767,32 @@
       <c r="C4" s="68"/>
       <c r="D4" s="64"/>
       <c r="E4" s="64"/>
+      <c r="F4" s="11">
+        <v>6.5867689399999999E-2</v>
+      </c>
+      <c r="G4" s="11">
+        <v>3.9309684000000001E-3</v>
+      </c>
+      <c r="H4" s="11">
+        <v>0.2533077661</v>
+      </c>
+      <c r="I4" s="11">
+        <v>0.69625611379999996</v>
+      </c>
+      <c r="J4" s="11">
+        <v>0.43599219389999999</v>
+      </c>
       <c r="K4" s="11">
         <f>SUM(F4*1/3,G4*1/3,I4*1/3)</f>
-        <v>0</v>
+        <v>0.25535159053333334</v>
       </c>
       <c r="L4" s="11">
         <f>SUM(H4*1/2,J4*1/2)</f>
-        <v>0</v>
+        <v>0.34464998000000002</v>
       </c>
       <c r="M4" s="11">
         <f>SUM(F4*1/5,G4*1/5,H4*1/5,I4*1/5,J4*1/5)</f>
-        <v>0</v>
+        <v>0.29107094631999997</v>
       </c>
       <c r="N4" s="66"/>
     </row>
@@ -3722,17 +3812,32 @@
       <c r="E6" s="64" t="s">
         <v>13</v>
       </c>
+      <c r="F6" s="11">
+        <v>9.81988887E-2</v>
+      </c>
+      <c r="G6" s="11">
+        <v>9.4845755999999996E-3</v>
+      </c>
+      <c r="H6" s="11">
+        <v>0.25560452189999999</v>
+      </c>
+      <c r="I6" s="11">
+        <v>0.68919924190000004</v>
+      </c>
+      <c r="J6" s="11">
+        <v>0.41944522960000002</v>
+      </c>
       <c r="K6" s="11">
         <f>SUM(F6*1/3,G6*1/3,I6*1/3)</f>
-        <v>0</v>
+        <v>0.26562756873333332</v>
       </c>
       <c r="L6" s="11">
         <f>SUM(H6*1/2,J6*1/2)</f>
-        <v>0</v>
+        <v>0.33752487575000001</v>
       </c>
       <c r="M6" s="11">
         <f>SUM(F6*1/5,G6*1/5,H6*1/5,I6*1/5,J6*1/5)</f>
-        <v>0</v>
+        <v>0.29438649154000002</v>
       </c>
       <c r="N6" s="66" t="s">
         <v>16</v>
@@ -3748,17 +3853,32 @@
       <c r="C7" s="68"/>
       <c r="D7" s="64"/>
       <c r="E7" s="64"/>
+      <c r="F7" s="11">
+        <v>1.3604138700000001E-2</v>
+      </c>
+      <c r="G7" s="11">
+        <v>2.77831E-3</v>
+      </c>
+      <c r="H7" s="11">
+        <v>0.36673692279999998</v>
+      </c>
+      <c r="I7" s="11">
+        <v>0.50241178500000006</v>
+      </c>
+      <c r="J7" s="11">
+        <v>0.49342533859999999</v>
+      </c>
       <c r="K7" s="11">
         <f>SUM(F7*1/3,G7*1/3,I7*1/3)</f>
-        <v>0</v>
+        <v>0.17293141123333336</v>
       </c>
       <c r="L7" s="11">
         <f>SUM(H7*1/2,J7*1/2)</f>
-        <v>0</v>
+        <v>0.43008113069999998</v>
       </c>
       <c r="M7" s="11">
         <f>SUM(F7*1/5,G7*1/5,H7*1/5,I7*1/5,J7*1/5)</f>
-        <v>0</v>
+        <v>0.27579129901999999</v>
       </c>
       <c r="N7" s="66"/>
     </row>
@@ -3772,17 +3892,32 @@
       <c r="C8" s="68"/>
       <c r="D8" s="64"/>
       <c r="E8" s="64"/>
+      <c r="F8" s="11">
+        <v>3.8321517499999999E-2</v>
+      </c>
+      <c r="G8" s="11">
+        <v>9.5803794000000001E-3</v>
+      </c>
+      <c r="H8" s="11">
+        <v>0.2387430542</v>
+      </c>
+      <c r="I8" s="11">
+        <v>0.59762281890000002</v>
+      </c>
+      <c r="J8" s="11">
+        <v>0.47463989049999999</v>
+      </c>
       <c r="K8" s="11">
         <f>SUM(F8*1/3,G8*1/3,I8*1/3)</f>
-        <v>0</v>
+        <v>0.21517490526666666</v>
       </c>
       <c r="L8" s="11">
         <f>SUM(H8*1/2,J8*1/2)</f>
-        <v>0</v>
+        <v>0.35669147234999998</v>
       </c>
       <c r="M8" s="11">
         <f>SUM(F8*1/5,G8*1/5,H8*1/5,I8*1/5,J8*1/5)</f>
-        <v>0</v>
+        <v>0.2717815321</v>
       </c>
       <c r="N8" s="66"/>
     </row>
@@ -3820,17 +3955,32 @@
       <c r="E12" s="64" t="s">
         <v>17</v>
       </c>
+      <c r="F12" s="11">
+        <v>4.5829338400000003E-2</v>
+      </c>
+      <c r="G12" s="11">
+        <v>1.0546500999999999E-3</v>
+      </c>
+      <c r="H12" s="11">
+        <v>0.53288590599999996</v>
+      </c>
+      <c r="I12" s="11">
+        <v>0.56245538740000001</v>
+      </c>
+      <c r="J12" s="11">
+        <v>0.53984978090000002</v>
+      </c>
       <c r="K12" s="11">
         <f>SUM(F12*1/3,G12*1/3,I12*1/3)</f>
-        <v>0</v>
+        <v>0.2031131253</v>
       </c>
       <c r="L12" s="11">
         <f>SUM(H12*1/2,J12*1/2)</f>
-        <v>0</v>
+        <v>0.53636784344999999</v>
       </c>
       <c r="M12" s="11">
         <f>SUM(F12*1/5,G12*1/5,H12*1/5,I12*1/5,J12*1/5)</f>
-        <v>0</v>
+        <v>0.33641501256</v>
       </c>
       <c r="N12" s="66" t="s">
         <v>18</v>
@@ -3846,17 +3996,32 @@
       <c r="C13" s="68"/>
       <c r="D13" s="64"/>
       <c r="E13" s="64"/>
+      <c r="F13" s="11">
+        <v>7.9194630899999993E-2</v>
+      </c>
+      <c r="G13" s="11">
+        <v>2.5886864999999999E-3</v>
+      </c>
+      <c r="H13" s="11">
+        <v>0.26001917549999998</v>
+      </c>
+      <c r="I13" s="11">
+        <v>0.51953307689999995</v>
+      </c>
+      <c r="J13" s="11">
+        <v>0.4732195669</v>
+      </c>
       <c r="K13" s="11">
         <f>SUM(F13*1/3,G13*1/3,I13*1/3)</f>
-        <v>0</v>
+        <v>0.20043879809999998</v>
       </c>
       <c r="L13" s="11">
         <f>SUM(H13*1/2,J13*1/2)</f>
-        <v>0</v>
+        <v>0.36661937119999999</v>
       </c>
       <c r="M13" s="11">
         <f>SUM(F13*1/5,G13*1/5,H13*1/5,I13*1/5,J13*1/5)</f>
-        <v>0</v>
+        <v>0.26691102733999994</v>
       </c>
       <c r="N13" s="66"/>
     </row>
@@ -3870,17 +4035,32 @@
       <c r="C14" s="68"/>
       <c r="D14" s="64"/>
       <c r="E14" s="64"/>
+      <c r="F14" s="11">
+        <v>3.8350910000000001E-4</v>
+      </c>
+      <c r="G14" s="11">
+        <v>1.0546500999999999E-3</v>
+      </c>
+      <c r="H14" s="11">
+        <v>9.3000958800000005E-2</v>
+      </c>
+      <c r="I14" s="11">
+        <v>0.55925740629999998</v>
+      </c>
+      <c r="J14" s="11">
+        <v>0.46283236560000002</v>
+      </c>
       <c r="K14" s="11">
         <f>SUM(F14*1/3,G14*1/3,I14*1/3)</f>
-        <v>0</v>
+        <v>0.18689852183333333</v>
       </c>
       <c r="L14" s="11">
         <f>SUM(H14*1/2,J14*1/2)</f>
-        <v>0</v>
+        <v>0.2779166622</v>
       </c>
       <c r="M14" s="11">
         <f>SUM(F14*1/5,G14*1/5,H14*1/5,I14*1/5,J14*1/5)</f>
-        <v>0</v>
+        <v>0.22330577798000001</v>
       </c>
       <c r="N14" s="66"/>
     </row>
@@ -3900,17 +4080,32 @@
       <c r="E16" s="64" t="s">
         <v>27</v>
       </c>
+      <c r="F16" s="11">
+        <v>9.5397890700000001E-2</v>
+      </c>
+      <c r="G16" s="11">
+        <v>1.6203259800000001E-2</v>
+      </c>
+      <c r="H16" s="11">
+        <v>0.38044103550000002</v>
+      </c>
+      <c r="I16" s="11">
+        <v>0.81662030279999998</v>
+      </c>
+      <c r="J16" s="11">
+        <v>0.42969558610000003</v>
+      </c>
       <c r="K16" s="11">
         <f>SUM(F16*1/3,G16*1/3,I16*1/3)</f>
-        <v>0</v>
+        <v>0.3094071511</v>
       </c>
       <c r="L16" s="11">
         <f>SUM(H16*1/2,J16*1/2)</f>
-        <v>0</v>
+        <v>0.40506831080000005</v>
       </c>
       <c r="M16" s="11">
         <f>SUM(F16*1/5,G16*1/5,H16*1/5,I16*1/5,J16*1/5)</f>
-        <v>0</v>
+        <v>0.34767161497999999</v>
       </c>
       <c r="N16" s="66" t="s">
         <v>36</v>
@@ -3926,17 +4121,32 @@
       <c r="C17" s="68"/>
       <c r="D17" s="64"/>
       <c r="E17" s="64"/>
+      <c r="F17" s="11">
+        <v>3.7296260800000001E-2</v>
+      </c>
+      <c r="G17" s="11">
+        <v>1.725791E-3</v>
+      </c>
+      <c r="H17" s="11">
+        <v>0.42818791950000001</v>
+      </c>
+      <c r="I17" s="11">
+        <v>0.76097577869999999</v>
+      </c>
+      <c r="J17" s="11">
+        <v>0.45324013530000001</v>
+      </c>
       <c r="K17" s="11">
         <f>SUM(F17*1/3,G17*1/3,I17*1/3)</f>
-        <v>0</v>
+        <v>0.2666659435</v>
       </c>
       <c r="L17" s="11">
         <f>SUM(H17*1/2,J17*1/2)</f>
-        <v>0</v>
+        <v>0.44071402739999999</v>
       </c>
       <c r="M17" s="11">
         <f>SUM(F17*1/5,G17*1/5,H17*1/5,I17*1/5,J17*1/5)</f>
-        <v>0</v>
+        <v>0.33628517706000005</v>
       </c>
       <c r="N17" s="66"/>
     </row>
@@ -3950,17 +4160,32 @@
       <c r="C18" s="68"/>
       <c r="D18" s="64"/>
       <c r="E18" s="64"/>
+      <c r="F18" s="11">
+        <v>1.0546500000000001E-3</v>
+      </c>
+      <c r="G18" s="11">
+        <v>1.725791E-3</v>
+      </c>
+      <c r="H18" s="11">
+        <v>3.73921381E-2</v>
+      </c>
+      <c r="I18" s="11">
+        <v>0.57534376239999996</v>
+      </c>
+      <c r="J18" s="11">
+        <v>0.41970516870000002</v>
+      </c>
       <c r="K18" s="11">
         <f>SUM(F18*1/3,G18*1/3,I18*1/3)</f>
-        <v>0</v>
-      </c>
-      <c r="L18" s="54">
+        <v>0.19270806779999999</v>
+      </c>
+      <c r="L18" s="11">
         <f>SUM(H18*1/2,J18*1/2)</f>
-        <v>0</v>
+        <v>0.22854865340000002</v>
       </c>
       <c r="M18" s="11">
         <f>SUM(F18*1/5,G18*1/5,H18*1/5,I18*1/5,J18*1/5)</f>
-        <v>0</v>
+        <v>0.20704430204000002</v>
       </c>
       <c r="N18" s="66"/>
     </row>
@@ -3980,17 +4205,32 @@
       <c r="E20" s="64" t="s">
         <v>28</v>
       </c>
+      <c r="F20" s="11">
+        <v>7.0565675899999999E-2</v>
+      </c>
+      <c r="G20" s="11">
+        <v>5.7526367E-3</v>
+      </c>
+      <c r="H20" s="11">
+        <v>0.24928092039999999</v>
+      </c>
+      <c r="I20" s="11">
+        <v>0.78841326899999997</v>
+      </c>
+      <c r="J20" s="11">
+        <v>0.44505542780000001</v>
+      </c>
       <c r="K20" s="11">
         <f>SUM(F20*1/3,G20*1/3,I20*1/3)</f>
-        <v>0</v>
+        <v>0.28824386053333334</v>
       </c>
       <c r="L20" s="11">
         <f>SUM(H20*1/2,J20*1/2)</f>
-        <v>0</v>
+        <v>0.3471681741</v>
       </c>
       <c r="M20" s="11">
         <f>SUM(F20*1/5,G20*1/5,H20*1/5,I20*1/5,J20*1/5)</f>
-        <v>0</v>
+        <v>0.31181358595999997</v>
       </c>
       <c r="N20" s="66" t="s">
         <v>35</v>
@@ -4006,17 +4246,32 @@
       <c r="C21" s="68"/>
       <c r="D21" s="64"/>
       <c r="E21" s="64"/>
+      <c r="F21" s="11">
+        <v>1.05465005E-2</v>
+      </c>
+      <c r="G21" s="11">
+        <v>4.0268457000000001E-3</v>
+      </c>
+      <c r="H21" s="11">
+        <v>0.37142857140000002</v>
+      </c>
+      <c r="I21" s="11">
+        <v>0.63057692489999995</v>
+      </c>
+      <c r="J21" s="11">
+        <v>0.47740912070000002</v>
+      </c>
       <c r="K21" s="11">
         <f>SUM(F21*1/3,G21*1/3,I21*1/3)</f>
-        <v>0</v>
+        <v>0.21505009036666667</v>
       </c>
       <c r="L21" s="11">
         <f>SUM(H21*1/2,J21*1/2)</f>
-        <v>0</v>
-      </c>
-      <c r="M21" s="54">
+        <v>0.42441884605000002</v>
+      </c>
+      <c r="M21" s="11">
         <f>SUM(F21*1/5,G21*1/5,H21*1/5,I21*1/5,J21*1/5)</f>
-        <v>0</v>
+        <v>0.29879759264</v>
       </c>
       <c r="N21" s="66"/>
     </row>
@@ -4030,17 +4285,32 @@
       <c r="C22" s="68"/>
       <c r="D22" s="64"/>
       <c r="E22" s="64"/>
+      <c r="F22" s="11">
+        <v>0</v>
+      </c>
+      <c r="G22" s="11">
+        <v>1.6299137E-3</v>
+      </c>
+      <c r="H22" s="11">
+        <v>0.16663470759999999</v>
+      </c>
+      <c r="I22" s="11">
+        <v>0.47885293839999998</v>
+      </c>
+      <c r="J22" s="11">
+        <v>0.4799734652</v>
+      </c>
       <c r="K22" s="11">
         <f>SUM(F22*1/3,G22*1/3,I22*1/3)</f>
-        <v>0</v>
+        <v>0.1601609507</v>
       </c>
       <c r="L22" s="11">
         <f>SUM(H22*1/2,J22*1/2)</f>
-        <v>0</v>
+        <v>0.32330408639999997</v>
       </c>
       <c r="M22" s="11">
         <f>SUM(F22*1/5,G22*1/5,H22*1/5,I22*1/5,J22*1/5)</f>
-        <v>0</v>
+        <v>0.22541820497999998</v>
       </c>
       <c r="N22" s="66"/>
     </row>
@@ -4060,17 +4330,32 @@
       <c r="E24" s="64" t="s">
         <v>32</v>
       </c>
+      <c r="F24" s="11">
+        <v>5.6088207100000002E-2</v>
+      </c>
+      <c r="G24" s="11">
+        <v>1.05465004E-2</v>
+      </c>
+      <c r="H24" s="11">
+        <v>0.37488015340000003</v>
+      </c>
+      <c r="I24" s="11">
+        <v>0.71524515099999997</v>
+      </c>
+      <c r="J24" s="11">
+        <v>0.4496405751</v>
+      </c>
       <c r="K24" s="11">
         <f>SUM(F24*1/3,G24*1/3,I24*1/3)</f>
-        <v>0</v>
+        <v>0.26062661949999999</v>
       </c>
       <c r="L24" s="11">
         <f>SUM(H24*1/2,J24*1/2)</f>
-        <v>0</v>
+        <v>0.41226036425000001</v>
       </c>
       <c r="M24" s="11">
         <f>SUM(F24*1/5,G24*1/5,H24*1/5,I24*1/5,J24*1/5)</f>
-        <v>0</v>
+        <v>0.32128011739999995</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.2">
@@ -4083,17 +4368,32 @@
       <c r="C25" s="68"/>
       <c r="D25" s="64"/>
       <c r="E25" s="64"/>
+      <c r="F25" s="11">
+        <v>2.7229146700000002E-2</v>
+      </c>
+      <c r="G25" s="11">
+        <v>2.2051774000000001E-3</v>
+      </c>
+      <c r="H25" s="11">
+        <v>0.33710450619999999</v>
+      </c>
+      <c r="I25" s="11">
+        <v>0.73998732089999997</v>
+      </c>
+      <c r="J25" s="11">
+        <v>0.45159151089999999</v>
+      </c>
       <c r="K25" s="11">
         <f>SUM(F25*1/3,G25*1/3,I25*1/3)</f>
-        <v>0</v>
+        <v>0.25647388166666663</v>
       </c>
       <c r="L25" s="11">
         <f>SUM(H25*1/2,J25*1/2)</f>
-        <v>0</v>
+        <v>0.39434800854999996</v>
       </c>
       <c r="M25" s="11">
         <f>SUM(F25*1/5,G25*1/5,H25*1/5,I25*1/5,J25*1/5)</f>
-        <v>0</v>
+        <v>0.31162353241999996</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.2">
@@ -4106,17 +4406,32 @@
       <c r="C26" s="68"/>
       <c r="D26" s="64"/>
       <c r="E26" s="64"/>
+      <c r="F26" s="11">
+        <v>3.8350910000000001E-4</v>
+      </c>
+      <c r="G26" s="11">
+        <v>1.725791E-3</v>
+      </c>
+      <c r="H26" s="11">
+        <v>6.3279002900000006E-2</v>
+      </c>
+      <c r="I26" s="11">
+        <v>0.45670477209999999</v>
+      </c>
+      <c r="J26" s="11">
+        <v>0.4808019818</v>
+      </c>
       <c r="K26" s="11">
         <f>SUM(F26*1/3,G26*1/3,I26*1/3)</f>
-        <v>0</v>
+        <v>0.15293802406666665</v>
       </c>
       <c r="L26" s="11">
         <f>SUM(H26*1/2,J26*1/2)</f>
-        <v>0</v>
+        <v>0.27204049235</v>
       </c>
       <c r="M26" s="11">
         <f>SUM(F26*1/5,G26*1/5,H26*1/5,I26*1/5,J26*1/5)</f>
-        <v>0</v>
+        <v>0.20057901138000001</v>
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.2">
@@ -4135,17 +4450,32 @@
       <c r="E28" s="64" t="s">
         <v>33</v>
       </c>
+      <c r="F28" s="11">
+        <v>4.0364333699999998E-2</v>
+      </c>
+      <c r="G28" s="11">
+        <v>3.3557047E-3</v>
+      </c>
+      <c r="H28" s="11">
+        <v>0.32425695110000002</v>
+      </c>
+      <c r="I28" s="11">
+        <v>0.70605234920000004</v>
+      </c>
+      <c r="J28" s="11">
+        <v>0.43611723260000002</v>
+      </c>
       <c r="K28" s="11">
         <f>SUM(F28*1/3,G28*1/3,I28*1/3)</f>
-        <v>0</v>
+        <v>0.24992412920000001</v>
       </c>
       <c r="L28" s="11">
         <f>SUM(H28*1/2,J28*1/2)</f>
-        <v>0</v>
+        <v>0.38018709184999999</v>
       </c>
       <c r="M28" s="11">
         <f>SUM(F28*1/5,G28*1/5,H28*1/5,I28*1/5,J28*1/5)</f>
-        <v>0</v>
+        <v>0.30202931426000001</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.2">
@@ -4158,17 +4488,32 @@
       <c r="C29" s="68"/>
       <c r="D29" s="64"/>
       <c r="E29" s="64"/>
+      <c r="F29" s="11">
+        <v>2.8475551299999999E-2</v>
+      </c>
+      <c r="G29" s="11">
+        <v>1.0546500999999999E-3</v>
+      </c>
+      <c r="H29" s="11">
+        <v>0.5637583893</v>
+      </c>
+      <c r="I29" s="11">
+        <v>0.85501700719999996</v>
+      </c>
+      <c r="J29" s="11">
+        <v>0.43641871859999998</v>
+      </c>
       <c r="K29" s="11">
         <f>SUM(F29*1/3,G29*1/3,I29*1/3)</f>
-        <v>0</v>
+        <v>0.29484906953333329</v>
       </c>
       <c r="L29" s="11">
         <f>SUM(H29*1/2,J29*1/2)</f>
-        <v>0</v>
+        <v>0.50008855394999996</v>
       </c>
       <c r="M29" s="11">
         <f>SUM(F29*1/5,G29*1/5,H29*1/5,I29*1/5,J29*1/5)</f>
-        <v>0</v>
+        <v>0.37694486329999999</v>
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.2">
@@ -4181,17 +4526,32 @@
       <c r="C30" s="68"/>
       <c r="D30" s="64"/>
       <c r="E30" s="64"/>
+      <c r="F30" s="11">
+        <v>1.917546E-4</v>
+      </c>
+      <c r="G30" s="11">
+        <v>2.1093001000000002E-3</v>
+      </c>
+      <c r="H30" s="11">
+        <v>0.81073825499999996</v>
+      </c>
+      <c r="I30" s="11">
+        <v>0.50746971929999996</v>
+      </c>
+      <c r="J30" s="11">
+        <v>0.48343524840000002</v>
+      </c>
       <c r="K30" s="11">
         <f>SUM(F30*1/3,G30*1/3,I30*1/3)</f>
-        <v>0</v>
-      </c>
-      <c r="L30" s="11">
+        <v>0.16992359133333332</v>
+      </c>
+      <c r="L30" s="54">
         <f>SUM(H30*1/2,J30*1/2)</f>
-        <v>0</v>
+        <v>0.64708675169999996</v>
       </c>
       <c r="M30" s="11">
         <f>SUM(F30*1/5,G30*1/5,H30*1/5,I30*1/5,J30*1/5)</f>
-        <v>0</v>
+        <v>0.36078885547999995</v>
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.2">
@@ -4210,17 +4570,32 @@
       <c r="E32" s="64" t="s">
         <v>29</v>
       </c>
-      <c r="K32" s="11">
+      <c r="F32" s="11">
+        <v>5.1094890499999997E-2</v>
+      </c>
+      <c r="G32" s="11">
+        <v>9.9884747999999992E-3</v>
+      </c>
+      <c r="H32" s="11">
+        <v>0.4692662313</v>
+      </c>
+      <c r="I32" s="11">
+        <v>0.89344463880000002</v>
+      </c>
+      <c r="J32" s="11">
+        <v>0.39221498240000002</v>
+      </c>
+      <c r="K32" s="54">
         <f>SUM(F32*1/3,G32*1/3,I32*1/3)</f>
-        <v>0</v>
+        <v>0.31817600136666668</v>
       </c>
       <c r="L32" s="11">
         <f>SUM(H32*1/2,J32*1/2)</f>
-        <v>0</v>
+        <v>0.43074060685000004</v>
       </c>
       <c r="M32" s="11">
         <f>SUM(F32*1/5,G32*1/5,H32*1/5,I32*1/5,J32*1/5)</f>
-        <v>0</v>
+        <v>0.36320184355999996</v>
       </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.2">
@@ -4233,17 +4608,32 @@
       <c r="C33" s="68"/>
       <c r="D33" s="64"/>
       <c r="E33" s="64"/>
-      <c r="K33" s="54">
+      <c r="F33" s="11">
+        <v>2.4010757000000001E-3</v>
+      </c>
+      <c r="G33" s="11">
+        <v>2.3050326E-3</v>
+      </c>
+      <c r="H33" s="11">
+        <v>0.27890895119999998</v>
+      </c>
+      <c r="I33" s="11">
+        <v>0.51170637990000001</v>
+      </c>
+      <c r="J33" s="11">
+        <v>0.47991897360000002</v>
+      </c>
+      <c r="K33" s="11">
         <f>SUM(F33*1/3,G33*1/3,I33*1/3)</f>
-        <v>0</v>
+        <v>0.17213749606666667</v>
       </c>
       <c r="L33" s="11">
         <f>SUM(H33*1/2,J33*1/2)</f>
-        <v>0</v>
+        <v>0.37941396240000003</v>
       </c>
       <c r="M33" s="11">
         <f>SUM(F33*1/5,G33*1/5,H33*1/5,I33*1/5,J33*1/5)</f>
-        <v>0</v>
+        <v>0.2550480826</v>
       </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.2">
@@ -4256,17 +4646,32 @@
       <c r="C34" s="68"/>
       <c r="D34" s="64"/>
       <c r="E34" s="64"/>
+      <c r="F34" s="11">
+        <v>0</v>
+      </c>
+      <c r="G34" s="11">
+        <v>3.2654629000000001E-3</v>
+      </c>
+      <c r="H34" s="11">
+        <v>2.53553592E-2</v>
+      </c>
+      <c r="I34" s="11">
+        <v>0.47971639189999998</v>
+      </c>
+      <c r="J34" s="11">
+        <v>0.46461151090000002</v>
+      </c>
       <c r="K34" s="11">
         <f>SUM(F34*1/3,G34*1/3,I34*1/3)</f>
-        <v>0</v>
+        <v>0.16099395159999999</v>
       </c>
       <c r="L34" s="11">
         <f>SUM(H34*1/2,J34*1/2)</f>
-        <v>0</v>
+        <v>0.24498343505</v>
       </c>
       <c r="M34" s="11">
         <f>SUM(F34*1/5,G34*1/5,H34*1/5,I34*1/5,J34*1/5)</f>
-        <v>0</v>
+        <v>0.19458974497999998</v>
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.2">
@@ -4285,17 +4690,32 @@
       <c r="E36" s="64" t="s">
         <v>34</v>
       </c>
+      <c r="F36" s="11">
+        <v>4.4007670200000001E-2</v>
+      </c>
+      <c r="G36" s="11">
+        <v>3.2598275E-3</v>
+      </c>
+      <c r="H36" s="11">
+        <v>0.29223394060000002</v>
+      </c>
+      <c r="I36" s="11">
+        <v>0.81481471809999995</v>
+      </c>
+      <c r="J36" s="11">
+        <v>0.38846176700000001</v>
+      </c>
       <c r="K36" s="11">
         <f>SUM(F36*1/3,G36*1/3,I36*1/3)</f>
-        <v>0</v>
+        <v>0.2873607386</v>
       </c>
       <c r="L36" s="11">
         <f>SUM(H36*1/2,J36*1/2)</f>
-        <v>0</v>
+        <v>0.34034785379999999</v>
       </c>
       <c r="M36" s="11">
         <f>SUM(F36*1/5,G36*1/5,H36*1/5,I36*1/5,J36*1/5)</f>
-        <v>0</v>
+        <v>0.30855558467999999</v>
       </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.2">
@@ -4308,17 +4728,32 @@
       <c r="C37" s="68"/>
       <c r="D37" s="64"/>
       <c r="E37" s="64"/>
+      <c r="F37" s="11">
+        <v>5.9443912000000003E-3</v>
+      </c>
+      <c r="G37" s="11">
+        <v>5.9443912000000003E-3</v>
+      </c>
+      <c r="H37" s="11">
+        <v>0.27842761269999999</v>
+      </c>
+      <c r="I37" s="11">
+        <v>0.55905358250000003</v>
+      </c>
+      <c r="J37" s="11">
+        <v>0.47092189779999999</v>
+      </c>
       <c r="K37" s="11">
         <f>SUM(F37*1/3,G37*1/3,I37*1/3)</f>
-        <v>0</v>
+        <v>0.19031412163333333</v>
       </c>
       <c r="L37" s="11">
         <f>SUM(H37*1/2,J37*1/2)</f>
-        <v>0</v>
+        <v>0.37467475524999999</v>
       </c>
       <c r="M37" s="11">
         <f>SUM(F37*1/5,G37*1/5,H37*1/5,I37*1/5,J37*1/5)</f>
-        <v>0</v>
+        <v>0.26405837507999996</v>
       </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.2">
@@ -4331,17 +4766,32 @@
       <c r="C38" s="68"/>
       <c r="D38" s="64"/>
       <c r="E38" s="64"/>
+      <c r="F38" s="11">
+        <v>1.917546E-4</v>
+      </c>
+      <c r="G38" s="11">
+        <v>1.5340364E-3</v>
+      </c>
+      <c r="H38" s="11">
+        <v>0.17104506229999999</v>
+      </c>
+      <c r="I38" s="11">
+        <v>0.48401786200000002</v>
+      </c>
+      <c r="J38" s="11">
+        <v>0.4750072092</v>
+      </c>
       <c r="K38" s="11">
         <f>SUM(F38*1/3,G38*1/3,I38*1/3)</f>
-        <v>0</v>
+        <v>0.16191455099999999</v>
       </c>
       <c r="L38" s="11">
         <f>SUM(H38*1/2,J38*1/2)</f>
-        <v>0</v>
+        <v>0.32302613575</v>
       </c>
       <c r="M38" s="11">
         <f>SUM(F38*1/5,G38*1/5,H38*1/5,I38*1/5,J38*1/5)</f>
-        <v>0</v>
+        <v>0.22635918490000001</v>
       </c>
     </row>
     <row r="40" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -4378,17 +4828,32 @@
       <c r="E42" s="64" t="s">
         <v>27</v>
       </c>
+      <c r="F42" s="11">
+        <v>3.9087947900000003E-2</v>
+      </c>
+      <c r="G42" s="11">
+        <v>8.7181451999999993E-3</v>
+      </c>
+      <c r="H42" s="11">
+        <v>0.3901130485</v>
+      </c>
+      <c r="I42" s="11">
+        <v>0.73645856980000002</v>
+      </c>
+      <c r="J42" s="11">
+        <v>0.47121172500000003</v>
+      </c>
       <c r="K42" s="11">
         <f>SUM(F42*1/3,G42*1/3,I42*1/3)</f>
-        <v>0</v>
+        <v>0.26142155430000003</v>
       </c>
       <c r="L42" s="11">
         <f>SUM(H42*1/2,J42*1/2)</f>
-        <v>0</v>
+        <v>0.43066238675000001</v>
       </c>
       <c r="M42" s="11">
         <f>SUM(F42*1/5,G42*1/5,H42*1/5,I42*1/5,J42*1/5)</f>
-        <v>0</v>
+        <v>0.32911788728000002</v>
       </c>
       <c r="N42" s="66" t="s">
         <v>30</v>
@@ -4404,17 +4869,32 @@
       <c r="C43" s="68"/>
       <c r="D43" s="64"/>
       <c r="E43" s="64"/>
+      <c r="F43" s="11">
+        <v>1.59034298E-2</v>
+      </c>
+      <c r="G43" s="11">
+        <v>2.2992910000000002E-3</v>
+      </c>
+      <c r="H43" s="11">
+        <v>0.48342594370000003</v>
+      </c>
+      <c r="I43" s="11">
+        <v>0.68715179920000002</v>
+      </c>
+      <c r="J43" s="11">
+        <v>0.48531944220000001</v>
+      </c>
       <c r="K43" s="11">
         <f>SUM(F43*1/3,G43*1/3,I43*1/3)</f>
-        <v>0</v>
+        <v>0.23511817333333332</v>
       </c>
       <c r="L43" s="11">
         <f>SUM(H43*1/2,J43*1/2)</f>
-        <v>0</v>
+        <v>0.48437269295000002</v>
       </c>
       <c r="M43" s="11">
         <f>SUM(F43*1/5,G43*1/5,H43*1/5,I43*1/5,J43*1/5)</f>
-        <v>0</v>
+        <v>0.33481998118</v>
       </c>
       <c r="N43" s="66"/>
     </row>
@@ -4428,18 +4908,32 @@
       <c r="C44" s="68"/>
       <c r="D44" s="64"/>
       <c r="E44" s="64"/>
-      <c r="F44" s="62"/>
+      <c r="F44" s="62">
+        <v>0</v>
+      </c>
+      <c r="G44" s="11">
+        <v>1.0538418000000001E-3</v>
+      </c>
+      <c r="H44" s="11">
+        <v>0.19294884079999999</v>
+      </c>
+      <c r="I44" s="11">
+        <v>0.47724684769999998</v>
+      </c>
+      <c r="J44" s="11">
+        <v>0.47960696060000002</v>
+      </c>
       <c r="K44" s="11">
         <f>SUM(F44*1/3,G44*1/3,I44*1/3)</f>
-        <v>0</v>
+        <v>0.15943356316666665</v>
       </c>
       <c r="L44" s="11">
         <f>SUM(H44*1/2,J44*1/2)</f>
-        <v>0</v>
+        <v>0.33627790070000002</v>
       </c>
       <c r="M44" s="11">
         <f>SUM(F44*1/5,G44*1/5,H44*1/5,I44*1/5,J44*1/5)</f>
-        <v>0</v>
+        <v>0.23017129817999998</v>
       </c>
       <c r="N44" s="66"/>
     </row>
@@ -4459,17 +4953,32 @@
       <c r="E46" s="64" t="s">
         <v>28</v>
       </c>
+      <c r="F46" s="11">
+        <v>5.4608162000000003E-3</v>
+      </c>
+      <c r="G46" s="11">
+        <v>3.8321518000000001E-3</v>
+      </c>
+      <c r="H46" s="11">
+        <v>0.32515807629999999</v>
+      </c>
+      <c r="I46" s="11">
+        <v>0.63049252609999995</v>
+      </c>
+      <c r="J46" s="11">
+        <v>0.45521605110000002</v>
+      </c>
       <c r="K46" s="11">
         <f>SUM(F46*1/3,G46*1/3,I46*1/3)</f>
-        <v>0</v>
+        <v>0.21326183136666665</v>
       </c>
       <c r="L46" s="11">
         <f>SUM(H46*1/2,J46*1/2)</f>
-        <v>0</v>
+        <v>0.3901870637</v>
       </c>
       <c r="M46" s="11">
         <f>SUM(F46*1/5,G46*1/5,H46*1/5,I46*1/5,J46*1/5)</f>
-        <v>0</v>
+        <v>0.28403192430000002</v>
       </c>
       <c r="N46" s="66" t="s">
         <v>31</v>
@@ -4485,17 +4994,32 @@
       <c r="C47" s="68"/>
       <c r="D47" s="64"/>
       <c r="E47" s="64"/>
+      <c r="F47" s="11">
+        <v>2.90285495E-2</v>
+      </c>
+      <c r="G47" s="11">
+        <v>8.6223409999999995E-4</v>
+      </c>
+      <c r="H47" s="11">
+        <v>0.4443379958</v>
+      </c>
+      <c r="I47" s="11">
+        <v>0.81897723840000003</v>
+      </c>
+      <c r="J47" s="11">
+        <v>0.46126102250000001</v>
+      </c>
       <c r="K47" s="11">
         <f>SUM(F47*1/3,G47*1/3,I47*1/3)</f>
-        <v>0</v>
+        <v>0.28295600733333337</v>
       </c>
       <c r="L47" s="11">
         <f>SUM(H47*1/2,J47*1/2)</f>
-        <v>0</v>
+        <v>0.45279950915</v>
       </c>
       <c r="M47" s="11">
         <f>SUM(F47*1/5,G47*1/5,H47*1/5,I47*1/5,J47*1/5)</f>
-        <v>0</v>
+        <v>0.35089340806000002</v>
       </c>
       <c r="N47" s="66"/>
     </row>
@@ -4509,17 +5033,32 @@
       <c r="C48" s="68"/>
       <c r="D48" s="64"/>
       <c r="E48" s="64"/>
+      <c r="F48" s="11">
+        <v>1.9160760000000001E-4</v>
+      </c>
+      <c r="G48" s="11">
+        <v>1.3412531E-3</v>
+      </c>
+      <c r="H48" s="11">
+        <v>0.71239701089999996</v>
+      </c>
+      <c r="I48" s="11">
+        <v>0.50377163940000003</v>
+      </c>
+      <c r="J48" s="11">
+        <v>0.4912146825</v>
+      </c>
       <c r="K48" s="11">
         <f>SUM(F48*1/3,G48*1/3,I48*1/3)</f>
-        <v>0</v>
+        <v>0.16843483336666668</v>
       </c>
       <c r="L48" s="11">
         <f>SUM(H48*1/2,J48*1/2)</f>
-        <v>0</v>
+        <v>0.60180584670000004</v>
       </c>
       <c r="M48" s="11">
         <f>SUM(F48*1/5,G48*1/5,H48*1/5,I48*1/5,J48*1/5)</f>
-        <v>0</v>
+        <v>0.34178323869999999</v>
       </c>
       <c r="N48" s="66"/>
     </row>
@@ -4539,17 +5078,32 @@
       <c r="E50" s="64" t="s">
         <v>29</v>
       </c>
+      <c r="F50" s="11">
+        <v>2.7399884999999999E-2</v>
+      </c>
+      <c r="G50" s="11">
+        <v>2.0693619399999998E-2</v>
+      </c>
+      <c r="H50" s="11">
+        <v>0.62962253310000005</v>
+      </c>
+      <c r="I50" s="11">
+        <v>0.85414416559999995</v>
+      </c>
+      <c r="J50" s="11">
+        <v>0.45041272119999998</v>
+      </c>
       <c r="K50" s="11">
         <f>SUM(F50*1/3,G50*1/3,I50*1/3)</f>
-        <v>0</v>
+        <v>0.30074588999999996</v>
       </c>
       <c r="L50" s="11">
         <f>SUM(H50*1/2,J50*1/2)</f>
-        <v>0</v>
-      </c>
-      <c r="M50" s="11">
+        <v>0.54001762715000001</v>
+      </c>
+      <c r="M50" s="54">
         <f>SUM(F50*1/5,G50*1/5,H50*1/5,I50*1/5,J50*1/5)</f>
-        <v>0</v>
+        <v>0.39645458486000001</v>
       </c>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.2">
@@ -4562,17 +5116,32 @@
       <c r="C51" s="68"/>
       <c r="D51" s="64"/>
       <c r="E51" s="64"/>
+      <c r="F51" s="11">
+        <v>3.4489365999999999E-3</v>
+      </c>
+      <c r="G51" s="11">
+        <v>2.77831E-3</v>
+      </c>
+      <c r="H51" s="11">
+        <v>0.28319601459999999</v>
+      </c>
+      <c r="I51" s="11">
+        <v>0.55856684919999999</v>
+      </c>
+      <c r="J51" s="11">
+        <v>0.48412258870000002</v>
+      </c>
       <c r="K51" s="11">
         <f>SUM(F51*1/3,G51*1/3,I51*1/3)</f>
-        <v>0</v>
+        <v>0.1882646986</v>
       </c>
       <c r="L51" s="11">
         <f>SUM(H51*1/2,J51*1/2)</f>
-        <v>0</v>
+        <v>0.38365930165000001</v>
       </c>
       <c r="M51" s="11">
         <f>SUM(F51*1/5,G51*1/5,H51*1/5,I51*1/5,J51*1/5)</f>
-        <v>0</v>
+        <v>0.26642253981999997</v>
       </c>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.2">
@@ -4585,18 +5154,32 @@
       <c r="C52" s="68"/>
       <c r="D52" s="64"/>
       <c r="E52" s="64"/>
-      <c r="F52" s="62"/>
+      <c r="F52" s="62">
+        <v>4.7901900000000002E-4</v>
+      </c>
+      <c r="G52" s="11">
+        <v>9.5803800000000003E-4</v>
+      </c>
+      <c r="H52" s="11">
+        <v>0.1588426902</v>
+      </c>
+      <c r="I52" s="11">
+        <v>0.51150557910000005</v>
+      </c>
+      <c r="J52" s="11">
+        <v>0.47634846359999999</v>
+      </c>
       <c r="K52" s="11">
         <f>SUM(F52*1/3,G52*1/3,I52*1/3)</f>
-        <v>0</v>
+        <v>0.17098087870000001</v>
       </c>
       <c r="L52" s="11">
         <f>SUM(H52*1/2,J52*1/2)</f>
-        <v>0</v>
+        <v>0.31759557690000001</v>
       </c>
       <c r="M52" s="11">
         <f>SUM(F52*1/5,G52*1/5,H52*1/5,I52*1/5,J52*1/5)</f>
-        <v>0</v>
+        <v>0.22962675798000001</v>
       </c>
     </row>
     <row r="55" spans="1:14" s="14" customFormat="1" x14ac:dyDescent="0.2">
@@ -4609,35 +5192,35 @@
       <c r="E55" s="15"/>
       <c r="F55" s="16">
         <f t="shared" ref="F55:M55" si="0">MAX(F2:F52)</f>
-        <v>0</v>
+        <v>9.81988887E-2</v>
       </c>
       <c r="G55" s="16">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2.0693619399999998E-2</v>
       </c>
       <c r="H55" s="16">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.81073825499999996</v>
       </c>
       <c r="I55" s="16">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.89344463880000002</v>
       </c>
       <c r="J55" s="16">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.53984978090000002</v>
       </c>
       <c r="K55" s="16">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.31817600136666668</v>
       </c>
       <c r="L55" s="16">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.64708675169999996</v>
       </c>
       <c r="M55" s="16">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.39645458486000001</v>
       </c>
       <c r="N55" s="17"/>
     </row>
@@ -4649,43 +5232,43 @@
       <c r="C56" s="77"/>
       <c r="D56" s="77"/>
       <c r="E56" s="19"/>
-      <c r="F56" s="20" t="e">
+      <c r="F56" s="20">
         <f t="shared" ref="F56:M56" si="1">AVERAGE(F2:F52)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G56" s="20" t="e">
+        <v>2.8208676708333331E-2</v>
+      </c>
+      <c r="G56" s="20">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H56" s="20" t="e">
+        <v>4.3324944694444444E-3</v>
+      </c>
+      <c r="H56" s="20">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I56" s="20" t="e">
+        <v>0.32975944002499991</v>
+      </c>
+      <c r="I56" s="20">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="J56" s="20" t="e">
+        <v>0.63286333159999986</v>
+      </c>
+      <c r="J56" s="20">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+        <v>0.4615904423916668</v>
       </c>
       <c r="K56" s="20">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.22180150092592596</v>
       </c>
       <c r="L56" s="20">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.39567494120833341</v>
       </c>
       <c r="M56" s="20">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.29135087703888896</v>
       </c>
       <c r="N56" s="21"/>
     </row>
     <row r="58" spans="1:14" s="22" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A58" s="74" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B58" s="74"/>
       <c r="C58" s="74"/>
@@ -4693,7 +5276,7 @@
       <c r="E58" s="74"/>
       <c r="F58" s="29">
         <f>SUM(F55*(1/3),  G55*(1/3), I55*(1/3))</f>
-        <v>0</v>
+        <v>0.33744571563333331</v>
       </c>
       <c r="G58" s="23"/>
       <c r="H58" s="23"/>
@@ -4706,7 +5289,7 @@
     </row>
     <row r="59" spans="1:14" s="27" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A59" s="75" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B59" s="75"/>
       <c r="C59" s="75"/>
@@ -4714,7 +5297,7 @@
       <c r="E59" s="75"/>
       <c r="F59" s="28">
         <f>SUM(H55*(1/2),  J55*(1/2))</f>
-        <v>0</v>
+        <v>0.67529401794999999</v>
       </c>
       <c r="G59" s="25"/>
       <c r="H59" s="25"/>
@@ -4727,7 +5310,7 @@
     </row>
     <row r="60" spans="1:14" s="33" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A60" s="76" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B60" s="76"/>
       <c r="C60" s="76"/>
@@ -4735,7 +5318,7 @@
       <c r="E60" s="76"/>
       <c r="F60" s="30">
         <f>SUM(F55*1/5, G55*1/5, H55*1/5, I55*1/5,J55*1/5)</f>
-        <v>0</v>
+        <v>0.47258503656</v>
       </c>
       <c r="G60" s="31"/>
       <c r="H60" s="31"/>
@@ -4748,7 +5331,7 @@
     </row>
     <row r="62" spans="1:14" s="37" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A62" s="72" t="s">
-        <v>64</v>
+        <v>83</v>
       </c>
       <c r="B62" s="72"/>
       <c r="C62" s="72"/>
@@ -4766,7 +5349,7 @@
     </row>
     <row r="63" spans="1:14" s="37" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A63" s="72" t="s">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="B63" s="73"/>
       <c r="C63" s="73"/>
@@ -4784,7 +5367,7 @@
     </row>
     <row r="64" spans="1:14" s="37" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A64" s="72" t="s">
-        <v>66</v>
+        <v>85</v>
       </c>
       <c r="B64" s="73"/>
       <c r="C64" s="73"/>
@@ -4936,7 +5519,7 @@
     </row>
     <row r="3" spans="1:14" s="47" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A3" s="77" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B3" s="77"/>
       <c r="C3" s="77"/>
@@ -4972,22 +5555,37 @@
         <v>5</v>
       </c>
       <c r="C5" s="66" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D5" s="66" t="s">
-        <v>71</v>
+        <v>68</v>
+      </c>
+      <c r="E5" s="11">
+        <v>5.7529773300000003E-2</v>
+      </c>
+      <c r="F5" s="11">
+        <v>6.7230119E-3</v>
+      </c>
+      <c r="G5" s="11">
+        <v>0.33499807910000001</v>
+      </c>
+      <c r="H5" s="11">
+        <v>0.89029599260000003</v>
+      </c>
+      <c r="I5" s="11">
+        <v>0.39083109230000002</v>
       </c>
       <c r="J5" s="11">
         <f>SUM(E5*1/3,F5*1/3,H5*1/3)</f>
-        <v>0</v>
+        <v>0.31818292593333336</v>
       </c>
       <c r="K5" s="11">
         <f>SUM(G5*1/2,I5*1/2)</f>
-        <v>0</v>
+        <v>0.36291458570000001</v>
       </c>
       <c r="L5" s="11">
         <f>SUM(E5*1/5,F5*1/5,G5*1/5,H5*1/5,I5*1/5)</f>
-        <v>0</v>
+        <v>0.33607558984000002</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -4999,17 +5597,32 @@
       </c>
       <c r="C6" s="66"/>
       <c r="D6" s="66"/>
+      <c r="E6" s="11">
+        <v>6.9727237799999994E-2</v>
+      </c>
+      <c r="F6" s="11">
+        <v>8.6438724000000005E-3</v>
+      </c>
+      <c r="G6" s="11">
+        <v>0.34959661930000002</v>
+      </c>
+      <c r="H6" s="11">
+        <v>0.87258270429999996</v>
+      </c>
+      <c r="I6" s="11">
+        <v>0.37624693279999999</v>
+      </c>
       <c r="J6" s="11">
         <f>SUM(E6*1/3,F6*1/3,H6*1/3)</f>
-        <v>0</v>
+        <v>0.31698460483333329</v>
       </c>
       <c r="K6" s="11">
         <f>SUM(G6*1/2,I6*1/2)</f>
-        <v>0</v>
+        <v>0.36292177604999998</v>
       </c>
       <c r="L6" s="11">
         <f>SUM(E6*1/5,F6*1/5,G6*1/5,H6*1/5,I6*1/5)</f>
-        <v>0</v>
+        <v>0.33535947332000005</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -5021,17 +5634,32 @@
       </c>
       <c r="C7" s="66"/>
       <c r="D7" s="66"/>
+      <c r="E7" s="11">
+        <v>2.8812910000000001E-4</v>
+      </c>
+      <c r="F7" s="11">
+        <v>1.5366883999999999E-3</v>
+      </c>
+      <c r="G7" s="11">
+        <v>0.25201690360000001</v>
+      </c>
+      <c r="H7" s="11">
+        <v>0.47203997120000002</v>
+      </c>
+      <c r="I7" s="11">
+        <v>0.4837691543</v>
+      </c>
       <c r="J7" s="11">
         <f>SUM(E7*1/3,F7*1/3,H7*1/3)</f>
-        <v>0</v>
+        <v>0.15795492956666668</v>
       </c>
       <c r="K7" s="11">
         <f>SUM(G7*1/2,I7*1/2)</f>
-        <v>0</v>
+        <v>0.36789302894999998</v>
       </c>
       <c r="L7" s="11">
         <f>SUM(E7*1/5,F7*1/5,G7*1/5,H7*1/5,I7*1/5)</f>
-        <v>0</v>
+        <v>0.24193016932</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -5042,22 +5670,37 @@
         <v>5</v>
       </c>
       <c r="C9" s="66" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D9" s="66" t="s">
-        <v>73</v>
+        <v>70</v>
+      </c>
+      <c r="E9" s="11">
+        <v>5.1094890499999997E-2</v>
+      </c>
+      <c r="F9" s="11">
+        <v>9.9884747999999992E-3</v>
+      </c>
+      <c r="G9" s="11">
+        <v>0.4692662313</v>
+      </c>
+      <c r="H9" s="11">
+        <v>0.89344463880000002</v>
+      </c>
+      <c r="I9" s="11">
+        <v>0.39221498240000002</v>
       </c>
       <c r="J9" s="11">
         <f>SUM(E9*1/3,F9*1/3,H9*1/3)</f>
-        <v>0</v>
+        <v>0.31817600136666668</v>
       </c>
       <c r="K9" s="11">
         <f>SUM(G9*1/2,I9*1/2)</f>
-        <v>0</v>
+        <v>0.43074060685000004</v>
       </c>
       <c r="L9" s="11">
         <f>SUM(E9*1/5,F9*1/5,G9*1/5,H9*1/5,I9*1/5)</f>
-        <v>0</v>
+        <v>0.36320184355999996</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -5069,17 +5712,32 @@
       </c>
       <c r="C10" s="66"/>
       <c r="D10" s="66"/>
+      <c r="E10" s="11">
+        <v>2.4010757000000001E-3</v>
+      </c>
+      <c r="F10" s="11">
+        <v>2.3050326E-3</v>
+      </c>
+      <c r="G10" s="11">
+        <v>0.27890895119999998</v>
+      </c>
+      <c r="H10" s="11">
+        <v>0.51170637990000001</v>
+      </c>
+      <c r="I10" s="11">
+        <v>0.47991897360000002</v>
+      </c>
       <c r="J10" s="11">
         <f>SUM(E10*1/3,F10*1/3,H10*1/3)</f>
-        <v>0</v>
+        <v>0.17213749606666667</v>
       </c>
       <c r="K10" s="11">
         <f>SUM(G10*1/2,I10*1/2)</f>
-        <v>0</v>
+        <v>0.37941396240000003</v>
       </c>
       <c r="L10" s="11">
         <f>SUM(E10*1/5,F10*1/5,G10*1/5,H10*1/5,I10*1/5)</f>
-        <v>0</v>
+        <v>0.2550480826</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -5091,17 +5749,32 @@
       </c>
       <c r="C11" s="66"/>
       <c r="D11" s="66"/>
+      <c r="E11" s="11">
+        <v>0</v>
+      </c>
+      <c r="F11" s="11">
+        <v>3.2654629000000001E-3</v>
+      </c>
+      <c r="G11" s="11">
+        <v>2.53553592E-2</v>
+      </c>
+      <c r="H11" s="11">
+        <v>0.47971639189999998</v>
+      </c>
+      <c r="I11" s="11">
+        <v>0.46461151090000002</v>
+      </c>
       <c r="J11" s="11">
         <f>SUM(E11*1/3,F11*1/3,H11*1/3)</f>
-        <v>0</v>
+        <v>0.16099395159999999</v>
       </c>
       <c r="K11" s="11">
         <f>SUM(G11*1/2,I11*1/2)</f>
-        <v>0</v>
+        <v>0.24498343505</v>
       </c>
       <c r="L11" s="11">
         <f>SUM(E11*1/5,F11*1/5,G11*1/5,H11*1/5,I11*1/5)</f>
-        <v>0</v>
+        <v>0.19458974497999998</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.2">
@@ -5112,10 +5785,10 @@
         <v>5</v>
       </c>
       <c r="C13" s="66" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D13" s="66" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="J13" s="11">
         <f>SUM(E13*1/3,F13*1/3,H13*1/3)</f>
@@ -5182,10 +5855,10 @@
         <v>5</v>
       </c>
       <c r="C17" s="66" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D17" s="66" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="J17" s="11">
         <f>SUM(E17*1/3,F17*1/3,H17*1/3)</f>
@@ -5255,10 +5928,10 @@
         <v>5</v>
       </c>
       <c r="C21" s="66" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="D21" s="66" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="J21" s="11">
         <f>SUM(E21*1/3,F21*1/3,H21*1/3)</f>
@@ -5325,10 +5998,10 @@
         <v>5</v>
       </c>
       <c r="C25" s="66" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D25" s="66" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="J25" s="11">
         <f>SUM(E25*1/3,F25*1/3,H25*1/3)</f>
@@ -5395,10 +6068,10 @@
         <v>5</v>
       </c>
       <c r="C29" s="66" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="D29" s="66" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="J29" s="11">
         <f>SUM(E29*1/3,F29*1/3,H29*1/3)</f>
@@ -5466,35 +6139,35 @@
       <c r="D34" s="79"/>
       <c r="E34" s="16">
         <f t="shared" ref="E34:L34" si="0">MAX(E4:E32)</f>
-        <v>0</v>
+        <v>6.9727237799999994E-2</v>
       </c>
       <c r="F34" s="16">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>9.9884747999999992E-3</v>
       </c>
       <c r="G34" s="16">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.4692662313</v>
       </c>
       <c r="H34" s="16">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.89344463880000002</v>
       </c>
       <c r="I34" s="16">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.4837691543</v>
       </c>
       <c r="J34" s="16">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.31818292593333336</v>
       </c>
       <c r="K34" s="16">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.43074060685000004</v>
       </c>
       <c r="L34" s="16">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.36320184355999996</v>
       </c>
       <c r="M34" s="16"/>
       <c r="N34" s="17"/>
@@ -5506,37 +6179,37 @@
       <c r="B35" s="74"/>
       <c r="C35" s="74"/>
       <c r="D35" s="74"/>
-      <c r="E35" s="29" t="e">
+      <c r="E35" s="29">
         <f t="shared" ref="E35:L35" si="1">AVERAGE(E5:E32)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F35" s="29" t="e">
+        <v>3.0173517733333332E-2</v>
+      </c>
+      <c r="F35" s="29">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G35" s="29" t="e">
+        <v>5.4104238333333339E-3</v>
+      </c>
+      <c r="G35" s="29">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H35" s="29" t="e">
+        <v>0.28502369061666666</v>
+      </c>
+      <c r="H35" s="29">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I35" s="29" t="e">
+        <v>0.68663101311666674</v>
+      </c>
+      <c r="I35" s="29">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+        <v>0.43126544105000003</v>
       </c>
       <c r="J35" s="29">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>6.878237663650795E-2</v>
       </c>
       <c r="K35" s="29">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.10232701880952383</v>
       </c>
       <c r="L35" s="29">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>8.2200233505714301E-2</v>
       </c>
       <c r="M35" s="29"/>
       <c r="N35" s="58"/>

--- a/benchmarking/results/results.xlsx
+++ b/benchmarking/results/results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/deborahdore/Documents/political-debates-graph-analysis/benchmarking/results/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49C871E4-A1B9-7148-9667-3B4F4FE704E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{183785B8-05BE-7242-87BF-44E75575E0F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="30240" windowHeight="18900" xr2:uid="{E2EDC037-19C4-FE46-A599-BB595128A04F}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="30240" windowHeight="18900" activeTab="3" xr2:uid="{E2EDC037-19C4-FE46-A599-BB595128A04F}"/>
   </bookViews>
   <sheets>
     <sheet name="Results BASIC" sheetId="1" r:id="rId1"/>

--- a/benchmarking/results/results.xlsx
+++ b/benchmarking/results/results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/deborahdore/Documents/political-debates-graph-analysis/benchmarking/results/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{183785B8-05BE-7242-87BF-44E75575E0F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A119E4E-18DC-F744-B11D-73AA464DC9A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="30240" windowHeight="18900" activeTab="3" xr2:uid="{E2EDC037-19C4-FE46-A599-BB595128A04F}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="51200" windowHeight="28800" activeTab="3" xr2:uid="{E2EDC037-19C4-FE46-A599-BB595128A04F}"/>
   </bookViews>
   <sheets>
     <sheet name="Results BASIC" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="470" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="588" uniqueCount="102">
   <si>
     <t>MODEL'S TYPE</t>
   </si>
@@ -311,6 +311,68 @@
   </si>
   <si>
     <t>BEST RESULT OF 3) text+claim_speaker_year</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">BEST EXPERIMENT WITH RELATION PREDICTION AND RELATION CLASSIFICATION with </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>text_claim_year</t>
+    </r>
+  </si>
+  <si>
+    <t>special/text_claim_year</t>
+  </si>
+  <si>
+    <t>pretrained/text_claim_year</t>
+  </si>
+  <si>
+    <t>trial2/downsampling</t>
+  </si>
+  <si>
+    <t>trial2/basic_sampler</t>
+  </si>
+  <si>
+    <t>trial2/bernoulli</t>
+  </si>
+  <si>
+    <t>trial2/downsampling_basic</t>
+  </si>
+  <si>
+    <t>trial2/downsampling_bernoulli</t>
+  </si>
+  <si>
+    <t>BEST EXPERIMENT WITH ALL with  text+claim_speaker_year</t>
+  </si>
+  <si>
+    <t>special/ text+claim_speaker_year</t>
+  </si>
+  <si>
+    <t>pretrained/ text+claim_speaker_year</t>
+  </si>
+  <si>
+    <t>trial3/downsampling</t>
+  </si>
+  <si>
+    <t>trial3/basic_sampler</t>
+  </si>
+  <si>
+    <t>trial3/bernoulli</t>
+  </si>
+  <si>
+    <t>trial3/downsampling_basic</t>
+  </si>
+  <si>
+    <t>trial3/downsampling_bernoulli</t>
   </si>
 </sst>
 </file>
@@ -471,7 +533,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="80">
+  <cellXfs count="89">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -659,31 +721,40 @@
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -701,14 +772,32 @@
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -718,8 +807,8 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFFFE699"/>
       <color rgb="FFE3EFDB"/>
-      <color rgb="FFFFE699"/>
       <color rgb="FFBED7EE"/>
     </mruColors>
   </colors>
@@ -1091,7 +1180,7 @@
       <c r="B2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="70" t="s">
+      <c r="C2" s="68" t="s">
         <v>41</v>
       </c>
       <c r="D2" s="67" t="s">
@@ -1115,7 +1204,7 @@
       <c r="J2" s="11">
         <v>0.52440008120000003</v>
       </c>
-      <c r="K2" s="65" t="s">
+      <c r="K2" s="70" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1126,9 +1215,9 @@
       <c r="B3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="68"/>
-      <c r="D3" s="64"/>
-      <c r="E3" s="64"/>
+      <c r="C3" s="64"/>
+      <c r="D3" s="65"/>
+      <c r="E3" s="65"/>
       <c r="F3" s="11">
         <v>3.9117929099999997E-2</v>
       </c>
@@ -1144,7 +1233,7 @@
       <c r="J3" s="11">
         <v>0.4957882649</v>
       </c>
-      <c r="K3" s="66"/>
+      <c r="K3" s="71"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
@@ -1153,9 +1242,9 @@
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="68"/>
-      <c r="D4" s="64"/>
-      <c r="E4" s="64"/>
+      <c r="C4" s="64"/>
+      <c r="D4" s="65"/>
+      <c r="E4" s="65"/>
       <c r="F4" s="11">
         <v>2.1093001000000002E-3</v>
       </c>
@@ -1171,7 +1260,7 @@
       <c r="J4" s="11">
         <v>0.4776301698</v>
       </c>
-      <c r="K4" s="66"/>
+      <c r="K4" s="71"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
@@ -1180,13 +1269,13 @@
       <c r="B6" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="68" t="s">
+      <c r="C6" s="64" t="s">
         <v>42</v>
       </c>
-      <c r="D6" s="64" t="s">
+      <c r="D6" s="65" t="s">
         <v>10</v>
       </c>
-      <c r="E6" s="64" t="s">
+      <c r="E6" s="65" t="s">
         <v>13</v>
       </c>
       <c r="F6" s="11">
@@ -1204,7 +1293,7 @@
       <c r="J6" s="11">
         <v>0.51801477490000003</v>
       </c>
-      <c r="K6" s="66" t="s">
+      <c r="K6" s="71" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1215,9 +1304,9 @@
       <c r="B7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="68"/>
-      <c r="D7" s="64"/>
-      <c r="E7" s="64"/>
+      <c r="C7" s="64"/>
+      <c r="D7" s="65"/>
+      <c r="E7" s="65"/>
       <c r="F7" s="11">
         <v>3.2094270899999999E-2</v>
       </c>
@@ -1233,7 +1322,7 @@
       <c r="J7" s="11">
         <v>0.50083099880000004</v>
       </c>
-      <c r="K7" s="66"/>
+      <c r="K7" s="71"/>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
@@ -1242,9 +1331,9 @@
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="68"/>
-      <c r="D8" s="64"/>
-      <c r="E8" s="64"/>
+      <c r="C8" s="64"/>
+      <c r="D8" s="65"/>
+      <c r="E8" s="65"/>
       <c r="F8" s="11">
         <v>2.8741139999999998E-4</v>
       </c>
@@ -1260,15 +1349,15 @@
       <c r="J8" s="11">
         <v>0.4887305689</v>
       </c>
-      <c r="K8" s="66"/>
+      <c r="K8" s="71"/>
     </row>
     <row r="10" spans="1:12" s="59" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="69" t="s">
+      <c r="A10" s="66" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="69"/>
-      <c r="C10" s="69"/>
-      <c r="D10" s="69"/>
+      <c r="B10" s="66"/>
+      <c r="C10" s="66"/>
+      <c r="D10" s="66"/>
       <c r="E10" s="60"/>
       <c r="F10" s="61"/>
       <c r="G10" s="61"/>
@@ -1284,13 +1373,13 @@
       <c r="B12" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C12" s="68" t="s">
+      <c r="C12" s="64" t="s">
         <v>43</v>
       </c>
-      <c r="D12" s="64" t="s">
+      <c r="D12" s="65" t="s">
         <v>11</v>
       </c>
-      <c r="E12" s="64" t="s">
+      <c r="E12" s="65" t="s">
         <v>17</v>
       </c>
       <c r="F12" s="11">
@@ -1308,7 +1397,7 @@
       <c r="J12" s="11">
         <v>0.65087326729999995</v>
       </c>
-      <c r="K12" s="66" t="s">
+      <c r="K12" s="71" t="s">
         <v>18</v>
       </c>
     </row>
@@ -1319,9 +1408,9 @@
       <c r="B13" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C13" s="68"/>
-      <c r="D13" s="64"/>
-      <c r="E13" s="64"/>
+      <c r="C13" s="64"/>
+      <c r="D13" s="65"/>
+      <c r="E13" s="65"/>
       <c r="F13" s="11">
         <v>1.0937623800000001E-2</v>
       </c>
@@ -1337,7 +1426,7 @@
       <c r="J13" s="11">
         <v>0.48031703009999999</v>
       </c>
-      <c r="K13" s="66"/>
+      <c r="K13" s="71"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
@@ -1346,9 +1435,9 @@
       <c r="B14" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C14" s="68"/>
-      <c r="D14" s="64"/>
-      <c r="E14" s="64"/>
+      <c r="C14" s="64"/>
+      <c r="D14" s="65"/>
+      <c r="E14" s="65"/>
       <c r="F14" s="11">
         <v>2.377744E-4</v>
       </c>
@@ -1364,7 +1453,7 @@
       <c r="J14" s="11">
         <v>0.49770047779999999</v>
       </c>
-      <c r="K14" s="66"/>
+      <c r="K14" s="71"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
@@ -1373,13 +1462,13 @@
       <c r="B16" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C16" s="68" t="s">
+      <c r="C16" s="64" t="s">
         <v>44</v>
       </c>
-      <c r="D16" s="64" t="s">
+      <c r="D16" s="65" t="s">
         <v>19</v>
       </c>
-      <c r="E16" s="64" t="s">
+      <c r="E16" s="65" t="s">
         <v>27</v>
       </c>
       <c r="F16" s="11">
@@ -1397,7 +1486,7 @@
       <c r="J16" s="11">
         <v>0.44106115289999998</v>
       </c>
-      <c r="K16" s="66" t="s">
+      <c r="K16" s="71" t="s">
         <v>36</v>
       </c>
     </row>
@@ -1408,9 +1497,9 @@
       <c r="B17" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C17" s="68"/>
-      <c r="D17" s="64"/>
-      <c r="E17" s="64"/>
+      <c r="C17" s="64"/>
+      <c r="D17" s="65"/>
+      <c r="E17" s="65"/>
       <c r="F17" s="11">
         <v>6.6187922000000001E-3</v>
       </c>
@@ -1426,7 +1515,7 @@
       <c r="J17" s="11">
         <v>0.48203358359999998</v>
       </c>
-      <c r="K17" s="66"/>
+      <c r="K17" s="71"/>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
@@ -1435,9 +1524,9 @@
       <c r="B18" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C18" s="68"/>
-      <c r="D18" s="64"/>
-      <c r="E18" s="64"/>
+      <c r="C18" s="64"/>
+      <c r="D18" s="65"/>
+      <c r="E18" s="65"/>
       <c r="F18" s="11">
         <v>1.9467035999999999E-3</v>
       </c>
@@ -1453,7 +1542,7 @@
       <c r="J18" s="11">
         <v>0.31319458500000003</v>
       </c>
-      <c r="K18" s="66"/>
+      <c r="K18" s="71"/>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
@@ -1462,13 +1551,13 @@
       <c r="B20" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C20" s="68" t="s">
+      <c r="C20" s="64" t="s">
         <v>45</v>
       </c>
-      <c r="D20" s="64" t="s">
+      <c r="D20" s="65" t="s">
         <v>20</v>
       </c>
-      <c r="E20" s="64" t="s">
+      <c r="E20" s="65" t="s">
         <v>28</v>
       </c>
       <c r="F20" s="11">
@@ -1486,7 +1575,7 @@
       <c r="J20" s="11">
         <v>0.42558258160000001</v>
       </c>
-      <c r="K20" s="66" t="s">
+      <c r="K20" s="71" t="s">
         <v>35</v>
       </c>
     </row>
@@ -1497,9 +1586,9 @@
       <c r="B21" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C21" s="68"/>
-      <c r="D21" s="64"/>
-      <c r="E21" s="64"/>
+      <c r="C21" s="64"/>
+      <c r="D21" s="65"/>
+      <c r="E21" s="65"/>
       <c r="F21" s="11">
         <v>0.36964094320000002</v>
       </c>
@@ -1515,7 +1604,7 @@
       <c r="J21" s="11">
         <v>0.71370811339999995</v>
       </c>
-      <c r="K21" s="66"/>
+      <c r="K21" s="71"/>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
@@ -1524,9 +1613,9 @@
       <c r="B22" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C22" s="68"/>
-      <c r="D22" s="64"/>
-      <c r="E22" s="64"/>
+      <c r="C22" s="64"/>
+      <c r="D22" s="65"/>
+      <c r="E22" s="65"/>
       <c r="F22" s="11">
         <v>1.786352E-4</v>
       </c>
@@ -1542,7 +1631,7 @@
       <c r="J22" s="11">
         <v>0.35677707139999998</v>
       </c>
-      <c r="K22" s="66"/>
+      <c r="K22" s="71"/>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
@@ -1551,13 +1640,13 @@
       <c r="B24" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C24" s="68" t="s">
+      <c r="C24" s="64" t="s">
         <v>46</v>
       </c>
-      <c r="D24" s="64" t="s">
+      <c r="D24" s="65" t="s">
         <v>21</v>
       </c>
-      <c r="E24" s="64" t="s">
+      <c r="E24" s="65" t="s">
         <v>32</v>
       </c>
       <c r="F24" s="11">
@@ -1583,9 +1672,9 @@
       <c r="B25" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C25" s="68"/>
-      <c r="D25" s="64"/>
-      <c r="E25" s="64"/>
+      <c r="C25" s="64"/>
+      <c r="D25" s="65"/>
+      <c r="E25" s="65"/>
       <c r="F25" s="11">
         <v>2.2257384000000002E-2</v>
       </c>
@@ -1609,9 +1698,9 @@
       <c r="B26" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C26" s="68"/>
-      <c r="D26" s="64"/>
-      <c r="E26" s="64"/>
+      <c r="C26" s="64"/>
+      <c r="D26" s="65"/>
+      <c r="E26" s="65"/>
       <c r="F26" s="11">
         <v>3.9556960000000001E-4</v>
       </c>
@@ -1635,13 +1724,13 @@
       <c r="B28" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C28" s="68" t="s">
+      <c r="C28" s="64" t="s">
         <v>47</v>
       </c>
-      <c r="D28" s="64" t="s">
+      <c r="D28" s="65" t="s">
         <v>22</v>
       </c>
-      <c r="E28" s="64" t="s">
+      <c r="E28" s="65" t="s">
         <v>33</v>
       </c>
       <c r="F28" s="11">
@@ -1667,9 +1756,9 @@
       <c r="B29" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C29" s="68"/>
-      <c r="D29" s="64"/>
-      <c r="E29" s="64"/>
+      <c r="C29" s="64"/>
+      <c r="D29" s="65"/>
+      <c r="E29" s="65"/>
       <c r="F29" s="11">
         <v>1.8442843300000001E-2</v>
       </c>
@@ -1693,9 +1782,9 @@
       <c r="B30" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C30" s="68"/>
-      <c r="D30" s="64"/>
-      <c r="E30" s="64"/>
+      <c r="C30" s="64"/>
+      <c r="D30" s="65"/>
+      <c r="E30" s="65"/>
       <c r="F30" s="11">
         <v>6.9899990000000004E-4</v>
       </c>
@@ -1719,13 +1808,13 @@
       <c r="B32" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C32" s="68" t="s">
+      <c r="C32" s="64" t="s">
         <v>48</v>
       </c>
-      <c r="D32" s="64" t="s">
+      <c r="D32" s="65" t="s">
         <v>23</v>
       </c>
-      <c r="E32" s="64" t="s">
+      <c r="E32" s="65" t="s">
         <v>29</v>
       </c>
       <c r="F32" s="11">
@@ -1751,9 +1840,9 @@
       <c r="B33" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C33" s="68"/>
-      <c r="D33" s="64"/>
-      <c r="E33" s="64"/>
+      <c r="C33" s="64"/>
+      <c r="D33" s="65"/>
+      <c r="E33" s="65"/>
       <c r="F33" s="11">
         <v>4.8571429999999999E-4</v>
       </c>
@@ -1777,9 +1866,9 @@
       <c r="B34" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C34" s="68"/>
-      <c r="D34" s="64"/>
-      <c r="E34" s="64"/>
+      <c r="C34" s="64"/>
+      <c r="D34" s="65"/>
+      <c r="E34" s="65"/>
       <c r="F34" s="11">
         <v>8.5714299999999993E-5</v>
       </c>
@@ -1803,13 +1892,13 @@
       <c r="B36" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C36" s="68" t="s">
+      <c r="C36" s="64" t="s">
         <v>49</v>
       </c>
-      <c r="D36" s="64" t="s">
+      <c r="D36" s="65" t="s">
         <v>24</v>
       </c>
-      <c r="E36" s="64" t="s">
+      <c r="E36" s="65" t="s">
         <v>34</v>
       </c>
       <c r="F36" s="11">
@@ -1835,9 +1924,9 @@
       <c r="B37" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C37" s="68"/>
-      <c r="D37" s="64"/>
-      <c r="E37" s="64"/>
+      <c r="C37" s="64"/>
+      <c r="D37" s="65"/>
+      <c r="E37" s="65"/>
       <c r="F37" s="11">
         <v>0.12567659680000001</v>
       </c>
@@ -1861,9 +1950,9 @@
       <c r="B38" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C38" s="68"/>
-      <c r="D38" s="64"/>
-      <c r="E38" s="64"/>
+      <c r="C38" s="64"/>
+      <c r="D38" s="65"/>
+      <c r="E38" s="65"/>
       <c r="F38" s="11">
         <v>5.4127739999999998E-4</v>
       </c>
@@ -1881,12 +1970,12 @@
       </c>
     </row>
     <row r="40" spans="1:11" s="59" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="69" t="s">
+      <c r="A40" s="66" t="s">
         <v>38</v>
       </c>
-      <c r="B40" s="69"/>
-      <c r="C40" s="69"/>
-      <c r="D40" s="69"/>
+      <c r="B40" s="66"/>
+      <c r="C40" s="66"/>
+      <c r="D40" s="66"/>
       <c r="E40" s="60"/>
       <c r="F40" s="61"/>
       <c r="G40" s="61"/>
@@ -1902,13 +1991,13 @@
       <c r="B42" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C42" s="68" t="s">
+      <c r="C42" s="64" t="s">
         <v>50</v>
       </c>
-      <c r="D42" s="64" t="s">
+      <c r="D42" s="65" t="s">
         <v>25</v>
       </c>
-      <c r="E42" s="64" t="s">
+      <c r="E42" s="65" t="s">
         <v>27</v>
       </c>
       <c r="F42" s="11">
@@ -1926,7 +2015,7 @@
       <c r="J42" s="11">
         <v>0.47978398890000001</v>
       </c>
-      <c r="K42" s="66" t="s">
+      <c r="K42" s="71" t="s">
         <v>30</v>
       </c>
     </row>
@@ -1937,9 +2026,9 @@
       <c r="B43" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C43" s="68"/>
-      <c r="D43" s="64"/>
-      <c r="E43" s="64"/>
+      <c r="C43" s="64"/>
+      <c r="D43" s="65"/>
+      <c r="E43" s="65"/>
       <c r="F43" s="11">
         <v>0.15768715</v>
       </c>
@@ -1955,7 +2044,7 @@
       <c r="J43" s="11">
         <v>0.64265883619999997</v>
       </c>
-      <c r="K43" s="66"/>
+      <c r="K43" s="71"/>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
@@ -1964,9 +2053,9 @@
       <c r="B44" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C44" s="68"/>
-      <c r="D44" s="64"/>
-      <c r="E44" s="64"/>
+      <c r="C44" s="64"/>
+      <c r="D44" s="65"/>
+      <c r="E44" s="65"/>
       <c r="F44" s="11">
         <v>1.5776599999999999E-4</v>
       </c>
@@ -1982,7 +2071,7 @@
       <c r="J44" s="11">
         <v>0.33957444949999999</v>
       </c>
-      <c r="K44" s="66"/>
+      <c r="K44" s="71"/>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
@@ -1991,13 +2080,13 @@
       <c r="B46" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C46" s="68" t="s">
+      <c r="C46" s="64" t="s">
         <v>51</v>
       </c>
-      <c r="D46" s="64" t="s">
+      <c r="D46" s="65" t="s">
         <v>26</v>
       </c>
-      <c r="E46" s="64" t="s">
+      <c r="E46" s="65" t="s">
         <v>28</v>
       </c>
       <c r="F46" s="11">
@@ -2015,7 +2104,7 @@
       <c r="J46" s="11">
         <v>0.43650638670000003</v>
       </c>
-      <c r="K46" s="66" t="s">
+      <c r="K46" s="71" t="s">
         <v>31</v>
       </c>
     </row>
@@ -2026,9 +2115,9 @@
       <c r="B47" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C47" s="68"/>
-      <c r="D47" s="64"/>
-      <c r="E47" s="64"/>
+      <c r="C47" s="64"/>
+      <c r="D47" s="65"/>
+      <c r="E47" s="65"/>
       <c r="F47" s="11">
         <v>0.28846457310000001</v>
       </c>
@@ -2044,7 +2133,7 @@
       <c r="J47" s="11">
         <v>0.62979789600000002</v>
       </c>
-      <c r="K47" s="66"/>
+      <c r="K47" s="71"/>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
@@ -2053,9 +2142,9 @@
       <c r="B48" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C48" s="68"/>
-      <c r="D48" s="64"/>
-      <c r="E48" s="64"/>
+      <c r="C48" s="64"/>
+      <c r="D48" s="65"/>
+      <c r="E48" s="65"/>
       <c r="F48" s="11">
         <v>2.7615590000000002E-4</v>
       </c>
@@ -2071,7 +2160,7 @@
       <c r="J48" s="11">
         <v>0.39453545410000002</v>
       </c>
-      <c r="K48" s="66"/>
+      <c r="K48" s="71"/>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
@@ -2080,13 +2169,13 @@
       <c r="B50" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C50" s="68" t="s">
+      <c r="C50" s="64" t="s">
         <v>52</v>
       </c>
-      <c r="D50" s="64" t="s">
+      <c r="D50" s="65" t="s">
         <v>39</v>
       </c>
-      <c r="E50" s="64" t="s">
+      <c r="E50" s="65" t="s">
         <v>29</v>
       </c>
       <c r="F50" s="11">
@@ -2112,9 +2201,9 @@
       <c r="B51" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C51" s="68"/>
-      <c r="D51" s="64"/>
-      <c r="E51" s="64"/>
+      <c r="C51" s="64"/>
+      <c r="D51" s="65"/>
+      <c r="E51" s="65"/>
       <c r="F51" s="11">
         <v>3.5391416699999997E-2</v>
       </c>
@@ -2138,9 +2227,9 @@
       <c r="B52" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C52" s="68"/>
-      <c r="D52" s="64"/>
-      <c r="E52" s="64"/>
+      <c r="C52" s="64"/>
+      <c r="D52" s="65"/>
+      <c r="E52" s="65"/>
       <c r="F52" s="11">
         <v>9.9344299999999997E-5</v>
       </c>
@@ -2158,12 +2247,12 @@
       </c>
     </row>
     <row r="55" spans="1:11" s="42" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="71" t="s">
+      <c r="A55" s="63" t="s">
         <v>59</v>
       </c>
-      <c r="B55" s="71"/>
-      <c r="C55" s="71"/>
-      <c r="D55" s="71"/>
+      <c r="B55" s="63"/>
+      <c r="C55" s="63"/>
+      <c r="D55" s="63"/>
       <c r="E55" s="39"/>
       <c r="F55" s="40">
         <f>MAX(F2:F52)</f>
@@ -2188,12 +2277,12 @@
       <c r="K55" s="41"/>
     </row>
     <row r="56" spans="1:11" s="46" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="63" t="s">
+      <c r="A56" s="69" t="s">
         <v>60</v>
       </c>
-      <c r="B56" s="63"/>
-      <c r="C56" s="63"/>
-      <c r="D56" s="63"/>
+      <c r="B56" s="69"/>
+      <c r="C56" s="69"/>
+      <c r="D56" s="69"/>
       <c r="E56" s="43"/>
       <c r="F56" s="44">
         <f>AVERAGE(F2:F52)</f>
@@ -2219,37 +2308,6 @@
     </row>
   </sheetData>
   <mergeCells count="47">
-    <mergeCell ref="A55:D55"/>
-    <mergeCell ref="C6:C8"/>
-    <mergeCell ref="C12:C14"/>
-    <mergeCell ref="C16:C18"/>
-    <mergeCell ref="C20:C22"/>
-    <mergeCell ref="C24:C26"/>
-    <mergeCell ref="C50:C52"/>
-    <mergeCell ref="D24:D26"/>
-    <mergeCell ref="D28:D30"/>
-    <mergeCell ref="D32:D34"/>
-    <mergeCell ref="D36:D38"/>
-    <mergeCell ref="D42:D44"/>
-    <mergeCell ref="D46:D48"/>
-    <mergeCell ref="D50:D52"/>
-    <mergeCell ref="A40:D40"/>
-    <mergeCell ref="D2:D4"/>
-    <mergeCell ref="D6:D8"/>
-    <mergeCell ref="D12:D14"/>
-    <mergeCell ref="D16:D18"/>
-    <mergeCell ref="D20:D22"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="C2:C4"/>
-    <mergeCell ref="E12:E14"/>
-    <mergeCell ref="E16:E18"/>
-    <mergeCell ref="E20:E22"/>
-    <mergeCell ref="C42:C44"/>
-    <mergeCell ref="C46:C48"/>
-    <mergeCell ref="C28:C30"/>
-    <mergeCell ref="C32:C34"/>
-    <mergeCell ref="C36:C38"/>
-    <mergeCell ref="E46:E48"/>
     <mergeCell ref="A56:D56"/>
     <mergeCell ref="E50:E52"/>
     <mergeCell ref="K2:K4"/>
@@ -2266,6 +2324,37 @@
     <mergeCell ref="E42:E44"/>
     <mergeCell ref="E2:E4"/>
     <mergeCell ref="E6:E8"/>
+    <mergeCell ref="E12:E14"/>
+    <mergeCell ref="E16:E18"/>
+    <mergeCell ref="E20:E22"/>
+    <mergeCell ref="C42:C44"/>
+    <mergeCell ref="C46:C48"/>
+    <mergeCell ref="C28:C30"/>
+    <mergeCell ref="C32:C34"/>
+    <mergeCell ref="C36:C38"/>
+    <mergeCell ref="E46:E48"/>
+    <mergeCell ref="D2:D4"/>
+    <mergeCell ref="D6:D8"/>
+    <mergeCell ref="D12:D14"/>
+    <mergeCell ref="D16:D18"/>
+    <mergeCell ref="D20:D22"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="C2:C4"/>
+    <mergeCell ref="A55:D55"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="C12:C14"/>
+    <mergeCell ref="C16:C18"/>
+    <mergeCell ref="C20:C22"/>
+    <mergeCell ref="C24:C26"/>
+    <mergeCell ref="C50:C52"/>
+    <mergeCell ref="D24:D26"/>
+    <mergeCell ref="D28:D30"/>
+    <mergeCell ref="D32:D34"/>
+    <mergeCell ref="D36:D38"/>
+    <mergeCell ref="D42:D44"/>
+    <mergeCell ref="D46:D48"/>
+    <mergeCell ref="D50:D52"/>
+    <mergeCell ref="A40:D40"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2333,7 +2422,7 @@
       <c r="B2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="70" t="s">
+      <c r="C2" s="68" t="s">
         <v>41</v>
       </c>
       <c r="D2" s="67" t="s">
@@ -2357,7 +2446,7 @@
       <c r="J2" s="11">
         <v>0.5008326072</v>
       </c>
-      <c r="K2" s="65" t="s">
+      <c r="K2" s="70" t="s">
         <v>15</v>
       </c>
     </row>
@@ -2368,9 +2457,9 @@
       <c r="B3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="68"/>
-      <c r="D3" s="64"/>
-      <c r="E3" s="64"/>
+      <c r="C3" s="64"/>
+      <c r="D3" s="65"/>
+      <c r="E3" s="65"/>
       <c r="F3" s="11">
         <v>2.8763183099999999E-2</v>
       </c>
@@ -2386,7 +2475,7 @@
       <c r="J3" s="11">
         <v>0.49456959480000001</v>
       </c>
-      <c r="K3" s="66"/>
+      <c r="K3" s="71"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
@@ -2395,9 +2484,9 @@
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="68"/>
-      <c r="D4" s="64"/>
-      <c r="E4" s="64"/>
+      <c r="C4" s="64"/>
+      <c r="D4" s="65"/>
+      <c r="E4" s="65"/>
       <c r="F4" s="11">
         <v>5.7526370000000003E-4</v>
       </c>
@@ -2413,7 +2502,7 @@
       <c r="J4" s="11">
         <v>0.46208879800000002</v>
       </c>
-      <c r="K4" s="66"/>
+      <c r="K4" s="71"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="G5" s="11"/>
@@ -2428,13 +2517,13 @@
       <c r="B6" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="68" t="s">
+      <c r="C6" s="64" t="s">
         <v>42</v>
       </c>
-      <c r="D6" s="64" t="s">
+      <c r="D6" s="65" t="s">
         <v>10</v>
       </c>
-      <c r="E6" s="64" t="s">
+      <c r="E6" s="65" t="s">
         <v>13</v>
       </c>
       <c r="F6" s="11">
@@ -2452,7 +2541,7 @@
       <c r="J6" s="11">
         <v>0.50993042769999997</v>
       </c>
-      <c r="K6" s="66" t="s">
+      <c r="K6" s="71" t="s">
         <v>16</v>
       </c>
     </row>
@@ -2463,9 +2552,9 @@
       <c r="B7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="68"/>
-      <c r="D7" s="64"/>
-      <c r="E7" s="64"/>
+      <c r="C7" s="64"/>
+      <c r="D7" s="65"/>
+      <c r="E7" s="65"/>
       <c r="F7" s="11">
         <v>3.3435524000000001E-2</v>
       </c>
@@ -2481,7 +2570,7 @@
       <c r="J7" s="11">
         <v>0.50392556320000004</v>
       </c>
-      <c r="K7" s="66"/>
+      <c r="K7" s="71"/>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
@@ -2490,9 +2579,9 @@
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="68"/>
-      <c r="D8" s="64"/>
-      <c r="E8" s="64"/>
+      <c r="C8" s="64"/>
+      <c r="D8" s="65"/>
+      <c r="E8" s="65"/>
       <c r="F8" s="11">
         <v>3.8321520000000002E-4</v>
       </c>
@@ -2508,7 +2597,7 @@
       <c r="J8" s="11">
         <v>0.47738500210000001</v>
       </c>
-      <c r="K8" s="66"/>
+      <c r="K8" s="71"/>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="G9" s="11"/>
@@ -2517,12 +2606,12 @@
       <c r="J9" s="11"/>
     </row>
     <row r="10" spans="1:12" s="59" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="69" t="s">
+      <c r="A10" s="66" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="69"/>
-      <c r="C10" s="69"/>
-      <c r="D10" s="69"/>
+      <c r="B10" s="66"/>
+      <c r="C10" s="66"/>
+      <c r="D10" s="66"/>
       <c r="E10" s="60"/>
       <c r="F10" s="61"/>
       <c r="G10" s="61"/>
@@ -2544,13 +2633,13 @@
       <c r="B12" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C12" s="68" t="s">
+      <c r="C12" s="64" t="s">
         <v>43</v>
       </c>
-      <c r="D12" s="64" t="s">
+      <c r="D12" s="65" t="s">
         <v>11</v>
       </c>
-      <c r="E12" s="64" t="s">
+      <c r="E12" s="65" t="s">
         <v>17</v>
       </c>
       <c r="F12" s="11">
@@ -2568,7 +2657,7 @@
       <c r="J12" s="11">
         <v>0.4966675035</v>
       </c>
-      <c r="K12" s="66" t="s">
+      <c r="K12" s="71" t="s">
         <v>18</v>
       </c>
     </row>
@@ -2579,9 +2668,9 @@
       <c r="B13" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C13" s="68"/>
-      <c r="D13" s="64"/>
-      <c r="E13" s="64"/>
+      <c r="C13" s="64"/>
+      <c r="D13" s="65"/>
+      <c r="E13" s="65"/>
       <c r="F13" s="11">
         <v>2.876318E-4</v>
       </c>
@@ -2597,7 +2686,7 @@
       <c r="J13" s="11">
         <v>0.48225264400000001</v>
       </c>
-      <c r="K13" s="66"/>
+      <c r="K13" s="71"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
@@ -2606,9 +2695,9 @@
       <c r="B14" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C14" s="68"/>
-      <c r="D14" s="64"/>
-      <c r="E14" s="64"/>
+      <c r="C14" s="64"/>
+      <c r="D14" s="65"/>
+      <c r="E14" s="65"/>
       <c r="F14" s="11">
         <v>6.7114089999999996E-4</v>
       </c>
@@ -2624,7 +2713,7 @@
       <c r="J14" s="11">
         <v>0.43776818420000002</v>
       </c>
-      <c r="K14" s="66"/>
+      <c r="K14" s="71"/>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="G15" s="11"/>
@@ -2639,13 +2728,13 @@
       <c r="B16" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C16" s="68" t="s">
+      <c r="C16" s="64" t="s">
         <v>44</v>
       </c>
-      <c r="D16" s="64" t="s">
+      <c r="D16" s="65" t="s">
         <v>19</v>
       </c>
-      <c r="E16" s="64" t="s">
+      <c r="E16" s="65" t="s">
         <v>27</v>
       </c>
       <c r="F16" s="11">
@@ -2663,7 +2752,7 @@
       <c r="J16" s="11">
         <v>0.44130707470000002</v>
       </c>
-      <c r="K16" s="66" t="s">
+      <c r="K16" s="71" t="s">
         <v>36</v>
       </c>
     </row>
@@ -2674,9 +2763,9 @@
       <c r="B17" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C17" s="68"/>
-      <c r="D17" s="64"/>
-      <c r="E17" s="64"/>
+      <c r="C17" s="64"/>
+      <c r="D17" s="65"/>
+      <c r="E17" s="65"/>
       <c r="F17" s="11">
         <v>7.7660593999999998E-3</v>
       </c>
@@ -2692,7 +2781,7 @@
       <c r="J17" s="11">
         <v>0.46778393010000002</v>
       </c>
-      <c r="K17" s="66"/>
+      <c r="K17" s="71"/>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
@@ -2701,9 +2790,9 @@
       <c r="B18" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C18" s="68"/>
-      <c r="D18" s="64"/>
-      <c r="E18" s="64"/>
+      <c r="C18" s="64"/>
+      <c r="D18" s="65"/>
+      <c r="E18" s="65"/>
       <c r="F18" s="11">
         <v>2.876318E-4</v>
       </c>
@@ -2719,7 +2808,7 @@
       <c r="J18" s="11">
         <v>0.46815617929999997</v>
       </c>
-      <c r="K18" s="66"/>
+      <c r="K18" s="71"/>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.2">
       <c r="G19" s="11"/>
@@ -2734,13 +2823,13 @@
       <c r="B20" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C20" s="68" t="s">
+      <c r="C20" s="64" t="s">
         <v>45</v>
       </c>
-      <c r="D20" s="64" t="s">
+      <c r="D20" s="65" t="s">
         <v>20</v>
       </c>
-      <c r="E20" s="64" t="s">
+      <c r="E20" s="65" t="s">
         <v>28</v>
       </c>
       <c r="F20" s="11">
@@ -2758,7 +2847,7 @@
       <c r="J20" s="11">
         <v>0.4434595543</v>
       </c>
-      <c r="K20" s="66" t="s">
+      <c r="K20" s="71" t="s">
         <v>35</v>
       </c>
     </row>
@@ -2769,9 +2858,9 @@
       <c r="B21" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C21" s="68"/>
-      <c r="D21" s="64"/>
-      <c r="E21" s="64"/>
+      <c r="C21" s="64"/>
+      <c r="D21" s="65"/>
+      <c r="E21" s="65"/>
       <c r="F21" s="11">
         <v>5.11025887E-2</v>
       </c>
@@ -2787,7 +2876,7 @@
       <c r="J21" s="11">
         <v>0.46092753450000001</v>
       </c>
-      <c r="K21" s="66"/>
+      <c r="K21" s="71"/>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
@@ -2796,9 +2885,9 @@
       <c r="B22" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C22" s="68"/>
-      <c r="D22" s="64"/>
-      <c r="E22" s="64"/>
+      <c r="C22" s="64"/>
+      <c r="D22" s="65"/>
+      <c r="E22" s="65"/>
       <c r="F22" s="11">
         <v>0</v>
       </c>
@@ -2814,7 +2903,7 @@
       <c r="J22" s="11">
         <v>0.4740446935</v>
       </c>
-      <c r="K22" s="66"/>
+      <c r="K22" s="71"/>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.2">
       <c r="G23" s="11"/>
@@ -2829,13 +2918,13 @@
       <c r="B24" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C24" s="68" t="s">
+      <c r="C24" s="64" t="s">
         <v>46</v>
       </c>
-      <c r="D24" s="64" t="s">
+      <c r="D24" s="65" t="s">
         <v>21</v>
       </c>
-      <c r="E24" s="64" t="s">
+      <c r="E24" s="65" t="s">
         <v>32</v>
       </c>
       <c r="F24" s="11">
@@ -2861,9 +2950,9 @@
       <c r="B25" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C25" s="68"/>
-      <c r="D25" s="64"/>
-      <c r="E25" s="64"/>
+      <c r="C25" s="64"/>
+      <c r="D25" s="65"/>
+      <c r="E25" s="65"/>
       <c r="F25" s="11">
         <v>3.0584851400000002E-2</v>
       </c>
@@ -2887,9 +2976,9 @@
       <c r="B26" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C26" s="68"/>
-      <c r="D26" s="64"/>
-      <c r="E26" s="64"/>
+      <c r="C26" s="64"/>
+      <c r="D26" s="65"/>
+      <c r="E26" s="65"/>
       <c r="F26" s="11">
         <v>6.7114089999999996E-4</v>
       </c>
@@ -2919,13 +3008,13 @@
       <c r="B28" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C28" s="68" t="s">
+      <c r="C28" s="64" t="s">
         <v>47</v>
       </c>
-      <c r="D28" s="64" t="s">
+      <c r="D28" s="65" t="s">
         <v>22</v>
       </c>
-      <c r="E28" s="64" t="s">
+      <c r="E28" s="65" t="s">
         <v>33</v>
       </c>
       <c r="F28" s="11">
@@ -2951,9 +3040,9 @@
       <c r="B29" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C29" s="68"/>
-      <c r="D29" s="64"/>
-      <c r="E29" s="64"/>
+      <c r="C29" s="64"/>
+      <c r="D29" s="65"/>
+      <c r="E29" s="65"/>
       <c r="F29" s="11">
         <v>1.42857143E-2</v>
       </c>
@@ -2977,9 +3066,9 @@
       <c r="B30" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C30" s="68"/>
-      <c r="D30" s="64"/>
-      <c r="E30" s="64"/>
+      <c r="C30" s="64"/>
+      <c r="D30" s="65"/>
+      <c r="E30" s="65"/>
       <c r="F30" s="11">
         <v>3.8350910000000001E-4</v>
       </c>
@@ -3009,13 +3098,13 @@
       <c r="B32" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C32" s="68" t="s">
+      <c r="C32" s="64" t="s">
         <v>48</v>
       </c>
-      <c r="D32" s="64" t="s">
+      <c r="D32" s="65" t="s">
         <v>23</v>
       </c>
-      <c r="E32" s="64" t="s">
+      <c r="E32" s="65" t="s">
         <v>29</v>
       </c>
       <c r="F32" s="11">
@@ -3041,9 +3130,9 @@
       <c r="B33" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C33" s="68"/>
-      <c r="D33" s="64"/>
-      <c r="E33" s="64"/>
+      <c r="C33" s="64"/>
+      <c r="D33" s="65"/>
+      <c r="E33" s="65"/>
       <c r="F33" s="11">
         <v>6.9727237799999994E-2</v>
       </c>
@@ -3067,9 +3156,9 @@
       <c r="B34" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C34" s="68"/>
-      <c r="D34" s="64"/>
-      <c r="E34" s="64"/>
+      <c r="C34" s="64"/>
+      <c r="D34" s="65"/>
+      <c r="E34" s="65"/>
       <c r="F34" s="11">
         <v>2.8812910000000001E-4</v>
       </c>
@@ -3099,13 +3188,13 @@
       <c r="B36" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C36" s="68" t="s">
+      <c r="C36" s="64" t="s">
         <v>49</v>
       </c>
-      <c r="D36" s="64" t="s">
+      <c r="D36" s="65" t="s">
         <v>24</v>
       </c>
-      <c r="E36" s="64" t="s">
+      <c r="E36" s="65" t="s">
         <v>34</v>
       </c>
       <c r="F36" s="11">
@@ -3131,9 +3220,9 @@
       <c r="B37" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C37" s="68"/>
-      <c r="D37" s="64"/>
-      <c r="E37" s="64"/>
+      <c r="C37" s="64"/>
+      <c r="D37" s="65"/>
+      <c r="E37" s="65"/>
       <c r="F37" s="11">
         <v>1.4189837E-2</v>
       </c>
@@ -3157,9 +3246,9 @@
       <c r="B38" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C38" s="68"/>
-      <c r="D38" s="64"/>
-      <c r="E38" s="64"/>
+      <c r="C38" s="64"/>
+      <c r="D38" s="65"/>
+      <c r="E38" s="65"/>
       <c r="F38" s="11">
         <v>2.876318E-4</v>
       </c>
@@ -3183,12 +3272,12 @@
       <c r="J39" s="11"/>
     </row>
     <row r="40" spans="1:11" s="59" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="69" t="s">
+      <c r="A40" s="66" t="s">
         <v>38</v>
       </c>
-      <c r="B40" s="69"/>
-      <c r="C40" s="69"/>
-      <c r="D40" s="69"/>
+      <c r="B40" s="66"/>
+      <c r="C40" s="66"/>
+      <c r="D40" s="66"/>
       <c r="E40" s="60"/>
       <c r="F40" s="61"/>
       <c r="G40" s="61"/>
@@ -3210,13 +3299,13 @@
       <c r="B42" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C42" s="68" t="s">
+      <c r="C42" s="64" t="s">
         <v>50</v>
       </c>
-      <c r="D42" s="64" t="s">
+      <c r="D42" s="65" t="s">
         <v>25</v>
       </c>
-      <c r="E42" s="64" t="s">
+      <c r="E42" s="65" t="s">
         <v>27</v>
       </c>
       <c r="F42" s="11">
@@ -3234,7 +3323,7 @@
       <c r="J42" s="11">
         <v>0.4587482034</v>
       </c>
-      <c r="K42" s="66" t="s">
+      <c r="K42" s="71" t="s">
         <v>30</v>
       </c>
     </row>
@@ -3245,9 +3334,9 @@
       <c r="B43" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C43" s="68"/>
-      <c r="D43" s="64"/>
-      <c r="E43" s="64"/>
+      <c r="C43" s="64"/>
+      <c r="D43" s="65"/>
+      <c r="E43" s="65"/>
       <c r="F43" s="11">
         <v>1.34125311E-2</v>
       </c>
@@ -3263,7 +3352,7 @@
       <c r="J43" s="11">
         <v>0.46907909489999999</v>
       </c>
-      <c r="K43" s="66"/>
+      <c r="K43" s="71"/>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
@@ -3272,9 +3361,9 @@
       <c r="B44" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C44" s="68"/>
-      <c r="D44" s="64"/>
-      <c r="E44" s="64"/>
+      <c r="C44" s="64"/>
+      <c r="D44" s="65"/>
+      <c r="E44" s="65"/>
       <c r="F44" s="11">
         <v>8.6223409999999995E-4</v>
       </c>
@@ -3290,7 +3379,7 @@
       <c r="J44" s="11">
         <v>0.49390839069999998</v>
       </c>
-      <c r="K44" s="66"/>
+      <c r="K44" s="71"/>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.2">
       <c r="G45" s="11"/>
@@ -3305,13 +3394,13 @@
       <c r="B46" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C46" s="68" t="s">
+      <c r="C46" s="64" t="s">
         <v>51</v>
       </c>
-      <c r="D46" s="64" t="s">
+      <c r="D46" s="65" t="s">
         <v>26</v>
       </c>
-      <c r="E46" s="64" t="s">
+      <c r="E46" s="65" t="s">
         <v>28</v>
       </c>
       <c r="F46" s="11">
@@ -3329,7 +3418,7 @@
       <c r="J46" s="11">
         <v>0.45388746419999998</v>
       </c>
-      <c r="K46" s="66" t="s">
+      <c r="K46" s="71" t="s">
         <v>31</v>
       </c>
     </row>
@@ -3340,9 +3429,9 @@
       <c r="B47" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C47" s="68"/>
-      <c r="D47" s="64"/>
-      <c r="E47" s="64"/>
+      <c r="C47" s="64"/>
+      <c r="D47" s="65"/>
+      <c r="E47" s="65"/>
       <c r="F47" s="11">
         <v>4.3303314799999999E-2</v>
       </c>
@@ -3358,7 +3447,7 @@
       <c r="J47" s="11">
         <v>0.45908136910000003</v>
       </c>
-      <c r="K47" s="66"/>
+      <c r="K47" s="71"/>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
@@ -3367,9 +3456,9 @@
       <c r="B48" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C48" s="68"/>
-      <c r="D48" s="64"/>
-      <c r="E48" s="64"/>
+      <c r="C48" s="64"/>
+      <c r="D48" s="65"/>
+      <c r="E48" s="65"/>
       <c r="F48" s="11">
         <v>9.5803800000000006E-5</v>
       </c>
@@ -3385,7 +3474,7 @@
       <c r="J48" s="11">
         <v>0.478579698</v>
       </c>
-      <c r="K48" s="66"/>
+      <c r="K48" s="71"/>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.2">
       <c r="G49" s="11"/>
@@ -3400,13 +3489,13 @@
       <c r="B50" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C50" s="68" t="s">
+      <c r="C50" s="64" t="s">
         <v>52</v>
       </c>
-      <c r="D50" s="64" t="s">
+      <c r="D50" s="65" t="s">
         <v>39</v>
       </c>
-      <c r="E50" s="64" t="s">
+      <c r="E50" s="65" t="s">
         <v>29</v>
       </c>
       <c r="F50" s="11">
@@ -3432,9 +3521,9 @@
       <c r="B51" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C51" s="68"/>
-      <c r="D51" s="64"/>
-      <c r="E51" s="64"/>
+      <c r="C51" s="64"/>
+      <c r="D51" s="65"/>
+      <c r="E51" s="65"/>
       <c r="F51" s="11">
         <v>8.8139489999999997E-3</v>
       </c>
@@ -3458,9 +3547,9 @@
       <c r="B52" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C52" s="68"/>
-      <c r="D52" s="64"/>
-      <c r="E52" s="64"/>
+      <c r="C52" s="64"/>
+      <c r="D52" s="65"/>
+      <c r="E52" s="65"/>
       <c r="F52" s="11">
         <v>1.9160760000000001E-4</v>
       </c>
@@ -3490,12 +3579,12 @@
       <c r="J54" s="11"/>
     </row>
     <row r="55" spans="1:11" s="42" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="71" t="s">
+      <c r="A55" s="63" t="s">
         <v>59</v>
       </c>
-      <c r="B55" s="71"/>
-      <c r="C55" s="71"/>
-      <c r="D55" s="71"/>
+      <c r="B55" s="63"/>
+      <c r="C55" s="63"/>
+      <c r="D55" s="63"/>
       <c r="E55" s="39"/>
       <c r="F55" s="40">
         <f>MAX(F2:F52)</f>
@@ -3520,12 +3609,12 @@
       <c r="K55" s="41"/>
     </row>
     <row r="56" spans="1:11" s="46" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="63" t="s">
+      <c r="A56" s="69" t="s">
         <v>60</v>
       </c>
-      <c r="B56" s="63"/>
-      <c r="C56" s="63"/>
-      <c r="D56" s="63"/>
+      <c r="B56" s="69"/>
+      <c r="C56" s="69"/>
+      <c r="D56" s="69"/>
       <c r="E56" s="43"/>
       <c r="F56" s="44">
         <f>AVERAGE(F2:F52)</f>
@@ -3551,37 +3640,6 @@
     </row>
   </sheetData>
   <mergeCells count="47">
-    <mergeCell ref="A55:D55"/>
-    <mergeCell ref="K42:K44"/>
-    <mergeCell ref="C46:C48"/>
-    <mergeCell ref="D46:D48"/>
-    <mergeCell ref="E46:E48"/>
-    <mergeCell ref="K46:K48"/>
-    <mergeCell ref="E50:E52"/>
-    <mergeCell ref="C36:C38"/>
-    <mergeCell ref="D36:D38"/>
-    <mergeCell ref="E36:E38"/>
-    <mergeCell ref="A40:D40"/>
-    <mergeCell ref="C42:C44"/>
-    <mergeCell ref="D42:D44"/>
-    <mergeCell ref="E42:E44"/>
-    <mergeCell ref="K12:K14"/>
-    <mergeCell ref="C20:C22"/>
-    <mergeCell ref="D20:D22"/>
-    <mergeCell ref="E20:E22"/>
-    <mergeCell ref="K20:K22"/>
-    <mergeCell ref="C16:C18"/>
-    <mergeCell ref="D16:D18"/>
-    <mergeCell ref="E16:E18"/>
-    <mergeCell ref="K16:K18"/>
-    <mergeCell ref="C2:C4"/>
-    <mergeCell ref="D2:D4"/>
-    <mergeCell ref="E2:E4"/>
-    <mergeCell ref="K2:K4"/>
-    <mergeCell ref="C6:C8"/>
-    <mergeCell ref="D6:D8"/>
-    <mergeCell ref="E6:E8"/>
-    <mergeCell ref="K6:K8"/>
     <mergeCell ref="A56:D56"/>
     <mergeCell ref="A10:D10"/>
     <mergeCell ref="C12:C14"/>
@@ -3598,6 +3656,37 @@
     <mergeCell ref="E32:E34"/>
     <mergeCell ref="C50:C52"/>
     <mergeCell ref="D50:D52"/>
+    <mergeCell ref="C2:C4"/>
+    <mergeCell ref="D2:D4"/>
+    <mergeCell ref="E2:E4"/>
+    <mergeCell ref="K2:K4"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="D6:D8"/>
+    <mergeCell ref="E6:E8"/>
+    <mergeCell ref="K6:K8"/>
+    <mergeCell ref="K12:K14"/>
+    <mergeCell ref="C20:C22"/>
+    <mergeCell ref="D20:D22"/>
+    <mergeCell ref="E20:E22"/>
+    <mergeCell ref="K20:K22"/>
+    <mergeCell ref="C16:C18"/>
+    <mergeCell ref="D16:D18"/>
+    <mergeCell ref="E16:E18"/>
+    <mergeCell ref="K16:K18"/>
+    <mergeCell ref="C36:C38"/>
+    <mergeCell ref="D36:D38"/>
+    <mergeCell ref="E36:E38"/>
+    <mergeCell ref="A40:D40"/>
+    <mergeCell ref="C42:C44"/>
+    <mergeCell ref="D42:D44"/>
+    <mergeCell ref="E42:E44"/>
+    <mergeCell ref="A55:D55"/>
+    <mergeCell ref="K42:K44"/>
+    <mergeCell ref="C46:C48"/>
+    <mergeCell ref="D46:D48"/>
+    <mergeCell ref="E46:E48"/>
+    <mergeCell ref="K46:K48"/>
+    <mergeCell ref="E50:E52"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -3678,7 +3767,7 @@
       <c r="B2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="70" t="s">
+      <c r="C2" s="68" t="s">
         <v>41</v>
       </c>
       <c r="D2" s="67" t="s">
@@ -3714,7 +3803,7 @@
         <f>SUM(F2*1/5,G2*1/5,H2*1/5,I2*1/5,J2*1/5)</f>
         <v>0.29130368856</v>
       </c>
-      <c r="N2" s="65" t="s">
+      <c r="N2" s="70" t="s">
         <v>15</v>
       </c>
     </row>
@@ -3725,9 +3814,9 @@
       <c r="B3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="68"/>
-      <c r="D3" s="64"/>
-      <c r="E3" s="64"/>
+      <c r="C3" s="64"/>
+      <c r="D3" s="65"/>
+      <c r="E3" s="65"/>
       <c r="F3" s="11">
         <v>2.3969319E-3</v>
       </c>
@@ -3755,7 +3844,7 @@
         <f>SUM(F3*1/5,G3*1/5,H3*1/5,I3*1/5,J3*1/5)</f>
         <v>0.26225518991999996</v>
       </c>
-      <c r="N3" s="66"/>
+      <c r="N3" s="71"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
@@ -3764,9 +3853,9 @@
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="68"/>
-      <c r="D4" s="64"/>
-      <c r="E4" s="64"/>
+      <c r="C4" s="64"/>
+      <c r="D4" s="65"/>
+      <c r="E4" s="65"/>
       <c r="F4" s="11">
         <v>6.5867689399999999E-2</v>
       </c>
@@ -3794,7 +3883,7 @@
         <f>SUM(F4*1/5,G4*1/5,H4*1/5,I4*1/5,J4*1/5)</f>
         <v>0.29107094631999997</v>
       </c>
-      <c r="N4" s="66"/>
+      <c r="N4" s="71"/>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
@@ -3803,13 +3892,13 @@
       <c r="B6" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="68" t="s">
+      <c r="C6" s="64" t="s">
         <v>42</v>
       </c>
-      <c r="D6" s="64" t="s">
+      <c r="D6" s="65" t="s">
         <v>10</v>
       </c>
-      <c r="E6" s="64" t="s">
+      <c r="E6" s="65" t="s">
         <v>13</v>
       </c>
       <c r="F6" s="11">
@@ -3839,7 +3928,7 @@
         <f>SUM(F6*1/5,G6*1/5,H6*1/5,I6*1/5,J6*1/5)</f>
         <v>0.29438649154000002</v>
       </c>
-      <c r="N6" s="66" t="s">
+      <c r="N6" s="71" t="s">
         <v>16</v>
       </c>
     </row>
@@ -3850,9 +3939,9 @@
       <c r="B7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="68"/>
-      <c r="D7" s="64"/>
-      <c r="E7" s="64"/>
+      <c r="C7" s="64"/>
+      <c r="D7" s="65"/>
+      <c r="E7" s="65"/>
       <c r="F7" s="11">
         <v>1.3604138700000001E-2</v>
       </c>
@@ -3880,7 +3969,7 @@
         <f>SUM(F7*1/5,G7*1/5,H7*1/5,I7*1/5,J7*1/5)</f>
         <v>0.27579129901999999</v>
       </c>
-      <c r="N7" s="66"/>
+      <c r="N7" s="71"/>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
@@ -3889,9 +3978,9 @@
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="68"/>
-      <c r="D8" s="64"/>
-      <c r="E8" s="64"/>
+      <c r="C8" s="64"/>
+      <c r="D8" s="65"/>
+      <c r="E8" s="65"/>
       <c r="F8" s="11">
         <v>3.8321517499999999E-2</v>
       </c>
@@ -3919,15 +4008,15 @@
         <f>SUM(F8*1/5,G8*1/5,H8*1/5,I8*1/5,J8*1/5)</f>
         <v>0.2717815321</v>
       </c>
-      <c r="N8" s="66"/>
+      <c r="N8" s="71"/>
     </row>
     <row r="10" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="78" t="s">
+      <c r="A10" s="73" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="78"/>
-      <c r="C10" s="78"/>
-      <c r="D10" s="78"/>
+      <c r="B10" s="73"/>
+      <c r="C10" s="73"/>
+      <c r="D10" s="73"/>
       <c r="E10" s="5"/>
       <c r="F10" s="13"/>
       <c r="G10" s="13"/>
@@ -3946,13 +4035,13 @@
       <c r="B12" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C12" s="68" t="s">
+      <c r="C12" s="64" t="s">
         <v>43</v>
       </c>
-      <c r="D12" s="64" t="s">
+      <c r="D12" s="65" t="s">
         <v>11</v>
       </c>
-      <c r="E12" s="64" t="s">
+      <c r="E12" s="65" t="s">
         <v>17</v>
       </c>
       <c r="F12" s="11">
@@ -3982,7 +4071,7 @@
         <f>SUM(F12*1/5,G12*1/5,H12*1/5,I12*1/5,J12*1/5)</f>
         <v>0.33641501256</v>
       </c>
-      <c r="N12" s="66" t="s">
+      <c r="N12" s="71" t="s">
         <v>18</v>
       </c>
     </row>
@@ -3993,9 +4082,9 @@
       <c r="B13" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C13" s="68"/>
-      <c r="D13" s="64"/>
-      <c r="E13" s="64"/>
+      <c r="C13" s="64"/>
+      <c r="D13" s="65"/>
+      <c r="E13" s="65"/>
       <c r="F13" s="11">
         <v>7.9194630899999993E-2</v>
       </c>
@@ -4023,7 +4112,7 @@
         <f>SUM(F13*1/5,G13*1/5,H13*1/5,I13*1/5,J13*1/5)</f>
         <v>0.26691102733999994</v>
       </c>
-      <c r="N13" s="66"/>
+      <c r="N13" s="71"/>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
@@ -4032,9 +4121,9 @@
       <c r="B14" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C14" s="68"/>
-      <c r="D14" s="64"/>
-      <c r="E14" s="64"/>
+      <c r="C14" s="64"/>
+      <c r="D14" s="65"/>
+      <c r="E14" s="65"/>
       <c r="F14" s="11">
         <v>3.8350910000000001E-4</v>
       </c>
@@ -4062,7 +4151,7 @@
         <f>SUM(F14*1/5,G14*1/5,H14*1/5,I14*1/5,J14*1/5)</f>
         <v>0.22330577798000001</v>
       </c>
-      <c r="N14" s="66"/>
+      <c r="N14" s="71"/>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
@@ -4071,13 +4160,13 @@
       <c r="B16" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C16" s="68" t="s">
+      <c r="C16" s="64" t="s">
         <v>44</v>
       </c>
-      <c r="D16" s="64" t="s">
+      <c r="D16" s="65" t="s">
         <v>19</v>
       </c>
-      <c r="E16" s="64" t="s">
+      <c r="E16" s="65" t="s">
         <v>27</v>
       </c>
       <c r="F16" s="11">
@@ -4107,7 +4196,7 @@
         <f>SUM(F16*1/5,G16*1/5,H16*1/5,I16*1/5,J16*1/5)</f>
         <v>0.34767161497999999</v>
       </c>
-      <c r="N16" s="66" t="s">
+      <c r="N16" s="71" t="s">
         <v>36</v>
       </c>
     </row>
@@ -4118,9 +4207,9 @@
       <c r="B17" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C17" s="68"/>
-      <c r="D17" s="64"/>
-      <c r="E17" s="64"/>
+      <c r="C17" s="64"/>
+      <c r="D17" s="65"/>
+      <c r="E17" s="65"/>
       <c r="F17" s="11">
         <v>3.7296260800000001E-2</v>
       </c>
@@ -4148,7 +4237,7 @@
         <f>SUM(F17*1/5,G17*1/5,H17*1/5,I17*1/5,J17*1/5)</f>
         <v>0.33628517706000005</v>
       </c>
-      <c r="N17" s="66"/>
+      <c r="N17" s="71"/>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
@@ -4157,9 +4246,9 @@
       <c r="B18" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C18" s="68"/>
-      <c r="D18" s="64"/>
-      <c r="E18" s="64"/>
+      <c r="C18" s="64"/>
+      <c r="D18" s="65"/>
+      <c r="E18" s="65"/>
       <c r="F18" s="11">
         <v>1.0546500000000001E-3</v>
       </c>
@@ -4187,7 +4276,7 @@
         <f>SUM(F18*1/5,G18*1/5,H18*1/5,I18*1/5,J18*1/5)</f>
         <v>0.20704430204000002</v>
       </c>
-      <c r="N18" s="66"/>
+      <c r="N18" s="71"/>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
@@ -4196,13 +4285,13 @@
       <c r="B20" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C20" s="68" t="s">
+      <c r="C20" s="64" t="s">
         <v>45</v>
       </c>
-      <c r="D20" s="64" t="s">
+      <c r="D20" s="65" t="s">
         <v>20</v>
       </c>
-      <c r="E20" s="64" t="s">
+      <c r="E20" s="65" t="s">
         <v>28</v>
       </c>
       <c r="F20" s="11">
@@ -4232,7 +4321,7 @@
         <f>SUM(F20*1/5,G20*1/5,H20*1/5,I20*1/5,J20*1/5)</f>
         <v>0.31181358595999997</v>
       </c>
-      <c r="N20" s="66" t="s">
+      <c r="N20" s="71" t="s">
         <v>35</v>
       </c>
     </row>
@@ -4243,9 +4332,9 @@
       <c r="B21" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C21" s="68"/>
-      <c r="D21" s="64"/>
-      <c r="E21" s="64"/>
+      <c r="C21" s="64"/>
+      <c r="D21" s="65"/>
+      <c r="E21" s="65"/>
       <c r="F21" s="11">
         <v>1.05465005E-2</v>
       </c>
@@ -4273,7 +4362,7 @@
         <f>SUM(F21*1/5,G21*1/5,H21*1/5,I21*1/5,J21*1/5)</f>
         <v>0.29879759264</v>
       </c>
-      <c r="N21" s="66"/>
+      <c r="N21" s="71"/>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
@@ -4282,9 +4371,9 @@
       <c r="B22" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C22" s="68"/>
-      <c r="D22" s="64"/>
-      <c r="E22" s="64"/>
+      <c r="C22" s="64"/>
+      <c r="D22" s="65"/>
+      <c r="E22" s="65"/>
       <c r="F22" s="11">
         <v>0</v>
       </c>
@@ -4312,7 +4401,7 @@
         <f>SUM(F22*1/5,G22*1/5,H22*1/5,I22*1/5,J22*1/5)</f>
         <v>0.22541820497999998</v>
       </c>
-      <c r="N22" s="66"/>
+      <c r="N22" s="71"/>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
@@ -4321,13 +4410,13 @@
       <c r="B24" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C24" s="68" t="s">
+      <c r="C24" s="64" t="s">
         <v>46</v>
       </c>
-      <c r="D24" s="64" t="s">
+      <c r="D24" s="65" t="s">
         <v>21</v>
       </c>
-      <c r="E24" s="64" t="s">
+      <c r="E24" s="65" t="s">
         <v>32</v>
       </c>
       <c r="F24" s="11">
@@ -4365,9 +4454,9 @@
       <c r="B25" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C25" s="68"/>
-      <c r="D25" s="64"/>
-      <c r="E25" s="64"/>
+      <c r="C25" s="64"/>
+      <c r="D25" s="65"/>
+      <c r="E25" s="65"/>
       <c r="F25" s="11">
         <v>2.7229146700000002E-2</v>
       </c>
@@ -4403,9 +4492,9 @@
       <c r="B26" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C26" s="68"/>
-      <c r="D26" s="64"/>
-      <c r="E26" s="64"/>
+      <c r="C26" s="64"/>
+      <c r="D26" s="65"/>
+      <c r="E26" s="65"/>
       <c r="F26" s="11">
         <v>3.8350910000000001E-4</v>
       </c>
@@ -4441,13 +4530,13 @@
       <c r="B28" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C28" s="68" t="s">
+      <c r="C28" s="64" t="s">
         <v>47</v>
       </c>
-      <c r="D28" s="64" t="s">
+      <c r="D28" s="65" t="s">
         <v>22</v>
       </c>
-      <c r="E28" s="64" t="s">
+      <c r="E28" s="65" t="s">
         <v>33</v>
       </c>
       <c r="F28" s="11">
@@ -4485,9 +4574,9 @@
       <c r="B29" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C29" s="68"/>
-      <c r="D29" s="64"/>
-      <c r="E29" s="64"/>
+      <c r="C29" s="64"/>
+      <c r="D29" s="65"/>
+      <c r="E29" s="65"/>
       <c r="F29" s="11">
         <v>2.8475551299999999E-2</v>
       </c>
@@ -4523,9 +4612,9 @@
       <c r="B30" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C30" s="68"/>
-      <c r="D30" s="64"/>
-      <c r="E30" s="64"/>
+      <c r="C30" s="64"/>
+      <c r="D30" s="65"/>
+      <c r="E30" s="65"/>
       <c r="F30" s="11">
         <v>1.917546E-4</v>
       </c>
@@ -4561,13 +4650,13 @@
       <c r="B32" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C32" s="68" t="s">
+      <c r="C32" s="64" t="s">
         <v>48</v>
       </c>
-      <c r="D32" s="64" t="s">
+      <c r="D32" s="65" t="s">
         <v>23</v>
       </c>
-      <c r="E32" s="64" t="s">
+      <c r="E32" s="65" t="s">
         <v>29</v>
       </c>
       <c r="F32" s="11">
@@ -4605,9 +4694,9 @@
       <c r="B33" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C33" s="68"/>
-      <c r="D33" s="64"/>
-      <c r="E33" s="64"/>
+      <c r="C33" s="64"/>
+      <c r="D33" s="65"/>
+      <c r="E33" s="65"/>
       <c r="F33" s="11">
         <v>2.4010757000000001E-3</v>
       </c>
@@ -4643,9 +4732,9 @@
       <c r="B34" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C34" s="68"/>
-      <c r="D34" s="64"/>
-      <c r="E34" s="64"/>
+      <c r="C34" s="64"/>
+      <c r="D34" s="65"/>
+      <c r="E34" s="65"/>
       <c r="F34" s="11">
         <v>0</v>
       </c>
@@ -4681,13 +4770,13 @@
       <c r="B36" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C36" s="68" t="s">
+      <c r="C36" s="64" t="s">
         <v>49</v>
       </c>
-      <c r="D36" s="64" t="s">
+      <c r="D36" s="65" t="s">
         <v>24</v>
       </c>
-      <c r="E36" s="64" t="s">
+      <c r="E36" s="65" t="s">
         <v>34</v>
       </c>
       <c r="F36" s="11">
@@ -4725,9 +4814,9 @@
       <c r="B37" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C37" s="68"/>
-      <c r="D37" s="64"/>
-      <c r="E37" s="64"/>
+      <c r="C37" s="64"/>
+      <c r="D37" s="65"/>
+      <c r="E37" s="65"/>
       <c r="F37" s="11">
         <v>5.9443912000000003E-3</v>
       </c>
@@ -4763,9 +4852,9 @@
       <c r="B38" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C38" s="68"/>
-      <c r="D38" s="64"/>
-      <c r="E38" s="64"/>
+      <c r="C38" s="64"/>
+      <c r="D38" s="65"/>
+      <c r="E38" s="65"/>
       <c r="F38" s="11">
         <v>1.917546E-4</v>
       </c>
@@ -4795,12 +4884,12 @@
       </c>
     </row>
     <row r="40" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="78" t="s">
+      <c r="A40" s="73" t="s">
         <v>38</v>
       </c>
-      <c r="B40" s="78"/>
-      <c r="C40" s="78"/>
-      <c r="D40" s="78"/>
+      <c r="B40" s="73"/>
+      <c r="C40" s="73"/>
+      <c r="D40" s="73"/>
       <c r="E40" s="5"/>
       <c r="F40" s="13"/>
       <c r="G40" s="13"/>
@@ -4819,13 +4908,13 @@
       <c r="B42" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C42" s="68" t="s">
+      <c r="C42" s="64" t="s">
         <v>50</v>
       </c>
-      <c r="D42" s="64" t="s">
+      <c r="D42" s="65" t="s">
         <v>25</v>
       </c>
-      <c r="E42" s="64" t="s">
+      <c r="E42" s="65" t="s">
         <v>27</v>
       </c>
       <c r="F42" s="11">
@@ -4855,7 +4944,7 @@
         <f>SUM(F42*1/5,G42*1/5,H42*1/5,I42*1/5,J42*1/5)</f>
         <v>0.32911788728000002</v>
       </c>
-      <c r="N42" s="66" t="s">
+      <c r="N42" s="71" t="s">
         <v>30</v>
       </c>
     </row>
@@ -4866,9 +4955,9 @@
       <c r="B43" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C43" s="68"/>
-      <c r="D43" s="64"/>
-      <c r="E43" s="64"/>
+      <c r="C43" s="64"/>
+      <c r="D43" s="65"/>
+      <c r="E43" s="65"/>
       <c r="F43" s="11">
         <v>1.59034298E-2</v>
       </c>
@@ -4896,7 +4985,7 @@
         <f>SUM(F43*1/5,G43*1/5,H43*1/5,I43*1/5,J43*1/5)</f>
         <v>0.33481998118</v>
       </c>
-      <c r="N43" s="66"/>
+      <c r="N43" s="71"/>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
@@ -4905,9 +4994,9 @@
       <c r="B44" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C44" s="68"/>
-      <c r="D44" s="64"/>
-      <c r="E44" s="64"/>
+      <c r="C44" s="64"/>
+      <c r="D44" s="65"/>
+      <c r="E44" s="65"/>
       <c r="F44" s="62">
         <v>0</v>
       </c>
@@ -4935,7 +5024,7 @@
         <f>SUM(F44*1/5,G44*1/5,H44*1/5,I44*1/5,J44*1/5)</f>
         <v>0.23017129817999998</v>
       </c>
-      <c r="N44" s="66"/>
+      <c r="N44" s="71"/>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
@@ -4944,13 +5033,13 @@
       <c r="B46" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C46" s="68" t="s">
+      <c r="C46" s="64" t="s">
         <v>51</v>
       </c>
-      <c r="D46" s="64" t="s">
+      <c r="D46" s="65" t="s">
         <v>26</v>
       </c>
-      <c r="E46" s="64" t="s">
+      <c r="E46" s="65" t="s">
         <v>28</v>
       </c>
       <c r="F46" s="11">
@@ -4980,7 +5069,7 @@
         <f>SUM(F46*1/5,G46*1/5,H46*1/5,I46*1/5,J46*1/5)</f>
         <v>0.28403192430000002</v>
       </c>
-      <c r="N46" s="66" t="s">
+      <c r="N46" s="71" t="s">
         <v>31</v>
       </c>
     </row>
@@ -4991,9 +5080,9 @@
       <c r="B47" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C47" s="68"/>
-      <c r="D47" s="64"/>
-      <c r="E47" s="64"/>
+      <c r="C47" s="64"/>
+      <c r="D47" s="65"/>
+      <c r="E47" s="65"/>
       <c r="F47" s="11">
         <v>2.90285495E-2</v>
       </c>
@@ -5021,7 +5110,7 @@
         <f>SUM(F47*1/5,G47*1/5,H47*1/5,I47*1/5,J47*1/5)</f>
         <v>0.35089340806000002</v>
       </c>
-      <c r="N47" s="66"/>
+      <c r="N47" s="71"/>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
@@ -5030,9 +5119,9 @@
       <c r="B48" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C48" s="68"/>
-      <c r="D48" s="64"/>
-      <c r="E48" s="64"/>
+      <c r="C48" s="64"/>
+      <c r="D48" s="65"/>
+      <c r="E48" s="65"/>
       <c r="F48" s="11">
         <v>1.9160760000000001E-4</v>
       </c>
@@ -5060,7 +5149,7 @@
         <f>SUM(F48*1/5,G48*1/5,H48*1/5,I48*1/5,J48*1/5)</f>
         <v>0.34178323869999999</v>
       </c>
-      <c r="N48" s="66"/>
+      <c r="N48" s="71"/>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
@@ -5069,13 +5158,13 @@
       <c r="B50" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C50" s="68" t="s">
+      <c r="C50" s="64" t="s">
         <v>52</v>
       </c>
-      <c r="D50" s="64" t="s">
+      <c r="D50" s="65" t="s">
         <v>39</v>
       </c>
-      <c r="E50" s="64" t="s">
+      <c r="E50" s="65" t="s">
         <v>29</v>
       </c>
       <c r="F50" s="11">
@@ -5113,9 +5202,9 @@
       <c r="B51" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C51" s="68"/>
-      <c r="D51" s="64"/>
-      <c r="E51" s="64"/>
+      <c r="C51" s="64"/>
+      <c r="D51" s="65"/>
+      <c r="E51" s="65"/>
       <c r="F51" s="11">
         <v>3.4489365999999999E-3</v>
       </c>
@@ -5151,9 +5240,9 @@
       <c r="B52" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C52" s="68"/>
-      <c r="D52" s="64"/>
-      <c r="E52" s="64"/>
+      <c r="C52" s="64"/>
+      <c r="D52" s="65"/>
+      <c r="E52" s="65"/>
       <c r="F52" s="62">
         <v>4.7901900000000002E-4</v>
       </c>
@@ -5183,12 +5272,12 @@
       </c>
     </row>
     <row r="55" spans="1:14" s="14" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="79" t="s">
+      <c r="A55" s="72" t="s">
         <v>59</v>
       </c>
-      <c r="B55" s="79"/>
-      <c r="C55" s="79"/>
-      <c r="D55" s="79"/>
+      <c r="B55" s="72"/>
+      <c r="C55" s="72"/>
+      <c r="D55" s="72"/>
       <c r="E55" s="15"/>
       <c r="F55" s="16">
         <f t="shared" ref="F55:M55" si="0">MAX(F2:F52)</f>
@@ -5225,12 +5314,12 @@
       <c r="N55" s="17"/>
     </row>
     <row r="56" spans="1:14" s="18" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="77" t="s">
+      <c r="A56" s="74" t="s">
         <v>60</v>
       </c>
-      <c r="B56" s="77"/>
-      <c r="C56" s="77"/>
-      <c r="D56" s="77"/>
+      <c r="B56" s="74"/>
+      <c r="C56" s="74"/>
+      <c r="D56" s="74"/>
       <c r="E56" s="19"/>
       <c r="F56" s="20">
         <f t="shared" ref="F56:M56" si="1">AVERAGE(F2:F52)</f>
@@ -5267,13 +5356,13 @@
       <c r="N56" s="21"/>
     </row>
     <row r="58" spans="1:14" s="22" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="74" t="s">
+      <c r="A58" s="77" t="s">
         <v>64</v>
       </c>
-      <c r="B58" s="74"/>
-      <c r="C58" s="74"/>
-      <c r="D58" s="74"/>
-      <c r="E58" s="74"/>
+      <c r="B58" s="77"/>
+      <c r="C58" s="77"/>
+      <c r="D58" s="77"/>
+      <c r="E58" s="77"/>
       <c r="F58" s="29">
         <f>SUM(F55*(1/3),  G55*(1/3), I55*(1/3))</f>
         <v>0.33744571563333331</v>
@@ -5288,13 +5377,13 @@
       <c r="N58" s="24"/>
     </row>
     <row r="59" spans="1:14" s="27" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="75" t="s">
+      <c r="A59" s="78" t="s">
         <v>65</v>
       </c>
-      <c r="B59" s="75"/>
-      <c r="C59" s="75"/>
-      <c r="D59" s="75"/>
-      <c r="E59" s="75"/>
+      <c r="B59" s="78"/>
+      <c r="C59" s="78"/>
+      <c r="D59" s="78"/>
+      <c r="E59" s="78"/>
       <c r="F59" s="28">
         <f>SUM(H55*(1/2),  J55*(1/2))</f>
         <v>0.67529401794999999</v>
@@ -5309,13 +5398,13 @@
       <c r="N59" s="26"/>
     </row>
     <row r="60" spans="1:14" s="33" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="76" t="s">
+      <c r="A60" s="79" t="s">
         <v>66</v>
       </c>
-      <c r="B60" s="76"/>
-      <c r="C60" s="76"/>
-      <c r="D60" s="76"/>
-      <c r="E60" s="76"/>
+      <c r="B60" s="79"/>
+      <c r="C60" s="79"/>
+      <c r="D60" s="79"/>
+      <c r="E60" s="79"/>
       <c r="F60" s="30">
         <f>SUM(F55*1/5, G55*1/5, H55*1/5, I55*1/5,J55*1/5)</f>
         <v>0.47258503656</v>
@@ -5330,12 +5419,12 @@
       <c r="N60" s="32"/>
     </row>
     <row r="62" spans="1:14" s="37" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="72" t="s">
+      <c r="A62" s="75" t="s">
         <v>83</v>
       </c>
-      <c r="B62" s="72"/>
-      <c r="C62" s="72"/>
-      <c r="D62" s="72"/>
+      <c r="B62" s="75"/>
+      <c r="C62" s="75"/>
+      <c r="D62" s="75"/>
       <c r="E62" s="34"/>
       <c r="F62" s="35"/>
       <c r="G62" s="35"/>
@@ -5348,12 +5437,12 @@
       <c r="N62" s="36"/>
     </row>
     <row r="63" spans="1:14" s="37" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A63" s="72" t="s">
+      <c r="A63" s="75" t="s">
         <v>84</v>
       </c>
-      <c r="B63" s="73"/>
-      <c r="C63" s="73"/>
-      <c r="D63" s="73"/>
+      <c r="B63" s="76"/>
+      <c r="C63" s="76"/>
+      <c r="D63" s="76"/>
       <c r="E63" s="38"/>
       <c r="F63" s="35"/>
       <c r="G63" s="35"/>
@@ -5366,12 +5455,12 @@
       <c r="N63" s="36"/>
     </row>
     <row r="64" spans="1:14" s="37" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="72" t="s">
+      <c r="A64" s="75" t="s">
         <v>85</v>
       </c>
-      <c r="B64" s="73"/>
-      <c r="C64" s="73"/>
-      <c r="D64" s="73"/>
+      <c r="B64" s="76"/>
+      <c r="C64" s="76"/>
+      <c r="D64" s="76"/>
       <c r="E64" s="38"/>
       <c r="F64" s="35"/>
       <c r="G64" s="35"/>
@@ -5385,37 +5474,12 @@
     </row>
   </sheetData>
   <mergeCells count="53">
-    <mergeCell ref="A55:D55"/>
-    <mergeCell ref="N42:N44"/>
-    <mergeCell ref="C46:C48"/>
-    <mergeCell ref="D46:D48"/>
-    <mergeCell ref="E46:E48"/>
-    <mergeCell ref="N46:N48"/>
-    <mergeCell ref="E50:E52"/>
-    <mergeCell ref="C36:C38"/>
-    <mergeCell ref="D36:D38"/>
-    <mergeCell ref="E36:E38"/>
-    <mergeCell ref="A40:D40"/>
-    <mergeCell ref="C42:C44"/>
-    <mergeCell ref="D42:D44"/>
-    <mergeCell ref="E42:E44"/>
-    <mergeCell ref="N12:N14"/>
-    <mergeCell ref="C20:C22"/>
-    <mergeCell ref="D20:D22"/>
-    <mergeCell ref="E20:E22"/>
-    <mergeCell ref="N20:N22"/>
-    <mergeCell ref="C16:C18"/>
-    <mergeCell ref="D16:D18"/>
-    <mergeCell ref="E16:E18"/>
-    <mergeCell ref="N16:N18"/>
-    <mergeCell ref="C2:C4"/>
-    <mergeCell ref="D2:D4"/>
-    <mergeCell ref="E2:E4"/>
-    <mergeCell ref="N2:N4"/>
-    <mergeCell ref="C6:C8"/>
-    <mergeCell ref="D6:D8"/>
-    <mergeCell ref="E6:E8"/>
-    <mergeCell ref="N6:N8"/>
+    <mergeCell ref="A63:D63"/>
+    <mergeCell ref="A64:D64"/>
+    <mergeCell ref="A58:E58"/>
+    <mergeCell ref="A59:E59"/>
+    <mergeCell ref="A60:E60"/>
+    <mergeCell ref="A62:D62"/>
     <mergeCell ref="A56:D56"/>
     <mergeCell ref="A10:D10"/>
     <mergeCell ref="C12:C14"/>
@@ -5432,12 +5496,37 @@
     <mergeCell ref="E32:E34"/>
     <mergeCell ref="C50:C52"/>
     <mergeCell ref="D50:D52"/>
-    <mergeCell ref="A63:D63"/>
-    <mergeCell ref="A64:D64"/>
-    <mergeCell ref="A58:E58"/>
-    <mergeCell ref="A59:E59"/>
-    <mergeCell ref="A60:E60"/>
-    <mergeCell ref="A62:D62"/>
+    <mergeCell ref="C2:C4"/>
+    <mergeCell ref="D2:D4"/>
+    <mergeCell ref="E2:E4"/>
+    <mergeCell ref="N2:N4"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="D6:D8"/>
+    <mergeCell ref="E6:E8"/>
+    <mergeCell ref="N6:N8"/>
+    <mergeCell ref="N12:N14"/>
+    <mergeCell ref="C20:C22"/>
+    <mergeCell ref="D20:D22"/>
+    <mergeCell ref="E20:E22"/>
+    <mergeCell ref="N20:N22"/>
+    <mergeCell ref="C16:C18"/>
+    <mergeCell ref="D16:D18"/>
+    <mergeCell ref="E16:E18"/>
+    <mergeCell ref="N16:N18"/>
+    <mergeCell ref="C36:C38"/>
+    <mergeCell ref="D36:D38"/>
+    <mergeCell ref="E36:E38"/>
+    <mergeCell ref="A40:D40"/>
+    <mergeCell ref="C42:C44"/>
+    <mergeCell ref="D42:D44"/>
+    <mergeCell ref="E42:E44"/>
+    <mergeCell ref="A55:D55"/>
+    <mergeCell ref="N42:N44"/>
+    <mergeCell ref="C46:C48"/>
+    <mergeCell ref="D46:D48"/>
+    <mergeCell ref="E46:E48"/>
+    <mergeCell ref="N46:N48"/>
+    <mergeCell ref="E50:E52"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5445,7 +5534,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84CDC51E-177F-BF40-BC8B-54510E0AFA97}">
-  <dimension ref="A1:N35"/>
+  <dimension ref="A1:N103"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="51.33203125" defaultRowHeight="21" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="28.1640625" style="1" customWidth="1"/>
@@ -5518,17 +5607,17 @@
       <c r="N2" s="9"/>
     </row>
     <row r="3" spans="1:14" s="47" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="77" t="s">
+      <c r="A3" s="74" t="s">
         <v>71</v>
       </c>
-      <c r="B3" s="77"/>
-      <c r="C3" s="77"/>
-      <c r="D3" s="77"/>
-      <c r="E3" s="77"/>
-      <c r="F3" s="77"/>
-      <c r="G3" s="77"/>
-      <c r="H3" s="77"/>
-      <c r="I3" s="77"/>
+      <c r="B3" s="74"/>
+      <c r="C3" s="74"/>
+      <c r="D3" s="74"/>
+      <c r="E3" s="74"/>
+      <c r="F3" s="74"/>
+      <c r="G3" s="74"/>
+      <c r="H3" s="74"/>
+      <c r="I3" s="74"/>
       <c r="J3" s="49"/>
       <c r="K3" s="56"/>
       <c r="L3" s="56"/>
@@ -5554,10 +5643,10 @@
       <c r="B5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="66" t="s">
+      <c r="C5" s="71" t="s">
         <v>67</v>
       </c>
-      <c r="D5" s="66" t="s">
+      <c r="D5" s="71" t="s">
         <v>68</v>
       </c>
       <c r="E5" s="11">
@@ -5595,8 +5684,8 @@
       <c r="B6" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="66"/>
-      <c r="D6" s="66"/>
+      <c r="C6" s="71"/>
+      <c r="D6" s="71"/>
       <c r="E6" s="11">
         <v>6.9727237799999994E-2</v>
       </c>
@@ -5632,8 +5721,8 @@
       <c r="B7" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="66"/>
-      <c r="D7" s="66"/>
+      <c r="C7" s="71"/>
+      <c r="D7" s="71"/>
       <c r="E7" s="11">
         <v>2.8812910000000001E-4</v>
       </c>
@@ -5669,10 +5758,10 @@
       <c r="B9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="66" t="s">
+      <c r="C9" s="71" t="s">
         <v>69</v>
       </c>
-      <c r="D9" s="66" t="s">
+      <c r="D9" s="71" t="s">
         <v>70</v>
       </c>
       <c r="E9" s="11">
@@ -5684,7 +5773,7 @@
       <c r="G9" s="11">
         <v>0.4692662313</v>
       </c>
-      <c r="H9" s="11">
+      <c r="H9" s="81">
         <v>0.89344463880000002</v>
       </c>
       <c r="I9" s="11">
@@ -5710,8 +5799,8 @@
       <c r="B10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="66"/>
-      <c r="D10" s="66"/>
+      <c r="C10" s="71"/>
+      <c r="D10" s="71"/>
       <c r="E10" s="11">
         <v>2.4010757000000001E-3</v>
       </c>
@@ -5747,8 +5836,8 @@
       <c r="B11" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C11" s="66"/>
-      <c r="D11" s="66"/>
+      <c r="C11" s="71"/>
+      <c r="D11" s="71"/>
       <c r="E11" s="11">
         <v>0</v>
       </c>
@@ -5784,23 +5873,38 @@
       <c r="B13" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C13" s="66" t="s">
+      <c r="C13" s="71" t="s">
         <v>74</v>
       </c>
-      <c r="D13" s="66" t="s">
+      <c r="D13" s="71" t="s">
         <v>81</v>
+      </c>
+      <c r="E13" s="11">
+        <v>2.40651965E-2</v>
+      </c>
+      <c r="F13" s="11">
+        <v>2.3010546000000001E-3</v>
+      </c>
+      <c r="G13" s="11">
+        <v>0.39271332689999999</v>
+      </c>
+      <c r="H13" s="11">
+        <v>0.50992464810000004</v>
+      </c>
+      <c r="I13" s="11">
+        <v>0.49790253379999999</v>
       </c>
       <c r="J13" s="11">
         <f>SUM(E13*1/3,F13*1/3,H13*1/3)</f>
-        <v>0</v>
+        <v>0.17876363306666671</v>
       </c>
       <c r="K13" s="11">
         <f>SUM(G13*1/2,I13*1/2)</f>
-        <v>0</v>
+        <v>0.44530793034999999</v>
       </c>
       <c r="L13" s="11">
         <f>SUM(E13*1/5,F13*1/5,G13*1/5,H13*1/5,I13*1/5)</f>
-        <v>0</v>
+        <v>0.28538135198000003</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
@@ -5810,19 +5914,34 @@
       <c r="B14" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C14" s="66"/>
-      <c r="D14" s="66"/>
+      <c r="C14" s="71"/>
+      <c r="D14" s="71"/>
+      <c r="E14" s="11">
+        <v>3.5474592999999999E-3</v>
+      </c>
+      <c r="F14" s="11">
+        <v>4.7938640000000002E-4</v>
+      </c>
+      <c r="G14" s="11">
+        <v>0.28053691279999998</v>
+      </c>
+      <c r="H14" s="11">
+        <v>0.50108990590000002</v>
+      </c>
+      <c r="I14" s="11">
+        <v>0.48514601400000001</v>
+      </c>
       <c r="J14" s="11">
         <f>SUM(E14*1/3,F14*1/3,H14*1/3)</f>
-        <v>0</v>
+        <v>0.16837225053333332</v>
       </c>
       <c r="K14" s="11">
         <f>SUM(G14*1/2,I14*1/2)</f>
-        <v>0</v>
+        <v>0.38284146340000003</v>
       </c>
       <c r="L14" s="11">
         <f>SUM(E14*1/5,F14*1/5,G14*1/5,H14*1/5,I14*1/5)</f>
-        <v>0</v>
+        <v>0.25415993568</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
@@ -5832,45 +5951,75 @@
       <c r="B15" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C15" s="66"/>
-      <c r="D15" s="66"/>
+      <c r="C15" s="71"/>
+      <c r="D15" s="71"/>
+      <c r="E15" s="11">
+        <v>3.8350910000000001E-4</v>
+      </c>
+      <c r="F15" s="11">
+        <v>1.5340365000000001E-3</v>
+      </c>
+      <c r="G15" s="11">
+        <v>0.75973154359999995</v>
+      </c>
+      <c r="H15" s="11">
+        <v>0.51676152419999999</v>
+      </c>
+      <c r="I15" s="11">
+        <v>0.50086111280000001</v>
+      </c>
       <c r="J15" s="11">
         <f>SUM(E15*1/3,F15*1/3,H15*1/3)</f>
-        <v>0</v>
+        <v>0.17289302326666667</v>
       </c>
       <c r="K15" s="11">
         <f>SUM(G15*1/2,I15*1/2)</f>
-        <v>0</v>
+        <v>0.63029632820000003</v>
       </c>
       <c r="L15" s="11">
         <f>SUM(E15*1/5,F15*1/5,G15*1/5,H15*1/5,I15*1/5)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A17" s="1" t="s">
+        <v>0.35585434523999993</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" s="83" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="83" t="s">
         <v>2</v>
       </c>
-      <c r="B17" s="1" t="s">
+      <c r="B17" s="83" t="s">
         <v>5</v>
       </c>
-      <c r="C17" s="66" t="s">
+      <c r="C17" s="71" t="s">
         <v>80</v>
       </c>
-      <c r="D17" s="66" t="s">
+      <c r="D17" s="71" t="s">
         <v>79</v>
       </c>
-      <c r="J17" s="11">
+      <c r="E17" s="84">
+        <v>3.5474592999999999E-3</v>
+      </c>
+      <c r="F17" s="84">
+        <v>2.3969319E-3</v>
+      </c>
+      <c r="G17" s="84">
+        <v>0.68648130389999995</v>
+      </c>
+      <c r="H17" s="84">
+        <v>0.73279006160000004</v>
+      </c>
+      <c r="I17" s="85">
+        <v>0.70502058919999999</v>
+      </c>
+      <c r="J17" s="84">
         <f>SUM(E17*1/3,F17*1/3,H17*1/3)</f>
-        <v>0</v>
-      </c>
-      <c r="K17" s="11">
+        <v>0.2462448176</v>
+      </c>
+      <c r="K17" s="84">
         <f>SUM(G17*1/2,I17*1/2)</f>
-        <v>0</v>
-      </c>
-      <c r="L17" s="11">
+        <v>0.69575094655000003</v>
+      </c>
+      <c r="L17" s="84">
         <f>SUM(E17*1/5,F17*1/5,G17*1/5,H17*1/5,I17*1/5)</f>
-        <v>0</v>
+        <v>0.42604726918000002</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.2">
@@ -5880,19 +6029,34 @@
       <c r="B18" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C18" s="66"/>
-      <c r="D18" s="66"/>
+      <c r="C18" s="71"/>
+      <c r="D18" s="71"/>
+      <c r="E18" s="11">
+        <v>3.0680729000000001E-3</v>
+      </c>
+      <c r="F18" s="11">
+        <v>2.5886864999999999E-3</v>
+      </c>
+      <c r="G18" s="11">
+        <v>0.51505273250000005</v>
+      </c>
+      <c r="H18" s="11">
+        <v>0.60190347580000003</v>
+      </c>
+      <c r="I18" s="11">
+        <v>0.52140253719999996</v>
+      </c>
       <c r="J18" s="11">
         <f>SUM(E18*1/3,F18*1/3,H18*1/3)</f>
-        <v>0</v>
+        <v>0.20252007840000003</v>
       </c>
       <c r="K18" s="11">
         <f>SUM(G18*1/2,I18*1/2)</f>
-        <v>0</v>
+        <v>0.51822763485000001</v>
       </c>
       <c r="L18" s="11">
         <f>SUM(E18*1/5,F18*1/5,G18*1/5,H18*1/5,I18*1/5)</f>
-        <v>0</v>
+        <v>0.32880310098000004</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.2">
@@ -5902,19 +6066,34 @@
       <c r="B19" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C19" s="66"/>
-      <c r="D19" s="66"/>
+      <c r="C19" s="71"/>
+      <c r="D19" s="71"/>
+      <c r="E19" s="11">
+        <v>2.876318E-4</v>
+      </c>
+      <c r="F19" s="11">
+        <v>1.0546500999999999E-3</v>
+      </c>
+      <c r="G19" s="11">
+        <v>3.79674017E-2</v>
+      </c>
+      <c r="H19" s="11">
+        <v>0.48511697329999998</v>
+      </c>
+      <c r="I19" s="11">
+        <v>0.43752120239999998</v>
+      </c>
       <c r="J19" s="11">
         <f>SUM(E19*1/3,F19*1/3,H19*1/3)</f>
-        <v>0</v>
+        <v>0.16215308506666665</v>
       </c>
       <c r="K19" s="11">
         <f>SUM(G19*1/2,I19*1/2)</f>
-        <v>0</v>
+        <v>0.23774430204999999</v>
       </c>
       <c r="L19" s="11">
         <f>SUM(E19*1/5,F19*1/5,G19*1/5,H19*1/5,I19*1/5)</f>
-        <v>0</v>
+        <v>0.19238957186</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.2">
@@ -5927,23 +6106,38 @@
       <c r="B21" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C21" s="66" t="s">
+      <c r="C21" s="71" t="s">
         <v>72</v>
       </c>
-      <c r="D21" s="66" t="s">
+      <c r="D21" s="71" t="s">
         <v>73</v>
+      </c>
+      <c r="E21" s="11">
+        <v>8.2742090099999999E-2</v>
+      </c>
+      <c r="F21" s="11">
+        <v>1.6107382600000001E-2</v>
+      </c>
+      <c r="G21" s="11">
+        <v>0.4293384468</v>
+      </c>
+      <c r="H21" s="11">
+        <v>0.86991481869999998</v>
+      </c>
+      <c r="I21" s="11">
+        <v>0.40505853110000001</v>
       </c>
       <c r="J21" s="11">
         <f>SUM(E21*1/3,F21*1/3,H21*1/3)</f>
-        <v>0</v>
+        <v>0.32292143046666666</v>
       </c>
       <c r="K21" s="11">
         <f>SUM(G21*1/2,I21*1/2)</f>
-        <v>0</v>
+        <v>0.41719848895</v>
       </c>
       <c r="L21" s="11">
         <f>SUM(E21*1/5,F21*1/5,G21*1/5,H21*1/5,I21*1/5)</f>
-        <v>0</v>
+        <v>0.36063225385999997</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.2">
@@ -5953,19 +6147,34 @@
       <c r="B22" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C22" s="66"/>
-      <c r="D22" s="66"/>
+      <c r="C22" s="71"/>
+      <c r="D22" s="71"/>
+      <c r="E22" s="11">
+        <v>3.1639501E-3</v>
+      </c>
+      <c r="F22" s="11">
+        <v>1.4381591999999999E-3</v>
+      </c>
+      <c r="G22" s="11">
+        <v>0.26596356659999998</v>
+      </c>
+      <c r="H22" s="11">
+        <v>0.48894575070000001</v>
+      </c>
+      <c r="I22" s="11">
+        <v>0.47475261759999998</v>
+      </c>
       <c r="J22" s="11">
         <f>SUM(E22*1/3,F22*1/3,H22*1/3)</f>
-        <v>0</v>
+        <v>0.16451595333333333</v>
       </c>
       <c r="K22" s="11">
         <f>SUM(G22*1/2,I22*1/2)</f>
-        <v>0</v>
+        <v>0.37035809209999998</v>
       </c>
       <c r="L22" s="11">
         <f>SUM(E22*1/5,F22*1/5,G22*1/5,H22*1/5,I22*1/5)</f>
-        <v>0</v>
+        <v>0.24685280883999999</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.2">
@@ -5975,19 +6184,34 @@
       <c r="B23" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C23" s="66"/>
-      <c r="D23" s="66"/>
+      <c r="C23" s="71"/>
+      <c r="D23" s="71"/>
+      <c r="E23" s="11">
+        <v>1.917546E-4</v>
+      </c>
+      <c r="F23" s="11">
+        <v>4.5062319999999998E-3</v>
+      </c>
+      <c r="G23" s="81">
+        <v>0.79884947269999995</v>
+      </c>
+      <c r="H23" s="11">
+        <v>0.53313908909999996</v>
+      </c>
+      <c r="I23" s="11">
+        <v>0.50595402629999997</v>
+      </c>
       <c r="J23" s="11">
         <f>SUM(E23*1/3,F23*1/3,H23*1/3)</f>
-        <v>0</v>
+        <v>0.17927902523333333</v>
       </c>
       <c r="K23" s="11">
         <f>SUM(G23*1/2,I23*1/2)</f>
-        <v>0</v>
+        <v>0.65240174949999996</v>
       </c>
       <c r="L23" s="11">
         <f>SUM(E23*1/5,F23*1/5,G23*1/5,H23*1/5,I23*1/5)</f>
-        <v>0</v>
+        <v>0.36852811494000004</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.2">
@@ -5997,23 +6221,38 @@
       <c r="B25" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C25" s="66" t="s">
+      <c r="C25" s="71" t="s">
         <v>77</v>
       </c>
-      <c r="D25" s="66" t="s">
+      <c r="D25" s="71" t="s">
         <v>75</v>
+      </c>
+      <c r="E25" s="11">
+        <v>4.0172579100000001E-2</v>
+      </c>
+      <c r="F25" s="11">
+        <v>3.6433364999999998E-3</v>
+      </c>
+      <c r="G25" s="11">
+        <v>0.31735378720000001</v>
+      </c>
+      <c r="H25" s="11">
+        <v>0.66111389819999999</v>
+      </c>
+      <c r="I25" s="11">
+        <v>0.4401939782</v>
       </c>
       <c r="J25" s="11">
         <f>SUM(E25*1/3,F25*1/3,H25*1/3)</f>
-        <v>0</v>
+        <v>0.2349766046</v>
       </c>
       <c r="K25" s="11">
         <f>SUM(G25*1/2,I25*1/2)</f>
-        <v>0</v>
+        <v>0.37877388270000001</v>
       </c>
       <c r="L25" s="11">
         <f>SUM(E25*1/5,F25*1/5,G25*1/5,H25*1/5,I25*1/5)</f>
-        <v>0</v>
+        <v>0.29249551584</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.2">
@@ -6023,19 +6262,34 @@
       <c r="B26" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C26" s="66"/>
-      <c r="D26" s="66"/>
+      <c r="C26" s="71"/>
+      <c r="D26" s="71"/>
+      <c r="E26" s="11">
+        <v>1.70661553E-2</v>
+      </c>
+      <c r="F26" s="11">
+        <v>2.1093001000000002E-3</v>
+      </c>
+      <c r="G26" s="11">
+        <v>0.37142857140000002</v>
+      </c>
+      <c r="H26" s="11">
+        <v>0.52517104670000003</v>
+      </c>
+      <c r="I26" s="11">
+        <v>0.51303041270000005</v>
+      </c>
       <c r="J26" s="11">
         <f>SUM(E26*1/3,F26*1/3,H26*1/3)</f>
-        <v>0</v>
+        <v>0.18144883403333334</v>
       </c>
       <c r="K26" s="11">
         <f>SUM(G26*1/2,I26*1/2)</f>
-        <v>0</v>
+        <v>0.44222949205000006</v>
       </c>
       <c r="L26" s="11">
         <f>SUM(E26*1/5,F26*1/5,G26*1/5,H26*1/5,I26*1/5)</f>
-        <v>0</v>
+        <v>0.28576109723999998</v>
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.2">
@@ -6045,19 +6299,34 @@
       <c r="B27" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C27" s="66"/>
-      <c r="D27" s="66"/>
+      <c r="C27" s="71"/>
+      <c r="D27" s="71"/>
+      <c r="E27" s="11">
+        <v>6.7114089999999996E-4</v>
+      </c>
+      <c r="F27" s="11">
+        <v>6.7114089999999996E-4</v>
+      </c>
+      <c r="G27" s="11">
+        <v>0.36260786189999999</v>
+      </c>
+      <c r="H27" s="11">
+        <v>0.50055614439999996</v>
+      </c>
+      <c r="I27" s="11">
+        <v>0.47861351050000001</v>
+      </c>
       <c r="J27" s="11">
         <f>SUM(E27*1/3,F27*1/3,H27*1/3)</f>
-        <v>0</v>
+        <v>0.16729947539999998</v>
       </c>
       <c r="K27" s="11">
         <f>SUM(G27*1/2,I27*1/2)</f>
-        <v>0</v>
+        <v>0.42061068619999997</v>
       </c>
       <c r="L27" s="11">
         <f>SUM(E27*1/5,F27*1/5,G27*1/5,H27*1/5,I27*1/5)</f>
-        <v>0</v>
+        <v>0.26862395971999997</v>
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.2">
@@ -6067,23 +6336,38 @@
       <c r="B29" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C29" s="66" t="s">
+      <c r="C29" s="71" t="s">
         <v>78</v>
       </c>
-      <c r="D29" s="66" t="s">
+      <c r="D29" s="71" t="s">
         <v>76</v>
+      </c>
+      <c r="E29" s="11">
+        <v>7.3250239699999997E-2</v>
+      </c>
+      <c r="F29" s="11">
+        <v>1.36145733E-2</v>
+      </c>
+      <c r="G29" s="11">
+        <v>0.104506232</v>
+      </c>
+      <c r="H29" s="11">
+        <v>0.59471253369999999</v>
+      </c>
+      <c r="I29" s="11">
+        <v>0.36557713930000002</v>
       </c>
       <c r="J29" s="11">
         <f>SUM(E29*1/3,F29*1/3,H29*1/3)</f>
-        <v>0</v>
+        <v>0.22719244890000001</v>
       </c>
       <c r="K29" s="11">
         <f>SUM(G29*1/2,I29*1/2)</f>
-        <v>0</v>
+        <v>0.23504168565</v>
       </c>
       <c r="L29" s="11">
         <f>SUM(E29*1/5,F29*1/5,G29*1/5,H29*1/5,I29*1/5)</f>
-        <v>0</v>
+        <v>0.23033214360000001</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.2">
@@ -6093,19 +6377,34 @@
       <c r="B30" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C30" s="66"/>
-      <c r="D30" s="66"/>
+      <c r="C30" s="71"/>
+      <c r="D30" s="71"/>
+      <c r="E30" s="11">
+        <v>7.2866731000000001E-3</v>
+      </c>
+      <c r="F30" s="11">
+        <v>2.4928092E-3</v>
+      </c>
+      <c r="G30" s="11">
+        <v>0.40325982739999999</v>
+      </c>
+      <c r="H30" s="11">
+        <v>0.50791210740000003</v>
+      </c>
+      <c r="I30" s="11">
+        <v>0.49345779690000002</v>
+      </c>
       <c r="J30" s="11">
         <f>SUM(E30*1/3,F30*1/3,H30*1/3)</f>
-        <v>0</v>
+        <v>0.17256386323333334</v>
       </c>
       <c r="K30" s="11">
         <f>SUM(G30*1/2,I30*1/2)</f>
-        <v>0</v>
+        <v>0.44835881215000001</v>
       </c>
       <c r="L30" s="11">
         <f>SUM(E30*1/5,F30*1/5,G30*1/5,H30*1/5,I30*1/5)</f>
-        <v>0</v>
+        <v>0.28288184280000001</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.2">
@@ -6115,39 +6414,54 @@
       <c r="B31" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C31" s="66"/>
-      <c r="D31" s="66"/>
+      <c r="C31" s="71"/>
+      <c r="D31" s="71"/>
+      <c r="E31" s="11">
+        <v>0</v>
+      </c>
+      <c r="F31" s="11">
+        <v>1.6299137E-3</v>
+      </c>
+      <c r="G31" s="11">
+        <v>0.25790987539999999</v>
+      </c>
+      <c r="H31" s="11">
+        <v>0.48580648799999998</v>
+      </c>
+      <c r="I31" s="11">
+        <v>0.48836600340000003</v>
+      </c>
       <c r="J31" s="11">
         <f>SUM(E31*1/3,F31*1/3,H31*1/3)</f>
-        <v>0</v>
+        <v>0.16247880056666666</v>
       </c>
       <c r="K31" s="11">
         <f>SUM(G31*1/2,I31*1/2)</f>
-        <v>0</v>
+        <v>0.37313793940000001</v>
       </c>
       <c r="L31" s="11">
         <f>SUM(E31*1/5,F31*1/5,G31*1/5,H31*1/5,I31*1/5)</f>
-        <v>0</v>
+        <v>0.24674245610000001</v>
       </c>
     </row>
     <row r="34" spans="1:14" s="14" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="79" t="s">
+      <c r="A34" s="72" t="s">
         <v>59</v>
       </c>
-      <c r="B34" s="79"/>
-      <c r="C34" s="79"/>
-      <c r="D34" s="79"/>
+      <c r="B34" s="72"/>
+      <c r="C34" s="72"/>
+      <c r="D34" s="72"/>
       <c r="E34" s="16">
         <f t="shared" ref="E34:L34" si="0">MAX(E4:E32)</f>
-        <v>6.9727237799999994E-2</v>
+        <v>8.2742090099999999E-2</v>
       </c>
       <c r="F34" s="16">
         <f t="shared" si="0"/>
-        <v>9.9884747999999992E-3</v>
+        <v>1.6107382600000001E-2</v>
       </c>
       <c r="G34" s="16">
         <f t="shared" si="0"/>
-        <v>0.4692662313</v>
+        <v>0.79884947269999995</v>
       </c>
       <c r="H34" s="16">
         <f t="shared" si="0"/>
@@ -6155,67 +6469,1922 @@
       </c>
       <c r="I34" s="16">
         <f t="shared" si="0"/>
-        <v>0.4837691543</v>
+        <v>0.70502058919999999</v>
       </c>
       <c r="J34" s="16">
         <f t="shared" si="0"/>
-        <v>0.31818292593333336</v>
+        <v>0.32292143046666666</v>
       </c>
       <c r="K34" s="16">
         <f t="shared" si="0"/>
-        <v>0.43074060685000004</v>
+        <v>0.69575094655000003</v>
       </c>
       <c r="L34" s="16">
         <f t="shared" si="0"/>
-        <v>0.36320184355999996</v>
+        <v>0.42604726918000002</v>
       </c>
       <c r="M34" s="16"/>
       <c r="N34" s="17"/>
     </row>
     <row r="35" spans="1:14" s="52" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="74" t="s">
+      <c r="A35" s="77" t="s">
         <v>60</v>
       </c>
-      <c r="B35" s="74"/>
-      <c r="C35" s="74"/>
-      <c r="D35" s="74"/>
+      <c r="B35" s="77"/>
+      <c r="C35" s="77"/>
+      <c r="D35" s="77"/>
       <c r="E35" s="29">
         <f t="shared" ref="E35:L35" si="1">AVERAGE(E5:E32)</f>
-        <v>3.0173517733333332E-2</v>
+        <v>2.0975477057142849E-2</v>
       </c>
       <c r="F35" s="29">
         <f t="shared" si="1"/>
-        <v>5.4104238333333339E-3</v>
+        <v>4.2395303095238103E-3</v>
       </c>
       <c r="G35" s="29">
         <f t="shared" si="1"/>
-        <v>0.28502369061666666</v>
+        <v>0.36637347650000002</v>
       </c>
       <c r="H35" s="29">
         <f t="shared" si="1"/>
-        <v>0.68663101311666674</v>
+        <v>0.60164974021428563</v>
       </c>
       <c r="I35" s="29">
         <f t="shared" si="1"/>
-        <v>0.43126544105000003</v>
+        <v>0.47145003103333344</v>
       </c>
       <c r="J35" s="29">
         <f t="shared" si="1"/>
-        <v>6.878237663650795E-2</v>
+        <v>0.20895491586031745</v>
       </c>
       <c r="K35" s="29">
         <f t="shared" si="1"/>
-        <v>0.10232701880952383</v>
+        <v>0.41891175376666662</v>
       </c>
       <c r="L35" s="29">
         <f t="shared" si="1"/>
-        <v>8.2200233505714301E-2</v>
+        <v>0.29293765102285718</v>
       </c>
       <c r="M35" s="29"/>
       <c r="N35" s="58"/>
     </row>
+    <row r="37" spans="1:14" s="47" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="74" t="s">
+        <v>86</v>
+      </c>
+      <c r="B37" s="74"/>
+      <c r="C37" s="74"/>
+      <c r="D37" s="74"/>
+      <c r="E37" s="74"/>
+      <c r="F37" s="74"/>
+      <c r="G37" s="74"/>
+      <c r="H37" s="74"/>
+      <c r="I37" s="74"/>
+      <c r="J37" s="49"/>
+      <c r="K37" s="56"/>
+      <c r="L37" s="56"/>
+    </row>
+    <row r="38" spans="1:14" s="48" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="8"/>
+      <c r="B38" s="8"/>
+      <c r="C38" s="8"/>
+      <c r="D38" s="51"/>
+      <c r="E38" s="54"/>
+      <c r="F38" s="54"/>
+      <c r="G38" s="54"/>
+      <c r="H38" s="54"/>
+      <c r="I38" s="54"/>
+      <c r="J38" s="57"/>
+      <c r="K38" s="57"/>
+      <c r="L38" s="57"/>
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A39" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C39" s="71" t="s">
+        <v>87</v>
+      </c>
+      <c r="D39" s="71" t="s">
+        <v>68</v>
+      </c>
+      <c r="E39" s="11">
+        <v>3.2885905999999999E-2</v>
+      </c>
+      <c r="F39" s="11">
+        <v>6.2320229999999997E-3</v>
+      </c>
+      <c r="G39" s="11">
+        <v>0.50393096839999996</v>
+      </c>
+      <c r="H39" s="11">
+        <v>0.77736178700000003</v>
+      </c>
+      <c r="I39" s="11">
+        <v>0.43943819899999997</v>
+      </c>
+      <c r="J39" s="11">
+        <f>SUM(E39*1/3,F39*1/3,H39*1/3)</f>
+        <v>0.27215990533333334</v>
+      </c>
+      <c r="K39" s="11">
+        <f>SUM(G39*1/2,I39*1/2)</f>
+        <v>0.47168458369999999</v>
+      </c>
+      <c r="L39" s="11">
+        <f>SUM(E39*1/5,F39*1/5,G39*1/5,H39*1/5,I39*1/5)</f>
+        <v>0.35196977668000007</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A40" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C40" s="71"/>
+      <c r="D40" s="71"/>
+      <c r="E40" s="11">
+        <v>1.42857143E-2</v>
+      </c>
+      <c r="F40" s="11">
+        <v>6.5196548E-3</v>
+      </c>
+      <c r="G40" s="11">
+        <v>0.41303930970000002</v>
+      </c>
+      <c r="H40" s="11">
+        <v>0.6898911875</v>
+      </c>
+      <c r="I40" s="11">
+        <v>0.46205572309999998</v>
+      </c>
+      <c r="J40" s="11">
+        <f>SUM(E40*1/3,F40*1/3,H40*1/3)</f>
+        <v>0.23689885219999998</v>
+      </c>
+      <c r="K40" s="11">
+        <f>SUM(G40*1/2,I40*1/2)</f>
+        <v>0.4375475164</v>
+      </c>
+      <c r="L40" s="11">
+        <f>SUM(E40*1/5,F40*1/5,G40*1/5,H40*1/5,I40*1/5)</f>
+        <v>0.31715831787999998</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A41" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C41" s="71"/>
+      <c r="D41" s="71"/>
+      <c r="E41" s="11">
+        <v>3.8350910000000001E-4</v>
+      </c>
+      <c r="F41" s="11">
+        <v>1.4381591999999999E-3</v>
+      </c>
+      <c r="G41" s="11">
+        <v>9.7794822599999998E-2</v>
+      </c>
+      <c r="H41" s="11">
+        <v>0.45026455949999999</v>
+      </c>
+      <c r="I41" s="11">
+        <v>0.46414172419999999</v>
+      </c>
+      <c r="J41" s="11">
+        <f>SUM(E41*1/3,F41*1/3,H41*1/3)</f>
+        <v>0.15069540926666666</v>
+      </c>
+      <c r="K41" s="11">
+        <f>SUM(G41*1/2,I41*1/2)</f>
+        <v>0.28096827339999997</v>
+      </c>
+      <c r="L41" s="11">
+        <f>SUM(E41*1/5,F41*1/5,G41*1/5,H41*1/5,I41*1/5)</f>
+        <v>0.20280455491999999</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="E42" s="80"/>
+      <c r="F42" s="80"/>
+      <c r="G42" s="80"/>
+      <c r="H42" s="80"/>
+      <c r="I42" s="80"/>
+    </row>
+    <row r="43" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A43" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C43" s="71" t="s">
+        <v>88</v>
+      </c>
+      <c r="D43" s="71" t="s">
+        <v>70</v>
+      </c>
+      <c r="E43" s="11">
+        <v>4.0364333699999998E-2</v>
+      </c>
+      <c r="F43" s="11">
+        <v>3.3557047E-3</v>
+      </c>
+      <c r="G43" s="11">
+        <v>0.32425695110000002</v>
+      </c>
+      <c r="H43" s="11">
+        <v>0.70605234920000004</v>
+      </c>
+      <c r="I43" s="11">
+        <v>0.43611723260000002</v>
+      </c>
+      <c r="J43" s="11">
+        <f>SUM(E43*1/3,F43*1/3,H43*1/3)</f>
+        <v>0.24992412920000001</v>
+      </c>
+      <c r="K43" s="11">
+        <f>SUM(G43*1/2,I43*1/2)</f>
+        <v>0.38018709184999999</v>
+      </c>
+      <c r="L43" s="11">
+        <f>SUM(E43*1/5,F43*1/5,G43*1/5,H43*1/5,I43*1/5)</f>
+        <v>0.30202931426000001</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A44" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44" s="71"/>
+      <c r="D44" s="71"/>
+      <c r="E44" s="11">
+        <v>2.8475551299999999E-2</v>
+      </c>
+      <c r="F44" s="11">
+        <v>1.0546500999999999E-3</v>
+      </c>
+      <c r="G44" s="11">
+        <v>0.5637583893</v>
+      </c>
+      <c r="H44" s="54">
+        <v>0.85501700719999996</v>
+      </c>
+      <c r="I44" s="11">
+        <v>0.43641871859999998</v>
+      </c>
+      <c r="J44" s="54">
+        <f>SUM(E44*1/3,F44*1/3,H44*1/3)</f>
+        <v>0.29484906953333329</v>
+      </c>
+      <c r="K44" s="11">
+        <f>SUM(G44*1/2,I44*1/2)</f>
+        <v>0.50008855394999996</v>
+      </c>
+      <c r="L44" s="11">
+        <f>SUM(E44*1/5,F44*1/5,G44*1/5,H44*1/5,I44*1/5)</f>
+        <v>0.37694486329999999</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A45" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C45" s="71"/>
+      <c r="D45" s="71"/>
+      <c r="E45" s="11">
+        <v>1.917546E-4</v>
+      </c>
+      <c r="F45" s="11">
+        <v>2.1093001000000002E-3</v>
+      </c>
+      <c r="G45" s="11">
+        <v>0.81073825499999996</v>
+      </c>
+      <c r="H45" s="11">
+        <v>0.50746971929999996</v>
+      </c>
+      <c r="I45" s="11">
+        <v>0.48343524840000002</v>
+      </c>
+      <c r="J45" s="11">
+        <f>SUM(E45*1/3,F45*1/3,H45*1/3)</f>
+        <v>0.16992359133333332</v>
+      </c>
+      <c r="K45" s="11">
+        <f>SUM(G45*1/2,I45*1/2)</f>
+        <v>0.64708675169999996</v>
+      </c>
+      <c r="L45" s="11">
+        <f>SUM(E45*1/5,F45*1/5,G45*1/5,H45*1/5,I45*1/5)</f>
+        <v>0.36078885547999995</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="E46" s="80"/>
+      <c r="F46" s="80"/>
+      <c r="G46" s="80"/>
+      <c r="H46" s="80"/>
+      <c r="I46" s="80"/>
+    </row>
+    <row r="47" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A47" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C47" s="71" t="s">
+        <v>89</v>
+      </c>
+      <c r="D47" s="71" t="s">
+        <v>81</v>
+      </c>
+      <c r="E47" s="80">
+        <v>2.1572387299999999E-2</v>
+      </c>
+      <c r="F47" s="80">
+        <v>1.725791E-3</v>
+      </c>
+      <c r="G47" s="80">
+        <v>0.21380632790000001</v>
+      </c>
+      <c r="H47" s="80">
+        <v>0.4996014688</v>
+      </c>
+      <c r="I47" s="80">
+        <v>0.49415116780000001</v>
+      </c>
+      <c r="J47" s="11">
+        <f>SUM(E47*1/3,F47*1/3,H47*1/3)</f>
+        <v>0.17429988236666666</v>
+      </c>
+      <c r="K47" s="11">
+        <f>SUM(G47*1/2,I47*1/2)</f>
+        <v>0.35397874785</v>
+      </c>
+      <c r="L47" s="11">
+        <f>SUM(E47*1/5,F47*1/5,G47*1/5,H47*1/5,I47*1/5)</f>
+        <v>0.24617142856000002</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A48" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C48" s="71"/>
+      <c r="D48" s="71"/>
+      <c r="E48" s="80">
+        <v>6.3279002999999997E-3</v>
+      </c>
+      <c r="F48" s="80">
+        <v>3.5474592999999999E-3</v>
+      </c>
+      <c r="G48" s="80">
+        <v>0.35973154359999998</v>
+      </c>
+      <c r="H48" s="80">
+        <v>0.50229272930000002</v>
+      </c>
+      <c r="I48" s="80">
+        <v>0.48684262210000001</v>
+      </c>
+      <c r="J48" s="11">
+        <f>SUM(E48*1/3,F48*1/3,H48*1/3)</f>
+        <v>0.1707226963</v>
+      </c>
+      <c r="K48" s="11">
+        <f>SUM(G48*1/2,I48*1/2)</f>
+        <v>0.42328708285</v>
+      </c>
+      <c r="L48" s="11">
+        <f>SUM(E48*1/5,F48*1/5,G48*1/5,H48*1/5,I48*1/5)</f>
+        <v>0.27174845092</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A49" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C49" s="71"/>
+      <c r="D49" s="71"/>
+      <c r="E49" s="80">
+        <v>2.876318E-4</v>
+      </c>
+      <c r="F49" s="80">
+        <v>1.725791E-3</v>
+      </c>
+      <c r="G49" s="80">
+        <v>0.67919463089999998</v>
+      </c>
+      <c r="H49" s="80">
+        <v>0.50784208630000005</v>
+      </c>
+      <c r="I49" s="80">
+        <v>0.4972537568</v>
+      </c>
+      <c r="J49" s="11">
+        <f>SUM(E49*1/3,F49*1/3,H49*1/3)</f>
+        <v>0.16995183636666669</v>
+      </c>
+      <c r="K49" s="11">
+        <f>SUM(G49*1/2,I49*1/2)</f>
+        <v>0.58822419385000002</v>
+      </c>
+      <c r="L49" s="11">
+        <f>SUM(E49*1/5,F49*1/5,G49*1/5,H49*1/5,I49*1/5)</f>
+        <v>0.33726077935999998</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="E50" s="80"/>
+      <c r="F50" s="80"/>
+      <c r="G50" s="80"/>
+      <c r="H50" s="80"/>
+      <c r="I50" s="80"/>
+    </row>
+    <row r="51" spans="1:12" s="83" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A51" s="83" t="s">
+        <v>2</v>
+      </c>
+      <c r="B51" s="83" t="s">
+        <v>5</v>
+      </c>
+      <c r="C51" s="71" t="s">
+        <v>90</v>
+      </c>
+      <c r="D51" s="71" t="s">
+        <v>79</v>
+      </c>
+      <c r="E51" s="84">
+        <v>1.23681687E-2</v>
+      </c>
+      <c r="F51" s="84">
+        <v>2.6845637999999999E-3</v>
+      </c>
+      <c r="G51" s="84">
+        <v>0.70795781400000002</v>
+      </c>
+      <c r="H51" s="84">
+        <v>0.71314872139999996</v>
+      </c>
+      <c r="I51" s="85">
+        <v>0.64805542540000005</v>
+      </c>
+      <c r="J51" s="84">
+        <f>SUM(E51*1/3,F51*1/3,H51*1/3)</f>
+        <v>0.24273381796666665</v>
+      </c>
+      <c r="K51" s="85">
+        <f>SUM(G51*1/2,I51*1/2)</f>
+        <v>0.67800661970000009</v>
+      </c>
+      <c r="L51" s="85">
+        <f>SUM(E51*1/5,F51*1/5,G51*1/5,H51*1/5,I51*1/5)</f>
+        <v>0.41684293866000005</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A52" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C52" s="71"/>
+      <c r="D52" s="71"/>
+      <c r="E52" s="80">
+        <v>2.0134227999999998E-3</v>
+      </c>
+      <c r="F52" s="80">
+        <v>7.6701829999999995E-4</v>
+      </c>
+      <c r="G52" s="80">
+        <v>0.27823585810000001</v>
+      </c>
+      <c r="H52" s="80">
+        <v>0.50316636969999995</v>
+      </c>
+      <c r="I52" s="80">
+        <v>0.47961395620000002</v>
+      </c>
+      <c r="J52" s="11">
+        <f>SUM(E52*1/3,F52*1/3,H52*1/3)</f>
+        <v>0.16864893693333333</v>
+      </c>
+      <c r="K52" s="11">
+        <f>SUM(G52*1/2,I52*1/2)</f>
+        <v>0.37892490715000005</v>
+      </c>
+      <c r="L52" s="11">
+        <f>SUM(E52*1/5,F52*1/5,G52*1/5,H52*1/5,I52*1/5)</f>
+        <v>0.25275932501999998</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A53" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C53" s="71"/>
+      <c r="D53" s="71"/>
+      <c r="E53" s="80">
+        <v>1.917546E-4</v>
+      </c>
+      <c r="F53" s="80">
+        <v>1.1505273E-3</v>
+      </c>
+      <c r="G53" s="80">
+        <v>2.9146692200000001E-2</v>
+      </c>
+      <c r="H53" s="80">
+        <v>0.37034050689999998</v>
+      </c>
+      <c r="I53" s="80">
+        <v>0.31939047450000002</v>
+      </c>
+      <c r="J53" s="11">
+        <f>SUM(E53*1/3,F53*1/3,H53*1/3)</f>
+        <v>0.12389426293333332</v>
+      </c>
+      <c r="K53" s="11">
+        <f>SUM(G53*1/2,I53*1/2)</f>
+        <v>0.17426858335000001</v>
+      </c>
+      <c r="L53" s="11">
+        <f>SUM(E53*1/5,F53*1/5,G53*1/5,H53*1/5,I53*1/5)</f>
+        <v>0.14404399109999999</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="C54" s="50"/>
+      <c r="E54" s="80"/>
+      <c r="F54" s="80"/>
+      <c r="G54" s="80"/>
+      <c r="H54" s="80"/>
+      <c r="I54" s="80"/>
+    </row>
+    <row r="55" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A55" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C55" s="71" t="s">
+        <v>91</v>
+      </c>
+      <c r="D55" s="71" t="s">
+        <v>73</v>
+      </c>
+      <c r="E55" s="80">
+        <v>9.0220517700000002E-2</v>
+      </c>
+      <c r="F55" s="80">
+        <v>1.2655800599999999E-2</v>
+      </c>
+      <c r="G55" s="80">
+        <v>0.24256951099999999</v>
+      </c>
+      <c r="H55" s="80">
+        <v>0.74882737740000005</v>
+      </c>
+      <c r="I55" s="80">
+        <v>0.41265332459999998</v>
+      </c>
+      <c r="J55" s="11">
+        <f>SUM(E55*1/3,F55*1/3,H55*1/3)</f>
+        <v>0.28390123190000005</v>
+      </c>
+      <c r="K55" s="11">
+        <f>SUM(G55*1/2,I55*1/2)</f>
+        <v>0.32761141779999997</v>
+      </c>
+      <c r="L55" s="11">
+        <f>SUM(E55*1/5,F55*1/5,G55*1/5,H55*1/5,I55*1/5)</f>
+        <v>0.30138530626000004</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A56" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C56" s="71"/>
+      <c r="D56" s="71"/>
+      <c r="E56" s="80">
+        <v>1.9558964500000001E-2</v>
+      </c>
+      <c r="F56" s="80">
+        <v>3.7392138000000002E-3</v>
+      </c>
+      <c r="G56" s="80">
+        <v>0.42703739210000002</v>
+      </c>
+      <c r="H56" s="80">
+        <v>0.54984708800000004</v>
+      </c>
+      <c r="I56" s="80">
+        <v>0.54163438399999997</v>
+      </c>
+      <c r="J56" s="11">
+        <f>SUM(E56*1/3,F56*1/3,H56*1/3)</f>
+        <v>0.1910484221</v>
+      </c>
+      <c r="K56" s="11">
+        <f>SUM(G56*1/2,I56*1/2)</f>
+        <v>0.48433588805</v>
+      </c>
+      <c r="L56" s="11">
+        <f>SUM(E56*1/5,F56*1/5,G56*1/5,H56*1/5,I56*1/5)</f>
+        <v>0.30836340847999999</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A57" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C57" s="71"/>
+      <c r="D57" s="71"/>
+      <c r="E57" s="80">
+        <v>0</v>
+      </c>
+      <c r="F57" s="80">
+        <v>2.8763183999999998E-3</v>
+      </c>
+      <c r="G57" s="81">
+        <v>0.81802492810000005</v>
+      </c>
+      <c r="H57" s="80">
+        <v>0.52913612850000002</v>
+      </c>
+      <c r="I57" s="80">
+        <v>0.49455716719999998</v>
+      </c>
+      <c r="J57" s="11">
+        <f>SUM(E57*1/3,F57*1/3,H57*1/3)</f>
+        <v>0.17733748230000002</v>
+      </c>
+      <c r="K57" s="11">
+        <f>SUM(G57*1/2,I57*1/2)</f>
+        <v>0.65629104765000001</v>
+      </c>
+      <c r="L57" s="11">
+        <f>SUM(E57*1/5,F57*1/5,G57*1/5,H57*1/5,I57*1/5)</f>
+        <v>0.36891890843999997</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="E58" s="80"/>
+      <c r="F58" s="80"/>
+      <c r="G58" s="80"/>
+      <c r="H58" s="80"/>
+      <c r="I58" s="80"/>
+    </row>
+    <row r="59" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A59" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C59" s="71" t="s">
+        <v>92</v>
+      </c>
+      <c r="D59" s="71" t="s">
+        <v>75</v>
+      </c>
+      <c r="E59" s="80">
+        <v>2.47363375E-2</v>
+      </c>
+      <c r="F59" s="80">
+        <v>4.3144773999999999E-3</v>
+      </c>
+      <c r="G59" s="80">
+        <v>0.60268456380000002</v>
+      </c>
+      <c r="H59" s="80">
+        <v>0.72139929479999998</v>
+      </c>
+      <c r="I59" s="80">
+        <v>0.61438299269999996</v>
+      </c>
+      <c r="J59" s="11">
+        <f>SUM(E59*1/3,F59*1/3,H59*1/3)</f>
+        <v>0.25015003656666668</v>
+      </c>
+      <c r="K59" s="11">
+        <f>SUM(G59*1/2,I59*1/2)</f>
+        <v>0.60853377824999999</v>
+      </c>
+      <c r="L59" s="11">
+        <f>SUM(E59*1/5,F59*1/5,G59*1/5,H59*1/5,I59*1/5)</f>
+        <v>0.39350353323999998</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A60" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C60" s="71"/>
+      <c r="D60" s="71"/>
+      <c r="E60" s="80">
+        <v>4.4103546999999998E-3</v>
+      </c>
+      <c r="F60" s="80">
+        <v>1.1505274000000001E-3</v>
+      </c>
+      <c r="G60" s="80">
+        <v>0.34458293379999999</v>
+      </c>
+      <c r="H60" s="80">
+        <v>0.49885476839999998</v>
+      </c>
+      <c r="I60" s="80">
+        <v>0.50106482159999999</v>
+      </c>
+      <c r="J60" s="11">
+        <f>SUM(E60*1/3,F60*1/3,H60*1/3)</f>
+        <v>0.16813855016666665</v>
+      </c>
+      <c r="K60" s="11">
+        <f>SUM(G60*1/2,I60*1/2)</f>
+        <v>0.42282387769999996</v>
+      </c>
+      <c r="L60" s="11">
+        <f>SUM(E60*1/5,F60*1/5,G60*1/5,H60*1/5,I60*1/5)</f>
+        <v>0.27001268117999999</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A61" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C61" s="71"/>
+      <c r="D61" s="71"/>
+      <c r="E61" s="80">
+        <v>2.8763183000000002E-3</v>
+      </c>
+      <c r="F61" s="80">
+        <v>2.0134228999999998E-3</v>
+      </c>
+      <c r="G61" s="80">
+        <v>0.51831255990000002</v>
+      </c>
+      <c r="H61" s="80">
+        <v>0.62305881009999997</v>
+      </c>
+      <c r="I61" s="80">
+        <v>0.5466724329</v>
+      </c>
+      <c r="J61" s="11">
+        <f>SUM(E61*1/3,F61*1/3,H61*1/3)</f>
+        <v>0.20931618376666664</v>
+      </c>
+      <c r="K61" s="11">
+        <f>SUM(G61*1/2,I61*1/2)</f>
+        <v>0.53249249639999996</v>
+      </c>
+      <c r="L61" s="11">
+        <f>SUM(E61*1/5,F61*1/5,G61*1/5,H61*1/5,I61*1/5)</f>
+        <v>0.33858670881999997</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="E62" s="80"/>
+      <c r="F62" s="80"/>
+      <c r="G62" s="80"/>
+      <c r="H62" s="80"/>
+      <c r="I62" s="80"/>
+    </row>
+    <row r="63" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A63" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C63" s="71" t="s">
+        <v>93</v>
+      </c>
+      <c r="D63" s="71" t="s">
+        <v>76</v>
+      </c>
+      <c r="E63" s="80">
+        <v>5.1006711400000002E-2</v>
+      </c>
+      <c r="F63" s="80">
+        <v>1.75455417E-2</v>
+      </c>
+      <c r="G63" s="80">
+        <v>0.14726749759999999</v>
+      </c>
+      <c r="H63" s="80">
+        <v>0.56786657309999999</v>
+      </c>
+      <c r="I63" s="80">
+        <v>0.33699644699999998</v>
+      </c>
+      <c r="J63" s="11">
+        <f>SUM(E63*1/3,F63*1/3,H63*1/3)</f>
+        <v>0.21213960873333335</v>
+      </c>
+      <c r="K63" s="11">
+        <f>SUM(G63*1/2,I63*1/2)</f>
+        <v>0.2421319723</v>
+      </c>
+      <c r="L63" s="11">
+        <f>SUM(E63*1/5,F63*1/5,G63*1/5,H63*1/5,I63*1/5)</f>
+        <v>0.22413655416</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A64" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C64" s="71"/>
+      <c r="D64" s="71"/>
+      <c r="E64" s="80">
+        <v>8.6289548999999993E-3</v>
+      </c>
+      <c r="F64" s="80">
+        <v>2.3010547000000001E-3</v>
+      </c>
+      <c r="G64" s="80">
+        <v>0.37871524449999999</v>
+      </c>
+      <c r="H64" s="80">
+        <v>0.5041079812</v>
+      </c>
+      <c r="I64" s="80">
+        <v>0.48737746469999998</v>
+      </c>
+      <c r="J64" s="11">
+        <f>SUM(E64*1/3,F64*1/3,H64*1/3)</f>
+        <v>0.17167933026666668</v>
+      </c>
+      <c r="K64" s="11">
+        <f>SUM(G64*1/2,I64*1/2)</f>
+        <v>0.43304635459999996</v>
+      </c>
+      <c r="L64" s="11">
+        <f>SUM(E64*1/5,F64*1/5,G64*1/5,H64*1/5,I64*1/5)</f>
+        <v>0.27622614000000001</v>
+      </c>
+    </row>
+    <row r="65" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A65" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C65" s="71"/>
+      <c r="D65" s="71"/>
+      <c r="E65" s="80">
+        <v>1.9175455000000001E-3</v>
+      </c>
+      <c r="F65" s="80">
+        <v>4.9856184E-3</v>
+      </c>
+      <c r="G65" s="80">
+        <v>0.2151486098</v>
+      </c>
+      <c r="H65" s="80">
+        <v>0.57976032990000004</v>
+      </c>
+      <c r="I65" s="80">
+        <v>0.46813920380000001</v>
+      </c>
+      <c r="J65" s="11">
+        <f>SUM(E65*1/3,F65*1/3,H65*1/3)</f>
+        <v>0.19555449793333335</v>
+      </c>
+      <c r="K65" s="11">
+        <f>SUM(G65*1/2,I65*1/2)</f>
+        <v>0.34164390680000001</v>
+      </c>
+      <c r="L65" s="11">
+        <f>SUM(E65*1/5,F65*1/5,G65*1/5,H65*1/5,I65*1/5)</f>
+        <v>0.25399026148000003</v>
+      </c>
+    </row>
+    <row r="68" spans="1:14" s="14" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A68" s="72" t="s">
+        <v>59</v>
+      </c>
+      <c r="B68" s="72"/>
+      <c r="C68" s="72"/>
+      <c r="D68" s="72"/>
+      <c r="E68" s="16">
+        <f t="shared" ref="E68:L68" si="2">MAX(E38:E66)</f>
+        <v>9.0220517700000002E-2</v>
+      </c>
+      <c r="F68" s="16">
+        <f t="shared" si="2"/>
+        <v>1.75455417E-2</v>
+      </c>
+      <c r="G68" s="16">
+        <f t="shared" si="2"/>
+        <v>0.81802492810000005</v>
+      </c>
+      <c r="H68" s="16">
+        <f t="shared" si="2"/>
+        <v>0.85501700719999996</v>
+      </c>
+      <c r="I68" s="16">
+        <f t="shared" si="2"/>
+        <v>0.64805542540000005</v>
+      </c>
+      <c r="J68" s="16">
+        <f>MAX(J38:J66)</f>
+        <v>0.29484906953333329</v>
+      </c>
+      <c r="K68" s="16">
+        <f t="shared" si="2"/>
+        <v>0.67800661970000009</v>
+      </c>
+      <c r="L68" s="16">
+        <f t="shared" si="2"/>
+        <v>0.41684293866000005</v>
+      </c>
+      <c r="M68" s="16"/>
+      <c r="N68" s="17"/>
+    </row>
+    <row r="69" spans="1:14" s="52" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A69" s="77" t="s">
+        <v>60</v>
+      </c>
+      <c r="B69" s="77"/>
+      <c r="C69" s="77"/>
+      <c r="D69" s="77"/>
+      <c r="E69" s="29">
+        <f t="shared" ref="E69:L69" si="3">AVERAGE(E39:E66)</f>
+        <v>1.7271606619047621E-2</v>
+      </c>
+      <c r="F69" s="29">
+        <f t="shared" si="3"/>
+        <v>3.9948865666666663E-3</v>
+      </c>
+      <c r="G69" s="29">
+        <f t="shared" si="3"/>
+        <v>0.41313975254285717</v>
+      </c>
+      <c r="H69" s="29">
+        <f t="shared" si="3"/>
+        <v>0.5907288973095236</v>
+      </c>
+      <c r="I69" s="29">
+        <f t="shared" si="3"/>
+        <v>0.47859011843809524</v>
+      </c>
+      <c r="J69" s="29">
+        <f t="shared" si="3"/>
+        <v>0.20399846349841269</v>
+      </c>
+      <c r="K69" s="29">
+        <f t="shared" si="3"/>
+        <v>0.44586493549047612</v>
+      </c>
+      <c r="L69" s="29">
+        <f t="shared" si="3"/>
+        <v>0.30074505229523812</v>
+      </c>
+      <c r="M69" s="29"/>
+      <c r="N69" s="58"/>
+    </row>
+    <row r="71" spans="1:14" s="47" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A71" s="74" t="s">
+        <v>94</v>
+      </c>
+      <c r="B71" s="74"/>
+      <c r="C71" s="74"/>
+      <c r="D71" s="74"/>
+      <c r="E71" s="74"/>
+      <c r="F71" s="74"/>
+      <c r="G71" s="74"/>
+      <c r="H71" s="74"/>
+      <c r="I71" s="74"/>
+      <c r="J71" s="49"/>
+      <c r="K71" s="56"/>
+      <c r="L71" s="56"/>
+    </row>
+    <row r="72" spans="1:14" s="48" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A72" s="8"/>
+      <c r="B72" s="8"/>
+      <c r="C72" s="8"/>
+      <c r="D72" s="51"/>
+      <c r="E72" s="54"/>
+      <c r="F72" s="54"/>
+      <c r="G72" s="54"/>
+      <c r="H72" s="54"/>
+      <c r="I72" s="54"/>
+      <c r="J72" s="57"/>
+      <c r="K72" s="57"/>
+      <c r="L72" s="57"/>
+    </row>
+    <row r="73" spans="1:14" s="82" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A73" s="82" t="s">
+        <v>2</v>
+      </c>
+      <c r="B73" s="82" t="s">
+        <v>5</v>
+      </c>
+      <c r="C73" s="86" t="s">
+        <v>95</v>
+      </c>
+      <c r="D73" s="86" t="s">
+        <v>68</v>
+      </c>
+      <c r="E73" s="11">
+        <v>3.1423644399999999E-2</v>
+      </c>
+      <c r="F73" s="11">
+        <v>4.5027783000000004E-3</v>
+      </c>
+      <c r="G73" s="11">
+        <v>0.31423644379999999</v>
+      </c>
+      <c r="H73" s="11">
+        <v>0.87912838900000001</v>
+      </c>
+      <c r="I73" s="11">
+        <v>0.37861748220000002</v>
+      </c>
+      <c r="J73" s="80">
+        <f>SUM(E73*1/3,F73*1/3,H73*1/3)</f>
+        <v>0.30501827056666669</v>
+      </c>
+      <c r="K73" s="80">
+        <f>SUM(G73*1/2,I73*1/2)</f>
+        <v>0.34642696299999998</v>
+      </c>
+      <c r="L73" s="80">
+        <f>SUM(E73*1/5,F73*1/5,G73*1/5,H73*1/5,I73*1/5)</f>
+        <v>0.32158174754000002</v>
+      </c>
+    </row>
+    <row r="74" spans="1:14" s="82" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A74" s="82" t="s">
+        <v>3</v>
+      </c>
+      <c r="B74" s="82" t="s">
+        <v>6</v>
+      </c>
+      <c r="C74" s="86"/>
+      <c r="D74" s="86"/>
+      <c r="E74" s="11">
+        <v>8.8139489999999997E-3</v>
+      </c>
+      <c r="F74" s="11">
+        <v>2.3950948999999998E-3</v>
+      </c>
+      <c r="G74" s="11">
+        <v>0.36865299870000001</v>
+      </c>
+      <c r="H74" s="11">
+        <v>0.73505614159999999</v>
+      </c>
+      <c r="I74" s="11">
+        <v>0.438803202</v>
+      </c>
+      <c r="J74" s="80">
+        <f>SUM(E74*1/3,F74*1/3,H74*1/3)</f>
+        <v>0.24875506183333332</v>
+      </c>
+      <c r="K74" s="80">
+        <f>SUM(G74*1/2,I74*1/2)</f>
+        <v>0.40372810035000001</v>
+      </c>
+      <c r="L74" s="80">
+        <f>SUM(E74*1/5,F74*1/5,G74*1/5,H74*1/5,I74*1/5)</f>
+        <v>0.31074427723999998</v>
+      </c>
+    </row>
+    <row r="75" spans="1:14" s="82" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A75" s="82" t="s">
+        <v>4</v>
+      </c>
+      <c r="B75" s="82" t="s">
+        <v>7</v>
+      </c>
+      <c r="C75" s="86"/>
+      <c r="D75" s="86"/>
+      <c r="E75" s="11">
+        <v>1.9160760000000001E-4</v>
+      </c>
+      <c r="F75" s="11">
+        <v>1.9160759E-3</v>
+      </c>
+      <c r="G75" s="11">
+        <v>4.4261352699999999E-2</v>
+      </c>
+      <c r="H75" s="11">
+        <v>0.4812790361</v>
+      </c>
+      <c r="I75" s="11">
+        <v>0.47962761110000002</v>
+      </c>
+      <c r="J75" s="80">
+        <f>SUM(E75*1/3,F75*1/3,H75*1/3)</f>
+        <v>0.16112890653333334</v>
+      </c>
+      <c r="K75" s="80">
+        <f>SUM(G75*1/2,I75*1/2)</f>
+        <v>0.26194448190000003</v>
+      </c>
+      <c r="L75" s="80">
+        <f>SUM(E75*1/5,F75*1/5,G75*1/5,H75*1/5,I75*1/5)</f>
+        <v>0.20145513668000001</v>
+      </c>
+    </row>
+    <row r="76" spans="1:14" s="82" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C76" s="87"/>
+      <c r="D76" s="87"/>
+      <c r="E76" s="80"/>
+      <c r="F76" s="80"/>
+      <c r="G76" s="80"/>
+      <c r="H76" s="80"/>
+      <c r="I76" s="80"/>
+      <c r="J76" s="80"/>
+      <c r="K76" s="80"/>
+      <c r="L76" s="80"/>
+    </row>
+    <row r="77" spans="1:14" s="82" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A77" s="82" t="s">
+        <v>2</v>
+      </c>
+      <c r="B77" s="82" t="s">
+        <v>5</v>
+      </c>
+      <c r="C77" s="86" t="s">
+        <v>96</v>
+      </c>
+      <c r="D77" s="86" t="s">
+        <v>70</v>
+      </c>
+      <c r="E77" s="11">
+        <v>2.7399884999999999E-2</v>
+      </c>
+      <c r="F77" s="11">
+        <v>2.0693619399999998E-2</v>
+      </c>
+      <c r="G77" s="11">
+        <v>0.62962253310000005</v>
+      </c>
+      <c r="H77" s="11">
+        <v>0.85414416559999995</v>
+      </c>
+      <c r="I77" s="11">
+        <v>0.45041272119999998</v>
+      </c>
+      <c r="J77" s="80">
+        <f>SUM(E77*1/3,F77*1/3,H77*1/3)</f>
+        <v>0.30074588999999996</v>
+      </c>
+      <c r="K77" s="80">
+        <f>SUM(G77*1/2,I77*1/2)</f>
+        <v>0.54001762715000001</v>
+      </c>
+      <c r="L77" s="80">
+        <f>SUM(E77*1/5,F77*1/5,G77*1/5,H77*1/5,I77*1/5)</f>
+        <v>0.39645458486000001</v>
+      </c>
+    </row>
+    <row r="78" spans="1:14" s="82" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A78" s="82" t="s">
+        <v>3</v>
+      </c>
+      <c r="B78" s="82" t="s">
+        <v>6</v>
+      </c>
+      <c r="C78" s="86"/>
+      <c r="D78" s="86"/>
+      <c r="E78" s="11">
+        <v>3.4489365999999999E-3</v>
+      </c>
+      <c r="F78" s="11">
+        <v>2.77831E-3</v>
+      </c>
+      <c r="G78" s="11">
+        <v>0.28319601459999999</v>
+      </c>
+      <c r="H78" s="11">
+        <v>0.55856684919999999</v>
+      </c>
+      <c r="I78" s="11">
+        <v>0.48412258870000002</v>
+      </c>
+      <c r="J78" s="80">
+        <f>SUM(E78*1/3,F78*1/3,H78*1/3)</f>
+        <v>0.1882646986</v>
+      </c>
+      <c r="K78" s="80">
+        <f>SUM(G78*1/2,I78*1/2)</f>
+        <v>0.38365930165000001</v>
+      </c>
+      <c r="L78" s="80">
+        <f>SUM(E78*1/5,F78*1/5,G78*1/5,H78*1/5,I78*1/5)</f>
+        <v>0.26642253981999997</v>
+      </c>
+    </row>
+    <row r="79" spans="1:14" s="82" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A79" s="82" t="s">
+        <v>4</v>
+      </c>
+      <c r="B79" s="82" t="s">
+        <v>7</v>
+      </c>
+      <c r="C79" s="86"/>
+      <c r="D79" s="86"/>
+      <c r="E79" s="62">
+        <v>4.7901900000000002E-4</v>
+      </c>
+      <c r="F79" s="11">
+        <v>9.5803800000000003E-4</v>
+      </c>
+      <c r="G79" s="11">
+        <v>0.1588426902</v>
+      </c>
+      <c r="H79" s="11">
+        <v>0.51150557910000005</v>
+      </c>
+      <c r="I79" s="11">
+        <v>0.47634846359999999</v>
+      </c>
+      <c r="J79" s="80">
+        <f>SUM(E79*1/3,F79*1/3,H79*1/3)</f>
+        <v>0.17098087870000001</v>
+      </c>
+      <c r="K79" s="80">
+        <f>SUM(G79*1/2,I79*1/2)</f>
+        <v>0.31759557690000001</v>
+      </c>
+      <c r="L79" s="80">
+        <f>SUM(E79*1/5,F79*1/5,G79*1/5,H79*1/5,I79*1/5)</f>
+        <v>0.22962675798000001</v>
+      </c>
+    </row>
+    <row r="80" spans="1:14" s="82" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C80" s="87"/>
+      <c r="D80" s="87"/>
+      <c r="E80" s="80"/>
+      <c r="F80" s="80"/>
+      <c r="G80" s="80"/>
+      <c r="H80" s="80"/>
+      <c r="I80" s="80"/>
+      <c r="J80" s="80"/>
+      <c r="K80" s="80"/>
+      <c r="L80" s="80"/>
+    </row>
+    <row r="81" spans="1:12" s="82" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A81" s="82" t="s">
+        <v>2</v>
+      </c>
+      <c r="B81" s="82" t="s">
+        <v>5</v>
+      </c>
+      <c r="C81" s="86" t="s">
+        <v>97</v>
+      </c>
+      <c r="D81" s="86" t="s">
+        <v>81</v>
+      </c>
+      <c r="E81" s="80"/>
+      <c r="F81" s="80"/>
+      <c r="G81" s="80"/>
+      <c r="H81" s="80"/>
+      <c r="I81" s="80"/>
+      <c r="J81" s="80">
+        <f>SUM(E81*1/3,F81*1/3,H81*1/3)</f>
+        <v>0</v>
+      </c>
+      <c r="K81" s="80">
+        <f>SUM(G81*1/2,I81*1/2)</f>
+        <v>0</v>
+      </c>
+      <c r="L81" s="80">
+        <f>SUM(E81*1/5,F81*1/5,G81*1/5,H81*1/5,I81*1/5)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:12" s="82" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A82" s="82" t="s">
+        <v>3</v>
+      </c>
+      <c r="B82" s="82" t="s">
+        <v>6</v>
+      </c>
+      <c r="C82" s="86"/>
+      <c r="D82" s="86"/>
+      <c r="E82" s="80"/>
+      <c r="F82" s="80"/>
+      <c r="G82" s="80"/>
+      <c r="H82" s="80"/>
+      <c r="I82" s="80"/>
+      <c r="J82" s="80">
+        <f>SUM(E82*1/3,F82*1/3,H82*1/3)</f>
+        <v>0</v>
+      </c>
+      <c r="K82" s="80">
+        <f>SUM(G82*1/2,I82*1/2)</f>
+        <v>0</v>
+      </c>
+      <c r="L82" s="80">
+        <f>SUM(E82*1/5,F82*1/5,G82*1/5,H82*1/5,I82*1/5)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:12" s="82" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A83" s="82" t="s">
+        <v>4</v>
+      </c>
+      <c r="B83" s="82" t="s">
+        <v>7</v>
+      </c>
+      <c r="C83" s="86"/>
+      <c r="D83" s="86"/>
+      <c r="E83" s="80"/>
+      <c r="F83" s="80"/>
+      <c r="G83" s="80"/>
+      <c r="H83" s="80"/>
+      <c r="I83" s="80"/>
+      <c r="J83" s="80">
+        <f>SUM(E83*1/3,F83*1/3,H83*1/3)</f>
+        <v>0</v>
+      </c>
+      <c r="K83" s="80">
+        <f>SUM(G83*1/2,I83*1/2)</f>
+        <v>0</v>
+      </c>
+      <c r="L83" s="80">
+        <f>SUM(E83*1/5,F83*1/5,G83*1/5,H83*1/5,I83*1/5)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:12" s="82" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C84" s="87"/>
+      <c r="D84" s="87"/>
+      <c r="E84" s="80"/>
+      <c r="F84" s="80"/>
+      <c r="G84" s="80"/>
+      <c r="H84" s="80"/>
+      <c r="I84" s="80"/>
+      <c r="J84" s="80"/>
+      <c r="K84" s="80"/>
+      <c r="L84" s="80"/>
+    </row>
+    <row r="85" spans="1:12" s="82" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A85" s="82" t="s">
+        <v>2</v>
+      </c>
+      <c r="B85" s="82" t="s">
+        <v>5</v>
+      </c>
+      <c r="C85" s="86" t="s">
+        <v>98</v>
+      </c>
+      <c r="D85" s="86" t="s">
+        <v>79</v>
+      </c>
+      <c r="E85" s="80"/>
+      <c r="F85" s="80"/>
+      <c r="G85" s="80"/>
+      <c r="H85" s="80"/>
+      <c r="I85" s="80"/>
+      <c r="J85" s="80">
+        <f>SUM(E85*1/3,F85*1/3,H85*1/3)</f>
+        <v>0</v>
+      </c>
+      <c r="K85" s="80">
+        <f>SUM(G85*1/2,I85*1/2)</f>
+        <v>0</v>
+      </c>
+      <c r="L85" s="80">
+        <f>SUM(E85*1/5,F85*1/5,G85*1/5,H85*1/5,I85*1/5)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:12" s="82" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A86" s="82" t="s">
+        <v>3</v>
+      </c>
+      <c r="B86" s="82" t="s">
+        <v>6</v>
+      </c>
+      <c r="C86" s="86"/>
+      <c r="D86" s="86"/>
+      <c r="E86" s="80"/>
+      <c r="F86" s="80"/>
+      <c r="G86" s="80"/>
+      <c r="H86" s="80"/>
+      <c r="I86" s="80"/>
+      <c r="J86" s="80">
+        <f>SUM(E86*1/3,F86*1/3,H86*1/3)</f>
+        <v>0</v>
+      </c>
+      <c r="K86" s="80">
+        <f>SUM(G86*1/2,I86*1/2)</f>
+        <v>0</v>
+      </c>
+      <c r="L86" s="80">
+        <f>SUM(E86*1/5,F86*1/5,G86*1/5,H86*1/5,I86*1/5)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:12" s="82" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A87" s="82" t="s">
+        <v>4</v>
+      </c>
+      <c r="B87" s="82" t="s">
+        <v>7</v>
+      </c>
+      <c r="C87" s="86"/>
+      <c r="D87" s="86"/>
+      <c r="E87" s="80"/>
+      <c r="F87" s="80"/>
+      <c r="G87" s="80"/>
+      <c r="H87" s="80"/>
+      <c r="I87" s="80"/>
+      <c r="J87" s="80">
+        <f>SUM(E87*1/3,F87*1/3,H87*1/3)</f>
+        <v>0</v>
+      </c>
+      <c r="K87" s="80">
+        <f>SUM(G87*1/2,I87*1/2)</f>
+        <v>0</v>
+      </c>
+      <c r="L87" s="80">
+        <f>SUM(E87*1/5,F87*1/5,G87*1/5,H87*1/5,I87*1/5)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:12" s="82" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C88" s="88"/>
+      <c r="D88" s="87"/>
+      <c r="E88" s="80"/>
+      <c r="F88" s="80"/>
+      <c r="G88" s="80"/>
+      <c r="H88" s="80"/>
+      <c r="I88" s="80"/>
+      <c r="J88" s="80"/>
+      <c r="K88" s="80"/>
+      <c r="L88" s="80"/>
+    </row>
+    <row r="89" spans="1:12" s="82" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A89" s="82" t="s">
+        <v>2</v>
+      </c>
+      <c r="B89" s="82" t="s">
+        <v>5</v>
+      </c>
+      <c r="C89" s="86" t="s">
+        <v>99</v>
+      </c>
+      <c r="D89" s="86" t="s">
+        <v>73</v>
+      </c>
+      <c r="E89" s="80"/>
+      <c r="F89" s="80"/>
+      <c r="G89" s="80"/>
+      <c r="H89" s="80"/>
+      <c r="I89" s="80"/>
+      <c r="J89" s="80">
+        <f>SUM(E89*1/3,F89*1/3,H89*1/3)</f>
+        <v>0</v>
+      </c>
+      <c r="K89" s="80">
+        <f>SUM(G89*1/2,I89*1/2)</f>
+        <v>0</v>
+      </c>
+      <c r="L89" s="80">
+        <f>SUM(E89*1/5,F89*1/5,G89*1/5,H89*1/5,I89*1/5)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:12" s="82" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A90" s="82" t="s">
+        <v>3</v>
+      </c>
+      <c r="B90" s="82" t="s">
+        <v>6</v>
+      </c>
+      <c r="C90" s="86"/>
+      <c r="D90" s="86"/>
+      <c r="E90" s="80"/>
+      <c r="F90" s="80"/>
+      <c r="G90" s="80"/>
+      <c r="H90" s="80"/>
+      <c r="I90" s="80"/>
+      <c r="J90" s="80">
+        <f>SUM(E90*1/3,F90*1/3,H90*1/3)</f>
+        <v>0</v>
+      </c>
+      <c r="K90" s="80">
+        <f>SUM(G90*1/2,I90*1/2)</f>
+        <v>0</v>
+      </c>
+      <c r="L90" s="80">
+        <f>SUM(E90*1/5,F90*1/5,G90*1/5,H90*1/5,I90*1/5)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:12" s="82" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A91" s="82" t="s">
+        <v>4</v>
+      </c>
+      <c r="B91" s="82" t="s">
+        <v>7</v>
+      </c>
+      <c r="C91" s="86"/>
+      <c r="D91" s="86"/>
+      <c r="E91" s="80"/>
+      <c r="F91" s="80"/>
+      <c r="G91" s="80"/>
+      <c r="H91" s="80"/>
+      <c r="I91" s="80"/>
+      <c r="J91" s="80">
+        <f>SUM(E91*1/3,F91*1/3,H91*1/3)</f>
+        <v>0</v>
+      </c>
+      <c r="K91" s="80">
+        <f>SUM(G91*1/2,I91*1/2)</f>
+        <v>0</v>
+      </c>
+      <c r="L91" s="80">
+        <f>SUM(E91*1/5,F91*1/5,G91*1/5,H91*1/5,I91*1/5)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:12" s="82" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C92" s="87"/>
+      <c r="D92" s="87"/>
+      <c r="E92" s="80"/>
+      <c r="F92" s="80"/>
+      <c r="G92" s="80"/>
+      <c r="H92" s="80"/>
+      <c r="I92" s="80"/>
+      <c r="J92" s="80"/>
+      <c r="K92" s="80"/>
+      <c r="L92" s="80"/>
+    </row>
+    <row r="93" spans="1:12" s="82" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A93" s="82" t="s">
+        <v>2</v>
+      </c>
+      <c r="B93" s="82" t="s">
+        <v>5</v>
+      </c>
+      <c r="C93" s="86" t="s">
+        <v>100</v>
+      </c>
+      <c r="D93" s="86" t="s">
+        <v>75</v>
+      </c>
+      <c r="E93" s="80"/>
+      <c r="F93" s="80"/>
+      <c r="G93" s="80"/>
+      <c r="H93" s="80"/>
+      <c r="I93" s="80"/>
+      <c r="J93" s="80">
+        <f>SUM(E93*1/3,F93*1/3,H93*1/3)</f>
+        <v>0</v>
+      </c>
+      <c r="K93" s="80">
+        <f>SUM(G93*1/2,I93*1/2)</f>
+        <v>0</v>
+      </c>
+      <c r="L93" s="80">
+        <f>SUM(E93*1/5,F93*1/5,G93*1/5,H93*1/5,I93*1/5)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:12" s="82" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A94" s="82" t="s">
+        <v>3</v>
+      </c>
+      <c r="B94" s="82" t="s">
+        <v>6</v>
+      </c>
+      <c r="C94" s="86"/>
+      <c r="D94" s="86"/>
+      <c r="E94" s="80"/>
+      <c r="F94" s="80"/>
+      <c r="G94" s="80"/>
+      <c r="H94" s="80"/>
+      <c r="I94" s="80"/>
+      <c r="J94" s="80">
+        <f>SUM(E94*1/3,F94*1/3,H94*1/3)</f>
+        <v>0</v>
+      </c>
+      <c r="K94" s="80">
+        <f>SUM(G94*1/2,I94*1/2)</f>
+        <v>0</v>
+      </c>
+      <c r="L94" s="80">
+        <f>SUM(E94*1/5,F94*1/5,G94*1/5,H94*1/5,I94*1/5)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:12" s="82" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A95" s="82" t="s">
+        <v>4</v>
+      </c>
+      <c r="B95" s="82" t="s">
+        <v>7</v>
+      </c>
+      <c r="C95" s="86"/>
+      <c r="D95" s="86"/>
+      <c r="E95" s="80"/>
+      <c r="F95" s="80"/>
+      <c r="G95" s="80"/>
+      <c r="H95" s="80"/>
+      <c r="I95" s="80"/>
+      <c r="J95" s="80">
+        <f>SUM(E95*1/3,F95*1/3,H95*1/3)</f>
+        <v>0</v>
+      </c>
+      <c r="K95" s="80">
+        <f>SUM(G95*1/2,I95*1/2)</f>
+        <v>0</v>
+      </c>
+      <c r="L95" s="80">
+        <f>SUM(E95*1/5,F95*1/5,G95*1/5,H95*1/5,I95*1/5)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:12" s="82" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C96" s="87"/>
+      <c r="D96" s="87"/>
+      <c r="E96" s="80"/>
+      <c r="F96" s="80"/>
+      <c r="G96" s="80"/>
+      <c r="H96" s="80"/>
+      <c r="I96" s="80"/>
+      <c r="J96" s="80"/>
+      <c r="K96" s="80"/>
+      <c r="L96" s="80"/>
+    </row>
+    <row r="97" spans="1:14" s="82" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A97" s="82" t="s">
+        <v>2</v>
+      </c>
+      <c r="B97" s="82" t="s">
+        <v>5</v>
+      </c>
+      <c r="C97" s="86" t="s">
+        <v>101</v>
+      </c>
+      <c r="D97" s="86" t="s">
+        <v>76</v>
+      </c>
+      <c r="E97" s="80"/>
+      <c r="F97" s="80"/>
+      <c r="G97" s="80"/>
+      <c r="H97" s="80"/>
+      <c r="I97" s="80"/>
+      <c r="J97" s="80">
+        <f>SUM(E97*1/3,F97*1/3,H97*1/3)</f>
+        <v>0</v>
+      </c>
+      <c r="K97" s="80">
+        <f>SUM(G97*1/2,I97*1/2)</f>
+        <v>0</v>
+      </c>
+      <c r="L97" s="80">
+        <f>SUM(E97*1/5,F97*1/5,G97*1/5,H97*1/5,I97*1/5)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:14" s="82" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A98" s="82" t="s">
+        <v>3</v>
+      </c>
+      <c r="B98" s="82" t="s">
+        <v>6</v>
+      </c>
+      <c r="C98" s="86"/>
+      <c r="D98" s="86"/>
+      <c r="E98" s="80"/>
+      <c r="F98" s="80"/>
+      <c r="G98" s="80"/>
+      <c r="H98" s="80"/>
+      <c r="I98" s="80"/>
+      <c r="J98" s="80">
+        <f>SUM(E98*1/3,F98*1/3,H98*1/3)</f>
+        <v>0</v>
+      </c>
+      <c r="K98" s="80">
+        <f>SUM(G98*1/2,I98*1/2)</f>
+        <v>0</v>
+      </c>
+      <c r="L98" s="80">
+        <f>SUM(E98*1/5,F98*1/5,G98*1/5,H98*1/5,I98*1/5)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:14" s="82" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A99" s="82" t="s">
+        <v>4</v>
+      </c>
+      <c r="B99" s="82" t="s">
+        <v>7</v>
+      </c>
+      <c r="C99" s="86"/>
+      <c r="D99" s="86"/>
+      <c r="E99" s="80"/>
+      <c r="F99" s="80"/>
+      <c r="G99" s="80"/>
+      <c r="H99" s="80"/>
+      <c r="I99" s="80"/>
+      <c r="J99" s="80">
+        <f>SUM(E99*1/3,F99*1/3,H99*1/3)</f>
+        <v>0</v>
+      </c>
+      <c r="K99" s="80">
+        <f>SUM(G99*1/2,I99*1/2)</f>
+        <v>0</v>
+      </c>
+      <c r="L99" s="80">
+        <f>SUM(E99*1/5,F99*1/5,G99*1/5,H99*1/5,I99*1/5)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:14" s="82" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C100" s="87"/>
+      <c r="D100" s="87"/>
+      <c r="E100" s="80"/>
+      <c r="F100" s="80"/>
+      <c r="G100" s="80"/>
+      <c r="H100" s="80"/>
+      <c r="I100" s="80"/>
+      <c r="J100" s="80"/>
+      <c r="K100" s="80"/>
+      <c r="L100" s="80"/>
+    </row>
+    <row r="102" spans="1:14" s="14" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A102" s="72" t="s">
+        <v>59</v>
+      </c>
+      <c r="B102" s="72"/>
+      <c r="C102" s="72"/>
+      <c r="D102" s="72"/>
+      <c r="E102" s="16">
+        <f t="shared" ref="E102:L102" si="4">MAX(E72:E100)</f>
+        <v>3.1423644399999999E-2</v>
+      </c>
+      <c r="F102" s="16">
+        <f t="shared" si="4"/>
+        <v>2.0693619399999998E-2</v>
+      </c>
+      <c r="G102" s="16">
+        <f t="shared" si="4"/>
+        <v>0.62962253310000005</v>
+      </c>
+      <c r="H102" s="16">
+        <f t="shared" si="4"/>
+        <v>0.87912838900000001</v>
+      </c>
+      <c r="I102" s="16">
+        <f t="shared" si="4"/>
+        <v>0.48412258870000002</v>
+      </c>
+      <c r="J102" s="16">
+        <f t="shared" si="4"/>
+        <v>0.30501827056666669</v>
+      </c>
+      <c r="K102" s="16">
+        <f t="shared" si="4"/>
+        <v>0.54001762715000001</v>
+      </c>
+      <c r="L102" s="16">
+        <f t="shared" si="4"/>
+        <v>0.39645458486000001</v>
+      </c>
+      <c r="M102" s="16"/>
+      <c r="N102" s="17"/>
+    </row>
+    <row r="103" spans="1:14" s="52" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A103" s="77" t="s">
+        <v>60</v>
+      </c>
+      <c r="B103" s="77"/>
+      <c r="C103" s="77"/>
+      <c r="D103" s="77"/>
+      <c r="E103" s="29">
+        <f t="shared" ref="E103:L103" si="5">AVERAGE(E73:E100)</f>
+        <v>1.1959506933333331E-2</v>
+      </c>
+      <c r="F103" s="29">
+        <f t="shared" si="5"/>
+        <v>5.5406527499999997E-3</v>
+      </c>
+      <c r="G103" s="29">
+        <f t="shared" si="5"/>
+        <v>0.29980200551666669</v>
+      </c>
+      <c r="H103" s="29">
+        <f t="shared" si="5"/>
+        <v>0.66994669343333335</v>
+      </c>
+      <c r="I103" s="29">
+        <f t="shared" si="5"/>
+        <v>0.45132201146666667</v>
+      </c>
+      <c r="J103" s="29">
+        <f t="shared" si="5"/>
+        <v>6.5471128868253972E-2</v>
+      </c>
+      <c r="K103" s="29">
+        <f t="shared" si="5"/>
+        <v>0.10730343099761905</v>
+      </c>
+      <c r="L103" s="29">
+        <f t="shared" si="5"/>
+        <v>8.2204049719999991E-2</v>
+      </c>
+      <c r="M103" s="29"/>
+      <c r="N103" s="58"/>
+    </row>
   </sheetData>
-  <mergeCells count="17">
+  <mergeCells count="51">
+    <mergeCell ref="A103:D103"/>
+    <mergeCell ref="C93:C95"/>
+    <mergeCell ref="D93:D95"/>
+    <mergeCell ref="C97:C99"/>
+    <mergeCell ref="D97:D99"/>
+    <mergeCell ref="A102:D102"/>
+    <mergeCell ref="C81:C83"/>
+    <mergeCell ref="D81:D83"/>
+    <mergeCell ref="C85:C87"/>
+    <mergeCell ref="D85:D87"/>
+    <mergeCell ref="C89:C91"/>
+    <mergeCell ref="D89:D91"/>
+    <mergeCell ref="A69:D69"/>
+    <mergeCell ref="A71:I71"/>
+    <mergeCell ref="C73:C75"/>
+    <mergeCell ref="D73:D75"/>
+    <mergeCell ref="C77:C79"/>
+    <mergeCell ref="D77:D79"/>
+    <mergeCell ref="C59:C61"/>
+    <mergeCell ref="D59:D61"/>
+    <mergeCell ref="C63:C65"/>
+    <mergeCell ref="D63:D65"/>
+    <mergeCell ref="A68:D68"/>
+    <mergeCell ref="C47:C49"/>
+    <mergeCell ref="D47:D49"/>
+    <mergeCell ref="C51:C53"/>
+    <mergeCell ref="D51:D53"/>
+    <mergeCell ref="C55:C57"/>
+    <mergeCell ref="D55:D57"/>
+    <mergeCell ref="A37:I37"/>
+    <mergeCell ref="C39:C41"/>
+    <mergeCell ref="D39:D41"/>
+    <mergeCell ref="C43:C45"/>
+    <mergeCell ref="D43:D45"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="C13:C15"/>
+    <mergeCell ref="D13:D15"/>
+    <mergeCell ref="C29:C31"/>
+    <mergeCell ref="D29:D31"/>
     <mergeCell ref="A3:I3"/>
     <mergeCell ref="C21:C23"/>
     <mergeCell ref="D21:D23"/>
@@ -6227,12 +8396,6 @@
     <mergeCell ref="C9:C11"/>
     <mergeCell ref="D17:D19"/>
     <mergeCell ref="C17:C19"/>
-    <mergeCell ref="A34:D34"/>
-    <mergeCell ref="A35:D35"/>
-    <mergeCell ref="C13:C15"/>
-    <mergeCell ref="D13:D15"/>
-    <mergeCell ref="C29:C31"/>
-    <mergeCell ref="D29:D31"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/benchmarking/results/results.xlsx
+++ b/benchmarking/results/results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/deborahdore/Documents/political-debates-graph-analysis/benchmarking/results/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A119E4E-18DC-F744-B11D-73AA464DC9A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{232E161B-BE29-F947-BD1B-83FE55367566}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="51200" windowHeight="28800" activeTab="3" xr2:uid="{E2EDC037-19C4-FE46-A599-BB595128A04F}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="30240" windowHeight="18900" activeTab="3" xr2:uid="{E2EDC037-19C4-FE46-A599-BB595128A04F}"/>
   </bookViews>
   <sheets>
     <sheet name="Results BASIC" sheetId="1" r:id="rId1"/>
@@ -533,7 +533,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="89">
+  <cellXfs count="87">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -721,55 +721,70 @@
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
@@ -777,27 +792,6 @@
     </xf>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1180,13 +1174,13 @@
       <c r="B2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="68" t="s">
+      <c r="C2" s="73" t="s">
         <v>41</v>
       </c>
-      <c r="D2" s="67" t="s">
+      <c r="D2" s="70" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="67" t="s">
+      <c r="E2" s="70" t="s">
         <v>13</v>
       </c>
       <c r="F2" s="11">
@@ -1204,7 +1198,7 @@
       <c r="J2" s="11">
         <v>0.52440008120000003</v>
       </c>
-      <c r="K2" s="70" t="s">
+      <c r="K2" s="68" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1215,9 +1209,9 @@
       <c r="B3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="64"/>
-      <c r="D3" s="65"/>
-      <c r="E3" s="65"/>
+      <c r="C3" s="71"/>
+      <c r="D3" s="67"/>
+      <c r="E3" s="67"/>
       <c r="F3" s="11">
         <v>3.9117929099999997E-2</v>
       </c>
@@ -1233,7 +1227,7 @@
       <c r="J3" s="11">
         <v>0.4957882649</v>
       </c>
-      <c r="K3" s="71"/>
+      <c r="K3" s="69"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
@@ -1242,9 +1236,9 @@
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="64"/>
-      <c r="D4" s="65"/>
-      <c r="E4" s="65"/>
+      <c r="C4" s="71"/>
+      <c r="D4" s="67"/>
+      <c r="E4" s="67"/>
       <c r="F4" s="11">
         <v>2.1093001000000002E-3</v>
       </c>
@@ -1260,7 +1254,7 @@
       <c r="J4" s="11">
         <v>0.4776301698</v>
       </c>
-      <c r="K4" s="71"/>
+      <c r="K4" s="69"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
@@ -1269,13 +1263,13 @@
       <c r="B6" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="64" t="s">
+      <c r="C6" s="71" t="s">
         <v>42</v>
       </c>
-      <c r="D6" s="65" t="s">
+      <c r="D6" s="67" t="s">
         <v>10</v>
       </c>
-      <c r="E6" s="65" t="s">
+      <c r="E6" s="67" t="s">
         <v>13</v>
       </c>
       <c r="F6" s="11">
@@ -1293,7 +1287,7 @@
       <c r="J6" s="11">
         <v>0.51801477490000003</v>
       </c>
-      <c r="K6" s="71" t="s">
+      <c r="K6" s="69" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1304,9 +1298,9 @@
       <c r="B7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="64"/>
-      <c r="D7" s="65"/>
-      <c r="E7" s="65"/>
+      <c r="C7" s="71"/>
+      <c r="D7" s="67"/>
+      <c r="E7" s="67"/>
       <c r="F7" s="11">
         <v>3.2094270899999999E-2</v>
       </c>
@@ -1322,7 +1316,7 @@
       <c r="J7" s="11">
         <v>0.50083099880000004</v>
       </c>
-      <c r="K7" s="71"/>
+      <c r="K7" s="69"/>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
@@ -1331,9 +1325,9 @@
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="64"/>
-      <c r="D8" s="65"/>
-      <c r="E8" s="65"/>
+      <c r="C8" s="71"/>
+      <c r="D8" s="67"/>
+      <c r="E8" s="67"/>
       <c r="F8" s="11">
         <v>2.8741139999999998E-4</v>
       </c>
@@ -1349,15 +1343,15 @@
       <c r="J8" s="11">
         <v>0.4887305689</v>
       </c>
-      <c r="K8" s="71"/>
+      <c r="K8" s="69"/>
     </row>
     <row r="10" spans="1:12" s="59" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="66" t="s">
+      <c r="A10" s="72" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="66"/>
-      <c r="C10" s="66"/>
-      <c r="D10" s="66"/>
+      <c r="B10" s="72"/>
+      <c r="C10" s="72"/>
+      <c r="D10" s="72"/>
       <c r="E10" s="60"/>
       <c r="F10" s="61"/>
       <c r="G10" s="61"/>
@@ -1373,13 +1367,13 @@
       <c r="B12" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C12" s="64" t="s">
+      <c r="C12" s="71" t="s">
         <v>43</v>
       </c>
-      <c r="D12" s="65" t="s">
+      <c r="D12" s="67" t="s">
         <v>11</v>
       </c>
-      <c r="E12" s="65" t="s">
+      <c r="E12" s="67" t="s">
         <v>17</v>
       </c>
       <c r="F12" s="11">
@@ -1397,7 +1391,7 @@
       <c r="J12" s="11">
         <v>0.65087326729999995</v>
       </c>
-      <c r="K12" s="71" t="s">
+      <c r="K12" s="69" t="s">
         <v>18</v>
       </c>
     </row>
@@ -1408,9 +1402,9 @@
       <c r="B13" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C13" s="64"/>
-      <c r="D13" s="65"/>
-      <c r="E13" s="65"/>
+      <c r="C13" s="71"/>
+      <c r="D13" s="67"/>
+      <c r="E13" s="67"/>
       <c r="F13" s="11">
         <v>1.0937623800000001E-2</v>
       </c>
@@ -1426,7 +1420,7 @@
       <c r="J13" s="11">
         <v>0.48031703009999999</v>
       </c>
-      <c r="K13" s="71"/>
+      <c r="K13" s="69"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
@@ -1435,9 +1429,9 @@
       <c r="B14" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C14" s="64"/>
-      <c r="D14" s="65"/>
-      <c r="E14" s="65"/>
+      <c r="C14" s="71"/>
+      <c r="D14" s="67"/>
+      <c r="E14" s="67"/>
       <c r="F14" s="11">
         <v>2.377744E-4</v>
       </c>
@@ -1453,7 +1447,7 @@
       <c r="J14" s="11">
         <v>0.49770047779999999</v>
       </c>
-      <c r="K14" s="71"/>
+      <c r="K14" s="69"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
@@ -1462,13 +1456,13 @@
       <c r="B16" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C16" s="64" t="s">
+      <c r="C16" s="71" t="s">
         <v>44</v>
       </c>
-      <c r="D16" s="65" t="s">
+      <c r="D16" s="67" t="s">
         <v>19</v>
       </c>
-      <c r="E16" s="65" t="s">
+      <c r="E16" s="67" t="s">
         <v>27</v>
       </c>
       <c r="F16" s="11">
@@ -1486,7 +1480,7 @@
       <c r="J16" s="11">
         <v>0.44106115289999998</v>
       </c>
-      <c r="K16" s="71" t="s">
+      <c r="K16" s="69" t="s">
         <v>36</v>
       </c>
     </row>
@@ -1497,9 +1491,9 @@
       <c r="B17" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C17" s="64"/>
-      <c r="D17" s="65"/>
-      <c r="E17" s="65"/>
+      <c r="C17" s="71"/>
+      <c r="D17" s="67"/>
+      <c r="E17" s="67"/>
       <c r="F17" s="11">
         <v>6.6187922000000001E-3</v>
       </c>
@@ -1515,7 +1509,7 @@
       <c r="J17" s="11">
         <v>0.48203358359999998</v>
       </c>
-      <c r="K17" s="71"/>
+      <c r="K17" s="69"/>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
@@ -1524,9 +1518,9 @@
       <c r="B18" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C18" s="64"/>
-      <c r="D18" s="65"/>
-      <c r="E18" s="65"/>
+      <c r="C18" s="71"/>
+      <c r="D18" s="67"/>
+      <c r="E18" s="67"/>
       <c r="F18" s="11">
         <v>1.9467035999999999E-3</v>
       </c>
@@ -1542,7 +1536,7 @@
       <c r="J18" s="11">
         <v>0.31319458500000003</v>
       </c>
-      <c r="K18" s="71"/>
+      <c r="K18" s="69"/>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
@@ -1551,13 +1545,13 @@
       <c r="B20" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C20" s="64" t="s">
+      <c r="C20" s="71" t="s">
         <v>45</v>
       </c>
-      <c r="D20" s="65" t="s">
+      <c r="D20" s="67" t="s">
         <v>20</v>
       </c>
-      <c r="E20" s="65" t="s">
+      <c r="E20" s="67" t="s">
         <v>28</v>
       </c>
       <c r="F20" s="11">
@@ -1575,7 +1569,7 @@
       <c r="J20" s="11">
         <v>0.42558258160000001</v>
       </c>
-      <c r="K20" s="71" t="s">
+      <c r="K20" s="69" t="s">
         <v>35</v>
       </c>
     </row>
@@ -1586,9 +1580,9 @@
       <c r="B21" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C21" s="64"/>
-      <c r="D21" s="65"/>
-      <c r="E21" s="65"/>
+      <c r="C21" s="71"/>
+      <c r="D21" s="67"/>
+      <c r="E21" s="67"/>
       <c r="F21" s="11">
         <v>0.36964094320000002</v>
       </c>
@@ -1604,7 +1598,7 @@
       <c r="J21" s="11">
         <v>0.71370811339999995</v>
       </c>
-      <c r="K21" s="71"/>
+      <c r="K21" s="69"/>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
@@ -1613,9 +1607,9 @@
       <c r="B22" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C22" s="64"/>
-      <c r="D22" s="65"/>
-      <c r="E22" s="65"/>
+      <c r="C22" s="71"/>
+      <c r="D22" s="67"/>
+      <c r="E22" s="67"/>
       <c r="F22" s="11">
         <v>1.786352E-4</v>
       </c>
@@ -1631,7 +1625,7 @@
       <c r="J22" s="11">
         <v>0.35677707139999998</v>
       </c>
-      <c r="K22" s="71"/>
+      <c r="K22" s="69"/>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
@@ -1640,13 +1634,13 @@
       <c r="B24" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C24" s="64" t="s">
+      <c r="C24" s="71" t="s">
         <v>46</v>
       </c>
-      <c r="D24" s="65" t="s">
+      <c r="D24" s="67" t="s">
         <v>21</v>
       </c>
-      <c r="E24" s="65" t="s">
+      <c r="E24" s="67" t="s">
         <v>32</v>
       </c>
       <c r="F24" s="11">
@@ -1672,9 +1666,9 @@
       <c r="B25" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C25" s="64"/>
-      <c r="D25" s="65"/>
-      <c r="E25" s="65"/>
+      <c r="C25" s="71"/>
+      <c r="D25" s="67"/>
+      <c r="E25" s="67"/>
       <c r="F25" s="11">
         <v>2.2257384000000002E-2</v>
       </c>
@@ -1698,9 +1692,9 @@
       <c r="B26" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C26" s="64"/>
-      <c r="D26" s="65"/>
-      <c r="E26" s="65"/>
+      <c r="C26" s="71"/>
+      <c r="D26" s="67"/>
+      <c r="E26" s="67"/>
       <c r="F26" s="11">
         <v>3.9556960000000001E-4</v>
       </c>
@@ -1724,13 +1718,13 @@
       <c r="B28" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C28" s="64" t="s">
+      <c r="C28" s="71" t="s">
         <v>47</v>
       </c>
-      <c r="D28" s="65" t="s">
+      <c r="D28" s="67" t="s">
         <v>22</v>
       </c>
-      <c r="E28" s="65" t="s">
+      <c r="E28" s="67" t="s">
         <v>33</v>
       </c>
       <c r="F28" s="11">
@@ -1756,9 +1750,9 @@
       <c r="B29" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C29" s="64"/>
-      <c r="D29" s="65"/>
-      <c r="E29" s="65"/>
+      <c r="C29" s="71"/>
+      <c r="D29" s="67"/>
+      <c r="E29" s="67"/>
       <c r="F29" s="11">
         <v>1.8442843300000001E-2</v>
       </c>
@@ -1782,9 +1776,9 @@
       <c r="B30" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C30" s="64"/>
-      <c r="D30" s="65"/>
-      <c r="E30" s="65"/>
+      <c r="C30" s="71"/>
+      <c r="D30" s="67"/>
+      <c r="E30" s="67"/>
       <c r="F30" s="11">
         <v>6.9899990000000004E-4</v>
       </c>
@@ -1808,13 +1802,13 @@
       <c r="B32" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C32" s="64" t="s">
+      <c r="C32" s="71" t="s">
         <v>48</v>
       </c>
-      <c r="D32" s="65" t="s">
+      <c r="D32" s="67" t="s">
         <v>23</v>
       </c>
-      <c r="E32" s="65" t="s">
+      <c r="E32" s="67" t="s">
         <v>29</v>
       </c>
       <c r="F32" s="11">
@@ -1840,9 +1834,9 @@
       <c r="B33" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C33" s="64"/>
-      <c r="D33" s="65"/>
-      <c r="E33" s="65"/>
+      <c r="C33" s="71"/>
+      <c r="D33" s="67"/>
+      <c r="E33" s="67"/>
       <c r="F33" s="11">
         <v>4.8571429999999999E-4</v>
       </c>
@@ -1866,9 +1860,9 @@
       <c r="B34" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C34" s="64"/>
-      <c r="D34" s="65"/>
-      <c r="E34" s="65"/>
+      <c r="C34" s="71"/>
+      <c r="D34" s="67"/>
+      <c r="E34" s="67"/>
       <c r="F34" s="11">
         <v>8.5714299999999993E-5</v>
       </c>
@@ -1892,13 +1886,13 @@
       <c r="B36" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C36" s="64" t="s">
+      <c r="C36" s="71" t="s">
         <v>49</v>
       </c>
-      <c r="D36" s="65" t="s">
+      <c r="D36" s="67" t="s">
         <v>24</v>
       </c>
-      <c r="E36" s="65" t="s">
+      <c r="E36" s="67" t="s">
         <v>34</v>
       </c>
       <c r="F36" s="11">
@@ -1924,9 +1918,9 @@
       <c r="B37" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C37" s="64"/>
-      <c r="D37" s="65"/>
-      <c r="E37" s="65"/>
+      <c r="C37" s="71"/>
+      <c r="D37" s="67"/>
+      <c r="E37" s="67"/>
       <c r="F37" s="11">
         <v>0.12567659680000001</v>
       </c>
@@ -1950,9 +1944,9 @@
       <c r="B38" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C38" s="64"/>
-      <c r="D38" s="65"/>
-      <c r="E38" s="65"/>
+      <c r="C38" s="71"/>
+      <c r="D38" s="67"/>
+      <c r="E38" s="67"/>
       <c r="F38" s="11">
         <v>5.4127739999999998E-4</v>
       </c>
@@ -1970,12 +1964,12 @@
       </c>
     </row>
     <row r="40" spans="1:11" s="59" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="66" t="s">
+      <c r="A40" s="72" t="s">
         <v>38</v>
       </c>
-      <c r="B40" s="66"/>
-      <c r="C40" s="66"/>
-      <c r="D40" s="66"/>
+      <c r="B40" s="72"/>
+      <c r="C40" s="72"/>
+      <c r="D40" s="72"/>
       <c r="E40" s="60"/>
       <c r="F40" s="61"/>
       <c r="G40" s="61"/>
@@ -1991,13 +1985,13 @@
       <c r="B42" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C42" s="64" t="s">
+      <c r="C42" s="71" t="s">
         <v>50</v>
       </c>
-      <c r="D42" s="65" t="s">
+      <c r="D42" s="67" t="s">
         <v>25</v>
       </c>
-      <c r="E42" s="65" t="s">
+      <c r="E42" s="67" t="s">
         <v>27</v>
       </c>
       <c r="F42" s="11">
@@ -2015,7 +2009,7 @@
       <c r="J42" s="11">
         <v>0.47978398890000001</v>
       </c>
-      <c r="K42" s="71" t="s">
+      <c r="K42" s="69" t="s">
         <v>30</v>
       </c>
     </row>
@@ -2026,9 +2020,9 @@
       <c r="B43" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C43" s="64"/>
-      <c r="D43" s="65"/>
-      <c r="E43" s="65"/>
+      <c r="C43" s="71"/>
+      <c r="D43" s="67"/>
+      <c r="E43" s="67"/>
       <c r="F43" s="11">
         <v>0.15768715</v>
       </c>
@@ -2044,7 +2038,7 @@
       <c r="J43" s="11">
         <v>0.64265883619999997</v>
       </c>
-      <c r="K43" s="71"/>
+      <c r="K43" s="69"/>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
@@ -2053,9 +2047,9 @@
       <c r="B44" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C44" s="64"/>
-      <c r="D44" s="65"/>
-      <c r="E44" s="65"/>
+      <c r="C44" s="71"/>
+      <c r="D44" s="67"/>
+      <c r="E44" s="67"/>
       <c r="F44" s="11">
         <v>1.5776599999999999E-4</v>
       </c>
@@ -2071,7 +2065,7 @@
       <c r="J44" s="11">
         <v>0.33957444949999999</v>
       </c>
-      <c r="K44" s="71"/>
+      <c r="K44" s="69"/>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
@@ -2080,13 +2074,13 @@
       <c r="B46" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C46" s="64" t="s">
+      <c r="C46" s="71" t="s">
         <v>51</v>
       </c>
-      <c r="D46" s="65" t="s">
+      <c r="D46" s="67" t="s">
         <v>26</v>
       </c>
-      <c r="E46" s="65" t="s">
+      <c r="E46" s="67" t="s">
         <v>28</v>
       </c>
       <c r="F46" s="11">
@@ -2104,7 +2098,7 @@
       <c r="J46" s="11">
         <v>0.43650638670000003</v>
       </c>
-      <c r="K46" s="71" t="s">
+      <c r="K46" s="69" t="s">
         <v>31</v>
       </c>
     </row>
@@ -2115,9 +2109,9 @@
       <c r="B47" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C47" s="64"/>
-      <c r="D47" s="65"/>
-      <c r="E47" s="65"/>
+      <c r="C47" s="71"/>
+      <c r="D47" s="67"/>
+      <c r="E47" s="67"/>
       <c r="F47" s="11">
         <v>0.28846457310000001</v>
       </c>
@@ -2133,7 +2127,7 @@
       <c r="J47" s="11">
         <v>0.62979789600000002</v>
       </c>
-      <c r="K47" s="71"/>
+      <c r="K47" s="69"/>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
@@ -2142,9 +2136,9 @@
       <c r="B48" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C48" s="64"/>
-      <c r="D48" s="65"/>
-      <c r="E48" s="65"/>
+      <c r="C48" s="71"/>
+      <c r="D48" s="67"/>
+      <c r="E48" s="67"/>
       <c r="F48" s="11">
         <v>2.7615590000000002E-4</v>
       </c>
@@ -2160,7 +2154,7 @@
       <c r="J48" s="11">
         <v>0.39453545410000002</v>
       </c>
-      <c r="K48" s="71"/>
+      <c r="K48" s="69"/>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
@@ -2169,13 +2163,13 @@
       <c r="B50" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C50" s="64" t="s">
+      <c r="C50" s="71" t="s">
         <v>52</v>
       </c>
-      <c r="D50" s="65" t="s">
+      <c r="D50" s="67" t="s">
         <v>39</v>
       </c>
-      <c r="E50" s="65" t="s">
+      <c r="E50" s="67" t="s">
         <v>29</v>
       </c>
       <c r="F50" s="11">
@@ -2201,9 +2195,9 @@
       <c r="B51" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C51" s="64"/>
-      <c r="D51" s="65"/>
-      <c r="E51" s="65"/>
+      <c r="C51" s="71"/>
+      <c r="D51" s="67"/>
+      <c r="E51" s="67"/>
       <c r="F51" s="11">
         <v>3.5391416699999997E-2</v>
       </c>
@@ -2227,9 +2221,9 @@
       <c r="B52" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C52" s="64"/>
-      <c r="D52" s="65"/>
-      <c r="E52" s="65"/>
+      <c r="C52" s="71"/>
+      <c r="D52" s="67"/>
+      <c r="E52" s="67"/>
       <c r="F52" s="11">
         <v>9.9344299999999997E-5</v>
       </c>
@@ -2247,12 +2241,12 @@
       </c>
     </row>
     <row r="55" spans="1:11" s="42" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="63" t="s">
+      <c r="A55" s="74" t="s">
         <v>59</v>
       </c>
-      <c r="B55" s="63"/>
-      <c r="C55" s="63"/>
-      <c r="D55" s="63"/>
+      <c r="B55" s="74"/>
+      <c r="C55" s="74"/>
+      <c r="D55" s="74"/>
       <c r="E55" s="39"/>
       <c r="F55" s="40">
         <f>MAX(F2:F52)</f>
@@ -2277,12 +2271,12 @@
       <c r="K55" s="41"/>
     </row>
     <row r="56" spans="1:11" s="46" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="69" t="s">
+      <c r="A56" s="66" t="s">
         <v>60</v>
       </c>
-      <c r="B56" s="69"/>
-      <c r="C56" s="69"/>
-      <c r="D56" s="69"/>
+      <c r="B56" s="66"/>
+      <c r="C56" s="66"/>
+      <c r="D56" s="66"/>
       <c r="E56" s="43"/>
       <c r="F56" s="44">
         <f>AVERAGE(F2:F52)</f>
@@ -2308,6 +2302,37 @@
     </row>
   </sheetData>
   <mergeCells count="47">
+    <mergeCell ref="A55:D55"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="C12:C14"/>
+    <mergeCell ref="C16:C18"/>
+    <mergeCell ref="C20:C22"/>
+    <mergeCell ref="C24:C26"/>
+    <mergeCell ref="C50:C52"/>
+    <mergeCell ref="D24:D26"/>
+    <mergeCell ref="D28:D30"/>
+    <mergeCell ref="D32:D34"/>
+    <mergeCell ref="D36:D38"/>
+    <mergeCell ref="D42:D44"/>
+    <mergeCell ref="D46:D48"/>
+    <mergeCell ref="D50:D52"/>
+    <mergeCell ref="A40:D40"/>
+    <mergeCell ref="D2:D4"/>
+    <mergeCell ref="D6:D8"/>
+    <mergeCell ref="D12:D14"/>
+    <mergeCell ref="D16:D18"/>
+    <mergeCell ref="D20:D22"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="C2:C4"/>
+    <mergeCell ref="E12:E14"/>
+    <mergeCell ref="E16:E18"/>
+    <mergeCell ref="E20:E22"/>
+    <mergeCell ref="C42:C44"/>
+    <mergeCell ref="C46:C48"/>
+    <mergeCell ref="C28:C30"/>
+    <mergeCell ref="C32:C34"/>
+    <mergeCell ref="C36:C38"/>
+    <mergeCell ref="E46:E48"/>
     <mergeCell ref="A56:D56"/>
     <mergeCell ref="E50:E52"/>
     <mergeCell ref="K2:K4"/>
@@ -2324,37 +2349,6 @@
     <mergeCell ref="E42:E44"/>
     <mergeCell ref="E2:E4"/>
     <mergeCell ref="E6:E8"/>
-    <mergeCell ref="E12:E14"/>
-    <mergeCell ref="E16:E18"/>
-    <mergeCell ref="E20:E22"/>
-    <mergeCell ref="C42:C44"/>
-    <mergeCell ref="C46:C48"/>
-    <mergeCell ref="C28:C30"/>
-    <mergeCell ref="C32:C34"/>
-    <mergeCell ref="C36:C38"/>
-    <mergeCell ref="E46:E48"/>
-    <mergeCell ref="D2:D4"/>
-    <mergeCell ref="D6:D8"/>
-    <mergeCell ref="D12:D14"/>
-    <mergeCell ref="D16:D18"/>
-    <mergeCell ref="D20:D22"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="C2:C4"/>
-    <mergeCell ref="A55:D55"/>
-    <mergeCell ref="C6:C8"/>
-    <mergeCell ref="C12:C14"/>
-    <mergeCell ref="C16:C18"/>
-    <mergeCell ref="C20:C22"/>
-    <mergeCell ref="C24:C26"/>
-    <mergeCell ref="C50:C52"/>
-    <mergeCell ref="D24:D26"/>
-    <mergeCell ref="D28:D30"/>
-    <mergeCell ref="D32:D34"/>
-    <mergeCell ref="D36:D38"/>
-    <mergeCell ref="D42:D44"/>
-    <mergeCell ref="D46:D48"/>
-    <mergeCell ref="D50:D52"/>
-    <mergeCell ref="A40:D40"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2422,13 +2416,13 @@
       <c r="B2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="68" t="s">
+      <c r="C2" s="73" t="s">
         <v>41</v>
       </c>
-      <c r="D2" s="67" t="s">
+      <c r="D2" s="70" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="67" t="s">
+      <c r="E2" s="70" t="s">
         <v>13</v>
       </c>
       <c r="F2" s="11">
@@ -2446,7 +2440,7 @@
       <c r="J2" s="11">
         <v>0.5008326072</v>
       </c>
-      <c r="K2" s="70" t="s">
+      <c r="K2" s="68" t="s">
         <v>15</v>
       </c>
     </row>
@@ -2457,9 +2451,9 @@
       <c r="B3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="64"/>
-      <c r="D3" s="65"/>
-      <c r="E3" s="65"/>
+      <c r="C3" s="71"/>
+      <c r="D3" s="67"/>
+      <c r="E3" s="67"/>
       <c r="F3" s="11">
         <v>2.8763183099999999E-2</v>
       </c>
@@ -2475,7 +2469,7 @@
       <c r="J3" s="11">
         <v>0.49456959480000001</v>
       </c>
-      <c r="K3" s="71"/>
+      <c r="K3" s="69"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
@@ -2484,9 +2478,9 @@
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="64"/>
-      <c r="D4" s="65"/>
-      <c r="E4" s="65"/>
+      <c r="C4" s="71"/>
+      <c r="D4" s="67"/>
+      <c r="E4" s="67"/>
       <c r="F4" s="11">
         <v>5.7526370000000003E-4</v>
       </c>
@@ -2502,7 +2496,7 @@
       <c r="J4" s="11">
         <v>0.46208879800000002</v>
       </c>
-      <c r="K4" s="71"/>
+      <c r="K4" s="69"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="G5" s="11"/>
@@ -2517,13 +2511,13 @@
       <c r="B6" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="64" t="s">
+      <c r="C6" s="71" t="s">
         <v>42</v>
       </c>
-      <c r="D6" s="65" t="s">
+      <c r="D6" s="67" t="s">
         <v>10</v>
       </c>
-      <c r="E6" s="65" t="s">
+      <c r="E6" s="67" t="s">
         <v>13</v>
       </c>
       <c r="F6" s="11">
@@ -2541,7 +2535,7 @@
       <c r="J6" s="11">
         <v>0.50993042769999997</v>
       </c>
-      <c r="K6" s="71" t="s">
+      <c r="K6" s="69" t="s">
         <v>16</v>
       </c>
     </row>
@@ -2552,9 +2546,9 @@
       <c r="B7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="64"/>
-      <c r="D7" s="65"/>
-      <c r="E7" s="65"/>
+      <c r="C7" s="71"/>
+      <c r="D7" s="67"/>
+      <c r="E7" s="67"/>
       <c r="F7" s="11">
         <v>3.3435524000000001E-2</v>
       </c>
@@ -2570,7 +2564,7 @@
       <c r="J7" s="11">
         <v>0.50392556320000004</v>
       </c>
-      <c r="K7" s="71"/>
+      <c r="K7" s="69"/>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
@@ -2579,9 +2573,9 @@
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="64"/>
-      <c r="D8" s="65"/>
-      <c r="E8" s="65"/>
+      <c r="C8" s="71"/>
+      <c r="D8" s="67"/>
+      <c r="E8" s="67"/>
       <c r="F8" s="11">
         <v>3.8321520000000002E-4</v>
       </c>
@@ -2597,7 +2591,7 @@
       <c r="J8" s="11">
         <v>0.47738500210000001</v>
       </c>
-      <c r="K8" s="71"/>
+      <c r="K8" s="69"/>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="G9" s="11"/>
@@ -2606,12 +2600,12 @@
       <c r="J9" s="11"/>
     </row>
     <row r="10" spans="1:12" s="59" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="66" t="s">
+      <c r="A10" s="72" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="66"/>
-      <c r="C10" s="66"/>
-      <c r="D10" s="66"/>
+      <c r="B10" s="72"/>
+      <c r="C10" s="72"/>
+      <c r="D10" s="72"/>
       <c r="E10" s="60"/>
       <c r="F10" s="61"/>
       <c r="G10" s="61"/>
@@ -2633,13 +2627,13 @@
       <c r="B12" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C12" s="64" t="s">
+      <c r="C12" s="71" t="s">
         <v>43</v>
       </c>
-      <c r="D12" s="65" t="s">
+      <c r="D12" s="67" t="s">
         <v>11</v>
       </c>
-      <c r="E12" s="65" t="s">
+      <c r="E12" s="67" t="s">
         <v>17</v>
       </c>
       <c r="F12" s="11">
@@ -2657,7 +2651,7 @@
       <c r="J12" s="11">
         <v>0.4966675035</v>
       </c>
-      <c r="K12" s="71" t="s">
+      <c r="K12" s="69" t="s">
         <v>18</v>
       </c>
     </row>
@@ -2668,9 +2662,9 @@
       <c r="B13" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C13" s="64"/>
-      <c r="D13" s="65"/>
-      <c r="E13" s="65"/>
+      <c r="C13" s="71"/>
+      <c r="D13" s="67"/>
+      <c r="E13" s="67"/>
       <c r="F13" s="11">
         <v>2.876318E-4</v>
       </c>
@@ -2686,7 +2680,7 @@
       <c r="J13" s="11">
         <v>0.48225264400000001</v>
       </c>
-      <c r="K13" s="71"/>
+      <c r="K13" s="69"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
@@ -2695,9 +2689,9 @@
       <c r="B14" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C14" s="64"/>
-      <c r="D14" s="65"/>
-      <c r="E14" s="65"/>
+      <c r="C14" s="71"/>
+      <c r="D14" s="67"/>
+      <c r="E14" s="67"/>
       <c r="F14" s="11">
         <v>6.7114089999999996E-4</v>
       </c>
@@ -2713,7 +2707,7 @@
       <c r="J14" s="11">
         <v>0.43776818420000002</v>
       </c>
-      <c r="K14" s="71"/>
+      <c r="K14" s="69"/>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="G15" s="11"/>
@@ -2728,13 +2722,13 @@
       <c r="B16" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C16" s="64" t="s">
+      <c r="C16" s="71" t="s">
         <v>44</v>
       </c>
-      <c r="D16" s="65" t="s">
+      <c r="D16" s="67" t="s">
         <v>19</v>
       </c>
-      <c r="E16" s="65" t="s">
+      <c r="E16" s="67" t="s">
         <v>27</v>
       </c>
       <c r="F16" s="11">
@@ -2752,7 +2746,7 @@
       <c r="J16" s="11">
         <v>0.44130707470000002</v>
       </c>
-      <c r="K16" s="71" t="s">
+      <c r="K16" s="69" t="s">
         <v>36</v>
       </c>
     </row>
@@ -2763,9 +2757,9 @@
       <c r="B17" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C17" s="64"/>
-      <c r="D17" s="65"/>
-      <c r="E17" s="65"/>
+      <c r="C17" s="71"/>
+      <c r="D17" s="67"/>
+      <c r="E17" s="67"/>
       <c r="F17" s="11">
         <v>7.7660593999999998E-3</v>
       </c>
@@ -2781,7 +2775,7 @@
       <c r="J17" s="11">
         <v>0.46778393010000002</v>
       </c>
-      <c r="K17" s="71"/>
+      <c r="K17" s="69"/>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
@@ -2790,9 +2784,9 @@
       <c r="B18" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C18" s="64"/>
-      <c r="D18" s="65"/>
-      <c r="E18" s="65"/>
+      <c r="C18" s="71"/>
+      <c r="D18" s="67"/>
+      <c r="E18" s="67"/>
       <c r="F18" s="11">
         <v>2.876318E-4</v>
       </c>
@@ -2808,7 +2802,7 @@
       <c r="J18" s="11">
         <v>0.46815617929999997</v>
       </c>
-      <c r="K18" s="71"/>
+      <c r="K18" s="69"/>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.2">
       <c r="G19" s="11"/>
@@ -2823,13 +2817,13 @@
       <c r="B20" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C20" s="64" t="s">
+      <c r="C20" s="71" t="s">
         <v>45</v>
       </c>
-      <c r="D20" s="65" t="s">
+      <c r="D20" s="67" t="s">
         <v>20</v>
       </c>
-      <c r="E20" s="65" t="s">
+      <c r="E20" s="67" t="s">
         <v>28</v>
       </c>
       <c r="F20" s="11">
@@ -2847,7 +2841,7 @@
       <c r="J20" s="11">
         <v>0.4434595543</v>
       </c>
-      <c r="K20" s="71" t="s">
+      <c r="K20" s="69" t="s">
         <v>35</v>
       </c>
     </row>
@@ -2858,9 +2852,9 @@
       <c r="B21" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C21" s="64"/>
-      <c r="D21" s="65"/>
-      <c r="E21" s="65"/>
+      <c r="C21" s="71"/>
+      <c r="D21" s="67"/>
+      <c r="E21" s="67"/>
       <c r="F21" s="11">
         <v>5.11025887E-2</v>
       </c>
@@ -2876,7 +2870,7 @@
       <c r="J21" s="11">
         <v>0.46092753450000001</v>
       </c>
-      <c r="K21" s="71"/>
+      <c r="K21" s="69"/>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
@@ -2885,9 +2879,9 @@
       <c r="B22" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C22" s="64"/>
-      <c r="D22" s="65"/>
-      <c r="E22" s="65"/>
+      <c r="C22" s="71"/>
+      <c r="D22" s="67"/>
+      <c r="E22" s="67"/>
       <c r="F22" s="11">
         <v>0</v>
       </c>
@@ -2903,7 +2897,7 @@
       <c r="J22" s="11">
         <v>0.4740446935</v>
       </c>
-      <c r="K22" s="71"/>
+      <c r="K22" s="69"/>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.2">
       <c r="G23" s="11"/>
@@ -2918,13 +2912,13 @@
       <c r="B24" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C24" s="64" t="s">
+      <c r="C24" s="71" t="s">
         <v>46</v>
       </c>
-      <c r="D24" s="65" t="s">
+      <c r="D24" s="67" t="s">
         <v>21</v>
       </c>
-      <c r="E24" s="65" t="s">
+      <c r="E24" s="67" t="s">
         <v>32</v>
       </c>
       <c r="F24" s="11">
@@ -2950,9 +2944,9 @@
       <c r="B25" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C25" s="64"/>
-      <c r="D25" s="65"/>
-      <c r="E25" s="65"/>
+      <c r="C25" s="71"/>
+      <c r="D25" s="67"/>
+      <c r="E25" s="67"/>
       <c r="F25" s="11">
         <v>3.0584851400000002E-2</v>
       </c>
@@ -2976,9 +2970,9 @@
       <c r="B26" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C26" s="64"/>
-      <c r="D26" s="65"/>
-      <c r="E26" s="65"/>
+      <c r="C26" s="71"/>
+      <c r="D26" s="67"/>
+      <c r="E26" s="67"/>
       <c r="F26" s="11">
         <v>6.7114089999999996E-4</v>
       </c>
@@ -3008,13 +3002,13 @@
       <c r="B28" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C28" s="64" t="s">
+      <c r="C28" s="71" t="s">
         <v>47</v>
       </c>
-      <c r="D28" s="65" t="s">
+      <c r="D28" s="67" t="s">
         <v>22</v>
       </c>
-      <c r="E28" s="65" t="s">
+      <c r="E28" s="67" t="s">
         <v>33</v>
       </c>
       <c r="F28" s="11">
@@ -3040,9 +3034,9 @@
       <c r="B29" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C29" s="64"/>
-      <c r="D29" s="65"/>
-      <c r="E29" s="65"/>
+      <c r="C29" s="71"/>
+      <c r="D29" s="67"/>
+      <c r="E29" s="67"/>
       <c r="F29" s="11">
         <v>1.42857143E-2</v>
       </c>
@@ -3066,9 +3060,9 @@
       <c r="B30" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C30" s="64"/>
-      <c r="D30" s="65"/>
-      <c r="E30" s="65"/>
+      <c r="C30" s="71"/>
+      <c r="D30" s="67"/>
+      <c r="E30" s="67"/>
       <c r="F30" s="11">
         <v>3.8350910000000001E-4</v>
       </c>
@@ -3098,13 +3092,13 @@
       <c r="B32" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C32" s="64" t="s">
+      <c r="C32" s="71" t="s">
         <v>48</v>
       </c>
-      <c r="D32" s="65" t="s">
+      <c r="D32" s="67" t="s">
         <v>23</v>
       </c>
-      <c r="E32" s="65" t="s">
+      <c r="E32" s="67" t="s">
         <v>29</v>
       </c>
       <c r="F32" s="11">
@@ -3130,9 +3124,9 @@
       <c r="B33" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C33" s="64"/>
-      <c r="D33" s="65"/>
-      <c r="E33" s="65"/>
+      <c r="C33" s="71"/>
+      <c r="D33" s="67"/>
+      <c r="E33" s="67"/>
       <c r="F33" s="11">
         <v>6.9727237799999994E-2</v>
       </c>
@@ -3156,9 +3150,9 @@
       <c r="B34" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C34" s="64"/>
-      <c r="D34" s="65"/>
-      <c r="E34" s="65"/>
+      <c r="C34" s="71"/>
+      <c r="D34" s="67"/>
+      <c r="E34" s="67"/>
       <c r="F34" s="11">
         <v>2.8812910000000001E-4</v>
       </c>
@@ -3188,13 +3182,13 @@
       <c r="B36" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C36" s="64" t="s">
+      <c r="C36" s="71" t="s">
         <v>49</v>
       </c>
-      <c r="D36" s="65" t="s">
+      <c r="D36" s="67" t="s">
         <v>24</v>
       </c>
-      <c r="E36" s="65" t="s">
+      <c r="E36" s="67" t="s">
         <v>34</v>
       </c>
       <c r="F36" s="11">
@@ -3220,9 +3214,9 @@
       <c r="B37" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C37" s="64"/>
-      <c r="D37" s="65"/>
-      <c r="E37" s="65"/>
+      <c r="C37" s="71"/>
+      <c r="D37" s="67"/>
+      <c r="E37" s="67"/>
       <c r="F37" s="11">
         <v>1.4189837E-2</v>
       </c>
@@ -3246,9 +3240,9 @@
       <c r="B38" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C38" s="64"/>
-      <c r="D38" s="65"/>
-      <c r="E38" s="65"/>
+      <c r="C38" s="71"/>
+      <c r="D38" s="67"/>
+      <c r="E38" s="67"/>
       <c r="F38" s="11">
         <v>2.876318E-4</v>
       </c>
@@ -3272,12 +3266,12 @@
       <c r="J39" s="11"/>
     </row>
     <row r="40" spans="1:11" s="59" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="66" t="s">
+      <c r="A40" s="72" t="s">
         <v>38</v>
       </c>
-      <c r="B40" s="66"/>
-      <c r="C40" s="66"/>
-      <c r="D40" s="66"/>
+      <c r="B40" s="72"/>
+      <c r="C40" s="72"/>
+      <c r="D40" s="72"/>
       <c r="E40" s="60"/>
       <c r="F40" s="61"/>
       <c r="G40" s="61"/>
@@ -3299,13 +3293,13 @@
       <c r="B42" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C42" s="64" t="s">
+      <c r="C42" s="71" t="s">
         <v>50</v>
       </c>
-      <c r="D42" s="65" t="s">
+      <c r="D42" s="67" t="s">
         <v>25</v>
       </c>
-      <c r="E42" s="65" t="s">
+      <c r="E42" s="67" t="s">
         <v>27</v>
       </c>
       <c r="F42" s="11">
@@ -3323,7 +3317,7 @@
       <c r="J42" s="11">
         <v>0.4587482034</v>
       </c>
-      <c r="K42" s="71" t="s">
+      <c r="K42" s="69" t="s">
         <v>30</v>
       </c>
     </row>
@@ -3334,9 +3328,9 @@
       <c r="B43" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C43" s="64"/>
-      <c r="D43" s="65"/>
-      <c r="E43" s="65"/>
+      <c r="C43" s="71"/>
+      <c r="D43" s="67"/>
+      <c r="E43" s="67"/>
       <c r="F43" s="11">
         <v>1.34125311E-2</v>
       </c>
@@ -3352,7 +3346,7 @@
       <c r="J43" s="11">
         <v>0.46907909489999999</v>
       </c>
-      <c r="K43" s="71"/>
+      <c r="K43" s="69"/>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
@@ -3361,9 +3355,9 @@
       <c r="B44" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C44" s="64"/>
-      <c r="D44" s="65"/>
-      <c r="E44" s="65"/>
+      <c r="C44" s="71"/>
+      <c r="D44" s="67"/>
+      <c r="E44" s="67"/>
       <c r="F44" s="11">
         <v>8.6223409999999995E-4</v>
       </c>
@@ -3379,7 +3373,7 @@
       <c r="J44" s="11">
         <v>0.49390839069999998</v>
       </c>
-      <c r="K44" s="71"/>
+      <c r="K44" s="69"/>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.2">
       <c r="G45" s="11"/>
@@ -3394,13 +3388,13 @@
       <c r="B46" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C46" s="64" t="s">
+      <c r="C46" s="71" t="s">
         <v>51</v>
       </c>
-      <c r="D46" s="65" t="s">
+      <c r="D46" s="67" t="s">
         <v>26</v>
       </c>
-      <c r="E46" s="65" t="s">
+      <c r="E46" s="67" t="s">
         <v>28</v>
       </c>
       <c r="F46" s="11">
@@ -3418,7 +3412,7 @@
       <c r="J46" s="11">
         <v>0.45388746419999998</v>
       </c>
-      <c r="K46" s="71" t="s">
+      <c r="K46" s="69" t="s">
         <v>31</v>
       </c>
     </row>
@@ -3429,9 +3423,9 @@
       <c r="B47" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C47" s="64"/>
-      <c r="D47" s="65"/>
-      <c r="E47" s="65"/>
+      <c r="C47" s="71"/>
+      <c r="D47" s="67"/>
+      <c r="E47" s="67"/>
       <c r="F47" s="11">
         <v>4.3303314799999999E-2</v>
       </c>
@@ -3447,7 +3441,7 @@
       <c r="J47" s="11">
         <v>0.45908136910000003</v>
       </c>
-      <c r="K47" s="71"/>
+      <c r="K47" s="69"/>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
@@ -3456,9 +3450,9 @@
       <c r="B48" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C48" s="64"/>
-      <c r="D48" s="65"/>
-      <c r="E48" s="65"/>
+      <c r="C48" s="71"/>
+      <c r="D48" s="67"/>
+      <c r="E48" s="67"/>
       <c r="F48" s="11">
         <v>9.5803800000000006E-5</v>
       </c>
@@ -3474,7 +3468,7 @@
       <c r="J48" s="11">
         <v>0.478579698</v>
       </c>
-      <c r="K48" s="71"/>
+      <c r="K48" s="69"/>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.2">
       <c r="G49" s="11"/>
@@ -3489,13 +3483,13 @@
       <c r="B50" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C50" s="64" t="s">
+      <c r="C50" s="71" t="s">
         <v>52</v>
       </c>
-      <c r="D50" s="65" t="s">
+      <c r="D50" s="67" t="s">
         <v>39</v>
       </c>
-      <c r="E50" s="65" t="s">
+      <c r="E50" s="67" t="s">
         <v>29</v>
       </c>
       <c r="F50" s="11">
@@ -3521,9 +3515,9 @@
       <c r="B51" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C51" s="64"/>
-      <c r="D51" s="65"/>
-      <c r="E51" s="65"/>
+      <c r="C51" s="71"/>
+      <c r="D51" s="67"/>
+      <c r="E51" s="67"/>
       <c r="F51" s="11">
         <v>8.8139489999999997E-3</v>
       </c>
@@ -3547,9 +3541,9 @@
       <c r="B52" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C52" s="64"/>
-      <c r="D52" s="65"/>
-      <c r="E52" s="65"/>
+      <c r="C52" s="71"/>
+      <c r="D52" s="67"/>
+      <c r="E52" s="67"/>
       <c r="F52" s="11">
         <v>1.9160760000000001E-4</v>
       </c>
@@ -3579,12 +3573,12 @@
       <c r="J54" s="11"/>
     </row>
     <row r="55" spans="1:11" s="42" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="63" t="s">
+      <c r="A55" s="74" t="s">
         <v>59</v>
       </c>
-      <c r="B55" s="63"/>
-      <c r="C55" s="63"/>
-      <c r="D55" s="63"/>
+      <c r="B55" s="74"/>
+      <c r="C55" s="74"/>
+      <c r="D55" s="74"/>
       <c r="E55" s="39"/>
       <c r="F55" s="40">
         <f>MAX(F2:F52)</f>
@@ -3609,12 +3603,12 @@
       <c r="K55" s="41"/>
     </row>
     <row r="56" spans="1:11" s="46" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="69" t="s">
+      <c r="A56" s="66" t="s">
         <v>60</v>
       </c>
-      <c r="B56" s="69"/>
-      <c r="C56" s="69"/>
-      <c r="D56" s="69"/>
+      <c r="B56" s="66"/>
+      <c r="C56" s="66"/>
+      <c r="D56" s="66"/>
       <c r="E56" s="43"/>
       <c r="F56" s="44">
         <f>AVERAGE(F2:F52)</f>
@@ -3640,6 +3634,37 @@
     </row>
   </sheetData>
   <mergeCells count="47">
+    <mergeCell ref="A55:D55"/>
+    <mergeCell ref="K42:K44"/>
+    <mergeCell ref="C46:C48"/>
+    <mergeCell ref="D46:D48"/>
+    <mergeCell ref="E46:E48"/>
+    <mergeCell ref="K46:K48"/>
+    <mergeCell ref="E50:E52"/>
+    <mergeCell ref="C36:C38"/>
+    <mergeCell ref="D36:D38"/>
+    <mergeCell ref="E36:E38"/>
+    <mergeCell ref="A40:D40"/>
+    <mergeCell ref="C42:C44"/>
+    <mergeCell ref="D42:D44"/>
+    <mergeCell ref="E42:E44"/>
+    <mergeCell ref="K12:K14"/>
+    <mergeCell ref="C20:C22"/>
+    <mergeCell ref="D20:D22"/>
+    <mergeCell ref="E20:E22"/>
+    <mergeCell ref="K20:K22"/>
+    <mergeCell ref="C16:C18"/>
+    <mergeCell ref="D16:D18"/>
+    <mergeCell ref="E16:E18"/>
+    <mergeCell ref="K16:K18"/>
+    <mergeCell ref="C2:C4"/>
+    <mergeCell ref="D2:D4"/>
+    <mergeCell ref="E2:E4"/>
+    <mergeCell ref="K2:K4"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="D6:D8"/>
+    <mergeCell ref="E6:E8"/>
+    <mergeCell ref="K6:K8"/>
     <mergeCell ref="A56:D56"/>
     <mergeCell ref="A10:D10"/>
     <mergeCell ref="C12:C14"/>
@@ -3656,37 +3681,6 @@
     <mergeCell ref="E32:E34"/>
     <mergeCell ref="C50:C52"/>
     <mergeCell ref="D50:D52"/>
-    <mergeCell ref="C2:C4"/>
-    <mergeCell ref="D2:D4"/>
-    <mergeCell ref="E2:E4"/>
-    <mergeCell ref="K2:K4"/>
-    <mergeCell ref="C6:C8"/>
-    <mergeCell ref="D6:D8"/>
-    <mergeCell ref="E6:E8"/>
-    <mergeCell ref="K6:K8"/>
-    <mergeCell ref="K12:K14"/>
-    <mergeCell ref="C20:C22"/>
-    <mergeCell ref="D20:D22"/>
-    <mergeCell ref="E20:E22"/>
-    <mergeCell ref="K20:K22"/>
-    <mergeCell ref="C16:C18"/>
-    <mergeCell ref="D16:D18"/>
-    <mergeCell ref="E16:E18"/>
-    <mergeCell ref="K16:K18"/>
-    <mergeCell ref="C36:C38"/>
-    <mergeCell ref="D36:D38"/>
-    <mergeCell ref="E36:E38"/>
-    <mergeCell ref="A40:D40"/>
-    <mergeCell ref="C42:C44"/>
-    <mergeCell ref="D42:D44"/>
-    <mergeCell ref="E42:E44"/>
-    <mergeCell ref="A55:D55"/>
-    <mergeCell ref="K42:K44"/>
-    <mergeCell ref="C46:C48"/>
-    <mergeCell ref="D46:D48"/>
-    <mergeCell ref="E46:E48"/>
-    <mergeCell ref="K46:K48"/>
-    <mergeCell ref="E50:E52"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -3767,13 +3761,13 @@
       <c r="B2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="68" t="s">
+      <c r="C2" s="73" t="s">
         <v>41</v>
       </c>
-      <c r="D2" s="67" t="s">
+      <c r="D2" s="70" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="67" t="s">
+      <c r="E2" s="70" t="s">
         <v>13</v>
       </c>
       <c r="F2" s="11">
@@ -3803,7 +3797,7 @@
         <f>SUM(F2*1/5,G2*1/5,H2*1/5,I2*1/5,J2*1/5)</f>
         <v>0.29130368856</v>
       </c>
-      <c r="N2" s="70" t="s">
+      <c r="N2" s="68" t="s">
         <v>15</v>
       </c>
     </row>
@@ -3814,9 +3808,9 @@
       <c r="B3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="64"/>
-      <c r="D3" s="65"/>
-      <c r="E3" s="65"/>
+      <c r="C3" s="71"/>
+      <c r="D3" s="67"/>
+      <c r="E3" s="67"/>
       <c r="F3" s="11">
         <v>2.3969319E-3</v>
       </c>
@@ -3844,7 +3838,7 @@
         <f>SUM(F3*1/5,G3*1/5,H3*1/5,I3*1/5,J3*1/5)</f>
         <v>0.26225518991999996</v>
       </c>
-      <c r="N3" s="71"/>
+      <c r="N3" s="69"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
@@ -3853,9 +3847,9 @@
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="64"/>
-      <c r="D4" s="65"/>
-      <c r="E4" s="65"/>
+      <c r="C4" s="71"/>
+      <c r="D4" s="67"/>
+      <c r="E4" s="67"/>
       <c r="F4" s="11">
         <v>6.5867689399999999E-2</v>
       </c>
@@ -3883,7 +3877,7 @@
         <f>SUM(F4*1/5,G4*1/5,H4*1/5,I4*1/5,J4*1/5)</f>
         <v>0.29107094631999997</v>
       </c>
-      <c r="N4" s="71"/>
+      <c r="N4" s="69"/>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
@@ -3892,13 +3886,13 @@
       <c r="B6" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="64" t="s">
+      <c r="C6" s="71" t="s">
         <v>42</v>
       </c>
-      <c r="D6" s="65" t="s">
+      <c r="D6" s="67" t="s">
         <v>10</v>
       </c>
-      <c r="E6" s="65" t="s">
+      <c r="E6" s="67" t="s">
         <v>13</v>
       </c>
       <c r="F6" s="11">
@@ -3928,7 +3922,7 @@
         <f>SUM(F6*1/5,G6*1/5,H6*1/5,I6*1/5,J6*1/5)</f>
         <v>0.29438649154000002</v>
       </c>
-      <c r="N6" s="71" t="s">
+      <c r="N6" s="69" t="s">
         <v>16</v>
       </c>
     </row>
@@ -3939,9 +3933,9 @@
       <c r="B7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="64"/>
-      <c r="D7" s="65"/>
-      <c r="E7" s="65"/>
+      <c r="C7" s="71"/>
+      <c r="D7" s="67"/>
+      <c r="E7" s="67"/>
       <c r="F7" s="11">
         <v>1.3604138700000001E-2</v>
       </c>
@@ -3969,7 +3963,7 @@
         <f>SUM(F7*1/5,G7*1/5,H7*1/5,I7*1/5,J7*1/5)</f>
         <v>0.27579129901999999</v>
       </c>
-      <c r="N7" s="71"/>
+      <c r="N7" s="69"/>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
@@ -3978,9 +3972,9 @@
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="64"/>
-      <c r="D8" s="65"/>
-      <c r="E8" s="65"/>
+      <c r="C8" s="71"/>
+      <c r="D8" s="67"/>
+      <c r="E8" s="67"/>
       <c r="F8" s="11">
         <v>3.8321517499999999E-2</v>
       </c>
@@ -4008,15 +4002,15 @@
         <f>SUM(F8*1/5,G8*1/5,H8*1/5,I8*1/5,J8*1/5)</f>
         <v>0.2717815321</v>
       </c>
-      <c r="N8" s="71"/>
+      <c r="N8" s="69"/>
     </row>
     <row r="10" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="73" t="s">
+      <c r="A10" s="81" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="73"/>
-      <c r="C10" s="73"/>
-      <c r="D10" s="73"/>
+      <c r="B10" s="81"/>
+      <c r="C10" s="81"/>
+      <c r="D10" s="81"/>
       <c r="E10" s="5"/>
       <c r="F10" s="13"/>
       <c r="G10" s="13"/>
@@ -4035,13 +4029,13 @@
       <c r="B12" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C12" s="64" t="s">
+      <c r="C12" s="71" t="s">
         <v>43</v>
       </c>
-      <c r="D12" s="65" t="s">
+      <c r="D12" s="67" t="s">
         <v>11</v>
       </c>
-      <c r="E12" s="65" t="s">
+      <c r="E12" s="67" t="s">
         <v>17</v>
       </c>
       <c r="F12" s="11">
@@ -4071,7 +4065,7 @@
         <f>SUM(F12*1/5,G12*1/5,H12*1/5,I12*1/5,J12*1/5)</f>
         <v>0.33641501256</v>
       </c>
-      <c r="N12" s="71" t="s">
+      <c r="N12" s="69" t="s">
         <v>18</v>
       </c>
     </row>
@@ -4082,9 +4076,9 @@
       <c r="B13" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C13" s="64"/>
-      <c r="D13" s="65"/>
-      <c r="E13" s="65"/>
+      <c r="C13" s="71"/>
+      <c r="D13" s="67"/>
+      <c r="E13" s="67"/>
       <c r="F13" s="11">
         <v>7.9194630899999993E-2</v>
       </c>
@@ -4112,7 +4106,7 @@
         <f>SUM(F13*1/5,G13*1/5,H13*1/5,I13*1/5,J13*1/5)</f>
         <v>0.26691102733999994</v>
       </c>
-      <c r="N13" s="71"/>
+      <c r="N13" s="69"/>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
@@ -4121,9 +4115,9 @@
       <c r="B14" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C14" s="64"/>
-      <c r="D14" s="65"/>
-      <c r="E14" s="65"/>
+      <c r="C14" s="71"/>
+      <c r="D14" s="67"/>
+      <c r="E14" s="67"/>
       <c r="F14" s="11">
         <v>3.8350910000000001E-4</v>
       </c>
@@ -4151,7 +4145,7 @@
         <f>SUM(F14*1/5,G14*1/5,H14*1/5,I14*1/5,J14*1/5)</f>
         <v>0.22330577798000001</v>
       </c>
-      <c r="N14" s="71"/>
+      <c r="N14" s="69"/>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
@@ -4160,13 +4154,13 @@
       <c r="B16" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C16" s="64" t="s">
+      <c r="C16" s="71" t="s">
         <v>44</v>
       </c>
-      <c r="D16" s="65" t="s">
+      <c r="D16" s="67" t="s">
         <v>19</v>
       </c>
-      <c r="E16" s="65" t="s">
+      <c r="E16" s="67" t="s">
         <v>27</v>
       </c>
       <c r="F16" s="11">
@@ -4196,7 +4190,7 @@
         <f>SUM(F16*1/5,G16*1/5,H16*1/5,I16*1/5,J16*1/5)</f>
         <v>0.34767161497999999</v>
       </c>
-      <c r="N16" s="71" t="s">
+      <c r="N16" s="69" t="s">
         <v>36</v>
       </c>
     </row>
@@ -4207,9 +4201,9 @@
       <c r="B17" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C17" s="64"/>
-      <c r="D17" s="65"/>
-      <c r="E17" s="65"/>
+      <c r="C17" s="71"/>
+      <c r="D17" s="67"/>
+      <c r="E17" s="67"/>
       <c r="F17" s="11">
         <v>3.7296260800000001E-2</v>
       </c>
@@ -4237,7 +4231,7 @@
         <f>SUM(F17*1/5,G17*1/5,H17*1/5,I17*1/5,J17*1/5)</f>
         <v>0.33628517706000005</v>
       </c>
-      <c r="N17" s="71"/>
+      <c r="N17" s="69"/>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
@@ -4246,9 +4240,9 @@
       <c r="B18" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C18" s="64"/>
-      <c r="D18" s="65"/>
-      <c r="E18" s="65"/>
+      <c r="C18" s="71"/>
+      <c r="D18" s="67"/>
+      <c r="E18" s="67"/>
       <c r="F18" s="11">
         <v>1.0546500000000001E-3</v>
       </c>
@@ -4276,7 +4270,7 @@
         <f>SUM(F18*1/5,G18*1/5,H18*1/5,I18*1/5,J18*1/5)</f>
         <v>0.20704430204000002</v>
       </c>
-      <c r="N18" s="71"/>
+      <c r="N18" s="69"/>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
@@ -4285,13 +4279,13 @@
       <c r="B20" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C20" s="64" t="s">
+      <c r="C20" s="71" t="s">
         <v>45</v>
       </c>
-      <c r="D20" s="65" t="s">
+      <c r="D20" s="67" t="s">
         <v>20</v>
       </c>
-      <c r="E20" s="65" t="s">
+      <c r="E20" s="67" t="s">
         <v>28</v>
       </c>
       <c r="F20" s="11">
@@ -4321,7 +4315,7 @@
         <f>SUM(F20*1/5,G20*1/5,H20*1/5,I20*1/5,J20*1/5)</f>
         <v>0.31181358595999997</v>
       </c>
-      <c r="N20" s="71" t="s">
+      <c r="N20" s="69" t="s">
         <v>35</v>
       </c>
     </row>
@@ -4332,9 +4326,9 @@
       <c r="B21" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C21" s="64"/>
-      <c r="D21" s="65"/>
-      <c r="E21" s="65"/>
+      <c r="C21" s="71"/>
+      <c r="D21" s="67"/>
+      <c r="E21" s="67"/>
       <c r="F21" s="11">
         <v>1.05465005E-2</v>
       </c>
@@ -4362,7 +4356,7 @@
         <f>SUM(F21*1/5,G21*1/5,H21*1/5,I21*1/5,J21*1/5)</f>
         <v>0.29879759264</v>
       </c>
-      <c r="N21" s="71"/>
+      <c r="N21" s="69"/>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
@@ -4371,9 +4365,9 @@
       <c r="B22" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C22" s="64"/>
-      <c r="D22" s="65"/>
-      <c r="E22" s="65"/>
+      <c r="C22" s="71"/>
+      <c r="D22" s="67"/>
+      <c r="E22" s="67"/>
       <c r="F22" s="11">
         <v>0</v>
       </c>
@@ -4401,7 +4395,7 @@
         <f>SUM(F22*1/5,G22*1/5,H22*1/5,I22*1/5,J22*1/5)</f>
         <v>0.22541820497999998</v>
       </c>
-      <c r="N22" s="71"/>
+      <c r="N22" s="69"/>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
@@ -4410,13 +4404,13 @@
       <c r="B24" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C24" s="64" t="s">
+      <c r="C24" s="71" t="s">
         <v>46</v>
       </c>
-      <c r="D24" s="65" t="s">
+      <c r="D24" s="67" t="s">
         <v>21</v>
       </c>
-      <c r="E24" s="65" t="s">
+      <c r="E24" s="67" t="s">
         <v>32</v>
       </c>
       <c r="F24" s="11">
@@ -4454,9 +4448,9 @@
       <c r="B25" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C25" s="64"/>
-      <c r="D25" s="65"/>
-      <c r="E25" s="65"/>
+      <c r="C25" s="71"/>
+      <c r="D25" s="67"/>
+      <c r="E25" s="67"/>
       <c r="F25" s="11">
         <v>2.7229146700000002E-2</v>
       </c>
@@ -4492,9 +4486,9 @@
       <c r="B26" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C26" s="64"/>
-      <c r="D26" s="65"/>
-      <c r="E26" s="65"/>
+      <c r="C26" s="71"/>
+      <c r="D26" s="67"/>
+      <c r="E26" s="67"/>
       <c r="F26" s="11">
         <v>3.8350910000000001E-4</v>
       </c>
@@ -4530,13 +4524,13 @@
       <c r="B28" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C28" s="64" t="s">
+      <c r="C28" s="71" t="s">
         <v>47</v>
       </c>
-      <c r="D28" s="65" t="s">
+      <c r="D28" s="67" t="s">
         <v>22</v>
       </c>
-      <c r="E28" s="65" t="s">
+      <c r="E28" s="67" t="s">
         <v>33</v>
       </c>
       <c r="F28" s="11">
@@ -4574,9 +4568,9 @@
       <c r="B29" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C29" s="64"/>
-      <c r="D29" s="65"/>
-      <c r="E29" s="65"/>
+      <c r="C29" s="71"/>
+      <c r="D29" s="67"/>
+      <c r="E29" s="67"/>
       <c r="F29" s="11">
         <v>2.8475551299999999E-2</v>
       </c>
@@ -4612,9 +4606,9 @@
       <c r="B30" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C30" s="64"/>
-      <c r="D30" s="65"/>
-      <c r="E30" s="65"/>
+      <c r="C30" s="71"/>
+      <c r="D30" s="67"/>
+      <c r="E30" s="67"/>
       <c r="F30" s="11">
         <v>1.917546E-4</v>
       </c>
@@ -4650,13 +4644,13 @@
       <c r="B32" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C32" s="64" t="s">
+      <c r="C32" s="71" t="s">
         <v>48</v>
       </c>
-      <c r="D32" s="65" t="s">
+      <c r="D32" s="67" t="s">
         <v>23</v>
       </c>
-      <c r="E32" s="65" t="s">
+      <c r="E32" s="67" t="s">
         <v>29</v>
       </c>
       <c r="F32" s="11">
@@ -4694,9 +4688,9 @@
       <c r="B33" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C33" s="64"/>
-      <c r="D33" s="65"/>
-      <c r="E33" s="65"/>
+      <c r="C33" s="71"/>
+      <c r="D33" s="67"/>
+      <c r="E33" s="67"/>
       <c r="F33" s="11">
         <v>2.4010757000000001E-3</v>
       </c>
@@ -4732,9 +4726,9 @@
       <c r="B34" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C34" s="64"/>
-      <c r="D34" s="65"/>
-      <c r="E34" s="65"/>
+      <c r="C34" s="71"/>
+      <c r="D34" s="67"/>
+      <c r="E34" s="67"/>
       <c r="F34" s="11">
         <v>0</v>
       </c>
@@ -4770,13 +4764,13 @@
       <c r="B36" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C36" s="64" t="s">
+      <c r="C36" s="71" t="s">
         <v>49</v>
       </c>
-      <c r="D36" s="65" t="s">
+      <c r="D36" s="67" t="s">
         <v>24</v>
       </c>
-      <c r="E36" s="65" t="s">
+      <c r="E36" s="67" t="s">
         <v>34</v>
       </c>
       <c r="F36" s="11">
@@ -4814,9 +4808,9 @@
       <c r="B37" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C37" s="64"/>
-      <c r="D37" s="65"/>
-      <c r="E37" s="65"/>
+      <c r="C37" s="71"/>
+      <c r="D37" s="67"/>
+      <c r="E37" s="67"/>
       <c r="F37" s="11">
         <v>5.9443912000000003E-3</v>
       </c>
@@ -4852,9 +4846,9 @@
       <c r="B38" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C38" s="64"/>
-      <c r="D38" s="65"/>
-      <c r="E38" s="65"/>
+      <c r="C38" s="71"/>
+      <c r="D38" s="67"/>
+      <c r="E38" s="67"/>
       <c r="F38" s="11">
         <v>1.917546E-4</v>
       </c>
@@ -4884,12 +4878,12 @@
       </c>
     </row>
     <row r="40" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="73" t="s">
+      <c r="A40" s="81" t="s">
         <v>38</v>
       </c>
-      <c r="B40" s="73"/>
-      <c r="C40" s="73"/>
-      <c r="D40" s="73"/>
+      <c r="B40" s="81"/>
+      <c r="C40" s="81"/>
+      <c r="D40" s="81"/>
       <c r="E40" s="5"/>
       <c r="F40" s="13"/>
       <c r="G40" s="13"/>
@@ -4908,13 +4902,13 @@
       <c r="B42" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C42" s="64" t="s">
+      <c r="C42" s="71" t="s">
         <v>50</v>
       </c>
-      <c r="D42" s="65" t="s">
+      <c r="D42" s="67" t="s">
         <v>25</v>
       </c>
-      <c r="E42" s="65" t="s">
+      <c r="E42" s="67" t="s">
         <v>27</v>
       </c>
       <c r="F42" s="11">
@@ -4944,7 +4938,7 @@
         <f>SUM(F42*1/5,G42*1/5,H42*1/5,I42*1/5,J42*1/5)</f>
         <v>0.32911788728000002</v>
       </c>
-      <c r="N42" s="71" t="s">
+      <c r="N42" s="69" t="s">
         <v>30</v>
       </c>
     </row>
@@ -4955,9 +4949,9 @@
       <c r="B43" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C43" s="64"/>
-      <c r="D43" s="65"/>
-      <c r="E43" s="65"/>
+      <c r="C43" s="71"/>
+      <c r="D43" s="67"/>
+      <c r="E43" s="67"/>
       <c r="F43" s="11">
         <v>1.59034298E-2</v>
       </c>
@@ -4985,7 +4979,7 @@
         <f>SUM(F43*1/5,G43*1/5,H43*1/5,I43*1/5,J43*1/5)</f>
         <v>0.33481998118</v>
       </c>
-      <c r="N43" s="71"/>
+      <c r="N43" s="69"/>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
@@ -4994,9 +4988,9 @@
       <c r="B44" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C44" s="64"/>
-      <c r="D44" s="65"/>
-      <c r="E44" s="65"/>
+      <c r="C44" s="71"/>
+      <c r="D44" s="67"/>
+      <c r="E44" s="67"/>
       <c r="F44" s="62">
         <v>0</v>
       </c>
@@ -5024,7 +5018,7 @@
         <f>SUM(F44*1/5,G44*1/5,H44*1/5,I44*1/5,J44*1/5)</f>
         <v>0.23017129817999998</v>
       </c>
-      <c r="N44" s="71"/>
+      <c r="N44" s="69"/>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
@@ -5033,13 +5027,13 @@
       <c r="B46" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C46" s="64" t="s">
+      <c r="C46" s="71" t="s">
         <v>51</v>
       </c>
-      <c r="D46" s="65" t="s">
+      <c r="D46" s="67" t="s">
         <v>26</v>
       </c>
-      <c r="E46" s="65" t="s">
+      <c r="E46" s="67" t="s">
         <v>28</v>
       </c>
       <c r="F46" s="11">
@@ -5069,7 +5063,7 @@
         <f>SUM(F46*1/5,G46*1/5,H46*1/5,I46*1/5,J46*1/5)</f>
         <v>0.28403192430000002</v>
       </c>
-      <c r="N46" s="71" t="s">
+      <c r="N46" s="69" t="s">
         <v>31</v>
       </c>
     </row>
@@ -5080,9 +5074,9 @@
       <c r="B47" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C47" s="64"/>
-      <c r="D47" s="65"/>
-      <c r="E47" s="65"/>
+      <c r="C47" s="71"/>
+      <c r="D47" s="67"/>
+      <c r="E47" s="67"/>
       <c r="F47" s="11">
         <v>2.90285495E-2</v>
       </c>
@@ -5110,7 +5104,7 @@
         <f>SUM(F47*1/5,G47*1/5,H47*1/5,I47*1/5,J47*1/5)</f>
         <v>0.35089340806000002</v>
       </c>
-      <c r="N47" s="71"/>
+      <c r="N47" s="69"/>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
@@ -5119,9 +5113,9 @@
       <c r="B48" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C48" s="64"/>
-      <c r="D48" s="65"/>
-      <c r="E48" s="65"/>
+      <c r="C48" s="71"/>
+      <c r="D48" s="67"/>
+      <c r="E48" s="67"/>
       <c r="F48" s="11">
         <v>1.9160760000000001E-4</v>
       </c>
@@ -5149,7 +5143,7 @@
         <f>SUM(F48*1/5,G48*1/5,H48*1/5,I48*1/5,J48*1/5)</f>
         <v>0.34178323869999999</v>
       </c>
-      <c r="N48" s="71"/>
+      <c r="N48" s="69"/>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
@@ -5158,13 +5152,13 @@
       <c r="B50" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C50" s="64" t="s">
+      <c r="C50" s="71" t="s">
         <v>52</v>
       </c>
-      <c r="D50" s="65" t="s">
+      <c r="D50" s="67" t="s">
         <v>39</v>
       </c>
-      <c r="E50" s="65" t="s">
+      <c r="E50" s="67" t="s">
         <v>29</v>
       </c>
       <c r="F50" s="11">
@@ -5202,9 +5196,9 @@
       <c r="B51" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C51" s="64"/>
-      <c r="D51" s="65"/>
-      <c r="E51" s="65"/>
+      <c r="C51" s="71"/>
+      <c r="D51" s="67"/>
+      <c r="E51" s="67"/>
       <c r="F51" s="11">
         <v>3.4489365999999999E-3</v>
       </c>
@@ -5240,9 +5234,9 @@
       <c r="B52" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C52" s="64"/>
-      <c r="D52" s="65"/>
-      <c r="E52" s="65"/>
+      <c r="C52" s="71"/>
+      <c r="D52" s="67"/>
+      <c r="E52" s="67"/>
       <c r="F52" s="62">
         <v>4.7901900000000002E-4</v>
       </c>
@@ -5272,12 +5266,12 @@
       </c>
     </row>
     <row r="55" spans="1:14" s="14" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="72" t="s">
+      <c r="A55" s="82" t="s">
         <v>59</v>
       </c>
-      <c r="B55" s="72"/>
-      <c r="C55" s="72"/>
-      <c r="D55" s="72"/>
+      <c r="B55" s="82"/>
+      <c r="C55" s="82"/>
+      <c r="D55" s="82"/>
       <c r="E55" s="15"/>
       <c r="F55" s="16">
         <f t="shared" ref="F55:M55" si="0">MAX(F2:F52)</f>
@@ -5314,12 +5308,12 @@
       <c r="N55" s="17"/>
     </row>
     <row r="56" spans="1:14" s="18" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="74" t="s">
+      <c r="A56" s="80" t="s">
         <v>60</v>
       </c>
-      <c r="B56" s="74"/>
-      <c r="C56" s="74"/>
-      <c r="D56" s="74"/>
+      <c r="B56" s="80"/>
+      <c r="C56" s="80"/>
+      <c r="D56" s="80"/>
       <c r="E56" s="19"/>
       <c r="F56" s="20">
         <f t="shared" ref="F56:M56" si="1">AVERAGE(F2:F52)</f>
@@ -5474,12 +5468,37 @@
     </row>
   </sheetData>
   <mergeCells count="53">
-    <mergeCell ref="A63:D63"/>
-    <mergeCell ref="A64:D64"/>
-    <mergeCell ref="A58:E58"/>
-    <mergeCell ref="A59:E59"/>
-    <mergeCell ref="A60:E60"/>
-    <mergeCell ref="A62:D62"/>
+    <mergeCell ref="A55:D55"/>
+    <mergeCell ref="N42:N44"/>
+    <mergeCell ref="C46:C48"/>
+    <mergeCell ref="D46:D48"/>
+    <mergeCell ref="E46:E48"/>
+    <mergeCell ref="N46:N48"/>
+    <mergeCell ref="E50:E52"/>
+    <mergeCell ref="C36:C38"/>
+    <mergeCell ref="D36:D38"/>
+    <mergeCell ref="E36:E38"/>
+    <mergeCell ref="A40:D40"/>
+    <mergeCell ref="C42:C44"/>
+    <mergeCell ref="D42:D44"/>
+    <mergeCell ref="E42:E44"/>
+    <mergeCell ref="N12:N14"/>
+    <mergeCell ref="C20:C22"/>
+    <mergeCell ref="D20:D22"/>
+    <mergeCell ref="E20:E22"/>
+    <mergeCell ref="N20:N22"/>
+    <mergeCell ref="C16:C18"/>
+    <mergeCell ref="D16:D18"/>
+    <mergeCell ref="E16:E18"/>
+    <mergeCell ref="N16:N18"/>
+    <mergeCell ref="C2:C4"/>
+    <mergeCell ref="D2:D4"/>
+    <mergeCell ref="E2:E4"/>
+    <mergeCell ref="N2:N4"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="D6:D8"/>
+    <mergeCell ref="E6:E8"/>
+    <mergeCell ref="N6:N8"/>
     <mergeCell ref="A56:D56"/>
     <mergeCell ref="A10:D10"/>
     <mergeCell ref="C12:C14"/>
@@ -5496,37 +5515,12 @@
     <mergeCell ref="E32:E34"/>
     <mergeCell ref="C50:C52"/>
     <mergeCell ref="D50:D52"/>
-    <mergeCell ref="C2:C4"/>
-    <mergeCell ref="D2:D4"/>
-    <mergeCell ref="E2:E4"/>
-    <mergeCell ref="N2:N4"/>
-    <mergeCell ref="C6:C8"/>
-    <mergeCell ref="D6:D8"/>
-    <mergeCell ref="E6:E8"/>
-    <mergeCell ref="N6:N8"/>
-    <mergeCell ref="N12:N14"/>
-    <mergeCell ref="C20:C22"/>
-    <mergeCell ref="D20:D22"/>
-    <mergeCell ref="E20:E22"/>
-    <mergeCell ref="N20:N22"/>
-    <mergeCell ref="C16:C18"/>
-    <mergeCell ref="D16:D18"/>
-    <mergeCell ref="E16:E18"/>
-    <mergeCell ref="N16:N18"/>
-    <mergeCell ref="C36:C38"/>
-    <mergeCell ref="D36:D38"/>
-    <mergeCell ref="E36:E38"/>
-    <mergeCell ref="A40:D40"/>
-    <mergeCell ref="C42:C44"/>
-    <mergeCell ref="D42:D44"/>
-    <mergeCell ref="E42:E44"/>
-    <mergeCell ref="A55:D55"/>
-    <mergeCell ref="N42:N44"/>
-    <mergeCell ref="C46:C48"/>
-    <mergeCell ref="D46:D48"/>
-    <mergeCell ref="E46:E48"/>
-    <mergeCell ref="N46:N48"/>
-    <mergeCell ref="E50:E52"/>
+    <mergeCell ref="A63:D63"/>
+    <mergeCell ref="A64:D64"/>
+    <mergeCell ref="A58:E58"/>
+    <mergeCell ref="A59:E59"/>
+    <mergeCell ref="A60:E60"/>
+    <mergeCell ref="A62:D62"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5544,7 +5538,7 @@
     <col min="5" max="5" width="27.83203125" style="11" customWidth="1"/>
     <col min="6" max="6" width="28.1640625" style="11" customWidth="1"/>
     <col min="7" max="7" width="30.83203125" style="11" customWidth="1"/>
-    <col min="8" max="8" width="27.83203125" style="11" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="29" style="11" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="28.6640625" style="11" customWidth="1"/>
     <col min="10" max="10" width="27.1640625" style="11" customWidth="1"/>
     <col min="11" max="11" width="24.83203125" style="11" customWidth="1"/>
@@ -5607,17 +5601,17 @@
       <c r="N2" s="9"/>
     </row>
     <row r="3" spans="1:14" s="47" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="74" t="s">
+      <c r="A3" s="80" t="s">
         <v>71</v>
       </c>
-      <c r="B3" s="74"/>
-      <c r="C3" s="74"/>
-      <c r="D3" s="74"/>
-      <c r="E3" s="74"/>
-      <c r="F3" s="74"/>
-      <c r="G3" s="74"/>
-      <c r="H3" s="74"/>
-      <c r="I3" s="74"/>
+      <c r="B3" s="80"/>
+      <c r="C3" s="80"/>
+      <c r="D3" s="80"/>
+      <c r="E3" s="80"/>
+      <c r="F3" s="80"/>
+      <c r="G3" s="80"/>
+      <c r="H3" s="80"/>
+      <c r="I3" s="80"/>
       <c r="J3" s="49"/>
       <c r="K3" s="56"/>
       <c r="L3" s="56"/>
@@ -5643,10 +5637,10 @@
       <c r="B5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="71" t="s">
+      <c r="C5" s="69" t="s">
         <v>67</v>
       </c>
-      <c r="D5" s="71" t="s">
+      <c r="D5" s="69" t="s">
         <v>68</v>
       </c>
       <c r="E5" s="11">
@@ -5684,8 +5678,8 @@
       <c r="B6" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="71"/>
-      <c r="D6" s="71"/>
+      <c r="C6" s="69"/>
+      <c r="D6" s="69"/>
       <c r="E6" s="11">
         <v>6.9727237799999994E-2</v>
       </c>
@@ -5721,8 +5715,8 @@
       <c r="B7" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="71"/>
-      <c r="D7" s="71"/>
+      <c r="C7" s="69"/>
+      <c r="D7" s="69"/>
       <c r="E7" s="11">
         <v>2.8812910000000001E-4</v>
       </c>
@@ -5758,10 +5752,10 @@
       <c r="B9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="71" t="s">
+      <c r="C9" s="69" t="s">
         <v>69</v>
       </c>
-      <c r="D9" s="71" t="s">
+      <c r="D9" s="69" t="s">
         <v>70</v>
       </c>
       <c r="E9" s="11">
@@ -5773,7 +5767,7 @@
       <c r="G9" s="11">
         <v>0.4692662313</v>
       </c>
-      <c r="H9" s="81">
+      <c r="H9" s="54">
         <v>0.89344463880000002</v>
       </c>
       <c r="I9" s="11">
@@ -5799,8 +5793,8 @@
       <c r="B10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="71"/>
-      <c r="D10" s="71"/>
+      <c r="C10" s="69"/>
+      <c r="D10" s="69"/>
       <c r="E10" s="11">
         <v>2.4010757000000001E-3</v>
       </c>
@@ -5836,8 +5830,8 @@
       <c r="B11" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C11" s="71"/>
-      <c r="D11" s="71"/>
+      <c r="C11" s="69"/>
+      <c r="D11" s="69"/>
       <c r="E11" s="11">
         <v>0</v>
       </c>
@@ -5873,10 +5867,10 @@
       <c r="B13" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C13" s="71" t="s">
+      <c r="C13" s="69" t="s">
         <v>74</v>
       </c>
-      <c r="D13" s="71" t="s">
+      <c r="D13" s="69" t="s">
         <v>81</v>
       </c>
       <c r="E13" s="11">
@@ -5914,8 +5908,8 @@
       <c r="B14" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C14" s="71"/>
-      <c r="D14" s="71"/>
+      <c r="C14" s="69"/>
+      <c r="D14" s="69"/>
       <c r="E14" s="11">
         <v>3.5474592999999999E-3</v>
       </c>
@@ -5951,8 +5945,8 @@
       <c r="B15" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C15" s="71"/>
-      <c r="D15" s="71"/>
+      <c r="C15" s="69"/>
+      <c r="D15" s="69"/>
       <c r="E15" s="11">
         <v>3.8350910000000001E-4</v>
       </c>
@@ -5981,43 +5975,43 @@
         <v>0.35585434523999993</v>
       </c>
     </row>
-    <row r="17" spans="1:12" s="83" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="83" t="s">
+    <row r="17" spans="1:12" s="63" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="63" t="s">
         <v>2</v>
       </c>
-      <c r="B17" s="83" t="s">
+      <c r="B17" s="63" t="s">
         <v>5</v>
       </c>
-      <c r="C17" s="71" t="s">
+      <c r="C17" s="69" t="s">
         <v>80</v>
       </c>
-      <c r="D17" s="71" t="s">
+      <c r="D17" s="69" t="s">
         <v>79</v>
       </c>
-      <c r="E17" s="84">
+      <c r="E17" s="64">
         <v>3.5474592999999999E-3</v>
       </c>
-      <c r="F17" s="84">
+      <c r="F17" s="64">
         <v>2.3969319E-3</v>
       </c>
-      <c r="G17" s="84">
+      <c r="G17" s="64">
         <v>0.68648130389999995</v>
       </c>
-      <c r="H17" s="84">
+      <c r="H17" s="64">
         <v>0.73279006160000004</v>
       </c>
-      <c r="I17" s="85">
+      <c r="I17" s="65">
         <v>0.70502058919999999</v>
       </c>
-      <c r="J17" s="84">
+      <c r="J17" s="64">
         <f>SUM(E17*1/3,F17*1/3,H17*1/3)</f>
         <v>0.2462448176</v>
       </c>
-      <c r="K17" s="84">
+      <c r="K17" s="64">
         <f>SUM(G17*1/2,I17*1/2)</f>
         <v>0.69575094655000003</v>
       </c>
-      <c r="L17" s="84">
+      <c r="L17" s="64">
         <f>SUM(E17*1/5,F17*1/5,G17*1/5,H17*1/5,I17*1/5)</f>
         <v>0.42604726918000002</v>
       </c>
@@ -6029,8 +6023,8 @@
       <c r="B18" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C18" s="71"/>
-      <c r="D18" s="71"/>
+      <c r="C18" s="69"/>
+      <c r="D18" s="69"/>
       <c r="E18" s="11">
         <v>3.0680729000000001E-3</v>
       </c>
@@ -6066,8 +6060,8 @@
       <c r="B19" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C19" s="71"/>
-      <c r="D19" s="71"/>
+      <c r="C19" s="69"/>
+      <c r="D19" s="69"/>
       <c r="E19" s="11">
         <v>2.876318E-4</v>
       </c>
@@ -6106,10 +6100,10 @@
       <c r="B21" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C21" s="71" t="s">
+      <c r="C21" s="69" t="s">
         <v>72</v>
       </c>
-      <c r="D21" s="71" t="s">
+      <c r="D21" s="69" t="s">
         <v>73</v>
       </c>
       <c r="E21" s="11">
@@ -6147,8 +6141,8 @@
       <c r="B22" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C22" s="71"/>
-      <c r="D22" s="71"/>
+      <c r="C22" s="69"/>
+      <c r="D22" s="69"/>
       <c r="E22" s="11">
         <v>3.1639501E-3</v>
       </c>
@@ -6184,15 +6178,15 @@
       <c r="B23" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C23" s="71"/>
-      <c r="D23" s="71"/>
+      <c r="C23" s="69"/>
+      <c r="D23" s="69"/>
       <c r="E23" s="11">
         <v>1.917546E-4</v>
       </c>
       <c r="F23" s="11">
         <v>4.5062319999999998E-3</v>
       </c>
-      <c r="G23" s="81">
+      <c r="G23" s="54">
         <v>0.79884947269999995</v>
       </c>
       <c r="H23" s="11">
@@ -6221,10 +6215,10 @@
       <c r="B25" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C25" s="71" t="s">
+      <c r="C25" s="69" t="s">
         <v>77</v>
       </c>
-      <c r="D25" s="71" t="s">
+      <c r="D25" s="69" t="s">
         <v>75</v>
       </c>
       <c r="E25" s="11">
@@ -6262,8 +6256,8 @@
       <c r="B26" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C26" s="71"/>
-      <c r="D26" s="71"/>
+      <c r="C26" s="69"/>
+      <c r="D26" s="69"/>
       <c r="E26" s="11">
         <v>1.70661553E-2</v>
       </c>
@@ -6299,8 +6293,8 @@
       <c r="B27" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C27" s="71"/>
-      <c r="D27" s="71"/>
+      <c r="C27" s="69"/>
+      <c r="D27" s="69"/>
       <c r="E27" s="11">
         <v>6.7114089999999996E-4</v>
       </c>
@@ -6336,10 +6330,10 @@
       <c r="B29" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C29" s="71" t="s">
+      <c r="C29" s="69" t="s">
         <v>78</v>
       </c>
-      <c r="D29" s="71" t="s">
+      <c r="D29" s="69" t="s">
         <v>76</v>
       </c>
       <c r="E29" s="11">
@@ -6377,8 +6371,8 @@
       <c r="B30" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C30" s="71"/>
-      <c r="D30" s="71"/>
+      <c r="C30" s="69"/>
+      <c r="D30" s="69"/>
       <c r="E30" s="11">
         <v>7.2866731000000001E-3</v>
       </c>
@@ -6414,8 +6408,8 @@
       <c r="B31" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C31" s="71"/>
-      <c r="D31" s="71"/>
+      <c r="C31" s="69"/>
+      <c r="D31" s="69"/>
       <c r="E31" s="11">
         <v>0</v>
       </c>
@@ -6445,12 +6439,12 @@
       </c>
     </row>
     <row r="34" spans="1:14" s="14" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="72" t="s">
+      <c r="A34" s="82" t="s">
         <v>59</v>
       </c>
-      <c r="B34" s="72"/>
-      <c r="C34" s="72"/>
-      <c r="D34" s="72"/>
+      <c r="B34" s="82"/>
+      <c r="C34" s="82"/>
+      <c r="D34" s="82"/>
       <c r="E34" s="16">
         <f t="shared" ref="E34:L34" si="0">MAX(E4:E32)</f>
         <v>8.2742090099999999E-2</v>
@@ -6529,17 +6523,17 @@
       <c r="N35" s="58"/>
     </row>
     <row r="37" spans="1:14" s="47" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="74" t="s">
+      <c r="A37" s="80" t="s">
         <v>86</v>
       </c>
-      <c r="B37" s="74"/>
-      <c r="C37" s="74"/>
-      <c r="D37" s="74"/>
-      <c r="E37" s="74"/>
-      <c r="F37" s="74"/>
-      <c r="G37" s="74"/>
-      <c r="H37" s="74"/>
-      <c r="I37" s="74"/>
+      <c r="B37" s="80"/>
+      <c r="C37" s="80"/>
+      <c r="D37" s="80"/>
+      <c r="E37" s="80"/>
+      <c r="F37" s="80"/>
+      <c r="G37" s="80"/>
+      <c r="H37" s="80"/>
+      <c r="I37" s="80"/>
       <c r="J37" s="49"/>
       <c r="K37" s="56"/>
       <c r="L37" s="56"/>
@@ -6565,10 +6559,10 @@
       <c r="B39" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C39" s="71" t="s">
+      <c r="C39" s="69" t="s">
         <v>87</v>
       </c>
-      <c r="D39" s="71" t="s">
+      <c r="D39" s="69" t="s">
         <v>68</v>
       </c>
       <c r="E39" s="11">
@@ -6606,8 +6600,8 @@
       <c r="B40" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C40" s="71"/>
-      <c r="D40" s="71"/>
+      <c r="C40" s="69"/>
+      <c r="D40" s="69"/>
       <c r="E40" s="11">
         <v>1.42857143E-2</v>
       </c>
@@ -6643,8 +6637,8 @@
       <c r="B41" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C41" s="71"/>
-      <c r="D41" s="71"/>
+      <c r="C41" s="69"/>
+      <c r="D41" s="69"/>
       <c r="E41" s="11">
         <v>3.8350910000000001E-4</v>
       </c>
@@ -6673,13 +6667,6 @@
         <v>0.20280455491999999</v>
       </c>
     </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="E42" s="80"/>
-      <c r="F42" s="80"/>
-      <c r="G42" s="80"/>
-      <c r="H42" s="80"/>
-      <c r="I42" s="80"/>
-    </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
         <v>2</v>
@@ -6687,10 +6674,10 @@
       <c r="B43" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C43" s="71" t="s">
+      <c r="C43" s="69" t="s">
         <v>88</v>
       </c>
-      <c r="D43" s="71" t="s">
+      <c r="D43" s="69" t="s">
         <v>70</v>
       </c>
       <c r="E43" s="11">
@@ -6728,8 +6715,8 @@
       <c r="B44" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C44" s="71"/>
-      <c r="D44" s="71"/>
+      <c r="C44" s="69"/>
+      <c r="D44" s="69"/>
       <c r="E44" s="11">
         <v>2.8475551299999999E-2</v>
       </c>
@@ -6765,8 +6752,8 @@
       <c r="B45" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C45" s="71"/>
-      <c r="D45" s="71"/>
+      <c r="C45" s="69"/>
+      <c r="D45" s="69"/>
       <c r="E45" s="11">
         <v>1.917546E-4</v>
       </c>
@@ -6795,13 +6782,6 @@
         <v>0.36078885547999995</v>
       </c>
     </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="E46" s="80"/>
-      <c r="F46" s="80"/>
-      <c r="G46" s="80"/>
-      <c r="H46" s="80"/>
-      <c r="I46" s="80"/>
-    </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A47" s="1" t="s">
         <v>2</v>
@@ -6809,25 +6789,25 @@
       <c r="B47" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C47" s="71" t="s">
+      <c r="C47" s="69" t="s">
         <v>89</v>
       </c>
-      <c r="D47" s="71" t="s">
+      <c r="D47" s="69" t="s">
         <v>81</v>
       </c>
-      <c r="E47" s="80">
+      <c r="E47" s="11">
         <v>2.1572387299999999E-2</v>
       </c>
-      <c r="F47" s="80">
+      <c r="F47" s="11">
         <v>1.725791E-3</v>
       </c>
-      <c r="G47" s="80">
+      <c r="G47" s="11">
         <v>0.21380632790000001</v>
       </c>
-      <c r="H47" s="80">
+      <c r="H47" s="11">
         <v>0.4996014688</v>
       </c>
-      <c r="I47" s="80">
+      <c r="I47" s="11">
         <v>0.49415116780000001</v>
       </c>
       <c r="J47" s="11">
@@ -6850,21 +6830,21 @@
       <c r="B48" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C48" s="71"/>
-      <c r="D48" s="71"/>
-      <c r="E48" s="80">
+      <c r="C48" s="69"/>
+      <c r="D48" s="69"/>
+      <c r="E48" s="11">
         <v>6.3279002999999997E-3</v>
       </c>
-      <c r="F48" s="80">
+      <c r="F48" s="11">
         <v>3.5474592999999999E-3</v>
       </c>
-      <c r="G48" s="80">
+      <c r="G48" s="11">
         <v>0.35973154359999998</v>
       </c>
-      <c r="H48" s="80">
+      <c r="H48" s="11">
         <v>0.50229272930000002</v>
       </c>
-      <c r="I48" s="80">
+      <c r="I48" s="11">
         <v>0.48684262210000001</v>
       </c>
       <c r="J48" s="11">
@@ -6887,21 +6867,21 @@
       <c r="B49" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C49" s="71"/>
-      <c r="D49" s="71"/>
-      <c r="E49" s="80">
+      <c r="C49" s="69"/>
+      <c r="D49" s="69"/>
+      <c r="E49" s="11">
         <v>2.876318E-4</v>
       </c>
-      <c r="F49" s="80">
+      <c r="F49" s="11">
         <v>1.725791E-3</v>
       </c>
-      <c r="G49" s="80">
+      <c r="G49" s="11">
         <v>0.67919463089999998</v>
       </c>
-      <c r="H49" s="80">
+      <c r="H49" s="11">
         <v>0.50784208630000005</v>
       </c>
-      <c r="I49" s="80">
+      <c r="I49" s="11">
         <v>0.4972537568</v>
       </c>
       <c r="J49" s="11">
@@ -6917,50 +6897,43 @@
         <v>0.33726077935999998</v>
       </c>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="E50" s="80"/>
-      <c r="F50" s="80"/>
-      <c r="G50" s="80"/>
-      <c r="H50" s="80"/>
-      <c r="I50" s="80"/>
-    </row>
-    <row r="51" spans="1:12" s="83" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="83" t="s">
+    <row r="51" spans="1:12" s="63" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A51" s="63" t="s">
         <v>2</v>
       </c>
-      <c r="B51" s="83" t="s">
+      <c r="B51" s="63" t="s">
         <v>5</v>
       </c>
-      <c r="C51" s="71" t="s">
+      <c r="C51" s="69" t="s">
         <v>90</v>
       </c>
-      <c r="D51" s="71" t="s">
+      <c r="D51" s="69" t="s">
         <v>79</v>
       </c>
-      <c r="E51" s="84">
+      <c r="E51" s="64">
         <v>1.23681687E-2</v>
       </c>
-      <c r="F51" s="84">
+      <c r="F51" s="64">
         <v>2.6845637999999999E-3</v>
       </c>
-      <c r="G51" s="84">
+      <c r="G51" s="64">
         <v>0.70795781400000002</v>
       </c>
-      <c r="H51" s="84">
+      <c r="H51" s="64">
         <v>0.71314872139999996</v>
       </c>
-      <c r="I51" s="85">
+      <c r="I51" s="65">
         <v>0.64805542540000005</v>
       </c>
-      <c r="J51" s="84">
+      <c r="J51" s="64">
         <f>SUM(E51*1/3,F51*1/3,H51*1/3)</f>
         <v>0.24273381796666665</v>
       </c>
-      <c r="K51" s="85">
+      <c r="K51" s="65">
         <f>SUM(G51*1/2,I51*1/2)</f>
         <v>0.67800661970000009</v>
       </c>
-      <c r="L51" s="85">
+      <c r="L51" s="65">
         <f>SUM(E51*1/5,F51*1/5,G51*1/5,H51*1/5,I51*1/5)</f>
         <v>0.41684293866000005</v>
       </c>
@@ -6972,21 +6945,21 @@
       <c r="B52" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C52" s="71"/>
-      <c r="D52" s="71"/>
-      <c r="E52" s="80">
+      <c r="C52" s="69"/>
+      <c r="D52" s="69"/>
+      <c r="E52" s="11">
         <v>2.0134227999999998E-3</v>
       </c>
-      <c r="F52" s="80">
+      <c r="F52" s="11">
         <v>7.6701829999999995E-4</v>
       </c>
-      <c r="G52" s="80">
+      <c r="G52" s="11">
         <v>0.27823585810000001</v>
       </c>
-      <c r="H52" s="80">
+      <c r="H52" s="11">
         <v>0.50316636969999995</v>
       </c>
-      <c r="I52" s="80">
+      <c r="I52" s="11">
         <v>0.47961395620000002</v>
       </c>
       <c r="J52" s="11">
@@ -7009,21 +6982,21 @@
       <c r="B53" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C53" s="71"/>
-      <c r="D53" s="71"/>
-      <c r="E53" s="80">
+      <c r="C53" s="69"/>
+      <c r="D53" s="69"/>
+      <c r="E53" s="11">
         <v>1.917546E-4</v>
       </c>
-      <c r="F53" s="80">
+      <c r="F53" s="11">
         <v>1.1505273E-3</v>
       </c>
-      <c r="G53" s="80">
+      <c r="G53" s="11">
         <v>2.9146692200000001E-2</v>
       </c>
-      <c r="H53" s="80">
+      <c r="H53" s="11">
         <v>0.37034050689999998</v>
       </c>
-      <c r="I53" s="80">
+      <c r="I53" s="11">
         <v>0.31939047450000002</v>
       </c>
       <c r="J53" s="11">
@@ -7041,11 +7014,6 @@
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C54" s="50"/>
-      <c r="E54" s="80"/>
-      <c r="F54" s="80"/>
-      <c r="G54" s="80"/>
-      <c r="H54" s="80"/>
-      <c r="I54" s="80"/>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A55" s="1" t="s">
@@ -7054,25 +7022,25 @@
       <c r="B55" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C55" s="71" t="s">
+      <c r="C55" s="69" t="s">
         <v>91</v>
       </c>
-      <c r="D55" s="71" t="s">
+      <c r="D55" s="69" t="s">
         <v>73</v>
       </c>
-      <c r="E55" s="80">
+      <c r="E55" s="11">
         <v>9.0220517700000002E-2</v>
       </c>
-      <c r="F55" s="80">
+      <c r="F55" s="11">
         <v>1.2655800599999999E-2</v>
       </c>
-      <c r="G55" s="80">
+      <c r="G55" s="11">
         <v>0.24256951099999999</v>
       </c>
-      <c r="H55" s="80">
+      <c r="H55" s="11">
         <v>0.74882737740000005</v>
       </c>
-      <c r="I55" s="80">
+      <c r="I55" s="11">
         <v>0.41265332459999998</v>
       </c>
       <c r="J55" s="11">
@@ -7095,21 +7063,21 @@
       <c r="B56" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C56" s="71"/>
-      <c r="D56" s="71"/>
-      <c r="E56" s="80">
+      <c r="C56" s="69"/>
+      <c r="D56" s="69"/>
+      <c r="E56" s="11">
         <v>1.9558964500000001E-2</v>
       </c>
-      <c r="F56" s="80">
+      <c r="F56" s="11">
         <v>3.7392138000000002E-3</v>
       </c>
-      <c r="G56" s="80">
+      <c r="G56" s="11">
         <v>0.42703739210000002</v>
       </c>
-      <c r="H56" s="80">
+      <c r="H56" s="11">
         <v>0.54984708800000004</v>
       </c>
-      <c r="I56" s="80">
+      <c r="I56" s="11">
         <v>0.54163438399999997</v>
       </c>
       <c r="J56" s="11">
@@ -7132,21 +7100,21 @@
       <c r="B57" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C57" s="71"/>
-      <c r="D57" s="71"/>
-      <c r="E57" s="80">
+      <c r="C57" s="69"/>
+      <c r="D57" s="69"/>
+      <c r="E57" s="11">
         <v>0</v>
       </c>
-      <c r="F57" s="80">
+      <c r="F57" s="11">
         <v>2.8763183999999998E-3</v>
       </c>
-      <c r="G57" s="81">
+      <c r="G57" s="54">
         <v>0.81802492810000005</v>
       </c>
-      <c r="H57" s="80">
+      <c r="H57" s="11">
         <v>0.52913612850000002</v>
       </c>
-      <c r="I57" s="80">
+      <c r="I57" s="11">
         <v>0.49455716719999998</v>
       </c>
       <c r="J57" s="11">
@@ -7162,13 +7130,6 @@
         <v>0.36891890843999997</v>
       </c>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="E58" s="80"/>
-      <c r="F58" s="80"/>
-      <c r="G58" s="80"/>
-      <c r="H58" s="80"/>
-      <c r="I58" s="80"/>
-    </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A59" s="1" t="s">
         <v>2</v>
@@ -7176,25 +7137,25 @@
       <c r="B59" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C59" s="71" t="s">
+      <c r="C59" s="69" t="s">
         <v>92</v>
       </c>
-      <c r="D59" s="71" t="s">
+      <c r="D59" s="69" t="s">
         <v>75</v>
       </c>
-      <c r="E59" s="80">
+      <c r="E59" s="11">
         <v>2.47363375E-2</v>
       </c>
-      <c r="F59" s="80">
+      <c r="F59" s="11">
         <v>4.3144773999999999E-3</v>
       </c>
-      <c r="G59" s="80">
+      <c r="G59" s="11">
         <v>0.60268456380000002</v>
       </c>
-      <c r="H59" s="80">
+      <c r="H59" s="11">
         <v>0.72139929479999998</v>
       </c>
-      <c r="I59" s="80">
+      <c r="I59" s="11">
         <v>0.61438299269999996</v>
       </c>
       <c r="J59" s="11">
@@ -7217,21 +7178,21 @@
       <c r="B60" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C60" s="71"/>
-      <c r="D60" s="71"/>
-      <c r="E60" s="80">
+      <c r="C60" s="69"/>
+      <c r="D60" s="69"/>
+      <c r="E60" s="11">
         <v>4.4103546999999998E-3</v>
       </c>
-      <c r="F60" s="80">
+      <c r="F60" s="11">
         <v>1.1505274000000001E-3</v>
       </c>
-      <c r="G60" s="80">
+      <c r="G60" s="11">
         <v>0.34458293379999999</v>
       </c>
-      <c r="H60" s="80">
+      <c r="H60" s="11">
         <v>0.49885476839999998</v>
       </c>
-      <c r="I60" s="80">
+      <c r="I60" s="11">
         <v>0.50106482159999999</v>
       </c>
       <c r="J60" s="11">
@@ -7254,21 +7215,21 @@
       <c r="B61" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C61" s="71"/>
-      <c r="D61" s="71"/>
-      <c r="E61" s="80">
+      <c r="C61" s="69"/>
+      <c r="D61" s="69"/>
+      <c r="E61" s="11">
         <v>2.8763183000000002E-3</v>
       </c>
-      <c r="F61" s="80">
+      <c r="F61" s="11">
         <v>2.0134228999999998E-3</v>
       </c>
-      <c r="G61" s="80">
+      <c r="G61" s="11">
         <v>0.51831255990000002</v>
       </c>
-      <c r="H61" s="80">
+      <c r="H61" s="11">
         <v>0.62305881009999997</v>
       </c>
-      <c r="I61" s="80">
+      <c r="I61" s="11">
         <v>0.5466724329</v>
       </c>
       <c r="J61" s="11">
@@ -7284,13 +7245,6 @@
         <v>0.33858670881999997</v>
       </c>
     </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="E62" s="80"/>
-      <c r="F62" s="80"/>
-      <c r="G62" s="80"/>
-      <c r="H62" s="80"/>
-      <c r="I62" s="80"/>
-    </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A63" s="1" t="s">
         <v>2</v>
@@ -7298,25 +7252,25 @@
       <c r="B63" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C63" s="71" t="s">
+      <c r="C63" s="69" t="s">
         <v>93</v>
       </c>
-      <c r="D63" s="71" t="s">
+      <c r="D63" s="69" t="s">
         <v>76</v>
       </c>
-      <c r="E63" s="80">
+      <c r="E63" s="11">
         <v>5.1006711400000002E-2</v>
       </c>
-      <c r="F63" s="80">
+      <c r="F63" s="11">
         <v>1.75455417E-2</v>
       </c>
-      <c r="G63" s="80">
+      <c r="G63" s="11">
         <v>0.14726749759999999</v>
       </c>
-      <c r="H63" s="80">
+      <c r="H63" s="11">
         <v>0.56786657309999999</v>
       </c>
-      <c r="I63" s="80">
+      <c r="I63" s="11">
         <v>0.33699644699999998</v>
       </c>
       <c r="J63" s="11">
@@ -7339,21 +7293,21 @@
       <c r="B64" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C64" s="71"/>
-      <c r="D64" s="71"/>
-      <c r="E64" s="80">
+      <c r="C64" s="69"/>
+      <c r="D64" s="69"/>
+      <c r="E64" s="11">
         <v>8.6289548999999993E-3</v>
       </c>
-      <c r="F64" s="80">
+      <c r="F64" s="11">
         <v>2.3010547000000001E-3</v>
       </c>
-      <c r="G64" s="80">
+      <c r="G64" s="11">
         <v>0.37871524449999999</v>
       </c>
-      <c r="H64" s="80">
+      <c r="H64" s="11">
         <v>0.5041079812</v>
       </c>
-      <c r="I64" s="80">
+      <c r="I64" s="11">
         <v>0.48737746469999998</v>
       </c>
       <c r="J64" s="11">
@@ -7376,21 +7330,21 @@
       <c r="B65" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C65" s="71"/>
-      <c r="D65" s="71"/>
-      <c r="E65" s="80">
+      <c r="C65" s="69"/>
+      <c r="D65" s="69"/>
+      <c r="E65" s="11">
         <v>1.9175455000000001E-3</v>
       </c>
-      <c r="F65" s="80">
+      <c r="F65" s="11">
         <v>4.9856184E-3</v>
       </c>
-      <c r="G65" s="80">
+      <c r="G65" s="11">
         <v>0.2151486098</v>
       </c>
-      <c r="H65" s="80">
+      <c r="H65" s="11">
         <v>0.57976032990000004</v>
       </c>
-      <c r="I65" s="80">
+      <c r="I65" s="11">
         <v>0.46813920380000001</v>
       </c>
       <c r="J65" s="11">
@@ -7407,12 +7361,12 @@
       </c>
     </row>
     <row r="68" spans="1:14" s="14" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="72" t="s">
+      <c r="A68" s="82" t="s">
         <v>59</v>
       </c>
-      <c r="B68" s="72"/>
-      <c r="C68" s="72"/>
-      <c r="D68" s="72"/>
+      <c r="B68" s="82"/>
+      <c r="C68" s="82"/>
+      <c r="D68" s="82"/>
       <c r="E68" s="16">
         <f t="shared" ref="E68:L68" si="2">MAX(E38:E66)</f>
         <v>9.0220517700000002E-2</v>
@@ -7491,17 +7445,17 @@
       <c r="N69" s="58"/>
     </row>
     <row r="71" spans="1:14" s="47" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A71" s="74" t="s">
+      <c r="A71" s="80" t="s">
         <v>94</v>
       </c>
-      <c r="B71" s="74"/>
-      <c r="C71" s="74"/>
-      <c r="D71" s="74"/>
-      <c r="E71" s="74"/>
-      <c r="F71" s="74"/>
-      <c r="G71" s="74"/>
-      <c r="H71" s="74"/>
-      <c r="I71" s="74"/>
+      <c r="B71" s="80"/>
+      <c r="C71" s="80"/>
+      <c r="D71" s="80"/>
+      <c r="E71" s="80"/>
+      <c r="F71" s="80"/>
+      <c r="G71" s="80"/>
+      <c r="H71" s="80"/>
+      <c r="I71" s="80"/>
       <c r="J71" s="49"/>
       <c r="K71" s="56"/>
       <c r="L71" s="56"/>
@@ -7520,17 +7474,17 @@
       <c r="K72" s="57"/>
       <c r="L72" s="57"/>
     </row>
-    <row r="73" spans="1:14" s="82" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A73" s="82" t="s">
+    <row r="73" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A73" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B73" s="82" t="s">
+      <c r="B73" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C73" s="86" t="s">
+      <c r="C73" s="69" t="s">
         <v>95</v>
       </c>
-      <c r="D73" s="86" t="s">
+      <c r="D73" s="69" t="s">
         <v>68</v>
       </c>
       <c r="E73" s="11">
@@ -7548,28 +7502,28 @@
       <c r="I73" s="11">
         <v>0.37861748220000002</v>
       </c>
-      <c r="J73" s="80">
+      <c r="J73" s="54">
         <f>SUM(E73*1/3,F73*1/3,H73*1/3)</f>
         <v>0.30501827056666669</v>
       </c>
-      <c r="K73" s="80">
+      <c r="K73" s="11">
         <f>SUM(G73*1/2,I73*1/2)</f>
         <v>0.34642696299999998</v>
       </c>
-      <c r="L73" s="80">
+      <c r="L73" s="11">
         <f>SUM(E73*1/5,F73*1/5,G73*1/5,H73*1/5,I73*1/5)</f>
         <v>0.32158174754000002</v>
       </c>
     </row>
-    <row r="74" spans="1:14" s="82" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A74" s="82" t="s">
+    <row r="74" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A74" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B74" s="82" t="s">
+      <c r="B74" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C74" s="86"/>
-      <c r="D74" s="86"/>
+      <c r="C74" s="69"/>
+      <c r="D74" s="69"/>
       <c r="E74" s="11">
         <v>8.8139489999999997E-3</v>
       </c>
@@ -7585,28 +7539,28 @@
       <c r="I74" s="11">
         <v>0.438803202</v>
       </c>
-      <c r="J74" s="80">
+      <c r="J74" s="11">
         <f>SUM(E74*1/3,F74*1/3,H74*1/3)</f>
         <v>0.24875506183333332</v>
       </c>
-      <c r="K74" s="80">
+      <c r="K74" s="11">
         <f>SUM(G74*1/2,I74*1/2)</f>
         <v>0.40372810035000001</v>
       </c>
-      <c r="L74" s="80">
+      <c r="L74" s="11">
         <f>SUM(E74*1/5,F74*1/5,G74*1/5,H74*1/5,I74*1/5)</f>
         <v>0.31074427723999998</v>
       </c>
     </row>
-    <row r="75" spans="1:14" s="82" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A75" s="82" t="s">
+    <row r="75" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A75" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B75" s="82" t="s">
+      <c r="B75" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C75" s="86"/>
-      <c r="D75" s="86"/>
+      <c r="C75" s="69"/>
+      <c r="D75" s="69"/>
       <c r="E75" s="11">
         <v>1.9160760000000001E-4</v>
       </c>
@@ -7622,42 +7576,30 @@
       <c r="I75" s="11">
         <v>0.47962761110000002</v>
       </c>
-      <c r="J75" s="80">
+      <c r="J75" s="11">
         <f>SUM(E75*1/3,F75*1/3,H75*1/3)</f>
         <v>0.16112890653333334</v>
       </c>
-      <c r="K75" s="80">
+      <c r="K75" s="11">
         <f>SUM(G75*1/2,I75*1/2)</f>
         <v>0.26194448190000003</v>
       </c>
-      <c r="L75" s="80">
+      <c r="L75" s="11">
         <f>SUM(E75*1/5,F75*1/5,G75*1/5,H75*1/5,I75*1/5)</f>
         <v>0.20145513668000001</v>
       </c>
     </row>
-    <row r="76" spans="1:14" s="82" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C76" s="87"/>
-      <c r="D76" s="87"/>
-      <c r="E76" s="80"/>
-      <c r="F76" s="80"/>
-      <c r="G76" s="80"/>
-      <c r="H76" s="80"/>
-      <c r="I76" s="80"/>
-      <c r="J76" s="80"/>
-      <c r="K76" s="80"/>
-      <c r="L76" s="80"/>
-    </row>
-    <row r="77" spans="1:14" s="82" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A77" s="82" t="s">
+    <row r="77" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A77" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B77" s="82" t="s">
+      <c r="B77" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C77" s="86" t="s">
+      <c r="C77" s="69" t="s">
         <v>96</v>
       </c>
-      <c r="D77" s="86" t="s">
+      <c r="D77" s="69" t="s">
         <v>70</v>
       </c>
       <c r="E77" s="11">
@@ -7675,28 +7617,28 @@
       <c r="I77" s="11">
         <v>0.45041272119999998</v>
       </c>
-      <c r="J77" s="80">
+      <c r="J77" s="11">
         <f>SUM(E77*1/3,F77*1/3,H77*1/3)</f>
         <v>0.30074588999999996</v>
       </c>
-      <c r="K77" s="80">
+      <c r="K77" s="11">
         <f>SUM(G77*1/2,I77*1/2)</f>
         <v>0.54001762715000001</v>
       </c>
-      <c r="L77" s="80">
+      <c r="L77" s="11">
         <f>SUM(E77*1/5,F77*1/5,G77*1/5,H77*1/5,I77*1/5)</f>
         <v>0.39645458486000001</v>
       </c>
     </row>
-    <row r="78" spans="1:14" s="82" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A78" s="82" t="s">
+    <row r="78" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A78" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B78" s="82" t="s">
+      <c r="B78" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C78" s="86"/>
-      <c r="D78" s="86"/>
+      <c r="C78" s="69"/>
+      <c r="D78" s="69"/>
       <c r="E78" s="11">
         <v>3.4489365999999999E-3</v>
       </c>
@@ -7712,28 +7654,28 @@
       <c r="I78" s="11">
         <v>0.48412258870000002</v>
       </c>
-      <c r="J78" s="80">
+      <c r="J78" s="11">
         <f>SUM(E78*1/3,F78*1/3,H78*1/3)</f>
         <v>0.1882646986</v>
       </c>
-      <c r="K78" s="80">
+      <c r="K78" s="11">
         <f>SUM(G78*1/2,I78*1/2)</f>
         <v>0.38365930165000001</v>
       </c>
-      <c r="L78" s="80">
+      <c r="L78" s="11">
         <f>SUM(E78*1/5,F78*1/5,G78*1/5,H78*1/5,I78*1/5)</f>
         <v>0.26642253981999997</v>
       </c>
     </row>
-    <row r="79" spans="1:14" s="82" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A79" s="82" t="s">
+    <row r="79" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A79" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B79" s="82" t="s">
+      <c r="B79" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C79" s="86"/>
-      <c r="D79" s="86"/>
+      <c r="C79" s="69"/>
+      <c r="D79" s="69"/>
       <c r="E79" s="62">
         <v>4.7901900000000002E-4</v>
       </c>
@@ -7749,534 +7691,600 @@
       <c r="I79" s="11">
         <v>0.47634846359999999</v>
       </c>
-      <c r="J79" s="80">
+      <c r="J79" s="11">
         <f>SUM(E79*1/3,F79*1/3,H79*1/3)</f>
         <v>0.17098087870000001</v>
       </c>
-      <c r="K79" s="80">
+      <c r="K79" s="11">
         <f>SUM(G79*1/2,I79*1/2)</f>
         <v>0.31759557690000001</v>
       </c>
-      <c r="L79" s="80">
+      <c r="L79" s="11">
         <f>SUM(E79*1/5,F79*1/5,G79*1/5,H79*1/5,I79*1/5)</f>
         <v>0.22962675798000001</v>
       </c>
     </row>
-    <row r="80" spans="1:14" s="82" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C80" s="87"/>
-      <c r="D80" s="87"/>
-      <c r="E80" s="80"/>
-      <c r="F80" s="80"/>
-      <c r="G80" s="80"/>
-      <c r="H80" s="80"/>
-      <c r="I80" s="80"/>
-      <c r="J80" s="80"/>
-      <c r="K80" s="80"/>
-      <c r="L80" s="80"/>
-    </row>
-    <row r="81" spans="1:12" s="82" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A81" s="82" t="s">
+    <row r="81" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A81" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B81" s="82" t="s">
+      <c r="B81" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C81" s="86" t="s">
+      <c r="C81" s="69" t="s">
         <v>97</v>
       </c>
-      <c r="D81" s="86" t="s">
+      <c r="D81" s="69" t="s">
         <v>81</v>
       </c>
-      <c r="E81" s="80"/>
-      <c r="F81" s="80"/>
-      <c r="G81" s="80"/>
-      <c r="H81" s="80"/>
-      <c r="I81" s="80"/>
-      <c r="J81" s="80">
+      <c r="E81" s="11">
+        <v>1.41789615E-2</v>
+      </c>
+      <c r="F81" s="11">
+        <v>3.8321517E-3</v>
+      </c>
+      <c r="G81" s="11">
+        <v>0.2103851313</v>
+      </c>
+      <c r="H81" s="11">
+        <v>0.49344389389999999</v>
+      </c>
+      <c r="I81" s="11">
+        <v>0.4601922155</v>
+      </c>
+      <c r="J81" s="11">
         <f>SUM(E81*1/3,F81*1/3,H81*1/3)</f>
+        <v>0.17048500236666667</v>
+      </c>
+      <c r="K81" s="11">
+        <f>SUM(G81*1/2,I81*1/2)</f>
+        <v>0.33528867340000001</v>
+      </c>
+      <c r="L81" s="11">
+        <f>SUM(E81*1/5,F81*1/5,G81*1/5,H81*1/5,I81*1/5)</f>
+        <v>0.23640647078000002</v>
+      </c>
+    </row>
+    <row r="82" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A82" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C82" s="69"/>
+      <c r="D82" s="69"/>
+      <c r="E82" s="11">
+        <v>4.3111707000000003E-3</v>
+      </c>
+      <c r="F82" s="11">
+        <v>2.5867024999999999E-3</v>
+      </c>
+      <c r="G82" s="11">
+        <v>0.31347001340000002</v>
+      </c>
+      <c r="H82" s="11">
+        <v>0.49771053859999997</v>
+      </c>
+      <c r="I82" s="11">
+        <v>0.49578055669999999</v>
+      </c>
+      <c r="J82" s="11">
+        <f>SUM(E82*1/3,F82*1/3,H82*1/3)</f>
+        <v>0.16820280393333331</v>
+      </c>
+      <c r="K82" s="11">
+        <f>SUM(G82*1/2,I82*1/2)</f>
+        <v>0.40462528505000001</v>
+      </c>
+      <c r="L82" s="11">
+        <f>SUM(E82*1/5,F82*1/5,G82*1/5,H82*1/5,I82*1/5)</f>
+        <v>0.26277179638000003</v>
+      </c>
+    </row>
+    <row r="83" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A83" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C83" s="69"/>
+      <c r="D83" s="69"/>
+      <c r="E83" s="11">
+        <v>2.1076835000000001E-3</v>
+      </c>
+      <c r="F83" s="11">
+        <v>2.4908986999999999E-3</v>
+      </c>
+      <c r="G83" s="11">
+        <v>0.46062464069999998</v>
+      </c>
+      <c r="H83" s="11">
+        <v>0.47368173790000001</v>
+      </c>
+      <c r="I83" s="11">
+        <v>0.48311123919999999</v>
+      </c>
+      <c r="J83" s="11">
+        <f>SUM(E83*1/3,F83*1/3,H83*1/3)</f>
+        <v>0.15942677336666666</v>
+      </c>
+      <c r="K83" s="11">
+        <f>SUM(G83*1/2,I83*1/2)</f>
+        <v>0.47186793994999998</v>
+      </c>
+      <c r="L83" s="11">
+        <f>SUM(E83*1/5,F83*1/5,G83*1/5,H83*1/5,I83*1/5)</f>
+        <v>0.28440324</v>
+      </c>
+    </row>
+    <row r="85" spans="1:12" s="84" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A85" s="84" t="s">
+        <v>2</v>
+      </c>
+      <c r="B85" s="84" t="s">
+        <v>5</v>
+      </c>
+      <c r="C85" s="69" t="s">
+        <v>98</v>
+      </c>
+      <c r="D85" s="69" t="s">
+        <v>79</v>
+      </c>
+      <c r="E85" s="85">
+        <v>4.7901900000000002E-4</v>
+      </c>
+      <c r="F85" s="85">
+        <v>3.6405442E-3</v>
+      </c>
+      <c r="G85" s="85">
+        <v>0.74458708559999998</v>
+      </c>
+      <c r="H85" s="85">
+        <v>0.70530976980000004</v>
+      </c>
+      <c r="I85" s="85">
+        <v>0.82515196759999998</v>
+      </c>
+      <c r="J85" s="85">
+        <f>SUM(E85*1/3,F85*1/3,H85*1/3)</f>
+        <v>0.23647644433333334</v>
+      </c>
+      <c r="K85" s="86">
+        <f>SUM(G85*1/2,I85*1/2)</f>
+        <v>0.78486952659999998</v>
+      </c>
+      <c r="L85" s="85">
+        <f>SUM(E85*1/5,F85*1/5,G85*1/5,H85*1/5,I85*1/5)</f>
+        <v>0.45583367724000001</v>
+      </c>
+    </row>
+    <row r="86" spans="1:12" s="42" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A86" s="42" t="s">
+        <v>3</v>
+      </c>
+      <c r="B86" s="42" t="s">
+        <v>6</v>
+      </c>
+      <c r="C86" s="69"/>
+      <c r="D86" s="69"/>
+      <c r="E86" s="83">
+        <v>2.24180878E-2</v>
+      </c>
+      <c r="F86" s="83">
+        <v>3.2573290000000002E-3</v>
+      </c>
+      <c r="G86" s="83">
+        <v>0.76911285689999997</v>
+      </c>
+      <c r="H86" s="83">
+        <v>0.87399711270000002</v>
+      </c>
+      <c r="I86" s="83">
+        <v>0.78457966379999999</v>
+      </c>
+      <c r="J86" s="83">
+        <f>SUM(E86*1/3,F86*1/3,H86*1/3)</f>
+        <v>0.2998908431666667</v>
+      </c>
+      <c r="K86" s="83">
+        <f>SUM(G86*1/2,I86*1/2)</f>
+        <v>0.77684626034999993</v>
+      </c>
+      <c r="L86" s="40">
+        <f>SUM(E86*1/5,F86*1/5,G86*1/5,H86*1/5,I86*1/5)</f>
+        <v>0.49067301003999997</v>
+      </c>
+    </row>
+    <row r="87" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A87" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C87" s="69"/>
+      <c r="D87" s="69"/>
+      <c r="E87" s="11">
         <v>0</v>
       </c>
-      <c r="K81" s="80">
-        <f>SUM(G81*1/2,I81*1/2)</f>
-        <v>0</v>
-      </c>
-      <c r="L81" s="80">
-        <f>SUM(E81*1/5,F81*1/5,G81*1/5,H81*1/5,I81*1/5)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" spans="1:12" s="82" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A82" s="82" t="s">
+      <c r="F87" s="11">
+        <v>9.5803800000000003E-4</v>
+      </c>
+      <c r="G87" s="11">
+        <v>5.8440314200000003E-2</v>
+      </c>
+      <c r="H87" s="11">
+        <v>0.49011553810000003</v>
+      </c>
+      <c r="I87" s="11">
+        <v>0.46326403129999999</v>
+      </c>
+      <c r="J87" s="11">
+        <f>SUM(E87*1/3,F87*1/3,H87*1/3)</f>
+        <v>0.16369119203333335</v>
+      </c>
+      <c r="K87" s="11">
+        <f>SUM(G87*1/2,I87*1/2)</f>
+        <v>0.26085217275</v>
+      </c>
+      <c r="L87" s="11">
+        <f>SUM(E87*1/5,F87*1/5,G87*1/5,H87*1/5,I87*1/5)</f>
+        <v>0.20255558432000001</v>
+      </c>
+    </row>
+    <row r="88" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="C88" s="50"/>
+    </row>
+    <row r="89" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A89" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C89" s="69" t="s">
+        <v>99</v>
+      </c>
+      <c r="D89" s="69" t="s">
+        <v>73</v>
+      </c>
+      <c r="E89" s="11">
+        <v>4.4165548999999998E-2</v>
+      </c>
+      <c r="F89" s="11">
+        <v>2.8166315300000001E-2</v>
+      </c>
+      <c r="G89" s="11">
+        <v>0.21670818159999999</v>
+      </c>
+      <c r="H89" s="11">
+        <v>0.73706262420000002</v>
+      </c>
+      <c r="I89" s="11">
+        <v>0.3688066217</v>
+      </c>
+      <c r="J89" s="11">
+        <f>SUM(E89*1/3,F89*1/3,H89*1/3)</f>
+        <v>0.26979816283333335</v>
+      </c>
+      <c r="K89" s="11">
+        <f>SUM(G89*1/2,I89*1/2)</f>
+        <v>0.29275740164999997</v>
+      </c>
+      <c r="L89" s="11">
+        <f>SUM(E89*1/5,F89*1/5,G89*1/5,H89*1/5,I89*1/5)</f>
+        <v>0.27898185836</v>
+      </c>
+    </row>
+    <row r="90" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A90" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B82" s="82" t="s">
+      <c r="B90" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C82" s="86"/>
-      <c r="D82" s="86"/>
-      <c r="E82" s="80"/>
-      <c r="F82" s="80"/>
-      <c r="G82" s="80"/>
-      <c r="H82" s="80"/>
-      <c r="I82" s="80"/>
-      <c r="J82" s="80">
-        <f>SUM(E82*1/3,F82*1/3,H82*1/3)</f>
-        <v>0</v>
-      </c>
-      <c r="K82" s="80">
-        <f>SUM(G82*1/2,I82*1/2)</f>
-        <v>0</v>
-      </c>
-      <c r="L82" s="80">
-        <f>SUM(E82*1/5,F82*1/5,G82*1/5,H82*1/5,I82*1/5)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="83" spans="1:12" s="82" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A83" s="82" t="s">
+      <c r="C90" s="69"/>
+      <c r="D90" s="69"/>
+      <c r="E90" s="11">
+        <v>1.59034298E-2</v>
+      </c>
+      <c r="F90" s="11">
+        <v>2.0118797000000001E-3</v>
+      </c>
+      <c r="G90" s="11">
+        <v>0.45717570419999998</v>
+      </c>
+      <c r="H90" s="11">
+        <v>0.59033409329999997</v>
+      </c>
+      <c r="I90" s="11">
+        <v>0.51348317779999997</v>
+      </c>
+      <c r="J90" s="11">
+        <f>SUM(E90*1/3,F90*1/3,H90*1/3)</f>
+        <v>0.20274980093333334</v>
+      </c>
+      <c r="K90" s="11">
+        <f>SUM(G90*1/2,I90*1/2)</f>
+        <v>0.48532944099999997</v>
+      </c>
+      <c r="L90" s="11">
+        <f>SUM(E90*1/5,F90*1/5,G90*1/5,H90*1/5,I90*1/5)</f>
+        <v>0.31578165695999999</v>
+      </c>
+    </row>
+    <row r="91" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A91" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B83" s="82" t="s">
+      <c r="B91" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C83" s="86"/>
-      <c r="D83" s="86"/>
-      <c r="E83" s="80"/>
-      <c r="F83" s="80"/>
-      <c r="G83" s="80"/>
-      <c r="H83" s="80"/>
-      <c r="I83" s="80"/>
-      <c r="J83" s="80">
-        <f>SUM(E83*1/3,F83*1/3,H83*1/3)</f>
-        <v>0</v>
-      </c>
-      <c r="K83" s="80">
-        <f>SUM(G83*1/2,I83*1/2)</f>
-        <v>0</v>
-      </c>
-      <c r="L83" s="80">
-        <f>SUM(E83*1/5,F83*1/5,G83*1/5,H83*1/5,I83*1/5)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="1:12" s="82" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C84" s="87"/>
-      <c r="D84" s="87"/>
-      <c r="E84" s="80"/>
-      <c r="F84" s="80"/>
-      <c r="G84" s="80"/>
-      <c r="H84" s="80"/>
-      <c r="I84" s="80"/>
-      <c r="J84" s="80"/>
-      <c r="K84" s="80"/>
-      <c r="L84" s="80"/>
-    </row>
-    <row r="85" spans="1:12" s="82" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A85" s="82" t="s">
-        <v>2</v>
-      </c>
-      <c r="B85" s="82" t="s">
-        <v>5</v>
-      </c>
-      <c r="C85" s="86" t="s">
-        <v>98</v>
-      </c>
-      <c r="D85" s="86" t="s">
-        <v>79</v>
-      </c>
-      <c r="E85" s="80"/>
-      <c r="F85" s="80"/>
-      <c r="G85" s="80"/>
-      <c r="H85" s="80"/>
-      <c r="I85" s="80"/>
-      <c r="J85" s="80">
-        <f>SUM(E85*1/3,F85*1/3,H85*1/3)</f>
-        <v>0</v>
-      </c>
-      <c r="K85" s="80">
-        <f>SUM(G85*1/2,I85*1/2)</f>
-        <v>0</v>
-      </c>
-      <c r="L85" s="80">
-        <f>SUM(E85*1/5,F85*1/5,G85*1/5,H85*1/5,I85*1/5)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="86" spans="1:12" s="82" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A86" s="82" t="s">
-        <v>3</v>
-      </c>
-      <c r="B86" s="82" t="s">
-        <v>6</v>
-      </c>
-      <c r="C86" s="86"/>
-      <c r="D86" s="86"/>
-      <c r="E86" s="80"/>
-      <c r="F86" s="80"/>
-      <c r="G86" s="80"/>
-      <c r="H86" s="80"/>
-      <c r="I86" s="80"/>
-      <c r="J86" s="80">
-        <f>SUM(E86*1/3,F86*1/3,H86*1/3)</f>
-        <v>0</v>
-      </c>
-      <c r="K86" s="80">
-        <f>SUM(G86*1/2,I86*1/2)</f>
-        <v>0</v>
-      </c>
-      <c r="L86" s="80">
-        <f>SUM(E86*1/5,F86*1/5,G86*1/5,H86*1/5,I86*1/5)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="87" spans="1:12" s="82" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A87" s="82" t="s">
-        <v>4</v>
-      </c>
-      <c r="B87" s="82" t="s">
-        <v>7</v>
-      </c>
-      <c r="C87" s="86"/>
-      <c r="D87" s="86"/>
-      <c r="E87" s="80"/>
-      <c r="F87" s="80"/>
-      <c r="G87" s="80"/>
-      <c r="H87" s="80"/>
-      <c r="I87" s="80"/>
-      <c r="J87" s="80">
-        <f>SUM(E87*1/3,F87*1/3,H87*1/3)</f>
-        <v>0</v>
-      </c>
-      <c r="K87" s="80">
-        <f>SUM(G87*1/2,I87*1/2)</f>
-        <v>0</v>
-      </c>
-      <c r="L87" s="80">
-        <f>SUM(E87*1/5,F87*1/5,G87*1/5,H87*1/5,I87*1/5)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="88" spans="1:12" s="82" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C88" s="88"/>
-      <c r="D88" s="87"/>
-      <c r="E88" s="80"/>
-      <c r="F88" s="80"/>
-      <c r="G88" s="80"/>
-      <c r="H88" s="80"/>
-      <c r="I88" s="80"/>
-      <c r="J88" s="80"/>
-      <c r="K88" s="80"/>
-      <c r="L88" s="80"/>
-    </row>
-    <row r="89" spans="1:12" s="82" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A89" s="82" t="s">
-        <v>2</v>
-      </c>
-      <c r="B89" s="82" t="s">
-        <v>5</v>
-      </c>
-      <c r="C89" s="86" t="s">
-        <v>99</v>
-      </c>
-      <c r="D89" s="86" t="s">
-        <v>73</v>
-      </c>
-      <c r="E89" s="80"/>
-      <c r="F89" s="80"/>
-      <c r="G89" s="80"/>
-      <c r="H89" s="80"/>
-      <c r="I89" s="80"/>
-      <c r="J89" s="80">
-        <f>SUM(E89*1/3,F89*1/3,H89*1/3)</f>
-        <v>0</v>
-      </c>
-      <c r="K89" s="80">
-        <f>SUM(G89*1/2,I89*1/2)</f>
-        <v>0</v>
-      </c>
-      <c r="L89" s="80">
-        <f>SUM(E89*1/5,F89*1/5,G89*1/5,H89*1/5,I89*1/5)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="1:12" s="82" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A90" s="82" t="s">
-        <v>3</v>
-      </c>
-      <c r="B90" s="82" t="s">
-        <v>6</v>
-      </c>
-      <c r="C90" s="86"/>
-      <c r="D90" s="86"/>
-      <c r="E90" s="80"/>
-      <c r="F90" s="80"/>
-      <c r="G90" s="80"/>
-      <c r="H90" s="80"/>
-      <c r="I90" s="80"/>
-      <c r="J90" s="80">
-        <f>SUM(E90*1/3,F90*1/3,H90*1/3)</f>
-        <v>0</v>
-      </c>
-      <c r="K90" s="80">
-        <f>SUM(G90*1/2,I90*1/2)</f>
-        <v>0</v>
-      </c>
-      <c r="L90" s="80">
-        <f>SUM(E90*1/5,F90*1/5,G90*1/5,H90*1/5,I90*1/5)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="91" spans="1:12" s="82" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A91" s="82" t="s">
-        <v>4</v>
-      </c>
-      <c r="B91" s="82" t="s">
-        <v>7</v>
-      </c>
-      <c r="C91" s="86"/>
-      <c r="D91" s="86"/>
-      <c r="E91" s="80"/>
-      <c r="F91" s="80"/>
-      <c r="G91" s="80"/>
-      <c r="H91" s="80"/>
-      <c r="I91" s="80"/>
-      <c r="J91" s="80">
+      <c r="C91" s="69"/>
+      <c r="D91" s="69"/>
+      <c r="J91" s="11">
         <f>SUM(E91*1/3,F91*1/3,H91*1/3)</f>
         <v>0</v>
       </c>
-      <c r="K91" s="80">
+      <c r="K91" s="11">
         <f>SUM(G91*1/2,I91*1/2)</f>
         <v>0</v>
       </c>
-      <c r="L91" s="80">
+      <c r="L91" s="11">
         <f>SUM(E91*1/5,F91*1/5,G91*1/5,H91*1/5,I91*1/5)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:12" s="82" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C92" s="87"/>
-      <c r="D92" s="87"/>
-      <c r="E92" s="80"/>
-      <c r="F92" s="80"/>
-      <c r="G92" s="80"/>
-      <c r="H92" s="80"/>
-      <c r="I92" s="80"/>
-      <c r="J92" s="80"/>
-      <c r="K92" s="80"/>
-      <c r="L92" s="80"/>
-    </row>
-    <row r="93" spans="1:12" s="82" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A93" s="82" t="s">
+    <row r="93" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A93" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B93" s="82" t="s">
+      <c r="B93" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C93" s="86" t="s">
+      <c r="C93" s="69" t="s">
         <v>100</v>
       </c>
-      <c r="D93" s="86" t="s">
+      <c r="D93" s="69" t="s">
         <v>75</v>
       </c>
-      <c r="E93" s="80"/>
-      <c r="F93" s="80"/>
-      <c r="G93" s="80"/>
-      <c r="H93" s="80"/>
-      <c r="I93" s="80"/>
-      <c r="J93" s="80">
+      <c r="E93" s="11">
+        <v>2.6537650900000001E-2</v>
+      </c>
+      <c r="F93" s="11">
+        <v>6.2272465999999999E-3</v>
+      </c>
+      <c r="G93" s="11">
+        <v>0.30906303889999998</v>
+      </c>
+      <c r="H93" s="11">
+        <v>0.65261878269999996</v>
+      </c>
+      <c r="I93" s="11">
+        <v>0.4517924425</v>
+      </c>
+      <c r="J93" s="11">
         <f>SUM(E93*1/3,F93*1/3,H93*1/3)</f>
-        <v>0</v>
-      </c>
-      <c r="K93" s="80">
+        <v>0.22846122673333333</v>
+      </c>
+      <c r="K93" s="11">
         <f>SUM(G93*1/2,I93*1/2)</f>
-        <v>0</v>
-      </c>
-      <c r="L93" s="80">
+        <v>0.38042774069999996</v>
+      </c>
+      <c r="L93" s="11">
         <f>SUM(E93*1/5,F93*1/5,G93*1/5,H93*1/5,I93*1/5)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="94" spans="1:12" s="82" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A94" s="82" t="s">
+        <v>0.28924783231999995</v>
+      </c>
+    </row>
+    <row r="94" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A94" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B94" s="82" t="s">
+      <c r="B94" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C94" s="86"/>
-      <c r="D94" s="86"/>
-      <c r="E94" s="80"/>
-      <c r="F94" s="80"/>
-      <c r="G94" s="80"/>
-      <c r="H94" s="80"/>
-      <c r="I94" s="80"/>
-      <c r="J94" s="80">
+      <c r="C94" s="69"/>
+      <c r="D94" s="69"/>
+      <c r="E94" s="11">
+        <v>9.4845755999999996E-3</v>
+      </c>
+      <c r="F94" s="11">
+        <v>1.2933512100000001E-2</v>
+      </c>
+      <c r="G94" s="11">
+        <v>0.35543207510000002</v>
+      </c>
+      <c r="H94" s="11">
+        <v>0.51356868389999999</v>
+      </c>
+      <c r="I94" s="11">
+        <v>0.4931959434</v>
+      </c>
+      <c r="J94" s="11">
         <f>SUM(E94*1/3,F94*1/3,H94*1/3)</f>
-        <v>0</v>
-      </c>
-      <c r="K94" s="80">
+        <v>0.17866225719999998</v>
+      </c>
+      <c r="K94" s="11">
         <f>SUM(G94*1/2,I94*1/2)</f>
-        <v>0</v>
-      </c>
-      <c r="L94" s="80">
+        <v>0.42431400925000001</v>
+      </c>
+      <c r="L94" s="11">
         <f>SUM(E94*1/5,F94*1/5,G94*1/5,H94*1/5,I94*1/5)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="1:12" s="82" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A95" s="82" t="s">
+        <v>0.27692295802</v>
+      </c>
+    </row>
+    <row r="95" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A95" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B95" s="82" t="s">
+      <c r="B95" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C95" s="86"/>
-      <c r="D95" s="86"/>
-      <c r="E95" s="80"/>
-      <c r="F95" s="80"/>
-      <c r="G95" s="80"/>
-      <c r="H95" s="80"/>
-      <c r="I95" s="80"/>
-      <c r="J95" s="80">
+      <c r="C95" s="69"/>
+      <c r="D95" s="69"/>
+      <c r="E95" s="11">
+        <v>1.9160760000000001E-4</v>
+      </c>
+      <c r="F95" s="11">
+        <v>2.5867024999999999E-3</v>
+      </c>
+      <c r="G95" s="11">
+        <v>0.67005173399999995</v>
+      </c>
+      <c r="H95" s="11">
+        <v>0.52593068870000004</v>
+      </c>
+      <c r="I95" s="11">
+        <v>0.4729815544</v>
+      </c>
+      <c r="J95" s="11">
         <f>SUM(E95*1/3,F95*1/3,H95*1/3)</f>
-        <v>0</v>
-      </c>
-      <c r="K95" s="80">
+        <v>0.17623633293333332</v>
+      </c>
+      <c r="K95" s="11">
         <f>SUM(G95*1/2,I95*1/2)</f>
-        <v>0</v>
-      </c>
-      <c r="L95" s="80">
+        <v>0.57151664419999992</v>
+      </c>
+      <c r="L95" s="11">
         <f>SUM(E95*1/5,F95*1/5,G95*1/5,H95*1/5,I95*1/5)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="96" spans="1:12" s="82" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C96" s="87"/>
-      <c r="D96" s="87"/>
-      <c r="E96" s="80"/>
-      <c r="F96" s="80"/>
-      <c r="G96" s="80"/>
-      <c r="H96" s="80"/>
-      <c r="I96" s="80"/>
-      <c r="J96" s="80"/>
-      <c r="K96" s="80"/>
-      <c r="L96" s="80"/>
-    </row>
-    <row r="97" spans="1:14" s="82" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A97" s="82" t="s">
+        <v>0.33434845743999997</v>
+      </c>
+    </row>
+    <row r="97" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A97" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B97" s="82" t="s">
+      <c r="B97" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C97" s="86" t="s">
+      <c r="C97" s="69" t="s">
         <v>101</v>
       </c>
-      <c r="D97" s="86" t="s">
+      <c r="D97" s="69" t="s">
         <v>76</v>
       </c>
-      <c r="E97" s="80"/>
-      <c r="F97" s="80"/>
-      <c r="G97" s="80"/>
-      <c r="H97" s="80"/>
-      <c r="I97" s="80"/>
-      <c r="J97" s="80">
+      <c r="E97" s="11">
+        <v>6.6104618E-3</v>
+      </c>
+      <c r="F97" s="11">
+        <v>3.9279555000000001E-3</v>
+      </c>
+      <c r="G97" s="11">
+        <v>0.18585936</v>
+      </c>
+      <c r="H97" s="11">
+        <v>0.43336886330000002</v>
+      </c>
+      <c r="I97" s="11">
+        <v>0.37657463089999998</v>
+      </c>
+      <c r="J97" s="11">
         <f>SUM(E97*1/3,F97*1/3,H97*1/3)</f>
-        <v>0</v>
-      </c>
-      <c r="K97" s="80">
+        <v>0.14796909353333332</v>
+      </c>
+      <c r="K97" s="11">
         <f>SUM(G97*1/2,I97*1/2)</f>
-        <v>0</v>
-      </c>
-      <c r="L97" s="80">
+        <v>0.28121699545000001</v>
+      </c>
+      <c r="L97" s="11">
         <f>SUM(E97*1/5,F97*1/5,G97*1/5,H97*1/5,I97*1/5)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="98" spans="1:14" s="82" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A98" s="82" t="s">
+        <v>0.2012682543</v>
+      </c>
+    </row>
+    <row r="98" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A98" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B98" s="82" t="s">
+      <c r="B98" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C98" s="86"/>
-      <c r="D98" s="86"/>
-      <c r="E98" s="80"/>
-      <c r="F98" s="80"/>
-      <c r="G98" s="80"/>
-      <c r="H98" s="80"/>
-      <c r="I98" s="80"/>
-      <c r="J98" s="80">
+      <c r="C98" s="69"/>
+      <c r="D98" s="69"/>
+      <c r="E98" s="11">
+        <v>8.9097528000000002E-3</v>
+      </c>
+      <c r="F98" s="11">
+        <v>3.3531327999999998E-3</v>
+      </c>
+      <c r="G98" s="11">
+        <v>0.36022226480000002</v>
+      </c>
+      <c r="H98" s="11">
+        <v>0.49774400880000003</v>
+      </c>
+      <c r="I98" s="11">
+        <v>0.48779777699999999</v>
+      </c>
+      <c r="J98" s="11">
         <f>SUM(E98*1/3,F98*1/3,H98*1/3)</f>
-        <v>0</v>
-      </c>
-      <c r="K98" s="80">
+        <v>0.17000229813333334</v>
+      </c>
+      <c r="K98" s="11">
         <f>SUM(G98*1/2,I98*1/2)</f>
-        <v>0</v>
-      </c>
-      <c r="L98" s="80">
+        <v>0.42401002090000001</v>
+      </c>
+      <c r="L98" s="11">
         <f>SUM(E98*1/5,F98*1/5,G98*1/5,H98*1/5,I98*1/5)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="99" spans="1:14" s="82" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A99" s="82" t="s">
+        <v>0.27160538724</v>
+      </c>
+    </row>
+    <row r="99" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A99" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B99" s="82" t="s">
+      <c r="B99" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C99" s="86"/>
-      <c r="D99" s="86"/>
-      <c r="E99" s="80"/>
-      <c r="F99" s="80"/>
-      <c r="G99" s="80"/>
-      <c r="H99" s="80"/>
-      <c r="I99" s="80"/>
-      <c r="J99" s="80">
+      <c r="C99" s="69"/>
+      <c r="D99" s="69"/>
+      <c r="E99" s="11">
+        <v>1.6286645000000001E-3</v>
+      </c>
+      <c r="F99" s="11">
+        <v>8.9097528999999998E-3</v>
+      </c>
+      <c r="G99" s="11">
+        <v>0.70549913779999995</v>
+      </c>
+      <c r="H99" s="11">
+        <v>0.56517988880000003</v>
+      </c>
+      <c r="I99" s="11">
+        <v>0.50091959919999995</v>
+      </c>
+      <c r="J99" s="11">
         <f>SUM(E99*1/3,F99*1/3,H99*1/3)</f>
-        <v>0</v>
-      </c>
-      <c r="K99" s="80">
+        <v>0.19190610206666667</v>
+      </c>
+      <c r="K99" s="11">
         <f>SUM(G99*1/2,I99*1/2)</f>
-        <v>0</v>
-      </c>
-      <c r="L99" s="80">
+        <v>0.60320936849999995</v>
+      </c>
+      <c r="L99" s="11">
         <f>SUM(E99*1/5,F99*1/5,G99*1/5,H99*1/5,I99*1/5)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="100" spans="1:14" s="82" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C100" s="87"/>
-      <c r="D100" s="87"/>
-      <c r="E100" s="80"/>
-      <c r="F100" s="80"/>
-      <c r="G100" s="80"/>
-      <c r="H100" s="80"/>
-      <c r="I100" s="80"/>
-      <c r="J100" s="80"/>
-      <c r="K100" s="80"/>
-      <c r="L100" s="80"/>
+        <v>0.35642740864</v>
+      </c>
     </row>
     <row r="102" spans="1:14" s="14" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A102" s="72" t="s">
+      <c r="A102" s="82" t="s">
         <v>59</v>
       </c>
-      <c r="B102" s="72"/>
-      <c r="C102" s="72"/>
-      <c r="D102" s="72"/>
+      <c r="B102" s="82"/>
+      <c r="C102" s="82"/>
+      <c r="D102" s="82"/>
       <c r="E102" s="16">
         <f t="shared" ref="E102:L102" si="4">MAX(E72:E100)</f>
-        <v>3.1423644399999999E-2</v>
+        <v>4.4165548999999998E-2</v>
       </c>
       <c r="F102" s="16">
         <f t="shared" si="4"/>
-        <v>2.0693619399999998E-2</v>
+        <v>2.8166315300000001E-2</v>
       </c>
       <c r="G102" s="16">
         <f t="shared" si="4"/>
-        <v>0.62962253310000005</v>
+        <v>0.76911285689999997</v>
       </c>
       <c r="H102" s="16">
         <f t="shared" si="4"/>
@@ -8284,7 +8292,7 @@
       </c>
       <c r="I102" s="16">
         <f t="shared" si="4"/>
-        <v>0.48412258870000002</v>
+        <v>0.82515196759999998</v>
       </c>
       <c r="J102" s="16">
         <f t="shared" si="4"/>
@@ -8292,11 +8300,11 @@
       </c>
       <c r="K102" s="16">
         <f t="shared" si="4"/>
-        <v>0.54001762715000001</v>
+        <v>0.78486952659999998</v>
       </c>
       <c r="L102" s="16">
         <f t="shared" si="4"/>
-        <v>0.39645458486000001</v>
+        <v>0.49067301003999997</v>
       </c>
       <c r="M102" s="16"/>
       <c r="N102" s="17"/>
@@ -8310,81 +8318,41 @@
       <c r="D103" s="77"/>
       <c r="E103" s="29">
         <f t="shared" ref="E103:L103" si="5">AVERAGE(E73:E100)</f>
-        <v>1.1959506933333331E-2</v>
+        <v>1.1434182804999998E-2</v>
       </c>
       <c r="F103" s="29">
         <f t="shared" si="5"/>
-        <v>5.5406527499999997E-3</v>
+        <v>5.9063039000000006E-3</v>
       </c>
       <c r="G103" s="29">
         <f t="shared" si="5"/>
-        <v>0.29980200551666669</v>
+        <v>0.38077217858000001</v>
       </c>
       <c r="H103" s="29">
         <f t="shared" si="5"/>
-        <v>0.66994669343333335</v>
+        <v>0.60348731926499988</v>
       </c>
       <c r="I103" s="29">
         <f t="shared" si="5"/>
-        <v>0.45132201146666667</v>
+        <v>0.49427817449000006</v>
       </c>
       <c r="J103" s="29">
         <f t="shared" si="5"/>
-        <v>6.5471128868253972E-2</v>
+        <v>0.19708819237142855</v>
       </c>
       <c r="K103" s="29">
         <f t="shared" si="5"/>
-        <v>0.10730343099761905</v>
+        <v>0.41669064431904768</v>
       </c>
       <c r="L103" s="29">
         <f t="shared" si="5"/>
-        <v>8.2204049719999991E-2</v>
+        <v>0.28492917315047628</v>
       </c>
       <c r="M103" s="29"/>
       <c r="N103" s="58"/>
     </row>
   </sheetData>
   <mergeCells count="51">
-    <mergeCell ref="A103:D103"/>
-    <mergeCell ref="C93:C95"/>
-    <mergeCell ref="D93:D95"/>
-    <mergeCell ref="C97:C99"/>
-    <mergeCell ref="D97:D99"/>
-    <mergeCell ref="A102:D102"/>
-    <mergeCell ref="C81:C83"/>
-    <mergeCell ref="D81:D83"/>
-    <mergeCell ref="C85:C87"/>
-    <mergeCell ref="D85:D87"/>
-    <mergeCell ref="C89:C91"/>
-    <mergeCell ref="D89:D91"/>
-    <mergeCell ref="A69:D69"/>
-    <mergeCell ref="A71:I71"/>
-    <mergeCell ref="C73:C75"/>
-    <mergeCell ref="D73:D75"/>
-    <mergeCell ref="C77:C79"/>
-    <mergeCell ref="D77:D79"/>
-    <mergeCell ref="C59:C61"/>
-    <mergeCell ref="D59:D61"/>
-    <mergeCell ref="C63:C65"/>
-    <mergeCell ref="D63:D65"/>
-    <mergeCell ref="A68:D68"/>
-    <mergeCell ref="C47:C49"/>
-    <mergeCell ref="D47:D49"/>
-    <mergeCell ref="C51:C53"/>
-    <mergeCell ref="D51:D53"/>
-    <mergeCell ref="C55:C57"/>
-    <mergeCell ref="D55:D57"/>
-    <mergeCell ref="A37:I37"/>
-    <mergeCell ref="C39:C41"/>
-    <mergeCell ref="D39:D41"/>
-    <mergeCell ref="C43:C45"/>
-    <mergeCell ref="D43:D45"/>
-    <mergeCell ref="A34:D34"/>
-    <mergeCell ref="A35:D35"/>
-    <mergeCell ref="C13:C15"/>
-    <mergeCell ref="D13:D15"/>
-    <mergeCell ref="C29:C31"/>
-    <mergeCell ref="D29:D31"/>
     <mergeCell ref="A3:I3"/>
     <mergeCell ref="C21:C23"/>
     <mergeCell ref="D21:D23"/>
@@ -8396,6 +8364,46 @@
     <mergeCell ref="C9:C11"/>
     <mergeCell ref="D17:D19"/>
     <mergeCell ref="C17:C19"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="C13:C15"/>
+    <mergeCell ref="D13:D15"/>
+    <mergeCell ref="C29:C31"/>
+    <mergeCell ref="D29:D31"/>
+    <mergeCell ref="A37:I37"/>
+    <mergeCell ref="C39:C41"/>
+    <mergeCell ref="D39:D41"/>
+    <mergeCell ref="C43:C45"/>
+    <mergeCell ref="D43:D45"/>
+    <mergeCell ref="C47:C49"/>
+    <mergeCell ref="D47:D49"/>
+    <mergeCell ref="C51:C53"/>
+    <mergeCell ref="D51:D53"/>
+    <mergeCell ref="C55:C57"/>
+    <mergeCell ref="D55:D57"/>
+    <mergeCell ref="C59:C61"/>
+    <mergeCell ref="D59:D61"/>
+    <mergeCell ref="C63:C65"/>
+    <mergeCell ref="D63:D65"/>
+    <mergeCell ref="A68:D68"/>
+    <mergeCell ref="A69:D69"/>
+    <mergeCell ref="A71:I71"/>
+    <mergeCell ref="C73:C75"/>
+    <mergeCell ref="D73:D75"/>
+    <mergeCell ref="C77:C79"/>
+    <mergeCell ref="D77:D79"/>
+    <mergeCell ref="C81:C83"/>
+    <mergeCell ref="D81:D83"/>
+    <mergeCell ref="C85:C87"/>
+    <mergeCell ref="D85:D87"/>
+    <mergeCell ref="C89:C91"/>
+    <mergeCell ref="D89:D91"/>
+    <mergeCell ref="A103:D103"/>
+    <mergeCell ref="C93:C95"/>
+    <mergeCell ref="D93:D95"/>
+    <mergeCell ref="C97:C99"/>
+    <mergeCell ref="D97:D99"/>
+    <mergeCell ref="A102:D102"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/benchmarking/results/results.xlsx
+++ b/benchmarking/results/results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/deborahdore/Documents/political-debates-graph-analysis/benchmarking/results/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{232E161B-BE29-F947-BD1B-83FE55367566}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{757F85C3-D682-6E44-B3C1-F6ACA5E93301}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="30240" windowHeight="18900" activeTab="3" xr2:uid="{E2EDC037-19C4-FE46-A599-BB595128A04F}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="51200" windowHeight="28800" activeTab="3" xr2:uid="{E2EDC037-19C4-FE46-A599-BB595128A04F}"/>
   </bookViews>
   <sheets>
     <sheet name="Results BASIC" sheetId="1" r:id="rId1"/>
@@ -533,7 +533,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="87">
+  <cellXfs count="84">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -730,11 +730,29 @@
     <xf numFmtId="164" fontId="5" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -742,19 +760,13 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -770,27 +782,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1174,13 +1165,13 @@
       <c r="B2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="73" t="s">
+      <c r="C2" s="72" t="s">
         <v>41</v>
       </c>
-      <c r="D2" s="70" t="s">
+      <c r="D2" s="71" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="70" t="s">
+      <c r="E2" s="71" t="s">
         <v>13</v>
       </c>
       <c r="F2" s="11">
@@ -1198,7 +1189,7 @@
       <c r="J2" s="11">
         <v>0.52440008120000003</v>
       </c>
-      <c r="K2" s="68" t="s">
+      <c r="K2" s="74" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1209,9 +1200,9 @@
       <c r="B3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="71"/>
-      <c r="D3" s="67"/>
-      <c r="E3" s="67"/>
+      <c r="C3" s="68"/>
+      <c r="D3" s="69"/>
+      <c r="E3" s="69"/>
       <c r="F3" s="11">
         <v>3.9117929099999997E-2</v>
       </c>
@@ -1227,7 +1218,7 @@
       <c r="J3" s="11">
         <v>0.4957882649</v>
       </c>
-      <c r="K3" s="69"/>
+      <c r="K3" s="75"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
@@ -1236,9 +1227,9 @@
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="71"/>
-      <c r="D4" s="67"/>
-      <c r="E4" s="67"/>
+      <c r="C4" s="68"/>
+      <c r="D4" s="69"/>
+      <c r="E4" s="69"/>
       <c r="F4" s="11">
         <v>2.1093001000000002E-3</v>
       </c>
@@ -1254,7 +1245,7 @@
       <c r="J4" s="11">
         <v>0.4776301698</v>
       </c>
-      <c r="K4" s="69"/>
+      <c r="K4" s="75"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
@@ -1263,13 +1254,13 @@
       <c r="B6" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="71" t="s">
+      <c r="C6" s="68" t="s">
         <v>42</v>
       </c>
-      <c r="D6" s="67" t="s">
+      <c r="D6" s="69" t="s">
         <v>10</v>
       </c>
-      <c r="E6" s="67" t="s">
+      <c r="E6" s="69" t="s">
         <v>13</v>
       </c>
       <c r="F6" s="11">
@@ -1287,7 +1278,7 @@
       <c r="J6" s="11">
         <v>0.51801477490000003</v>
       </c>
-      <c r="K6" s="69" t="s">
+      <c r="K6" s="75" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1298,9 +1289,9 @@
       <c r="B7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="71"/>
-      <c r="D7" s="67"/>
-      <c r="E7" s="67"/>
+      <c r="C7" s="68"/>
+      <c r="D7" s="69"/>
+      <c r="E7" s="69"/>
       <c r="F7" s="11">
         <v>3.2094270899999999E-2</v>
       </c>
@@ -1316,7 +1307,7 @@
       <c r="J7" s="11">
         <v>0.50083099880000004</v>
       </c>
-      <c r="K7" s="69"/>
+      <c r="K7" s="75"/>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
@@ -1325,9 +1316,9 @@
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="71"/>
-      <c r="D8" s="67"/>
-      <c r="E8" s="67"/>
+      <c r="C8" s="68"/>
+      <c r="D8" s="69"/>
+      <c r="E8" s="69"/>
       <c r="F8" s="11">
         <v>2.8741139999999998E-4</v>
       </c>
@@ -1343,15 +1334,15 @@
       <c r="J8" s="11">
         <v>0.4887305689</v>
       </c>
-      <c r="K8" s="69"/>
+      <c r="K8" s="75"/>
     </row>
     <row r="10" spans="1:12" s="59" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="72" t="s">
+      <c r="A10" s="70" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="72"/>
-      <c r="C10" s="72"/>
-      <c r="D10" s="72"/>
+      <c r="B10" s="70"/>
+      <c r="C10" s="70"/>
+      <c r="D10" s="70"/>
       <c r="E10" s="60"/>
       <c r="F10" s="61"/>
       <c r="G10" s="61"/>
@@ -1367,13 +1358,13 @@
       <c r="B12" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C12" s="71" t="s">
+      <c r="C12" s="68" t="s">
         <v>43</v>
       </c>
-      <c r="D12" s="67" t="s">
+      <c r="D12" s="69" t="s">
         <v>11</v>
       </c>
-      <c r="E12" s="67" t="s">
+      <c r="E12" s="69" t="s">
         <v>17</v>
       </c>
       <c r="F12" s="11">
@@ -1391,7 +1382,7 @@
       <c r="J12" s="11">
         <v>0.65087326729999995</v>
       </c>
-      <c r="K12" s="69" t="s">
+      <c r="K12" s="75" t="s">
         <v>18</v>
       </c>
     </row>
@@ -1402,9 +1393,9 @@
       <c r="B13" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C13" s="71"/>
-      <c r="D13" s="67"/>
-      <c r="E13" s="67"/>
+      <c r="C13" s="68"/>
+      <c r="D13" s="69"/>
+      <c r="E13" s="69"/>
       <c r="F13" s="11">
         <v>1.0937623800000001E-2</v>
       </c>
@@ -1420,7 +1411,7 @@
       <c r="J13" s="11">
         <v>0.48031703009999999</v>
       </c>
-      <c r="K13" s="69"/>
+      <c r="K13" s="75"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
@@ -1429,9 +1420,9 @@
       <c r="B14" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C14" s="71"/>
-      <c r="D14" s="67"/>
-      <c r="E14" s="67"/>
+      <c r="C14" s="68"/>
+      <c r="D14" s="69"/>
+      <c r="E14" s="69"/>
       <c r="F14" s="11">
         <v>2.377744E-4</v>
       </c>
@@ -1447,7 +1438,7 @@
       <c r="J14" s="11">
         <v>0.49770047779999999</v>
       </c>
-      <c r="K14" s="69"/>
+      <c r="K14" s="75"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
@@ -1456,13 +1447,13 @@
       <c r="B16" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C16" s="71" t="s">
+      <c r="C16" s="68" t="s">
         <v>44</v>
       </c>
-      <c r="D16" s="67" t="s">
+      <c r="D16" s="69" t="s">
         <v>19</v>
       </c>
-      <c r="E16" s="67" t="s">
+      <c r="E16" s="69" t="s">
         <v>27</v>
       </c>
       <c r="F16" s="11">
@@ -1480,7 +1471,7 @@
       <c r="J16" s="11">
         <v>0.44106115289999998</v>
       </c>
-      <c r="K16" s="69" t="s">
+      <c r="K16" s="75" t="s">
         <v>36</v>
       </c>
     </row>
@@ -1491,9 +1482,9 @@
       <c r="B17" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C17" s="71"/>
-      <c r="D17" s="67"/>
-      <c r="E17" s="67"/>
+      <c r="C17" s="68"/>
+      <c r="D17" s="69"/>
+      <c r="E17" s="69"/>
       <c r="F17" s="11">
         <v>6.6187922000000001E-3</v>
       </c>
@@ -1509,7 +1500,7 @@
       <c r="J17" s="11">
         <v>0.48203358359999998</v>
       </c>
-      <c r="K17" s="69"/>
+      <c r="K17" s="75"/>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
@@ -1518,9 +1509,9 @@
       <c r="B18" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C18" s="71"/>
-      <c r="D18" s="67"/>
-      <c r="E18" s="67"/>
+      <c r="C18" s="68"/>
+      <c r="D18" s="69"/>
+      <c r="E18" s="69"/>
       <c r="F18" s="11">
         <v>1.9467035999999999E-3</v>
       </c>
@@ -1536,7 +1527,7 @@
       <c r="J18" s="11">
         <v>0.31319458500000003</v>
       </c>
-      <c r="K18" s="69"/>
+      <c r="K18" s="75"/>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
@@ -1545,13 +1536,13 @@
       <c r="B20" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C20" s="71" t="s">
+      <c r="C20" s="68" t="s">
         <v>45</v>
       </c>
-      <c r="D20" s="67" t="s">
+      <c r="D20" s="69" t="s">
         <v>20</v>
       </c>
-      <c r="E20" s="67" t="s">
+      <c r="E20" s="69" t="s">
         <v>28</v>
       </c>
       <c r="F20" s="11">
@@ -1569,7 +1560,7 @@
       <c r="J20" s="11">
         <v>0.42558258160000001</v>
       </c>
-      <c r="K20" s="69" t="s">
+      <c r="K20" s="75" t="s">
         <v>35</v>
       </c>
     </row>
@@ -1580,9 +1571,9 @@
       <c r="B21" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C21" s="71"/>
-      <c r="D21" s="67"/>
-      <c r="E21" s="67"/>
+      <c r="C21" s="68"/>
+      <c r="D21" s="69"/>
+      <c r="E21" s="69"/>
       <c r="F21" s="11">
         <v>0.36964094320000002</v>
       </c>
@@ -1598,7 +1589,7 @@
       <c r="J21" s="11">
         <v>0.71370811339999995</v>
       </c>
-      <c r="K21" s="69"/>
+      <c r="K21" s="75"/>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
@@ -1607,9 +1598,9 @@
       <c r="B22" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C22" s="71"/>
-      <c r="D22" s="67"/>
-      <c r="E22" s="67"/>
+      <c r="C22" s="68"/>
+      <c r="D22" s="69"/>
+      <c r="E22" s="69"/>
       <c r="F22" s="11">
         <v>1.786352E-4</v>
       </c>
@@ -1625,7 +1616,7 @@
       <c r="J22" s="11">
         <v>0.35677707139999998</v>
       </c>
-      <c r="K22" s="69"/>
+      <c r="K22" s="75"/>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
@@ -1634,13 +1625,13 @@
       <c r="B24" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C24" s="71" t="s">
+      <c r="C24" s="68" t="s">
         <v>46</v>
       </c>
-      <c r="D24" s="67" t="s">
+      <c r="D24" s="69" t="s">
         <v>21</v>
       </c>
-      <c r="E24" s="67" t="s">
+      <c r="E24" s="69" t="s">
         <v>32</v>
       </c>
       <c r="F24" s="11">
@@ -1666,9 +1657,9 @@
       <c r="B25" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C25" s="71"/>
-      <c r="D25" s="67"/>
-      <c r="E25" s="67"/>
+      <c r="C25" s="68"/>
+      <c r="D25" s="69"/>
+      <c r="E25" s="69"/>
       <c r="F25" s="11">
         <v>2.2257384000000002E-2</v>
       </c>
@@ -1692,9 +1683,9 @@
       <c r="B26" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C26" s="71"/>
-      <c r="D26" s="67"/>
-      <c r="E26" s="67"/>
+      <c r="C26" s="68"/>
+      <c r="D26" s="69"/>
+      <c r="E26" s="69"/>
       <c r="F26" s="11">
         <v>3.9556960000000001E-4</v>
       </c>
@@ -1718,13 +1709,13 @@
       <c r="B28" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C28" s="71" t="s">
+      <c r="C28" s="68" t="s">
         <v>47</v>
       </c>
-      <c r="D28" s="67" t="s">
+      <c r="D28" s="69" t="s">
         <v>22</v>
       </c>
-      <c r="E28" s="67" t="s">
+      <c r="E28" s="69" t="s">
         <v>33</v>
       </c>
       <c r="F28" s="11">
@@ -1750,9 +1741,9 @@
       <c r="B29" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C29" s="71"/>
-      <c r="D29" s="67"/>
-      <c r="E29" s="67"/>
+      <c r="C29" s="68"/>
+      <c r="D29" s="69"/>
+      <c r="E29" s="69"/>
       <c r="F29" s="11">
         <v>1.8442843300000001E-2</v>
       </c>
@@ -1776,9 +1767,9 @@
       <c r="B30" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C30" s="71"/>
-      <c r="D30" s="67"/>
-      <c r="E30" s="67"/>
+      <c r="C30" s="68"/>
+      <c r="D30" s="69"/>
+      <c r="E30" s="69"/>
       <c r="F30" s="11">
         <v>6.9899990000000004E-4</v>
       </c>
@@ -1802,13 +1793,13 @@
       <c r="B32" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C32" s="71" t="s">
+      <c r="C32" s="68" t="s">
         <v>48</v>
       </c>
-      <c r="D32" s="67" t="s">
+      <c r="D32" s="69" t="s">
         <v>23</v>
       </c>
-      <c r="E32" s="67" t="s">
+      <c r="E32" s="69" t="s">
         <v>29</v>
       </c>
       <c r="F32" s="11">
@@ -1834,9 +1825,9 @@
       <c r="B33" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C33" s="71"/>
-      <c r="D33" s="67"/>
-      <c r="E33" s="67"/>
+      <c r="C33" s="68"/>
+      <c r="D33" s="69"/>
+      <c r="E33" s="69"/>
       <c r="F33" s="11">
         <v>4.8571429999999999E-4</v>
       </c>
@@ -1860,9 +1851,9 @@
       <c r="B34" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C34" s="71"/>
-      <c r="D34" s="67"/>
-      <c r="E34" s="67"/>
+      <c r="C34" s="68"/>
+      <c r="D34" s="69"/>
+      <c r="E34" s="69"/>
       <c r="F34" s="11">
         <v>8.5714299999999993E-5</v>
       </c>
@@ -1886,13 +1877,13 @@
       <c r="B36" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C36" s="71" t="s">
+      <c r="C36" s="68" t="s">
         <v>49</v>
       </c>
-      <c r="D36" s="67" t="s">
+      <c r="D36" s="69" t="s">
         <v>24</v>
       </c>
-      <c r="E36" s="67" t="s">
+      <c r="E36" s="69" t="s">
         <v>34</v>
       </c>
       <c r="F36" s="11">
@@ -1918,9 +1909,9 @@
       <c r="B37" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C37" s="71"/>
-      <c r="D37" s="67"/>
-      <c r="E37" s="67"/>
+      <c r="C37" s="68"/>
+      <c r="D37" s="69"/>
+      <c r="E37" s="69"/>
       <c r="F37" s="11">
         <v>0.12567659680000001</v>
       </c>
@@ -1944,9 +1935,9 @@
       <c r="B38" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C38" s="71"/>
-      <c r="D38" s="67"/>
-      <c r="E38" s="67"/>
+      <c r="C38" s="68"/>
+      <c r="D38" s="69"/>
+      <c r="E38" s="69"/>
       <c r="F38" s="11">
         <v>5.4127739999999998E-4</v>
       </c>
@@ -1964,12 +1955,12 @@
       </c>
     </row>
     <row r="40" spans="1:11" s="59" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="72" t="s">
+      <c r="A40" s="70" t="s">
         <v>38</v>
       </c>
-      <c r="B40" s="72"/>
-      <c r="C40" s="72"/>
-      <c r="D40" s="72"/>
+      <c r="B40" s="70"/>
+      <c r="C40" s="70"/>
+      <c r="D40" s="70"/>
       <c r="E40" s="60"/>
       <c r="F40" s="61"/>
       <c r="G40" s="61"/>
@@ -1985,13 +1976,13 @@
       <c r="B42" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C42" s="71" t="s">
+      <c r="C42" s="68" t="s">
         <v>50</v>
       </c>
-      <c r="D42" s="67" t="s">
+      <c r="D42" s="69" t="s">
         <v>25</v>
       </c>
-      <c r="E42" s="67" t="s">
+      <c r="E42" s="69" t="s">
         <v>27</v>
       </c>
       <c r="F42" s="11">
@@ -2009,7 +2000,7 @@
       <c r="J42" s="11">
         <v>0.47978398890000001</v>
       </c>
-      <c r="K42" s="69" t="s">
+      <c r="K42" s="75" t="s">
         <v>30</v>
       </c>
     </row>
@@ -2020,9 +2011,9 @@
       <c r="B43" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C43" s="71"/>
-      <c r="D43" s="67"/>
-      <c r="E43" s="67"/>
+      <c r="C43" s="68"/>
+      <c r="D43" s="69"/>
+      <c r="E43" s="69"/>
       <c r="F43" s="11">
         <v>0.15768715</v>
       </c>
@@ -2038,7 +2029,7 @@
       <c r="J43" s="11">
         <v>0.64265883619999997</v>
       </c>
-      <c r="K43" s="69"/>
+      <c r="K43" s="75"/>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
@@ -2047,9 +2038,9 @@
       <c r="B44" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C44" s="71"/>
-      <c r="D44" s="67"/>
-      <c r="E44" s="67"/>
+      <c r="C44" s="68"/>
+      <c r="D44" s="69"/>
+      <c r="E44" s="69"/>
       <c r="F44" s="11">
         <v>1.5776599999999999E-4</v>
       </c>
@@ -2065,7 +2056,7 @@
       <c r="J44" s="11">
         <v>0.33957444949999999</v>
       </c>
-      <c r="K44" s="69"/>
+      <c r="K44" s="75"/>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
@@ -2074,13 +2065,13 @@
       <c r="B46" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C46" s="71" t="s">
+      <c r="C46" s="68" t="s">
         <v>51</v>
       </c>
-      <c r="D46" s="67" t="s">
+      <c r="D46" s="69" t="s">
         <v>26</v>
       </c>
-      <c r="E46" s="67" t="s">
+      <c r="E46" s="69" t="s">
         <v>28</v>
       </c>
       <c r="F46" s="11">
@@ -2098,7 +2089,7 @@
       <c r="J46" s="11">
         <v>0.43650638670000003</v>
       </c>
-      <c r="K46" s="69" t="s">
+      <c r="K46" s="75" t="s">
         <v>31</v>
       </c>
     </row>
@@ -2109,9 +2100,9 @@
       <c r="B47" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C47" s="71"/>
-      <c r="D47" s="67"/>
-      <c r="E47" s="67"/>
+      <c r="C47" s="68"/>
+      <c r="D47" s="69"/>
+      <c r="E47" s="69"/>
       <c r="F47" s="11">
         <v>0.28846457310000001</v>
       </c>
@@ -2127,7 +2118,7 @@
       <c r="J47" s="11">
         <v>0.62979789600000002</v>
       </c>
-      <c r="K47" s="69"/>
+      <c r="K47" s="75"/>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
@@ -2136,9 +2127,9 @@
       <c r="B48" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C48" s="71"/>
-      <c r="D48" s="67"/>
-      <c r="E48" s="67"/>
+      <c r="C48" s="68"/>
+      <c r="D48" s="69"/>
+      <c r="E48" s="69"/>
       <c r="F48" s="11">
         <v>2.7615590000000002E-4</v>
       </c>
@@ -2154,7 +2145,7 @@
       <c r="J48" s="11">
         <v>0.39453545410000002</v>
       </c>
-      <c r="K48" s="69"/>
+      <c r="K48" s="75"/>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
@@ -2163,13 +2154,13 @@
       <c r="B50" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C50" s="71" t="s">
+      <c r="C50" s="68" t="s">
         <v>52</v>
       </c>
-      <c r="D50" s="67" t="s">
+      <c r="D50" s="69" t="s">
         <v>39</v>
       </c>
-      <c r="E50" s="67" t="s">
+      <c r="E50" s="69" t="s">
         <v>29</v>
       </c>
       <c r="F50" s="11">
@@ -2195,9 +2186,9 @@
       <c r="B51" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C51" s="71"/>
-      <c r="D51" s="67"/>
-      <c r="E51" s="67"/>
+      <c r="C51" s="68"/>
+      <c r="D51" s="69"/>
+      <c r="E51" s="69"/>
       <c r="F51" s="11">
         <v>3.5391416699999997E-2</v>
       </c>
@@ -2221,9 +2212,9 @@
       <c r="B52" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C52" s="71"/>
-      <c r="D52" s="67"/>
-      <c r="E52" s="67"/>
+      <c r="C52" s="68"/>
+      <c r="D52" s="69"/>
+      <c r="E52" s="69"/>
       <c r="F52" s="11">
         <v>9.9344299999999997E-5</v>
       </c>
@@ -2241,12 +2232,12 @@
       </c>
     </row>
     <row r="55" spans="1:11" s="42" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="74" t="s">
+      <c r="A55" s="67" t="s">
         <v>59</v>
       </c>
-      <c r="B55" s="74"/>
-      <c r="C55" s="74"/>
-      <c r="D55" s="74"/>
+      <c r="B55" s="67"/>
+      <c r="C55" s="67"/>
+      <c r="D55" s="67"/>
       <c r="E55" s="39"/>
       <c r="F55" s="40">
         <f>MAX(F2:F52)</f>
@@ -2271,12 +2262,12 @@
       <c r="K55" s="41"/>
     </row>
     <row r="56" spans="1:11" s="46" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="66" t="s">
+      <c r="A56" s="73" t="s">
         <v>60</v>
       </c>
-      <c r="B56" s="66"/>
-      <c r="C56" s="66"/>
-      <c r="D56" s="66"/>
+      <c r="B56" s="73"/>
+      <c r="C56" s="73"/>
+      <c r="D56" s="73"/>
       <c r="E56" s="43"/>
       <c r="F56" s="44">
         <f>AVERAGE(F2:F52)</f>
@@ -2302,37 +2293,6 @@
     </row>
   </sheetData>
   <mergeCells count="47">
-    <mergeCell ref="A55:D55"/>
-    <mergeCell ref="C6:C8"/>
-    <mergeCell ref="C12:C14"/>
-    <mergeCell ref="C16:C18"/>
-    <mergeCell ref="C20:C22"/>
-    <mergeCell ref="C24:C26"/>
-    <mergeCell ref="C50:C52"/>
-    <mergeCell ref="D24:D26"/>
-    <mergeCell ref="D28:D30"/>
-    <mergeCell ref="D32:D34"/>
-    <mergeCell ref="D36:D38"/>
-    <mergeCell ref="D42:D44"/>
-    <mergeCell ref="D46:D48"/>
-    <mergeCell ref="D50:D52"/>
-    <mergeCell ref="A40:D40"/>
-    <mergeCell ref="D2:D4"/>
-    <mergeCell ref="D6:D8"/>
-    <mergeCell ref="D12:D14"/>
-    <mergeCell ref="D16:D18"/>
-    <mergeCell ref="D20:D22"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="C2:C4"/>
-    <mergeCell ref="E12:E14"/>
-    <mergeCell ref="E16:E18"/>
-    <mergeCell ref="E20:E22"/>
-    <mergeCell ref="C42:C44"/>
-    <mergeCell ref="C46:C48"/>
-    <mergeCell ref="C28:C30"/>
-    <mergeCell ref="C32:C34"/>
-    <mergeCell ref="C36:C38"/>
-    <mergeCell ref="E46:E48"/>
     <mergeCell ref="A56:D56"/>
     <mergeCell ref="E50:E52"/>
     <mergeCell ref="K2:K4"/>
@@ -2349,6 +2309,37 @@
     <mergeCell ref="E42:E44"/>
     <mergeCell ref="E2:E4"/>
     <mergeCell ref="E6:E8"/>
+    <mergeCell ref="E12:E14"/>
+    <mergeCell ref="E16:E18"/>
+    <mergeCell ref="E20:E22"/>
+    <mergeCell ref="C42:C44"/>
+    <mergeCell ref="C46:C48"/>
+    <mergeCell ref="C28:C30"/>
+    <mergeCell ref="C32:C34"/>
+    <mergeCell ref="C36:C38"/>
+    <mergeCell ref="E46:E48"/>
+    <mergeCell ref="D2:D4"/>
+    <mergeCell ref="D6:D8"/>
+    <mergeCell ref="D12:D14"/>
+    <mergeCell ref="D16:D18"/>
+    <mergeCell ref="D20:D22"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="C2:C4"/>
+    <mergeCell ref="A55:D55"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="C12:C14"/>
+    <mergeCell ref="C16:C18"/>
+    <mergeCell ref="C20:C22"/>
+    <mergeCell ref="C24:C26"/>
+    <mergeCell ref="C50:C52"/>
+    <mergeCell ref="D24:D26"/>
+    <mergeCell ref="D28:D30"/>
+    <mergeCell ref="D32:D34"/>
+    <mergeCell ref="D36:D38"/>
+    <mergeCell ref="D42:D44"/>
+    <mergeCell ref="D46:D48"/>
+    <mergeCell ref="D50:D52"/>
+    <mergeCell ref="A40:D40"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2416,13 +2407,13 @@
       <c r="B2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="73" t="s">
+      <c r="C2" s="72" t="s">
         <v>41</v>
       </c>
-      <c r="D2" s="70" t="s">
+      <c r="D2" s="71" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="70" t="s">
+      <c r="E2" s="71" t="s">
         <v>13</v>
       </c>
       <c r="F2" s="11">
@@ -2440,7 +2431,7 @@
       <c r="J2" s="11">
         <v>0.5008326072</v>
       </c>
-      <c r="K2" s="68" t="s">
+      <c r="K2" s="74" t="s">
         <v>15</v>
       </c>
     </row>
@@ -2451,9 +2442,9 @@
       <c r="B3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="71"/>
-      <c r="D3" s="67"/>
-      <c r="E3" s="67"/>
+      <c r="C3" s="68"/>
+      <c r="D3" s="69"/>
+      <c r="E3" s="69"/>
       <c r="F3" s="11">
         <v>2.8763183099999999E-2</v>
       </c>
@@ -2469,7 +2460,7 @@
       <c r="J3" s="11">
         <v>0.49456959480000001</v>
       </c>
-      <c r="K3" s="69"/>
+      <c r="K3" s="75"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
@@ -2478,9 +2469,9 @@
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="71"/>
-      <c r="D4" s="67"/>
-      <c r="E4" s="67"/>
+      <c r="C4" s="68"/>
+      <c r="D4" s="69"/>
+      <c r="E4" s="69"/>
       <c r="F4" s="11">
         <v>5.7526370000000003E-4</v>
       </c>
@@ -2496,7 +2487,7 @@
       <c r="J4" s="11">
         <v>0.46208879800000002</v>
       </c>
-      <c r="K4" s="69"/>
+      <c r="K4" s="75"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="G5" s="11"/>
@@ -2511,13 +2502,13 @@
       <c r="B6" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="71" t="s">
+      <c r="C6" s="68" t="s">
         <v>42</v>
       </c>
-      <c r="D6" s="67" t="s">
+      <c r="D6" s="69" t="s">
         <v>10</v>
       </c>
-      <c r="E6" s="67" t="s">
+      <c r="E6" s="69" t="s">
         <v>13</v>
       </c>
       <c r="F6" s="11">
@@ -2535,7 +2526,7 @@
       <c r="J6" s="11">
         <v>0.50993042769999997</v>
       </c>
-      <c r="K6" s="69" t="s">
+      <c r="K6" s="75" t="s">
         <v>16</v>
       </c>
     </row>
@@ -2546,9 +2537,9 @@
       <c r="B7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="71"/>
-      <c r="D7" s="67"/>
-      <c r="E7" s="67"/>
+      <c r="C7" s="68"/>
+      <c r="D7" s="69"/>
+      <c r="E7" s="69"/>
       <c r="F7" s="11">
         <v>3.3435524000000001E-2</v>
       </c>
@@ -2564,7 +2555,7 @@
       <c r="J7" s="11">
         <v>0.50392556320000004</v>
       </c>
-      <c r="K7" s="69"/>
+      <c r="K7" s="75"/>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
@@ -2573,9 +2564,9 @@
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="71"/>
-      <c r="D8" s="67"/>
-      <c r="E8" s="67"/>
+      <c r="C8" s="68"/>
+      <c r="D8" s="69"/>
+      <c r="E8" s="69"/>
       <c r="F8" s="11">
         <v>3.8321520000000002E-4</v>
       </c>
@@ -2591,7 +2582,7 @@
       <c r="J8" s="11">
         <v>0.47738500210000001</v>
       </c>
-      <c r="K8" s="69"/>
+      <c r="K8" s="75"/>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="G9" s="11"/>
@@ -2600,12 +2591,12 @@
       <c r="J9" s="11"/>
     </row>
     <row r="10" spans="1:12" s="59" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="72" t="s">
+      <c r="A10" s="70" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="72"/>
-      <c r="C10" s="72"/>
-      <c r="D10" s="72"/>
+      <c r="B10" s="70"/>
+      <c r="C10" s="70"/>
+      <c r="D10" s="70"/>
       <c r="E10" s="60"/>
       <c r="F10" s="61"/>
       <c r="G10" s="61"/>
@@ -2627,13 +2618,13 @@
       <c r="B12" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C12" s="71" t="s">
+      <c r="C12" s="68" t="s">
         <v>43</v>
       </c>
-      <c r="D12" s="67" t="s">
+      <c r="D12" s="69" t="s">
         <v>11</v>
       </c>
-      <c r="E12" s="67" t="s">
+      <c r="E12" s="69" t="s">
         <v>17</v>
       </c>
       <c r="F12" s="11">
@@ -2651,7 +2642,7 @@
       <c r="J12" s="11">
         <v>0.4966675035</v>
       </c>
-      <c r="K12" s="69" t="s">
+      <c r="K12" s="75" t="s">
         <v>18</v>
       </c>
     </row>
@@ -2662,9 +2653,9 @@
       <c r="B13" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C13" s="71"/>
-      <c r="D13" s="67"/>
-      <c r="E13" s="67"/>
+      <c r="C13" s="68"/>
+      <c r="D13" s="69"/>
+      <c r="E13" s="69"/>
       <c r="F13" s="11">
         <v>2.876318E-4</v>
       </c>
@@ -2680,7 +2671,7 @@
       <c r="J13" s="11">
         <v>0.48225264400000001</v>
       </c>
-      <c r="K13" s="69"/>
+      <c r="K13" s="75"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
@@ -2689,9 +2680,9 @@
       <c r="B14" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C14" s="71"/>
-      <c r="D14" s="67"/>
-      <c r="E14" s="67"/>
+      <c r="C14" s="68"/>
+      <c r="D14" s="69"/>
+      <c r="E14" s="69"/>
       <c r="F14" s="11">
         <v>6.7114089999999996E-4</v>
       </c>
@@ -2707,7 +2698,7 @@
       <c r="J14" s="11">
         <v>0.43776818420000002</v>
       </c>
-      <c r="K14" s="69"/>
+      <c r="K14" s="75"/>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="G15" s="11"/>
@@ -2722,13 +2713,13 @@
       <c r="B16" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C16" s="71" t="s">
+      <c r="C16" s="68" t="s">
         <v>44</v>
       </c>
-      <c r="D16" s="67" t="s">
+      <c r="D16" s="69" t="s">
         <v>19</v>
       </c>
-      <c r="E16" s="67" t="s">
+      <c r="E16" s="69" t="s">
         <v>27</v>
       </c>
       <c r="F16" s="11">
@@ -2746,7 +2737,7 @@
       <c r="J16" s="11">
         <v>0.44130707470000002</v>
       </c>
-      <c r="K16" s="69" t="s">
+      <c r="K16" s="75" t="s">
         <v>36</v>
       </c>
     </row>
@@ -2757,9 +2748,9 @@
       <c r="B17" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C17" s="71"/>
-      <c r="D17" s="67"/>
-      <c r="E17" s="67"/>
+      <c r="C17" s="68"/>
+      <c r="D17" s="69"/>
+      <c r="E17" s="69"/>
       <c r="F17" s="11">
         <v>7.7660593999999998E-3</v>
       </c>
@@ -2775,7 +2766,7 @@
       <c r="J17" s="11">
         <v>0.46778393010000002</v>
       </c>
-      <c r="K17" s="69"/>
+      <c r="K17" s="75"/>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
@@ -2784,9 +2775,9 @@
       <c r="B18" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C18" s="71"/>
-      <c r="D18" s="67"/>
-      <c r="E18" s="67"/>
+      <c r="C18" s="68"/>
+      <c r="D18" s="69"/>
+      <c r="E18" s="69"/>
       <c r="F18" s="11">
         <v>2.876318E-4</v>
       </c>
@@ -2802,7 +2793,7 @@
       <c r="J18" s="11">
         <v>0.46815617929999997</v>
       </c>
-      <c r="K18" s="69"/>
+      <c r="K18" s="75"/>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.2">
       <c r="G19" s="11"/>
@@ -2817,13 +2808,13 @@
       <c r="B20" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C20" s="71" t="s">
+      <c r="C20" s="68" t="s">
         <v>45</v>
       </c>
-      <c r="D20" s="67" t="s">
+      <c r="D20" s="69" t="s">
         <v>20</v>
       </c>
-      <c r="E20" s="67" t="s">
+      <c r="E20" s="69" t="s">
         <v>28</v>
       </c>
       <c r="F20" s="11">
@@ -2841,7 +2832,7 @@
       <c r="J20" s="11">
         <v>0.4434595543</v>
       </c>
-      <c r="K20" s="69" t="s">
+      <c r="K20" s="75" t="s">
         <v>35</v>
       </c>
     </row>
@@ -2852,9 +2843,9 @@
       <c r="B21" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C21" s="71"/>
-      <c r="D21" s="67"/>
-      <c r="E21" s="67"/>
+      <c r="C21" s="68"/>
+      <c r="D21" s="69"/>
+      <c r="E21" s="69"/>
       <c r="F21" s="11">
         <v>5.11025887E-2</v>
       </c>
@@ -2870,7 +2861,7 @@
       <c r="J21" s="11">
         <v>0.46092753450000001</v>
       </c>
-      <c r="K21" s="69"/>
+      <c r="K21" s="75"/>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
@@ -2879,9 +2870,9 @@
       <c r="B22" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C22" s="71"/>
-      <c r="D22" s="67"/>
-      <c r="E22" s="67"/>
+      <c r="C22" s="68"/>
+      <c r="D22" s="69"/>
+      <c r="E22" s="69"/>
       <c r="F22" s="11">
         <v>0</v>
       </c>
@@ -2897,7 +2888,7 @@
       <c r="J22" s="11">
         <v>0.4740446935</v>
       </c>
-      <c r="K22" s="69"/>
+      <c r="K22" s="75"/>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.2">
       <c r="G23" s="11"/>
@@ -2912,13 +2903,13 @@
       <c r="B24" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C24" s="71" t="s">
+      <c r="C24" s="68" t="s">
         <v>46</v>
       </c>
-      <c r="D24" s="67" t="s">
+      <c r="D24" s="69" t="s">
         <v>21</v>
       </c>
-      <c r="E24" s="67" t="s">
+      <c r="E24" s="69" t="s">
         <v>32</v>
       </c>
       <c r="F24" s="11">
@@ -2944,9 +2935,9 @@
       <c r="B25" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C25" s="71"/>
-      <c r="D25" s="67"/>
-      <c r="E25" s="67"/>
+      <c r="C25" s="68"/>
+      <c r="D25" s="69"/>
+      <c r="E25" s="69"/>
       <c r="F25" s="11">
         <v>3.0584851400000002E-2</v>
       </c>
@@ -2970,9 +2961,9 @@
       <c r="B26" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C26" s="71"/>
-      <c r="D26" s="67"/>
-      <c r="E26" s="67"/>
+      <c r="C26" s="68"/>
+      <c r="D26" s="69"/>
+      <c r="E26" s="69"/>
       <c r="F26" s="11">
         <v>6.7114089999999996E-4</v>
       </c>
@@ -3002,13 +2993,13 @@
       <c r="B28" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C28" s="71" t="s">
+      <c r="C28" s="68" t="s">
         <v>47</v>
       </c>
-      <c r="D28" s="67" t="s">
+      <c r="D28" s="69" t="s">
         <v>22</v>
       </c>
-      <c r="E28" s="67" t="s">
+      <c r="E28" s="69" t="s">
         <v>33</v>
       </c>
       <c r="F28" s="11">
@@ -3034,9 +3025,9 @@
       <c r="B29" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C29" s="71"/>
-      <c r="D29" s="67"/>
-      <c r="E29" s="67"/>
+      <c r="C29" s="68"/>
+      <c r="D29" s="69"/>
+      <c r="E29" s="69"/>
       <c r="F29" s="11">
         <v>1.42857143E-2</v>
       </c>
@@ -3060,9 +3051,9 @@
       <c r="B30" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C30" s="71"/>
-      <c r="D30" s="67"/>
-      <c r="E30" s="67"/>
+      <c r="C30" s="68"/>
+      <c r="D30" s="69"/>
+      <c r="E30" s="69"/>
       <c r="F30" s="11">
         <v>3.8350910000000001E-4</v>
       </c>
@@ -3092,13 +3083,13 @@
       <c r="B32" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C32" s="71" t="s">
+      <c r="C32" s="68" t="s">
         <v>48</v>
       </c>
-      <c r="D32" s="67" t="s">
+      <c r="D32" s="69" t="s">
         <v>23</v>
       </c>
-      <c r="E32" s="67" t="s">
+      <c r="E32" s="69" t="s">
         <v>29</v>
       </c>
       <c r="F32" s="11">
@@ -3124,9 +3115,9 @@
       <c r="B33" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C33" s="71"/>
-      <c r="D33" s="67"/>
-      <c r="E33" s="67"/>
+      <c r="C33" s="68"/>
+      <c r="D33" s="69"/>
+      <c r="E33" s="69"/>
       <c r="F33" s="11">
         <v>6.9727237799999994E-2</v>
       </c>
@@ -3150,9 +3141,9 @@
       <c r="B34" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C34" s="71"/>
-      <c r="D34" s="67"/>
-      <c r="E34" s="67"/>
+      <c r="C34" s="68"/>
+      <c r="D34" s="69"/>
+      <c r="E34" s="69"/>
       <c r="F34" s="11">
         <v>2.8812910000000001E-4</v>
       </c>
@@ -3182,13 +3173,13 @@
       <c r="B36" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C36" s="71" t="s">
+      <c r="C36" s="68" t="s">
         <v>49</v>
       </c>
-      <c r="D36" s="67" t="s">
+      <c r="D36" s="69" t="s">
         <v>24</v>
       </c>
-      <c r="E36" s="67" t="s">
+      <c r="E36" s="69" t="s">
         <v>34</v>
       </c>
       <c r="F36" s="11">
@@ -3214,9 +3205,9 @@
       <c r="B37" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C37" s="71"/>
-      <c r="D37" s="67"/>
-      <c r="E37" s="67"/>
+      <c r="C37" s="68"/>
+      <c r="D37" s="69"/>
+      <c r="E37" s="69"/>
       <c r="F37" s="11">
         <v>1.4189837E-2</v>
       </c>
@@ -3240,9 +3231,9 @@
       <c r="B38" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C38" s="71"/>
-      <c r="D38" s="67"/>
-      <c r="E38" s="67"/>
+      <c r="C38" s="68"/>
+      <c r="D38" s="69"/>
+      <c r="E38" s="69"/>
       <c r="F38" s="11">
         <v>2.876318E-4</v>
       </c>
@@ -3266,12 +3257,12 @@
       <c r="J39" s="11"/>
     </row>
     <row r="40" spans="1:11" s="59" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="72" t="s">
+      <c r="A40" s="70" t="s">
         <v>38</v>
       </c>
-      <c r="B40" s="72"/>
-      <c r="C40" s="72"/>
-      <c r="D40" s="72"/>
+      <c r="B40" s="70"/>
+      <c r="C40" s="70"/>
+      <c r="D40" s="70"/>
       <c r="E40" s="60"/>
       <c r="F40" s="61"/>
       <c r="G40" s="61"/>
@@ -3293,13 +3284,13 @@
       <c r="B42" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C42" s="71" t="s">
+      <c r="C42" s="68" t="s">
         <v>50</v>
       </c>
-      <c r="D42" s="67" t="s">
+      <c r="D42" s="69" t="s">
         <v>25</v>
       </c>
-      <c r="E42" s="67" t="s">
+      <c r="E42" s="69" t="s">
         <v>27</v>
       </c>
       <c r="F42" s="11">
@@ -3317,7 +3308,7 @@
       <c r="J42" s="11">
         <v>0.4587482034</v>
       </c>
-      <c r="K42" s="69" t="s">
+      <c r="K42" s="75" t="s">
         <v>30</v>
       </c>
     </row>
@@ -3328,9 +3319,9 @@
       <c r="B43" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C43" s="71"/>
-      <c r="D43" s="67"/>
-      <c r="E43" s="67"/>
+      <c r="C43" s="68"/>
+      <c r="D43" s="69"/>
+      <c r="E43" s="69"/>
       <c r="F43" s="11">
         <v>1.34125311E-2</v>
       </c>
@@ -3346,7 +3337,7 @@
       <c r="J43" s="11">
         <v>0.46907909489999999</v>
       </c>
-      <c r="K43" s="69"/>
+      <c r="K43" s="75"/>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
@@ -3355,9 +3346,9 @@
       <c r="B44" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C44" s="71"/>
-      <c r="D44" s="67"/>
-      <c r="E44" s="67"/>
+      <c r="C44" s="68"/>
+      <c r="D44" s="69"/>
+      <c r="E44" s="69"/>
       <c r="F44" s="11">
         <v>8.6223409999999995E-4</v>
       </c>
@@ -3373,7 +3364,7 @@
       <c r="J44" s="11">
         <v>0.49390839069999998</v>
       </c>
-      <c r="K44" s="69"/>
+      <c r="K44" s="75"/>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.2">
       <c r="G45" s="11"/>
@@ -3388,13 +3379,13 @@
       <c r="B46" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C46" s="71" t="s">
+      <c r="C46" s="68" t="s">
         <v>51</v>
       </c>
-      <c r="D46" s="67" t="s">
+      <c r="D46" s="69" t="s">
         <v>26</v>
       </c>
-      <c r="E46" s="67" t="s">
+      <c r="E46" s="69" t="s">
         <v>28</v>
       </c>
       <c r="F46" s="11">
@@ -3412,7 +3403,7 @@
       <c r="J46" s="11">
         <v>0.45388746419999998</v>
       </c>
-      <c r="K46" s="69" t="s">
+      <c r="K46" s="75" t="s">
         <v>31</v>
       </c>
     </row>
@@ -3423,9 +3414,9 @@
       <c r="B47" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C47" s="71"/>
-      <c r="D47" s="67"/>
-      <c r="E47" s="67"/>
+      <c r="C47" s="68"/>
+      <c r="D47" s="69"/>
+      <c r="E47" s="69"/>
       <c r="F47" s="11">
         <v>4.3303314799999999E-2</v>
       </c>
@@ -3441,7 +3432,7 @@
       <c r="J47" s="11">
         <v>0.45908136910000003</v>
       </c>
-      <c r="K47" s="69"/>
+      <c r="K47" s="75"/>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
@@ -3450,9 +3441,9 @@
       <c r="B48" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C48" s="71"/>
-      <c r="D48" s="67"/>
-      <c r="E48" s="67"/>
+      <c r="C48" s="68"/>
+      <c r="D48" s="69"/>
+      <c r="E48" s="69"/>
       <c r="F48" s="11">
         <v>9.5803800000000006E-5</v>
       </c>
@@ -3468,7 +3459,7 @@
       <c r="J48" s="11">
         <v>0.478579698</v>
       </c>
-      <c r="K48" s="69"/>
+      <c r="K48" s="75"/>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.2">
       <c r="G49" s="11"/>
@@ -3483,13 +3474,13 @@
       <c r="B50" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C50" s="71" t="s">
+      <c r="C50" s="68" t="s">
         <v>52</v>
       </c>
-      <c r="D50" s="67" t="s">
+      <c r="D50" s="69" t="s">
         <v>39</v>
       </c>
-      <c r="E50" s="67" t="s">
+      <c r="E50" s="69" t="s">
         <v>29</v>
       </c>
       <c r="F50" s="11">
@@ -3515,9 +3506,9 @@
       <c r="B51" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C51" s="71"/>
-      <c r="D51" s="67"/>
-      <c r="E51" s="67"/>
+      <c r="C51" s="68"/>
+      <c r="D51" s="69"/>
+      <c r="E51" s="69"/>
       <c r="F51" s="11">
         <v>8.8139489999999997E-3</v>
       </c>
@@ -3541,9 +3532,9 @@
       <c r="B52" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C52" s="71"/>
-      <c r="D52" s="67"/>
-      <c r="E52" s="67"/>
+      <c r="C52" s="68"/>
+      <c r="D52" s="69"/>
+      <c r="E52" s="69"/>
       <c r="F52" s="11">
         <v>1.9160760000000001E-4</v>
       </c>
@@ -3573,12 +3564,12 @@
       <c r="J54" s="11"/>
     </row>
     <row r="55" spans="1:11" s="42" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="74" t="s">
+      <c r="A55" s="67" t="s">
         <v>59</v>
       </c>
-      <c r="B55" s="74"/>
-      <c r="C55" s="74"/>
-      <c r="D55" s="74"/>
+      <c r="B55" s="67"/>
+      <c r="C55" s="67"/>
+      <c r="D55" s="67"/>
       <c r="E55" s="39"/>
       <c r="F55" s="40">
         <f>MAX(F2:F52)</f>
@@ -3603,12 +3594,12 @@
       <c r="K55" s="41"/>
     </row>
     <row r="56" spans="1:11" s="46" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="66" t="s">
+      <c r="A56" s="73" t="s">
         <v>60</v>
       </c>
-      <c r="B56" s="66"/>
-      <c r="C56" s="66"/>
-      <c r="D56" s="66"/>
+      <c r="B56" s="73"/>
+      <c r="C56" s="73"/>
+      <c r="D56" s="73"/>
       <c r="E56" s="43"/>
       <c r="F56" s="44">
         <f>AVERAGE(F2:F52)</f>
@@ -3634,37 +3625,6 @@
     </row>
   </sheetData>
   <mergeCells count="47">
-    <mergeCell ref="A55:D55"/>
-    <mergeCell ref="K42:K44"/>
-    <mergeCell ref="C46:C48"/>
-    <mergeCell ref="D46:D48"/>
-    <mergeCell ref="E46:E48"/>
-    <mergeCell ref="K46:K48"/>
-    <mergeCell ref="E50:E52"/>
-    <mergeCell ref="C36:C38"/>
-    <mergeCell ref="D36:D38"/>
-    <mergeCell ref="E36:E38"/>
-    <mergeCell ref="A40:D40"/>
-    <mergeCell ref="C42:C44"/>
-    <mergeCell ref="D42:D44"/>
-    <mergeCell ref="E42:E44"/>
-    <mergeCell ref="K12:K14"/>
-    <mergeCell ref="C20:C22"/>
-    <mergeCell ref="D20:D22"/>
-    <mergeCell ref="E20:E22"/>
-    <mergeCell ref="K20:K22"/>
-    <mergeCell ref="C16:C18"/>
-    <mergeCell ref="D16:D18"/>
-    <mergeCell ref="E16:E18"/>
-    <mergeCell ref="K16:K18"/>
-    <mergeCell ref="C2:C4"/>
-    <mergeCell ref="D2:D4"/>
-    <mergeCell ref="E2:E4"/>
-    <mergeCell ref="K2:K4"/>
-    <mergeCell ref="C6:C8"/>
-    <mergeCell ref="D6:D8"/>
-    <mergeCell ref="E6:E8"/>
-    <mergeCell ref="K6:K8"/>
     <mergeCell ref="A56:D56"/>
     <mergeCell ref="A10:D10"/>
     <mergeCell ref="C12:C14"/>
@@ -3681,6 +3641,37 @@
     <mergeCell ref="E32:E34"/>
     <mergeCell ref="C50:C52"/>
     <mergeCell ref="D50:D52"/>
+    <mergeCell ref="C2:C4"/>
+    <mergeCell ref="D2:D4"/>
+    <mergeCell ref="E2:E4"/>
+    <mergeCell ref="K2:K4"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="D6:D8"/>
+    <mergeCell ref="E6:E8"/>
+    <mergeCell ref="K6:K8"/>
+    <mergeCell ref="K12:K14"/>
+    <mergeCell ref="C20:C22"/>
+    <mergeCell ref="D20:D22"/>
+    <mergeCell ref="E20:E22"/>
+    <mergeCell ref="K20:K22"/>
+    <mergeCell ref="C16:C18"/>
+    <mergeCell ref="D16:D18"/>
+    <mergeCell ref="E16:E18"/>
+    <mergeCell ref="K16:K18"/>
+    <mergeCell ref="C36:C38"/>
+    <mergeCell ref="D36:D38"/>
+    <mergeCell ref="E36:E38"/>
+    <mergeCell ref="A40:D40"/>
+    <mergeCell ref="C42:C44"/>
+    <mergeCell ref="D42:D44"/>
+    <mergeCell ref="E42:E44"/>
+    <mergeCell ref="A55:D55"/>
+    <mergeCell ref="K42:K44"/>
+    <mergeCell ref="C46:C48"/>
+    <mergeCell ref="D46:D48"/>
+    <mergeCell ref="E46:E48"/>
+    <mergeCell ref="K46:K48"/>
+    <mergeCell ref="E50:E52"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -3761,13 +3752,13 @@
       <c r="B2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="73" t="s">
+      <c r="C2" s="72" t="s">
         <v>41</v>
       </c>
-      <c r="D2" s="70" t="s">
+      <c r="D2" s="71" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="70" t="s">
+      <c r="E2" s="71" t="s">
         <v>13</v>
       </c>
       <c r="F2" s="11">
@@ -3797,7 +3788,7 @@
         <f>SUM(F2*1/5,G2*1/5,H2*1/5,I2*1/5,J2*1/5)</f>
         <v>0.29130368856</v>
       </c>
-      <c r="N2" s="68" t="s">
+      <c r="N2" s="74" t="s">
         <v>15</v>
       </c>
     </row>
@@ -3808,9 +3799,9 @@
       <c r="B3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="71"/>
-      <c r="D3" s="67"/>
-      <c r="E3" s="67"/>
+      <c r="C3" s="68"/>
+      <c r="D3" s="69"/>
+      <c r="E3" s="69"/>
       <c r="F3" s="11">
         <v>2.3969319E-3</v>
       </c>
@@ -3838,7 +3829,7 @@
         <f>SUM(F3*1/5,G3*1/5,H3*1/5,I3*1/5,J3*1/5)</f>
         <v>0.26225518991999996</v>
       </c>
-      <c r="N3" s="69"/>
+      <c r="N3" s="75"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
@@ -3847,9 +3838,9 @@
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="71"/>
-      <c r="D4" s="67"/>
-      <c r="E4" s="67"/>
+      <c r="C4" s="68"/>
+      <c r="D4" s="69"/>
+      <c r="E4" s="69"/>
       <c r="F4" s="11">
         <v>6.5867689399999999E-2</v>
       </c>
@@ -3877,7 +3868,7 @@
         <f>SUM(F4*1/5,G4*1/5,H4*1/5,I4*1/5,J4*1/5)</f>
         <v>0.29107094631999997</v>
       </c>
-      <c r="N4" s="69"/>
+      <c r="N4" s="75"/>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
@@ -3886,13 +3877,13 @@
       <c r="B6" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="71" t="s">
+      <c r="C6" s="68" t="s">
         <v>42</v>
       </c>
-      <c r="D6" s="67" t="s">
+      <c r="D6" s="69" t="s">
         <v>10</v>
       </c>
-      <c r="E6" s="67" t="s">
+      <c r="E6" s="69" t="s">
         <v>13</v>
       </c>
       <c r="F6" s="11">
@@ -3922,7 +3913,7 @@
         <f>SUM(F6*1/5,G6*1/5,H6*1/5,I6*1/5,J6*1/5)</f>
         <v>0.29438649154000002</v>
       </c>
-      <c r="N6" s="69" t="s">
+      <c r="N6" s="75" t="s">
         <v>16</v>
       </c>
     </row>
@@ -3933,9 +3924,9 @@
       <c r="B7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="71"/>
-      <c r="D7" s="67"/>
-      <c r="E7" s="67"/>
+      <c r="C7" s="68"/>
+      <c r="D7" s="69"/>
+      <c r="E7" s="69"/>
       <c r="F7" s="11">
         <v>1.3604138700000001E-2</v>
       </c>
@@ -3963,7 +3954,7 @@
         <f>SUM(F7*1/5,G7*1/5,H7*1/5,I7*1/5,J7*1/5)</f>
         <v>0.27579129901999999</v>
       </c>
-      <c r="N7" s="69"/>
+      <c r="N7" s="75"/>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
@@ -3972,9 +3963,9 @@
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="71"/>
-      <c r="D8" s="67"/>
-      <c r="E8" s="67"/>
+      <c r="C8" s="68"/>
+      <c r="D8" s="69"/>
+      <c r="E8" s="69"/>
       <c r="F8" s="11">
         <v>3.8321517499999999E-2</v>
       </c>
@@ -4002,15 +3993,15 @@
         <f>SUM(F8*1/5,G8*1/5,H8*1/5,I8*1/5,J8*1/5)</f>
         <v>0.2717815321</v>
       </c>
-      <c r="N8" s="69"/>
+      <c r="N8" s="75"/>
     </row>
     <row r="10" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="81" t="s">
+      <c r="A10" s="77" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="81"/>
-      <c r="C10" s="81"/>
-      <c r="D10" s="81"/>
+      <c r="B10" s="77"/>
+      <c r="C10" s="77"/>
+      <c r="D10" s="77"/>
       <c r="E10" s="5"/>
       <c r="F10" s="13"/>
       <c r="G10" s="13"/>
@@ -4029,13 +4020,13 @@
       <c r="B12" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C12" s="71" t="s">
+      <c r="C12" s="68" t="s">
         <v>43</v>
       </c>
-      <c r="D12" s="67" t="s">
+      <c r="D12" s="69" t="s">
         <v>11</v>
       </c>
-      <c r="E12" s="67" t="s">
+      <c r="E12" s="69" t="s">
         <v>17</v>
       </c>
       <c r="F12" s="11">
@@ -4065,7 +4056,7 @@
         <f>SUM(F12*1/5,G12*1/5,H12*1/5,I12*1/5,J12*1/5)</f>
         <v>0.33641501256</v>
       </c>
-      <c r="N12" s="69" t="s">
+      <c r="N12" s="75" t="s">
         <v>18</v>
       </c>
     </row>
@@ -4076,9 +4067,9 @@
       <c r="B13" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C13" s="71"/>
-      <c r="D13" s="67"/>
-      <c r="E13" s="67"/>
+      <c r="C13" s="68"/>
+      <c r="D13" s="69"/>
+      <c r="E13" s="69"/>
       <c r="F13" s="11">
         <v>7.9194630899999993E-2</v>
       </c>
@@ -4106,7 +4097,7 @@
         <f>SUM(F13*1/5,G13*1/5,H13*1/5,I13*1/5,J13*1/5)</f>
         <v>0.26691102733999994</v>
       </c>
-      <c r="N13" s="69"/>
+      <c r="N13" s="75"/>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
@@ -4115,9 +4106,9 @@
       <c r="B14" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C14" s="71"/>
-      <c r="D14" s="67"/>
-      <c r="E14" s="67"/>
+      <c r="C14" s="68"/>
+      <c r="D14" s="69"/>
+      <c r="E14" s="69"/>
       <c r="F14" s="11">
         <v>3.8350910000000001E-4</v>
       </c>
@@ -4145,7 +4136,7 @@
         <f>SUM(F14*1/5,G14*1/5,H14*1/5,I14*1/5,J14*1/5)</f>
         <v>0.22330577798000001</v>
       </c>
-      <c r="N14" s="69"/>
+      <c r="N14" s="75"/>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
@@ -4154,13 +4145,13 @@
       <c r="B16" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C16" s="71" t="s">
+      <c r="C16" s="68" t="s">
         <v>44</v>
       </c>
-      <c r="D16" s="67" t="s">
+      <c r="D16" s="69" t="s">
         <v>19</v>
       </c>
-      <c r="E16" s="67" t="s">
+      <c r="E16" s="69" t="s">
         <v>27</v>
       </c>
       <c r="F16" s="11">
@@ -4190,7 +4181,7 @@
         <f>SUM(F16*1/5,G16*1/5,H16*1/5,I16*1/5,J16*1/5)</f>
         <v>0.34767161497999999</v>
       </c>
-      <c r="N16" s="69" t="s">
+      <c r="N16" s="75" t="s">
         <v>36</v>
       </c>
     </row>
@@ -4201,9 +4192,9 @@
       <c r="B17" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C17" s="71"/>
-      <c r="D17" s="67"/>
-      <c r="E17" s="67"/>
+      <c r="C17" s="68"/>
+      <c r="D17" s="69"/>
+      <c r="E17" s="69"/>
       <c r="F17" s="11">
         <v>3.7296260800000001E-2</v>
       </c>
@@ -4231,7 +4222,7 @@
         <f>SUM(F17*1/5,G17*1/5,H17*1/5,I17*1/5,J17*1/5)</f>
         <v>0.33628517706000005</v>
       </c>
-      <c r="N17" s="69"/>
+      <c r="N17" s="75"/>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
@@ -4240,9 +4231,9 @@
       <c r="B18" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C18" s="71"/>
-      <c r="D18" s="67"/>
-      <c r="E18" s="67"/>
+      <c r="C18" s="68"/>
+      <c r="D18" s="69"/>
+      <c r="E18" s="69"/>
       <c r="F18" s="11">
         <v>1.0546500000000001E-3</v>
       </c>
@@ -4270,7 +4261,7 @@
         <f>SUM(F18*1/5,G18*1/5,H18*1/5,I18*1/5,J18*1/5)</f>
         <v>0.20704430204000002</v>
       </c>
-      <c r="N18" s="69"/>
+      <c r="N18" s="75"/>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
@@ -4279,13 +4270,13 @@
       <c r="B20" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C20" s="71" t="s">
+      <c r="C20" s="68" t="s">
         <v>45</v>
       </c>
-      <c r="D20" s="67" t="s">
+      <c r="D20" s="69" t="s">
         <v>20</v>
       </c>
-      <c r="E20" s="67" t="s">
+      <c r="E20" s="69" t="s">
         <v>28</v>
       </c>
       <c r="F20" s="11">
@@ -4315,7 +4306,7 @@
         <f>SUM(F20*1/5,G20*1/5,H20*1/5,I20*1/5,J20*1/5)</f>
         <v>0.31181358595999997</v>
       </c>
-      <c r="N20" s="69" t="s">
+      <c r="N20" s="75" t="s">
         <v>35</v>
       </c>
     </row>
@@ -4326,9 +4317,9 @@
       <c r="B21" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C21" s="71"/>
-      <c r="D21" s="67"/>
-      <c r="E21" s="67"/>
+      <c r="C21" s="68"/>
+      <c r="D21" s="69"/>
+      <c r="E21" s="69"/>
       <c r="F21" s="11">
         <v>1.05465005E-2</v>
       </c>
@@ -4356,7 +4347,7 @@
         <f>SUM(F21*1/5,G21*1/5,H21*1/5,I21*1/5,J21*1/5)</f>
         <v>0.29879759264</v>
       </c>
-      <c r="N21" s="69"/>
+      <c r="N21" s="75"/>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
@@ -4365,9 +4356,9 @@
       <c r="B22" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C22" s="71"/>
-      <c r="D22" s="67"/>
-      <c r="E22" s="67"/>
+      <c r="C22" s="68"/>
+      <c r="D22" s="69"/>
+      <c r="E22" s="69"/>
       <c r="F22" s="11">
         <v>0</v>
       </c>
@@ -4395,7 +4386,7 @@
         <f>SUM(F22*1/5,G22*1/5,H22*1/5,I22*1/5,J22*1/5)</f>
         <v>0.22541820497999998</v>
       </c>
-      <c r="N22" s="69"/>
+      <c r="N22" s="75"/>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
@@ -4404,13 +4395,13 @@
       <c r="B24" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C24" s="71" t="s">
+      <c r="C24" s="68" t="s">
         <v>46</v>
       </c>
-      <c r="D24" s="67" t="s">
+      <c r="D24" s="69" t="s">
         <v>21</v>
       </c>
-      <c r="E24" s="67" t="s">
+      <c r="E24" s="69" t="s">
         <v>32</v>
       </c>
       <c r="F24" s="11">
@@ -4448,9 +4439,9 @@
       <c r="B25" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C25" s="71"/>
-      <c r="D25" s="67"/>
-      <c r="E25" s="67"/>
+      <c r="C25" s="68"/>
+      <c r="D25" s="69"/>
+      <c r="E25" s="69"/>
       <c r="F25" s="11">
         <v>2.7229146700000002E-2</v>
       </c>
@@ -4486,9 +4477,9 @@
       <c r="B26" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C26" s="71"/>
-      <c r="D26" s="67"/>
-      <c r="E26" s="67"/>
+      <c r="C26" s="68"/>
+      <c r="D26" s="69"/>
+      <c r="E26" s="69"/>
       <c r="F26" s="11">
         <v>3.8350910000000001E-4</v>
       </c>
@@ -4524,13 +4515,13 @@
       <c r="B28" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C28" s="71" t="s">
+      <c r="C28" s="68" t="s">
         <v>47</v>
       </c>
-      <c r="D28" s="67" t="s">
+      <c r="D28" s="69" t="s">
         <v>22</v>
       </c>
-      <c r="E28" s="67" t="s">
+      <c r="E28" s="69" t="s">
         <v>33</v>
       </c>
       <c r="F28" s="11">
@@ -4568,9 +4559,9 @@
       <c r="B29" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C29" s="71"/>
-      <c r="D29" s="67"/>
-      <c r="E29" s="67"/>
+      <c r="C29" s="68"/>
+      <c r="D29" s="69"/>
+      <c r="E29" s="69"/>
       <c r="F29" s="11">
         <v>2.8475551299999999E-2</v>
       </c>
@@ -4606,9 +4597,9 @@
       <c r="B30" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C30" s="71"/>
-      <c r="D30" s="67"/>
-      <c r="E30" s="67"/>
+      <c r="C30" s="68"/>
+      <c r="D30" s="69"/>
+      <c r="E30" s="69"/>
       <c r="F30" s="11">
         <v>1.917546E-4</v>
       </c>
@@ -4644,13 +4635,13 @@
       <c r="B32" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C32" s="71" t="s">
+      <c r="C32" s="68" t="s">
         <v>48</v>
       </c>
-      <c r="D32" s="67" t="s">
+      <c r="D32" s="69" t="s">
         <v>23</v>
       </c>
-      <c r="E32" s="67" t="s">
+      <c r="E32" s="69" t="s">
         <v>29</v>
       </c>
       <c r="F32" s="11">
@@ -4688,9 +4679,9 @@
       <c r="B33" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C33" s="71"/>
-      <c r="D33" s="67"/>
-      <c r="E33" s="67"/>
+      <c r="C33" s="68"/>
+      <c r="D33" s="69"/>
+      <c r="E33" s="69"/>
       <c r="F33" s="11">
         <v>2.4010757000000001E-3</v>
       </c>
@@ -4726,9 +4717,9 @@
       <c r="B34" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C34" s="71"/>
-      <c r="D34" s="67"/>
-      <c r="E34" s="67"/>
+      <c r="C34" s="68"/>
+      <c r="D34" s="69"/>
+      <c r="E34" s="69"/>
       <c r="F34" s="11">
         <v>0</v>
       </c>
@@ -4764,13 +4755,13 @@
       <c r="B36" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C36" s="71" t="s">
+      <c r="C36" s="68" t="s">
         <v>49</v>
       </c>
-      <c r="D36" s="67" t="s">
+      <c r="D36" s="69" t="s">
         <v>24</v>
       </c>
-      <c r="E36" s="67" t="s">
+      <c r="E36" s="69" t="s">
         <v>34</v>
       </c>
       <c r="F36" s="11">
@@ -4808,9 +4799,9 @@
       <c r="B37" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C37" s="71"/>
-      <c r="D37" s="67"/>
-      <c r="E37" s="67"/>
+      <c r="C37" s="68"/>
+      <c r="D37" s="69"/>
+      <c r="E37" s="69"/>
       <c r="F37" s="11">
         <v>5.9443912000000003E-3</v>
       </c>
@@ -4846,9 +4837,9 @@
       <c r="B38" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C38" s="71"/>
-      <c r="D38" s="67"/>
-      <c r="E38" s="67"/>
+      <c r="C38" s="68"/>
+      <c r="D38" s="69"/>
+      <c r="E38" s="69"/>
       <c r="F38" s="11">
         <v>1.917546E-4</v>
       </c>
@@ -4878,12 +4869,12 @@
       </c>
     </row>
     <row r="40" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="81" t="s">
+      <c r="A40" s="77" t="s">
         <v>38</v>
       </c>
-      <c r="B40" s="81"/>
-      <c r="C40" s="81"/>
-      <c r="D40" s="81"/>
+      <c r="B40" s="77"/>
+      <c r="C40" s="77"/>
+      <c r="D40" s="77"/>
       <c r="E40" s="5"/>
       <c r="F40" s="13"/>
       <c r="G40" s="13"/>
@@ -4902,13 +4893,13 @@
       <c r="B42" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C42" s="71" t="s">
+      <c r="C42" s="68" t="s">
         <v>50</v>
       </c>
-      <c r="D42" s="67" t="s">
+      <c r="D42" s="69" t="s">
         <v>25</v>
       </c>
-      <c r="E42" s="67" t="s">
+      <c r="E42" s="69" t="s">
         <v>27</v>
       </c>
       <c r="F42" s="11">
@@ -4938,7 +4929,7 @@
         <f>SUM(F42*1/5,G42*1/5,H42*1/5,I42*1/5,J42*1/5)</f>
         <v>0.32911788728000002</v>
       </c>
-      <c r="N42" s="69" t="s">
+      <c r="N42" s="75" t="s">
         <v>30</v>
       </c>
     </row>
@@ -4949,9 +4940,9 @@
       <c r="B43" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C43" s="71"/>
-      <c r="D43" s="67"/>
-      <c r="E43" s="67"/>
+      <c r="C43" s="68"/>
+      <c r="D43" s="69"/>
+      <c r="E43" s="69"/>
       <c r="F43" s="11">
         <v>1.59034298E-2</v>
       </c>
@@ -4979,7 +4970,7 @@
         <f>SUM(F43*1/5,G43*1/5,H43*1/5,I43*1/5,J43*1/5)</f>
         <v>0.33481998118</v>
       </c>
-      <c r="N43" s="69"/>
+      <c r="N43" s="75"/>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
@@ -4988,9 +4979,9 @@
       <c r="B44" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C44" s="71"/>
-      <c r="D44" s="67"/>
-      <c r="E44" s="67"/>
+      <c r="C44" s="68"/>
+      <c r="D44" s="69"/>
+      <c r="E44" s="69"/>
       <c r="F44" s="62">
         <v>0</v>
       </c>
@@ -5018,7 +5009,7 @@
         <f>SUM(F44*1/5,G44*1/5,H44*1/5,I44*1/5,J44*1/5)</f>
         <v>0.23017129817999998</v>
       </c>
-      <c r="N44" s="69"/>
+      <c r="N44" s="75"/>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
@@ -5027,13 +5018,13 @@
       <c r="B46" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C46" s="71" t="s">
+      <c r="C46" s="68" t="s">
         <v>51</v>
       </c>
-      <c r="D46" s="67" t="s">
+      <c r="D46" s="69" t="s">
         <v>26</v>
       </c>
-      <c r="E46" s="67" t="s">
+      <c r="E46" s="69" t="s">
         <v>28</v>
       </c>
       <c r="F46" s="11">
@@ -5063,7 +5054,7 @@
         <f>SUM(F46*1/5,G46*1/5,H46*1/5,I46*1/5,J46*1/5)</f>
         <v>0.28403192430000002</v>
       </c>
-      <c r="N46" s="69" t="s">
+      <c r="N46" s="75" t="s">
         <v>31</v>
       </c>
     </row>
@@ -5074,9 +5065,9 @@
       <c r="B47" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C47" s="71"/>
-      <c r="D47" s="67"/>
-      <c r="E47" s="67"/>
+      <c r="C47" s="68"/>
+      <c r="D47" s="69"/>
+      <c r="E47" s="69"/>
       <c r="F47" s="11">
         <v>2.90285495E-2</v>
       </c>
@@ -5104,7 +5095,7 @@
         <f>SUM(F47*1/5,G47*1/5,H47*1/5,I47*1/5,J47*1/5)</f>
         <v>0.35089340806000002</v>
       </c>
-      <c r="N47" s="69"/>
+      <c r="N47" s="75"/>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
@@ -5113,9 +5104,9 @@
       <c r="B48" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C48" s="71"/>
-      <c r="D48" s="67"/>
-      <c r="E48" s="67"/>
+      <c r="C48" s="68"/>
+      <c r="D48" s="69"/>
+      <c r="E48" s="69"/>
       <c r="F48" s="11">
         <v>1.9160760000000001E-4</v>
       </c>
@@ -5143,7 +5134,7 @@
         <f>SUM(F48*1/5,G48*1/5,H48*1/5,I48*1/5,J48*1/5)</f>
         <v>0.34178323869999999</v>
       </c>
-      <c r="N48" s="69"/>
+      <c r="N48" s="75"/>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
@@ -5152,13 +5143,13 @@
       <c r="B50" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C50" s="71" t="s">
+      <c r="C50" s="68" t="s">
         <v>52</v>
       </c>
-      <c r="D50" s="67" t="s">
+      <c r="D50" s="69" t="s">
         <v>39</v>
       </c>
-      <c r="E50" s="67" t="s">
+      <c r="E50" s="69" t="s">
         <v>29</v>
       </c>
       <c r="F50" s="11">
@@ -5196,9 +5187,9 @@
       <c r="B51" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C51" s="71"/>
-      <c r="D51" s="67"/>
-      <c r="E51" s="67"/>
+      <c r="C51" s="68"/>
+      <c r="D51" s="69"/>
+      <c r="E51" s="69"/>
       <c r="F51" s="11">
         <v>3.4489365999999999E-3</v>
       </c>
@@ -5234,9 +5225,9 @@
       <c r="B52" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C52" s="71"/>
-      <c r="D52" s="67"/>
-      <c r="E52" s="67"/>
+      <c r="C52" s="68"/>
+      <c r="D52" s="69"/>
+      <c r="E52" s="69"/>
       <c r="F52" s="62">
         <v>4.7901900000000002E-4</v>
       </c>
@@ -5266,12 +5257,12 @@
       </c>
     </row>
     <row r="55" spans="1:14" s="14" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="82" t="s">
+      <c r="A55" s="76" t="s">
         <v>59</v>
       </c>
-      <c r="B55" s="82"/>
-      <c r="C55" s="82"/>
-      <c r="D55" s="82"/>
+      <c r="B55" s="76"/>
+      <c r="C55" s="76"/>
+      <c r="D55" s="76"/>
       <c r="E55" s="15"/>
       <c r="F55" s="16">
         <f t="shared" ref="F55:M55" si="0">MAX(F2:F52)</f>
@@ -5308,12 +5299,12 @@
       <c r="N55" s="17"/>
     </row>
     <row r="56" spans="1:14" s="18" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="80" t="s">
+      <c r="A56" s="78" t="s">
         <v>60</v>
       </c>
-      <c r="B56" s="80"/>
-      <c r="C56" s="80"/>
-      <c r="D56" s="80"/>
+      <c r="B56" s="78"/>
+      <c r="C56" s="78"/>
+      <c r="D56" s="78"/>
       <c r="E56" s="19"/>
       <c r="F56" s="20">
         <f t="shared" ref="F56:M56" si="1">AVERAGE(F2:F52)</f>
@@ -5350,13 +5341,13 @@
       <c r="N56" s="21"/>
     </row>
     <row r="58" spans="1:14" s="22" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="77" t="s">
+      <c r="A58" s="81" t="s">
         <v>64</v>
       </c>
-      <c r="B58" s="77"/>
-      <c r="C58" s="77"/>
-      <c r="D58" s="77"/>
-      <c r="E58" s="77"/>
+      <c r="B58" s="81"/>
+      <c r="C58" s="81"/>
+      <c r="D58" s="81"/>
+      <c r="E58" s="81"/>
       <c r="F58" s="29">
         <f>SUM(F55*(1/3),  G55*(1/3), I55*(1/3))</f>
         <v>0.33744571563333331</v>
@@ -5371,13 +5362,13 @@
       <c r="N58" s="24"/>
     </row>
     <row r="59" spans="1:14" s="27" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="78" t="s">
+      <c r="A59" s="82" t="s">
         <v>65</v>
       </c>
-      <c r="B59" s="78"/>
-      <c r="C59" s="78"/>
-      <c r="D59" s="78"/>
-      <c r="E59" s="78"/>
+      <c r="B59" s="82"/>
+      <c r="C59" s="82"/>
+      <c r="D59" s="82"/>
+      <c r="E59" s="82"/>
       <c r="F59" s="28">
         <f>SUM(H55*(1/2),  J55*(1/2))</f>
         <v>0.67529401794999999</v>
@@ -5392,13 +5383,13 @@
       <c r="N59" s="26"/>
     </row>
     <row r="60" spans="1:14" s="33" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="79" t="s">
+      <c r="A60" s="83" t="s">
         <v>66</v>
       </c>
-      <c r="B60" s="79"/>
-      <c r="C60" s="79"/>
-      <c r="D60" s="79"/>
-      <c r="E60" s="79"/>
+      <c r="B60" s="83"/>
+      <c r="C60" s="83"/>
+      <c r="D60" s="83"/>
+      <c r="E60" s="83"/>
       <c r="F60" s="30">
         <f>SUM(F55*1/5, G55*1/5, H55*1/5, I55*1/5,J55*1/5)</f>
         <v>0.47258503656</v>
@@ -5413,12 +5404,12 @@
       <c r="N60" s="32"/>
     </row>
     <row r="62" spans="1:14" s="37" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="75" t="s">
+      <c r="A62" s="79" t="s">
         <v>83</v>
       </c>
-      <c r="B62" s="75"/>
-      <c r="C62" s="75"/>
-      <c r="D62" s="75"/>
+      <c r="B62" s="79"/>
+      <c r="C62" s="79"/>
+      <c r="D62" s="79"/>
       <c r="E62" s="34"/>
       <c r="F62" s="35"/>
       <c r="G62" s="35"/>
@@ -5431,12 +5422,12 @@
       <c r="N62" s="36"/>
     </row>
     <row r="63" spans="1:14" s="37" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A63" s="75" t="s">
+      <c r="A63" s="79" t="s">
         <v>84</v>
       </c>
-      <c r="B63" s="76"/>
-      <c r="C63" s="76"/>
-      <c r="D63" s="76"/>
+      <c r="B63" s="80"/>
+      <c r="C63" s="80"/>
+      <c r="D63" s="80"/>
       <c r="E63" s="38"/>
       <c r="F63" s="35"/>
       <c r="G63" s="35"/>
@@ -5449,12 +5440,12 @@
       <c r="N63" s="36"/>
     </row>
     <row r="64" spans="1:14" s="37" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="75" t="s">
+      <c r="A64" s="79" t="s">
         <v>85</v>
       </c>
-      <c r="B64" s="76"/>
-      <c r="C64" s="76"/>
-      <c r="D64" s="76"/>
+      <c r="B64" s="80"/>
+      <c r="C64" s="80"/>
+      <c r="D64" s="80"/>
       <c r="E64" s="38"/>
       <c r="F64" s="35"/>
       <c r="G64" s="35"/>
@@ -5468,37 +5459,12 @@
     </row>
   </sheetData>
   <mergeCells count="53">
-    <mergeCell ref="A55:D55"/>
-    <mergeCell ref="N42:N44"/>
-    <mergeCell ref="C46:C48"/>
-    <mergeCell ref="D46:D48"/>
-    <mergeCell ref="E46:E48"/>
-    <mergeCell ref="N46:N48"/>
-    <mergeCell ref="E50:E52"/>
-    <mergeCell ref="C36:C38"/>
-    <mergeCell ref="D36:D38"/>
-    <mergeCell ref="E36:E38"/>
-    <mergeCell ref="A40:D40"/>
-    <mergeCell ref="C42:C44"/>
-    <mergeCell ref="D42:D44"/>
-    <mergeCell ref="E42:E44"/>
-    <mergeCell ref="N12:N14"/>
-    <mergeCell ref="C20:C22"/>
-    <mergeCell ref="D20:D22"/>
-    <mergeCell ref="E20:E22"/>
-    <mergeCell ref="N20:N22"/>
-    <mergeCell ref="C16:C18"/>
-    <mergeCell ref="D16:D18"/>
-    <mergeCell ref="E16:E18"/>
-    <mergeCell ref="N16:N18"/>
-    <mergeCell ref="C2:C4"/>
-    <mergeCell ref="D2:D4"/>
-    <mergeCell ref="E2:E4"/>
-    <mergeCell ref="N2:N4"/>
-    <mergeCell ref="C6:C8"/>
-    <mergeCell ref="D6:D8"/>
-    <mergeCell ref="E6:E8"/>
-    <mergeCell ref="N6:N8"/>
+    <mergeCell ref="A63:D63"/>
+    <mergeCell ref="A64:D64"/>
+    <mergeCell ref="A58:E58"/>
+    <mergeCell ref="A59:E59"/>
+    <mergeCell ref="A60:E60"/>
+    <mergeCell ref="A62:D62"/>
     <mergeCell ref="A56:D56"/>
     <mergeCell ref="A10:D10"/>
     <mergeCell ref="C12:C14"/>
@@ -5515,12 +5481,37 @@
     <mergeCell ref="E32:E34"/>
     <mergeCell ref="C50:C52"/>
     <mergeCell ref="D50:D52"/>
-    <mergeCell ref="A63:D63"/>
-    <mergeCell ref="A64:D64"/>
-    <mergeCell ref="A58:E58"/>
-    <mergeCell ref="A59:E59"/>
-    <mergeCell ref="A60:E60"/>
-    <mergeCell ref="A62:D62"/>
+    <mergeCell ref="C2:C4"/>
+    <mergeCell ref="D2:D4"/>
+    <mergeCell ref="E2:E4"/>
+    <mergeCell ref="N2:N4"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="D6:D8"/>
+    <mergeCell ref="E6:E8"/>
+    <mergeCell ref="N6:N8"/>
+    <mergeCell ref="N12:N14"/>
+    <mergeCell ref="C20:C22"/>
+    <mergeCell ref="D20:D22"/>
+    <mergeCell ref="E20:E22"/>
+    <mergeCell ref="N20:N22"/>
+    <mergeCell ref="C16:C18"/>
+    <mergeCell ref="D16:D18"/>
+    <mergeCell ref="E16:E18"/>
+    <mergeCell ref="N16:N18"/>
+    <mergeCell ref="C36:C38"/>
+    <mergeCell ref="D36:D38"/>
+    <mergeCell ref="E36:E38"/>
+    <mergeCell ref="A40:D40"/>
+    <mergeCell ref="C42:C44"/>
+    <mergeCell ref="D42:D44"/>
+    <mergeCell ref="E42:E44"/>
+    <mergeCell ref="A55:D55"/>
+    <mergeCell ref="N42:N44"/>
+    <mergeCell ref="C46:C48"/>
+    <mergeCell ref="D46:D48"/>
+    <mergeCell ref="E46:E48"/>
+    <mergeCell ref="N46:N48"/>
+    <mergeCell ref="E50:E52"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5601,17 +5592,17 @@
       <c r="N2" s="9"/>
     </row>
     <row r="3" spans="1:14" s="47" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="80" t="s">
+      <c r="A3" s="78" t="s">
         <v>71</v>
       </c>
-      <c r="B3" s="80"/>
-      <c r="C3" s="80"/>
-      <c r="D3" s="80"/>
-      <c r="E3" s="80"/>
-      <c r="F3" s="80"/>
-      <c r="G3" s="80"/>
-      <c r="H3" s="80"/>
-      <c r="I3" s="80"/>
+      <c r="B3" s="78"/>
+      <c r="C3" s="78"/>
+      <c r="D3" s="78"/>
+      <c r="E3" s="78"/>
+      <c r="F3" s="78"/>
+      <c r="G3" s="78"/>
+      <c r="H3" s="78"/>
+      <c r="I3" s="78"/>
       <c r="J3" s="49"/>
       <c r="K3" s="56"/>
       <c r="L3" s="56"/>
@@ -5637,10 +5628,10 @@
       <c r="B5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="69" t="s">
+      <c r="C5" s="75" t="s">
         <v>67</v>
       </c>
-      <c r="D5" s="69" t="s">
+      <c r="D5" s="75" t="s">
         <v>68</v>
       </c>
       <c r="E5" s="11">
@@ -5678,8 +5669,8 @@
       <c r="B6" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="69"/>
-      <c r="D6" s="69"/>
+      <c r="C6" s="75"/>
+      <c r="D6" s="75"/>
       <c r="E6" s="11">
         <v>6.9727237799999994E-2</v>
       </c>
@@ -5715,8 +5706,8 @@
       <c r="B7" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="69"/>
-      <c r="D7" s="69"/>
+      <c r="C7" s="75"/>
+      <c r="D7" s="75"/>
       <c r="E7" s="11">
         <v>2.8812910000000001E-4</v>
       </c>
@@ -5752,10 +5743,10 @@
       <c r="B9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="69" t="s">
+      <c r="C9" s="75" t="s">
         <v>69</v>
       </c>
-      <c r="D9" s="69" t="s">
+      <c r="D9" s="75" t="s">
         <v>70</v>
       </c>
       <c r="E9" s="11">
@@ -5793,8 +5784,8 @@
       <c r="B10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="69"/>
-      <c r="D10" s="69"/>
+      <c r="C10" s="75"/>
+      <c r="D10" s="75"/>
       <c r="E10" s="11">
         <v>2.4010757000000001E-3</v>
       </c>
@@ -5830,8 +5821,8 @@
       <c r="B11" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C11" s="69"/>
-      <c r="D11" s="69"/>
+      <c r="C11" s="75"/>
+      <c r="D11" s="75"/>
       <c r="E11" s="11">
         <v>0</v>
       </c>
@@ -5867,10 +5858,10 @@
       <c r="B13" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C13" s="69" t="s">
+      <c r="C13" s="75" t="s">
         <v>74</v>
       </c>
-      <c r="D13" s="69" t="s">
+      <c r="D13" s="75" t="s">
         <v>81</v>
       </c>
       <c r="E13" s="11">
@@ -5908,8 +5899,8 @@
       <c r="B14" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C14" s="69"/>
-      <c r="D14" s="69"/>
+      <c r="C14" s="75"/>
+      <c r="D14" s="75"/>
       <c r="E14" s="11">
         <v>3.5474592999999999E-3</v>
       </c>
@@ -5945,8 +5936,8 @@
       <c r="B15" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C15" s="69"/>
-      <c r="D15" s="69"/>
+      <c r="C15" s="75"/>
+      <c r="D15" s="75"/>
       <c r="E15" s="11">
         <v>3.8350910000000001E-4</v>
       </c>
@@ -5982,10 +5973,10 @@
       <c r="B17" s="63" t="s">
         <v>5</v>
       </c>
-      <c r="C17" s="69" t="s">
+      <c r="C17" s="75" t="s">
         <v>80</v>
       </c>
-      <c r="D17" s="69" t="s">
+      <c r="D17" s="75" t="s">
         <v>79</v>
       </c>
       <c r="E17" s="64">
@@ -6023,8 +6014,8 @@
       <c r="B18" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C18" s="69"/>
-      <c r="D18" s="69"/>
+      <c r="C18" s="75"/>
+      <c r="D18" s="75"/>
       <c r="E18" s="11">
         <v>3.0680729000000001E-3</v>
       </c>
@@ -6060,8 +6051,8 @@
       <c r="B19" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C19" s="69"/>
-      <c r="D19" s="69"/>
+      <c r="C19" s="75"/>
+      <c r="D19" s="75"/>
       <c r="E19" s="11">
         <v>2.876318E-4</v>
       </c>
@@ -6100,10 +6091,10 @@
       <c r="B21" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C21" s="69" t="s">
+      <c r="C21" s="75" t="s">
         <v>72</v>
       </c>
-      <c r="D21" s="69" t="s">
+      <c r="D21" s="75" t="s">
         <v>73</v>
       </c>
       <c r="E21" s="11">
@@ -6141,8 +6132,8 @@
       <c r="B22" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C22" s="69"/>
-      <c r="D22" s="69"/>
+      <c r="C22" s="75"/>
+      <c r="D22" s="75"/>
       <c r="E22" s="11">
         <v>3.1639501E-3</v>
       </c>
@@ -6178,8 +6169,8 @@
       <c r="B23" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C23" s="69"/>
-      <c r="D23" s="69"/>
+      <c r="C23" s="75"/>
+      <c r="D23" s="75"/>
       <c r="E23" s="11">
         <v>1.917546E-4</v>
       </c>
@@ -6215,10 +6206,10 @@
       <c r="B25" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C25" s="69" t="s">
+      <c r="C25" s="75" t="s">
         <v>77</v>
       </c>
-      <c r="D25" s="69" t="s">
+      <c r="D25" s="75" t="s">
         <v>75</v>
       </c>
       <c r="E25" s="11">
@@ -6256,8 +6247,8 @@
       <c r="B26" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C26" s="69"/>
-      <c r="D26" s="69"/>
+      <c r="C26" s="75"/>
+      <c r="D26" s="75"/>
       <c r="E26" s="11">
         <v>1.70661553E-2</v>
       </c>
@@ -6293,8 +6284,8 @@
       <c r="B27" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C27" s="69"/>
-      <c r="D27" s="69"/>
+      <c r="C27" s="75"/>
+      <c r="D27" s="75"/>
       <c r="E27" s="11">
         <v>6.7114089999999996E-4</v>
       </c>
@@ -6330,10 +6321,10 @@
       <c r="B29" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C29" s="69" t="s">
+      <c r="C29" s="75" t="s">
         <v>78</v>
       </c>
-      <c r="D29" s="69" t="s">
+      <c r="D29" s="75" t="s">
         <v>76</v>
       </c>
       <c r="E29" s="11">
@@ -6371,8 +6362,8 @@
       <c r="B30" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C30" s="69"/>
-      <c r="D30" s="69"/>
+      <c r="C30" s="75"/>
+      <c r="D30" s="75"/>
       <c r="E30" s="11">
         <v>7.2866731000000001E-3</v>
       </c>
@@ -6408,8 +6399,8 @@
       <c r="B31" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C31" s="69"/>
-      <c r="D31" s="69"/>
+      <c r="C31" s="75"/>
+      <c r="D31" s="75"/>
       <c r="E31" s="11">
         <v>0</v>
       </c>
@@ -6439,12 +6430,12 @@
       </c>
     </row>
     <row r="34" spans="1:14" s="14" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="82" t="s">
+      <c r="A34" s="76" t="s">
         <v>59</v>
       </c>
-      <c r="B34" s="82"/>
-      <c r="C34" s="82"/>
-      <c r="D34" s="82"/>
+      <c r="B34" s="76"/>
+      <c r="C34" s="76"/>
+      <c r="D34" s="76"/>
       <c r="E34" s="16">
         <f t="shared" ref="E34:L34" si="0">MAX(E4:E32)</f>
         <v>8.2742090099999999E-2</v>
@@ -6481,12 +6472,12 @@
       <c r="N34" s="17"/>
     </row>
     <row r="35" spans="1:14" s="52" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="77" t="s">
+      <c r="A35" s="81" t="s">
         <v>60</v>
       </c>
-      <c r="B35" s="77"/>
-      <c r="C35" s="77"/>
-      <c r="D35" s="77"/>
+      <c r="B35" s="81"/>
+      <c r="C35" s="81"/>
+      <c r="D35" s="81"/>
       <c r="E35" s="29">
         <f t="shared" ref="E35:L35" si="1">AVERAGE(E5:E32)</f>
         <v>2.0975477057142849E-2</v>
@@ -6523,17 +6514,17 @@
       <c r="N35" s="58"/>
     </row>
     <row r="37" spans="1:14" s="47" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="80" t="s">
+      <c r="A37" s="78" t="s">
         <v>86</v>
       </c>
-      <c r="B37" s="80"/>
-      <c r="C37" s="80"/>
-      <c r="D37" s="80"/>
-      <c r="E37" s="80"/>
-      <c r="F37" s="80"/>
-      <c r="G37" s="80"/>
-      <c r="H37" s="80"/>
-      <c r="I37" s="80"/>
+      <c r="B37" s="78"/>
+      <c r="C37" s="78"/>
+      <c r="D37" s="78"/>
+      <c r="E37" s="78"/>
+      <c r="F37" s="78"/>
+      <c r="G37" s="78"/>
+      <c r="H37" s="78"/>
+      <c r="I37" s="78"/>
       <c r="J37" s="49"/>
       <c r="K37" s="56"/>
       <c r="L37" s="56"/>
@@ -6559,10 +6550,10 @@
       <c r="B39" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C39" s="69" t="s">
+      <c r="C39" s="75" t="s">
         <v>87</v>
       </c>
-      <c r="D39" s="69" t="s">
+      <c r="D39" s="75" t="s">
         <v>68</v>
       </c>
       <c r="E39" s="11">
@@ -6600,8 +6591,8 @@
       <c r="B40" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C40" s="69"/>
-      <c r="D40" s="69"/>
+      <c r="C40" s="75"/>
+      <c r="D40" s="75"/>
       <c r="E40" s="11">
         <v>1.42857143E-2</v>
       </c>
@@ -6637,8 +6628,8 @@
       <c r="B41" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C41" s="69"/>
-      <c r="D41" s="69"/>
+      <c r="C41" s="75"/>
+      <c r="D41" s="75"/>
       <c r="E41" s="11">
         <v>3.8350910000000001E-4</v>
       </c>
@@ -6674,10 +6665,10 @@
       <c r="B43" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C43" s="69" t="s">
+      <c r="C43" s="75" t="s">
         <v>88</v>
       </c>
-      <c r="D43" s="69" t="s">
+      <c r="D43" s="75" t="s">
         <v>70</v>
       </c>
       <c r="E43" s="11">
@@ -6715,8 +6706,8 @@
       <c r="B44" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C44" s="69"/>
-      <c r="D44" s="69"/>
+      <c r="C44" s="75"/>
+      <c r="D44" s="75"/>
       <c r="E44" s="11">
         <v>2.8475551299999999E-2</v>
       </c>
@@ -6752,8 +6743,8 @@
       <c r="B45" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C45" s="69"/>
-      <c r="D45" s="69"/>
+      <c r="C45" s="75"/>
+      <c r="D45" s="75"/>
       <c r="E45" s="11">
         <v>1.917546E-4</v>
       </c>
@@ -6789,10 +6780,10 @@
       <c r="B47" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C47" s="69" t="s">
+      <c r="C47" s="75" t="s">
         <v>89</v>
       </c>
-      <c r="D47" s="69" t="s">
+      <c r="D47" s="75" t="s">
         <v>81</v>
       </c>
       <c r="E47" s="11">
@@ -6830,8 +6821,8 @@
       <c r="B48" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C48" s="69"/>
-      <c r="D48" s="69"/>
+      <c r="C48" s="75"/>
+      <c r="D48" s="75"/>
       <c r="E48" s="11">
         <v>6.3279002999999997E-3</v>
       </c>
@@ -6867,8 +6858,8 @@
       <c r="B49" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C49" s="69"/>
-      <c r="D49" s="69"/>
+      <c r="C49" s="75"/>
+      <c r="D49" s="75"/>
       <c r="E49" s="11">
         <v>2.876318E-4</v>
       </c>
@@ -6904,10 +6895,10 @@
       <c r="B51" s="63" t="s">
         <v>5</v>
       </c>
-      <c r="C51" s="69" t="s">
+      <c r="C51" s="75" t="s">
         <v>90</v>
       </c>
-      <c r="D51" s="69" t="s">
+      <c r="D51" s="75" t="s">
         <v>79</v>
       </c>
       <c r="E51" s="64">
@@ -6945,8 +6936,8 @@
       <c r="B52" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C52" s="69"/>
-      <c r="D52" s="69"/>
+      <c r="C52" s="75"/>
+      <c r="D52" s="75"/>
       <c r="E52" s="11">
         <v>2.0134227999999998E-3</v>
       </c>
@@ -6982,8 +6973,8 @@
       <c r="B53" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C53" s="69"/>
-      <c r="D53" s="69"/>
+      <c r="C53" s="75"/>
+      <c r="D53" s="75"/>
       <c r="E53" s="11">
         <v>1.917546E-4</v>
       </c>
@@ -7022,10 +7013,10 @@
       <c r="B55" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C55" s="69" t="s">
+      <c r="C55" s="75" t="s">
         <v>91</v>
       </c>
-      <c r="D55" s="69" t="s">
+      <c r="D55" s="75" t="s">
         <v>73</v>
       </c>
       <c r="E55" s="11">
@@ -7063,8 +7054,8 @@
       <c r="B56" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C56" s="69"/>
-      <c r="D56" s="69"/>
+      <c r="C56" s="75"/>
+      <c r="D56" s="75"/>
       <c r="E56" s="11">
         <v>1.9558964500000001E-2</v>
       </c>
@@ -7100,8 +7091,8 @@
       <c r="B57" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C57" s="69"/>
-      <c r="D57" s="69"/>
+      <c r="C57" s="75"/>
+      <c r="D57" s="75"/>
       <c r="E57" s="11">
         <v>0</v>
       </c>
@@ -7137,10 +7128,10 @@
       <c r="B59" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C59" s="69" t="s">
+      <c r="C59" s="75" t="s">
         <v>92</v>
       </c>
-      <c r="D59" s="69" t="s">
+      <c r="D59" s="75" t="s">
         <v>75</v>
       </c>
       <c r="E59" s="11">
@@ -7178,8 +7169,8 @@
       <c r="B60" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C60" s="69"/>
-      <c r="D60" s="69"/>
+      <c r="C60" s="75"/>
+      <c r="D60" s="75"/>
       <c r="E60" s="11">
         <v>4.4103546999999998E-3</v>
       </c>
@@ -7215,8 +7206,8 @@
       <c r="B61" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C61" s="69"/>
-      <c r="D61" s="69"/>
+      <c r="C61" s="75"/>
+      <c r="D61" s="75"/>
       <c r="E61" s="11">
         <v>2.8763183000000002E-3</v>
       </c>
@@ -7252,10 +7243,10 @@
       <c r="B63" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C63" s="69" t="s">
+      <c r="C63" s="75" t="s">
         <v>93</v>
       </c>
-      <c r="D63" s="69" t="s">
+      <c r="D63" s="75" t="s">
         <v>76</v>
       </c>
       <c r="E63" s="11">
@@ -7293,8 +7284,8 @@
       <c r="B64" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C64" s="69"/>
-      <c r="D64" s="69"/>
+      <c r="C64" s="75"/>
+      <c r="D64" s="75"/>
       <c r="E64" s="11">
         <v>8.6289548999999993E-3</v>
       </c>
@@ -7330,8 +7321,8 @@
       <c r="B65" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C65" s="69"/>
-      <c r="D65" s="69"/>
+      <c r="C65" s="75"/>
+      <c r="D65" s="75"/>
       <c r="E65" s="11">
         <v>1.9175455000000001E-3</v>
       </c>
@@ -7361,12 +7352,12 @@
       </c>
     </row>
     <row r="68" spans="1:14" s="14" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="82" t="s">
+      <c r="A68" s="76" t="s">
         <v>59</v>
       </c>
-      <c r="B68" s="82"/>
-      <c r="C68" s="82"/>
-      <c r="D68" s="82"/>
+      <c r="B68" s="76"/>
+      <c r="C68" s="76"/>
+      <c r="D68" s="76"/>
       <c r="E68" s="16">
         <f t="shared" ref="E68:L68" si="2">MAX(E38:E66)</f>
         <v>9.0220517700000002E-2</v>
@@ -7403,12 +7394,12 @@
       <c r="N68" s="17"/>
     </row>
     <row r="69" spans="1:14" s="52" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="77" t="s">
+      <c r="A69" s="81" t="s">
         <v>60</v>
       </c>
-      <c r="B69" s="77"/>
-      <c r="C69" s="77"/>
-      <c r="D69" s="77"/>
+      <c r="B69" s="81"/>
+      <c r="C69" s="81"/>
+      <c r="D69" s="81"/>
       <c r="E69" s="29">
         <f t="shared" ref="E69:L69" si="3">AVERAGE(E39:E66)</f>
         <v>1.7271606619047621E-2</v>
@@ -7445,17 +7436,17 @@
       <c r="N69" s="58"/>
     </row>
     <row r="71" spans="1:14" s="47" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A71" s="80" t="s">
+      <c r="A71" s="78" t="s">
         <v>94</v>
       </c>
-      <c r="B71" s="80"/>
-      <c r="C71" s="80"/>
-      <c r="D71" s="80"/>
-      <c r="E71" s="80"/>
-      <c r="F71" s="80"/>
-      <c r="G71" s="80"/>
-      <c r="H71" s="80"/>
-      <c r="I71" s="80"/>
+      <c r="B71" s="78"/>
+      <c r="C71" s="78"/>
+      <c r="D71" s="78"/>
+      <c r="E71" s="78"/>
+      <c r="F71" s="78"/>
+      <c r="G71" s="78"/>
+      <c r="H71" s="78"/>
+      <c r="I71" s="78"/>
       <c r="J71" s="49"/>
       <c r="K71" s="56"/>
       <c r="L71" s="56"/>
@@ -7481,10 +7472,10 @@
       <c r="B73" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C73" s="69" t="s">
+      <c r="C73" s="75" t="s">
         <v>95</v>
       </c>
-      <c r="D73" s="69" t="s">
+      <c r="D73" s="75" t="s">
         <v>68</v>
       </c>
       <c r="E73" s="11">
@@ -7522,8 +7513,8 @@
       <c r="B74" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C74" s="69"/>
-      <c r="D74" s="69"/>
+      <c r="C74" s="75"/>
+      <c r="D74" s="75"/>
       <c r="E74" s="11">
         <v>8.8139489999999997E-3</v>
       </c>
@@ -7559,8 +7550,8 @@
       <c r="B75" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C75" s="69"/>
-      <c r="D75" s="69"/>
+      <c r="C75" s="75"/>
+      <c r="D75" s="75"/>
       <c r="E75" s="11">
         <v>1.9160760000000001E-4</v>
       </c>
@@ -7596,10 +7587,10 @@
       <c r="B77" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C77" s="69" t="s">
+      <c r="C77" s="75" t="s">
         <v>96</v>
       </c>
-      <c r="D77" s="69" t="s">
+      <c r="D77" s="75" t="s">
         <v>70</v>
       </c>
       <c r="E77" s="11">
@@ -7637,8 +7628,8 @@
       <c r="B78" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C78" s="69"/>
-      <c r="D78" s="69"/>
+      <c r="C78" s="75"/>
+      <c r="D78" s="75"/>
       <c r="E78" s="11">
         <v>3.4489365999999999E-3</v>
       </c>
@@ -7674,8 +7665,8 @@
       <c r="B79" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C79" s="69"/>
-      <c r="D79" s="69"/>
+      <c r="C79" s="75"/>
+      <c r="D79" s="75"/>
       <c r="E79" s="62">
         <v>4.7901900000000002E-4</v>
       </c>
@@ -7711,10 +7702,10 @@
       <c r="B81" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C81" s="69" t="s">
+      <c r="C81" s="75" t="s">
         <v>97</v>
       </c>
-      <c r="D81" s="69" t="s">
+      <c r="D81" s="75" t="s">
         <v>81</v>
       </c>
       <c r="E81" s="11">
@@ -7752,8 +7743,8 @@
       <c r="B82" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C82" s="69"/>
-      <c r="D82" s="69"/>
+      <c r="C82" s="75"/>
+      <c r="D82" s="75"/>
       <c r="E82" s="11">
         <v>4.3111707000000003E-3</v>
       </c>
@@ -7789,8 +7780,8 @@
       <c r="B83" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C83" s="69"/>
-      <c r="D83" s="69"/>
+      <c r="C83" s="75"/>
+      <c r="D83" s="75"/>
       <c r="E83" s="11">
         <v>2.1076835000000001E-3</v>
       </c>
@@ -7819,43 +7810,43 @@
         <v>0.28440324</v>
       </c>
     </row>
-    <row r="85" spans="1:12" s="84" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A85" s="84" t="s">
+    <row r="85" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A85" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B85" s="84" t="s">
+      <c r="B85" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C85" s="69" t="s">
+      <c r="C85" s="75" t="s">
         <v>98</v>
       </c>
-      <c r="D85" s="69" t="s">
+      <c r="D85" s="75" t="s">
         <v>79</v>
       </c>
-      <c r="E85" s="85">
+      <c r="E85" s="11">
         <v>4.7901900000000002E-4</v>
       </c>
-      <c r="F85" s="85">
+      <c r="F85" s="11">
         <v>3.6405442E-3</v>
       </c>
-      <c r="G85" s="85">
+      <c r="G85" s="11">
         <v>0.74458708559999998</v>
       </c>
-      <c r="H85" s="85">
+      <c r="H85" s="11">
         <v>0.70530976980000004</v>
       </c>
-      <c r="I85" s="85">
+      <c r="I85" s="11">
         <v>0.82515196759999998</v>
       </c>
-      <c r="J85" s="85">
+      <c r="J85" s="11">
         <f>SUM(E85*1/3,F85*1/3,H85*1/3)</f>
         <v>0.23647644433333334</v>
       </c>
-      <c r="K85" s="86">
+      <c r="K85" s="54">
         <f>SUM(G85*1/2,I85*1/2)</f>
         <v>0.78486952659999998</v>
       </c>
-      <c r="L85" s="85">
+      <c r="L85" s="11">
         <f>SUM(E85*1/5,F85*1/5,G85*1/5,H85*1/5,I85*1/5)</f>
         <v>0.45583367724000001</v>
       </c>
@@ -7867,28 +7858,28 @@
       <c r="B86" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="C86" s="69"/>
-      <c r="D86" s="69"/>
-      <c r="E86" s="83">
+      <c r="C86" s="75"/>
+      <c r="D86" s="75"/>
+      <c r="E86" s="66">
         <v>2.24180878E-2</v>
       </c>
-      <c r="F86" s="83">
+      <c r="F86" s="66">
         <v>3.2573290000000002E-3</v>
       </c>
-      <c r="G86" s="83">
+      <c r="G86" s="66">
         <v>0.76911285689999997</v>
       </c>
-      <c r="H86" s="83">
+      <c r="H86" s="66">
         <v>0.87399711270000002</v>
       </c>
-      <c r="I86" s="83">
+      <c r="I86" s="66">
         <v>0.78457966379999999</v>
       </c>
-      <c r="J86" s="83">
+      <c r="J86" s="66">
         <f>SUM(E86*1/3,F86*1/3,H86*1/3)</f>
         <v>0.2998908431666667</v>
       </c>
-      <c r="K86" s="83">
+      <c r="K86" s="66">
         <f>SUM(G86*1/2,I86*1/2)</f>
         <v>0.77684626034999993</v>
       </c>
@@ -7904,8 +7895,8 @@
       <c r="B87" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C87" s="69"/>
-      <c r="D87" s="69"/>
+      <c r="C87" s="75"/>
+      <c r="D87" s="75"/>
       <c r="E87" s="11">
         <v>0</v>
       </c>
@@ -7944,10 +7935,10 @@
       <c r="B89" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C89" s="69" t="s">
+      <c r="C89" s="75" t="s">
         <v>99</v>
       </c>
-      <c r="D89" s="69" t="s">
+      <c r="D89" s="75" t="s">
         <v>73</v>
       </c>
       <c r="E89" s="11">
@@ -7985,8 +7976,8 @@
       <c r="B90" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C90" s="69"/>
-      <c r="D90" s="69"/>
+      <c r="C90" s="75"/>
+      <c r="D90" s="75"/>
       <c r="E90" s="11">
         <v>1.59034298E-2</v>
       </c>
@@ -8022,19 +8013,34 @@
       <c r="B91" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C91" s="69"/>
-      <c r="D91" s="69"/>
+      <c r="C91" s="75"/>
+      <c r="D91" s="75"/>
+      <c r="E91" s="11">
+        <v>0</v>
+      </c>
+      <c r="F91" s="11">
+        <v>3.2573290000000002E-3</v>
+      </c>
+      <c r="G91" s="11">
+        <v>0.1509867791</v>
+      </c>
+      <c r="H91" s="11">
+        <v>0.50179758129999996</v>
+      </c>
+      <c r="I91" s="11">
+        <v>0.47369240169999999</v>
+      </c>
       <c r="J91" s="11">
         <f>SUM(E91*1/3,F91*1/3,H91*1/3)</f>
-        <v>0</v>
+        <v>0.16835163676666667</v>
       </c>
       <c r="K91" s="11">
         <f>SUM(G91*1/2,I91*1/2)</f>
-        <v>0</v>
+        <v>0.31233959039999998</v>
       </c>
       <c r="L91" s="11">
         <f>SUM(E91*1/5,F91*1/5,G91*1/5,H91*1/5,I91*1/5)</f>
-        <v>0</v>
+        <v>0.22594681822000001</v>
       </c>
     </row>
     <row r="93" spans="1:12" x14ac:dyDescent="0.2">
@@ -8044,10 +8050,10 @@
       <c r="B93" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C93" s="69" t="s">
+      <c r="C93" s="75" t="s">
         <v>100</v>
       </c>
-      <c r="D93" s="69" t="s">
+      <c r="D93" s="75" t="s">
         <v>75</v>
       </c>
       <c r="E93" s="11">
@@ -8085,8 +8091,8 @@
       <c r="B94" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C94" s="69"/>
-      <c r="D94" s="69"/>
+      <c r="C94" s="75"/>
+      <c r="D94" s="75"/>
       <c r="E94" s="11">
         <v>9.4845755999999996E-3</v>
       </c>
@@ -8122,8 +8128,8 @@
       <c r="B95" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C95" s="69"/>
-      <c r="D95" s="69"/>
+      <c r="C95" s="75"/>
+      <c r="D95" s="75"/>
       <c r="E95" s="11">
         <v>1.9160760000000001E-4</v>
       </c>
@@ -8159,10 +8165,10 @@
       <c r="B97" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C97" s="69" t="s">
+      <c r="C97" s="75" t="s">
         <v>101</v>
       </c>
-      <c r="D97" s="69" t="s">
+      <c r="D97" s="75" t="s">
         <v>76</v>
       </c>
       <c r="E97" s="11">
@@ -8200,8 +8206,8 @@
       <c r="B98" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C98" s="69"/>
-      <c r="D98" s="69"/>
+      <c r="C98" s="75"/>
+      <c r="D98" s="75"/>
       <c r="E98" s="11">
         <v>8.9097528000000002E-3</v>
       </c>
@@ -8237,8 +8243,8 @@
       <c r="B99" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C99" s="69"/>
-      <c r="D99" s="69"/>
+      <c r="C99" s="75"/>
+      <c r="D99" s="75"/>
       <c r="E99" s="11">
         <v>1.6286645000000001E-3</v>
       </c>
@@ -8268,12 +8274,12 @@
       </c>
     </row>
     <row r="102" spans="1:14" s="14" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A102" s="82" t="s">
+      <c r="A102" s="76" t="s">
         <v>59</v>
       </c>
-      <c r="B102" s="82"/>
-      <c r="C102" s="82"/>
-      <c r="D102" s="82"/>
+      <c r="B102" s="76"/>
+      <c r="C102" s="76"/>
+      <c r="D102" s="76"/>
       <c r="E102" s="16">
         <f t="shared" ref="E102:L102" si="4">MAX(E72:E100)</f>
         <v>4.4165548999999998E-2</v>
@@ -8310,49 +8316,89 @@
       <c r="N102" s="17"/>
     </row>
     <row r="103" spans="1:14" s="52" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A103" s="77" t="s">
+      <c r="A103" s="81" t="s">
         <v>60</v>
       </c>
-      <c r="B103" s="77"/>
-      <c r="C103" s="77"/>
-      <c r="D103" s="77"/>
+      <c r="B103" s="81"/>
+      <c r="C103" s="81"/>
+      <c r="D103" s="81"/>
       <c r="E103" s="29">
         <f t="shared" ref="E103:L103" si="5">AVERAGE(E73:E100)</f>
-        <v>1.1434182804999998E-2</v>
+        <v>1.0889697909523807E-2</v>
       </c>
       <c r="F103" s="29">
         <f t="shared" si="5"/>
-        <v>5.9063039000000006E-3</v>
+        <v>5.780162238095239E-3</v>
       </c>
       <c r="G103" s="29">
         <f t="shared" si="5"/>
-        <v>0.38077217858000001</v>
+        <v>0.36983001670000004</v>
       </c>
       <c r="H103" s="29">
         <f t="shared" si="5"/>
-        <v>0.60348731926499988</v>
+        <v>0.59864495079047608</v>
       </c>
       <c r="I103" s="29">
         <f t="shared" si="5"/>
-        <v>0.49427817449000006</v>
+        <v>0.49329789959523812</v>
       </c>
       <c r="J103" s="29">
         <f t="shared" si="5"/>
-        <v>0.19708819237142855</v>
+        <v>0.20510493697936505</v>
       </c>
       <c r="K103" s="29">
         <f t="shared" si="5"/>
-        <v>0.41669064431904768</v>
+        <v>0.43156395814761905</v>
       </c>
       <c r="L103" s="29">
         <f t="shared" si="5"/>
-        <v>0.28492917315047628</v>
+        <v>0.29568854544666673</v>
       </c>
       <c r="M103" s="29"/>
       <c r="N103" s="58"/>
     </row>
   </sheetData>
   <mergeCells count="51">
+    <mergeCell ref="A103:D103"/>
+    <mergeCell ref="C93:C95"/>
+    <mergeCell ref="D93:D95"/>
+    <mergeCell ref="C97:C99"/>
+    <mergeCell ref="D97:D99"/>
+    <mergeCell ref="A102:D102"/>
+    <mergeCell ref="C81:C83"/>
+    <mergeCell ref="D81:D83"/>
+    <mergeCell ref="C85:C87"/>
+    <mergeCell ref="D85:D87"/>
+    <mergeCell ref="C89:C91"/>
+    <mergeCell ref="D89:D91"/>
+    <mergeCell ref="A69:D69"/>
+    <mergeCell ref="A71:I71"/>
+    <mergeCell ref="C73:C75"/>
+    <mergeCell ref="D73:D75"/>
+    <mergeCell ref="C77:C79"/>
+    <mergeCell ref="D77:D79"/>
+    <mergeCell ref="C59:C61"/>
+    <mergeCell ref="D59:D61"/>
+    <mergeCell ref="C63:C65"/>
+    <mergeCell ref="D63:D65"/>
+    <mergeCell ref="A68:D68"/>
+    <mergeCell ref="C47:C49"/>
+    <mergeCell ref="D47:D49"/>
+    <mergeCell ref="C51:C53"/>
+    <mergeCell ref="D51:D53"/>
+    <mergeCell ref="C55:C57"/>
+    <mergeCell ref="D55:D57"/>
+    <mergeCell ref="A37:I37"/>
+    <mergeCell ref="C39:C41"/>
+    <mergeCell ref="D39:D41"/>
+    <mergeCell ref="C43:C45"/>
+    <mergeCell ref="D43:D45"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="C13:C15"/>
+    <mergeCell ref="D13:D15"/>
+    <mergeCell ref="C29:C31"/>
+    <mergeCell ref="D29:D31"/>
     <mergeCell ref="A3:I3"/>
     <mergeCell ref="C21:C23"/>
     <mergeCell ref="D21:D23"/>
@@ -8364,46 +8410,6 @@
     <mergeCell ref="C9:C11"/>
     <mergeCell ref="D17:D19"/>
     <mergeCell ref="C17:C19"/>
-    <mergeCell ref="A34:D34"/>
-    <mergeCell ref="A35:D35"/>
-    <mergeCell ref="C13:C15"/>
-    <mergeCell ref="D13:D15"/>
-    <mergeCell ref="C29:C31"/>
-    <mergeCell ref="D29:D31"/>
-    <mergeCell ref="A37:I37"/>
-    <mergeCell ref="C39:C41"/>
-    <mergeCell ref="D39:D41"/>
-    <mergeCell ref="C43:C45"/>
-    <mergeCell ref="D43:D45"/>
-    <mergeCell ref="C47:C49"/>
-    <mergeCell ref="D47:D49"/>
-    <mergeCell ref="C51:C53"/>
-    <mergeCell ref="D51:D53"/>
-    <mergeCell ref="C55:C57"/>
-    <mergeCell ref="D55:D57"/>
-    <mergeCell ref="C59:C61"/>
-    <mergeCell ref="D59:D61"/>
-    <mergeCell ref="C63:C65"/>
-    <mergeCell ref="D63:D65"/>
-    <mergeCell ref="A68:D68"/>
-    <mergeCell ref="A69:D69"/>
-    <mergeCell ref="A71:I71"/>
-    <mergeCell ref="C73:C75"/>
-    <mergeCell ref="D73:D75"/>
-    <mergeCell ref="C77:C79"/>
-    <mergeCell ref="D77:D79"/>
-    <mergeCell ref="C81:C83"/>
-    <mergeCell ref="D81:D83"/>
-    <mergeCell ref="C85:C87"/>
-    <mergeCell ref="D85:D87"/>
-    <mergeCell ref="C89:C91"/>
-    <mergeCell ref="D89:D91"/>
-    <mergeCell ref="A103:D103"/>
-    <mergeCell ref="C93:C95"/>
-    <mergeCell ref="D93:D95"/>
-    <mergeCell ref="C97:C99"/>
-    <mergeCell ref="D97:D99"/>
-    <mergeCell ref="A102:D102"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/benchmarking/results/results.xlsx
+++ b/benchmarking/results/results.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/deborahdore/Documents/political-debates-graph-analysis/benchmarking/results/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{757F85C3-D682-6E44-B3C1-F6ACA5E93301}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D70A337-E4EE-A245-BA87-630F406C6AB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="51200" windowHeight="28800" activeTab="3" xr2:uid="{E2EDC037-19C4-FE46-A599-BB595128A04F}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="51200" windowHeight="26600" activeTab="4" xr2:uid="{E2EDC037-19C4-FE46-A599-BB595128A04F}"/>
   </bookViews>
   <sheets>
     <sheet name="Results BASIC" sheetId="1" r:id="rId1"/>
     <sheet name="Results SPECIAL" sheetId="5" r:id="rId2"/>
     <sheet name="Results PRETRAINED" sheetId="6" r:id="rId3"/>
     <sheet name="Trials" sheetId="7" r:id="rId4"/>
+    <sheet name="Check Bias of Models" sheetId="8" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="588" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="621" uniqueCount="114">
   <si>
     <t>MODEL'S TYPE</t>
   </si>
@@ -373,6 +374,42 @@
   </si>
   <si>
     <t>trial3/downsampling_bernoulli</t>
+  </si>
+  <si>
+    <t>NODES TYPES IN EXPERIMENT</t>
+  </si>
+  <si>
+    <t>SUPPORT PREDICTION HITS@1</t>
+  </si>
+  <si>
+    <t>ATTACK PREDICTION HITS@1</t>
+  </si>
+  <si>
+    <t>EQUIVALENT PREDICTION HITS@1</t>
+  </si>
+  <si>
+    <t>NODES DISTRIBUTION</t>
+  </si>
+  <si>
+    <t>basic_sampler/text_speaker_year</t>
+  </si>
+  <si>
+    <t>RELATION PREDICTION HITS@2</t>
+  </si>
+  <si>
+    <t>said by: 36.13%, said in: 34.10%, support: 24.62%, attack: 4.35%,  equivalent:0.76%, role:0.03%</t>
+  </si>
+  <si>
+    <t>basic_sampler/text_claim_year</t>
+  </si>
+  <si>
+    <t>is a: 39.80%, said in: 32.16%, support: 23.22%, attack: 4.10%, equivalent: 0.72%</t>
+  </si>
+  <si>
+    <t>basic_sampler/text+claim_speaker_year</t>
+  </si>
+  <si>
+    <t>said in: 37.03%, said by: 37.02%, support: 21.46%, attack: 3.79%, equivalent: 0.67%, role: 0.03%</t>
   </si>
 </sst>
 </file>
@@ -533,7 +570,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="84">
+  <cellXfs count="85">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -733,26 +770,11 @@
     <xf numFmtId="164" fontId="2" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -760,13 +782,19 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -782,6 +810,18 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1165,7 +1205,7 @@
       <c r="B2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="72" t="s">
+      <c r="C2" s="74" t="s">
         <v>41</v>
       </c>
       <c r="D2" s="71" t="s">
@@ -1189,7 +1229,7 @@
       <c r="J2" s="11">
         <v>0.52440008120000003</v>
       </c>
-      <c r="K2" s="74" t="s">
+      <c r="K2" s="69" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1200,9 +1240,9 @@
       <c r="B3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="68"/>
-      <c r="D3" s="69"/>
-      <c r="E3" s="69"/>
+      <c r="C3" s="72"/>
+      <c r="D3" s="68"/>
+      <c r="E3" s="68"/>
       <c r="F3" s="11">
         <v>3.9117929099999997E-2</v>
       </c>
@@ -1218,7 +1258,7 @@
       <c r="J3" s="11">
         <v>0.4957882649</v>
       </c>
-      <c r="K3" s="75"/>
+      <c r="K3" s="70"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
@@ -1227,9 +1267,9 @@
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="68"/>
-      <c r="D4" s="69"/>
-      <c r="E4" s="69"/>
+      <c r="C4" s="72"/>
+      <c r="D4" s="68"/>
+      <c r="E4" s="68"/>
       <c r="F4" s="11">
         <v>2.1093001000000002E-3</v>
       </c>
@@ -1245,7 +1285,7 @@
       <c r="J4" s="11">
         <v>0.4776301698</v>
       </c>
-      <c r="K4" s="75"/>
+      <c r="K4" s="70"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
@@ -1254,13 +1294,13 @@
       <c r="B6" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="68" t="s">
+      <c r="C6" s="72" t="s">
         <v>42</v>
       </c>
-      <c r="D6" s="69" t="s">
+      <c r="D6" s="68" t="s">
         <v>10</v>
       </c>
-      <c r="E6" s="69" t="s">
+      <c r="E6" s="68" t="s">
         <v>13</v>
       </c>
       <c r="F6" s="11">
@@ -1278,7 +1318,7 @@
       <c r="J6" s="11">
         <v>0.51801477490000003</v>
       </c>
-      <c r="K6" s="75" t="s">
+      <c r="K6" s="70" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1289,9 +1329,9 @@
       <c r="B7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="68"/>
-      <c r="D7" s="69"/>
-      <c r="E7" s="69"/>
+      <c r="C7" s="72"/>
+      <c r="D7" s="68"/>
+      <c r="E7" s="68"/>
       <c r="F7" s="11">
         <v>3.2094270899999999E-2</v>
       </c>
@@ -1307,7 +1347,7 @@
       <c r="J7" s="11">
         <v>0.50083099880000004</v>
       </c>
-      <c r="K7" s="75"/>
+      <c r="K7" s="70"/>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
@@ -1316,9 +1356,9 @@
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="68"/>
-      <c r="D8" s="69"/>
-      <c r="E8" s="69"/>
+      <c r="C8" s="72"/>
+      <c r="D8" s="68"/>
+      <c r="E8" s="68"/>
       <c r="F8" s="11">
         <v>2.8741139999999998E-4</v>
       </c>
@@ -1334,15 +1374,15 @@
       <c r="J8" s="11">
         <v>0.4887305689</v>
       </c>
-      <c r="K8" s="75"/>
+      <c r="K8" s="70"/>
     </row>
     <row r="10" spans="1:12" s="59" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="70" t="s">
+      <c r="A10" s="73" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="70"/>
-      <c r="C10" s="70"/>
-      <c r="D10" s="70"/>
+      <c r="B10" s="73"/>
+      <c r="C10" s="73"/>
+      <c r="D10" s="73"/>
       <c r="E10" s="60"/>
       <c r="F10" s="61"/>
       <c r="G10" s="61"/>
@@ -1358,13 +1398,13 @@
       <c r="B12" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C12" s="68" t="s">
+      <c r="C12" s="72" t="s">
         <v>43</v>
       </c>
-      <c r="D12" s="69" t="s">
+      <c r="D12" s="68" t="s">
         <v>11</v>
       </c>
-      <c r="E12" s="69" t="s">
+      <c r="E12" s="68" t="s">
         <v>17</v>
       </c>
       <c r="F12" s="11">
@@ -1382,7 +1422,7 @@
       <c r="J12" s="11">
         <v>0.65087326729999995</v>
       </c>
-      <c r="K12" s="75" t="s">
+      <c r="K12" s="70" t="s">
         <v>18</v>
       </c>
     </row>
@@ -1393,9 +1433,9 @@
       <c r="B13" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C13" s="68"/>
-      <c r="D13" s="69"/>
-      <c r="E13" s="69"/>
+      <c r="C13" s="72"/>
+      <c r="D13" s="68"/>
+      <c r="E13" s="68"/>
       <c r="F13" s="11">
         <v>1.0937623800000001E-2</v>
       </c>
@@ -1411,7 +1451,7 @@
       <c r="J13" s="11">
         <v>0.48031703009999999</v>
       </c>
-      <c r="K13" s="75"/>
+      <c r="K13" s="70"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
@@ -1420,9 +1460,9 @@
       <c r="B14" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C14" s="68"/>
-      <c r="D14" s="69"/>
-      <c r="E14" s="69"/>
+      <c r="C14" s="72"/>
+      <c r="D14" s="68"/>
+      <c r="E14" s="68"/>
       <c r="F14" s="11">
         <v>2.377744E-4</v>
       </c>
@@ -1438,7 +1478,7 @@
       <c r="J14" s="11">
         <v>0.49770047779999999</v>
       </c>
-      <c r="K14" s="75"/>
+      <c r="K14" s="70"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
@@ -1447,13 +1487,13 @@
       <c r="B16" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C16" s="68" t="s">
+      <c r="C16" s="72" t="s">
         <v>44</v>
       </c>
-      <c r="D16" s="69" t="s">
+      <c r="D16" s="68" t="s">
         <v>19</v>
       </c>
-      <c r="E16" s="69" t="s">
+      <c r="E16" s="68" t="s">
         <v>27</v>
       </c>
       <c r="F16" s="11">
@@ -1471,7 +1511,7 @@
       <c r="J16" s="11">
         <v>0.44106115289999998</v>
       </c>
-      <c r="K16" s="75" t="s">
+      <c r="K16" s="70" t="s">
         <v>36</v>
       </c>
     </row>
@@ -1482,9 +1522,9 @@
       <c r="B17" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C17" s="68"/>
-      <c r="D17" s="69"/>
-      <c r="E17" s="69"/>
+      <c r="C17" s="72"/>
+      <c r="D17" s="68"/>
+      <c r="E17" s="68"/>
       <c r="F17" s="11">
         <v>6.6187922000000001E-3</v>
       </c>
@@ -1500,7 +1540,7 @@
       <c r="J17" s="11">
         <v>0.48203358359999998</v>
       </c>
-      <c r="K17" s="75"/>
+      <c r="K17" s="70"/>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
@@ -1509,9 +1549,9 @@
       <c r="B18" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C18" s="68"/>
-      <c r="D18" s="69"/>
-      <c r="E18" s="69"/>
+      <c r="C18" s="72"/>
+      <c r="D18" s="68"/>
+      <c r="E18" s="68"/>
       <c r="F18" s="11">
         <v>1.9467035999999999E-3</v>
       </c>
@@ -1527,7 +1567,7 @@
       <c r="J18" s="11">
         <v>0.31319458500000003</v>
       </c>
-      <c r="K18" s="75"/>
+      <c r="K18" s="70"/>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
@@ -1536,13 +1576,13 @@
       <c r="B20" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C20" s="68" t="s">
+      <c r="C20" s="72" t="s">
         <v>45</v>
       </c>
-      <c r="D20" s="69" t="s">
+      <c r="D20" s="68" t="s">
         <v>20</v>
       </c>
-      <c r="E20" s="69" t="s">
+      <c r="E20" s="68" t="s">
         <v>28</v>
       </c>
       <c r="F20" s="11">
@@ -1560,7 +1600,7 @@
       <c r="J20" s="11">
         <v>0.42558258160000001</v>
       </c>
-      <c r="K20" s="75" t="s">
+      <c r="K20" s="70" t="s">
         <v>35</v>
       </c>
     </row>
@@ -1571,9 +1611,9 @@
       <c r="B21" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C21" s="68"/>
-      <c r="D21" s="69"/>
-      <c r="E21" s="69"/>
+      <c r="C21" s="72"/>
+      <c r="D21" s="68"/>
+      <c r="E21" s="68"/>
       <c r="F21" s="11">
         <v>0.36964094320000002</v>
       </c>
@@ -1589,7 +1629,7 @@
       <c r="J21" s="11">
         <v>0.71370811339999995</v>
       </c>
-      <c r="K21" s="75"/>
+      <c r="K21" s="70"/>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
@@ -1598,9 +1638,9 @@
       <c r="B22" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C22" s="68"/>
-      <c r="D22" s="69"/>
-      <c r="E22" s="69"/>
+      <c r="C22" s="72"/>
+      <c r="D22" s="68"/>
+      <c r="E22" s="68"/>
       <c r="F22" s="11">
         <v>1.786352E-4</v>
       </c>
@@ -1616,7 +1656,7 @@
       <c r="J22" s="11">
         <v>0.35677707139999998</v>
       </c>
-      <c r="K22" s="75"/>
+      <c r="K22" s="70"/>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
@@ -1625,13 +1665,13 @@
       <c r="B24" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C24" s="68" t="s">
+      <c r="C24" s="72" t="s">
         <v>46</v>
       </c>
-      <c r="D24" s="69" t="s">
+      <c r="D24" s="68" t="s">
         <v>21</v>
       </c>
-      <c r="E24" s="69" t="s">
+      <c r="E24" s="68" t="s">
         <v>32</v>
       </c>
       <c r="F24" s="11">
@@ -1657,9 +1697,9 @@
       <c r="B25" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C25" s="68"/>
-      <c r="D25" s="69"/>
-      <c r="E25" s="69"/>
+      <c r="C25" s="72"/>
+      <c r="D25" s="68"/>
+      <c r="E25" s="68"/>
       <c r="F25" s="11">
         <v>2.2257384000000002E-2</v>
       </c>
@@ -1683,9 +1723,9 @@
       <c r="B26" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C26" s="68"/>
-      <c r="D26" s="69"/>
-      <c r="E26" s="69"/>
+      <c r="C26" s="72"/>
+      <c r="D26" s="68"/>
+      <c r="E26" s="68"/>
       <c r="F26" s="11">
         <v>3.9556960000000001E-4</v>
       </c>
@@ -1709,13 +1749,13 @@
       <c r="B28" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C28" s="68" t="s">
+      <c r="C28" s="72" t="s">
         <v>47</v>
       </c>
-      <c r="D28" s="69" t="s">
+      <c r="D28" s="68" t="s">
         <v>22</v>
       </c>
-      <c r="E28" s="69" t="s">
+      <c r="E28" s="68" t="s">
         <v>33</v>
       </c>
       <c r="F28" s="11">
@@ -1741,9 +1781,9 @@
       <c r="B29" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C29" s="68"/>
-      <c r="D29" s="69"/>
-      <c r="E29" s="69"/>
+      <c r="C29" s="72"/>
+      <c r="D29" s="68"/>
+      <c r="E29" s="68"/>
       <c r="F29" s="11">
         <v>1.8442843300000001E-2</v>
       </c>
@@ -1767,9 +1807,9 @@
       <c r="B30" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C30" s="68"/>
-      <c r="D30" s="69"/>
-      <c r="E30" s="69"/>
+      <c r="C30" s="72"/>
+      <c r="D30" s="68"/>
+      <c r="E30" s="68"/>
       <c r="F30" s="11">
         <v>6.9899990000000004E-4</v>
       </c>
@@ -1793,13 +1833,13 @@
       <c r="B32" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C32" s="68" t="s">
+      <c r="C32" s="72" t="s">
         <v>48</v>
       </c>
-      <c r="D32" s="69" t="s">
+      <c r="D32" s="68" t="s">
         <v>23</v>
       </c>
-      <c r="E32" s="69" t="s">
+      <c r="E32" s="68" t="s">
         <v>29</v>
       </c>
       <c r="F32" s="11">
@@ -1825,9 +1865,9 @@
       <c r="B33" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C33" s="68"/>
-      <c r="D33" s="69"/>
-      <c r="E33" s="69"/>
+      <c r="C33" s="72"/>
+      <c r="D33" s="68"/>
+      <c r="E33" s="68"/>
       <c r="F33" s="11">
         <v>4.8571429999999999E-4</v>
       </c>
@@ -1851,9 +1891,9 @@
       <c r="B34" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C34" s="68"/>
-      <c r="D34" s="69"/>
-      <c r="E34" s="69"/>
+      <c r="C34" s="72"/>
+      <c r="D34" s="68"/>
+      <c r="E34" s="68"/>
       <c r="F34" s="11">
         <v>8.5714299999999993E-5</v>
       </c>
@@ -1877,13 +1917,13 @@
       <c r="B36" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C36" s="68" t="s">
+      <c r="C36" s="72" t="s">
         <v>49</v>
       </c>
-      <c r="D36" s="69" t="s">
+      <c r="D36" s="68" t="s">
         <v>24</v>
       </c>
-      <c r="E36" s="69" t="s">
+      <c r="E36" s="68" t="s">
         <v>34</v>
       </c>
       <c r="F36" s="11">
@@ -1909,9 +1949,9 @@
       <c r="B37" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C37" s="68"/>
-      <c r="D37" s="69"/>
-      <c r="E37" s="69"/>
+      <c r="C37" s="72"/>
+      <c r="D37" s="68"/>
+      <c r="E37" s="68"/>
       <c r="F37" s="11">
         <v>0.12567659680000001</v>
       </c>
@@ -1935,9 +1975,9 @@
       <c r="B38" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C38" s="68"/>
-      <c r="D38" s="69"/>
-      <c r="E38" s="69"/>
+      <c r="C38" s="72"/>
+      <c r="D38" s="68"/>
+      <c r="E38" s="68"/>
       <c r="F38" s="11">
         <v>5.4127739999999998E-4</v>
       </c>
@@ -1955,12 +1995,12 @@
       </c>
     </row>
     <row r="40" spans="1:11" s="59" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="70" t="s">
+      <c r="A40" s="73" t="s">
         <v>38</v>
       </c>
-      <c r="B40" s="70"/>
-      <c r="C40" s="70"/>
-      <c r="D40" s="70"/>
+      <c r="B40" s="73"/>
+      <c r="C40" s="73"/>
+      <c r="D40" s="73"/>
       <c r="E40" s="60"/>
       <c r="F40" s="61"/>
       <c r="G40" s="61"/>
@@ -1976,13 +2016,13 @@
       <c r="B42" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C42" s="68" t="s">
+      <c r="C42" s="72" t="s">
         <v>50</v>
       </c>
-      <c r="D42" s="69" t="s">
+      <c r="D42" s="68" t="s">
         <v>25</v>
       </c>
-      <c r="E42" s="69" t="s">
+      <c r="E42" s="68" t="s">
         <v>27</v>
       </c>
       <c r="F42" s="11">
@@ -2000,7 +2040,7 @@
       <c r="J42" s="11">
         <v>0.47978398890000001</v>
       </c>
-      <c r="K42" s="75" t="s">
+      <c r="K42" s="70" t="s">
         <v>30</v>
       </c>
     </row>
@@ -2011,9 +2051,9 @@
       <c r="B43" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C43" s="68"/>
-      <c r="D43" s="69"/>
-      <c r="E43" s="69"/>
+      <c r="C43" s="72"/>
+      <c r="D43" s="68"/>
+      <c r="E43" s="68"/>
       <c r="F43" s="11">
         <v>0.15768715</v>
       </c>
@@ -2029,7 +2069,7 @@
       <c r="J43" s="11">
         <v>0.64265883619999997</v>
       </c>
-      <c r="K43" s="75"/>
+      <c r="K43" s="70"/>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
@@ -2038,9 +2078,9 @@
       <c r="B44" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C44" s="68"/>
-      <c r="D44" s="69"/>
-      <c r="E44" s="69"/>
+      <c r="C44" s="72"/>
+      <c r="D44" s="68"/>
+      <c r="E44" s="68"/>
       <c r="F44" s="11">
         <v>1.5776599999999999E-4</v>
       </c>
@@ -2056,7 +2096,7 @@
       <c r="J44" s="11">
         <v>0.33957444949999999</v>
       </c>
-      <c r="K44" s="75"/>
+      <c r="K44" s="70"/>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
@@ -2065,13 +2105,13 @@
       <c r="B46" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C46" s="68" t="s">
+      <c r="C46" s="72" t="s">
         <v>51</v>
       </c>
-      <c r="D46" s="69" t="s">
+      <c r="D46" s="68" t="s">
         <v>26</v>
       </c>
-      <c r="E46" s="69" t="s">
+      <c r="E46" s="68" t="s">
         <v>28</v>
       </c>
       <c r="F46" s="11">
@@ -2089,7 +2129,7 @@
       <c r="J46" s="11">
         <v>0.43650638670000003</v>
       </c>
-      <c r="K46" s="75" t="s">
+      <c r="K46" s="70" t="s">
         <v>31</v>
       </c>
     </row>
@@ -2100,9 +2140,9 @@
       <c r="B47" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C47" s="68"/>
-      <c r="D47" s="69"/>
-      <c r="E47" s="69"/>
+      <c r="C47" s="72"/>
+      <c r="D47" s="68"/>
+      <c r="E47" s="68"/>
       <c r="F47" s="11">
         <v>0.28846457310000001</v>
       </c>
@@ -2118,7 +2158,7 @@
       <c r="J47" s="11">
         <v>0.62979789600000002</v>
       </c>
-      <c r="K47" s="75"/>
+      <c r="K47" s="70"/>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
@@ -2127,9 +2167,9 @@
       <c r="B48" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C48" s="68"/>
-      <c r="D48" s="69"/>
-      <c r="E48" s="69"/>
+      <c r="C48" s="72"/>
+      <c r="D48" s="68"/>
+      <c r="E48" s="68"/>
       <c r="F48" s="11">
         <v>2.7615590000000002E-4</v>
       </c>
@@ -2145,7 +2185,7 @@
       <c r="J48" s="11">
         <v>0.39453545410000002</v>
       </c>
-      <c r="K48" s="75"/>
+      <c r="K48" s="70"/>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
@@ -2154,13 +2194,13 @@
       <c r="B50" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C50" s="68" t="s">
+      <c r="C50" s="72" t="s">
         <v>52</v>
       </c>
-      <c r="D50" s="69" t="s">
+      <c r="D50" s="68" t="s">
         <v>39</v>
       </c>
-      <c r="E50" s="69" t="s">
+      <c r="E50" s="68" t="s">
         <v>29</v>
       </c>
       <c r="F50" s="11">
@@ -2186,9 +2226,9 @@
       <c r="B51" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C51" s="68"/>
-      <c r="D51" s="69"/>
-      <c r="E51" s="69"/>
+      <c r="C51" s="72"/>
+      <c r="D51" s="68"/>
+      <c r="E51" s="68"/>
       <c r="F51" s="11">
         <v>3.5391416699999997E-2</v>
       </c>
@@ -2212,9 +2252,9 @@
       <c r="B52" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C52" s="68"/>
-      <c r="D52" s="69"/>
-      <c r="E52" s="69"/>
+      <c r="C52" s="72"/>
+      <c r="D52" s="68"/>
+      <c r="E52" s="68"/>
       <c r="F52" s="11">
         <v>9.9344299999999997E-5</v>
       </c>
@@ -2232,12 +2272,12 @@
       </c>
     </row>
     <row r="55" spans="1:11" s="42" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="67" t="s">
+      <c r="A55" s="75" t="s">
         <v>59</v>
       </c>
-      <c r="B55" s="67"/>
-      <c r="C55" s="67"/>
-      <c r="D55" s="67"/>
+      <c r="B55" s="75"/>
+      <c r="C55" s="75"/>
+      <c r="D55" s="75"/>
       <c r="E55" s="39"/>
       <c r="F55" s="40">
         <f>MAX(F2:F52)</f>
@@ -2262,12 +2302,12 @@
       <c r="K55" s="41"/>
     </row>
     <row r="56" spans="1:11" s="46" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="73" t="s">
+      <c r="A56" s="67" t="s">
         <v>60</v>
       </c>
-      <c r="B56" s="73"/>
-      <c r="C56" s="73"/>
-      <c r="D56" s="73"/>
+      <c r="B56" s="67"/>
+      <c r="C56" s="67"/>
+      <c r="D56" s="67"/>
       <c r="E56" s="43"/>
       <c r="F56" s="44">
         <f>AVERAGE(F2:F52)</f>
@@ -2293,6 +2333,37 @@
     </row>
   </sheetData>
   <mergeCells count="47">
+    <mergeCell ref="A55:D55"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="C12:C14"/>
+    <mergeCell ref="C16:C18"/>
+    <mergeCell ref="C20:C22"/>
+    <mergeCell ref="C24:C26"/>
+    <mergeCell ref="C50:C52"/>
+    <mergeCell ref="D24:D26"/>
+    <mergeCell ref="D28:D30"/>
+    <mergeCell ref="D32:D34"/>
+    <mergeCell ref="D36:D38"/>
+    <mergeCell ref="D42:D44"/>
+    <mergeCell ref="D46:D48"/>
+    <mergeCell ref="D50:D52"/>
+    <mergeCell ref="A40:D40"/>
+    <mergeCell ref="D2:D4"/>
+    <mergeCell ref="D6:D8"/>
+    <mergeCell ref="D12:D14"/>
+    <mergeCell ref="D16:D18"/>
+    <mergeCell ref="D20:D22"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="C2:C4"/>
+    <mergeCell ref="E12:E14"/>
+    <mergeCell ref="E16:E18"/>
+    <mergeCell ref="E20:E22"/>
+    <mergeCell ref="C42:C44"/>
+    <mergeCell ref="C46:C48"/>
+    <mergeCell ref="C28:C30"/>
+    <mergeCell ref="C32:C34"/>
+    <mergeCell ref="C36:C38"/>
+    <mergeCell ref="E46:E48"/>
     <mergeCell ref="A56:D56"/>
     <mergeCell ref="E50:E52"/>
     <mergeCell ref="K2:K4"/>
@@ -2309,37 +2380,6 @@
     <mergeCell ref="E42:E44"/>
     <mergeCell ref="E2:E4"/>
     <mergeCell ref="E6:E8"/>
-    <mergeCell ref="E12:E14"/>
-    <mergeCell ref="E16:E18"/>
-    <mergeCell ref="E20:E22"/>
-    <mergeCell ref="C42:C44"/>
-    <mergeCell ref="C46:C48"/>
-    <mergeCell ref="C28:C30"/>
-    <mergeCell ref="C32:C34"/>
-    <mergeCell ref="C36:C38"/>
-    <mergeCell ref="E46:E48"/>
-    <mergeCell ref="D2:D4"/>
-    <mergeCell ref="D6:D8"/>
-    <mergeCell ref="D12:D14"/>
-    <mergeCell ref="D16:D18"/>
-    <mergeCell ref="D20:D22"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="C2:C4"/>
-    <mergeCell ref="A55:D55"/>
-    <mergeCell ref="C6:C8"/>
-    <mergeCell ref="C12:C14"/>
-    <mergeCell ref="C16:C18"/>
-    <mergeCell ref="C20:C22"/>
-    <mergeCell ref="C24:C26"/>
-    <mergeCell ref="C50:C52"/>
-    <mergeCell ref="D24:D26"/>
-    <mergeCell ref="D28:D30"/>
-    <mergeCell ref="D32:D34"/>
-    <mergeCell ref="D36:D38"/>
-    <mergeCell ref="D42:D44"/>
-    <mergeCell ref="D46:D48"/>
-    <mergeCell ref="D50:D52"/>
-    <mergeCell ref="A40:D40"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2407,7 +2447,7 @@
       <c r="B2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="72" t="s">
+      <c r="C2" s="74" t="s">
         <v>41</v>
       </c>
       <c r="D2" s="71" t="s">
@@ -2431,7 +2471,7 @@
       <c r="J2" s="11">
         <v>0.5008326072</v>
       </c>
-      <c r="K2" s="74" t="s">
+      <c r="K2" s="69" t="s">
         <v>15</v>
       </c>
     </row>
@@ -2442,9 +2482,9 @@
       <c r="B3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="68"/>
-      <c r="D3" s="69"/>
-      <c r="E3" s="69"/>
+      <c r="C3" s="72"/>
+      <c r="D3" s="68"/>
+      <c r="E3" s="68"/>
       <c r="F3" s="11">
         <v>2.8763183099999999E-2</v>
       </c>
@@ -2460,7 +2500,7 @@
       <c r="J3" s="11">
         <v>0.49456959480000001</v>
       </c>
-      <c r="K3" s="75"/>
+      <c r="K3" s="70"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
@@ -2469,9 +2509,9 @@
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="68"/>
-      <c r="D4" s="69"/>
-      <c r="E4" s="69"/>
+      <c r="C4" s="72"/>
+      <c r="D4" s="68"/>
+      <c r="E4" s="68"/>
       <c r="F4" s="11">
         <v>5.7526370000000003E-4</v>
       </c>
@@ -2487,7 +2527,7 @@
       <c r="J4" s="11">
         <v>0.46208879800000002</v>
       </c>
-      <c r="K4" s="75"/>
+      <c r="K4" s="70"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="G5" s="11"/>
@@ -2502,13 +2542,13 @@
       <c r="B6" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="68" t="s">
+      <c r="C6" s="72" t="s">
         <v>42</v>
       </c>
-      <c r="D6" s="69" t="s">
+      <c r="D6" s="68" t="s">
         <v>10</v>
       </c>
-      <c r="E6" s="69" t="s">
+      <c r="E6" s="68" t="s">
         <v>13</v>
       </c>
       <c r="F6" s="11">
@@ -2526,7 +2566,7 @@
       <c r="J6" s="11">
         <v>0.50993042769999997</v>
       </c>
-      <c r="K6" s="75" t="s">
+      <c r="K6" s="70" t="s">
         <v>16</v>
       </c>
     </row>
@@ -2537,9 +2577,9 @@
       <c r="B7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="68"/>
-      <c r="D7" s="69"/>
-      <c r="E7" s="69"/>
+      <c r="C7" s="72"/>
+      <c r="D7" s="68"/>
+      <c r="E7" s="68"/>
       <c r="F7" s="11">
         <v>3.3435524000000001E-2</v>
       </c>
@@ -2555,7 +2595,7 @@
       <c r="J7" s="11">
         <v>0.50392556320000004</v>
       </c>
-      <c r="K7" s="75"/>
+      <c r="K7" s="70"/>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
@@ -2564,9 +2604,9 @@
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="68"/>
-      <c r="D8" s="69"/>
-      <c r="E8" s="69"/>
+      <c r="C8" s="72"/>
+      <c r="D8" s="68"/>
+      <c r="E8" s="68"/>
       <c r="F8" s="11">
         <v>3.8321520000000002E-4</v>
       </c>
@@ -2582,7 +2622,7 @@
       <c r="J8" s="11">
         <v>0.47738500210000001</v>
       </c>
-      <c r="K8" s="75"/>
+      <c r="K8" s="70"/>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="G9" s="11"/>
@@ -2591,12 +2631,12 @@
       <c r="J9" s="11"/>
     </row>
     <row r="10" spans="1:12" s="59" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="70" t="s">
+      <c r="A10" s="73" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="70"/>
-      <c r="C10" s="70"/>
-      <c r="D10" s="70"/>
+      <c r="B10" s="73"/>
+      <c r="C10" s="73"/>
+      <c r="D10" s="73"/>
       <c r="E10" s="60"/>
       <c r="F10" s="61"/>
       <c r="G10" s="61"/>
@@ -2618,13 +2658,13 @@
       <c r="B12" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C12" s="68" t="s">
+      <c r="C12" s="72" t="s">
         <v>43</v>
       </c>
-      <c r="D12" s="69" t="s">
+      <c r="D12" s="68" t="s">
         <v>11</v>
       </c>
-      <c r="E12" s="69" t="s">
+      <c r="E12" s="68" t="s">
         <v>17</v>
       </c>
       <c r="F12" s="11">
@@ -2642,7 +2682,7 @@
       <c r="J12" s="11">
         <v>0.4966675035</v>
       </c>
-      <c r="K12" s="75" t="s">
+      <c r="K12" s="70" t="s">
         <v>18</v>
       </c>
     </row>
@@ -2653,9 +2693,9 @@
       <c r="B13" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C13" s="68"/>
-      <c r="D13" s="69"/>
-      <c r="E13" s="69"/>
+      <c r="C13" s="72"/>
+      <c r="D13" s="68"/>
+      <c r="E13" s="68"/>
       <c r="F13" s="11">
         <v>2.876318E-4</v>
       </c>
@@ -2671,7 +2711,7 @@
       <c r="J13" s="11">
         <v>0.48225264400000001</v>
       </c>
-      <c r="K13" s="75"/>
+      <c r="K13" s="70"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
@@ -2680,9 +2720,9 @@
       <c r="B14" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C14" s="68"/>
-      <c r="D14" s="69"/>
-      <c r="E14" s="69"/>
+      <c r="C14" s="72"/>
+      <c r="D14" s="68"/>
+      <c r="E14" s="68"/>
       <c r="F14" s="11">
         <v>6.7114089999999996E-4</v>
       </c>
@@ -2698,7 +2738,7 @@
       <c r="J14" s="11">
         <v>0.43776818420000002</v>
       </c>
-      <c r="K14" s="75"/>
+      <c r="K14" s="70"/>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="G15" s="11"/>
@@ -2713,13 +2753,13 @@
       <c r="B16" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C16" s="68" t="s">
+      <c r="C16" s="72" t="s">
         <v>44</v>
       </c>
-      <c r="D16" s="69" t="s">
+      <c r="D16" s="68" t="s">
         <v>19</v>
       </c>
-      <c r="E16" s="69" t="s">
+      <c r="E16" s="68" t="s">
         <v>27</v>
       </c>
       <c r="F16" s="11">
@@ -2737,7 +2777,7 @@
       <c r="J16" s="11">
         <v>0.44130707470000002</v>
       </c>
-      <c r="K16" s="75" t="s">
+      <c r="K16" s="70" t="s">
         <v>36</v>
       </c>
     </row>
@@ -2748,9 +2788,9 @@
       <c r="B17" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C17" s="68"/>
-      <c r="D17" s="69"/>
-      <c r="E17" s="69"/>
+      <c r="C17" s="72"/>
+      <c r="D17" s="68"/>
+      <c r="E17" s="68"/>
       <c r="F17" s="11">
         <v>7.7660593999999998E-3</v>
       </c>
@@ -2766,7 +2806,7 @@
       <c r="J17" s="11">
         <v>0.46778393010000002</v>
       </c>
-      <c r="K17" s="75"/>
+      <c r="K17" s="70"/>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
@@ -2775,9 +2815,9 @@
       <c r="B18" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C18" s="68"/>
-      <c r="D18" s="69"/>
-      <c r="E18" s="69"/>
+      <c r="C18" s="72"/>
+      <c r="D18" s="68"/>
+      <c r="E18" s="68"/>
       <c r="F18" s="11">
         <v>2.876318E-4</v>
       </c>
@@ -2793,7 +2833,7 @@
       <c r="J18" s="11">
         <v>0.46815617929999997</v>
       </c>
-      <c r="K18" s="75"/>
+      <c r="K18" s="70"/>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.2">
       <c r="G19" s="11"/>
@@ -2808,13 +2848,13 @@
       <c r="B20" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C20" s="68" t="s">
+      <c r="C20" s="72" t="s">
         <v>45</v>
       </c>
-      <c r="D20" s="69" t="s">
+      <c r="D20" s="68" t="s">
         <v>20</v>
       </c>
-      <c r="E20" s="69" t="s">
+      <c r="E20" s="68" t="s">
         <v>28</v>
       </c>
       <c r="F20" s="11">
@@ -2832,7 +2872,7 @@
       <c r="J20" s="11">
         <v>0.4434595543</v>
       </c>
-      <c r="K20" s="75" t="s">
+      <c r="K20" s="70" t="s">
         <v>35</v>
       </c>
     </row>
@@ -2843,9 +2883,9 @@
       <c r="B21" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C21" s="68"/>
-      <c r="D21" s="69"/>
-      <c r="E21" s="69"/>
+      <c r="C21" s="72"/>
+      <c r="D21" s="68"/>
+      <c r="E21" s="68"/>
       <c r="F21" s="11">
         <v>5.11025887E-2</v>
       </c>
@@ -2861,7 +2901,7 @@
       <c r="J21" s="11">
         <v>0.46092753450000001</v>
       </c>
-      <c r="K21" s="75"/>
+      <c r="K21" s="70"/>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
@@ -2870,9 +2910,9 @@
       <c r="B22" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C22" s="68"/>
-      <c r="D22" s="69"/>
-      <c r="E22" s="69"/>
+      <c r="C22" s="72"/>
+      <c r="D22" s="68"/>
+      <c r="E22" s="68"/>
       <c r="F22" s="11">
         <v>0</v>
       </c>
@@ -2888,7 +2928,7 @@
       <c r="J22" s="11">
         <v>0.4740446935</v>
       </c>
-      <c r="K22" s="75"/>
+      <c r="K22" s="70"/>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.2">
       <c r="G23" s="11"/>
@@ -2903,13 +2943,13 @@
       <c r="B24" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C24" s="68" t="s">
+      <c r="C24" s="72" t="s">
         <v>46</v>
       </c>
-      <c r="D24" s="69" t="s">
+      <c r="D24" s="68" t="s">
         <v>21</v>
       </c>
-      <c r="E24" s="69" t="s">
+      <c r="E24" s="68" t="s">
         <v>32</v>
       </c>
       <c r="F24" s="11">
@@ -2935,9 +2975,9 @@
       <c r="B25" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C25" s="68"/>
-      <c r="D25" s="69"/>
-      <c r="E25" s="69"/>
+      <c r="C25" s="72"/>
+      <c r="D25" s="68"/>
+      <c r="E25" s="68"/>
       <c r="F25" s="11">
         <v>3.0584851400000002E-2</v>
       </c>
@@ -2961,9 +3001,9 @@
       <c r="B26" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C26" s="68"/>
-      <c r="D26" s="69"/>
-      <c r="E26" s="69"/>
+      <c r="C26" s="72"/>
+      <c r="D26" s="68"/>
+      <c r="E26" s="68"/>
       <c r="F26" s="11">
         <v>6.7114089999999996E-4</v>
       </c>
@@ -2993,13 +3033,13 @@
       <c r="B28" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C28" s="68" t="s">
+      <c r="C28" s="72" t="s">
         <v>47</v>
       </c>
-      <c r="D28" s="69" t="s">
+      <c r="D28" s="68" t="s">
         <v>22</v>
       </c>
-      <c r="E28" s="69" t="s">
+      <c r="E28" s="68" t="s">
         <v>33</v>
       </c>
       <c r="F28" s="11">
@@ -3025,9 +3065,9 @@
       <c r="B29" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C29" s="68"/>
-      <c r="D29" s="69"/>
-      <c r="E29" s="69"/>
+      <c r="C29" s="72"/>
+      <c r="D29" s="68"/>
+      <c r="E29" s="68"/>
       <c r="F29" s="11">
         <v>1.42857143E-2</v>
       </c>
@@ -3051,9 +3091,9 @@
       <c r="B30" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C30" s="68"/>
-      <c r="D30" s="69"/>
-      <c r="E30" s="69"/>
+      <c r="C30" s="72"/>
+      <c r="D30" s="68"/>
+      <c r="E30" s="68"/>
       <c r="F30" s="11">
         <v>3.8350910000000001E-4</v>
       </c>
@@ -3083,13 +3123,13 @@
       <c r="B32" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C32" s="68" t="s">
+      <c r="C32" s="72" t="s">
         <v>48</v>
       </c>
-      <c r="D32" s="69" t="s">
+      <c r="D32" s="68" t="s">
         <v>23</v>
       </c>
-      <c r="E32" s="69" t="s">
+      <c r="E32" s="68" t="s">
         <v>29</v>
       </c>
       <c r="F32" s="11">
@@ -3115,9 +3155,9 @@
       <c r="B33" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C33" s="68"/>
-      <c r="D33" s="69"/>
-      <c r="E33" s="69"/>
+      <c r="C33" s="72"/>
+      <c r="D33" s="68"/>
+      <c r="E33" s="68"/>
       <c r="F33" s="11">
         <v>6.9727237799999994E-2</v>
       </c>
@@ -3141,9 +3181,9 @@
       <c r="B34" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C34" s="68"/>
-      <c r="D34" s="69"/>
-      <c r="E34" s="69"/>
+      <c r="C34" s="72"/>
+      <c r="D34" s="68"/>
+      <c r="E34" s="68"/>
       <c r="F34" s="11">
         <v>2.8812910000000001E-4</v>
       </c>
@@ -3173,13 +3213,13 @@
       <c r="B36" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C36" s="68" t="s">
+      <c r="C36" s="72" t="s">
         <v>49</v>
       </c>
-      <c r="D36" s="69" t="s">
+      <c r="D36" s="68" t="s">
         <v>24</v>
       </c>
-      <c r="E36" s="69" t="s">
+      <c r="E36" s="68" t="s">
         <v>34</v>
       </c>
       <c r="F36" s="11">
@@ -3205,9 +3245,9 @@
       <c r="B37" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C37" s="68"/>
-      <c r="D37" s="69"/>
-      <c r="E37" s="69"/>
+      <c r="C37" s="72"/>
+      <c r="D37" s="68"/>
+      <c r="E37" s="68"/>
       <c r="F37" s="11">
         <v>1.4189837E-2</v>
       </c>
@@ -3231,9 +3271,9 @@
       <c r="B38" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C38" s="68"/>
-      <c r="D38" s="69"/>
-      <c r="E38" s="69"/>
+      <c r="C38" s="72"/>
+      <c r="D38" s="68"/>
+      <c r="E38" s="68"/>
       <c r="F38" s="11">
         <v>2.876318E-4</v>
       </c>
@@ -3257,12 +3297,12 @@
       <c r="J39" s="11"/>
     </row>
     <row r="40" spans="1:11" s="59" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="70" t="s">
+      <c r="A40" s="73" t="s">
         <v>38</v>
       </c>
-      <c r="B40" s="70"/>
-      <c r="C40" s="70"/>
-      <c r="D40" s="70"/>
+      <c r="B40" s="73"/>
+      <c r="C40" s="73"/>
+      <c r="D40" s="73"/>
       <c r="E40" s="60"/>
       <c r="F40" s="61"/>
       <c r="G40" s="61"/>
@@ -3284,13 +3324,13 @@
       <c r="B42" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C42" s="68" t="s">
+      <c r="C42" s="72" t="s">
         <v>50</v>
       </c>
-      <c r="D42" s="69" t="s">
+      <c r="D42" s="68" t="s">
         <v>25</v>
       </c>
-      <c r="E42" s="69" t="s">
+      <c r="E42" s="68" t="s">
         <v>27</v>
       </c>
       <c r="F42" s="11">
@@ -3308,7 +3348,7 @@
       <c r="J42" s="11">
         <v>0.4587482034</v>
       </c>
-      <c r="K42" s="75" t="s">
+      <c r="K42" s="70" t="s">
         <v>30</v>
       </c>
     </row>
@@ -3319,9 +3359,9 @@
       <c r="B43" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C43" s="68"/>
-      <c r="D43" s="69"/>
-      <c r="E43" s="69"/>
+      <c r="C43" s="72"/>
+      <c r="D43" s="68"/>
+      <c r="E43" s="68"/>
       <c r="F43" s="11">
         <v>1.34125311E-2</v>
       </c>
@@ -3337,7 +3377,7 @@
       <c r="J43" s="11">
         <v>0.46907909489999999</v>
       </c>
-      <c r="K43" s="75"/>
+      <c r="K43" s="70"/>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
@@ -3346,9 +3386,9 @@
       <c r="B44" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C44" s="68"/>
-      <c r="D44" s="69"/>
-      <c r="E44" s="69"/>
+      <c r="C44" s="72"/>
+      <c r="D44" s="68"/>
+      <c r="E44" s="68"/>
       <c r="F44" s="11">
         <v>8.6223409999999995E-4</v>
       </c>
@@ -3364,7 +3404,7 @@
       <c r="J44" s="11">
         <v>0.49390839069999998</v>
       </c>
-      <c r="K44" s="75"/>
+      <c r="K44" s="70"/>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.2">
       <c r="G45" s="11"/>
@@ -3379,13 +3419,13 @@
       <c r="B46" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C46" s="68" t="s">
+      <c r="C46" s="72" t="s">
         <v>51</v>
       </c>
-      <c r="D46" s="69" t="s">
+      <c r="D46" s="68" t="s">
         <v>26</v>
       </c>
-      <c r="E46" s="69" t="s">
+      <c r="E46" s="68" t="s">
         <v>28</v>
       </c>
       <c r="F46" s="11">
@@ -3403,7 +3443,7 @@
       <c r="J46" s="11">
         <v>0.45388746419999998</v>
       </c>
-      <c r="K46" s="75" t="s">
+      <c r="K46" s="70" t="s">
         <v>31</v>
       </c>
     </row>
@@ -3414,9 +3454,9 @@
       <c r="B47" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C47" s="68"/>
-      <c r="D47" s="69"/>
-      <c r="E47" s="69"/>
+      <c r="C47" s="72"/>
+      <c r="D47" s="68"/>
+      <c r="E47" s="68"/>
       <c r="F47" s="11">
         <v>4.3303314799999999E-2</v>
       </c>
@@ -3432,7 +3472,7 @@
       <c r="J47" s="11">
         <v>0.45908136910000003</v>
       </c>
-      <c r="K47" s="75"/>
+      <c r="K47" s="70"/>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
@@ -3441,9 +3481,9 @@
       <c r="B48" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C48" s="68"/>
-      <c r="D48" s="69"/>
-      <c r="E48" s="69"/>
+      <c r="C48" s="72"/>
+      <c r="D48" s="68"/>
+      <c r="E48" s="68"/>
       <c r="F48" s="11">
         <v>9.5803800000000006E-5</v>
       </c>
@@ -3459,7 +3499,7 @@
       <c r="J48" s="11">
         <v>0.478579698</v>
       </c>
-      <c r="K48" s="75"/>
+      <c r="K48" s="70"/>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.2">
       <c r="G49" s="11"/>
@@ -3474,13 +3514,13 @@
       <c r="B50" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C50" s="68" t="s">
+      <c r="C50" s="72" t="s">
         <v>52</v>
       </c>
-      <c r="D50" s="69" t="s">
+      <c r="D50" s="68" t="s">
         <v>39</v>
       </c>
-      <c r="E50" s="69" t="s">
+      <c r="E50" s="68" t="s">
         <v>29</v>
       </c>
       <c r="F50" s="11">
@@ -3506,9 +3546,9 @@
       <c r="B51" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C51" s="68"/>
-      <c r="D51" s="69"/>
-      <c r="E51" s="69"/>
+      <c r="C51" s="72"/>
+      <c r="D51" s="68"/>
+      <c r="E51" s="68"/>
       <c r="F51" s="11">
         <v>8.8139489999999997E-3</v>
       </c>
@@ -3532,9 +3572,9 @@
       <c r="B52" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C52" s="68"/>
-      <c r="D52" s="69"/>
-      <c r="E52" s="69"/>
+      <c r="C52" s="72"/>
+      <c r="D52" s="68"/>
+      <c r="E52" s="68"/>
       <c r="F52" s="11">
         <v>1.9160760000000001E-4</v>
       </c>
@@ -3564,12 +3604,12 @@
       <c r="J54" s="11"/>
     </row>
     <row r="55" spans="1:11" s="42" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="67" t="s">
+      <c r="A55" s="75" t="s">
         <v>59</v>
       </c>
-      <c r="B55" s="67"/>
-      <c r="C55" s="67"/>
-      <c r="D55" s="67"/>
+      <c r="B55" s="75"/>
+      <c r="C55" s="75"/>
+      <c r="D55" s="75"/>
       <c r="E55" s="39"/>
       <c r="F55" s="40">
         <f>MAX(F2:F52)</f>
@@ -3594,12 +3634,12 @@
       <c r="K55" s="41"/>
     </row>
     <row r="56" spans="1:11" s="46" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="73" t="s">
+      <c r="A56" s="67" t="s">
         <v>60</v>
       </c>
-      <c r="B56" s="73"/>
-      <c r="C56" s="73"/>
-      <c r="D56" s="73"/>
+      <c r="B56" s="67"/>
+      <c r="C56" s="67"/>
+      <c r="D56" s="67"/>
       <c r="E56" s="43"/>
       <c r="F56" s="44">
         <f>AVERAGE(F2:F52)</f>
@@ -3625,6 +3665,37 @@
     </row>
   </sheetData>
   <mergeCells count="47">
+    <mergeCell ref="A55:D55"/>
+    <mergeCell ref="K42:K44"/>
+    <mergeCell ref="C46:C48"/>
+    <mergeCell ref="D46:D48"/>
+    <mergeCell ref="E46:E48"/>
+    <mergeCell ref="K46:K48"/>
+    <mergeCell ref="E50:E52"/>
+    <mergeCell ref="C36:C38"/>
+    <mergeCell ref="D36:D38"/>
+    <mergeCell ref="E36:E38"/>
+    <mergeCell ref="A40:D40"/>
+    <mergeCell ref="C42:C44"/>
+    <mergeCell ref="D42:D44"/>
+    <mergeCell ref="E42:E44"/>
+    <mergeCell ref="K12:K14"/>
+    <mergeCell ref="C20:C22"/>
+    <mergeCell ref="D20:D22"/>
+    <mergeCell ref="E20:E22"/>
+    <mergeCell ref="K20:K22"/>
+    <mergeCell ref="C16:C18"/>
+    <mergeCell ref="D16:D18"/>
+    <mergeCell ref="E16:E18"/>
+    <mergeCell ref="K16:K18"/>
+    <mergeCell ref="C2:C4"/>
+    <mergeCell ref="D2:D4"/>
+    <mergeCell ref="E2:E4"/>
+    <mergeCell ref="K2:K4"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="D6:D8"/>
+    <mergeCell ref="E6:E8"/>
+    <mergeCell ref="K6:K8"/>
     <mergeCell ref="A56:D56"/>
     <mergeCell ref="A10:D10"/>
     <mergeCell ref="C12:C14"/>
@@ -3641,37 +3712,6 @@
     <mergeCell ref="E32:E34"/>
     <mergeCell ref="C50:C52"/>
     <mergeCell ref="D50:D52"/>
-    <mergeCell ref="C2:C4"/>
-    <mergeCell ref="D2:D4"/>
-    <mergeCell ref="E2:E4"/>
-    <mergeCell ref="K2:K4"/>
-    <mergeCell ref="C6:C8"/>
-    <mergeCell ref="D6:D8"/>
-    <mergeCell ref="E6:E8"/>
-    <mergeCell ref="K6:K8"/>
-    <mergeCell ref="K12:K14"/>
-    <mergeCell ref="C20:C22"/>
-    <mergeCell ref="D20:D22"/>
-    <mergeCell ref="E20:E22"/>
-    <mergeCell ref="K20:K22"/>
-    <mergeCell ref="C16:C18"/>
-    <mergeCell ref="D16:D18"/>
-    <mergeCell ref="E16:E18"/>
-    <mergeCell ref="K16:K18"/>
-    <mergeCell ref="C36:C38"/>
-    <mergeCell ref="D36:D38"/>
-    <mergeCell ref="E36:E38"/>
-    <mergeCell ref="A40:D40"/>
-    <mergeCell ref="C42:C44"/>
-    <mergeCell ref="D42:D44"/>
-    <mergeCell ref="E42:E44"/>
-    <mergeCell ref="A55:D55"/>
-    <mergeCell ref="K42:K44"/>
-    <mergeCell ref="C46:C48"/>
-    <mergeCell ref="D46:D48"/>
-    <mergeCell ref="E46:E48"/>
-    <mergeCell ref="K46:K48"/>
-    <mergeCell ref="E50:E52"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -3752,7 +3792,7 @@
       <c r="B2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="72" t="s">
+      <c r="C2" s="74" t="s">
         <v>41</v>
       </c>
       <c r="D2" s="71" t="s">
@@ -3788,7 +3828,7 @@
         <f>SUM(F2*1/5,G2*1/5,H2*1/5,I2*1/5,J2*1/5)</f>
         <v>0.29130368856</v>
       </c>
-      <c r="N2" s="74" t="s">
+      <c r="N2" s="69" t="s">
         <v>15</v>
       </c>
     </row>
@@ -3799,9 +3839,9 @@
       <c r="B3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="68"/>
-      <c r="D3" s="69"/>
-      <c r="E3" s="69"/>
+      <c r="C3" s="72"/>
+      <c r="D3" s="68"/>
+      <c r="E3" s="68"/>
       <c r="F3" s="11">
         <v>2.3969319E-3</v>
       </c>
@@ -3829,7 +3869,7 @@
         <f>SUM(F3*1/5,G3*1/5,H3*1/5,I3*1/5,J3*1/5)</f>
         <v>0.26225518991999996</v>
       </c>
-      <c r="N3" s="75"/>
+      <c r="N3" s="70"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
@@ -3838,9 +3878,9 @@
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="68"/>
-      <c r="D4" s="69"/>
-      <c r="E4" s="69"/>
+      <c r="C4" s="72"/>
+      <c r="D4" s="68"/>
+      <c r="E4" s="68"/>
       <c r="F4" s="11">
         <v>6.5867689399999999E-2</v>
       </c>
@@ -3868,7 +3908,7 @@
         <f>SUM(F4*1/5,G4*1/5,H4*1/5,I4*1/5,J4*1/5)</f>
         <v>0.29107094631999997</v>
       </c>
-      <c r="N4" s="75"/>
+      <c r="N4" s="70"/>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
@@ -3877,13 +3917,13 @@
       <c r="B6" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="68" t="s">
+      <c r="C6" s="72" t="s">
         <v>42</v>
       </c>
-      <c r="D6" s="69" t="s">
+      <c r="D6" s="68" t="s">
         <v>10</v>
       </c>
-      <c r="E6" s="69" t="s">
+      <c r="E6" s="68" t="s">
         <v>13</v>
       </c>
       <c r="F6" s="11">
@@ -3913,7 +3953,7 @@
         <f>SUM(F6*1/5,G6*1/5,H6*1/5,I6*1/5,J6*1/5)</f>
         <v>0.29438649154000002</v>
       </c>
-      <c r="N6" s="75" t="s">
+      <c r="N6" s="70" t="s">
         <v>16</v>
       </c>
     </row>
@@ -3924,9 +3964,9 @@
       <c r="B7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="68"/>
-      <c r="D7" s="69"/>
-      <c r="E7" s="69"/>
+      <c r="C7" s="72"/>
+      <c r="D7" s="68"/>
+      <c r="E7" s="68"/>
       <c r="F7" s="11">
         <v>1.3604138700000001E-2</v>
       </c>
@@ -3954,7 +3994,7 @@
         <f>SUM(F7*1/5,G7*1/5,H7*1/5,I7*1/5,J7*1/5)</f>
         <v>0.27579129901999999</v>
       </c>
-      <c r="N7" s="75"/>
+      <c r="N7" s="70"/>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
@@ -3963,9 +4003,9 @@
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="68"/>
-      <c r="D8" s="69"/>
-      <c r="E8" s="69"/>
+      <c r="C8" s="72"/>
+      <c r="D8" s="68"/>
+      <c r="E8" s="68"/>
       <c r="F8" s="11">
         <v>3.8321517499999999E-2</v>
       </c>
@@ -3993,15 +4033,15 @@
         <f>SUM(F8*1/5,G8*1/5,H8*1/5,I8*1/5,J8*1/5)</f>
         <v>0.2717815321</v>
       </c>
-      <c r="N8" s="75"/>
+      <c r="N8" s="70"/>
     </row>
     <row r="10" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="77" t="s">
+      <c r="A10" s="82" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="77"/>
-      <c r="C10" s="77"/>
-      <c r="D10" s="77"/>
+      <c r="B10" s="82"/>
+      <c r="C10" s="82"/>
+      <c r="D10" s="82"/>
       <c r="E10" s="5"/>
       <c r="F10" s="13"/>
       <c r="G10" s="13"/>
@@ -4020,13 +4060,13 @@
       <c r="B12" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C12" s="68" t="s">
+      <c r="C12" s="72" t="s">
         <v>43</v>
       </c>
-      <c r="D12" s="69" t="s">
+      <c r="D12" s="68" t="s">
         <v>11</v>
       </c>
-      <c r="E12" s="69" t="s">
+      <c r="E12" s="68" t="s">
         <v>17</v>
       </c>
       <c r="F12" s="11">
@@ -4056,7 +4096,7 @@
         <f>SUM(F12*1/5,G12*1/5,H12*1/5,I12*1/5,J12*1/5)</f>
         <v>0.33641501256</v>
       </c>
-      <c r="N12" s="75" t="s">
+      <c r="N12" s="70" t="s">
         <v>18</v>
       </c>
     </row>
@@ -4067,9 +4107,9 @@
       <c r="B13" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C13" s="68"/>
-      <c r="D13" s="69"/>
-      <c r="E13" s="69"/>
+      <c r="C13" s="72"/>
+      <c r="D13" s="68"/>
+      <c r="E13" s="68"/>
       <c r="F13" s="11">
         <v>7.9194630899999993E-2</v>
       </c>
@@ -4097,7 +4137,7 @@
         <f>SUM(F13*1/5,G13*1/5,H13*1/5,I13*1/5,J13*1/5)</f>
         <v>0.26691102733999994</v>
       </c>
-      <c r="N13" s="75"/>
+      <c r="N13" s="70"/>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
@@ -4106,9 +4146,9 @@
       <c r="B14" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C14" s="68"/>
-      <c r="D14" s="69"/>
-      <c r="E14" s="69"/>
+      <c r="C14" s="72"/>
+      <c r="D14" s="68"/>
+      <c r="E14" s="68"/>
       <c r="F14" s="11">
         <v>3.8350910000000001E-4</v>
       </c>
@@ -4136,7 +4176,7 @@
         <f>SUM(F14*1/5,G14*1/5,H14*1/5,I14*1/5,J14*1/5)</f>
         <v>0.22330577798000001</v>
       </c>
-      <c r="N14" s="75"/>
+      <c r="N14" s="70"/>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
@@ -4145,13 +4185,13 @@
       <c r="B16" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C16" s="68" t="s">
+      <c r="C16" s="72" t="s">
         <v>44</v>
       </c>
-      <c r="D16" s="69" t="s">
+      <c r="D16" s="68" t="s">
         <v>19</v>
       </c>
-      <c r="E16" s="69" t="s">
+      <c r="E16" s="68" t="s">
         <v>27</v>
       </c>
       <c r="F16" s="11">
@@ -4181,7 +4221,7 @@
         <f>SUM(F16*1/5,G16*1/5,H16*1/5,I16*1/5,J16*1/5)</f>
         <v>0.34767161497999999</v>
       </c>
-      <c r="N16" s="75" t="s">
+      <c r="N16" s="70" t="s">
         <v>36</v>
       </c>
     </row>
@@ -4192,9 +4232,9 @@
       <c r="B17" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C17" s="68"/>
-      <c r="D17" s="69"/>
-      <c r="E17" s="69"/>
+      <c r="C17" s="72"/>
+      <c r="D17" s="68"/>
+      <c r="E17" s="68"/>
       <c r="F17" s="11">
         <v>3.7296260800000001E-2</v>
       </c>
@@ -4222,7 +4262,7 @@
         <f>SUM(F17*1/5,G17*1/5,H17*1/5,I17*1/5,J17*1/5)</f>
         <v>0.33628517706000005</v>
       </c>
-      <c r="N17" s="75"/>
+      <c r="N17" s="70"/>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
@@ -4231,9 +4271,9 @@
       <c r="B18" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C18" s="68"/>
-      <c r="D18" s="69"/>
-      <c r="E18" s="69"/>
+      <c r="C18" s="72"/>
+      <c r="D18" s="68"/>
+      <c r="E18" s="68"/>
       <c r="F18" s="11">
         <v>1.0546500000000001E-3</v>
       </c>
@@ -4261,7 +4301,7 @@
         <f>SUM(F18*1/5,G18*1/5,H18*1/5,I18*1/5,J18*1/5)</f>
         <v>0.20704430204000002</v>
       </c>
-      <c r="N18" s="75"/>
+      <c r="N18" s="70"/>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
@@ -4270,13 +4310,13 @@
       <c r="B20" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C20" s="68" t="s">
+      <c r="C20" s="72" t="s">
         <v>45</v>
       </c>
-      <c r="D20" s="69" t="s">
+      <c r="D20" s="68" t="s">
         <v>20</v>
       </c>
-      <c r="E20" s="69" t="s">
+      <c r="E20" s="68" t="s">
         <v>28</v>
       </c>
       <c r="F20" s="11">
@@ -4306,7 +4346,7 @@
         <f>SUM(F20*1/5,G20*1/5,H20*1/5,I20*1/5,J20*1/5)</f>
         <v>0.31181358595999997</v>
       </c>
-      <c r="N20" s="75" t="s">
+      <c r="N20" s="70" t="s">
         <v>35</v>
       </c>
     </row>
@@ -4317,9 +4357,9 @@
       <c r="B21" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C21" s="68"/>
-      <c r="D21" s="69"/>
-      <c r="E21" s="69"/>
+      <c r="C21" s="72"/>
+      <c r="D21" s="68"/>
+      <c r="E21" s="68"/>
       <c r="F21" s="11">
         <v>1.05465005E-2</v>
       </c>
@@ -4347,7 +4387,7 @@
         <f>SUM(F21*1/5,G21*1/5,H21*1/5,I21*1/5,J21*1/5)</f>
         <v>0.29879759264</v>
       </c>
-      <c r="N21" s="75"/>
+      <c r="N21" s="70"/>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
@@ -4356,9 +4396,9 @@
       <c r="B22" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C22" s="68"/>
-      <c r="D22" s="69"/>
-      <c r="E22" s="69"/>
+      <c r="C22" s="72"/>
+      <c r="D22" s="68"/>
+      <c r="E22" s="68"/>
       <c r="F22" s="11">
         <v>0</v>
       </c>
@@ -4386,7 +4426,7 @@
         <f>SUM(F22*1/5,G22*1/5,H22*1/5,I22*1/5,J22*1/5)</f>
         <v>0.22541820497999998</v>
       </c>
-      <c r="N22" s="75"/>
+      <c r="N22" s="70"/>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
@@ -4395,13 +4435,13 @@
       <c r="B24" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C24" s="68" t="s">
+      <c r="C24" s="72" t="s">
         <v>46</v>
       </c>
-      <c r="D24" s="69" t="s">
+      <c r="D24" s="68" t="s">
         <v>21</v>
       </c>
-      <c r="E24" s="69" t="s">
+      <c r="E24" s="68" t="s">
         <v>32</v>
       </c>
       <c r="F24" s="11">
@@ -4439,9 +4479,9 @@
       <c r="B25" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C25" s="68"/>
-      <c r="D25" s="69"/>
-      <c r="E25" s="69"/>
+      <c r="C25" s="72"/>
+      <c r="D25" s="68"/>
+      <c r="E25" s="68"/>
       <c r="F25" s="11">
         <v>2.7229146700000002E-2</v>
       </c>
@@ -4477,9 +4517,9 @@
       <c r="B26" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C26" s="68"/>
-      <c r="D26" s="69"/>
-      <c r="E26" s="69"/>
+      <c r="C26" s="72"/>
+      <c r="D26" s="68"/>
+      <c r="E26" s="68"/>
       <c r="F26" s="11">
         <v>3.8350910000000001E-4</v>
       </c>
@@ -4515,13 +4555,13 @@
       <c r="B28" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C28" s="68" t="s">
+      <c r="C28" s="72" t="s">
         <v>47</v>
       </c>
-      <c r="D28" s="69" t="s">
+      <c r="D28" s="68" t="s">
         <v>22</v>
       </c>
-      <c r="E28" s="69" t="s">
+      <c r="E28" s="68" t="s">
         <v>33</v>
       </c>
       <c r="F28" s="11">
@@ -4559,9 +4599,9 @@
       <c r="B29" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C29" s="68"/>
-      <c r="D29" s="69"/>
-      <c r="E29" s="69"/>
+      <c r="C29" s="72"/>
+      <c r="D29" s="68"/>
+      <c r="E29" s="68"/>
       <c r="F29" s="11">
         <v>2.8475551299999999E-2</v>
       </c>
@@ -4597,9 +4637,9 @@
       <c r="B30" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C30" s="68"/>
-      <c r="D30" s="69"/>
-      <c r="E30" s="69"/>
+      <c r="C30" s="72"/>
+      <c r="D30" s="68"/>
+      <c r="E30" s="68"/>
       <c r="F30" s="11">
         <v>1.917546E-4</v>
       </c>
@@ -4635,13 +4675,13 @@
       <c r="B32" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C32" s="68" t="s">
+      <c r="C32" s="72" t="s">
         <v>48</v>
       </c>
-      <c r="D32" s="69" t="s">
+      <c r="D32" s="68" t="s">
         <v>23</v>
       </c>
-      <c r="E32" s="69" t="s">
+      <c r="E32" s="68" t="s">
         <v>29</v>
       </c>
       <c r="F32" s="11">
@@ -4679,9 +4719,9 @@
       <c r="B33" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C33" s="68"/>
-      <c r="D33" s="69"/>
-      <c r="E33" s="69"/>
+      <c r="C33" s="72"/>
+      <c r="D33" s="68"/>
+      <c r="E33" s="68"/>
       <c r="F33" s="11">
         <v>2.4010757000000001E-3</v>
       </c>
@@ -4717,9 +4757,9 @@
       <c r="B34" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C34" s="68"/>
-      <c r="D34" s="69"/>
-      <c r="E34" s="69"/>
+      <c r="C34" s="72"/>
+      <c r="D34" s="68"/>
+      <c r="E34" s="68"/>
       <c r="F34" s="11">
         <v>0</v>
       </c>
@@ -4755,13 +4795,13 @@
       <c r="B36" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C36" s="68" t="s">
+      <c r="C36" s="72" t="s">
         <v>49</v>
       </c>
-      <c r="D36" s="69" t="s">
+      <c r="D36" s="68" t="s">
         <v>24</v>
       </c>
-      <c r="E36" s="69" t="s">
+      <c r="E36" s="68" t="s">
         <v>34</v>
       </c>
       <c r="F36" s="11">
@@ -4799,9 +4839,9 @@
       <c r="B37" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C37" s="68"/>
-      <c r="D37" s="69"/>
-      <c r="E37" s="69"/>
+      <c r="C37" s="72"/>
+      <c r="D37" s="68"/>
+      <c r="E37" s="68"/>
       <c r="F37" s="11">
         <v>5.9443912000000003E-3</v>
       </c>
@@ -4837,9 +4877,9 @@
       <c r="B38" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C38" s="68"/>
-      <c r="D38" s="69"/>
-      <c r="E38" s="69"/>
+      <c r="C38" s="72"/>
+      <c r="D38" s="68"/>
+      <c r="E38" s="68"/>
       <c r="F38" s="11">
         <v>1.917546E-4</v>
       </c>
@@ -4869,12 +4909,12 @@
       </c>
     </row>
     <row r="40" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="77" t="s">
+      <c r="A40" s="82" t="s">
         <v>38</v>
       </c>
-      <c r="B40" s="77"/>
-      <c r="C40" s="77"/>
-      <c r="D40" s="77"/>
+      <c r="B40" s="82"/>
+      <c r="C40" s="82"/>
+      <c r="D40" s="82"/>
       <c r="E40" s="5"/>
       <c r="F40" s="13"/>
       <c r="G40" s="13"/>
@@ -4893,13 +4933,13 @@
       <c r="B42" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C42" s="68" t="s">
+      <c r="C42" s="72" t="s">
         <v>50</v>
       </c>
-      <c r="D42" s="69" t="s">
+      <c r="D42" s="68" t="s">
         <v>25</v>
       </c>
-      <c r="E42" s="69" t="s">
+      <c r="E42" s="68" t="s">
         <v>27</v>
       </c>
       <c r="F42" s="11">
@@ -4929,7 +4969,7 @@
         <f>SUM(F42*1/5,G42*1/5,H42*1/5,I42*1/5,J42*1/5)</f>
         <v>0.32911788728000002</v>
       </c>
-      <c r="N42" s="75" t="s">
+      <c r="N42" s="70" t="s">
         <v>30</v>
       </c>
     </row>
@@ -4940,9 +4980,9 @@
       <c r="B43" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C43" s="68"/>
-      <c r="D43" s="69"/>
-      <c r="E43" s="69"/>
+      <c r="C43" s="72"/>
+      <c r="D43" s="68"/>
+      <c r="E43" s="68"/>
       <c r="F43" s="11">
         <v>1.59034298E-2</v>
       </c>
@@ -4970,7 +5010,7 @@
         <f>SUM(F43*1/5,G43*1/5,H43*1/5,I43*1/5,J43*1/5)</f>
         <v>0.33481998118</v>
       </c>
-      <c r="N43" s="75"/>
+      <c r="N43" s="70"/>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
@@ -4979,9 +5019,9 @@
       <c r="B44" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C44" s="68"/>
-      <c r="D44" s="69"/>
-      <c r="E44" s="69"/>
+      <c r="C44" s="72"/>
+      <c r="D44" s="68"/>
+      <c r="E44" s="68"/>
       <c r="F44" s="62">
         <v>0</v>
       </c>
@@ -5009,7 +5049,7 @@
         <f>SUM(F44*1/5,G44*1/5,H44*1/5,I44*1/5,J44*1/5)</f>
         <v>0.23017129817999998</v>
       </c>
-      <c r="N44" s="75"/>
+      <c r="N44" s="70"/>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
@@ -5018,13 +5058,13 @@
       <c r="B46" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C46" s="68" t="s">
+      <c r="C46" s="72" t="s">
         <v>51</v>
       </c>
-      <c r="D46" s="69" t="s">
+      <c r="D46" s="68" t="s">
         <v>26</v>
       </c>
-      <c r="E46" s="69" t="s">
+      <c r="E46" s="68" t="s">
         <v>28</v>
       </c>
       <c r="F46" s="11">
@@ -5054,7 +5094,7 @@
         <f>SUM(F46*1/5,G46*1/5,H46*1/5,I46*1/5,J46*1/5)</f>
         <v>0.28403192430000002</v>
       </c>
-      <c r="N46" s="75" t="s">
+      <c r="N46" s="70" t="s">
         <v>31</v>
       </c>
     </row>
@@ -5065,9 +5105,9 @@
       <c r="B47" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C47" s="68"/>
-      <c r="D47" s="69"/>
-      <c r="E47" s="69"/>
+      <c r="C47" s="72"/>
+      <c r="D47" s="68"/>
+      <c r="E47" s="68"/>
       <c r="F47" s="11">
         <v>2.90285495E-2</v>
       </c>
@@ -5095,7 +5135,7 @@
         <f>SUM(F47*1/5,G47*1/5,H47*1/5,I47*1/5,J47*1/5)</f>
         <v>0.35089340806000002</v>
       </c>
-      <c r="N47" s="75"/>
+      <c r="N47" s="70"/>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
@@ -5104,9 +5144,9 @@
       <c r="B48" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C48" s="68"/>
-      <c r="D48" s="69"/>
-      <c r="E48" s="69"/>
+      <c r="C48" s="72"/>
+      <c r="D48" s="68"/>
+      <c r="E48" s="68"/>
       <c r="F48" s="11">
         <v>1.9160760000000001E-4</v>
       </c>
@@ -5134,7 +5174,7 @@
         <f>SUM(F48*1/5,G48*1/5,H48*1/5,I48*1/5,J48*1/5)</f>
         <v>0.34178323869999999</v>
       </c>
-      <c r="N48" s="75"/>
+      <c r="N48" s="70"/>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
@@ -5143,13 +5183,13 @@
       <c r="B50" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C50" s="68" t="s">
+      <c r="C50" s="72" t="s">
         <v>52</v>
       </c>
-      <c r="D50" s="69" t="s">
+      <c r="D50" s="68" t="s">
         <v>39</v>
       </c>
-      <c r="E50" s="69" t="s">
+      <c r="E50" s="68" t="s">
         <v>29</v>
       </c>
       <c r="F50" s="11">
@@ -5187,9 +5227,9 @@
       <c r="B51" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C51" s="68"/>
-      <c r="D51" s="69"/>
-      <c r="E51" s="69"/>
+      <c r="C51" s="72"/>
+      <c r="D51" s="68"/>
+      <c r="E51" s="68"/>
       <c r="F51" s="11">
         <v>3.4489365999999999E-3</v>
       </c>
@@ -5225,9 +5265,9 @@
       <c r="B52" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C52" s="68"/>
-      <c r="D52" s="69"/>
-      <c r="E52" s="69"/>
+      <c r="C52" s="72"/>
+      <c r="D52" s="68"/>
+      <c r="E52" s="68"/>
       <c r="F52" s="62">
         <v>4.7901900000000002E-4</v>
       </c>
@@ -5257,12 +5297,12 @@
       </c>
     </row>
     <row r="55" spans="1:14" s="14" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="76" t="s">
+      <c r="A55" s="83" t="s">
         <v>59</v>
       </c>
-      <c r="B55" s="76"/>
-      <c r="C55" s="76"/>
-      <c r="D55" s="76"/>
+      <c r="B55" s="83"/>
+      <c r="C55" s="83"/>
+      <c r="D55" s="83"/>
       <c r="E55" s="15"/>
       <c r="F55" s="16">
         <f t="shared" ref="F55:M55" si="0">MAX(F2:F52)</f>
@@ -5299,12 +5339,12 @@
       <c r="N55" s="17"/>
     </row>
     <row r="56" spans="1:14" s="18" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="78" t="s">
+      <c r="A56" s="81" t="s">
         <v>60</v>
       </c>
-      <c r="B56" s="78"/>
-      <c r="C56" s="78"/>
-      <c r="D56" s="78"/>
+      <c r="B56" s="81"/>
+      <c r="C56" s="81"/>
+      <c r="D56" s="81"/>
       <c r="E56" s="19"/>
       <c r="F56" s="20">
         <f t="shared" ref="F56:M56" si="1">AVERAGE(F2:F52)</f>
@@ -5341,13 +5381,13 @@
       <c r="N56" s="21"/>
     </row>
     <row r="58" spans="1:14" s="22" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="81" t="s">
+      <c r="A58" s="78" t="s">
         <v>64</v>
       </c>
-      <c r="B58" s="81"/>
-      <c r="C58" s="81"/>
-      <c r="D58" s="81"/>
-      <c r="E58" s="81"/>
+      <c r="B58" s="78"/>
+      <c r="C58" s="78"/>
+      <c r="D58" s="78"/>
+      <c r="E58" s="78"/>
       <c r="F58" s="29">
         <f>SUM(F55*(1/3),  G55*(1/3), I55*(1/3))</f>
         <v>0.33744571563333331</v>
@@ -5362,13 +5402,13 @@
       <c r="N58" s="24"/>
     </row>
     <row r="59" spans="1:14" s="27" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="82" t="s">
+      <c r="A59" s="79" t="s">
         <v>65</v>
       </c>
-      <c r="B59" s="82"/>
-      <c r="C59" s="82"/>
-      <c r="D59" s="82"/>
-      <c r="E59" s="82"/>
+      <c r="B59" s="79"/>
+      <c r="C59" s="79"/>
+      <c r="D59" s="79"/>
+      <c r="E59" s="79"/>
       <c r="F59" s="28">
         <f>SUM(H55*(1/2),  J55*(1/2))</f>
         <v>0.67529401794999999</v>
@@ -5383,13 +5423,13 @@
       <c r="N59" s="26"/>
     </row>
     <row r="60" spans="1:14" s="33" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="83" t="s">
+      <c r="A60" s="80" t="s">
         <v>66</v>
       </c>
-      <c r="B60" s="83"/>
-      <c r="C60" s="83"/>
-      <c r="D60" s="83"/>
-      <c r="E60" s="83"/>
+      <c r="B60" s="80"/>
+      <c r="C60" s="80"/>
+      <c r="D60" s="80"/>
+      <c r="E60" s="80"/>
       <c r="F60" s="30">
         <f>SUM(F55*1/5, G55*1/5, H55*1/5, I55*1/5,J55*1/5)</f>
         <v>0.47258503656</v>
@@ -5404,12 +5444,12 @@
       <c r="N60" s="32"/>
     </row>
     <row r="62" spans="1:14" s="37" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="79" t="s">
+      <c r="A62" s="76" t="s">
         <v>83</v>
       </c>
-      <c r="B62" s="79"/>
-      <c r="C62" s="79"/>
-      <c r="D62" s="79"/>
+      <c r="B62" s="76"/>
+      <c r="C62" s="76"/>
+      <c r="D62" s="76"/>
       <c r="E62" s="34"/>
       <c r="F62" s="35"/>
       <c r="G62" s="35"/>
@@ -5422,12 +5462,12 @@
       <c r="N62" s="36"/>
     </row>
     <row r="63" spans="1:14" s="37" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A63" s="79" t="s">
+      <c r="A63" s="76" t="s">
         <v>84</v>
       </c>
-      <c r="B63" s="80"/>
-      <c r="C63" s="80"/>
-      <c r="D63" s="80"/>
+      <c r="B63" s="77"/>
+      <c r="C63" s="77"/>
+      <c r="D63" s="77"/>
       <c r="E63" s="38"/>
       <c r="F63" s="35"/>
       <c r="G63" s="35"/>
@@ -5440,12 +5480,12 @@
       <c r="N63" s="36"/>
     </row>
     <row r="64" spans="1:14" s="37" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="79" t="s">
+      <c r="A64" s="76" t="s">
         <v>85</v>
       </c>
-      <c r="B64" s="80"/>
-      <c r="C64" s="80"/>
-      <c r="D64" s="80"/>
+      <c r="B64" s="77"/>
+      <c r="C64" s="77"/>
+      <c r="D64" s="77"/>
       <c r="E64" s="38"/>
       <c r="F64" s="35"/>
       <c r="G64" s="35"/>
@@ -5459,12 +5499,37 @@
     </row>
   </sheetData>
   <mergeCells count="53">
-    <mergeCell ref="A63:D63"/>
-    <mergeCell ref="A64:D64"/>
-    <mergeCell ref="A58:E58"/>
-    <mergeCell ref="A59:E59"/>
-    <mergeCell ref="A60:E60"/>
-    <mergeCell ref="A62:D62"/>
+    <mergeCell ref="A55:D55"/>
+    <mergeCell ref="N42:N44"/>
+    <mergeCell ref="C46:C48"/>
+    <mergeCell ref="D46:D48"/>
+    <mergeCell ref="E46:E48"/>
+    <mergeCell ref="N46:N48"/>
+    <mergeCell ref="E50:E52"/>
+    <mergeCell ref="C36:C38"/>
+    <mergeCell ref="D36:D38"/>
+    <mergeCell ref="E36:E38"/>
+    <mergeCell ref="A40:D40"/>
+    <mergeCell ref="C42:C44"/>
+    <mergeCell ref="D42:D44"/>
+    <mergeCell ref="E42:E44"/>
+    <mergeCell ref="N12:N14"/>
+    <mergeCell ref="C20:C22"/>
+    <mergeCell ref="D20:D22"/>
+    <mergeCell ref="E20:E22"/>
+    <mergeCell ref="N20:N22"/>
+    <mergeCell ref="C16:C18"/>
+    <mergeCell ref="D16:D18"/>
+    <mergeCell ref="E16:E18"/>
+    <mergeCell ref="N16:N18"/>
+    <mergeCell ref="C2:C4"/>
+    <mergeCell ref="D2:D4"/>
+    <mergeCell ref="E2:E4"/>
+    <mergeCell ref="N2:N4"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="D6:D8"/>
+    <mergeCell ref="E6:E8"/>
+    <mergeCell ref="N6:N8"/>
     <mergeCell ref="A56:D56"/>
     <mergeCell ref="A10:D10"/>
     <mergeCell ref="C12:C14"/>
@@ -5481,37 +5546,12 @@
     <mergeCell ref="E32:E34"/>
     <mergeCell ref="C50:C52"/>
     <mergeCell ref="D50:D52"/>
-    <mergeCell ref="C2:C4"/>
-    <mergeCell ref="D2:D4"/>
-    <mergeCell ref="E2:E4"/>
-    <mergeCell ref="N2:N4"/>
-    <mergeCell ref="C6:C8"/>
-    <mergeCell ref="D6:D8"/>
-    <mergeCell ref="E6:E8"/>
-    <mergeCell ref="N6:N8"/>
-    <mergeCell ref="N12:N14"/>
-    <mergeCell ref="C20:C22"/>
-    <mergeCell ref="D20:D22"/>
-    <mergeCell ref="E20:E22"/>
-    <mergeCell ref="N20:N22"/>
-    <mergeCell ref="C16:C18"/>
-    <mergeCell ref="D16:D18"/>
-    <mergeCell ref="E16:E18"/>
-    <mergeCell ref="N16:N18"/>
-    <mergeCell ref="C36:C38"/>
-    <mergeCell ref="D36:D38"/>
-    <mergeCell ref="E36:E38"/>
-    <mergeCell ref="A40:D40"/>
-    <mergeCell ref="C42:C44"/>
-    <mergeCell ref="D42:D44"/>
-    <mergeCell ref="E42:E44"/>
-    <mergeCell ref="A55:D55"/>
-    <mergeCell ref="N42:N44"/>
-    <mergeCell ref="C46:C48"/>
-    <mergeCell ref="D46:D48"/>
-    <mergeCell ref="E46:E48"/>
-    <mergeCell ref="N46:N48"/>
-    <mergeCell ref="E50:E52"/>
+    <mergeCell ref="A63:D63"/>
+    <mergeCell ref="A64:D64"/>
+    <mergeCell ref="A58:E58"/>
+    <mergeCell ref="A59:E59"/>
+    <mergeCell ref="A60:E60"/>
+    <mergeCell ref="A62:D62"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5592,17 +5632,17 @@
       <c r="N2" s="9"/>
     </row>
     <row r="3" spans="1:14" s="47" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="78" t="s">
+      <c r="A3" s="81" t="s">
         <v>71</v>
       </c>
-      <c r="B3" s="78"/>
-      <c r="C3" s="78"/>
-      <c r="D3" s="78"/>
-      <c r="E3" s="78"/>
-      <c r="F3" s="78"/>
-      <c r="G3" s="78"/>
-      <c r="H3" s="78"/>
-      <c r="I3" s="78"/>
+      <c r="B3" s="81"/>
+      <c r="C3" s="81"/>
+      <c r="D3" s="81"/>
+      <c r="E3" s="81"/>
+      <c r="F3" s="81"/>
+      <c r="G3" s="81"/>
+      <c r="H3" s="81"/>
+      <c r="I3" s="81"/>
       <c r="J3" s="49"/>
       <c r="K3" s="56"/>
       <c r="L3" s="56"/>
@@ -5628,10 +5668,10 @@
       <c r="B5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="75" t="s">
+      <c r="C5" s="70" t="s">
         <v>67</v>
       </c>
-      <c r="D5" s="75" t="s">
+      <c r="D5" s="70" t="s">
         <v>68</v>
       </c>
       <c r="E5" s="11">
@@ -5669,8 +5709,8 @@
       <c r="B6" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="75"/>
-      <c r="D6" s="75"/>
+      <c r="C6" s="70"/>
+      <c r="D6" s="70"/>
       <c r="E6" s="11">
         <v>6.9727237799999994E-2</v>
       </c>
@@ -5706,8 +5746,8 @@
       <c r="B7" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="75"/>
-      <c r="D7" s="75"/>
+      <c r="C7" s="70"/>
+      <c r="D7" s="70"/>
       <c r="E7" s="11">
         <v>2.8812910000000001E-4</v>
       </c>
@@ -5743,10 +5783,10 @@
       <c r="B9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="75" t="s">
+      <c r="C9" s="70" t="s">
         <v>69</v>
       </c>
-      <c r="D9" s="75" t="s">
+      <c r="D9" s="70" t="s">
         <v>70</v>
       </c>
       <c r="E9" s="11">
@@ -5784,8 +5824,8 @@
       <c r="B10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="75"/>
-      <c r="D10" s="75"/>
+      <c r="C10" s="70"/>
+      <c r="D10" s="70"/>
       <c r="E10" s="11">
         <v>2.4010757000000001E-3</v>
       </c>
@@ -5821,8 +5861,8 @@
       <c r="B11" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C11" s="75"/>
-      <c r="D11" s="75"/>
+      <c r="C11" s="70"/>
+      <c r="D11" s="70"/>
       <c r="E11" s="11">
         <v>0</v>
       </c>
@@ -5858,10 +5898,10 @@
       <c r="B13" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C13" s="75" t="s">
+      <c r="C13" s="70" t="s">
         <v>74</v>
       </c>
-      <c r="D13" s="75" t="s">
+      <c r="D13" s="70" t="s">
         <v>81</v>
       </c>
       <c r="E13" s="11">
@@ -5899,8 +5939,8 @@
       <c r="B14" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C14" s="75"/>
-      <c r="D14" s="75"/>
+      <c r="C14" s="70"/>
+      <c r="D14" s="70"/>
       <c r="E14" s="11">
         <v>3.5474592999999999E-3</v>
       </c>
@@ -5936,8 +5976,8 @@
       <c r="B15" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C15" s="75"/>
-      <c r="D15" s="75"/>
+      <c r="C15" s="70"/>
+      <c r="D15" s="70"/>
       <c r="E15" s="11">
         <v>3.8350910000000001E-4</v>
       </c>
@@ -5973,10 +6013,10 @@
       <c r="B17" s="63" t="s">
         <v>5</v>
       </c>
-      <c r="C17" s="75" t="s">
+      <c r="C17" s="70" t="s">
         <v>80</v>
       </c>
-      <c r="D17" s="75" t="s">
+      <c r="D17" s="70" t="s">
         <v>79</v>
       </c>
       <c r="E17" s="64">
@@ -6014,8 +6054,8 @@
       <c r="B18" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C18" s="75"/>
-      <c r="D18" s="75"/>
+      <c r="C18" s="70"/>
+      <c r="D18" s="70"/>
       <c r="E18" s="11">
         <v>3.0680729000000001E-3</v>
       </c>
@@ -6051,8 +6091,8 @@
       <c r="B19" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C19" s="75"/>
-      <c r="D19" s="75"/>
+      <c r="C19" s="70"/>
+      <c r="D19" s="70"/>
       <c r="E19" s="11">
         <v>2.876318E-4</v>
       </c>
@@ -6091,10 +6131,10 @@
       <c r="B21" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C21" s="75" t="s">
+      <c r="C21" s="70" t="s">
         <v>72</v>
       </c>
-      <c r="D21" s="75" t="s">
+      <c r="D21" s="70" t="s">
         <v>73</v>
       </c>
       <c r="E21" s="11">
@@ -6132,8 +6172,8 @@
       <c r="B22" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C22" s="75"/>
-      <c r="D22" s="75"/>
+      <c r="C22" s="70"/>
+      <c r="D22" s="70"/>
       <c r="E22" s="11">
         <v>3.1639501E-3</v>
       </c>
@@ -6169,8 +6209,8 @@
       <c r="B23" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C23" s="75"/>
-      <c r="D23" s="75"/>
+      <c r="C23" s="70"/>
+      <c r="D23" s="70"/>
       <c r="E23" s="11">
         <v>1.917546E-4</v>
       </c>
@@ -6206,10 +6246,10 @@
       <c r="B25" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C25" s="75" t="s">
+      <c r="C25" s="70" t="s">
         <v>77</v>
       </c>
-      <c r="D25" s="75" t="s">
+      <c r="D25" s="70" t="s">
         <v>75</v>
       </c>
       <c r="E25" s="11">
@@ -6247,8 +6287,8 @@
       <c r="B26" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C26" s="75"/>
-      <c r="D26" s="75"/>
+      <c r="C26" s="70"/>
+      <c r="D26" s="70"/>
       <c r="E26" s="11">
         <v>1.70661553E-2</v>
       </c>
@@ -6284,8 +6324,8 @@
       <c r="B27" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C27" s="75"/>
-      <c r="D27" s="75"/>
+      <c r="C27" s="70"/>
+      <c r="D27" s="70"/>
       <c r="E27" s="11">
         <v>6.7114089999999996E-4</v>
       </c>
@@ -6321,10 +6361,10 @@
       <c r="B29" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C29" s="75" t="s">
+      <c r="C29" s="70" t="s">
         <v>78</v>
       </c>
-      <c r="D29" s="75" t="s">
+      <c r="D29" s="70" t="s">
         <v>76</v>
       </c>
       <c r="E29" s="11">
@@ -6362,8 +6402,8 @@
       <c r="B30" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C30" s="75"/>
-      <c r="D30" s="75"/>
+      <c r="C30" s="70"/>
+      <c r="D30" s="70"/>
       <c r="E30" s="11">
         <v>7.2866731000000001E-3</v>
       </c>
@@ -6399,8 +6439,8 @@
       <c r="B31" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C31" s="75"/>
-      <c r="D31" s="75"/>
+      <c r="C31" s="70"/>
+      <c r="D31" s="70"/>
       <c r="E31" s="11">
         <v>0</v>
       </c>
@@ -6430,12 +6470,12 @@
       </c>
     </row>
     <row r="34" spans="1:14" s="14" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="76" t="s">
+      <c r="A34" s="83" t="s">
         <v>59</v>
       </c>
-      <c r="B34" s="76"/>
-      <c r="C34" s="76"/>
-      <c r="D34" s="76"/>
+      <c r="B34" s="83"/>
+      <c r="C34" s="83"/>
+      <c r="D34" s="83"/>
       <c r="E34" s="16">
         <f t="shared" ref="E34:L34" si="0">MAX(E4:E32)</f>
         <v>8.2742090099999999E-2</v>
@@ -6472,12 +6512,12 @@
       <c r="N34" s="17"/>
     </row>
     <row r="35" spans="1:14" s="52" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="81" t="s">
+      <c r="A35" s="78" t="s">
         <v>60</v>
       </c>
-      <c r="B35" s="81"/>
-      <c r="C35" s="81"/>
-      <c r="D35" s="81"/>
+      <c r="B35" s="78"/>
+      <c r="C35" s="78"/>
+      <c r="D35" s="78"/>
       <c r="E35" s="29">
         <f t="shared" ref="E35:L35" si="1">AVERAGE(E5:E32)</f>
         <v>2.0975477057142849E-2</v>
@@ -6514,17 +6554,17 @@
       <c r="N35" s="58"/>
     </row>
     <row r="37" spans="1:14" s="47" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="78" t="s">
+      <c r="A37" s="81" t="s">
         <v>86</v>
       </c>
-      <c r="B37" s="78"/>
-      <c r="C37" s="78"/>
-      <c r="D37" s="78"/>
-      <c r="E37" s="78"/>
-      <c r="F37" s="78"/>
-      <c r="G37" s="78"/>
-      <c r="H37" s="78"/>
-      <c r="I37" s="78"/>
+      <c r="B37" s="81"/>
+      <c r="C37" s="81"/>
+      <c r="D37" s="81"/>
+      <c r="E37" s="81"/>
+      <c r="F37" s="81"/>
+      <c r="G37" s="81"/>
+      <c r="H37" s="81"/>
+      <c r="I37" s="81"/>
       <c r="J37" s="49"/>
       <c r="K37" s="56"/>
       <c r="L37" s="56"/>
@@ -6550,10 +6590,10 @@
       <c r="B39" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C39" s="75" t="s">
+      <c r="C39" s="70" t="s">
         <v>87</v>
       </c>
-      <c r="D39" s="75" t="s">
+      <c r="D39" s="70" t="s">
         <v>68</v>
       </c>
       <c r="E39" s="11">
@@ -6591,8 +6631,8 @@
       <c r="B40" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C40" s="75"/>
-      <c r="D40" s="75"/>
+      <c r="C40" s="70"/>
+      <c r="D40" s="70"/>
       <c r="E40" s="11">
         <v>1.42857143E-2</v>
       </c>
@@ -6628,8 +6668,8 @@
       <c r="B41" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C41" s="75"/>
-      <c r="D41" s="75"/>
+      <c r="C41" s="70"/>
+      <c r="D41" s="70"/>
       <c r="E41" s="11">
         <v>3.8350910000000001E-4</v>
       </c>
@@ -6665,10 +6705,10 @@
       <c r="B43" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C43" s="75" t="s">
+      <c r="C43" s="70" t="s">
         <v>88</v>
       </c>
-      <c r="D43" s="75" t="s">
+      <c r="D43" s="70" t="s">
         <v>70</v>
       </c>
       <c r="E43" s="11">
@@ -6706,8 +6746,8 @@
       <c r="B44" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C44" s="75"/>
-      <c r="D44" s="75"/>
+      <c r="C44" s="70"/>
+      <c r="D44" s="70"/>
       <c r="E44" s="11">
         <v>2.8475551299999999E-2</v>
       </c>
@@ -6743,8 +6783,8 @@
       <c r="B45" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C45" s="75"/>
-      <c r="D45" s="75"/>
+      <c r="C45" s="70"/>
+      <c r="D45" s="70"/>
       <c r="E45" s="11">
         <v>1.917546E-4</v>
       </c>
@@ -6780,10 +6820,10 @@
       <c r="B47" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C47" s="75" t="s">
+      <c r="C47" s="70" t="s">
         <v>89</v>
       </c>
-      <c r="D47" s="75" t="s">
+      <c r="D47" s="70" t="s">
         <v>81</v>
       </c>
       <c r="E47" s="11">
@@ -6821,8 +6861,8 @@
       <c r="B48" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C48" s="75"/>
-      <c r="D48" s="75"/>
+      <c r="C48" s="70"/>
+      <c r="D48" s="70"/>
       <c r="E48" s="11">
         <v>6.3279002999999997E-3</v>
       </c>
@@ -6858,8 +6898,8 @@
       <c r="B49" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C49" s="75"/>
-      <c r="D49" s="75"/>
+      <c r="C49" s="70"/>
+      <c r="D49" s="70"/>
       <c r="E49" s="11">
         <v>2.876318E-4</v>
       </c>
@@ -6895,10 +6935,10 @@
       <c r="B51" s="63" t="s">
         <v>5</v>
       </c>
-      <c r="C51" s="75" t="s">
+      <c r="C51" s="70" t="s">
         <v>90</v>
       </c>
-      <c r="D51" s="75" t="s">
+      <c r="D51" s="70" t="s">
         <v>79</v>
       </c>
       <c r="E51" s="64">
@@ -6936,8 +6976,8 @@
       <c r="B52" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C52" s="75"/>
-      <c r="D52" s="75"/>
+      <c r="C52" s="70"/>
+      <c r="D52" s="70"/>
       <c r="E52" s="11">
         <v>2.0134227999999998E-3</v>
       </c>
@@ -6973,8 +7013,8 @@
       <c r="B53" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C53" s="75"/>
-      <c r="D53" s="75"/>
+      <c r="C53" s="70"/>
+      <c r="D53" s="70"/>
       <c r="E53" s="11">
         <v>1.917546E-4</v>
       </c>
@@ -7013,10 +7053,10 @@
       <c r="B55" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C55" s="75" t="s">
+      <c r="C55" s="70" t="s">
         <v>91</v>
       </c>
-      <c r="D55" s="75" t="s">
+      <c r="D55" s="70" t="s">
         <v>73</v>
       </c>
       <c r="E55" s="11">
@@ -7054,8 +7094,8 @@
       <c r="B56" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C56" s="75"/>
-      <c r="D56" s="75"/>
+      <c r="C56" s="70"/>
+      <c r="D56" s="70"/>
       <c r="E56" s="11">
         <v>1.9558964500000001E-2</v>
       </c>
@@ -7091,8 +7131,8 @@
       <c r="B57" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C57" s="75"/>
-      <c r="D57" s="75"/>
+      <c r="C57" s="70"/>
+      <c r="D57" s="70"/>
       <c r="E57" s="11">
         <v>0</v>
       </c>
@@ -7128,10 +7168,10 @@
       <c r="B59" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C59" s="75" t="s">
+      <c r="C59" s="70" t="s">
         <v>92</v>
       </c>
-      <c r="D59" s="75" t="s">
+      <c r="D59" s="70" t="s">
         <v>75</v>
       </c>
       <c r="E59" s="11">
@@ -7169,8 +7209,8 @@
       <c r="B60" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C60" s="75"/>
-      <c r="D60" s="75"/>
+      <c r="C60" s="70"/>
+      <c r="D60" s="70"/>
       <c r="E60" s="11">
         <v>4.4103546999999998E-3</v>
       </c>
@@ -7206,8 +7246,8 @@
       <c r="B61" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C61" s="75"/>
-      <c r="D61" s="75"/>
+      <c r="C61" s="70"/>
+      <c r="D61" s="70"/>
       <c r="E61" s="11">
         <v>2.8763183000000002E-3</v>
       </c>
@@ -7243,10 +7283,10 @@
       <c r="B63" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C63" s="75" t="s">
+      <c r="C63" s="70" t="s">
         <v>93</v>
       </c>
-      <c r="D63" s="75" t="s">
+      <c r="D63" s="70" t="s">
         <v>76</v>
       </c>
       <c r="E63" s="11">
@@ -7284,8 +7324,8 @@
       <c r="B64" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C64" s="75"/>
-      <c r="D64" s="75"/>
+      <c r="C64" s="70"/>
+      <c r="D64" s="70"/>
       <c r="E64" s="11">
         <v>8.6289548999999993E-3</v>
       </c>
@@ -7321,8 +7361,8 @@
       <c r="B65" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C65" s="75"/>
-      <c r="D65" s="75"/>
+      <c r="C65" s="70"/>
+      <c r="D65" s="70"/>
       <c r="E65" s="11">
         <v>1.9175455000000001E-3</v>
       </c>
@@ -7352,12 +7392,12 @@
       </c>
     </row>
     <row r="68" spans="1:14" s="14" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="76" t="s">
+      <c r="A68" s="83" t="s">
         <v>59</v>
       </c>
-      <c r="B68" s="76"/>
-      <c r="C68" s="76"/>
-      <c r="D68" s="76"/>
+      <c r="B68" s="83"/>
+      <c r="C68" s="83"/>
+      <c r="D68" s="83"/>
       <c r="E68" s="16">
         <f t="shared" ref="E68:L68" si="2">MAX(E38:E66)</f>
         <v>9.0220517700000002E-2</v>
@@ -7394,12 +7434,12 @@
       <c r="N68" s="17"/>
     </row>
     <row r="69" spans="1:14" s="52" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="81" t="s">
+      <c r="A69" s="78" t="s">
         <v>60</v>
       </c>
-      <c r="B69" s="81"/>
-      <c r="C69" s="81"/>
-      <c r="D69" s="81"/>
+      <c r="B69" s="78"/>
+      <c r="C69" s="78"/>
+      <c r="D69" s="78"/>
       <c r="E69" s="29">
         <f t="shared" ref="E69:L69" si="3">AVERAGE(E39:E66)</f>
         <v>1.7271606619047621E-2</v>
@@ -7436,17 +7476,17 @@
       <c r="N69" s="58"/>
     </row>
     <row r="71" spans="1:14" s="47" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A71" s="78" t="s">
+      <c r="A71" s="81" t="s">
         <v>94</v>
       </c>
-      <c r="B71" s="78"/>
-      <c r="C71" s="78"/>
-      <c r="D71" s="78"/>
-      <c r="E71" s="78"/>
-      <c r="F71" s="78"/>
-      <c r="G71" s="78"/>
-      <c r="H71" s="78"/>
-      <c r="I71" s="78"/>
+      <c r="B71" s="81"/>
+      <c r="C71" s="81"/>
+      <c r="D71" s="81"/>
+      <c r="E71" s="81"/>
+      <c r="F71" s="81"/>
+      <c r="G71" s="81"/>
+      <c r="H71" s="81"/>
+      <c r="I71" s="81"/>
       <c r="J71" s="49"/>
       <c r="K71" s="56"/>
       <c r="L71" s="56"/>
@@ -7472,10 +7512,10 @@
       <c r="B73" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C73" s="75" t="s">
+      <c r="C73" s="70" t="s">
         <v>95</v>
       </c>
-      <c r="D73" s="75" t="s">
+      <c r="D73" s="70" t="s">
         <v>68</v>
       </c>
       <c r="E73" s="11">
@@ -7513,8 +7553,8 @@
       <c r="B74" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C74" s="75"/>
-      <c r="D74" s="75"/>
+      <c r="C74" s="70"/>
+      <c r="D74" s="70"/>
       <c r="E74" s="11">
         <v>8.8139489999999997E-3</v>
       </c>
@@ -7550,8 +7590,8 @@
       <c r="B75" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C75" s="75"/>
-      <c r="D75" s="75"/>
+      <c r="C75" s="70"/>
+      <c r="D75" s="70"/>
       <c r="E75" s="11">
         <v>1.9160760000000001E-4</v>
       </c>
@@ -7587,10 +7627,10 @@
       <c r="B77" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C77" s="75" t="s">
+      <c r="C77" s="70" t="s">
         <v>96</v>
       </c>
-      <c r="D77" s="75" t="s">
+      <c r="D77" s="70" t="s">
         <v>70</v>
       </c>
       <c r="E77" s="11">
@@ -7628,8 +7668,8 @@
       <c r="B78" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C78" s="75"/>
-      <c r="D78" s="75"/>
+      <c r="C78" s="70"/>
+      <c r="D78" s="70"/>
       <c r="E78" s="11">
         <v>3.4489365999999999E-3</v>
       </c>
@@ -7665,8 +7705,8 @@
       <c r="B79" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C79" s="75"/>
-      <c r="D79" s="75"/>
+      <c r="C79" s="70"/>
+      <c r="D79" s="70"/>
       <c r="E79" s="62">
         <v>4.7901900000000002E-4</v>
       </c>
@@ -7702,10 +7742,10 @@
       <c r="B81" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C81" s="75" t="s">
+      <c r="C81" s="70" t="s">
         <v>97</v>
       </c>
-      <c r="D81" s="75" t="s">
+      <c r="D81" s="70" t="s">
         <v>81</v>
       </c>
       <c r="E81" s="11">
@@ -7743,8 +7783,8 @@
       <c r="B82" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C82" s="75"/>
-      <c r="D82" s="75"/>
+      <c r="C82" s="70"/>
+      <c r="D82" s="70"/>
       <c r="E82" s="11">
         <v>4.3111707000000003E-3</v>
       </c>
@@ -7780,8 +7820,8 @@
       <c r="B83" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C83" s="75"/>
-      <c r="D83" s="75"/>
+      <c r="C83" s="70"/>
+      <c r="D83" s="70"/>
       <c r="E83" s="11">
         <v>2.1076835000000001E-3</v>
       </c>
@@ -7817,38 +7857,23 @@
       <c r="B85" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C85" s="75" t="s">
+      <c r="C85" s="70" t="s">
         <v>98</v>
       </c>
-      <c r="D85" s="75" t="s">
+      <c r="D85" s="70" t="s">
         <v>79</v>
-      </c>
-      <c r="E85" s="11">
-        <v>4.7901900000000002E-4</v>
-      </c>
-      <c r="F85" s="11">
-        <v>3.6405442E-3</v>
-      </c>
-      <c r="G85" s="11">
-        <v>0.74458708559999998</v>
-      </c>
-      <c r="H85" s="11">
-        <v>0.70530976980000004</v>
-      </c>
-      <c r="I85" s="11">
-        <v>0.82515196759999998</v>
       </c>
       <c r="J85" s="11">
         <f>SUM(E85*1/3,F85*1/3,H85*1/3)</f>
-        <v>0.23647644433333334</v>
+        <v>0</v>
       </c>
       <c r="K85" s="54">
         <f>SUM(G85*1/2,I85*1/2)</f>
-        <v>0.78486952659999998</v>
+        <v>0</v>
       </c>
       <c r="L85" s="11">
         <f>SUM(E85*1/5,F85*1/5,G85*1/5,H85*1/5,I85*1/5)</f>
-        <v>0.45583367724000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86" spans="1:12" s="42" customFormat="1" x14ac:dyDescent="0.2">
@@ -7858,34 +7883,24 @@
       <c r="B86" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="C86" s="75"/>
-      <c r="D86" s="75"/>
-      <c r="E86" s="66">
-        <v>2.24180878E-2</v>
-      </c>
-      <c r="F86" s="66">
-        <v>3.2573290000000002E-3</v>
-      </c>
-      <c r="G86" s="66">
-        <v>0.76911285689999997</v>
-      </c>
-      <c r="H86" s="66">
-        <v>0.87399711270000002</v>
-      </c>
-      <c r="I86" s="66">
-        <v>0.78457966379999999</v>
-      </c>
+      <c r="C86" s="70"/>
+      <c r="D86" s="70"/>
+      <c r="E86" s="66"/>
+      <c r="F86" s="66"/>
+      <c r="G86" s="66"/>
+      <c r="H86" s="66"/>
+      <c r="I86" s="66"/>
       <c r="J86" s="66">
         <f>SUM(E86*1/3,F86*1/3,H86*1/3)</f>
-        <v>0.2998908431666667</v>
+        <v>0</v>
       </c>
       <c r="K86" s="66">
         <f>SUM(G86*1/2,I86*1/2)</f>
-        <v>0.77684626034999993</v>
+        <v>0</v>
       </c>
       <c r="L86" s="40">
         <f>SUM(E86*1/5,F86*1/5,G86*1/5,H86*1/5,I86*1/5)</f>
-        <v>0.49067301003999997</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87" spans="1:12" x14ac:dyDescent="0.2">
@@ -7895,34 +7910,19 @@
       <c r="B87" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C87" s="75"/>
-      <c r="D87" s="75"/>
-      <c r="E87" s="11">
-        <v>0</v>
-      </c>
-      <c r="F87" s="11">
-        <v>9.5803800000000003E-4</v>
-      </c>
-      <c r="G87" s="11">
-        <v>5.8440314200000003E-2</v>
-      </c>
-      <c r="H87" s="11">
-        <v>0.49011553810000003</v>
-      </c>
-      <c r="I87" s="11">
-        <v>0.46326403129999999</v>
-      </c>
+      <c r="C87" s="70"/>
+      <c r="D87" s="70"/>
       <c r="J87" s="11">
         <f>SUM(E87*1/3,F87*1/3,H87*1/3)</f>
-        <v>0.16369119203333335</v>
+        <v>0</v>
       </c>
       <c r="K87" s="11">
         <f>SUM(G87*1/2,I87*1/2)</f>
-        <v>0.26085217275</v>
+        <v>0</v>
       </c>
       <c r="L87" s="11">
         <f>SUM(E87*1/5,F87*1/5,G87*1/5,H87*1/5,I87*1/5)</f>
-        <v>0.20255558432000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88" spans="1:12" x14ac:dyDescent="0.2">
@@ -7935,10 +7935,10 @@
       <c r="B89" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C89" s="75" t="s">
+      <c r="C89" s="70" t="s">
         <v>99</v>
       </c>
-      <c r="D89" s="75" t="s">
+      <c r="D89" s="70" t="s">
         <v>73</v>
       </c>
       <c r="E89" s="11">
@@ -7976,8 +7976,8 @@
       <c r="B90" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C90" s="75"/>
-      <c r="D90" s="75"/>
+      <c r="C90" s="70"/>
+      <c r="D90" s="70"/>
       <c r="E90" s="11">
         <v>1.59034298E-2</v>
       </c>
@@ -8013,8 +8013,8 @@
       <c r="B91" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C91" s="75"/>
-      <c r="D91" s="75"/>
+      <c r="C91" s="70"/>
+      <c r="D91" s="70"/>
       <c r="E91" s="11">
         <v>0</v>
       </c>
@@ -8050,10 +8050,10 @@
       <c r="B93" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C93" s="75" t="s">
+      <c r="C93" s="70" t="s">
         <v>100</v>
       </c>
-      <c r="D93" s="75" t="s">
+      <c r="D93" s="70" t="s">
         <v>75</v>
       </c>
       <c r="E93" s="11">
@@ -8091,8 +8091,8 @@
       <c r="B94" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C94" s="75"/>
-      <c r="D94" s="75"/>
+      <c r="C94" s="70"/>
+      <c r="D94" s="70"/>
       <c r="E94" s="11">
         <v>9.4845755999999996E-3</v>
       </c>
@@ -8128,8 +8128,8 @@
       <c r="B95" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C95" s="75"/>
-      <c r="D95" s="75"/>
+      <c r="C95" s="70"/>
+      <c r="D95" s="70"/>
       <c r="E95" s="11">
         <v>1.9160760000000001E-4</v>
       </c>
@@ -8165,10 +8165,10 @@
       <c r="B97" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C97" s="75" t="s">
+      <c r="C97" s="70" t="s">
         <v>101</v>
       </c>
-      <c r="D97" s="75" t="s">
+      <c r="D97" s="70" t="s">
         <v>76</v>
       </c>
       <c r="E97" s="11">
@@ -8206,8 +8206,8 @@
       <c r="B98" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C98" s="75"/>
-      <c r="D98" s="75"/>
+      <c r="C98" s="70"/>
+      <c r="D98" s="70"/>
       <c r="E98" s="11">
         <v>8.9097528000000002E-3</v>
       </c>
@@ -8243,8 +8243,8 @@
       <c r="B99" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C99" s="75"/>
-      <c r="D99" s="75"/>
+      <c r="C99" s="70"/>
+      <c r="D99" s="70"/>
       <c r="E99" s="11">
         <v>1.6286645000000001E-3</v>
       </c>
@@ -8274,12 +8274,12 @@
       </c>
     </row>
     <row r="102" spans="1:14" s="14" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A102" s="76" t="s">
+      <c r="A102" s="83" t="s">
         <v>59</v>
       </c>
-      <c r="B102" s="76"/>
-      <c r="C102" s="76"/>
-      <c r="D102" s="76"/>
+      <c r="B102" s="83"/>
+      <c r="C102" s="83"/>
+      <c r="D102" s="83"/>
       <c r="E102" s="16">
         <f t="shared" ref="E102:L102" si="4">MAX(E72:E100)</f>
         <v>4.4165548999999998E-2</v>
@@ -8290,7 +8290,7 @@
       </c>
       <c r="G102" s="16">
         <f t="shared" si="4"/>
-        <v>0.76911285689999997</v>
+        <v>0.70549913779999995</v>
       </c>
       <c r="H102" s="16">
         <f t="shared" si="4"/>
@@ -8298,7 +8298,7 @@
       </c>
       <c r="I102" s="16">
         <f t="shared" si="4"/>
-        <v>0.82515196759999998</v>
+        <v>0.51348317779999997</v>
       </c>
       <c r="J102" s="16">
         <f t="shared" si="4"/>
@@ -8306,99 +8306,59 @@
       </c>
       <c r="K102" s="16">
         <f t="shared" si="4"/>
-        <v>0.78486952659999998</v>
+        <v>0.60320936849999995</v>
       </c>
       <c r="L102" s="16">
         <f t="shared" si="4"/>
-        <v>0.49067301003999997</v>
+        <v>0.39645458486000001</v>
       </c>
       <c r="M102" s="16"/>
       <c r="N102" s="17"/>
     </row>
     <row r="103" spans="1:14" s="52" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A103" s="81" t="s">
+      <c r="A103" s="78" t="s">
         <v>60</v>
       </c>
-      <c r="B103" s="81"/>
-      <c r="C103" s="81"/>
-      <c r="D103" s="81"/>
+      <c r="B103" s="78"/>
+      <c r="C103" s="78"/>
+      <c r="D103" s="78"/>
       <c r="E103" s="29">
         <f t="shared" ref="E103:L103" si="5">AVERAGE(E73:E100)</f>
-        <v>1.0889697909523807E-2</v>
+        <v>1.1432586072222223E-2</v>
       </c>
       <c r="F103" s="29">
         <f t="shared" si="5"/>
-        <v>5.780162238095239E-3</v>
+        <v>6.3070831000000003E-3</v>
       </c>
       <c r="G103" s="29">
         <f t="shared" si="5"/>
-        <v>0.36983001670000004</v>
+        <v>0.34412722744444452</v>
       </c>
       <c r="H103" s="29">
         <f t="shared" si="5"/>
-        <v>0.59864495079047608</v>
+        <v>0.58345119700000003</v>
       </c>
       <c r="I103" s="29">
         <f t="shared" si="5"/>
-        <v>0.49329789959523812</v>
+        <v>0.46034779048888896</v>
       </c>
       <c r="J103" s="29">
         <f t="shared" si="5"/>
-        <v>0.20510493697936505</v>
+        <v>0.17176881890634921</v>
       </c>
       <c r="K103" s="29">
         <f t="shared" si="5"/>
-        <v>0.43156395814761905</v>
+        <v>0.34477500768571429</v>
       </c>
       <c r="L103" s="29">
         <f t="shared" si="5"/>
-        <v>0.29568854544666673</v>
+        <v>0.24097129441809528</v>
       </c>
       <c r="M103" s="29"/>
       <c r="N103" s="58"/>
     </row>
   </sheetData>
   <mergeCells count="51">
-    <mergeCell ref="A103:D103"/>
-    <mergeCell ref="C93:C95"/>
-    <mergeCell ref="D93:D95"/>
-    <mergeCell ref="C97:C99"/>
-    <mergeCell ref="D97:D99"/>
-    <mergeCell ref="A102:D102"/>
-    <mergeCell ref="C81:C83"/>
-    <mergeCell ref="D81:D83"/>
-    <mergeCell ref="C85:C87"/>
-    <mergeCell ref="D85:D87"/>
-    <mergeCell ref="C89:C91"/>
-    <mergeCell ref="D89:D91"/>
-    <mergeCell ref="A69:D69"/>
-    <mergeCell ref="A71:I71"/>
-    <mergeCell ref="C73:C75"/>
-    <mergeCell ref="D73:D75"/>
-    <mergeCell ref="C77:C79"/>
-    <mergeCell ref="D77:D79"/>
-    <mergeCell ref="C59:C61"/>
-    <mergeCell ref="D59:D61"/>
-    <mergeCell ref="C63:C65"/>
-    <mergeCell ref="D63:D65"/>
-    <mergeCell ref="A68:D68"/>
-    <mergeCell ref="C47:C49"/>
-    <mergeCell ref="D47:D49"/>
-    <mergeCell ref="C51:C53"/>
-    <mergeCell ref="D51:D53"/>
-    <mergeCell ref="C55:C57"/>
-    <mergeCell ref="D55:D57"/>
-    <mergeCell ref="A37:I37"/>
-    <mergeCell ref="C39:C41"/>
-    <mergeCell ref="D39:D41"/>
-    <mergeCell ref="C43:C45"/>
-    <mergeCell ref="D43:D45"/>
-    <mergeCell ref="A34:D34"/>
-    <mergeCell ref="A35:D35"/>
-    <mergeCell ref="C13:C15"/>
-    <mergeCell ref="D13:D15"/>
-    <mergeCell ref="C29:C31"/>
-    <mergeCell ref="D29:D31"/>
     <mergeCell ref="A3:I3"/>
     <mergeCell ref="C21:C23"/>
     <mergeCell ref="D21:D23"/>
@@ -8410,6 +8370,293 @@
     <mergeCell ref="C9:C11"/>
     <mergeCell ref="D17:D19"/>
     <mergeCell ref="C17:C19"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="C13:C15"/>
+    <mergeCell ref="D13:D15"/>
+    <mergeCell ref="C29:C31"/>
+    <mergeCell ref="D29:D31"/>
+    <mergeCell ref="A37:I37"/>
+    <mergeCell ref="C39:C41"/>
+    <mergeCell ref="D39:D41"/>
+    <mergeCell ref="C43:C45"/>
+    <mergeCell ref="D43:D45"/>
+    <mergeCell ref="C47:C49"/>
+    <mergeCell ref="D47:D49"/>
+    <mergeCell ref="C51:C53"/>
+    <mergeCell ref="D51:D53"/>
+    <mergeCell ref="C55:C57"/>
+    <mergeCell ref="D55:D57"/>
+    <mergeCell ref="C59:C61"/>
+    <mergeCell ref="D59:D61"/>
+    <mergeCell ref="C63:C65"/>
+    <mergeCell ref="D63:D65"/>
+    <mergeCell ref="A68:D68"/>
+    <mergeCell ref="A69:D69"/>
+    <mergeCell ref="A71:I71"/>
+    <mergeCell ref="C73:C75"/>
+    <mergeCell ref="D73:D75"/>
+    <mergeCell ref="C77:C79"/>
+    <mergeCell ref="D77:D79"/>
+    <mergeCell ref="C81:C83"/>
+    <mergeCell ref="D81:D83"/>
+    <mergeCell ref="C85:C87"/>
+    <mergeCell ref="D85:D87"/>
+    <mergeCell ref="C89:C91"/>
+    <mergeCell ref="D89:D91"/>
+    <mergeCell ref="A103:D103"/>
+    <mergeCell ref="C93:C95"/>
+    <mergeCell ref="D93:D95"/>
+    <mergeCell ref="C97:C99"/>
+    <mergeCell ref="D97:D99"/>
+    <mergeCell ref="A102:D102"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B868A83-228E-4B46-AAFD-22D8E7035CA7}">
+  <dimension ref="A1:I13"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="22.6640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="34.5" style="84" customWidth="1"/>
+    <col min="2" max="2" width="22.6640625" style="84"/>
+    <col min="3" max="3" width="42" style="84" customWidth="1"/>
+    <col min="4" max="4" width="38.6640625" style="84" customWidth="1"/>
+    <col min="5" max="6" width="26.1640625" style="84" customWidth="1"/>
+    <col min="7" max="16384" width="22.6640625" style="84"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" s="6" customFormat="1" ht="66" x14ac:dyDescent="0.2">
+      <c r="A1" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="G1" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="H1" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="I1" s="12" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="70" t="s">
+        <v>107</v>
+      </c>
+      <c r="D3" s="70" t="s">
+        <v>109</v>
+      </c>
+      <c r="E3" s="1">
+        <v>0.68648130389999995</v>
+      </c>
+      <c r="F3" s="1">
+        <v>0.93000958769999997</v>
+      </c>
+      <c r="G3" s="11">
+        <v>0.76609541449999996</v>
+      </c>
+      <c r="H3" s="11">
+        <v>0.3481675393</v>
+      </c>
+      <c r="I3" s="11">
+        <v>4.5112781999999997E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.2">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="70"/>
+      <c r="D4" s="70"/>
+      <c r="E4" s="1">
+        <v>0.51505273250000005</v>
+      </c>
+      <c r="F4" s="1">
+        <v>0.71179290510000004</v>
+      </c>
+      <c r="G4" s="11">
+        <v>0.5907827698</v>
+      </c>
+      <c r="H4" s="11">
+        <v>0.1230366492</v>
+      </c>
+      <c r="I4" s="11">
+        <v>0.30827067670000002</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.2">
+      <c r="A5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="70"/>
+      <c r="D5" s="70"/>
+      <c r="E5" s="1">
+        <v>3.79674017E-2</v>
+      </c>
+      <c r="F5" s="1">
+        <v>0.24506232019999999</v>
+      </c>
+      <c r="G5" s="11">
+        <v>9.7267253000000008E-3</v>
+      </c>
+      <c r="H5" s="11">
+        <v>3.6649214700000002E-2</v>
+      </c>
+      <c r="I5" s="11">
+        <v>0.962406015</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.2">
+      <c r="A7" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="70" t="s">
+        <v>110</v>
+      </c>
+      <c r="D7" s="70" t="s">
+        <v>111</v>
+      </c>
+      <c r="E7" s="1">
+        <v>0.70795781400000002</v>
+      </c>
+      <c r="F7" s="1">
+        <v>0.89434324070000004</v>
+      </c>
+      <c r="G7" s="11">
+        <v>0.79573876789999998</v>
+      </c>
+      <c r="H7" s="11">
+        <v>0.31020942410000002</v>
+      </c>
+      <c r="I7" s="11">
+        <v>0.14285714290000001</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.2">
+      <c r="A8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" s="70"/>
+      <c r="D8" s="70"/>
+      <c r="E8" s="1">
+        <v>0.27823585810000001</v>
+      </c>
+      <c r="F8" s="1">
+        <v>0.69242569509999996</v>
+      </c>
+      <c r="G8" s="11">
+        <v>0.26146364059999999</v>
+      </c>
+      <c r="H8" s="11">
+        <v>0.33900523560000001</v>
+      </c>
+      <c r="I8" s="11">
+        <v>0.47368421049999998</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.2">
+      <c r="A9" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="70"/>
+      <c r="D9" s="70"/>
+      <c r="E9" s="1">
+        <v>2.9146692200000001E-2</v>
+      </c>
+      <c r="F9" s="1">
+        <v>0.1883029722</v>
+      </c>
+      <c r="G9" s="11">
+        <v>6.9476610000000002E-4</v>
+      </c>
+      <c r="H9" s="11">
+        <v>2.4869109899999998E-2</v>
+      </c>
+      <c r="I9" s="11">
+        <v>0.97744360900000005</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="21" x14ac:dyDescent="0.2">
+      <c r="A11" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C11" s="70" t="s">
+        <v>112</v>
+      </c>
+      <c r="D11" s="70" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="21" x14ac:dyDescent="0.2">
+      <c r="A12" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12" s="70"/>
+      <c r="D12" s="70"/>
+    </row>
+    <row r="13" spans="1:9" ht="21" x14ac:dyDescent="0.2">
+      <c r="A13" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="70"/>
+      <c r="D13" s="70"/>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="C11:C13"/>
+    <mergeCell ref="D11:D13"/>
+    <mergeCell ref="C3:C5"/>
+    <mergeCell ref="D3:D5"/>
+    <mergeCell ref="C7:C9"/>
+    <mergeCell ref="D7:D9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/benchmarking/results/results.xlsx
+++ b/benchmarking/results/results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/deborahdore/Documents/political-debates-graph-analysis/benchmarking/results/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D70A337-E4EE-A245-BA87-630F406C6AB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6A08E89-7ED9-F041-84F2-E7459DCB3B6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="51200" windowHeight="26600" activeTab="4" xr2:uid="{E2EDC037-19C4-FE46-A599-BB595128A04F}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="51200" windowHeight="28800" activeTab="4" xr2:uid="{E2EDC037-19C4-FE46-A599-BB595128A04F}"/>
   </bookViews>
   <sheets>
     <sheet name="Results BASIC" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="621" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="622" uniqueCount="115">
   <si>
     <t>MODEL'S TYPE</t>
   </si>
@@ -410,6 +410,9 @@
   </si>
   <si>
     <t>said in: 37.03%, said by: 37.02%, support: 21.46%, attack: 3.79%, equivalent: 0.67%, role: 0.03%</t>
+  </si>
+  <si>
+    <t>WEIGHTED RELATION PREDICTION HITS@1</t>
   </si>
 </sst>
 </file>
@@ -570,7 +573,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="85">
+  <cellXfs count="86">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -767,7 +770,7 @@
     <xf numFmtId="164" fontId="5" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -821,8 +824,11 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -849,9 +855,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema di Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - Tema 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -889,7 +895,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -995,7 +1001,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1137,7 +1143,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -7527,7 +7533,7 @@
       <c r="G73" s="11">
         <v>0.31423644379999999</v>
       </c>
-      <c r="H73" s="11">
+      <c r="H73" s="54">
         <v>0.87912838900000001</v>
       </c>
       <c r="I73" s="11">
@@ -7850,11 +7856,11 @@
         <v>0.28440324</v>
       </c>
     </row>
-    <row r="85" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A85" s="1" t="s">
+    <row r="85" spans="1:12" s="42" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A85" s="42" t="s">
         <v>2</v>
       </c>
-      <c r="B85" s="1" t="s">
+      <c r="B85" s="42" t="s">
         <v>5</v>
       </c>
       <c r="C85" s="70" t="s">
@@ -7863,44 +7869,69 @@
       <c r="D85" s="70" t="s">
         <v>79</v>
       </c>
-      <c r="J85" s="11">
+      <c r="E85" s="84">
+        <v>1.9543973900000001E-2</v>
+      </c>
+      <c r="F85" s="84">
+        <v>8.0475187000000007E-3</v>
+      </c>
+      <c r="G85" s="40">
+        <v>0.7549338954</v>
+      </c>
+      <c r="H85" s="84">
+        <v>0.80678453409999995</v>
+      </c>
+      <c r="I85" s="40">
+        <v>0.68024081950000004</v>
+      </c>
+      <c r="J85" s="84">
         <f>SUM(E85*1/3,F85*1/3,H85*1/3)</f>
-        <v>0</v>
-      </c>
-      <c r="K85" s="54">
+        <v>0.27812534223333329</v>
+      </c>
+      <c r="K85" s="40">
         <f>SUM(G85*1/2,I85*1/2)</f>
-        <v>0</v>
-      </c>
-      <c r="L85" s="11">
+        <v>0.71758735745000002</v>
+      </c>
+      <c r="L85" s="84">
         <f>SUM(E85*1/5,F85*1/5,G85*1/5,H85*1/5,I85*1/5)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="86" spans="1:12" s="42" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A86" s="42" t="s">
+        <v>0.45391014831999998</v>
+      </c>
+    </row>
+    <row r="86" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A86" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B86" s="42" t="s">
+      <c r="B86" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C86" s="70"/>
       <c r="D86" s="70"/>
-      <c r="E86" s="66"/>
-      <c r="F86" s="66"/>
-      <c r="G86" s="66"/>
-      <c r="H86" s="66"/>
-      <c r="I86" s="66"/>
-      <c r="J86" s="66">
+      <c r="E86" s="11">
+        <v>8.6223409999999995E-4</v>
+      </c>
+      <c r="F86" s="11">
+        <v>4.8859934999999997E-3</v>
+      </c>
+      <c r="G86" s="11">
+        <v>0.42057865490000002</v>
+      </c>
+      <c r="H86" s="11">
+        <v>0.55166023060000002</v>
+      </c>
+      <c r="I86" s="11">
+        <v>0.49520081519999998</v>
+      </c>
+      <c r="J86" s="11">
         <f>SUM(E86*1/3,F86*1/3,H86*1/3)</f>
-        <v>0</v>
-      </c>
-      <c r="K86" s="66">
+        <v>0.18580281940000001</v>
+      </c>
+      <c r="K86" s="11">
         <f>SUM(G86*1/2,I86*1/2)</f>
-        <v>0</v>
-      </c>
-      <c r="L86" s="40">
+        <v>0.45788973504999997</v>
+      </c>
+      <c r="L86" s="54">
         <f>SUM(E86*1/5,F86*1/5,G86*1/5,H86*1/5,I86*1/5)</f>
-        <v>0</v>
+        <v>0.29463758565999998</v>
       </c>
     </row>
     <row r="87" spans="1:12" x14ac:dyDescent="0.2">
@@ -8290,7 +8321,7 @@
       </c>
       <c r="G102" s="16">
         <f t="shared" si="4"/>
-        <v>0.70549913779999995</v>
+        <v>0.7549338954</v>
       </c>
       <c r="H102" s="16">
         <f t="shared" si="4"/>
@@ -8298,7 +8329,7 @@
       </c>
       <c r="I102" s="16">
         <f t="shared" si="4"/>
-        <v>0.51348317779999997</v>
+        <v>0.68024081950000004</v>
       </c>
       <c r="J102" s="16">
         <f t="shared" si="4"/>
@@ -8306,11 +8337,11 @@
       </c>
       <c r="K102" s="16">
         <f t="shared" si="4"/>
-        <v>0.60320936849999995</v>
+        <v>0.71758735745000002</v>
       </c>
       <c r="L102" s="16">
         <f t="shared" si="4"/>
-        <v>0.39645458486000001</v>
+        <v>0.45391014831999998</v>
       </c>
       <c r="M102" s="16"/>
       <c r="N102" s="17"/>
@@ -8324,35 +8355,35 @@
       <c r="D103" s="78"/>
       <c r="E103" s="29">
         <f t="shared" ref="E103:L103" si="5">AVERAGE(E73:E100)</f>
-        <v>1.1432586072222223E-2</v>
+        <v>1.1309637865E-2</v>
       </c>
       <c r="F103" s="29">
         <f t="shared" si="5"/>
-        <v>6.3070831000000003E-3</v>
+        <v>6.3230504000000003E-3</v>
       </c>
       <c r="G103" s="29">
         <f t="shared" si="5"/>
-        <v>0.34412722744444452</v>
+        <v>0.36849013221499999</v>
       </c>
       <c r="H103" s="29">
         <f t="shared" si="5"/>
-        <v>0.58345119700000003</v>
+        <v>0.59302831553500002</v>
       </c>
       <c r="I103" s="29">
         <f t="shared" si="5"/>
-        <v>0.46034779048888896</v>
+        <v>0.47308509317500003</v>
       </c>
       <c r="J103" s="29">
         <f t="shared" si="5"/>
-        <v>0.17176881890634921</v>
+        <v>0.19386063612698415</v>
       </c>
       <c r="K103" s="29">
         <f t="shared" si="5"/>
-        <v>0.34477500768571429</v>
+        <v>0.40075010732857141</v>
       </c>
       <c r="L103" s="29">
         <f t="shared" si="5"/>
-        <v>0.24097129441809528</v>
+        <v>0.27661642460761909</v>
       </c>
       <c r="M103" s="29"/>
       <c r="N103" s="58"/>
@@ -8417,18 +8448,20 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B868A83-228E-4B46-AAFD-22D8E7035CA7}">
-  <dimension ref="A1:I13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="22.6640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:J13"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="22.6640625" defaultRowHeight="21" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="34.5" style="84" customWidth="1"/>
-    <col min="2" max="2" width="22.6640625" style="84"/>
-    <col min="3" max="3" width="42" style="84" customWidth="1"/>
-    <col min="4" max="4" width="38.6640625" style="84" customWidth="1"/>
-    <col min="5" max="6" width="26.1640625" style="84" customWidth="1"/>
-    <col min="7" max="16384" width="22.6640625" style="84"/>
+    <col min="1" max="1" width="34.5" style="1" customWidth="1"/>
+    <col min="2" max="2" width="22.6640625" style="1"/>
+    <col min="3" max="3" width="42" style="1" customWidth="1"/>
+    <col min="4" max="4" width="38.6640625" style="1" customWidth="1"/>
+    <col min="5" max="6" width="26.1640625" style="1" customWidth="1"/>
+    <col min="7" max="9" width="22.6640625" style="1"/>
+    <col min="10" max="10" width="31.1640625" style="1" customWidth="1"/>
+    <col min="11" max="16384" width="22.6640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="6" customFormat="1" ht="66" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" s="6" customFormat="1" ht="88" x14ac:dyDescent="0.2">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -8456,8 +8489,11 @@
       <c r="I1" s="12" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.2">
+      <c r="J1" s="7" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -8485,8 +8521,12 @@
       <c r="I3" s="11">
         <v>4.5112781999999997E-2</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.2">
+      <c r="J3" s="1">
+        <f>G3*1/3+H3*1/3+I3*1/3</f>
+        <v>0.38645857859999999</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
@@ -8510,8 +8550,12 @@
       <c r="I4" s="11">
         <v>0.30827067670000002</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.2">
+      <c r="J4" s="1">
+        <f t="shared" ref="J4:J12" si="0">G4*1/3+H4*1/3+I4*1/3</f>
+        <v>0.34069669856666668</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
@@ -8535,44 +8579,52 @@
       <c r="I5" s="11">
         <v>0.962406015</v>
       </c>
-    </row>
-    <row r="7" spans="1:9" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.2">
-      <c r="A7" s="1" t="s">
+      <c r="J5" s="1">
+        <f t="shared" si="0"/>
+        <v>0.33626065166666669</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" s="42" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="42" t="s">
         <v>2</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="42" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="70" t="s">
+      <c r="C7" s="85" t="s">
         <v>110</v>
       </c>
       <c r="D7" s="70" t="s">
         <v>111</v>
       </c>
-      <c r="E7" s="1">
+      <c r="E7" s="42">
         <v>0.70795781400000002</v>
       </c>
-      <c r="F7" s="1">
+      <c r="F7" s="42">
         <v>0.89434324070000004</v>
       </c>
-      <c r="G7" s="11">
+      <c r="G7" s="84">
         <v>0.79573876789999998</v>
       </c>
-      <c r="H7" s="11">
+      <c r="H7" s="84">
         <v>0.31020942410000002</v>
       </c>
-      <c r="I7" s="11">
+      <c r="I7" s="84">
         <v>0.14285714290000001</v>
       </c>
-    </row>
-    <row r="8" spans="1:9" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.2">
+      <c r="J7" s="66">
+        <f t="shared" si="0"/>
+        <v>0.41626844496666671</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="70"/>
+      <c r="C8" s="85"/>
       <c r="D8" s="70"/>
       <c r="E8" s="1">
         <v>0.27823585810000001</v>
@@ -8589,15 +8641,19 @@
       <c r="I8" s="11">
         <v>0.47368421049999998</v>
       </c>
-    </row>
-    <row r="9" spans="1:9" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.2">
+      <c r="J8" s="1">
+        <f t="shared" si="0"/>
+        <v>0.35805102890000001</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="70"/>
+      <c r="C9" s="85"/>
       <c r="D9" s="70"/>
       <c r="E9" s="1">
         <v>2.9146692200000001E-2</v>
@@ -8614,8 +8670,12 @@
       <c r="I9" s="11">
         <v>0.97744360900000005</v>
       </c>
-    </row>
-    <row r="11" spans="1:9" ht="21" x14ac:dyDescent="0.2">
+      <c r="J9" s="1">
+        <f t="shared" si="0"/>
+        <v>0.33433582833333336</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>2</v>
       </c>
@@ -8628,8 +8688,27 @@
       <c r="D11" s="70" t="s">
         <v>113</v>
       </c>
-    </row>
-    <row r="12" spans="1:9" ht="21" x14ac:dyDescent="0.2">
+      <c r="E11" s="1">
+        <v>0.7549338954</v>
+      </c>
+      <c r="F11" s="1">
+        <v>0.95612186239999997</v>
+      </c>
+      <c r="G11" s="1">
+        <v>0.85370370370000004</v>
+      </c>
+      <c r="H11" s="1">
+        <v>0.32460732980000001</v>
+      </c>
+      <c r="I11" s="1">
+        <v>2.9629629599999999E-2</v>
+      </c>
+      <c r="J11" s="1">
+        <f t="shared" si="0"/>
+        <v>0.40264688770000001</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>3</v>
       </c>
@@ -8638,8 +8717,27 @@
       </c>
       <c r="C12" s="70"/>
       <c r="D12" s="70"/>
-    </row>
-    <row r="13" spans="1:9" ht="21" x14ac:dyDescent="0.2">
+      <c r="E12" s="1">
+        <v>0.42057865490000002</v>
+      </c>
+      <c r="F12" s="1">
+        <v>0.64073577309999996</v>
+      </c>
+      <c r="G12" s="1">
+        <v>0.45162037040000003</v>
+      </c>
+      <c r="H12" s="1">
+        <v>0.25130890049999999</v>
+      </c>
+      <c r="I12" s="1">
+        <v>0.3851851852</v>
+      </c>
+      <c r="J12" s="1">
+        <f t="shared" si="0"/>
+        <v>0.36270481870000004</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
         <v>4</v>
       </c>

--- a/benchmarking/results/results.xlsx
+++ b/benchmarking/results/results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/deborahdore/Documents/political-debates-graph-analysis/benchmarking/results/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6A08E89-7ED9-F041-84F2-E7459DCB3B6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2906EF9E-2F6B-114F-8242-EB3F72FFED7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="51200" windowHeight="28800" activeTab="4" xr2:uid="{E2EDC037-19C4-FE46-A599-BB595128A04F}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="30240" windowHeight="18900" activeTab="4" xr2:uid="{E2EDC037-19C4-FE46-A599-BB595128A04F}"/>
   </bookViews>
   <sheets>
     <sheet name="Results BASIC" sheetId="1" r:id="rId1"/>
@@ -773,11 +773,29 @@
     <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -785,19 +803,13 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -813,18 +825,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1211,13 +1211,13 @@
       <c r="B2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="74" t="s">
+      <c r="C2" s="73" t="s">
         <v>41</v>
       </c>
-      <c r="D2" s="71" t="s">
+      <c r="D2" s="72" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="71" t="s">
+      <c r="E2" s="72" t="s">
         <v>13</v>
       </c>
       <c r="F2" s="11">
@@ -1235,7 +1235,7 @@
       <c r="J2" s="11">
         <v>0.52440008120000003</v>
       </c>
-      <c r="K2" s="69" t="s">
+      <c r="K2" s="75" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1246,9 +1246,9 @@
       <c r="B3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="72"/>
-      <c r="D3" s="68"/>
-      <c r="E3" s="68"/>
+      <c r="C3" s="69"/>
+      <c r="D3" s="70"/>
+      <c r="E3" s="70"/>
       <c r="F3" s="11">
         <v>3.9117929099999997E-2</v>
       </c>
@@ -1264,7 +1264,7 @@
       <c r="J3" s="11">
         <v>0.4957882649</v>
       </c>
-      <c r="K3" s="70"/>
+      <c r="K3" s="76"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
@@ -1273,9 +1273,9 @@
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="72"/>
-      <c r="D4" s="68"/>
-      <c r="E4" s="68"/>
+      <c r="C4" s="69"/>
+      <c r="D4" s="70"/>
+      <c r="E4" s="70"/>
       <c r="F4" s="11">
         <v>2.1093001000000002E-3</v>
       </c>
@@ -1291,7 +1291,7 @@
       <c r="J4" s="11">
         <v>0.4776301698</v>
       </c>
-      <c r="K4" s="70"/>
+      <c r="K4" s="76"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
@@ -1300,13 +1300,13 @@
       <c r="B6" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="72" t="s">
+      <c r="C6" s="69" t="s">
         <v>42</v>
       </c>
-      <c r="D6" s="68" t="s">
+      <c r="D6" s="70" t="s">
         <v>10</v>
       </c>
-      <c r="E6" s="68" t="s">
+      <c r="E6" s="70" t="s">
         <v>13</v>
       </c>
       <c r="F6" s="11">
@@ -1324,7 +1324,7 @@
       <c r="J6" s="11">
         <v>0.51801477490000003</v>
       </c>
-      <c r="K6" s="70" t="s">
+      <c r="K6" s="76" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1335,9 +1335,9 @@
       <c r="B7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="72"/>
-      <c r="D7" s="68"/>
-      <c r="E7" s="68"/>
+      <c r="C7" s="69"/>
+      <c r="D7" s="70"/>
+      <c r="E7" s="70"/>
       <c r="F7" s="11">
         <v>3.2094270899999999E-2</v>
       </c>
@@ -1353,7 +1353,7 @@
       <c r="J7" s="11">
         <v>0.50083099880000004</v>
       </c>
-      <c r="K7" s="70"/>
+      <c r="K7" s="76"/>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
@@ -1362,9 +1362,9 @@
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="72"/>
-      <c r="D8" s="68"/>
-      <c r="E8" s="68"/>
+      <c r="C8" s="69"/>
+      <c r="D8" s="70"/>
+      <c r="E8" s="70"/>
       <c r="F8" s="11">
         <v>2.8741139999999998E-4</v>
       </c>
@@ -1380,15 +1380,15 @@
       <c r="J8" s="11">
         <v>0.4887305689</v>
       </c>
-      <c r="K8" s="70"/>
+      <c r="K8" s="76"/>
     </row>
     <row r="10" spans="1:12" s="59" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="73" t="s">
+      <c r="A10" s="71" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="73"/>
-      <c r="C10" s="73"/>
-      <c r="D10" s="73"/>
+      <c r="B10" s="71"/>
+      <c r="C10" s="71"/>
+      <c r="D10" s="71"/>
       <c r="E10" s="60"/>
       <c r="F10" s="61"/>
       <c r="G10" s="61"/>
@@ -1404,13 +1404,13 @@
       <c r="B12" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C12" s="72" t="s">
+      <c r="C12" s="69" t="s">
         <v>43</v>
       </c>
-      <c r="D12" s="68" t="s">
+      <c r="D12" s="70" t="s">
         <v>11</v>
       </c>
-      <c r="E12" s="68" t="s">
+      <c r="E12" s="70" t="s">
         <v>17</v>
       </c>
       <c r="F12" s="11">
@@ -1428,7 +1428,7 @@
       <c r="J12" s="11">
         <v>0.65087326729999995</v>
       </c>
-      <c r="K12" s="70" t="s">
+      <c r="K12" s="76" t="s">
         <v>18</v>
       </c>
     </row>
@@ -1439,9 +1439,9 @@
       <c r="B13" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C13" s="72"/>
-      <c r="D13" s="68"/>
-      <c r="E13" s="68"/>
+      <c r="C13" s="69"/>
+      <c r="D13" s="70"/>
+      <c r="E13" s="70"/>
       <c r="F13" s="11">
         <v>1.0937623800000001E-2</v>
       </c>
@@ -1457,7 +1457,7 @@
       <c r="J13" s="11">
         <v>0.48031703009999999</v>
       </c>
-      <c r="K13" s="70"/>
+      <c r="K13" s="76"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
@@ -1466,9 +1466,9 @@
       <c r="B14" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C14" s="72"/>
-      <c r="D14" s="68"/>
-      <c r="E14" s="68"/>
+      <c r="C14" s="69"/>
+      <c r="D14" s="70"/>
+      <c r="E14" s="70"/>
       <c r="F14" s="11">
         <v>2.377744E-4</v>
       </c>
@@ -1484,7 +1484,7 @@
       <c r="J14" s="11">
         <v>0.49770047779999999</v>
       </c>
-      <c r="K14" s="70"/>
+      <c r="K14" s="76"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
@@ -1493,13 +1493,13 @@
       <c r="B16" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C16" s="72" t="s">
+      <c r="C16" s="69" t="s">
         <v>44</v>
       </c>
-      <c r="D16" s="68" t="s">
+      <c r="D16" s="70" t="s">
         <v>19</v>
       </c>
-      <c r="E16" s="68" t="s">
+      <c r="E16" s="70" t="s">
         <v>27</v>
       </c>
       <c r="F16" s="11">
@@ -1517,7 +1517,7 @@
       <c r="J16" s="11">
         <v>0.44106115289999998</v>
       </c>
-      <c r="K16" s="70" t="s">
+      <c r="K16" s="76" t="s">
         <v>36</v>
       </c>
     </row>
@@ -1528,9 +1528,9 @@
       <c r="B17" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C17" s="72"/>
-      <c r="D17" s="68"/>
-      <c r="E17" s="68"/>
+      <c r="C17" s="69"/>
+      <c r="D17" s="70"/>
+      <c r="E17" s="70"/>
       <c r="F17" s="11">
         <v>6.6187922000000001E-3</v>
       </c>
@@ -1546,7 +1546,7 @@
       <c r="J17" s="11">
         <v>0.48203358359999998</v>
       </c>
-      <c r="K17" s="70"/>
+      <c r="K17" s="76"/>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
@@ -1555,9 +1555,9 @@
       <c r="B18" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C18" s="72"/>
-      <c r="D18" s="68"/>
-      <c r="E18" s="68"/>
+      <c r="C18" s="69"/>
+      <c r="D18" s="70"/>
+      <c r="E18" s="70"/>
       <c r="F18" s="11">
         <v>1.9467035999999999E-3</v>
       </c>
@@ -1573,7 +1573,7 @@
       <c r="J18" s="11">
         <v>0.31319458500000003</v>
       </c>
-      <c r="K18" s="70"/>
+      <c r="K18" s="76"/>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
@@ -1582,13 +1582,13 @@
       <c r="B20" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C20" s="72" t="s">
+      <c r="C20" s="69" t="s">
         <v>45</v>
       </c>
-      <c r="D20" s="68" t="s">
+      <c r="D20" s="70" t="s">
         <v>20</v>
       </c>
-      <c r="E20" s="68" t="s">
+      <c r="E20" s="70" t="s">
         <v>28</v>
       </c>
       <c r="F20" s="11">
@@ -1606,7 +1606,7 @@
       <c r="J20" s="11">
         <v>0.42558258160000001</v>
       </c>
-      <c r="K20" s="70" t="s">
+      <c r="K20" s="76" t="s">
         <v>35</v>
       </c>
     </row>
@@ -1617,9 +1617,9 @@
       <c r="B21" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C21" s="72"/>
-      <c r="D21" s="68"/>
-      <c r="E21" s="68"/>
+      <c r="C21" s="69"/>
+      <c r="D21" s="70"/>
+      <c r="E21" s="70"/>
       <c r="F21" s="11">
         <v>0.36964094320000002</v>
       </c>
@@ -1635,7 +1635,7 @@
       <c r="J21" s="11">
         <v>0.71370811339999995</v>
       </c>
-      <c r="K21" s="70"/>
+      <c r="K21" s="76"/>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
@@ -1644,9 +1644,9 @@
       <c r="B22" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C22" s="72"/>
-      <c r="D22" s="68"/>
-      <c r="E22" s="68"/>
+      <c r="C22" s="69"/>
+      <c r="D22" s="70"/>
+      <c r="E22" s="70"/>
       <c r="F22" s="11">
         <v>1.786352E-4</v>
       </c>
@@ -1662,7 +1662,7 @@
       <c r="J22" s="11">
         <v>0.35677707139999998</v>
       </c>
-      <c r="K22" s="70"/>
+      <c r="K22" s="76"/>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
@@ -1671,13 +1671,13 @@
       <c r="B24" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C24" s="72" t="s">
+      <c r="C24" s="69" t="s">
         <v>46</v>
       </c>
-      <c r="D24" s="68" t="s">
+      <c r="D24" s="70" t="s">
         <v>21</v>
       </c>
-      <c r="E24" s="68" t="s">
+      <c r="E24" s="70" t="s">
         <v>32</v>
       </c>
       <c r="F24" s="11">
@@ -1703,9 +1703,9 @@
       <c r="B25" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C25" s="72"/>
-      <c r="D25" s="68"/>
-      <c r="E25" s="68"/>
+      <c r="C25" s="69"/>
+      <c r="D25" s="70"/>
+      <c r="E25" s="70"/>
       <c r="F25" s="11">
         <v>2.2257384000000002E-2</v>
       </c>
@@ -1729,9 +1729,9 @@
       <c r="B26" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C26" s="72"/>
-      <c r="D26" s="68"/>
-      <c r="E26" s="68"/>
+      <c r="C26" s="69"/>
+      <c r="D26" s="70"/>
+      <c r="E26" s="70"/>
       <c r="F26" s="11">
         <v>3.9556960000000001E-4</v>
       </c>
@@ -1755,13 +1755,13 @@
       <c r="B28" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C28" s="72" t="s">
+      <c r="C28" s="69" t="s">
         <v>47</v>
       </c>
-      <c r="D28" s="68" t="s">
+      <c r="D28" s="70" t="s">
         <v>22</v>
       </c>
-      <c r="E28" s="68" t="s">
+      <c r="E28" s="70" t="s">
         <v>33</v>
       </c>
       <c r="F28" s="11">
@@ -1787,9 +1787,9 @@
       <c r="B29" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C29" s="72"/>
-      <c r="D29" s="68"/>
-      <c r="E29" s="68"/>
+      <c r="C29" s="69"/>
+      <c r="D29" s="70"/>
+      <c r="E29" s="70"/>
       <c r="F29" s="11">
         <v>1.8442843300000001E-2</v>
       </c>
@@ -1813,9 +1813,9 @@
       <c r="B30" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C30" s="72"/>
-      <c r="D30" s="68"/>
-      <c r="E30" s="68"/>
+      <c r="C30" s="69"/>
+      <c r="D30" s="70"/>
+      <c r="E30" s="70"/>
       <c r="F30" s="11">
         <v>6.9899990000000004E-4</v>
       </c>
@@ -1839,13 +1839,13 @@
       <c r="B32" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C32" s="72" t="s">
+      <c r="C32" s="69" t="s">
         <v>48</v>
       </c>
-      <c r="D32" s="68" t="s">
+      <c r="D32" s="70" t="s">
         <v>23</v>
       </c>
-      <c r="E32" s="68" t="s">
+      <c r="E32" s="70" t="s">
         <v>29</v>
       </c>
       <c r="F32" s="11">
@@ -1871,9 +1871,9 @@
       <c r="B33" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C33" s="72"/>
-      <c r="D33" s="68"/>
-      <c r="E33" s="68"/>
+      <c r="C33" s="69"/>
+      <c r="D33" s="70"/>
+      <c r="E33" s="70"/>
       <c r="F33" s="11">
         <v>4.8571429999999999E-4</v>
       </c>
@@ -1897,9 +1897,9 @@
       <c r="B34" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C34" s="72"/>
-      <c r="D34" s="68"/>
-      <c r="E34" s="68"/>
+      <c r="C34" s="69"/>
+      <c r="D34" s="70"/>
+      <c r="E34" s="70"/>
       <c r="F34" s="11">
         <v>8.5714299999999993E-5</v>
       </c>
@@ -1923,13 +1923,13 @@
       <c r="B36" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C36" s="72" t="s">
+      <c r="C36" s="69" t="s">
         <v>49</v>
       </c>
-      <c r="D36" s="68" t="s">
+      <c r="D36" s="70" t="s">
         <v>24</v>
       </c>
-      <c r="E36" s="68" t="s">
+      <c r="E36" s="70" t="s">
         <v>34</v>
       </c>
       <c r="F36" s="11">
@@ -1955,9 +1955,9 @@
       <c r="B37" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C37" s="72"/>
-      <c r="D37" s="68"/>
-      <c r="E37" s="68"/>
+      <c r="C37" s="69"/>
+      <c r="D37" s="70"/>
+      <c r="E37" s="70"/>
       <c r="F37" s="11">
         <v>0.12567659680000001</v>
       </c>
@@ -1981,9 +1981,9 @@
       <c r="B38" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C38" s="72"/>
-      <c r="D38" s="68"/>
-      <c r="E38" s="68"/>
+      <c r="C38" s="69"/>
+      <c r="D38" s="70"/>
+      <c r="E38" s="70"/>
       <c r="F38" s="11">
         <v>5.4127739999999998E-4</v>
       </c>
@@ -2001,12 +2001,12 @@
       </c>
     </row>
     <row r="40" spans="1:11" s="59" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="73" t="s">
+      <c r="A40" s="71" t="s">
         <v>38</v>
       </c>
-      <c r="B40" s="73"/>
-      <c r="C40" s="73"/>
-      <c r="D40" s="73"/>
+      <c r="B40" s="71"/>
+      <c r="C40" s="71"/>
+      <c r="D40" s="71"/>
       <c r="E40" s="60"/>
       <c r="F40" s="61"/>
       <c r="G40" s="61"/>
@@ -2022,13 +2022,13 @@
       <c r="B42" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C42" s="72" t="s">
+      <c r="C42" s="69" t="s">
         <v>50</v>
       </c>
-      <c r="D42" s="68" t="s">
+      <c r="D42" s="70" t="s">
         <v>25</v>
       </c>
-      <c r="E42" s="68" t="s">
+      <c r="E42" s="70" t="s">
         <v>27</v>
       </c>
       <c r="F42" s="11">
@@ -2046,7 +2046,7 @@
       <c r="J42" s="11">
         <v>0.47978398890000001</v>
       </c>
-      <c r="K42" s="70" t="s">
+      <c r="K42" s="76" t="s">
         <v>30</v>
       </c>
     </row>
@@ -2057,9 +2057,9 @@
       <c r="B43" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C43" s="72"/>
-      <c r="D43" s="68"/>
-      <c r="E43" s="68"/>
+      <c r="C43" s="69"/>
+      <c r="D43" s="70"/>
+      <c r="E43" s="70"/>
       <c r="F43" s="11">
         <v>0.15768715</v>
       </c>
@@ -2075,7 +2075,7 @@
       <c r="J43" s="11">
         <v>0.64265883619999997</v>
       </c>
-      <c r="K43" s="70"/>
+      <c r="K43" s="76"/>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
@@ -2084,9 +2084,9 @@
       <c r="B44" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C44" s="72"/>
-      <c r="D44" s="68"/>
-      <c r="E44" s="68"/>
+      <c r="C44" s="69"/>
+      <c r="D44" s="70"/>
+      <c r="E44" s="70"/>
       <c r="F44" s="11">
         <v>1.5776599999999999E-4</v>
       </c>
@@ -2102,7 +2102,7 @@
       <c r="J44" s="11">
         <v>0.33957444949999999</v>
       </c>
-      <c r="K44" s="70"/>
+      <c r="K44" s="76"/>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
@@ -2111,13 +2111,13 @@
       <c r="B46" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C46" s="72" t="s">
+      <c r="C46" s="69" t="s">
         <v>51</v>
       </c>
-      <c r="D46" s="68" t="s">
+      <c r="D46" s="70" t="s">
         <v>26</v>
       </c>
-      <c r="E46" s="68" t="s">
+      <c r="E46" s="70" t="s">
         <v>28</v>
       </c>
       <c r="F46" s="11">
@@ -2135,7 +2135,7 @@
       <c r="J46" s="11">
         <v>0.43650638670000003</v>
       </c>
-      <c r="K46" s="70" t="s">
+      <c r="K46" s="76" t="s">
         <v>31</v>
       </c>
     </row>
@@ -2146,9 +2146,9 @@
       <c r="B47" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C47" s="72"/>
-      <c r="D47" s="68"/>
-      <c r="E47" s="68"/>
+      <c r="C47" s="69"/>
+      <c r="D47" s="70"/>
+      <c r="E47" s="70"/>
       <c r="F47" s="11">
         <v>0.28846457310000001</v>
       </c>
@@ -2164,7 +2164,7 @@
       <c r="J47" s="11">
         <v>0.62979789600000002</v>
       </c>
-      <c r="K47" s="70"/>
+      <c r="K47" s="76"/>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
@@ -2173,9 +2173,9 @@
       <c r="B48" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C48" s="72"/>
-      <c r="D48" s="68"/>
-      <c r="E48" s="68"/>
+      <c r="C48" s="69"/>
+      <c r="D48" s="70"/>
+      <c r="E48" s="70"/>
       <c r="F48" s="11">
         <v>2.7615590000000002E-4</v>
       </c>
@@ -2191,7 +2191,7 @@
       <c r="J48" s="11">
         <v>0.39453545410000002</v>
       </c>
-      <c r="K48" s="70"/>
+      <c r="K48" s="76"/>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
@@ -2200,13 +2200,13 @@
       <c r="B50" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C50" s="72" t="s">
+      <c r="C50" s="69" t="s">
         <v>52</v>
       </c>
-      <c r="D50" s="68" t="s">
+      <c r="D50" s="70" t="s">
         <v>39</v>
       </c>
-      <c r="E50" s="68" t="s">
+      <c r="E50" s="70" t="s">
         <v>29</v>
       </c>
       <c r="F50" s="11">
@@ -2232,9 +2232,9 @@
       <c r="B51" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C51" s="72"/>
-      <c r="D51" s="68"/>
-      <c r="E51" s="68"/>
+      <c r="C51" s="69"/>
+      <c r="D51" s="70"/>
+      <c r="E51" s="70"/>
       <c r="F51" s="11">
         <v>3.5391416699999997E-2</v>
       </c>
@@ -2258,9 +2258,9 @@
       <c r="B52" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C52" s="72"/>
-      <c r="D52" s="68"/>
-      <c r="E52" s="68"/>
+      <c r="C52" s="69"/>
+      <c r="D52" s="70"/>
+      <c r="E52" s="70"/>
       <c r="F52" s="11">
         <v>9.9344299999999997E-5</v>
       </c>
@@ -2278,12 +2278,12 @@
       </c>
     </row>
     <row r="55" spans="1:11" s="42" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="75" t="s">
+      <c r="A55" s="68" t="s">
         <v>59</v>
       </c>
-      <c r="B55" s="75"/>
-      <c r="C55" s="75"/>
-      <c r="D55" s="75"/>
+      <c r="B55" s="68"/>
+      <c r="C55" s="68"/>
+      <c r="D55" s="68"/>
       <c r="E55" s="39"/>
       <c r="F55" s="40">
         <f>MAX(F2:F52)</f>
@@ -2308,12 +2308,12 @@
       <c r="K55" s="41"/>
     </row>
     <row r="56" spans="1:11" s="46" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="67" t="s">
+      <c r="A56" s="74" t="s">
         <v>60</v>
       </c>
-      <c r="B56" s="67"/>
-      <c r="C56" s="67"/>
-      <c r="D56" s="67"/>
+      <c r="B56" s="74"/>
+      <c r="C56" s="74"/>
+      <c r="D56" s="74"/>
       <c r="E56" s="43"/>
       <c r="F56" s="44">
         <f>AVERAGE(F2:F52)</f>
@@ -2339,37 +2339,6 @@
     </row>
   </sheetData>
   <mergeCells count="47">
-    <mergeCell ref="A55:D55"/>
-    <mergeCell ref="C6:C8"/>
-    <mergeCell ref="C12:C14"/>
-    <mergeCell ref="C16:C18"/>
-    <mergeCell ref="C20:C22"/>
-    <mergeCell ref="C24:C26"/>
-    <mergeCell ref="C50:C52"/>
-    <mergeCell ref="D24:D26"/>
-    <mergeCell ref="D28:D30"/>
-    <mergeCell ref="D32:D34"/>
-    <mergeCell ref="D36:D38"/>
-    <mergeCell ref="D42:D44"/>
-    <mergeCell ref="D46:D48"/>
-    <mergeCell ref="D50:D52"/>
-    <mergeCell ref="A40:D40"/>
-    <mergeCell ref="D2:D4"/>
-    <mergeCell ref="D6:D8"/>
-    <mergeCell ref="D12:D14"/>
-    <mergeCell ref="D16:D18"/>
-    <mergeCell ref="D20:D22"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="C2:C4"/>
-    <mergeCell ref="E12:E14"/>
-    <mergeCell ref="E16:E18"/>
-    <mergeCell ref="E20:E22"/>
-    <mergeCell ref="C42:C44"/>
-    <mergeCell ref="C46:C48"/>
-    <mergeCell ref="C28:C30"/>
-    <mergeCell ref="C32:C34"/>
-    <mergeCell ref="C36:C38"/>
-    <mergeCell ref="E46:E48"/>
     <mergeCell ref="A56:D56"/>
     <mergeCell ref="E50:E52"/>
     <mergeCell ref="K2:K4"/>
@@ -2386,6 +2355,37 @@
     <mergeCell ref="E42:E44"/>
     <mergeCell ref="E2:E4"/>
     <mergeCell ref="E6:E8"/>
+    <mergeCell ref="E12:E14"/>
+    <mergeCell ref="E16:E18"/>
+    <mergeCell ref="E20:E22"/>
+    <mergeCell ref="C42:C44"/>
+    <mergeCell ref="C46:C48"/>
+    <mergeCell ref="C28:C30"/>
+    <mergeCell ref="C32:C34"/>
+    <mergeCell ref="C36:C38"/>
+    <mergeCell ref="E46:E48"/>
+    <mergeCell ref="D2:D4"/>
+    <mergeCell ref="D6:D8"/>
+    <mergeCell ref="D12:D14"/>
+    <mergeCell ref="D16:D18"/>
+    <mergeCell ref="D20:D22"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="C2:C4"/>
+    <mergeCell ref="A55:D55"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="C12:C14"/>
+    <mergeCell ref="C16:C18"/>
+    <mergeCell ref="C20:C22"/>
+    <mergeCell ref="C24:C26"/>
+    <mergeCell ref="C50:C52"/>
+    <mergeCell ref="D24:D26"/>
+    <mergeCell ref="D28:D30"/>
+    <mergeCell ref="D32:D34"/>
+    <mergeCell ref="D36:D38"/>
+    <mergeCell ref="D42:D44"/>
+    <mergeCell ref="D46:D48"/>
+    <mergeCell ref="D50:D52"/>
+    <mergeCell ref="A40:D40"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2453,13 +2453,13 @@
       <c r="B2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="74" t="s">
+      <c r="C2" s="73" t="s">
         <v>41</v>
       </c>
-      <c r="D2" s="71" t="s">
+      <c r="D2" s="72" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="71" t="s">
+      <c r="E2" s="72" t="s">
         <v>13</v>
       </c>
       <c r="F2" s="11">
@@ -2477,7 +2477,7 @@
       <c r="J2" s="11">
         <v>0.5008326072</v>
       </c>
-      <c r="K2" s="69" t="s">
+      <c r="K2" s="75" t="s">
         <v>15</v>
       </c>
     </row>
@@ -2488,9 +2488,9 @@
       <c r="B3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="72"/>
-      <c r="D3" s="68"/>
-      <c r="E3" s="68"/>
+      <c r="C3" s="69"/>
+      <c r="D3" s="70"/>
+      <c r="E3" s="70"/>
       <c r="F3" s="11">
         <v>2.8763183099999999E-2</v>
       </c>
@@ -2506,7 +2506,7 @@
       <c r="J3" s="11">
         <v>0.49456959480000001</v>
       </c>
-      <c r="K3" s="70"/>
+      <c r="K3" s="76"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
@@ -2515,9 +2515,9 @@
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="72"/>
-      <c r="D4" s="68"/>
-      <c r="E4" s="68"/>
+      <c r="C4" s="69"/>
+      <c r="D4" s="70"/>
+      <c r="E4" s="70"/>
       <c r="F4" s="11">
         <v>5.7526370000000003E-4</v>
       </c>
@@ -2533,7 +2533,7 @@
       <c r="J4" s="11">
         <v>0.46208879800000002</v>
       </c>
-      <c r="K4" s="70"/>
+      <c r="K4" s="76"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="G5" s="11"/>
@@ -2548,13 +2548,13 @@
       <c r="B6" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="72" t="s">
+      <c r="C6" s="69" t="s">
         <v>42</v>
       </c>
-      <c r="D6" s="68" t="s">
+      <c r="D6" s="70" t="s">
         <v>10</v>
       </c>
-      <c r="E6" s="68" t="s">
+      <c r="E6" s="70" t="s">
         <v>13</v>
       </c>
       <c r="F6" s="11">
@@ -2572,7 +2572,7 @@
       <c r="J6" s="11">
         <v>0.50993042769999997</v>
       </c>
-      <c r="K6" s="70" t="s">
+      <c r="K6" s="76" t="s">
         <v>16</v>
       </c>
     </row>
@@ -2583,9 +2583,9 @@
       <c r="B7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="72"/>
-      <c r="D7" s="68"/>
-      <c r="E7" s="68"/>
+      <c r="C7" s="69"/>
+      <c r="D7" s="70"/>
+      <c r="E7" s="70"/>
       <c r="F7" s="11">
         <v>3.3435524000000001E-2</v>
       </c>
@@ -2601,7 +2601,7 @@
       <c r="J7" s="11">
         <v>0.50392556320000004</v>
       </c>
-      <c r="K7" s="70"/>
+      <c r="K7" s="76"/>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
@@ -2610,9 +2610,9 @@
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="72"/>
-      <c r="D8" s="68"/>
-      <c r="E8" s="68"/>
+      <c r="C8" s="69"/>
+      <c r="D8" s="70"/>
+      <c r="E8" s="70"/>
       <c r="F8" s="11">
         <v>3.8321520000000002E-4</v>
       </c>
@@ -2628,7 +2628,7 @@
       <c r="J8" s="11">
         <v>0.47738500210000001</v>
       </c>
-      <c r="K8" s="70"/>
+      <c r="K8" s="76"/>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="G9" s="11"/>
@@ -2637,12 +2637,12 @@
       <c r="J9" s="11"/>
     </row>
     <row r="10" spans="1:12" s="59" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="73" t="s">
+      <c r="A10" s="71" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="73"/>
-      <c r="C10" s="73"/>
-      <c r="D10" s="73"/>
+      <c r="B10" s="71"/>
+      <c r="C10" s="71"/>
+      <c r="D10" s="71"/>
       <c r="E10" s="60"/>
       <c r="F10" s="61"/>
       <c r="G10" s="61"/>
@@ -2664,13 +2664,13 @@
       <c r="B12" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C12" s="72" t="s">
+      <c r="C12" s="69" t="s">
         <v>43</v>
       </c>
-      <c r="D12" s="68" t="s">
+      <c r="D12" s="70" t="s">
         <v>11</v>
       </c>
-      <c r="E12" s="68" t="s">
+      <c r="E12" s="70" t="s">
         <v>17</v>
       </c>
       <c r="F12" s="11">
@@ -2688,7 +2688,7 @@
       <c r="J12" s="11">
         <v>0.4966675035</v>
       </c>
-      <c r="K12" s="70" t="s">
+      <c r="K12" s="76" t="s">
         <v>18</v>
       </c>
     </row>
@@ -2699,9 +2699,9 @@
       <c r="B13" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C13" s="72"/>
-      <c r="D13" s="68"/>
-      <c r="E13" s="68"/>
+      <c r="C13" s="69"/>
+      <c r="D13" s="70"/>
+      <c r="E13" s="70"/>
       <c r="F13" s="11">
         <v>2.876318E-4</v>
       </c>
@@ -2717,7 +2717,7 @@
       <c r="J13" s="11">
         <v>0.48225264400000001</v>
       </c>
-      <c r="K13" s="70"/>
+      <c r="K13" s="76"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
@@ -2726,9 +2726,9 @@
       <c r="B14" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C14" s="72"/>
-      <c r="D14" s="68"/>
-      <c r="E14" s="68"/>
+      <c r="C14" s="69"/>
+      <c r="D14" s="70"/>
+      <c r="E14" s="70"/>
       <c r="F14" s="11">
         <v>6.7114089999999996E-4</v>
       </c>
@@ -2744,7 +2744,7 @@
       <c r="J14" s="11">
         <v>0.43776818420000002</v>
       </c>
-      <c r="K14" s="70"/>
+      <c r="K14" s="76"/>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="G15" s="11"/>
@@ -2759,13 +2759,13 @@
       <c r="B16" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C16" s="72" t="s">
+      <c r="C16" s="69" t="s">
         <v>44</v>
       </c>
-      <c r="D16" s="68" t="s">
+      <c r="D16" s="70" t="s">
         <v>19</v>
       </c>
-      <c r="E16" s="68" t="s">
+      <c r="E16" s="70" t="s">
         <v>27</v>
       </c>
       <c r="F16" s="11">
@@ -2783,7 +2783,7 @@
       <c r="J16" s="11">
         <v>0.44130707470000002</v>
       </c>
-      <c r="K16" s="70" t="s">
+      <c r="K16" s="76" t="s">
         <v>36</v>
       </c>
     </row>
@@ -2794,9 +2794,9 @@
       <c r="B17" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C17" s="72"/>
-      <c r="D17" s="68"/>
-      <c r="E17" s="68"/>
+      <c r="C17" s="69"/>
+      <c r="D17" s="70"/>
+      <c r="E17" s="70"/>
       <c r="F17" s="11">
         <v>7.7660593999999998E-3</v>
       </c>
@@ -2812,7 +2812,7 @@
       <c r="J17" s="11">
         <v>0.46778393010000002</v>
       </c>
-      <c r="K17" s="70"/>
+      <c r="K17" s="76"/>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
@@ -2821,9 +2821,9 @@
       <c r="B18" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C18" s="72"/>
-      <c r="D18" s="68"/>
-      <c r="E18" s="68"/>
+      <c r="C18" s="69"/>
+      <c r="D18" s="70"/>
+      <c r="E18" s="70"/>
       <c r="F18" s="11">
         <v>2.876318E-4</v>
       </c>
@@ -2839,7 +2839,7 @@
       <c r="J18" s="11">
         <v>0.46815617929999997</v>
       </c>
-      <c r="K18" s="70"/>
+      <c r="K18" s="76"/>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.2">
       <c r="G19" s="11"/>
@@ -2854,13 +2854,13 @@
       <c r="B20" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C20" s="72" t="s">
+      <c r="C20" s="69" t="s">
         <v>45</v>
       </c>
-      <c r="D20" s="68" t="s">
+      <c r="D20" s="70" t="s">
         <v>20</v>
       </c>
-      <c r="E20" s="68" t="s">
+      <c r="E20" s="70" t="s">
         <v>28</v>
       </c>
       <c r="F20" s="11">
@@ -2878,7 +2878,7 @@
       <c r="J20" s="11">
         <v>0.4434595543</v>
       </c>
-      <c r="K20" s="70" t="s">
+      <c r="K20" s="76" t="s">
         <v>35</v>
       </c>
     </row>
@@ -2889,9 +2889,9 @@
       <c r="B21" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C21" s="72"/>
-      <c r="D21" s="68"/>
-      <c r="E21" s="68"/>
+      <c r="C21" s="69"/>
+      <c r="D21" s="70"/>
+      <c r="E21" s="70"/>
       <c r="F21" s="11">
         <v>5.11025887E-2</v>
       </c>
@@ -2907,7 +2907,7 @@
       <c r="J21" s="11">
         <v>0.46092753450000001</v>
       </c>
-      <c r="K21" s="70"/>
+      <c r="K21" s="76"/>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
@@ -2916,9 +2916,9 @@
       <c r="B22" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C22" s="72"/>
-      <c r="D22" s="68"/>
-      <c r="E22" s="68"/>
+      <c r="C22" s="69"/>
+      <c r="D22" s="70"/>
+      <c r="E22" s="70"/>
       <c r="F22" s="11">
         <v>0</v>
       </c>
@@ -2934,7 +2934,7 @@
       <c r="J22" s="11">
         <v>0.4740446935</v>
       </c>
-      <c r="K22" s="70"/>
+      <c r="K22" s="76"/>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.2">
       <c r="G23" s="11"/>
@@ -2949,13 +2949,13 @@
       <c r="B24" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C24" s="72" t="s">
+      <c r="C24" s="69" t="s">
         <v>46</v>
       </c>
-      <c r="D24" s="68" t="s">
+      <c r="D24" s="70" t="s">
         <v>21</v>
       </c>
-      <c r="E24" s="68" t="s">
+      <c r="E24" s="70" t="s">
         <v>32</v>
       </c>
       <c r="F24" s="11">
@@ -2981,9 +2981,9 @@
       <c r="B25" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C25" s="72"/>
-      <c r="D25" s="68"/>
-      <c r="E25" s="68"/>
+      <c r="C25" s="69"/>
+      <c r="D25" s="70"/>
+      <c r="E25" s="70"/>
       <c r="F25" s="11">
         <v>3.0584851400000002E-2</v>
       </c>
@@ -3007,9 +3007,9 @@
       <c r="B26" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C26" s="72"/>
-      <c r="D26" s="68"/>
-      <c r="E26" s="68"/>
+      <c r="C26" s="69"/>
+      <c r="D26" s="70"/>
+      <c r="E26" s="70"/>
       <c r="F26" s="11">
         <v>6.7114089999999996E-4</v>
       </c>
@@ -3039,13 +3039,13 @@
       <c r="B28" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C28" s="72" t="s">
+      <c r="C28" s="69" t="s">
         <v>47</v>
       </c>
-      <c r="D28" s="68" t="s">
+      <c r="D28" s="70" t="s">
         <v>22</v>
       </c>
-      <c r="E28" s="68" t="s">
+      <c r="E28" s="70" t="s">
         <v>33</v>
       </c>
       <c r="F28" s="11">
@@ -3071,9 +3071,9 @@
       <c r="B29" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C29" s="72"/>
-      <c r="D29" s="68"/>
-      <c r="E29" s="68"/>
+      <c r="C29" s="69"/>
+      <c r="D29" s="70"/>
+      <c r="E29" s="70"/>
       <c r="F29" s="11">
         <v>1.42857143E-2</v>
       </c>
@@ -3097,9 +3097,9 @@
       <c r="B30" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C30" s="72"/>
-      <c r="D30" s="68"/>
-      <c r="E30" s="68"/>
+      <c r="C30" s="69"/>
+      <c r="D30" s="70"/>
+      <c r="E30" s="70"/>
       <c r="F30" s="11">
         <v>3.8350910000000001E-4</v>
       </c>
@@ -3129,13 +3129,13 @@
       <c r="B32" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C32" s="72" t="s">
+      <c r="C32" s="69" t="s">
         <v>48</v>
       </c>
-      <c r="D32" s="68" t="s">
+      <c r="D32" s="70" t="s">
         <v>23</v>
       </c>
-      <c r="E32" s="68" t="s">
+      <c r="E32" s="70" t="s">
         <v>29</v>
       </c>
       <c r="F32" s="11">
@@ -3161,9 +3161,9 @@
       <c r="B33" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C33" s="72"/>
-      <c r="D33" s="68"/>
-      <c r="E33" s="68"/>
+      <c r="C33" s="69"/>
+      <c r="D33" s="70"/>
+      <c r="E33" s="70"/>
       <c r="F33" s="11">
         <v>6.9727237799999994E-2</v>
       </c>
@@ -3187,9 +3187,9 @@
       <c r="B34" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C34" s="72"/>
-      <c r="D34" s="68"/>
-      <c r="E34" s="68"/>
+      <c r="C34" s="69"/>
+      <c r="D34" s="70"/>
+      <c r="E34" s="70"/>
       <c r="F34" s="11">
         <v>2.8812910000000001E-4</v>
       </c>
@@ -3219,13 +3219,13 @@
       <c r="B36" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C36" s="72" t="s">
+      <c r="C36" s="69" t="s">
         <v>49</v>
       </c>
-      <c r="D36" s="68" t="s">
+      <c r="D36" s="70" t="s">
         <v>24</v>
       </c>
-      <c r="E36" s="68" t="s">
+      <c r="E36" s="70" t="s">
         <v>34</v>
       </c>
       <c r="F36" s="11">
@@ -3251,9 +3251,9 @@
       <c r="B37" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C37" s="72"/>
-      <c r="D37" s="68"/>
-      <c r="E37" s="68"/>
+      <c r="C37" s="69"/>
+      <c r="D37" s="70"/>
+      <c r="E37" s="70"/>
       <c r="F37" s="11">
         <v>1.4189837E-2</v>
       </c>
@@ -3277,9 +3277,9 @@
       <c r="B38" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C38" s="72"/>
-      <c r="D38" s="68"/>
-      <c r="E38" s="68"/>
+      <c r="C38" s="69"/>
+      <c r="D38" s="70"/>
+      <c r="E38" s="70"/>
       <c r="F38" s="11">
         <v>2.876318E-4</v>
       </c>
@@ -3303,12 +3303,12 @@
       <c r="J39" s="11"/>
     </row>
     <row r="40" spans="1:11" s="59" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="73" t="s">
+      <c r="A40" s="71" t="s">
         <v>38</v>
       </c>
-      <c r="B40" s="73"/>
-      <c r="C40" s="73"/>
-      <c r="D40" s="73"/>
+      <c r="B40" s="71"/>
+      <c r="C40" s="71"/>
+      <c r="D40" s="71"/>
       <c r="E40" s="60"/>
       <c r="F40" s="61"/>
       <c r="G40" s="61"/>
@@ -3330,13 +3330,13 @@
       <c r="B42" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C42" s="72" t="s">
+      <c r="C42" s="69" t="s">
         <v>50</v>
       </c>
-      <c r="D42" s="68" t="s">
+      <c r="D42" s="70" t="s">
         <v>25</v>
       </c>
-      <c r="E42" s="68" t="s">
+      <c r="E42" s="70" t="s">
         <v>27</v>
       </c>
       <c r="F42" s="11">
@@ -3354,7 +3354,7 @@
       <c r="J42" s="11">
         <v>0.4587482034</v>
       </c>
-      <c r="K42" s="70" t="s">
+      <c r="K42" s="76" t="s">
         <v>30</v>
       </c>
     </row>
@@ -3365,9 +3365,9 @@
       <c r="B43" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C43" s="72"/>
-      <c r="D43" s="68"/>
-      <c r="E43" s="68"/>
+      <c r="C43" s="69"/>
+      <c r="D43" s="70"/>
+      <c r="E43" s="70"/>
       <c r="F43" s="11">
         <v>1.34125311E-2</v>
       </c>
@@ -3383,7 +3383,7 @@
       <c r="J43" s="11">
         <v>0.46907909489999999</v>
       </c>
-      <c r="K43" s="70"/>
+      <c r="K43" s="76"/>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
@@ -3392,9 +3392,9 @@
       <c r="B44" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C44" s="72"/>
-      <c r="D44" s="68"/>
-      <c r="E44" s="68"/>
+      <c r="C44" s="69"/>
+      <c r="D44" s="70"/>
+      <c r="E44" s="70"/>
       <c r="F44" s="11">
         <v>8.6223409999999995E-4</v>
       </c>
@@ -3410,7 +3410,7 @@
       <c r="J44" s="11">
         <v>0.49390839069999998</v>
       </c>
-      <c r="K44" s="70"/>
+      <c r="K44" s="76"/>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.2">
       <c r="G45" s="11"/>
@@ -3425,13 +3425,13 @@
       <c r="B46" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C46" s="72" t="s">
+      <c r="C46" s="69" t="s">
         <v>51</v>
       </c>
-      <c r="D46" s="68" t="s">
+      <c r="D46" s="70" t="s">
         <v>26</v>
       </c>
-      <c r="E46" s="68" t="s">
+      <c r="E46" s="70" t="s">
         <v>28</v>
       </c>
       <c r="F46" s="11">
@@ -3449,7 +3449,7 @@
       <c r="J46" s="11">
         <v>0.45388746419999998</v>
       </c>
-      <c r="K46" s="70" t="s">
+      <c r="K46" s="76" t="s">
         <v>31</v>
       </c>
     </row>
@@ -3460,9 +3460,9 @@
       <c r="B47" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C47" s="72"/>
-      <c r="D47" s="68"/>
-      <c r="E47" s="68"/>
+      <c r="C47" s="69"/>
+      <c r="D47" s="70"/>
+      <c r="E47" s="70"/>
       <c r="F47" s="11">
         <v>4.3303314799999999E-2</v>
       </c>
@@ -3478,7 +3478,7 @@
       <c r="J47" s="11">
         <v>0.45908136910000003</v>
       </c>
-      <c r="K47" s="70"/>
+      <c r="K47" s="76"/>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
@@ -3487,9 +3487,9 @@
       <c r="B48" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C48" s="72"/>
-      <c r="D48" s="68"/>
-      <c r="E48" s="68"/>
+      <c r="C48" s="69"/>
+      <c r="D48" s="70"/>
+      <c r="E48" s="70"/>
       <c r="F48" s="11">
         <v>9.5803800000000006E-5</v>
       </c>
@@ -3505,7 +3505,7 @@
       <c r="J48" s="11">
         <v>0.478579698</v>
       </c>
-      <c r="K48" s="70"/>
+      <c r="K48" s="76"/>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.2">
       <c r="G49" s="11"/>
@@ -3520,13 +3520,13 @@
       <c r="B50" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C50" s="72" t="s">
+      <c r="C50" s="69" t="s">
         <v>52</v>
       </c>
-      <c r="D50" s="68" t="s">
+      <c r="D50" s="70" t="s">
         <v>39</v>
       </c>
-      <c r="E50" s="68" t="s">
+      <c r="E50" s="70" t="s">
         <v>29</v>
       </c>
       <c r="F50" s="11">
@@ -3552,9 +3552,9 @@
       <c r="B51" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C51" s="72"/>
-      <c r="D51" s="68"/>
-      <c r="E51" s="68"/>
+      <c r="C51" s="69"/>
+      <c r="D51" s="70"/>
+      <c r="E51" s="70"/>
       <c r="F51" s="11">
         <v>8.8139489999999997E-3</v>
       </c>
@@ -3578,9 +3578,9 @@
       <c r="B52" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C52" s="72"/>
-      <c r="D52" s="68"/>
-      <c r="E52" s="68"/>
+      <c r="C52" s="69"/>
+      <c r="D52" s="70"/>
+      <c r="E52" s="70"/>
       <c r="F52" s="11">
         <v>1.9160760000000001E-4</v>
       </c>
@@ -3610,12 +3610,12 @@
       <c r="J54" s="11"/>
     </row>
     <row r="55" spans="1:11" s="42" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="75" t="s">
+      <c r="A55" s="68" t="s">
         <v>59</v>
       </c>
-      <c r="B55" s="75"/>
-      <c r="C55" s="75"/>
-      <c r="D55" s="75"/>
+      <c r="B55" s="68"/>
+      <c r="C55" s="68"/>
+      <c r="D55" s="68"/>
       <c r="E55" s="39"/>
       <c r="F55" s="40">
         <f>MAX(F2:F52)</f>
@@ -3640,12 +3640,12 @@
       <c r="K55" s="41"/>
     </row>
     <row r="56" spans="1:11" s="46" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="67" t="s">
+      <c r="A56" s="74" t="s">
         <v>60</v>
       </c>
-      <c r="B56" s="67"/>
-      <c r="C56" s="67"/>
-      <c r="D56" s="67"/>
+      <c r="B56" s="74"/>
+      <c r="C56" s="74"/>
+      <c r="D56" s="74"/>
       <c r="E56" s="43"/>
       <c r="F56" s="44">
         <f>AVERAGE(F2:F52)</f>
@@ -3671,37 +3671,6 @@
     </row>
   </sheetData>
   <mergeCells count="47">
-    <mergeCell ref="A55:D55"/>
-    <mergeCell ref="K42:K44"/>
-    <mergeCell ref="C46:C48"/>
-    <mergeCell ref="D46:D48"/>
-    <mergeCell ref="E46:E48"/>
-    <mergeCell ref="K46:K48"/>
-    <mergeCell ref="E50:E52"/>
-    <mergeCell ref="C36:C38"/>
-    <mergeCell ref="D36:D38"/>
-    <mergeCell ref="E36:E38"/>
-    <mergeCell ref="A40:D40"/>
-    <mergeCell ref="C42:C44"/>
-    <mergeCell ref="D42:D44"/>
-    <mergeCell ref="E42:E44"/>
-    <mergeCell ref="K12:K14"/>
-    <mergeCell ref="C20:C22"/>
-    <mergeCell ref="D20:D22"/>
-    <mergeCell ref="E20:E22"/>
-    <mergeCell ref="K20:K22"/>
-    <mergeCell ref="C16:C18"/>
-    <mergeCell ref="D16:D18"/>
-    <mergeCell ref="E16:E18"/>
-    <mergeCell ref="K16:K18"/>
-    <mergeCell ref="C2:C4"/>
-    <mergeCell ref="D2:D4"/>
-    <mergeCell ref="E2:E4"/>
-    <mergeCell ref="K2:K4"/>
-    <mergeCell ref="C6:C8"/>
-    <mergeCell ref="D6:D8"/>
-    <mergeCell ref="E6:E8"/>
-    <mergeCell ref="K6:K8"/>
     <mergeCell ref="A56:D56"/>
     <mergeCell ref="A10:D10"/>
     <mergeCell ref="C12:C14"/>
@@ -3718,6 +3687,37 @@
     <mergeCell ref="E32:E34"/>
     <mergeCell ref="C50:C52"/>
     <mergeCell ref="D50:D52"/>
+    <mergeCell ref="C2:C4"/>
+    <mergeCell ref="D2:D4"/>
+    <mergeCell ref="E2:E4"/>
+    <mergeCell ref="K2:K4"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="D6:D8"/>
+    <mergeCell ref="E6:E8"/>
+    <mergeCell ref="K6:K8"/>
+    <mergeCell ref="K12:K14"/>
+    <mergeCell ref="C20:C22"/>
+    <mergeCell ref="D20:D22"/>
+    <mergeCell ref="E20:E22"/>
+    <mergeCell ref="K20:K22"/>
+    <mergeCell ref="C16:C18"/>
+    <mergeCell ref="D16:D18"/>
+    <mergeCell ref="E16:E18"/>
+    <mergeCell ref="K16:K18"/>
+    <mergeCell ref="C36:C38"/>
+    <mergeCell ref="D36:D38"/>
+    <mergeCell ref="E36:E38"/>
+    <mergeCell ref="A40:D40"/>
+    <mergeCell ref="C42:C44"/>
+    <mergeCell ref="D42:D44"/>
+    <mergeCell ref="E42:E44"/>
+    <mergeCell ref="A55:D55"/>
+    <mergeCell ref="K42:K44"/>
+    <mergeCell ref="C46:C48"/>
+    <mergeCell ref="D46:D48"/>
+    <mergeCell ref="E46:E48"/>
+    <mergeCell ref="K46:K48"/>
+    <mergeCell ref="E50:E52"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -3798,13 +3798,13 @@
       <c r="B2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="74" t="s">
+      <c r="C2" s="73" t="s">
         <v>41</v>
       </c>
-      <c r="D2" s="71" t="s">
+      <c r="D2" s="72" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="71" t="s">
+      <c r="E2" s="72" t="s">
         <v>13</v>
       </c>
       <c r="F2" s="11">
@@ -3834,7 +3834,7 @@
         <f>SUM(F2*1/5,G2*1/5,H2*1/5,I2*1/5,J2*1/5)</f>
         <v>0.29130368856</v>
       </c>
-      <c r="N2" s="69" t="s">
+      <c r="N2" s="75" t="s">
         <v>15</v>
       </c>
     </row>
@@ -3845,9 +3845,9 @@
       <c r="B3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="72"/>
-      <c r="D3" s="68"/>
-      <c r="E3" s="68"/>
+      <c r="C3" s="69"/>
+      <c r="D3" s="70"/>
+      <c r="E3" s="70"/>
       <c r="F3" s="11">
         <v>2.3969319E-3</v>
       </c>
@@ -3875,7 +3875,7 @@
         <f>SUM(F3*1/5,G3*1/5,H3*1/5,I3*1/5,J3*1/5)</f>
         <v>0.26225518991999996</v>
       </c>
-      <c r="N3" s="70"/>
+      <c r="N3" s="76"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
@@ -3884,9 +3884,9 @@
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="72"/>
-      <c r="D4" s="68"/>
-      <c r="E4" s="68"/>
+      <c r="C4" s="69"/>
+      <c r="D4" s="70"/>
+      <c r="E4" s="70"/>
       <c r="F4" s="11">
         <v>6.5867689399999999E-2</v>
       </c>
@@ -3914,7 +3914,7 @@
         <f>SUM(F4*1/5,G4*1/5,H4*1/5,I4*1/5,J4*1/5)</f>
         <v>0.29107094631999997</v>
       </c>
-      <c r="N4" s="70"/>
+      <c r="N4" s="76"/>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
@@ -3923,13 +3923,13 @@
       <c r="B6" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="72" t="s">
+      <c r="C6" s="69" t="s">
         <v>42</v>
       </c>
-      <c r="D6" s="68" t="s">
+      <c r="D6" s="70" t="s">
         <v>10</v>
       </c>
-      <c r="E6" s="68" t="s">
+      <c r="E6" s="70" t="s">
         <v>13</v>
       </c>
       <c r="F6" s="11">
@@ -3959,7 +3959,7 @@
         <f>SUM(F6*1/5,G6*1/5,H6*1/5,I6*1/5,J6*1/5)</f>
         <v>0.29438649154000002</v>
       </c>
-      <c r="N6" s="70" t="s">
+      <c r="N6" s="76" t="s">
         <v>16</v>
       </c>
     </row>
@@ -3970,9 +3970,9 @@
       <c r="B7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="72"/>
-      <c r="D7" s="68"/>
-      <c r="E7" s="68"/>
+      <c r="C7" s="69"/>
+      <c r="D7" s="70"/>
+      <c r="E7" s="70"/>
       <c r="F7" s="11">
         <v>1.3604138700000001E-2</v>
       </c>
@@ -4000,7 +4000,7 @@
         <f>SUM(F7*1/5,G7*1/5,H7*1/5,I7*1/5,J7*1/5)</f>
         <v>0.27579129901999999</v>
       </c>
-      <c r="N7" s="70"/>
+      <c r="N7" s="76"/>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
@@ -4009,9 +4009,9 @@
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="72"/>
-      <c r="D8" s="68"/>
-      <c r="E8" s="68"/>
+      <c r="C8" s="69"/>
+      <c r="D8" s="70"/>
+      <c r="E8" s="70"/>
       <c r="F8" s="11">
         <v>3.8321517499999999E-2</v>
       </c>
@@ -4039,15 +4039,15 @@
         <f>SUM(F8*1/5,G8*1/5,H8*1/5,I8*1/5,J8*1/5)</f>
         <v>0.2717815321</v>
       </c>
-      <c r="N8" s="70"/>
+      <c r="N8" s="76"/>
     </row>
     <row r="10" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="82" t="s">
+      <c r="A10" s="78" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="82"/>
-      <c r="C10" s="82"/>
-      <c r="D10" s="82"/>
+      <c r="B10" s="78"/>
+      <c r="C10" s="78"/>
+      <c r="D10" s="78"/>
       <c r="E10" s="5"/>
       <c r="F10" s="13"/>
       <c r="G10" s="13"/>
@@ -4066,13 +4066,13 @@
       <c r="B12" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C12" s="72" t="s">
+      <c r="C12" s="69" t="s">
         <v>43</v>
       </c>
-      <c r="D12" s="68" t="s">
+      <c r="D12" s="70" t="s">
         <v>11</v>
       </c>
-      <c r="E12" s="68" t="s">
+      <c r="E12" s="70" t="s">
         <v>17</v>
       </c>
       <c r="F12" s="11">
@@ -4102,7 +4102,7 @@
         <f>SUM(F12*1/5,G12*1/5,H12*1/5,I12*1/5,J12*1/5)</f>
         <v>0.33641501256</v>
       </c>
-      <c r="N12" s="70" t="s">
+      <c r="N12" s="76" t="s">
         <v>18</v>
       </c>
     </row>
@@ -4113,9 +4113,9 @@
       <c r="B13" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C13" s="72"/>
-      <c r="D13" s="68"/>
-      <c r="E13" s="68"/>
+      <c r="C13" s="69"/>
+      <c r="D13" s="70"/>
+      <c r="E13" s="70"/>
       <c r="F13" s="11">
         <v>7.9194630899999993E-2</v>
       </c>
@@ -4143,7 +4143,7 @@
         <f>SUM(F13*1/5,G13*1/5,H13*1/5,I13*1/5,J13*1/5)</f>
         <v>0.26691102733999994</v>
       </c>
-      <c r="N13" s="70"/>
+      <c r="N13" s="76"/>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
@@ -4152,9 +4152,9 @@
       <c r="B14" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C14" s="72"/>
-      <c r="D14" s="68"/>
-      <c r="E14" s="68"/>
+      <c r="C14" s="69"/>
+      <c r="D14" s="70"/>
+      <c r="E14" s="70"/>
       <c r="F14" s="11">
         <v>3.8350910000000001E-4</v>
       </c>
@@ -4182,7 +4182,7 @@
         <f>SUM(F14*1/5,G14*1/5,H14*1/5,I14*1/5,J14*1/5)</f>
         <v>0.22330577798000001</v>
       </c>
-      <c r="N14" s="70"/>
+      <c r="N14" s="76"/>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
@@ -4191,13 +4191,13 @@
       <c r="B16" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C16" s="72" t="s">
+      <c r="C16" s="69" t="s">
         <v>44</v>
       </c>
-      <c r="D16" s="68" t="s">
+      <c r="D16" s="70" t="s">
         <v>19</v>
       </c>
-      <c r="E16" s="68" t="s">
+      <c r="E16" s="70" t="s">
         <v>27</v>
       </c>
       <c r="F16" s="11">
@@ -4227,7 +4227,7 @@
         <f>SUM(F16*1/5,G16*1/5,H16*1/5,I16*1/5,J16*1/5)</f>
         <v>0.34767161497999999</v>
       </c>
-      <c r="N16" s="70" t="s">
+      <c r="N16" s="76" t="s">
         <v>36</v>
       </c>
     </row>
@@ -4238,9 +4238,9 @@
       <c r="B17" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C17" s="72"/>
-      <c r="D17" s="68"/>
-      <c r="E17" s="68"/>
+      <c r="C17" s="69"/>
+      <c r="D17" s="70"/>
+      <c r="E17" s="70"/>
       <c r="F17" s="11">
         <v>3.7296260800000001E-2</v>
       </c>
@@ -4268,7 +4268,7 @@
         <f>SUM(F17*1/5,G17*1/5,H17*1/5,I17*1/5,J17*1/5)</f>
         <v>0.33628517706000005</v>
       </c>
-      <c r="N17" s="70"/>
+      <c r="N17" s="76"/>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
@@ -4277,9 +4277,9 @@
       <c r="B18" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C18" s="72"/>
-      <c r="D18" s="68"/>
-      <c r="E18" s="68"/>
+      <c r="C18" s="69"/>
+      <c r="D18" s="70"/>
+      <c r="E18" s="70"/>
       <c r="F18" s="11">
         <v>1.0546500000000001E-3</v>
       </c>
@@ -4307,7 +4307,7 @@
         <f>SUM(F18*1/5,G18*1/5,H18*1/5,I18*1/5,J18*1/5)</f>
         <v>0.20704430204000002</v>
       </c>
-      <c r="N18" s="70"/>
+      <c r="N18" s="76"/>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
@@ -4316,13 +4316,13 @@
       <c r="B20" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C20" s="72" t="s">
+      <c r="C20" s="69" t="s">
         <v>45</v>
       </c>
-      <c r="D20" s="68" t="s">
+      <c r="D20" s="70" t="s">
         <v>20</v>
       </c>
-      <c r="E20" s="68" t="s">
+      <c r="E20" s="70" t="s">
         <v>28</v>
       </c>
       <c r="F20" s="11">
@@ -4352,7 +4352,7 @@
         <f>SUM(F20*1/5,G20*1/5,H20*1/5,I20*1/5,J20*1/5)</f>
         <v>0.31181358595999997</v>
       </c>
-      <c r="N20" s="70" t="s">
+      <c r="N20" s="76" t="s">
         <v>35</v>
       </c>
     </row>
@@ -4363,9 +4363,9 @@
       <c r="B21" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C21" s="72"/>
-      <c r="D21" s="68"/>
-      <c r="E21" s="68"/>
+      <c r="C21" s="69"/>
+      <c r="D21" s="70"/>
+      <c r="E21" s="70"/>
       <c r="F21" s="11">
         <v>1.05465005E-2</v>
       </c>
@@ -4393,7 +4393,7 @@
         <f>SUM(F21*1/5,G21*1/5,H21*1/5,I21*1/5,J21*1/5)</f>
         <v>0.29879759264</v>
       </c>
-      <c r="N21" s="70"/>
+      <c r="N21" s="76"/>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
@@ -4402,9 +4402,9 @@
       <c r="B22" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C22" s="72"/>
-      <c r="D22" s="68"/>
-      <c r="E22" s="68"/>
+      <c r="C22" s="69"/>
+      <c r="D22" s="70"/>
+      <c r="E22" s="70"/>
       <c r="F22" s="11">
         <v>0</v>
       </c>
@@ -4432,7 +4432,7 @@
         <f>SUM(F22*1/5,G22*1/5,H22*1/5,I22*1/5,J22*1/5)</f>
         <v>0.22541820497999998</v>
       </c>
-      <c r="N22" s="70"/>
+      <c r="N22" s="76"/>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
@@ -4441,13 +4441,13 @@
       <c r="B24" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C24" s="72" t="s">
+      <c r="C24" s="69" t="s">
         <v>46</v>
       </c>
-      <c r="D24" s="68" t="s">
+      <c r="D24" s="70" t="s">
         <v>21</v>
       </c>
-      <c r="E24" s="68" t="s">
+      <c r="E24" s="70" t="s">
         <v>32</v>
       </c>
       <c r="F24" s="11">
@@ -4485,9 +4485,9 @@
       <c r="B25" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C25" s="72"/>
-      <c r="D25" s="68"/>
-      <c r="E25" s="68"/>
+      <c r="C25" s="69"/>
+      <c r="D25" s="70"/>
+      <c r="E25" s="70"/>
       <c r="F25" s="11">
         <v>2.7229146700000002E-2</v>
       </c>
@@ -4523,9 +4523,9 @@
       <c r="B26" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C26" s="72"/>
-      <c r="D26" s="68"/>
-      <c r="E26" s="68"/>
+      <c r="C26" s="69"/>
+      <c r="D26" s="70"/>
+      <c r="E26" s="70"/>
       <c r="F26" s="11">
         <v>3.8350910000000001E-4</v>
       </c>
@@ -4561,13 +4561,13 @@
       <c r="B28" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C28" s="72" t="s">
+      <c r="C28" s="69" t="s">
         <v>47</v>
       </c>
-      <c r="D28" s="68" t="s">
+      <c r="D28" s="70" t="s">
         <v>22</v>
       </c>
-      <c r="E28" s="68" t="s">
+      <c r="E28" s="70" t="s">
         <v>33</v>
       </c>
       <c r="F28" s="11">
@@ -4605,9 +4605,9 @@
       <c r="B29" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C29" s="72"/>
-      <c r="D29" s="68"/>
-      <c r="E29" s="68"/>
+      <c r="C29" s="69"/>
+      <c r="D29" s="70"/>
+      <c r="E29" s="70"/>
       <c r="F29" s="11">
         <v>2.8475551299999999E-2</v>
       </c>
@@ -4643,9 +4643,9 @@
       <c r="B30" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C30" s="72"/>
-      <c r="D30" s="68"/>
-      <c r="E30" s="68"/>
+      <c r="C30" s="69"/>
+      <c r="D30" s="70"/>
+      <c r="E30" s="70"/>
       <c r="F30" s="11">
         <v>1.917546E-4</v>
       </c>
@@ -4681,13 +4681,13 @@
       <c r="B32" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C32" s="72" t="s">
+      <c r="C32" s="69" t="s">
         <v>48</v>
       </c>
-      <c r="D32" s="68" t="s">
+      <c r="D32" s="70" t="s">
         <v>23</v>
       </c>
-      <c r="E32" s="68" t="s">
+      <c r="E32" s="70" t="s">
         <v>29</v>
       </c>
       <c r="F32" s="11">
@@ -4725,9 +4725,9 @@
       <c r="B33" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C33" s="72"/>
-      <c r="D33" s="68"/>
-      <c r="E33" s="68"/>
+      <c r="C33" s="69"/>
+      <c r="D33" s="70"/>
+      <c r="E33" s="70"/>
       <c r="F33" s="11">
         <v>2.4010757000000001E-3</v>
       </c>
@@ -4763,9 +4763,9 @@
       <c r="B34" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C34" s="72"/>
-      <c r="D34" s="68"/>
-      <c r="E34" s="68"/>
+      <c r="C34" s="69"/>
+      <c r="D34" s="70"/>
+      <c r="E34" s="70"/>
       <c r="F34" s="11">
         <v>0</v>
       </c>
@@ -4801,13 +4801,13 @@
       <c r="B36" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C36" s="72" t="s">
+      <c r="C36" s="69" t="s">
         <v>49</v>
       </c>
-      <c r="D36" s="68" t="s">
+      <c r="D36" s="70" t="s">
         <v>24</v>
       </c>
-      <c r="E36" s="68" t="s">
+      <c r="E36" s="70" t="s">
         <v>34</v>
       </c>
       <c r="F36" s="11">
@@ -4845,9 +4845,9 @@
       <c r="B37" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C37" s="72"/>
-      <c r="D37" s="68"/>
-      <c r="E37" s="68"/>
+      <c r="C37" s="69"/>
+      <c r="D37" s="70"/>
+      <c r="E37" s="70"/>
       <c r="F37" s="11">
         <v>5.9443912000000003E-3</v>
       </c>
@@ -4883,9 +4883,9 @@
       <c r="B38" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C38" s="72"/>
-      <c r="D38" s="68"/>
-      <c r="E38" s="68"/>
+      <c r="C38" s="69"/>
+      <c r="D38" s="70"/>
+      <c r="E38" s="70"/>
       <c r="F38" s="11">
         <v>1.917546E-4</v>
       </c>
@@ -4915,12 +4915,12 @@
       </c>
     </row>
     <row r="40" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="82" t="s">
+      <c r="A40" s="78" t="s">
         <v>38</v>
       </c>
-      <c r="B40" s="82"/>
-      <c r="C40" s="82"/>
-      <c r="D40" s="82"/>
+      <c r="B40" s="78"/>
+      <c r="C40" s="78"/>
+      <c r="D40" s="78"/>
       <c r="E40" s="5"/>
       <c r="F40" s="13"/>
       <c r="G40" s="13"/>
@@ -4939,13 +4939,13 @@
       <c r="B42" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C42" s="72" t="s">
+      <c r="C42" s="69" t="s">
         <v>50</v>
       </c>
-      <c r="D42" s="68" t="s">
+      <c r="D42" s="70" t="s">
         <v>25</v>
       </c>
-      <c r="E42" s="68" t="s">
+      <c r="E42" s="70" t="s">
         <v>27</v>
       </c>
       <c r="F42" s="11">
@@ -4975,7 +4975,7 @@
         <f>SUM(F42*1/5,G42*1/5,H42*1/5,I42*1/5,J42*1/5)</f>
         <v>0.32911788728000002</v>
       </c>
-      <c r="N42" s="70" t="s">
+      <c r="N42" s="76" t="s">
         <v>30</v>
       </c>
     </row>
@@ -4986,9 +4986,9 @@
       <c r="B43" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C43" s="72"/>
-      <c r="D43" s="68"/>
-      <c r="E43" s="68"/>
+      <c r="C43" s="69"/>
+      <c r="D43" s="70"/>
+      <c r="E43" s="70"/>
       <c r="F43" s="11">
         <v>1.59034298E-2</v>
       </c>
@@ -5016,7 +5016,7 @@
         <f>SUM(F43*1/5,G43*1/5,H43*1/5,I43*1/5,J43*1/5)</f>
         <v>0.33481998118</v>
       </c>
-      <c r="N43" s="70"/>
+      <c r="N43" s="76"/>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
@@ -5025,9 +5025,9 @@
       <c r="B44" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C44" s="72"/>
-      <c r="D44" s="68"/>
-      <c r="E44" s="68"/>
+      <c r="C44" s="69"/>
+      <c r="D44" s="70"/>
+      <c r="E44" s="70"/>
       <c r="F44" s="62">
         <v>0</v>
       </c>
@@ -5055,7 +5055,7 @@
         <f>SUM(F44*1/5,G44*1/5,H44*1/5,I44*1/5,J44*1/5)</f>
         <v>0.23017129817999998</v>
       </c>
-      <c r="N44" s="70"/>
+      <c r="N44" s="76"/>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
@@ -5064,13 +5064,13 @@
       <c r="B46" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C46" s="72" t="s">
+      <c r="C46" s="69" t="s">
         <v>51</v>
       </c>
-      <c r="D46" s="68" t="s">
+      <c r="D46" s="70" t="s">
         <v>26</v>
       </c>
-      <c r="E46" s="68" t="s">
+      <c r="E46" s="70" t="s">
         <v>28</v>
       </c>
       <c r="F46" s="11">
@@ -5100,7 +5100,7 @@
         <f>SUM(F46*1/5,G46*1/5,H46*1/5,I46*1/5,J46*1/5)</f>
         <v>0.28403192430000002</v>
       </c>
-      <c r="N46" s="70" t="s">
+      <c r="N46" s="76" t="s">
         <v>31</v>
       </c>
     </row>
@@ -5111,9 +5111,9 @@
       <c r="B47" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C47" s="72"/>
-      <c r="D47" s="68"/>
-      <c r="E47" s="68"/>
+      <c r="C47" s="69"/>
+      <c r="D47" s="70"/>
+      <c r="E47" s="70"/>
       <c r="F47" s="11">
         <v>2.90285495E-2</v>
       </c>
@@ -5141,7 +5141,7 @@
         <f>SUM(F47*1/5,G47*1/5,H47*1/5,I47*1/5,J47*1/5)</f>
         <v>0.35089340806000002</v>
       </c>
-      <c r="N47" s="70"/>
+      <c r="N47" s="76"/>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
@@ -5150,9 +5150,9 @@
       <c r="B48" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C48" s="72"/>
-      <c r="D48" s="68"/>
-      <c r="E48" s="68"/>
+      <c r="C48" s="69"/>
+      <c r="D48" s="70"/>
+      <c r="E48" s="70"/>
       <c r="F48" s="11">
         <v>1.9160760000000001E-4</v>
       </c>
@@ -5180,7 +5180,7 @@
         <f>SUM(F48*1/5,G48*1/5,H48*1/5,I48*1/5,J48*1/5)</f>
         <v>0.34178323869999999</v>
       </c>
-      <c r="N48" s="70"/>
+      <c r="N48" s="76"/>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
@@ -5189,13 +5189,13 @@
       <c r="B50" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C50" s="72" t="s">
+      <c r="C50" s="69" t="s">
         <v>52</v>
       </c>
-      <c r="D50" s="68" t="s">
+      <c r="D50" s="70" t="s">
         <v>39</v>
       </c>
-      <c r="E50" s="68" t="s">
+      <c r="E50" s="70" t="s">
         <v>29</v>
       </c>
       <c r="F50" s="11">
@@ -5233,9 +5233,9 @@
       <c r="B51" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C51" s="72"/>
-      <c r="D51" s="68"/>
-      <c r="E51" s="68"/>
+      <c r="C51" s="69"/>
+      <c r="D51" s="70"/>
+      <c r="E51" s="70"/>
       <c r="F51" s="11">
         <v>3.4489365999999999E-3</v>
       </c>
@@ -5271,9 +5271,9 @@
       <c r="B52" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C52" s="72"/>
-      <c r="D52" s="68"/>
-      <c r="E52" s="68"/>
+      <c r="C52" s="69"/>
+      <c r="D52" s="70"/>
+      <c r="E52" s="70"/>
       <c r="F52" s="62">
         <v>4.7901900000000002E-4</v>
       </c>
@@ -5303,12 +5303,12 @@
       </c>
     </row>
     <row r="55" spans="1:14" s="14" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="83" t="s">
+      <c r="A55" s="77" t="s">
         <v>59</v>
       </c>
-      <c r="B55" s="83"/>
-      <c r="C55" s="83"/>
-      <c r="D55" s="83"/>
+      <c r="B55" s="77"/>
+      <c r="C55" s="77"/>
+      <c r="D55" s="77"/>
       <c r="E55" s="15"/>
       <c r="F55" s="16">
         <f t="shared" ref="F55:M55" si="0">MAX(F2:F52)</f>
@@ -5345,12 +5345,12 @@
       <c r="N55" s="17"/>
     </row>
     <row r="56" spans="1:14" s="18" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="81" t="s">
+      <c r="A56" s="79" t="s">
         <v>60</v>
       </c>
-      <c r="B56" s="81"/>
-      <c r="C56" s="81"/>
-      <c r="D56" s="81"/>
+      <c r="B56" s="79"/>
+      <c r="C56" s="79"/>
+      <c r="D56" s="79"/>
       <c r="E56" s="19"/>
       <c r="F56" s="20">
         <f t="shared" ref="F56:M56" si="1">AVERAGE(F2:F52)</f>
@@ -5387,13 +5387,13 @@
       <c r="N56" s="21"/>
     </row>
     <row r="58" spans="1:14" s="22" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="78" t="s">
+      <c r="A58" s="82" t="s">
         <v>64</v>
       </c>
-      <c r="B58" s="78"/>
-      <c r="C58" s="78"/>
-      <c r="D58" s="78"/>
-      <c r="E58" s="78"/>
+      <c r="B58" s="82"/>
+      <c r="C58" s="82"/>
+      <c r="D58" s="82"/>
+      <c r="E58" s="82"/>
       <c r="F58" s="29">
         <f>SUM(F55*(1/3),  G55*(1/3), I55*(1/3))</f>
         <v>0.33744571563333331</v>
@@ -5408,13 +5408,13 @@
       <c r="N58" s="24"/>
     </row>
     <row r="59" spans="1:14" s="27" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="79" t="s">
+      <c r="A59" s="83" t="s">
         <v>65</v>
       </c>
-      <c r="B59" s="79"/>
-      <c r="C59" s="79"/>
-      <c r="D59" s="79"/>
-      <c r="E59" s="79"/>
+      <c r="B59" s="83"/>
+      <c r="C59" s="83"/>
+      <c r="D59" s="83"/>
+      <c r="E59" s="83"/>
       <c r="F59" s="28">
         <f>SUM(H55*(1/2),  J55*(1/2))</f>
         <v>0.67529401794999999</v>
@@ -5429,13 +5429,13 @@
       <c r="N59" s="26"/>
     </row>
     <row r="60" spans="1:14" s="33" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="80" t="s">
+      <c r="A60" s="84" t="s">
         <v>66</v>
       </c>
-      <c r="B60" s="80"/>
-      <c r="C60" s="80"/>
-      <c r="D60" s="80"/>
-      <c r="E60" s="80"/>
+      <c r="B60" s="84"/>
+      <c r="C60" s="84"/>
+      <c r="D60" s="84"/>
+      <c r="E60" s="84"/>
       <c r="F60" s="30">
         <f>SUM(F55*1/5, G55*1/5, H55*1/5, I55*1/5,J55*1/5)</f>
         <v>0.47258503656</v>
@@ -5450,12 +5450,12 @@
       <c r="N60" s="32"/>
     </row>
     <row r="62" spans="1:14" s="37" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="76" t="s">
+      <c r="A62" s="80" t="s">
         <v>83</v>
       </c>
-      <c r="B62" s="76"/>
-      <c r="C62" s="76"/>
-      <c r="D62" s="76"/>
+      <c r="B62" s="80"/>
+      <c r="C62" s="80"/>
+      <c r="D62" s="80"/>
       <c r="E62" s="34"/>
       <c r="F62" s="35"/>
       <c r="G62" s="35"/>
@@ -5468,12 +5468,12 @@
       <c r="N62" s="36"/>
     </row>
     <row r="63" spans="1:14" s="37" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A63" s="76" t="s">
+      <c r="A63" s="80" t="s">
         <v>84</v>
       </c>
-      <c r="B63" s="77"/>
-      <c r="C63" s="77"/>
-      <c r="D63" s="77"/>
+      <c r="B63" s="81"/>
+      <c r="C63" s="81"/>
+      <c r="D63" s="81"/>
       <c r="E63" s="38"/>
       <c r="F63" s="35"/>
       <c r="G63" s="35"/>
@@ -5486,12 +5486,12 @@
       <c r="N63" s="36"/>
     </row>
     <row r="64" spans="1:14" s="37" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="76" t="s">
+      <c r="A64" s="80" t="s">
         <v>85</v>
       </c>
-      <c r="B64" s="77"/>
-      <c r="C64" s="77"/>
-      <c r="D64" s="77"/>
+      <c r="B64" s="81"/>
+      <c r="C64" s="81"/>
+      <c r="D64" s="81"/>
       <c r="E64" s="38"/>
       <c r="F64" s="35"/>
       <c r="G64" s="35"/>
@@ -5505,37 +5505,12 @@
     </row>
   </sheetData>
   <mergeCells count="53">
-    <mergeCell ref="A55:D55"/>
-    <mergeCell ref="N42:N44"/>
-    <mergeCell ref="C46:C48"/>
-    <mergeCell ref="D46:D48"/>
-    <mergeCell ref="E46:E48"/>
-    <mergeCell ref="N46:N48"/>
-    <mergeCell ref="E50:E52"/>
-    <mergeCell ref="C36:C38"/>
-    <mergeCell ref="D36:D38"/>
-    <mergeCell ref="E36:E38"/>
-    <mergeCell ref="A40:D40"/>
-    <mergeCell ref="C42:C44"/>
-    <mergeCell ref="D42:D44"/>
-    <mergeCell ref="E42:E44"/>
-    <mergeCell ref="N12:N14"/>
-    <mergeCell ref="C20:C22"/>
-    <mergeCell ref="D20:D22"/>
-    <mergeCell ref="E20:E22"/>
-    <mergeCell ref="N20:N22"/>
-    <mergeCell ref="C16:C18"/>
-    <mergeCell ref="D16:D18"/>
-    <mergeCell ref="E16:E18"/>
-    <mergeCell ref="N16:N18"/>
-    <mergeCell ref="C2:C4"/>
-    <mergeCell ref="D2:D4"/>
-    <mergeCell ref="E2:E4"/>
-    <mergeCell ref="N2:N4"/>
-    <mergeCell ref="C6:C8"/>
-    <mergeCell ref="D6:D8"/>
-    <mergeCell ref="E6:E8"/>
-    <mergeCell ref="N6:N8"/>
+    <mergeCell ref="A63:D63"/>
+    <mergeCell ref="A64:D64"/>
+    <mergeCell ref="A58:E58"/>
+    <mergeCell ref="A59:E59"/>
+    <mergeCell ref="A60:E60"/>
+    <mergeCell ref="A62:D62"/>
     <mergeCell ref="A56:D56"/>
     <mergeCell ref="A10:D10"/>
     <mergeCell ref="C12:C14"/>
@@ -5552,12 +5527,37 @@
     <mergeCell ref="E32:E34"/>
     <mergeCell ref="C50:C52"/>
     <mergeCell ref="D50:D52"/>
-    <mergeCell ref="A63:D63"/>
-    <mergeCell ref="A64:D64"/>
-    <mergeCell ref="A58:E58"/>
-    <mergeCell ref="A59:E59"/>
-    <mergeCell ref="A60:E60"/>
-    <mergeCell ref="A62:D62"/>
+    <mergeCell ref="C2:C4"/>
+    <mergeCell ref="D2:D4"/>
+    <mergeCell ref="E2:E4"/>
+    <mergeCell ref="N2:N4"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="D6:D8"/>
+    <mergeCell ref="E6:E8"/>
+    <mergeCell ref="N6:N8"/>
+    <mergeCell ref="N12:N14"/>
+    <mergeCell ref="C20:C22"/>
+    <mergeCell ref="D20:D22"/>
+    <mergeCell ref="E20:E22"/>
+    <mergeCell ref="N20:N22"/>
+    <mergeCell ref="C16:C18"/>
+    <mergeCell ref="D16:D18"/>
+    <mergeCell ref="E16:E18"/>
+    <mergeCell ref="N16:N18"/>
+    <mergeCell ref="C36:C38"/>
+    <mergeCell ref="D36:D38"/>
+    <mergeCell ref="E36:E38"/>
+    <mergeCell ref="A40:D40"/>
+    <mergeCell ref="C42:C44"/>
+    <mergeCell ref="D42:D44"/>
+    <mergeCell ref="E42:E44"/>
+    <mergeCell ref="A55:D55"/>
+    <mergeCell ref="N42:N44"/>
+    <mergeCell ref="C46:C48"/>
+    <mergeCell ref="D46:D48"/>
+    <mergeCell ref="E46:E48"/>
+    <mergeCell ref="N46:N48"/>
+    <mergeCell ref="E50:E52"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5638,17 +5638,17 @@
       <c r="N2" s="9"/>
     </row>
     <row r="3" spans="1:14" s="47" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="81" t="s">
+      <c r="A3" s="79" t="s">
         <v>71</v>
       </c>
-      <c r="B3" s="81"/>
-      <c r="C3" s="81"/>
-      <c r="D3" s="81"/>
-      <c r="E3" s="81"/>
-      <c r="F3" s="81"/>
-      <c r="G3" s="81"/>
-      <c r="H3" s="81"/>
-      <c r="I3" s="81"/>
+      <c r="B3" s="79"/>
+      <c r="C3" s="79"/>
+      <c r="D3" s="79"/>
+      <c r="E3" s="79"/>
+      <c r="F3" s="79"/>
+      <c r="G3" s="79"/>
+      <c r="H3" s="79"/>
+      <c r="I3" s="79"/>
       <c r="J3" s="49"/>
       <c r="K3" s="56"/>
       <c r="L3" s="56"/>
@@ -5674,10 +5674,10 @@
       <c r="B5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="70" t="s">
+      <c r="C5" s="76" t="s">
         <v>67</v>
       </c>
-      <c r="D5" s="70" t="s">
+      <c r="D5" s="76" t="s">
         <v>68</v>
       </c>
       <c r="E5" s="11">
@@ -5715,8 +5715,8 @@
       <c r="B6" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="70"/>
-      <c r="D6" s="70"/>
+      <c r="C6" s="76"/>
+      <c r="D6" s="76"/>
       <c r="E6" s="11">
         <v>6.9727237799999994E-2</v>
       </c>
@@ -5752,8 +5752,8 @@
       <c r="B7" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="70"/>
-      <c r="D7" s="70"/>
+      <c r="C7" s="76"/>
+      <c r="D7" s="76"/>
       <c r="E7" s="11">
         <v>2.8812910000000001E-4</v>
       </c>
@@ -5789,10 +5789,10 @@
       <c r="B9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="70" t="s">
+      <c r="C9" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="D9" s="70" t="s">
+      <c r="D9" s="76" t="s">
         <v>70</v>
       </c>
       <c r="E9" s="11">
@@ -5830,8 +5830,8 @@
       <c r="B10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="70"/>
-      <c r="D10" s="70"/>
+      <c r="C10" s="76"/>
+      <c r="D10" s="76"/>
       <c r="E10" s="11">
         <v>2.4010757000000001E-3</v>
       </c>
@@ -5867,8 +5867,8 @@
       <c r="B11" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C11" s="70"/>
-      <c r="D11" s="70"/>
+      <c r="C11" s="76"/>
+      <c r="D11" s="76"/>
       <c r="E11" s="11">
         <v>0</v>
       </c>
@@ -5904,10 +5904,10 @@
       <c r="B13" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C13" s="70" t="s">
+      <c r="C13" s="76" t="s">
         <v>74</v>
       </c>
-      <c r="D13" s="70" t="s">
+      <c r="D13" s="76" t="s">
         <v>81</v>
       </c>
       <c r="E13" s="11">
@@ -5945,8 +5945,8 @@
       <c r="B14" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C14" s="70"/>
-      <c r="D14" s="70"/>
+      <c r="C14" s="76"/>
+      <c r="D14" s="76"/>
       <c r="E14" s="11">
         <v>3.5474592999999999E-3</v>
       </c>
@@ -5982,8 +5982,8 @@
       <c r="B15" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C15" s="70"/>
-      <c r="D15" s="70"/>
+      <c r="C15" s="76"/>
+      <c r="D15" s="76"/>
       <c r="E15" s="11">
         <v>3.8350910000000001E-4</v>
       </c>
@@ -6019,10 +6019,10 @@
       <c r="B17" s="63" t="s">
         <v>5</v>
       </c>
-      <c r="C17" s="70" t="s">
+      <c r="C17" s="76" t="s">
         <v>80</v>
       </c>
-      <c r="D17" s="70" t="s">
+      <c r="D17" s="76" t="s">
         <v>79</v>
       </c>
       <c r="E17" s="64">
@@ -6060,8 +6060,8 @@
       <c r="B18" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C18" s="70"/>
-      <c r="D18" s="70"/>
+      <c r="C18" s="76"/>
+      <c r="D18" s="76"/>
       <c r="E18" s="11">
         <v>3.0680729000000001E-3</v>
       </c>
@@ -6097,8 +6097,8 @@
       <c r="B19" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C19" s="70"/>
-      <c r="D19" s="70"/>
+      <c r="C19" s="76"/>
+      <c r="D19" s="76"/>
       <c r="E19" s="11">
         <v>2.876318E-4</v>
       </c>
@@ -6137,10 +6137,10 @@
       <c r="B21" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C21" s="70" t="s">
+      <c r="C21" s="76" t="s">
         <v>72</v>
       </c>
-      <c r="D21" s="70" t="s">
+      <c r="D21" s="76" t="s">
         <v>73</v>
       </c>
       <c r="E21" s="11">
@@ -6178,8 +6178,8 @@
       <c r="B22" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C22" s="70"/>
-      <c r="D22" s="70"/>
+      <c r="C22" s="76"/>
+      <c r="D22" s="76"/>
       <c r="E22" s="11">
         <v>3.1639501E-3</v>
       </c>
@@ -6215,8 +6215,8 @@
       <c r="B23" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C23" s="70"/>
-      <c r="D23" s="70"/>
+      <c r="C23" s="76"/>
+      <c r="D23" s="76"/>
       <c r="E23" s="11">
         <v>1.917546E-4</v>
       </c>
@@ -6252,10 +6252,10 @@
       <c r="B25" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C25" s="70" t="s">
+      <c r="C25" s="76" t="s">
         <v>77</v>
       </c>
-      <c r="D25" s="70" t="s">
+      <c r="D25" s="76" t="s">
         <v>75</v>
       </c>
       <c r="E25" s="11">
@@ -6293,8 +6293,8 @@
       <c r="B26" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C26" s="70"/>
-      <c r="D26" s="70"/>
+      <c r="C26" s="76"/>
+      <c r="D26" s="76"/>
       <c r="E26" s="11">
         <v>1.70661553E-2</v>
       </c>
@@ -6330,8 +6330,8 @@
       <c r="B27" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C27" s="70"/>
-      <c r="D27" s="70"/>
+      <c r="C27" s="76"/>
+      <c r="D27" s="76"/>
       <c r="E27" s="11">
         <v>6.7114089999999996E-4</v>
       </c>
@@ -6367,10 +6367,10 @@
       <c r="B29" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C29" s="70" t="s">
+      <c r="C29" s="76" t="s">
         <v>78</v>
       </c>
-      <c r="D29" s="70" t="s">
+      <c r="D29" s="76" t="s">
         <v>76</v>
       </c>
       <c r="E29" s="11">
@@ -6408,8 +6408,8 @@
       <c r="B30" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C30" s="70"/>
-      <c r="D30" s="70"/>
+      <c r="C30" s="76"/>
+      <c r="D30" s="76"/>
       <c r="E30" s="11">
         <v>7.2866731000000001E-3</v>
       </c>
@@ -6445,8 +6445,8 @@
       <c r="B31" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C31" s="70"/>
-      <c r="D31" s="70"/>
+      <c r="C31" s="76"/>
+      <c r="D31" s="76"/>
       <c r="E31" s="11">
         <v>0</v>
       </c>
@@ -6476,12 +6476,12 @@
       </c>
     </row>
     <row r="34" spans="1:14" s="14" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="83" t="s">
+      <c r="A34" s="77" t="s">
         <v>59</v>
       </c>
-      <c r="B34" s="83"/>
-      <c r="C34" s="83"/>
-      <c r="D34" s="83"/>
+      <c r="B34" s="77"/>
+      <c r="C34" s="77"/>
+      <c r="D34" s="77"/>
       <c r="E34" s="16">
         <f t="shared" ref="E34:L34" si="0">MAX(E4:E32)</f>
         <v>8.2742090099999999E-2</v>
@@ -6518,12 +6518,12 @@
       <c r="N34" s="17"/>
     </row>
     <row r="35" spans="1:14" s="52" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="78" t="s">
+      <c r="A35" s="82" t="s">
         <v>60</v>
       </c>
-      <c r="B35" s="78"/>
-      <c r="C35" s="78"/>
-      <c r="D35" s="78"/>
+      <c r="B35" s="82"/>
+      <c r="C35" s="82"/>
+      <c r="D35" s="82"/>
       <c r="E35" s="29">
         <f t="shared" ref="E35:L35" si="1">AVERAGE(E5:E32)</f>
         <v>2.0975477057142849E-2</v>
@@ -6560,17 +6560,17 @@
       <c r="N35" s="58"/>
     </row>
     <row r="37" spans="1:14" s="47" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="81" t="s">
+      <c r="A37" s="79" t="s">
         <v>86</v>
       </c>
-      <c r="B37" s="81"/>
-      <c r="C37" s="81"/>
-      <c r="D37" s="81"/>
-      <c r="E37" s="81"/>
-      <c r="F37" s="81"/>
-      <c r="G37" s="81"/>
-      <c r="H37" s="81"/>
-      <c r="I37" s="81"/>
+      <c r="B37" s="79"/>
+      <c r="C37" s="79"/>
+      <c r="D37" s="79"/>
+      <c r="E37" s="79"/>
+      <c r="F37" s="79"/>
+      <c r="G37" s="79"/>
+      <c r="H37" s="79"/>
+      <c r="I37" s="79"/>
       <c r="J37" s="49"/>
       <c r="K37" s="56"/>
       <c r="L37" s="56"/>
@@ -6596,10 +6596,10 @@
       <c r="B39" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C39" s="70" t="s">
+      <c r="C39" s="76" t="s">
         <v>87</v>
       </c>
-      <c r="D39" s="70" t="s">
+      <c r="D39" s="76" t="s">
         <v>68</v>
       </c>
       <c r="E39" s="11">
@@ -6637,8 +6637,8 @@
       <c r="B40" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C40" s="70"/>
-      <c r="D40" s="70"/>
+      <c r="C40" s="76"/>
+      <c r="D40" s="76"/>
       <c r="E40" s="11">
         <v>1.42857143E-2</v>
       </c>
@@ -6674,8 +6674,8 @@
       <c r="B41" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C41" s="70"/>
-      <c r="D41" s="70"/>
+      <c r="C41" s="76"/>
+      <c r="D41" s="76"/>
       <c r="E41" s="11">
         <v>3.8350910000000001E-4</v>
       </c>
@@ -6711,10 +6711,10 @@
       <c r="B43" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C43" s="70" t="s">
+      <c r="C43" s="76" t="s">
         <v>88</v>
       </c>
-      <c r="D43" s="70" t="s">
+      <c r="D43" s="76" t="s">
         <v>70</v>
       </c>
       <c r="E43" s="11">
@@ -6752,8 +6752,8 @@
       <c r="B44" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C44" s="70"/>
-      <c r="D44" s="70"/>
+      <c r="C44" s="76"/>
+      <c r="D44" s="76"/>
       <c r="E44" s="11">
         <v>2.8475551299999999E-2</v>
       </c>
@@ -6789,8 +6789,8 @@
       <c r="B45" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C45" s="70"/>
-      <c r="D45" s="70"/>
+      <c r="C45" s="76"/>
+      <c r="D45" s="76"/>
       <c r="E45" s="11">
         <v>1.917546E-4</v>
       </c>
@@ -6826,10 +6826,10 @@
       <c r="B47" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C47" s="70" t="s">
+      <c r="C47" s="76" t="s">
         <v>89</v>
       </c>
-      <c r="D47" s="70" t="s">
+      <c r="D47" s="76" t="s">
         <v>81</v>
       </c>
       <c r="E47" s="11">
@@ -6867,8 +6867,8 @@
       <c r="B48" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C48" s="70"/>
-      <c r="D48" s="70"/>
+      <c r="C48" s="76"/>
+      <c r="D48" s="76"/>
       <c r="E48" s="11">
         <v>6.3279002999999997E-3</v>
       </c>
@@ -6904,8 +6904,8 @@
       <c r="B49" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C49" s="70"/>
-      <c r="D49" s="70"/>
+      <c r="C49" s="76"/>
+      <c r="D49" s="76"/>
       <c r="E49" s="11">
         <v>2.876318E-4</v>
       </c>
@@ -6941,10 +6941,10 @@
       <c r="B51" s="63" t="s">
         <v>5</v>
       </c>
-      <c r="C51" s="70" t="s">
+      <c r="C51" s="76" t="s">
         <v>90</v>
       </c>
-      <c r="D51" s="70" t="s">
+      <c r="D51" s="76" t="s">
         <v>79</v>
       </c>
       <c r="E51" s="64">
@@ -6982,8 +6982,8 @@
       <c r="B52" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C52" s="70"/>
-      <c r="D52" s="70"/>
+      <c r="C52" s="76"/>
+      <c r="D52" s="76"/>
       <c r="E52" s="11">
         <v>2.0134227999999998E-3</v>
       </c>
@@ -7019,8 +7019,8 @@
       <c r="B53" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C53" s="70"/>
-      <c r="D53" s="70"/>
+      <c r="C53" s="76"/>
+      <c r="D53" s="76"/>
       <c r="E53" s="11">
         <v>1.917546E-4</v>
       </c>
@@ -7059,10 +7059,10 @@
       <c r="B55" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C55" s="70" t="s">
+      <c r="C55" s="76" t="s">
         <v>91</v>
       </c>
-      <c r="D55" s="70" t="s">
+      <c r="D55" s="76" t="s">
         <v>73</v>
       </c>
       <c r="E55" s="11">
@@ -7100,8 +7100,8 @@
       <c r="B56" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C56" s="70"/>
-      <c r="D56" s="70"/>
+      <c r="C56" s="76"/>
+      <c r="D56" s="76"/>
       <c r="E56" s="11">
         <v>1.9558964500000001E-2</v>
       </c>
@@ -7137,8 +7137,8 @@
       <c r="B57" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C57" s="70"/>
-      <c r="D57" s="70"/>
+      <c r="C57" s="76"/>
+      <c r="D57" s="76"/>
       <c r="E57" s="11">
         <v>0</v>
       </c>
@@ -7174,10 +7174,10 @@
       <c r="B59" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C59" s="70" t="s">
+      <c r="C59" s="76" t="s">
         <v>92</v>
       </c>
-      <c r="D59" s="70" t="s">
+      <c r="D59" s="76" t="s">
         <v>75</v>
       </c>
       <c r="E59" s="11">
@@ -7215,8 +7215,8 @@
       <c r="B60" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C60" s="70"/>
-      <c r="D60" s="70"/>
+      <c r="C60" s="76"/>
+      <c r="D60" s="76"/>
       <c r="E60" s="11">
         <v>4.4103546999999998E-3</v>
       </c>
@@ -7252,8 +7252,8 @@
       <c r="B61" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C61" s="70"/>
-      <c r="D61" s="70"/>
+      <c r="C61" s="76"/>
+      <c r="D61" s="76"/>
       <c r="E61" s="11">
         <v>2.8763183000000002E-3</v>
       </c>
@@ -7289,10 +7289,10 @@
       <c r="B63" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C63" s="70" t="s">
+      <c r="C63" s="76" t="s">
         <v>93</v>
       </c>
-      <c r="D63" s="70" t="s">
+      <c r="D63" s="76" t="s">
         <v>76</v>
       </c>
       <c r="E63" s="11">
@@ -7330,8 +7330,8 @@
       <c r="B64" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C64" s="70"/>
-      <c r="D64" s="70"/>
+      <c r="C64" s="76"/>
+      <c r="D64" s="76"/>
       <c r="E64" s="11">
         <v>8.6289548999999993E-3</v>
       </c>
@@ -7367,8 +7367,8 @@
       <c r="B65" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C65" s="70"/>
-      <c r="D65" s="70"/>
+      <c r="C65" s="76"/>
+      <c r="D65" s="76"/>
       <c r="E65" s="11">
         <v>1.9175455000000001E-3</v>
       </c>
@@ -7398,12 +7398,12 @@
       </c>
     </row>
     <row r="68" spans="1:14" s="14" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="83" t="s">
+      <c r="A68" s="77" t="s">
         <v>59</v>
       </c>
-      <c r="B68" s="83"/>
-      <c r="C68" s="83"/>
-      <c r="D68" s="83"/>
+      <c r="B68" s="77"/>
+      <c r="C68" s="77"/>
+      <c r="D68" s="77"/>
       <c r="E68" s="16">
         <f t="shared" ref="E68:L68" si="2">MAX(E38:E66)</f>
         <v>9.0220517700000002E-2</v>
@@ -7440,12 +7440,12 @@
       <c r="N68" s="17"/>
     </row>
     <row r="69" spans="1:14" s="52" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="78" t="s">
+      <c r="A69" s="82" t="s">
         <v>60</v>
       </c>
-      <c r="B69" s="78"/>
-      <c r="C69" s="78"/>
-      <c r="D69" s="78"/>
+      <c r="B69" s="82"/>
+      <c r="C69" s="82"/>
+      <c r="D69" s="82"/>
       <c r="E69" s="29">
         <f t="shared" ref="E69:L69" si="3">AVERAGE(E39:E66)</f>
         <v>1.7271606619047621E-2</v>
@@ -7482,17 +7482,17 @@
       <c r="N69" s="58"/>
     </row>
     <row r="71" spans="1:14" s="47" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A71" s="81" t="s">
+      <c r="A71" s="79" t="s">
         <v>94</v>
       </c>
-      <c r="B71" s="81"/>
-      <c r="C71" s="81"/>
-      <c r="D71" s="81"/>
-      <c r="E71" s="81"/>
-      <c r="F71" s="81"/>
-      <c r="G71" s="81"/>
-      <c r="H71" s="81"/>
-      <c r="I71" s="81"/>
+      <c r="B71" s="79"/>
+      <c r="C71" s="79"/>
+      <c r="D71" s="79"/>
+      <c r="E71" s="79"/>
+      <c r="F71" s="79"/>
+      <c r="G71" s="79"/>
+      <c r="H71" s="79"/>
+      <c r="I71" s="79"/>
       <c r="J71" s="49"/>
       <c r="K71" s="56"/>
       <c r="L71" s="56"/>
@@ -7518,10 +7518,10 @@
       <c r="B73" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C73" s="70" t="s">
+      <c r="C73" s="76" t="s">
         <v>95</v>
       </c>
-      <c r="D73" s="70" t="s">
+      <c r="D73" s="76" t="s">
         <v>68</v>
       </c>
       <c r="E73" s="11">
@@ -7559,8 +7559,8 @@
       <c r="B74" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C74" s="70"/>
-      <c r="D74" s="70"/>
+      <c r="C74" s="76"/>
+      <c r="D74" s="76"/>
       <c r="E74" s="11">
         <v>8.8139489999999997E-3</v>
       </c>
@@ -7596,8 +7596,8 @@
       <c r="B75" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C75" s="70"/>
-      <c r="D75" s="70"/>
+      <c r="C75" s="76"/>
+      <c r="D75" s="76"/>
       <c r="E75" s="11">
         <v>1.9160760000000001E-4</v>
       </c>
@@ -7633,10 +7633,10 @@
       <c r="B77" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C77" s="70" t="s">
+      <c r="C77" s="76" t="s">
         <v>96</v>
       </c>
-      <c r="D77" s="70" t="s">
+      <c r="D77" s="76" t="s">
         <v>70</v>
       </c>
       <c r="E77" s="11">
@@ -7674,8 +7674,8 @@
       <c r="B78" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C78" s="70"/>
-      <c r="D78" s="70"/>
+      <c r="C78" s="76"/>
+      <c r="D78" s="76"/>
       <c r="E78" s="11">
         <v>3.4489365999999999E-3</v>
       </c>
@@ -7711,8 +7711,8 @@
       <c r="B79" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C79" s="70"/>
-      <c r="D79" s="70"/>
+      <c r="C79" s="76"/>
+      <c r="D79" s="76"/>
       <c r="E79" s="62">
         <v>4.7901900000000002E-4</v>
       </c>
@@ -7748,10 +7748,10 @@
       <c r="B81" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C81" s="70" t="s">
+      <c r="C81" s="76" t="s">
         <v>97</v>
       </c>
-      <c r="D81" s="70" t="s">
+      <c r="D81" s="76" t="s">
         <v>81</v>
       </c>
       <c r="E81" s="11">
@@ -7789,8 +7789,8 @@
       <c r="B82" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C82" s="70"/>
-      <c r="D82" s="70"/>
+      <c r="C82" s="76"/>
+      <c r="D82" s="76"/>
       <c r="E82" s="11">
         <v>4.3111707000000003E-3</v>
       </c>
@@ -7826,8 +7826,8 @@
       <c r="B83" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C83" s="70"/>
-      <c r="D83" s="70"/>
+      <c r="C83" s="76"/>
+      <c r="D83" s="76"/>
       <c r="E83" s="11">
         <v>2.1076835000000001E-3</v>
       </c>
@@ -7863,36 +7863,36 @@
       <c r="B85" s="42" t="s">
         <v>5</v>
       </c>
-      <c r="C85" s="70" t="s">
+      <c r="C85" s="76" t="s">
         <v>98</v>
       </c>
-      <c r="D85" s="70" t="s">
+      <c r="D85" s="76" t="s">
         <v>79</v>
       </c>
-      <c r="E85" s="84">
+      <c r="E85" s="67">
         <v>1.9543973900000001E-2</v>
       </c>
-      <c r="F85" s="84">
+      <c r="F85" s="67">
         <v>8.0475187000000007E-3</v>
       </c>
-      <c r="G85" s="40">
+      <c r="G85" s="67">
         <v>0.7549338954</v>
       </c>
-      <c r="H85" s="84">
+      <c r="H85" s="67">
         <v>0.80678453409999995</v>
       </c>
       <c r="I85" s="40">
         <v>0.68024081950000004</v>
       </c>
-      <c r="J85" s="84">
+      <c r="J85" s="67">
         <f>SUM(E85*1/3,F85*1/3,H85*1/3)</f>
         <v>0.27812534223333329</v>
       </c>
-      <c r="K85" s="40">
+      <c r="K85" s="67">
         <f>SUM(G85*1/2,I85*1/2)</f>
         <v>0.71758735745000002</v>
       </c>
-      <c r="L85" s="84">
+      <c r="L85" s="67">
         <f>SUM(E85*1/5,F85*1/5,G85*1/5,H85*1/5,I85*1/5)</f>
         <v>0.45391014831999998</v>
       </c>
@@ -7904,8 +7904,8 @@
       <c r="B86" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C86" s="70"/>
-      <c r="D86" s="70"/>
+      <c r="C86" s="76"/>
+      <c r="D86" s="76"/>
       <c r="E86" s="11">
         <v>8.6223409999999995E-4</v>
       </c>
@@ -7941,19 +7941,34 @@
       <c r="B87" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C87" s="70"/>
-      <c r="D87" s="70"/>
+      <c r="C87" s="76"/>
+      <c r="D87" s="76"/>
+      <c r="E87" s="11">
+        <v>3.8321520000000002E-4</v>
+      </c>
+      <c r="F87" s="11">
+        <v>2.1076835000000001E-3</v>
+      </c>
+      <c r="G87" s="54">
+        <v>0.78884843839999996</v>
+      </c>
+      <c r="H87" s="11">
+        <v>0.62326305770000001</v>
+      </c>
+      <c r="I87" s="11">
+        <v>0.64865882360000005</v>
+      </c>
       <c r="J87" s="11">
         <f>SUM(E87*1/3,F87*1/3,H87*1/3)</f>
-        <v>0</v>
-      </c>
-      <c r="K87" s="11">
+        <v>0.20858465213333333</v>
+      </c>
+      <c r="K87" s="54">
         <f>SUM(G87*1/2,I87*1/2)</f>
-        <v>0</v>
+        <v>0.718753631</v>
       </c>
       <c r="L87" s="11">
         <f>SUM(E87*1/5,F87*1/5,G87*1/5,H87*1/5,I87*1/5)</f>
-        <v>0</v>
+        <v>0.41265224367999997</v>
       </c>
     </row>
     <row r="88" spans="1:12" x14ac:dyDescent="0.2">
@@ -7966,10 +7981,10 @@
       <c r="B89" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C89" s="70" t="s">
+      <c r="C89" s="76" t="s">
         <v>99</v>
       </c>
-      <c r="D89" s="70" t="s">
+      <c r="D89" s="76" t="s">
         <v>73</v>
       </c>
       <c r="E89" s="11">
@@ -8007,8 +8022,8 @@
       <c r="B90" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C90" s="70"/>
-      <c r="D90" s="70"/>
+      <c r="C90" s="76"/>
+      <c r="D90" s="76"/>
       <c r="E90" s="11">
         <v>1.59034298E-2</v>
       </c>
@@ -8044,8 +8059,8 @@
       <c r="B91" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C91" s="70"/>
-      <c r="D91" s="70"/>
+      <c r="C91" s="76"/>
+      <c r="D91" s="76"/>
       <c r="E91" s="11">
         <v>0</v>
       </c>
@@ -8081,10 +8096,10 @@
       <c r="B93" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C93" s="70" t="s">
+      <c r="C93" s="76" t="s">
         <v>100</v>
       </c>
-      <c r="D93" s="70" t="s">
+      <c r="D93" s="76" t="s">
         <v>75</v>
       </c>
       <c r="E93" s="11">
@@ -8122,8 +8137,8 @@
       <c r="B94" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C94" s="70"/>
-      <c r="D94" s="70"/>
+      <c r="C94" s="76"/>
+      <c r="D94" s="76"/>
       <c r="E94" s="11">
         <v>9.4845755999999996E-3</v>
       </c>
@@ -8159,8 +8174,8 @@
       <c r="B95" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C95" s="70"/>
-      <c r="D95" s="70"/>
+      <c r="C95" s="76"/>
+      <c r="D95" s="76"/>
       <c r="E95" s="11">
         <v>1.9160760000000001E-4</v>
       </c>
@@ -8196,10 +8211,10 @@
       <c r="B97" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C97" s="70" t="s">
+      <c r="C97" s="76" t="s">
         <v>101</v>
       </c>
-      <c r="D97" s="70" t="s">
+      <c r="D97" s="76" t="s">
         <v>76</v>
       </c>
       <c r="E97" s="11">
@@ -8237,8 +8252,8 @@
       <c r="B98" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C98" s="70"/>
-      <c r="D98" s="70"/>
+      <c r="C98" s="76"/>
+      <c r="D98" s="76"/>
       <c r="E98" s="11">
         <v>8.9097528000000002E-3</v>
       </c>
@@ -8274,8 +8289,8 @@
       <c r="B99" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C99" s="70"/>
-      <c r="D99" s="70"/>
+      <c r="C99" s="76"/>
+      <c r="D99" s="76"/>
       <c r="E99" s="11">
         <v>1.6286645000000001E-3</v>
       </c>
@@ -8305,12 +8320,12 @@
       </c>
     </row>
     <row r="102" spans="1:14" s="14" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A102" s="83" t="s">
+      <c r="A102" s="77" t="s">
         <v>59</v>
       </c>
-      <c r="B102" s="83"/>
-      <c r="C102" s="83"/>
-      <c r="D102" s="83"/>
+      <c r="B102" s="77"/>
+      <c r="C102" s="77"/>
+      <c r="D102" s="77"/>
       <c r="E102" s="16">
         <f t="shared" ref="E102:L102" si="4">MAX(E72:E100)</f>
         <v>4.4165548999999998E-2</v>
@@ -8321,7 +8336,7 @@
       </c>
       <c r="G102" s="16">
         <f t="shared" si="4"/>
-        <v>0.7549338954</v>
+        <v>0.78884843839999996</v>
       </c>
       <c r="H102" s="16">
         <f t="shared" si="4"/>
@@ -8337,7 +8352,7 @@
       </c>
       <c r="K102" s="16">
         <f t="shared" si="4"/>
-        <v>0.71758735745000002</v>
+        <v>0.718753631</v>
       </c>
       <c r="L102" s="16">
         <f t="shared" si="4"/>
@@ -8347,49 +8362,89 @@
       <c r="N102" s="17"/>
     </row>
     <row r="103" spans="1:14" s="52" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A103" s="78" t="s">
+      <c r="A103" s="82" t="s">
         <v>60</v>
       </c>
-      <c r="B103" s="78"/>
-      <c r="C103" s="78"/>
-      <c r="D103" s="78"/>
+      <c r="B103" s="82"/>
+      <c r="C103" s="82"/>
+      <c r="D103" s="82"/>
       <c r="E103" s="29">
         <f t="shared" ref="E103:L103" si="5">AVERAGE(E73:E100)</f>
-        <v>1.1309637865E-2</v>
+        <v>1.0789332023809524E-2</v>
       </c>
       <c r="F103" s="29">
         <f t="shared" si="5"/>
-        <v>6.3230504000000003E-3</v>
+        <v>6.1223186428571424E-3</v>
       </c>
       <c r="G103" s="29">
         <f t="shared" si="5"/>
-        <v>0.36849013221499999</v>
+        <v>0.38850719441428572</v>
       </c>
       <c r="H103" s="29">
         <f t="shared" si="5"/>
-        <v>0.59302831553500002</v>
+        <v>0.59446806516190465</v>
       </c>
       <c r="I103" s="29">
         <f t="shared" si="5"/>
-        <v>0.47308509317500003</v>
+        <v>0.481445747004762</v>
       </c>
       <c r="J103" s="29">
         <f t="shared" si="5"/>
-        <v>0.19386063612698415</v>
+        <v>0.20379323860952378</v>
       </c>
       <c r="K103" s="29">
         <f t="shared" si="5"/>
-        <v>0.40075010732857141</v>
+        <v>0.43497647070952389</v>
       </c>
       <c r="L103" s="29">
         <f t="shared" si="5"/>
-        <v>0.27661642460761909</v>
+        <v>0.29626653144952381</v>
       </c>
       <c r="M103" s="29"/>
       <c r="N103" s="58"/>
     </row>
   </sheetData>
   <mergeCells count="51">
+    <mergeCell ref="A103:D103"/>
+    <mergeCell ref="C93:C95"/>
+    <mergeCell ref="D93:D95"/>
+    <mergeCell ref="C97:C99"/>
+    <mergeCell ref="D97:D99"/>
+    <mergeCell ref="A102:D102"/>
+    <mergeCell ref="C81:C83"/>
+    <mergeCell ref="D81:D83"/>
+    <mergeCell ref="C85:C87"/>
+    <mergeCell ref="D85:D87"/>
+    <mergeCell ref="C89:C91"/>
+    <mergeCell ref="D89:D91"/>
+    <mergeCell ref="A69:D69"/>
+    <mergeCell ref="A71:I71"/>
+    <mergeCell ref="C73:C75"/>
+    <mergeCell ref="D73:D75"/>
+    <mergeCell ref="C77:C79"/>
+    <mergeCell ref="D77:D79"/>
+    <mergeCell ref="C59:C61"/>
+    <mergeCell ref="D59:D61"/>
+    <mergeCell ref="C63:C65"/>
+    <mergeCell ref="D63:D65"/>
+    <mergeCell ref="A68:D68"/>
+    <mergeCell ref="C47:C49"/>
+    <mergeCell ref="D47:D49"/>
+    <mergeCell ref="C51:C53"/>
+    <mergeCell ref="D51:D53"/>
+    <mergeCell ref="C55:C57"/>
+    <mergeCell ref="D55:D57"/>
+    <mergeCell ref="A37:I37"/>
+    <mergeCell ref="C39:C41"/>
+    <mergeCell ref="D39:D41"/>
+    <mergeCell ref="C43:C45"/>
+    <mergeCell ref="D43:D45"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="C13:C15"/>
+    <mergeCell ref="D13:D15"/>
+    <mergeCell ref="C29:C31"/>
+    <mergeCell ref="D29:D31"/>
     <mergeCell ref="A3:I3"/>
     <mergeCell ref="C21:C23"/>
     <mergeCell ref="D21:D23"/>
@@ -8401,46 +8456,6 @@
     <mergeCell ref="C9:C11"/>
     <mergeCell ref="D17:D19"/>
     <mergeCell ref="C17:C19"/>
-    <mergeCell ref="A34:D34"/>
-    <mergeCell ref="A35:D35"/>
-    <mergeCell ref="C13:C15"/>
-    <mergeCell ref="D13:D15"/>
-    <mergeCell ref="C29:C31"/>
-    <mergeCell ref="D29:D31"/>
-    <mergeCell ref="A37:I37"/>
-    <mergeCell ref="C39:C41"/>
-    <mergeCell ref="D39:D41"/>
-    <mergeCell ref="C43:C45"/>
-    <mergeCell ref="D43:D45"/>
-    <mergeCell ref="C47:C49"/>
-    <mergeCell ref="D47:D49"/>
-    <mergeCell ref="C51:C53"/>
-    <mergeCell ref="D51:D53"/>
-    <mergeCell ref="C55:C57"/>
-    <mergeCell ref="D55:D57"/>
-    <mergeCell ref="C59:C61"/>
-    <mergeCell ref="D59:D61"/>
-    <mergeCell ref="C63:C65"/>
-    <mergeCell ref="D63:D65"/>
-    <mergeCell ref="A68:D68"/>
-    <mergeCell ref="A69:D69"/>
-    <mergeCell ref="A71:I71"/>
-    <mergeCell ref="C73:C75"/>
-    <mergeCell ref="D73:D75"/>
-    <mergeCell ref="C77:C79"/>
-    <mergeCell ref="D77:D79"/>
-    <mergeCell ref="C81:C83"/>
-    <mergeCell ref="D81:D83"/>
-    <mergeCell ref="C85:C87"/>
-    <mergeCell ref="D85:D87"/>
-    <mergeCell ref="C89:C91"/>
-    <mergeCell ref="D89:D91"/>
-    <mergeCell ref="A103:D103"/>
-    <mergeCell ref="C93:C95"/>
-    <mergeCell ref="D93:D95"/>
-    <mergeCell ref="C97:C99"/>
-    <mergeCell ref="D97:D99"/>
-    <mergeCell ref="A102:D102"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -8500,10 +8515,10 @@
       <c r="B3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="70" t="s">
+      <c r="C3" s="76" t="s">
         <v>107</v>
       </c>
-      <c r="D3" s="70" t="s">
+      <c r="D3" s="76" t="s">
         <v>109</v>
       </c>
       <c r="E3" s="1">
@@ -8533,8 +8548,8 @@
       <c r="B4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="70"/>
-      <c r="D4" s="70"/>
+      <c r="C4" s="76"/>
+      <c r="D4" s="76"/>
       <c r="E4" s="1">
         <v>0.51505273250000005</v>
       </c>
@@ -8551,7 +8566,7 @@
         <v>0.30827067670000002</v>
       </c>
       <c r="J4" s="1">
-        <f t="shared" ref="J4:J12" si="0">G4*1/3+H4*1/3+I4*1/3</f>
+        <f t="shared" ref="J4:J13" si="0">G4*1/3+H4*1/3+I4*1/3</f>
         <v>0.34069669856666668</v>
       </c>
     </row>
@@ -8562,8 +8577,8 @@
       <c r="B5" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="70"/>
-      <c r="D5" s="70"/>
+      <c r="C5" s="76"/>
+      <c r="D5" s="76"/>
       <c r="E5" s="1">
         <v>3.79674017E-2</v>
       </c>
@@ -8594,7 +8609,7 @@
       <c r="C7" s="85" t="s">
         <v>110</v>
       </c>
-      <c r="D7" s="70" t="s">
+      <c r="D7" s="76" t="s">
         <v>111</v>
       </c>
       <c r="E7" s="42">
@@ -8603,13 +8618,13 @@
       <c r="F7" s="42">
         <v>0.89434324070000004</v>
       </c>
-      <c r="G7" s="84">
+      <c r="G7" s="67">
         <v>0.79573876789999998</v>
       </c>
-      <c r="H7" s="84">
+      <c r="H7" s="67">
         <v>0.31020942410000002</v>
       </c>
-      <c r="I7" s="84">
+      <c r="I7" s="67">
         <v>0.14285714290000001</v>
       </c>
       <c r="J7" s="66">
@@ -8625,7 +8640,7 @@
         <v>6</v>
       </c>
       <c r="C8" s="85"/>
-      <c r="D8" s="70"/>
+      <c r="D8" s="76"/>
       <c r="E8" s="1">
         <v>0.27823585810000001</v>
       </c>
@@ -8654,7 +8669,7 @@
         <v>7</v>
       </c>
       <c r="C9" s="85"/>
-      <c r="D9" s="70"/>
+      <c r="D9" s="76"/>
       <c r="E9" s="1">
         <v>2.9146692200000001E-2</v>
       </c>
@@ -8682,10 +8697,10 @@
       <c r="B11" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C11" s="70" t="s">
+      <c r="C11" s="76" t="s">
         <v>112</v>
       </c>
-      <c r="D11" s="70" t="s">
+      <c r="D11" s="76" t="s">
         <v>113</v>
       </c>
       <c r="E11" s="1">
@@ -8715,8 +8730,8 @@
       <c r="B12" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C12" s="70"/>
-      <c r="D12" s="70"/>
+      <c r="C12" s="76"/>
+      <c r="D12" s="76"/>
       <c r="E12" s="1">
         <v>0.42057865490000002</v>
       </c>
@@ -8744,8 +8759,27 @@
       <c r="B13" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C13" s="70"/>
-      <c r="D13" s="70"/>
+      <c r="C13" s="76"/>
+      <c r="D13" s="76"/>
+      <c r="E13" s="1">
+        <v>0.78884843839999996</v>
+      </c>
+      <c r="F13" s="1">
+        <v>0.94194290089999999</v>
+      </c>
+      <c r="G13" s="1">
+        <v>0.95115740739999999</v>
+      </c>
+      <c r="H13" s="1">
+        <v>5.2356021000000003E-3</v>
+      </c>
+      <c r="I13" s="1">
+        <v>2.9629629599999999E-2</v>
+      </c>
+      <c r="J13" s="1">
+        <f t="shared" si="0"/>
+        <v>0.32867421303333333</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="6">

--- a/benchmarking/results/results.xlsx
+++ b/benchmarking/results/results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/deborahdore/Documents/political-debates-graph-analysis/benchmarking/results/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF06695A-C85F-3840-8689-7B3F4DA0C746}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B9E7A9B-A0E9-D64A-B40F-D53CC5E4DD04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="51200" windowHeight="28800" activeTab="5" xr2:uid="{E2EDC037-19C4-FE46-A599-BB595128A04F}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="652" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="654" uniqueCount="133">
   <si>
     <t>MODEL'S TYPE</t>
   </si>
@@ -462,6 +462,12 @@
   </si>
   <si>
     <t>ConvKB</t>
+  </si>
+  <si>
+    <t>BIASED TOWARDS SUPPORT</t>
+  </si>
+  <si>
+    <t>GIVES MORE IMPORTANCE TO THE EQUIVALENT RELATION</t>
   </si>
 </sst>
 </file>
@@ -658,7 +664,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="90">
+  <cellXfs count="91">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -861,26 +867,23 @@
     <xf numFmtId="164" fontId="2" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -888,13 +891,19 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -912,20 +921,20 @@
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1265,46 +1274,46 @@
     <col min="12" max="16384" width="51.33203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="89" customFormat="1" ht="27" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="89" t="s">
+    <row r="1" spans="1:12" s="71" customFormat="1" ht="27" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="71" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="2" spans="1:12" s="86" customFormat="1" ht="66" x14ac:dyDescent="0.2">
-      <c r="A2" s="86" t="s">
+    <row r="2" spans="1:12" s="68" customFormat="1" ht="66" x14ac:dyDescent="0.2">
+      <c r="A2" s="68" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="86" t="s">
+      <c r="B2" s="68" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="87" t="s">
+      <c r="C2" s="69" t="s">
         <v>40</v>
       </c>
-      <c r="D2" s="87" t="s">
+      <c r="D2" s="69" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="87" t="s">
+      <c r="E2" s="69" t="s">
         <v>12</v>
       </c>
-      <c r="F2" s="88" t="s">
+      <c r="F2" s="70" t="s">
         <v>53</v>
       </c>
-      <c r="G2" s="88" t="s">
+      <c r="G2" s="70" t="s">
         <v>54</v>
       </c>
-      <c r="H2" s="88" t="s">
+      <c r="H2" s="70" t="s">
         <v>55</v>
       </c>
-      <c r="I2" s="88" t="s">
+      <c r="I2" s="70" t="s">
         <v>56</v>
       </c>
-      <c r="J2" s="88" t="s">
+      <c r="J2" s="70" t="s">
         <v>82</v>
       </c>
-      <c r="K2" s="87" t="s">
+      <c r="K2" s="69" t="s">
         <v>14</v>
       </c>
-      <c r="L2" s="87"/>
+      <c r="L2" s="69"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
@@ -1313,13 +1322,13 @@
       <c r="B3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="73" t="s">
+      <c r="C3" s="79" t="s">
         <v>41</v>
       </c>
-      <c r="D3" s="72" t="s">
+      <c r="D3" s="76" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="72" t="s">
+      <c r="E3" s="76" t="s">
         <v>13</v>
       </c>
       <c r="F3" s="11">
@@ -1337,7 +1346,7 @@
       <c r="J3" s="11">
         <v>0.52440008120000003</v>
       </c>
-      <c r="K3" s="75" t="s">
+      <c r="K3" s="74" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1348,9 +1357,9 @@
       <c r="B4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="69"/>
-      <c r="D4" s="70"/>
-      <c r="E4" s="70"/>
+      <c r="C4" s="77"/>
+      <c r="D4" s="73"/>
+      <c r="E4" s="73"/>
       <c r="F4" s="11">
         <v>3.9117929099999997E-2</v>
       </c>
@@ -1366,7 +1375,7 @@
       <c r="J4" s="11">
         <v>0.4957882649</v>
       </c>
-      <c r="K4" s="76"/>
+      <c r="K4" s="75"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
@@ -1375,9 +1384,9 @@
       <c r="B5" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="69"/>
-      <c r="D5" s="70"/>
-      <c r="E5" s="70"/>
+      <c r="C5" s="77"/>
+      <c r="D5" s="73"/>
+      <c r="E5" s="73"/>
       <c r="F5" s="11">
         <v>2.1093001000000002E-3</v>
       </c>
@@ -1393,7 +1402,7 @@
       <c r="J5" s="11">
         <v>0.4776301698</v>
       </c>
-      <c r="K5" s="76"/>
+      <c r="K5" s="75"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
@@ -1402,13 +1411,13 @@
       <c r="B7" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="69" t="s">
+      <c r="C7" s="77" t="s">
         <v>42</v>
       </c>
-      <c r="D7" s="70" t="s">
+      <c r="D7" s="73" t="s">
         <v>10</v>
       </c>
-      <c r="E7" s="70" t="s">
+      <c r="E7" s="73" t="s">
         <v>13</v>
       </c>
       <c r="F7" s="11">
@@ -1426,7 +1435,7 @@
       <c r="J7" s="11">
         <v>0.51801477490000003</v>
       </c>
-      <c r="K7" s="76" t="s">
+      <c r="K7" s="75" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1437,9 +1446,9 @@
       <c r="B8" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="69"/>
-      <c r="D8" s="70"/>
-      <c r="E8" s="70"/>
+      <c r="C8" s="77"/>
+      <c r="D8" s="73"/>
+      <c r="E8" s="73"/>
       <c r="F8" s="11">
         <v>3.2094270899999999E-2</v>
       </c>
@@ -1455,7 +1464,7 @@
       <c r="J8" s="11">
         <v>0.50083099880000004</v>
       </c>
-      <c r="K8" s="76"/>
+      <c r="K8" s="75"/>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
@@ -1464,9 +1473,9 @@
       <c r="B9" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="69"/>
-      <c r="D9" s="70"/>
-      <c r="E9" s="70"/>
+      <c r="C9" s="77"/>
+      <c r="D9" s="73"/>
+      <c r="E9" s="73"/>
       <c r="F9" s="11">
         <v>2.8741139999999998E-4</v>
       </c>
@@ -1482,15 +1491,15 @@
       <c r="J9" s="11">
         <v>0.4887305689</v>
       </c>
-      <c r="K9" s="76"/>
+      <c r="K9" s="75"/>
     </row>
     <row r="11" spans="1:12" s="59" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="71" t="s">
+      <c r="A11" s="78" t="s">
         <v>37</v>
       </c>
-      <c r="B11" s="71"/>
-      <c r="C11" s="71"/>
-      <c r="D11" s="71"/>
+      <c r="B11" s="78"/>
+      <c r="C11" s="78"/>
+      <c r="D11" s="78"/>
       <c r="E11" s="60"/>
       <c r="F11" s="61"/>
       <c r="G11" s="61"/>
@@ -1506,13 +1515,13 @@
       <c r="B13" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C13" s="69" t="s">
+      <c r="C13" s="77" t="s">
         <v>43</v>
       </c>
-      <c r="D13" s="70" t="s">
+      <c r="D13" s="73" t="s">
         <v>11</v>
       </c>
-      <c r="E13" s="70" t="s">
+      <c r="E13" s="73" t="s">
         <v>17</v>
       </c>
       <c r="F13" s="11">
@@ -1530,7 +1539,7 @@
       <c r="J13" s="11">
         <v>0.65087326729999995</v>
       </c>
-      <c r="K13" s="76" t="s">
+      <c r="K13" s="75" t="s">
         <v>18</v>
       </c>
     </row>
@@ -1541,9 +1550,9 @@
       <c r="B14" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C14" s="69"/>
-      <c r="D14" s="70"/>
-      <c r="E14" s="70"/>
+      <c r="C14" s="77"/>
+      <c r="D14" s="73"/>
+      <c r="E14" s="73"/>
       <c r="F14" s="11">
         <v>1.0937623800000001E-2</v>
       </c>
@@ -1559,7 +1568,7 @@
       <c r="J14" s="11">
         <v>0.48031703009999999</v>
       </c>
-      <c r="K14" s="76"/>
+      <c r="K14" s="75"/>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
@@ -1568,9 +1577,9 @@
       <c r="B15" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C15" s="69"/>
-      <c r="D15" s="70"/>
-      <c r="E15" s="70"/>
+      <c r="C15" s="77"/>
+      <c r="D15" s="73"/>
+      <c r="E15" s="73"/>
       <c r="F15" s="11">
         <v>2.377744E-4</v>
       </c>
@@ -1586,7 +1595,7 @@
       <c r="J15" s="11">
         <v>0.49770047779999999</v>
       </c>
-      <c r="K15" s="76"/>
+      <c r="K15" s="75"/>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
@@ -1595,13 +1604,13 @@
       <c r="B17" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C17" s="69" t="s">
+      <c r="C17" s="77" t="s">
         <v>44</v>
       </c>
-      <c r="D17" s="70" t="s">
+      <c r="D17" s="73" t="s">
         <v>19</v>
       </c>
-      <c r="E17" s="70" t="s">
+      <c r="E17" s="73" t="s">
         <v>27</v>
       </c>
       <c r="F17" s="11">
@@ -1619,7 +1628,7 @@
       <c r="J17" s="11">
         <v>0.44106115289999998</v>
       </c>
-      <c r="K17" s="76" t="s">
+      <c r="K17" s="75" t="s">
         <v>36</v>
       </c>
     </row>
@@ -1630,9 +1639,9 @@
       <c r="B18" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C18" s="69"/>
-      <c r="D18" s="70"/>
-      <c r="E18" s="70"/>
+      <c r="C18" s="77"/>
+      <c r="D18" s="73"/>
+      <c r="E18" s="73"/>
       <c r="F18" s="11">
         <v>6.6187922000000001E-3</v>
       </c>
@@ -1648,7 +1657,7 @@
       <c r="J18" s="11">
         <v>0.48203358359999998</v>
       </c>
-      <c r="K18" s="76"/>
+      <c r="K18" s="75"/>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
@@ -1657,9 +1666,9 @@
       <c r="B19" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C19" s="69"/>
-      <c r="D19" s="70"/>
-      <c r="E19" s="70"/>
+      <c r="C19" s="77"/>
+      <c r="D19" s="73"/>
+      <c r="E19" s="73"/>
       <c r="F19" s="11">
         <v>1.9467035999999999E-3</v>
       </c>
@@ -1675,7 +1684,7 @@
       <c r="J19" s="11">
         <v>0.31319458500000003</v>
       </c>
-      <c r="K19" s="76"/>
+      <c r="K19" s="75"/>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
@@ -1684,13 +1693,13 @@
       <c r="B21" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C21" s="69" t="s">
+      <c r="C21" s="77" t="s">
         <v>45</v>
       </c>
-      <c r="D21" s="70" t="s">
+      <c r="D21" s="73" t="s">
         <v>20</v>
       </c>
-      <c r="E21" s="70" t="s">
+      <c r="E21" s="73" t="s">
         <v>28</v>
       </c>
       <c r="F21" s="11">
@@ -1708,7 +1717,7 @@
       <c r="J21" s="11">
         <v>0.42558258160000001</v>
       </c>
-      <c r="K21" s="76" t="s">
+      <c r="K21" s="75" t="s">
         <v>35</v>
       </c>
     </row>
@@ -1719,9 +1728,9 @@
       <c r="B22" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C22" s="69"/>
-      <c r="D22" s="70"/>
-      <c r="E22" s="70"/>
+      <c r="C22" s="77"/>
+      <c r="D22" s="73"/>
+      <c r="E22" s="73"/>
       <c r="F22" s="11">
         <v>0.36964094320000002</v>
       </c>
@@ -1737,7 +1746,7 @@
       <c r="J22" s="11">
         <v>0.71370811339999995</v>
       </c>
-      <c r="K22" s="76"/>
+      <c r="K22" s="75"/>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
@@ -1746,9 +1755,9 @@
       <c r="B23" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C23" s="69"/>
-      <c r="D23" s="70"/>
-      <c r="E23" s="70"/>
+      <c r="C23" s="77"/>
+      <c r="D23" s="73"/>
+      <c r="E23" s="73"/>
       <c r="F23" s="11">
         <v>1.786352E-4</v>
       </c>
@@ -1764,7 +1773,7 @@
       <c r="J23" s="11">
         <v>0.35677707139999998</v>
       </c>
-      <c r="K23" s="76"/>
+      <c r="K23" s="75"/>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
@@ -1773,13 +1782,13 @@
       <c r="B25" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C25" s="69" t="s">
+      <c r="C25" s="77" t="s">
         <v>46</v>
       </c>
-      <c r="D25" s="70" t="s">
+      <c r="D25" s="73" t="s">
         <v>21</v>
       </c>
-      <c r="E25" s="70" t="s">
+      <c r="E25" s="73" t="s">
         <v>32</v>
       </c>
       <c r="F25" s="11">
@@ -1805,9 +1814,9 @@
       <c r="B26" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C26" s="69"/>
-      <c r="D26" s="70"/>
-      <c r="E26" s="70"/>
+      <c r="C26" s="77"/>
+      <c r="D26" s="73"/>
+      <c r="E26" s="73"/>
       <c r="F26" s="11">
         <v>2.2257384000000002E-2</v>
       </c>
@@ -1831,9 +1840,9 @@
       <c r="B27" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C27" s="69"/>
-      <c r="D27" s="70"/>
-      <c r="E27" s="70"/>
+      <c r="C27" s="77"/>
+      <c r="D27" s="73"/>
+      <c r="E27" s="73"/>
       <c r="F27" s="11">
         <v>3.9556960000000001E-4</v>
       </c>
@@ -1857,13 +1866,13 @@
       <c r="B29" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C29" s="69" t="s">
+      <c r="C29" s="77" t="s">
         <v>47</v>
       </c>
-      <c r="D29" s="70" t="s">
+      <c r="D29" s="73" t="s">
         <v>22</v>
       </c>
-      <c r="E29" s="70" t="s">
+      <c r="E29" s="73" t="s">
         <v>33</v>
       </c>
       <c r="F29" s="11">
@@ -1889,9 +1898,9 @@
       <c r="B30" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C30" s="69"/>
-      <c r="D30" s="70"/>
-      <c r="E30" s="70"/>
+      <c r="C30" s="77"/>
+      <c r="D30" s="73"/>
+      <c r="E30" s="73"/>
       <c r="F30" s="11">
         <v>1.8442843300000001E-2</v>
       </c>
@@ -1915,9 +1924,9 @@
       <c r="B31" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C31" s="69"/>
-      <c r="D31" s="70"/>
-      <c r="E31" s="70"/>
+      <c r="C31" s="77"/>
+      <c r="D31" s="73"/>
+      <c r="E31" s="73"/>
       <c r="F31" s="11">
         <v>6.9899990000000004E-4</v>
       </c>
@@ -1941,13 +1950,13 @@
       <c r="B33" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C33" s="69" t="s">
+      <c r="C33" s="77" t="s">
         <v>48</v>
       </c>
-      <c r="D33" s="70" t="s">
+      <c r="D33" s="73" t="s">
         <v>23</v>
       </c>
-      <c r="E33" s="70" t="s">
+      <c r="E33" s="73" t="s">
         <v>29</v>
       </c>
       <c r="F33" s="11">
@@ -1973,9 +1982,9 @@
       <c r="B34" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C34" s="69"/>
-      <c r="D34" s="70"/>
-      <c r="E34" s="70"/>
+      <c r="C34" s="77"/>
+      <c r="D34" s="73"/>
+      <c r="E34" s="73"/>
       <c r="F34" s="11">
         <v>4.8571429999999999E-4</v>
       </c>
@@ -1999,9 +2008,9 @@
       <c r="B35" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C35" s="69"/>
-      <c r="D35" s="70"/>
-      <c r="E35" s="70"/>
+      <c r="C35" s="77"/>
+      <c r="D35" s="73"/>
+      <c r="E35" s="73"/>
       <c r="F35" s="11">
         <v>8.5714299999999993E-5</v>
       </c>
@@ -2025,13 +2034,13 @@
       <c r="B37" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C37" s="69" t="s">
+      <c r="C37" s="77" t="s">
         <v>49</v>
       </c>
-      <c r="D37" s="70" t="s">
+      <c r="D37" s="73" t="s">
         <v>24</v>
       </c>
-      <c r="E37" s="70" t="s">
+      <c r="E37" s="73" t="s">
         <v>34</v>
       </c>
       <c r="F37" s="11">
@@ -2057,9 +2066,9 @@
       <c r="B38" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C38" s="69"/>
-      <c r="D38" s="70"/>
-      <c r="E38" s="70"/>
+      <c r="C38" s="77"/>
+      <c r="D38" s="73"/>
+      <c r="E38" s="73"/>
       <c r="F38" s="11">
         <v>0.12567659680000001</v>
       </c>
@@ -2083,9 +2092,9 @@
       <c r="B39" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C39" s="69"/>
-      <c r="D39" s="70"/>
-      <c r="E39" s="70"/>
+      <c r="C39" s="77"/>
+      <c r="D39" s="73"/>
+      <c r="E39" s="73"/>
       <c r="F39" s="11">
         <v>5.4127739999999998E-4</v>
       </c>
@@ -2103,12 +2112,12 @@
       </c>
     </row>
     <row r="41" spans="1:11" s="59" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="71" t="s">
+      <c r="A41" s="78" t="s">
         <v>38</v>
       </c>
-      <c r="B41" s="71"/>
-      <c r="C41" s="71"/>
-      <c r="D41" s="71"/>
+      <c r="B41" s="78"/>
+      <c r="C41" s="78"/>
+      <c r="D41" s="78"/>
       <c r="E41" s="60"/>
       <c r="F41" s="61"/>
       <c r="G41" s="61"/>
@@ -2124,13 +2133,13 @@
       <c r="B43" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C43" s="69" t="s">
+      <c r="C43" s="77" t="s">
         <v>50</v>
       </c>
-      <c r="D43" s="70" t="s">
+      <c r="D43" s="73" t="s">
         <v>25</v>
       </c>
-      <c r="E43" s="70" t="s">
+      <c r="E43" s="73" t="s">
         <v>27</v>
       </c>
       <c r="F43" s="11">
@@ -2148,7 +2157,7 @@
       <c r="J43" s="11">
         <v>0.47978398890000001</v>
       </c>
-      <c r="K43" s="76" t="s">
+      <c r="K43" s="75" t="s">
         <v>30</v>
       </c>
     </row>
@@ -2159,9 +2168,9 @@
       <c r="B44" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C44" s="69"/>
-      <c r="D44" s="70"/>
-      <c r="E44" s="70"/>
+      <c r="C44" s="77"/>
+      <c r="D44" s="73"/>
+      <c r="E44" s="73"/>
       <c r="F44" s="11">
         <v>0.15768715</v>
       </c>
@@ -2177,7 +2186,7 @@
       <c r="J44" s="11">
         <v>0.64265883619999997</v>
       </c>
-      <c r="K44" s="76"/>
+      <c r="K44" s="75"/>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
@@ -2186,9 +2195,9 @@
       <c r="B45" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C45" s="69"/>
-      <c r="D45" s="70"/>
-      <c r="E45" s="70"/>
+      <c r="C45" s="77"/>
+      <c r="D45" s="73"/>
+      <c r="E45" s="73"/>
       <c r="F45" s="11">
         <v>1.5776599999999999E-4</v>
       </c>
@@ -2204,7 +2213,7 @@
       <c r="J45" s="11">
         <v>0.33957444949999999</v>
       </c>
-      <c r="K45" s="76"/>
+      <c r="K45" s="75"/>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A47" s="1" t="s">
@@ -2213,13 +2222,13 @@
       <c r="B47" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C47" s="69" t="s">
+      <c r="C47" s="77" t="s">
         <v>51</v>
       </c>
-      <c r="D47" s="70" t="s">
+      <c r="D47" s="73" t="s">
         <v>26</v>
       </c>
-      <c r="E47" s="70" t="s">
+      <c r="E47" s="73" t="s">
         <v>28</v>
       </c>
       <c r="F47" s="11">
@@ -2237,7 +2246,7 @@
       <c r="J47" s="11">
         <v>0.43650638670000003</v>
       </c>
-      <c r="K47" s="76" t="s">
+      <c r="K47" s="75" t="s">
         <v>31</v>
       </c>
     </row>
@@ -2248,9 +2257,9 @@
       <c r="B48" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C48" s="69"/>
-      <c r="D48" s="70"/>
-      <c r="E48" s="70"/>
+      <c r="C48" s="77"/>
+      <c r="D48" s="73"/>
+      <c r="E48" s="73"/>
       <c r="F48" s="11">
         <v>0.28846457310000001</v>
       </c>
@@ -2266,7 +2275,7 @@
       <c r="J48" s="11">
         <v>0.62979789600000002</v>
       </c>
-      <c r="K48" s="76"/>
+      <c r="K48" s="75"/>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A49" s="1" t="s">
@@ -2275,9 +2284,9 @@
       <c r="B49" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C49" s="69"/>
-      <c r="D49" s="70"/>
-      <c r="E49" s="70"/>
+      <c r="C49" s="77"/>
+      <c r="D49" s="73"/>
+      <c r="E49" s="73"/>
       <c r="F49" s="11">
         <v>2.7615590000000002E-4</v>
       </c>
@@ -2293,7 +2302,7 @@
       <c r="J49" s="11">
         <v>0.39453545410000002</v>
       </c>
-      <c r="K49" s="76"/>
+      <c r="K49" s="75"/>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A51" s="1" t="s">
@@ -2302,13 +2311,13 @@
       <c r="B51" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C51" s="69" t="s">
+      <c r="C51" s="77" t="s">
         <v>52</v>
       </c>
-      <c r="D51" s="70" t="s">
+      <c r="D51" s="73" t="s">
         <v>39</v>
       </c>
-      <c r="E51" s="70" t="s">
+      <c r="E51" s="73" t="s">
         <v>29</v>
       </c>
       <c r="F51" s="11">
@@ -2334,9 +2343,9 @@
       <c r="B52" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C52" s="69"/>
-      <c r="D52" s="70"/>
-      <c r="E52" s="70"/>
+      <c r="C52" s="77"/>
+      <c r="D52" s="73"/>
+      <c r="E52" s="73"/>
       <c r="F52" s="11">
         <v>3.5391416699999997E-2</v>
       </c>
@@ -2360,9 +2369,9 @@
       <c r="B53" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C53" s="69"/>
-      <c r="D53" s="70"/>
-      <c r="E53" s="70"/>
+      <c r="C53" s="77"/>
+      <c r="D53" s="73"/>
+      <c r="E53" s="73"/>
       <c r="F53" s="11">
         <v>9.9344299999999997E-5</v>
       </c>
@@ -2380,12 +2389,12 @@
       </c>
     </row>
     <row r="56" spans="1:11" s="42" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="68" t="s">
+      <c r="A56" s="80" t="s">
         <v>59</v>
       </c>
-      <c r="B56" s="68"/>
-      <c r="C56" s="68"/>
-      <c r="D56" s="68"/>
+      <c r="B56" s="80"/>
+      <c r="C56" s="80"/>
+      <c r="D56" s="80"/>
       <c r="E56" s="39"/>
       <c r="F56" s="40">
         <f>MAX(F3:F53)</f>
@@ -2410,12 +2419,12 @@
       <c r="K56" s="41"/>
     </row>
     <row r="57" spans="1:11" s="46" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="74" t="s">
+      <c r="A57" s="72" t="s">
         <v>60</v>
       </c>
-      <c r="B57" s="74"/>
-      <c r="C57" s="74"/>
-      <c r="D57" s="74"/>
+      <c r="B57" s="72"/>
+      <c r="C57" s="72"/>
+      <c r="D57" s="72"/>
       <c r="E57" s="43"/>
       <c r="F57" s="44">
         <f>AVERAGE(F3:F53)</f>
@@ -2441,6 +2450,38 @@
     </row>
   </sheetData>
   <mergeCells count="48">
+    <mergeCell ref="A56:D56"/>
+    <mergeCell ref="C7:C9"/>
+    <mergeCell ref="C13:C15"/>
+    <mergeCell ref="C17:C19"/>
+    <mergeCell ref="C21:C23"/>
+    <mergeCell ref="C25:C27"/>
+    <mergeCell ref="C51:C53"/>
+    <mergeCell ref="D25:D27"/>
+    <mergeCell ref="D29:D31"/>
+    <mergeCell ref="D33:D35"/>
+    <mergeCell ref="D37:D39"/>
+    <mergeCell ref="D43:D45"/>
+    <mergeCell ref="D47:D49"/>
+    <mergeCell ref="D51:D53"/>
+    <mergeCell ref="A41:D41"/>
+    <mergeCell ref="C47:C49"/>
+    <mergeCell ref="D3:D5"/>
+    <mergeCell ref="D7:D9"/>
+    <mergeCell ref="D13:D15"/>
+    <mergeCell ref="D17:D19"/>
+    <mergeCell ref="D21:D23"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="C3:C5"/>
+    <mergeCell ref="C29:C31"/>
+    <mergeCell ref="C33:C35"/>
+    <mergeCell ref="C37:C39"/>
+    <mergeCell ref="E47:E49"/>
+    <mergeCell ref="E7:E9"/>
+    <mergeCell ref="E13:E15"/>
+    <mergeCell ref="E17:E19"/>
+    <mergeCell ref="E21:E23"/>
+    <mergeCell ref="C43:C45"/>
     <mergeCell ref="A1:XFD1"/>
     <mergeCell ref="A57:D57"/>
     <mergeCell ref="E51:E53"/>
@@ -2457,38 +2498,6 @@
     <mergeCell ref="E37:E39"/>
     <mergeCell ref="E43:E45"/>
     <mergeCell ref="E3:E5"/>
-    <mergeCell ref="E7:E9"/>
-    <mergeCell ref="E13:E15"/>
-    <mergeCell ref="E17:E19"/>
-    <mergeCell ref="E21:E23"/>
-    <mergeCell ref="C43:C45"/>
-    <mergeCell ref="C47:C49"/>
-    <mergeCell ref="C29:C31"/>
-    <mergeCell ref="C33:C35"/>
-    <mergeCell ref="C37:C39"/>
-    <mergeCell ref="E47:E49"/>
-    <mergeCell ref="D3:D5"/>
-    <mergeCell ref="D7:D9"/>
-    <mergeCell ref="D13:D15"/>
-    <mergeCell ref="D17:D19"/>
-    <mergeCell ref="D21:D23"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="C3:C5"/>
-    <mergeCell ref="A56:D56"/>
-    <mergeCell ref="C7:C9"/>
-    <mergeCell ref="C13:C15"/>
-    <mergeCell ref="C17:C19"/>
-    <mergeCell ref="C21:C23"/>
-    <mergeCell ref="C25:C27"/>
-    <mergeCell ref="C51:C53"/>
-    <mergeCell ref="D25:D27"/>
-    <mergeCell ref="D29:D31"/>
-    <mergeCell ref="D33:D35"/>
-    <mergeCell ref="D37:D39"/>
-    <mergeCell ref="D43:D45"/>
-    <mergeCell ref="D47:D49"/>
-    <mergeCell ref="D51:D53"/>
-    <mergeCell ref="A41:D41"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2513,8 +2522,8 @@
     <col min="12" max="16384" width="51.33203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="89" customFormat="1" ht="27" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="89" t="s">
+    <row r="1" spans="1:12" s="71" customFormat="1" ht="27" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="71" t="s">
         <v>116</v>
       </c>
     </row>
@@ -2561,13 +2570,13 @@
       <c r="B3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="73" t="s">
+      <c r="C3" s="79" t="s">
         <v>41</v>
       </c>
-      <c r="D3" s="72" t="s">
+      <c r="D3" s="76" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="72" t="s">
+      <c r="E3" s="76" t="s">
         <v>13</v>
       </c>
       <c r="F3" s="11">
@@ -2585,7 +2594,7 @@
       <c r="J3" s="11">
         <v>0.5008326072</v>
       </c>
-      <c r="K3" s="75" t="s">
+      <c r="K3" s="74" t="s">
         <v>15</v>
       </c>
     </row>
@@ -2596,9 +2605,9 @@
       <c r="B4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="69"/>
-      <c r="D4" s="70"/>
-      <c r="E4" s="70"/>
+      <c r="C4" s="77"/>
+      <c r="D4" s="73"/>
+      <c r="E4" s="73"/>
       <c r="F4" s="11">
         <v>2.8763183099999999E-2</v>
       </c>
@@ -2614,7 +2623,7 @@
       <c r="J4" s="11">
         <v>0.49456959480000001</v>
       </c>
-      <c r="K4" s="76"/>
+      <c r="K4" s="75"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
@@ -2623,9 +2632,9 @@
       <c r="B5" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="69"/>
-      <c r="D5" s="70"/>
-      <c r="E5" s="70"/>
+      <c r="C5" s="77"/>
+      <c r="D5" s="73"/>
+      <c r="E5" s="73"/>
       <c r="F5" s="11">
         <v>5.7526370000000003E-4</v>
       </c>
@@ -2641,7 +2650,7 @@
       <c r="J5" s="11">
         <v>0.46208879800000002</v>
       </c>
-      <c r="K5" s="76"/>
+      <c r="K5" s="75"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="G6" s="11"/>
@@ -2656,13 +2665,13 @@
       <c r="B7" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="69" t="s">
+      <c r="C7" s="77" t="s">
         <v>42</v>
       </c>
-      <c r="D7" s="70" t="s">
+      <c r="D7" s="73" t="s">
         <v>10</v>
       </c>
-      <c r="E7" s="70" t="s">
+      <c r="E7" s="73" t="s">
         <v>13</v>
       </c>
       <c r="F7" s="11">
@@ -2680,7 +2689,7 @@
       <c r="J7" s="11">
         <v>0.50993042769999997</v>
       </c>
-      <c r="K7" s="76" t="s">
+      <c r="K7" s="75" t="s">
         <v>16</v>
       </c>
     </row>
@@ -2691,9 +2700,9 @@
       <c r="B8" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="69"/>
-      <c r="D8" s="70"/>
-      <c r="E8" s="70"/>
+      <c r="C8" s="77"/>
+      <c r="D8" s="73"/>
+      <c r="E8" s="73"/>
       <c r="F8" s="11">
         <v>3.3435524000000001E-2</v>
       </c>
@@ -2709,7 +2718,7 @@
       <c r="J8" s="11">
         <v>0.50392556320000004</v>
       </c>
-      <c r="K8" s="76"/>
+      <c r="K8" s="75"/>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
@@ -2718,9 +2727,9 @@
       <c r="B9" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="69"/>
-      <c r="D9" s="70"/>
-      <c r="E9" s="70"/>
+      <c r="C9" s="77"/>
+      <c r="D9" s="73"/>
+      <c r="E9" s="73"/>
       <c r="F9" s="11">
         <v>3.8321520000000002E-4</v>
       </c>
@@ -2736,7 +2745,7 @@
       <c r="J9" s="11">
         <v>0.47738500210000001</v>
       </c>
-      <c r="K9" s="76"/>
+      <c r="K9" s="75"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="G10" s="11"/>
@@ -2745,12 +2754,12 @@
       <c r="J10" s="11"/>
     </row>
     <row r="11" spans="1:12" s="59" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="71" t="s">
+      <c r="A11" s="78" t="s">
         <v>37</v>
       </c>
-      <c r="B11" s="71"/>
-      <c r="C11" s="71"/>
-      <c r="D11" s="71"/>
+      <c r="B11" s="78"/>
+      <c r="C11" s="78"/>
+      <c r="D11" s="78"/>
       <c r="E11" s="60"/>
       <c r="F11" s="61"/>
       <c r="G11" s="61"/>
@@ -2772,13 +2781,13 @@
       <c r="B13" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C13" s="69" t="s">
+      <c r="C13" s="77" t="s">
         <v>43</v>
       </c>
-      <c r="D13" s="70" t="s">
+      <c r="D13" s="73" t="s">
         <v>11</v>
       </c>
-      <c r="E13" s="70" t="s">
+      <c r="E13" s="73" t="s">
         <v>17</v>
       </c>
       <c r="F13" s="11">
@@ -2796,7 +2805,7 @@
       <c r="J13" s="11">
         <v>0.4966675035</v>
       </c>
-      <c r="K13" s="76" t="s">
+      <c r="K13" s="75" t="s">
         <v>18</v>
       </c>
     </row>
@@ -2807,9 +2816,9 @@
       <c r="B14" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C14" s="69"/>
-      <c r="D14" s="70"/>
-      <c r="E14" s="70"/>
+      <c r="C14" s="77"/>
+      <c r="D14" s="73"/>
+      <c r="E14" s="73"/>
       <c r="F14" s="11">
         <v>2.876318E-4</v>
       </c>
@@ -2825,7 +2834,7 @@
       <c r="J14" s="11">
         <v>0.48225264400000001</v>
       </c>
-      <c r="K14" s="76"/>
+      <c r="K14" s="75"/>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
@@ -2834,9 +2843,9 @@
       <c r="B15" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C15" s="69"/>
-      <c r="D15" s="70"/>
-      <c r="E15" s="70"/>
+      <c r="C15" s="77"/>
+      <c r="D15" s="73"/>
+      <c r="E15" s="73"/>
       <c r="F15" s="11">
         <v>6.7114089999999996E-4</v>
       </c>
@@ -2852,7 +2861,7 @@
       <c r="J15" s="11">
         <v>0.43776818420000002</v>
       </c>
-      <c r="K15" s="76"/>
+      <c r="K15" s="75"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="G16" s="11"/>
@@ -2867,13 +2876,13 @@
       <c r="B17" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C17" s="69" t="s">
+      <c r="C17" s="77" t="s">
         <v>44</v>
       </c>
-      <c r="D17" s="70" t="s">
+      <c r="D17" s="73" t="s">
         <v>19</v>
       </c>
-      <c r="E17" s="70" t="s">
+      <c r="E17" s="73" t="s">
         <v>27</v>
       </c>
       <c r="F17" s="11">
@@ -2891,7 +2900,7 @@
       <c r="J17" s="11">
         <v>0.44130707470000002</v>
       </c>
-      <c r="K17" s="76" t="s">
+      <c r="K17" s="75" t="s">
         <v>36</v>
       </c>
     </row>
@@ -2902,9 +2911,9 @@
       <c r="B18" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C18" s="69"/>
-      <c r="D18" s="70"/>
-      <c r="E18" s="70"/>
+      <c r="C18" s="77"/>
+      <c r="D18" s="73"/>
+      <c r="E18" s="73"/>
       <c r="F18" s="11">
         <v>7.7660593999999998E-3</v>
       </c>
@@ -2920,7 +2929,7 @@
       <c r="J18" s="11">
         <v>0.46778393010000002</v>
       </c>
-      <c r="K18" s="76"/>
+      <c r="K18" s="75"/>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
@@ -2929,9 +2938,9 @@
       <c r="B19" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C19" s="69"/>
-      <c r="D19" s="70"/>
-      <c r="E19" s="70"/>
+      <c r="C19" s="77"/>
+      <c r="D19" s="73"/>
+      <c r="E19" s="73"/>
       <c r="F19" s="11">
         <v>2.876318E-4</v>
       </c>
@@ -2947,7 +2956,7 @@
       <c r="J19" s="11">
         <v>0.46815617929999997</v>
       </c>
-      <c r="K19" s="76"/>
+      <c r="K19" s="75"/>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.2">
       <c r="G20" s="11"/>
@@ -2962,13 +2971,13 @@
       <c r="B21" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C21" s="69" t="s">
+      <c r="C21" s="77" t="s">
         <v>45</v>
       </c>
-      <c r="D21" s="70" t="s">
+      <c r="D21" s="73" t="s">
         <v>20</v>
       </c>
-      <c r="E21" s="70" t="s">
+      <c r="E21" s="73" t="s">
         <v>28</v>
       </c>
       <c r="F21" s="11">
@@ -2986,7 +2995,7 @@
       <c r="J21" s="11">
         <v>0.4434595543</v>
       </c>
-      <c r="K21" s="76" t="s">
+      <c r="K21" s="75" t="s">
         <v>35</v>
       </c>
     </row>
@@ -2997,9 +3006,9 @@
       <c r="B22" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C22" s="69"/>
-      <c r="D22" s="70"/>
-      <c r="E22" s="70"/>
+      <c r="C22" s="77"/>
+      <c r="D22" s="73"/>
+      <c r="E22" s="73"/>
       <c r="F22" s="11">
         <v>5.11025887E-2</v>
       </c>
@@ -3015,7 +3024,7 @@
       <c r="J22" s="11">
         <v>0.46092753450000001</v>
       </c>
-      <c r="K22" s="76"/>
+      <c r="K22" s="75"/>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
@@ -3024,9 +3033,9 @@
       <c r="B23" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C23" s="69"/>
-      <c r="D23" s="70"/>
-      <c r="E23" s="70"/>
+      <c r="C23" s="77"/>
+      <c r="D23" s="73"/>
+      <c r="E23" s="73"/>
       <c r="F23" s="11">
         <v>0</v>
       </c>
@@ -3042,7 +3051,7 @@
       <c r="J23" s="11">
         <v>0.4740446935</v>
       </c>
-      <c r="K23" s="76"/>
+      <c r="K23" s="75"/>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.2">
       <c r="G24" s="11"/>
@@ -3057,13 +3066,13 @@
       <c r="B25" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C25" s="69" t="s">
+      <c r="C25" s="77" t="s">
         <v>46</v>
       </c>
-      <c r="D25" s="70" t="s">
+      <c r="D25" s="73" t="s">
         <v>21</v>
       </c>
-      <c r="E25" s="70" t="s">
+      <c r="E25" s="73" t="s">
         <v>32</v>
       </c>
       <c r="F25" s="11">
@@ -3089,9 +3098,9 @@
       <c r="B26" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C26" s="69"/>
-      <c r="D26" s="70"/>
-      <c r="E26" s="70"/>
+      <c r="C26" s="77"/>
+      <c r="D26" s="73"/>
+      <c r="E26" s="73"/>
       <c r="F26" s="11">
         <v>3.0584851400000002E-2</v>
       </c>
@@ -3115,9 +3124,9 @@
       <c r="B27" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C27" s="69"/>
-      <c r="D27" s="70"/>
-      <c r="E27" s="70"/>
+      <c r="C27" s="77"/>
+      <c r="D27" s="73"/>
+      <c r="E27" s="73"/>
       <c r="F27" s="11">
         <v>6.7114089999999996E-4</v>
       </c>
@@ -3147,13 +3156,13 @@
       <c r="B29" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C29" s="69" t="s">
+      <c r="C29" s="77" t="s">
         <v>47</v>
       </c>
-      <c r="D29" s="70" t="s">
+      <c r="D29" s="73" t="s">
         <v>22</v>
       </c>
-      <c r="E29" s="70" t="s">
+      <c r="E29" s="73" t="s">
         <v>33</v>
       </c>
       <c r="F29" s="11">
@@ -3179,9 +3188,9 @@
       <c r="B30" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C30" s="69"/>
-      <c r="D30" s="70"/>
-      <c r="E30" s="70"/>
+      <c r="C30" s="77"/>
+      <c r="D30" s="73"/>
+      <c r="E30" s="73"/>
       <c r="F30" s="11">
         <v>1.42857143E-2</v>
       </c>
@@ -3205,9 +3214,9 @@
       <c r="B31" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C31" s="69"/>
-      <c r="D31" s="70"/>
-      <c r="E31" s="70"/>
+      <c r="C31" s="77"/>
+      <c r="D31" s="73"/>
+      <c r="E31" s="73"/>
       <c r="F31" s="11">
         <v>3.8350910000000001E-4</v>
       </c>
@@ -3237,13 +3246,13 @@
       <c r="B33" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C33" s="69" t="s">
+      <c r="C33" s="77" t="s">
         <v>48</v>
       </c>
-      <c r="D33" s="70" t="s">
+      <c r="D33" s="73" t="s">
         <v>23</v>
       </c>
-      <c r="E33" s="70" t="s">
+      <c r="E33" s="73" t="s">
         <v>29</v>
       </c>
       <c r="F33" s="11">
@@ -3269,9 +3278,9 @@
       <c r="B34" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C34" s="69"/>
-      <c r="D34" s="70"/>
-      <c r="E34" s="70"/>
+      <c r="C34" s="77"/>
+      <c r="D34" s="73"/>
+      <c r="E34" s="73"/>
       <c r="F34" s="11">
         <v>6.9727237799999994E-2</v>
       </c>
@@ -3295,9 +3304,9 @@
       <c r="B35" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C35" s="69"/>
-      <c r="D35" s="70"/>
-      <c r="E35" s="70"/>
+      <c r="C35" s="77"/>
+      <c r="D35" s="73"/>
+      <c r="E35" s="73"/>
       <c r="F35" s="11">
         <v>2.8812910000000001E-4</v>
       </c>
@@ -3327,13 +3336,13 @@
       <c r="B37" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C37" s="69" t="s">
+      <c r="C37" s="77" t="s">
         <v>49</v>
       </c>
-      <c r="D37" s="70" t="s">
+      <c r="D37" s="73" t="s">
         <v>24</v>
       </c>
-      <c r="E37" s="70" t="s">
+      <c r="E37" s="73" t="s">
         <v>34</v>
       </c>
       <c r="F37" s="11">
@@ -3359,9 +3368,9 @@
       <c r="B38" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C38" s="69"/>
-      <c r="D38" s="70"/>
-      <c r="E38" s="70"/>
+      <c r="C38" s="77"/>
+      <c r="D38" s="73"/>
+      <c r="E38" s="73"/>
       <c r="F38" s="11">
         <v>1.4189837E-2</v>
       </c>
@@ -3385,9 +3394,9 @@
       <c r="B39" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C39" s="69"/>
-      <c r="D39" s="70"/>
-      <c r="E39" s="70"/>
+      <c r="C39" s="77"/>
+      <c r="D39" s="73"/>
+      <c r="E39" s="73"/>
       <c r="F39" s="11">
         <v>2.876318E-4</v>
       </c>
@@ -3411,12 +3420,12 @@
       <c r="J40" s="11"/>
     </row>
     <row r="41" spans="1:11" s="59" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="71" t="s">
+      <c r="A41" s="78" t="s">
         <v>38</v>
       </c>
-      <c r="B41" s="71"/>
-      <c r="C41" s="71"/>
-      <c r="D41" s="71"/>
+      <c r="B41" s="78"/>
+      <c r="C41" s="78"/>
+      <c r="D41" s="78"/>
       <c r="E41" s="60"/>
       <c r="F41" s="61"/>
       <c r="G41" s="61"/>
@@ -3438,13 +3447,13 @@
       <c r="B43" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C43" s="69" t="s">
+      <c r="C43" s="77" t="s">
         <v>50</v>
       </c>
-      <c r="D43" s="70" t="s">
+      <c r="D43" s="73" t="s">
         <v>25</v>
       </c>
-      <c r="E43" s="70" t="s">
+      <c r="E43" s="73" t="s">
         <v>27</v>
       </c>
       <c r="F43" s="11">
@@ -3462,7 +3471,7 @@
       <c r="J43" s="11">
         <v>0.4587482034</v>
       </c>
-      <c r="K43" s="76" t="s">
+      <c r="K43" s="75" t="s">
         <v>30</v>
       </c>
     </row>
@@ -3473,9 +3482,9 @@
       <c r="B44" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C44" s="69"/>
-      <c r="D44" s="70"/>
-      <c r="E44" s="70"/>
+      <c r="C44" s="77"/>
+      <c r="D44" s="73"/>
+      <c r="E44" s="73"/>
       <c r="F44" s="11">
         <v>1.34125311E-2</v>
       </c>
@@ -3491,7 +3500,7 @@
       <c r="J44" s="11">
         <v>0.46907909489999999</v>
       </c>
-      <c r="K44" s="76"/>
+      <c r="K44" s="75"/>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
@@ -3500,9 +3509,9 @@
       <c r="B45" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C45" s="69"/>
-      <c r="D45" s="70"/>
-      <c r="E45" s="70"/>
+      <c r="C45" s="77"/>
+      <c r="D45" s="73"/>
+      <c r="E45" s="73"/>
       <c r="F45" s="11">
         <v>8.6223409999999995E-4</v>
       </c>
@@ -3518,7 +3527,7 @@
       <c r="J45" s="11">
         <v>0.49390839069999998</v>
       </c>
-      <c r="K45" s="76"/>
+      <c r="K45" s="75"/>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.2">
       <c r="G46" s="11"/>
@@ -3533,13 +3542,13 @@
       <c r="B47" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C47" s="69" t="s">
+      <c r="C47" s="77" t="s">
         <v>51</v>
       </c>
-      <c r="D47" s="70" t="s">
+      <c r="D47" s="73" t="s">
         <v>26</v>
       </c>
-      <c r="E47" s="70" t="s">
+      <c r="E47" s="73" t="s">
         <v>28</v>
       </c>
       <c r="F47" s="11">
@@ -3557,7 +3566,7 @@
       <c r="J47" s="11">
         <v>0.45388746419999998</v>
       </c>
-      <c r="K47" s="76" t="s">
+      <c r="K47" s="75" t="s">
         <v>31</v>
       </c>
     </row>
@@ -3568,9 +3577,9 @@
       <c r="B48" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C48" s="69"/>
-      <c r="D48" s="70"/>
-      <c r="E48" s="70"/>
+      <c r="C48" s="77"/>
+      <c r="D48" s="73"/>
+      <c r="E48" s="73"/>
       <c r="F48" s="11">
         <v>4.3303314799999999E-2</v>
       </c>
@@ -3586,7 +3595,7 @@
       <c r="J48" s="11">
         <v>0.45908136910000003</v>
       </c>
-      <c r="K48" s="76"/>
+      <c r="K48" s="75"/>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A49" s="1" t="s">
@@ -3595,9 +3604,9 @@
       <c r="B49" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C49" s="69"/>
-      <c r="D49" s="70"/>
-      <c r="E49" s="70"/>
+      <c r="C49" s="77"/>
+      <c r="D49" s="73"/>
+      <c r="E49" s="73"/>
       <c r="F49" s="11">
         <v>9.5803800000000006E-5</v>
       </c>
@@ -3613,7 +3622,7 @@
       <c r="J49" s="11">
         <v>0.478579698</v>
       </c>
-      <c r="K49" s="76"/>
+      <c r="K49" s="75"/>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.2">
       <c r="G50" s="11"/>
@@ -3628,13 +3637,13 @@
       <c r="B51" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C51" s="69" t="s">
+      <c r="C51" s="77" t="s">
         <v>52</v>
       </c>
-      <c r="D51" s="70" t="s">
+      <c r="D51" s="73" t="s">
         <v>39</v>
       </c>
-      <c r="E51" s="70" t="s">
+      <c r="E51" s="73" t="s">
         <v>29</v>
       </c>
       <c r="F51" s="11">
@@ -3660,9 +3669,9 @@
       <c r="B52" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C52" s="69"/>
-      <c r="D52" s="70"/>
-      <c r="E52" s="70"/>
+      <c r="C52" s="77"/>
+      <c r="D52" s="73"/>
+      <c r="E52" s="73"/>
       <c r="F52" s="11">
         <v>8.8139489999999997E-3</v>
       </c>
@@ -3686,9 +3695,9 @@
       <c r="B53" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C53" s="69"/>
-      <c r="D53" s="70"/>
-      <c r="E53" s="70"/>
+      <c r="C53" s="77"/>
+      <c r="D53" s="73"/>
+      <c r="E53" s="73"/>
       <c r="F53" s="11">
         <v>1.9160760000000001E-4</v>
       </c>
@@ -3718,12 +3727,12 @@
       <c r="J55" s="11"/>
     </row>
     <row r="56" spans="1:11" s="42" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="68" t="s">
+      <c r="A56" s="80" t="s">
         <v>59</v>
       </c>
-      <c r="B56" s="68"/>
-      <c r="C56" s="68"/>
-      <c r="D56" s="68"/>
+      <c r="B56" s="80"/>
+      <c r="C56" s="80"/>
+      <c r="D56" s="80"/>
       <c r="E56" s="39"/>
       <c r="F56" s="40">
         <f>MAX(F3:F53)</f>
@@ -3748,12 +3757,12 @@
       <c r="K56" s="41"/>
     </row>
     <row r="57" spans="1:11" s="46" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="74" t="s">
+      <c r="A57" s="72" t="s">
         <v>60</v>
       </c>
-      <c r="B57" s="74"/>
-      <c r="C57" s="74"/>
-      <c r="D57" s="74"/>
+      <c r="B57" s="72"/>
+      <c r="C57" s="72"/>
+      <c r="D57" s="72"/>
       <c r="E57" s="43"/>
       <c r="F57" s="44">
         <f>AVERAGE(F3:F53)</f>
@@ -3779,23 +3788,21 @@
     </row>
   </sheetData>
   <mergeCells count="48">
-    <mergeCell ref="A1:XFD1"/>
-    <mergeCell ref="A57:D57"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="C13:C15"/>
-    <mergeCell ref="D13:D15"/>
-    <mergeCell ref="E13:E15"/>
-    <mergeCell ref="C25:C27"/>
-    <mergeCell ref="D25:D27"/>
-    <mergeCell ref="E25:E27"/>
-    <mergeCell ref="C29:C31"/>
-    <mergeCell ref="D29:D31"/>
-    <mergeCell ref="E29:E31"/>
-    <mergeCell ref="C33:C35"/>
-    <mergeCell ref="D33:D35"/>
-    <mergeCell ref="E33:E35"/>
-    <mergeCell ref="C51:C53"/>
+    <mergeCell ref="A56:D56"/>
+    <mergeCell ref="E51:E53"/>
     <mergeCell ref="D51:D53"/>
+    <mergeCell ref="K43:K45"/>
+    <mergeCell ref="C47:C49"/>
+    <mergeCell ref="D47:D49"/>
+    <mergeCell ref="E47:E49"/>
+    <mergeCell ref="K47:K49"/>
+    <mergeCell ref="C37:C39"/>
+    <mergeCell ref="D37:D39"/>
+    <mergeCell ref="E37:E39"/>
+    <mergeCell ref="A41:D41"/>
+    <mergeCell ref="C43:C45"/>
+    <mergeCell ref="D43:D45"/>
+    <mergeCell ref="E43:E45"/>
     <mergeCell ref="C3:C5"/>
     <mergeCell ref="D3:D5"/>
     <mergeCell ref="E3:E5"/>
@@ -3813,20 +3820,22 @@
     <mergeCell ref="D17:D19"/>
     <mergeCell ref="E17:E19"/>
     <mergeCell ref="K17:K19"/>
-    <mergeCell ref="C37:C39"/>
-    <mergeCell ref="D37:D39"/>
-    <mergeCell ref="E37:E39"/>
-    <mergeCell ref="A41:D41"/>
-    <mergeCell ref="C43:C45"/>
-    <mergeCell ref="D43:D45"/>
-    <mergeCell ref="E43:E45"/>
-    <mergeCell ref="A56:D56"/>
-    <mergeCell ref="K43:K45"/>
-    <mergeCell ref="C47:C49"/>
-    <mergeCell ref="D47:D49"/>
-    <mergeCell ref="E47:E49"/>
-    <mergeCell ref="K47:K49"/>
-    <mergeCell ref="E51:E53"/>
+    <mergeCell ref="A1:XFD1"/>
+    <mergeCell ref="A57:D57"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="C13:C15"/>
+    <mergeCell ref="D13:D15"/>
+    <mergeCell ref="E13:E15"/>
+    <mergeCell ref="C25:C27"/>
+    <mergeCell ref="D25:D27"/>
+    <mergeCell ref="E25:E27"/>
+    <mergeCell ref="C29:C31"/>
+    <mergeCell ref="D29:D31"/>
+    <mergeCell ref="E29:E31"/>
+    <mergeCell ref="C33:C35"/>
+    <mergeCell ref="D33:D35"/>
+    <mergeCell ref="E33:E35"/>
+    <mergeCell ref="C51:C53"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -3855,8 +3864,8 @@
     <col min="15" max="16384" width="51.33203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" s="89" customFormat="1" ht="27" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="89" t="s">
+    <row r="1" spans="1:15" s="71" customFormat="1" ht="27" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="71" t="s">
         <v>117</v>
       </c>
     </row>
@@ -3912,13 +3921,13 @@
       <c r="B3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="73" t="s">
+      <c r="C3" s="79" t="s">
         <v>41</v>
       </c>
-      <c r="D3" s="72" t="s">
+      <c r="D3" s="76" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="72" t="s">
+      <c r="E3" s="76" t="s">
         <v>13</v>
       </c>
       <c r="F3" s="11">
@@ -3948,7 +3957,7 @@
         <f>SUM(F3*1/5,G3*1/5,H3*1/5,I3*1/5,J3*1/5)</f>
         <v>0.29130368856</v>
       </c>
-      <c r="N3" s="75" t="s">
+      <c r="N3" s="74" t="s">
         <v>15</v>
       </c>
     </row>
@@ -3959,9 +3968,9 @@
       <c r="B4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="69"/>
-      <c r="D4" s="70"/>
-      <c r="E4" s="70"/>
+      <c r="C4" s="77"/>
+      <c r="D4" s="73"/>
+      <c r="E4" s="73"/>
       <c r="F4" s="11">
         <v>2.3969319E-3</v>
       </c>
@@ -3989,7 +3998,7 @@
         <f>SUM(F4*1/5,G4*1/5,H4*1/5,I4*1/5,J4*1/5)</f>
         <v>0.26225518991999996</v>
       </c>
-      <c r="N4" s="76"/>
+      <c r="N4" s="75"/>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
@@ -3998,9 +4007,9 @@
       <c r="B5" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="69"/>
-      <c r="D5" s="70"/>
-      <c r="E5" s="70"/>
+      <c r="C5" s="77"/>
+      <c r="D5" s="73"/>
+      <c r="E5" s="73"/>
       <c r="F5" s="11">
         <v>6.5867689399999999E-2</v>
       </c>
@@ -4028,7 +4037,7 @@
         <f>SUM(F5*1/5,G5*1/5,H5*1/5,I5*1/5,J5*1/5)</f>
         <v>0.29107094631999997</v>
       </c>
-      <c r="N5" s="76"/>
+      <c r="N5" s="75"/>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
@@ -4037,13 +4046,13 @@
       <c r="B7" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="69" t="s">
+      <c r="C7" s="77" t="s">
         <v>42</v>
       </c>
-      <c r="D7" s="70" t="s">
+      <c r="D7" s="73" t="s">
         <v>10</v>
       </c>
-      <c r="E7" s="70" t="s">
+      <c r="E7" s="73" t="s">
         <v>13</v>
       </c>
       <c r="F7" s="11">
@@ -4073,7 +4082,7 @@
         <f>SUM(F7*1/5,G7*1/5,H7*1/5,I7*1/5,J7*1/5)</f>
         <v>0.29438649154000002</v>
       </c>
-      <c r="N7" s="76" t="s">
+      <c r="N7" s="75" t="s">
         <v>16</v>
       </c>
     </row>
@@ -4084,9 +4093,9 @@
       <c r="B8" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="69"/>
-      <c r="D8" s="70"/>
-      <c r="E8" s="70"/>
+      <c r="C8" s="77"/>
+      <c r="D8" s="73"/>
+      <c r="E8" s="73"/>
       <c r="F8" s="11">
         <v>1.3604138700000001E-2</v>
       </c>
@@ -4114,7 +4123,7 @@
         <f>SUM(F8*1/5,G8*1/5,H8*1/5,I8*1/5,J8*1/5)</f>
         <v>0.27579129901999999</v>
       </c>
-      <c r="N8" s="76"/>
+      <c r="N8" s="75"/>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
@@ -4123,9 +4132,9 @@
       <c r="B9" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="69"/>
-      <c r="D9" s="70"/>
-      <c r="E9" s="70"/>
+      <c r="C9" s="77"/>
+      <c r="D9" s="73"/>
+      <c r="E9" s="73"/>
       <c r="F9" s="11">
         <v>3.8321517499999999E-2</v>
       </c>
@@ -4153,15 +4162,15 @@
         <f>SUM(F9*1/5,G9*1/5,H9*1/5,I9*1/5,J9*1/5)</f>
         <v>0.2717815321</v>
       </c>
-      <c r="N9" s="76"/>
+      <c r="N9" s="75"/>
     </row>
     <row r="11" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="78" t="s">
+      <c r="A11" s="87" t="s">
         <v>37</v>
       </c>
-      <c r="B11" s="78"/>
-      <c r="C11" s="78"/>
-      <c r="D11" s="78"/>
+      <c r="B11" s="87"/>
+      <c r="C11" s="87"/>
+      <c r="D11" s="87"/>
       <c r="E11" s="5"/>
       <c r="F11" s="13"/>
       <c r="G11" s="13"/>
@@ -4180,13 +4189,13 @@
       <c r="B13" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C13" s="69" t="s">
+      <c r="C13" s="77" t="s">
         <v>43</v>
       </c>
-      <c r="D13" s="70" t="s">
+      <c r="D13" s="73" t="s">
         <v>11</v>
       </c>
-      <c r="E13" s="70" t="s">
+      <c r="E13" s="73" t="s">
         <v>17</v>
       </c>
       <c r="F13" s="11">
@@ -4216,7 +4225,7 @@
         <f>SUM(F13*1/5,G13*1/5,H13*1/5,I13*1/5,J13*1/5)</f>
         <v>0.33641501256</v>
       </c>
-      <c r="N13" s="76" t="s">
+      <c r="N13" s="75" t="s">
         <v>18</v>
       </c>
     </row>
@@ -4227,9 +4236,9 @@
       <c r="B14" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C14" s="69"/>
-      <c r="D14" s="70"/>
-      <c r="E14" s="70"/>
+      <c r="C14" s="77"/>
+      <c r="D14" s="73"/>
+      <c r="E14" s="73"/>
       <c r="F14" s="11">
         <v>7.9194630899999993E-2</v>
       </c>
@@ -4257,7 +4266,7 @@
         <f>SUM(F14*1/5,G14*1/5,H14*1/5,I14*1/5,J14*1/5)</f>
         <v>0.26691102733999994</v>
       </c>
-      <c r="N14" s="76"/>
+      <c r="N14" s="75"/>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
@@ -4266,9 +4275,9 @@
       <c r="B15" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C15" s="69"/>
-      <c r="D15" s="70"/>
-      <c r="E15" s="70"/>
+      <c r="C15" s="77"/>
+      <c r="D15" s="73"/>
+      <c r="E15" s="73"/>
       <c r="F15" s="11">
         <v>3.8350910000000001E-4</v>
       </c>
@@ -4296,7 +4305,7 @@
         <f>SUM(F15*1/5,G15*1/5,H15*1/5,I15*1/5,J15*1/5)</f>
         <v>0.22330577798000001</v>
       </c>
-      <c r="N15" s="76"/>
+      <c r="N15" s="75"/>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
@@ -4305,13 +4314,13 @@
       <c r="B17" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C17" s="69" t="s">
+      <c r="C17" s="77" t="s">
         <v>44</v>
       </c>
-      <c r="D17" s="70" t="s">
+      <c r="D17" s="73" t="s">
         <v>19</v>
       </c>
-      <c r="E17" s="70" t="s">
+      <c r="E17" s="73" t="s">
         <v>27</v>
       </c>
       <c r="F17" s="11">
@@ -4341,7 +4350,7 @@
         <f>SUM(F17*1/5,G17*1/5,H17*1/5,I17*1/5,J17*1/5)</f>
         <v>0.34767161497999999</v>
       </c>
-      <c r="N17" s="76" t="s">
+      <c r="N17" s="75" t="s">
         <v>36</v>
       </c>
     </row>
@@ -4352,9 +4361,9 @@
       <c r="B18" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C18" s="69"/>
-      <c r="D18" s="70"/>
-      <c r="E18" s="70"/>
+      <c r="C18" s="77"/>
+      <c r="D18" s="73"/>
+      <c r="E18" s="73"/>
       <c r="F18" s="11">
         <v>3.7296260800000001E-2</v>
       </c>
@@ -4382,7 +4391,7 @@
         <f>SUM(F18*1/5,G18*1/5,H18*1/5,I18*1/5,J18*1/5)</f>
         <v>0.33628517706000005</v>
       </c>
-      <c r="N18" s="76"/>
+      <c r="N18" s="75"/>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
@@ -4391,9 +4400,9 @@
       <c r="B19" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C19" s="69"/>
-      <c r="D19" s="70"/>
-      <c r="E19" s="70"/>
+      <c r="C19" s="77"/>
+      <c r="D19" s="73"/>
+      <c r="E19" s="73"/>
       <c r="F19" s="11">
         <v>1.0546500000000001E-3</v>
       </c>
@@ -4421,7 +4430,7 @@
         <f>SUM(F19*1/5,G19*1/5,H19*1/5,I19*1/5,J19*1/5)</f>
         <v>0.20704430204000002</v>
       </c>
-      <c r="N19" s="76"/>
+      <c r="N19" s="75"/>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
@@ -4430,13 +4439,13 @@
       <c r="B21" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C21" s="69" t="s">
+      <c r="C21" s="77" t="s">
         <v>45</v>
       </c>
-      <c r="D21" s="70" t="s">
+      <c r="D21" s="73" t="s">
         <v>20</v>
       </c>
-      <c r="E21" s="70" t="s">
+      <c r="E21" s="73" t="s">
         <v>28</v>
       </c>
       <c r="F21" s="11">
@@ -4466,7 +4475,7 @@
         <f>SUM(F21*1/5,G21*1/5,H21*1/5,I21*1/5,J21*1/5)</f>
         <v>0.31181358595999997</v>
       </c>
-      <c r="N21" s="76" t="s">
+      <c r="N21" s="75" t="s">
         <v>35</v>
       </c>
     </row>
@@ -4477,9 +4486,9 @@
       <c r="B22" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C22" s="69"/>
-      <c r="D22" s="70"/>
-      <c r="E22" s="70"/>
+      <c r="C22" s="77"/>
+      <c r="D22" s="73"/>
+      <c r="E22" s="73"/>
       <c r="F22" s="11">
         <v>1.05465005E-2</v>
       </c>
@@ -4507,7 +4516,7 @@
         <f>SUM(F22*1/5,G22*1/5,H22*1/5,I22*1/5,J22*1/5)</f>
         <v>0.29879759264</v>
       </c>
-      <c r="N22" s="76"/>
+      <c r="N22" s="75"/>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
@@ -4516,9 +4525,9 @@
       <c r="B23" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C23" s="69"/>
-      <c r="D23" s="70"/>
-      <c r="E23" s="70"/>
+      <c r="C23" s="77"/>
+      <c r="D23" s="73"/>
+      <c r="E23" s="73"/>
       <c r="F23" s="11">
         <v>0</v>
       </c>
@@ -4546,7 +4555,7 @@
         <f>SUM(F23*1/5,G23*1/5,H23*1/5,I23*1/5,J23*1/5)</f>
         <v>0.22541820497999998</v>
       </c>
-      <c r="N23" s="76"/>
+      <c r="N23" s="75"/>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
@@ -4555,13 +4564,13 @@
       <c r="B25" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C25" s="69" t="s">
+      <c r="C25" s="77" t="s">
         <v>46</v>
       </c>
-      <c r="D25" s="70" t="s">
+      <c r="D25" s="73" t="s">
         <v>21</v>
       </c>
-      <c r="E25" s="70" t="s">
+      <c r="E25" s="73" t="s">
         <v>32</v>
       </c>
       <c r="F25" s="11">
@@ -4599,9 +4608,9 @@
       <c r="B26" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C26" s="69"/>
-      <c r="D26" s="70"/>
-      <c r="E26" s="70"/>
+      <c r="C26" s="77"/>
+      <c r="D26" s="73"/>
+      <c r="E26" s="73"/>
       <c r="F26" s="11">
         <v>2.7229146700000002E-2</v>
       </c>
@@ -4637,9 +4646,9 @@
       <c r="B27" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C27" s="69"/>
-      <c r="D27" s="70"/>
-      <c r="E27" s="70"/>
+      <c r="C27" s="77"/>
+      <c r="D27" s="73"/>
+      <c r="E27" s="73"/>
       <c r="F27" s="11">
         <v>3.8350910000000001E-4</v>
       </c>
@@ -4675,13 +4684,13 @@
       <c r="B29" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C29" s="69" t="s">
+      <c r="C29" s="77" t="s">
         <v>47</v>
       </c>
-      <c r="D29" s="70" t="s">
+      <c r="D29" s="73" t="s">
         <v>22</v>
       </c>
-      <c r="E29" s="70" t="s">
+      <c r="E29" s="73" t="s">
         <v>33</v>
       </c>
       <c r="F29" s="11">
@@ -4719,9 +4728,9 @@
       <c r="B30" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C30" s="69"/>
-      <c r="D30" s="70"/>
-      <c r="E30" s="70"/>
+      <c r="C30" s="77"/>
+      <c r="D30" s="73"/>
+      <c r="E30" s="73"/>
       <c r="F30" s="11">
         <v>2.8475551299999999E-2</v>
       </c>
@@ -4757,9 +4766,9 @@
       <c r="B31" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C31" s="69"/>
-      <c r="D31" s="70"/>
-      <c r="E31" s="70"/>
+      <c r="C31" s="77"/>
+      <c r="D31" s="73"/>
+      <c r="E31" s="73"/>
       <c r="F31" s="11">
         <v>1.917546E-4</v>
       </c>
@@ -4795,13 +4804,13 @@
       <c r="B33" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C33" s="69" t="s">
+      <c r="C33" s="77" t="s">
         <v>48</v>
       </c>
-      <c r="D33" s="70" t="s">
+      <c r="D33" s="73" t="s">
         <v>23</v>
       </c>
-      <c r="E33" s="70" t="s">
+      <c r="E33" s="73" t="s">
         <v>29</v>
       </c>
       <c r="F33" s="11">
@@ -4839,9 +4848,9 @@
       <c r="B34" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C34" s="69"/>
-      <c r="D34" s="70"/>
-      <c r="E34" s="70"/>
+      <c r="C34" s="77"/>
+      <c r="D34" s="73"/>
+      <c r="E34" s="73"/>
       <c r="F34" s="11">
         <v>2.4010757000000001E-3</v>
       </c>
@@ -4877,9 +4886,9 @@
       <c r="B35" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C35" s="69"/>
-      <c r="D35" s="70"/>
-      <c r="E35" s="70"/>
+      <c r="C35" s="77"/>
+      <c r="D35" s="73"/>
+      <c r="E35" s="73"/>
       <c r="F35" s="11">
         <v>0</v>
       </c>
@@ -4915,13 +4924,13 @@
       <c r="B37" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C37" s="69" t="s">
+      <c r="C37" s="77" t="s">
         <v>49</v>
       </c>
-      <c r="D37" s="70" t="s">
+      <c r="D37" s="73" t="s">
         <v>24</v>
       </c>
-      <c r="E37" s="70" t="s">
+      <c r="E37" s="73" t="s">
         <v>34</v>
       </c>
       <c r="F37" s="11">
@@ -4959,9 +4968,9 @@
       <c r="B38" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C38" s="69"/>
-      <c r="D38" s="70"/>
-      <c r="E38" s="70"/>
+      <c r="C38" s="77"/>
+      <c r="D38" s="73"/>
+      <c r="E38" s="73"/>
       <c r="F38" s="11">
         <v>5.9443912000000003E-3</v>
       </c>
@@ -4997,9 +5006,9 @@
       <c r="B39" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C39" s="69"/>
-      <c r="D39" s="70"/>
-      <c r="E39" s="70"/>
+      <c r="C39" s="77"/>
+      <c r="D39" s="73"/>
+      <c r="E39" s="73"/>
       <c r="F39" s="11">
         <v>1.917546E-4</v>
       </c>
@@ -5029,12 +5038,12 @@
       </c>
     </row>
     <row r="41" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="78" t="s">
+      <c r="A41" s="87" t="s">
         <v>38</v>
       </c>
-      <c r="B41" s="78"/>
-      <c r="C41" s="78"/>
-      <c r="D41" s="78"/>
+      <c r="B41" s="87"/>
+      <c r="C41" s="87"/>
+      <c r="D41" s="87"/>
       <c r="E41" s="5"/>
       <c r="F41" s="13"/>
       <c r="G41" s="13"/>
@@ -5053,13 +5062,13 @@
       <c r="B43" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C43" s="69" t="s">
+      <c r="C43" s="77" t="s">
         <v>50</v>
       </c>
-      <c r="D43" s="70" t="s">
+      <c r="D43" s="73" t="s">
         <v>25</v>
       </c>
-      <c r="E43" s="70" t="s">
+      <c r="E43" s="73" t="s">
         <v>27</v>
       </c>
       <c r="F43" s="11">
@@ -5089,7 +5098,7 @@
         <f>SUM(F43*1/5,G43*1/5,H43*1/5,I43*1/5,J43*1/5)</f>
         <v>0.32911788728000002</v>
       </c>
-      <c r="N43" s="76" t="s">
+      <c r="N43" s="75" t="s">
         <v>30</v>
       </c>
     </row>
@@ -5100,9 +5109,9 @@
       <c r="B44" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C44" s="69"/>
-      <c r="D44" s="70"/>
-      <c r="E44" s="70"/>
+      <c r="C44" s="77"/>
+      <c r="D44" s="73"/>
+      <c r="E44" s="73"/>
       <c r="F44" s="11">
         <v>1.59034298E-2</v>
       </c>
@@ -5130,7 +5139,7 @@
         <f>SUM(F44*1/5,G44*1/5,H44*1/5,I44*1/5,J44*1/5)</f>
         <v>0.33481998118</v>
       </c>
-      <c r="N44" s="76"/>
+      <c r="N44" s="75"/>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
@@ -5139,9 +5148,9 @@
       <c r="B45" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C45" s="69"/>
-      <c r="D45" s="70"/>
-      <c r="E45" s="70"/>
+      <c r="C45" s="77"/>
+      <c r="D45" s="73"/>
+      <c r="E45" s="73"/>
       <c r="F45" s="62">
         <v>0</v>
       </c>
@@ -5169,7 +5178,7 @@
         <f>SUM(F45*1/5,G45*1/5,H45*1/5,I45*1/5,J45*1/5)</f>
         <v>0.23017129817999998</v>
       </c>
-      <c r="N45" s="76"/>
+      <c r="N45" s="75"/>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A47" s="1" t="s">
@@ -5178,13 +5187,13 @@
       <c r="B47" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C47" s="69" t="s">
+      <c r="C47" s="77" t="s">
         <v>51</v>
       </c>
-      <c r="D47" s="70" t="s">
+      <c r="D47" s="73" t="s">
         <v>26</v>
       </c>
-      <c r="E47" s="70" t="s">
+      <c r="E47" s="73" t="s">
         <v>28</v>
       </c>
       <c r="F47" s="11">
@@ -5214,7 +5223,7 @@
         <f>SUM(F47*1/5,G47*1/5,H47*1/5,I47*1/5,J47*1/5)</f>
         <v>0.28403192430000002</v>
       </c>
-      <c r="N47" s="76" t="s">
+      <c r="N47" s="75" t="s">
         <v>31</v>
       </c>
     </row>
@@ -5225,9 +5234,9 @@
       <c r="B48" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C48" s="69"/>
-      <c r="D48" s="70"/>
-      <c r="E48" s="70"/>
+      <c r="C48" s="77"/>
+      <c r="D48" s="73"/>
+      <c r="E48" s="73"/>
       <c r="F48" s="11">
         <v>2.90285495E-2</v>
       </c>
@@ -5255,7 +5264,7 @@
         <f>SUM(F48*1/5,G48*1/5,H48*1/5,I48*1/5,J48*1/5)</f>
         <v>0.35089340806000002</v>
       </c>
-      <c r="N48" s="76"/>
+      <c r="N48" s="75"/>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A49" s="1" t="s">
@@ -5264,9 +5273,9 @@
       <c r="B49" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C49" s="69"/>
-      <c r="D49" s="70"/>
-      <c r="E49" s="70"/>
+      <c r="C49" s="77"/>
+      <c r="D49" s="73"/>
+      <c r="E49" s="73"/>
       <c r="F49" s="11">
         <v>1.9160760000000001E-4</v>
       </c>
@@ -5294,7 +5303,7 @@
         <f>SUM(F49*1/5,G49*1/5,H49*1/5,I49*1/5,J49*1/5)</f>
         <v>0.34178323869999999</v>
       </c>
-      <c r="N49" s="76"/>
+      <c r="N49" s="75"/>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A51" s="1" t="s">
@@ -5303,13 +5312,13 @@
       <c r="B51" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C51" s="69" t="s">
+      <c r="C51" s="77" t="s">
         <v>52</v>
       </c>
-      <c r="D51" s="70" t="s">
+      <c r="D51" s="73" t="s">
         <v>39</v>
       </c>
-      <c r="E51" s="70" t="s">
+      <c r="E51" s="73" t="s">
         <v>29</v>
       </c>
       <c r="F51" s="11">
@@ -5347,9 +5356,9 @@
       <c r="B52" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C52" s="69"/>
-      <c r="D52" s="70"/>
-      <c r="E52" s="70"/>
+      <c r="C52" s="77"/>
+      <c r="D52" s="73"/>
+      <c r="E52" s="73"/>
       <c r="F52" s="11">
         <v>3.4489365999999999E-3</v>
       </c>
@@ -5385,9 +5394,9 @@
       <c r="B53" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C53" s="69"/>
-      <c r="D53" s="70"/>
-      <c r="E53" s="70"/>
+      <c r="C53" s="77"/>
+      <c r="D53" s="73"/>
+      <c r="E53" s="73"/>
       <c r="F53" s="62">
         <v>4.7901900000000002E-4</v>
       </c>
@@ -5417,12 +5426,12 @@
       </c>
     </row>
     <row r="56" spans="1:14" s="14" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="77" t="s">
+      <c r="A56" s="88" t="s">
         <v>59</v>
       </c>
-      <c r="B56" s="77"/>
-      <c r="C56" s="77"/>
-      <c r="D56" s="77"/>
+      <c r="B56" s="88"/>
+      <c r="C56" s="88"/>
+      <c r="D56" s="88"/>
       <c r="E56" s="15"/>
       <c r="F56" s="16">
         <f t="shared" ref="F56:M56" si="0">MAX(F3:F53)</f>
@@ -5459,12 +5468,12 @@
       <c r="N56" s="17"/>
     </row>
     <row r="57" spans="1:14" s="18" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="79" t="s">
+      <c r="A57" s="86" t="s">
         <v>60</v>
       </c>
-      <c r="B57" s="79"/>
-      <c r="C57" s="79"/>
-      <c r="D57" s="79"/>
+      <c r="B57" s="86"/>
+      <c r="C57" s="86"/>
+      <c r="D57" s="86"/>
       <c r="E57" s="19"/>
       <c r="F57" s="20">
         <f t="shared" ref="F57:M57" si="1">AVERAGE(F3:F53)</f>
@@ -5501,13 +5510,13 @@
       <c r="N57" s="21"/>
     </row>
     <row r="59" spans="1:14" s="22" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="82" t="s">
+      <c r="A59" s="83" t="s">
         <v>64</v>
       </c>
-      <c r="B59" s="82"/>
-      <c r="C59" s="82"/>
-      <c r="D59" s="82"/>
-      <c r="E59" s="82"/>
+      <c r="B59" s="83"/>
+      <c r="C59" s="83"/>
+      <c r="D59" s="83"/>
+      <c r="E59" s="83"/>
       <c r="F59" s="29">
         <f>SUM(F56*(1/3),  G56*(1/3), I56*(1/3))</f>
         <v>0.33744571563333331</v>
@@ -5522,13 +5531,13 @@
       <c r="N59" s="24"/>
     </row>
     <row r="60" spans="1:14" s="27" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="83" t="s">
+      <c r="A60" s="84" t="s">
         <v>65</v>
       </c>
-      <c r="B60" s="83"/>
-      <c r="C60" s="83"/>
-      <c r="D60" s="83"/>
-      <c r="E60" s="83"/>
+      <c r="B60" s="84"/>
+      <c r="C60" s="84"/>
+      <c r="D60" s="84"/>
+      <c r="E60" s="84"/>
       <c r="F60" s="28">
         <f>SUM(H56*(1/2),  J56*(1/2))</f>
         <v>0.67529401794999999</v>
@@ -5543,13 +5552,13 @@
       <c r="N60" s="26"/>
     </row>
     <row r="61" spans="1:14" s="33" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="84" t="s">
+      <c r="A61" s="85" t="s">
         <v>66</v>
       </c>
-      <c r="B61" s="84"/>
-      <c r="C61" s="84"/>
-      <c r="D61" s="84"/>
-      <c r="E61" s="84"/>
+      <c r="B61" s="85"/>
+      <c r="C61" s="85"/>
+      <c r="D61" s="85"/>
+      <c r="E61" s="85"/>
       <c r="F61" s="30">
         <f>SUM(F56*1/5, G56*1/5, H56*1/5, I56*1/5,J56*1/5)</f>
         <v>0.47258503656</v>
@@ -5564,12 +5573,12 @@
       <c r="N61" s="32"/>
     </row>
     <row r="63" spans="1:14" s="37" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A63" s="80" t="s">
+      <c r="A63" s="81" t="s">
         <v>83</v>
       </c>
-      <c r="B63" s="80"/>
-      <c r="C63" s="80"/>
-      <c r="D63" s="80"/>
+      <c r="B63" s="81"/>
+      <c r="C63" s="81"/>
+      <c r="D63" s="81"/>
       <c r="E63" s="34"/>
       <c r="F63" s="35"/>
       <c r="G63" s="35"/>
@@ -5582,12 +5591,12 @@
       <c r="N63" s="36"/>
     </row>
     <row r="64" spans="1:14" s="37" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="80" t="s">
+      <c r="A64" s="81" t="s">
         <v>84</v>
       </c>
-      <c r="B64" s="81"/>
-      <c r="C64" s="81"/>
-      <c r="D64" s="81"/>
+      <c r="B64" s="82"/>
+      <c r="C64" s="82"/>
+      <c r="D64" s="82"/>
       <c r="E64" s="38"/>
       <c r="F64" s="35"/>
       <c r="G64" s="35"/>
@@ -5600,12 +5609,12 @@
       <c r="N64" s="36"/>
     </row>
     <row r="65" spans="1:14" s="37" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="80" t="s">
+      <c r="A65" s="81" t="s">
         <v>85</v>
       </c>
-      <c r="B65" s="81"/>
-      <c r="C65" s="81"/>
-      <c r="D65" s="81"/>
+      <c r="B65" s="82"/>
+      <c r="C65" s="82"/>
+      <c r="D65" s="82"/>
       <c r="E65" s="38"/>
       <c r="F65" s="35"/>
       <c r="G65" s="35"/>
@@ -5619,6 +5628,44 @@
     </row>
   </sheetData>
   <mergeCells count="54">
+    <mergeCell ref="A56:D56"/>
+    <mergeCell ref="N43:N45"/>
+    <mergeCell ref="C47:C49"/>
+    <mergeCell ref="D47:D49"/>
+    <mergeCell ref="E47:E49"/>
+    <mergeCell ref="N47:N49"/>
+    <mergeCell ref="E51:E53"/>
+    <mergeCell ref="C51:C53"/>
+    <mergeCell ref="D51:D53"/>
+    <mergeCell ref="N13:N15"/>
+    <mergeCell ref="C21:C23"/>
+    <mergeCell ref="D21:D23"/>
+    <mergeCell ref="E21:E23"/>
+    <mergeCell ref="N21:N23"/>
+    <mergeCell ref="C17:C19"/>
+    <mergeCell ref="D17:D19"/>
+    <mergeCell ref="E17:E19"/>
+    <mergeCell ref="N17:N19"/>
+    <mergeCell ref="N3:N5"/>
+    <mergeCell ref="C7:C9"/>
+    <mergeCell ref="D7:D9"/>
+    <mergeCell ref="E7:E9"/>
+    <mergeCell ref="N7:N9"/>
+    <mergeCell ref="C3:C5"/>
+    <mergeCell ref="D3:D5"/>
+    <mergeCell ref="E3:E5"/>
+    <mergeCell ref="C37:C39"/>
+    <mergeCell ref="D37:D39"/>
+    <mergeCell ref="E37:E39"/>
+    <mergeCell ref="A41:D41"/>
+    <mergeCell ref="C43:C45"/>
+    <mergeCell ref="D43:D45"/>
+    <mergeCell ref="E43:E45"/>
+    <mergeCell ref="D29:D31"/>
+    <mergeCell ref="E29:E31"/>
+    <mergeCell ref="C33:C35"/>
+    <mergeCell ref="D33:D35"/>
+    <mergeCell ref="E33:E35"/>
     <mergeCell ref="A1:XFD1"/>
     <mergeCell ref="A64:D64"/>
     <mergeCell ref="A65:D65"/>
@@ -5635,44 +5682,6 @@
     <mergeCell ref="D25:D27"/>
     <mergeCell ref="E25:E27"/>
     <mergeCell ref="C29:C31"/>
-    <mergeCell ref="D29:D31"/>
-    <mergeCell ref="E29:E31"/>
-    <mergeCell ref="C33:C35"/>
-    <mergeCell ref="D33:D35"/>
-    <mergeCell ref="E33:E35"/>
-    <mergeCell ref="C51:C53"/>
-    <mergeCell ref="D51:D53"/>
-    <mergeCell ref="C3:C5"/>
-    <mergeCell ref="D3:D5"/>
-    <mergeCell ref="E3:E5"/>
-    <mergeCell ref="N3:N5"/>
-    <mergeCell ref="C7:C9"/>
-    <mergeCell ref="D7:D9"/>
-    <mergeCell ref="E7:E9"/>
-    <mergeCell ref="N7:N9"/>
-    <mergeCell ref="N13:N15"/>
-    <mergeCell ref="C21:C23"/>
-    <mergeCell ref="D21:D23"/>
-    <mergeCell ref="E21:E23"/>
-    <mergeCell ref="N21:N23"/>
-    <mergeCell ref="C17:C19"/>
-    <mergeCell ref="D17:D19"/>
-    <mergeCell ref="E17:E19"/>
-    <mergeCell ref="N17:N19"/>
-    <mergeCell ref="C37:C39"/>
-    <mergeCell ref="D37:D39"/>
-    <mergeCell ref="E37:E39"/>
-    <mergeCell ref="A41:D41"/>
-    <mergeCell ref="C43:C45"/>
-    <mergeCell ref="D43:D45"/>
-    <mergeCell ref="E43:E45"/>
-    <mergeCell ref="A56:D56"/>
-    <mergeCell ref="N43:N45"/>
-    <mergeCell ref="C47:C49"/>
-    <mergeCell ref="D47:D49"/>
-    <mergeCell ref="E47:E49"/>
-    <mergeCell ref="N47:N49"/>
-    <mergeCell ref="E51:E53"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5698,8 +5707,8 @@
     <col min="13" max="16384" width="51.33203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="89" customFormat="1" ht="27" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="89" t="s">
+    <row r="1" spans="1:14" s="71" customFormat="1" ht="27" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="71" t="s">
         <v>118</v>
       </c>
     </row>
@@ -5758,17 +5767,17 @@
       <c r="N3" s="9"/>
     </row>
     <row r="4" spans="1:14" s="47" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="79" t="s">
+      <c r="A4" s="86" t="s">
         <v>71</v>
       </c>
-      <c r="B4" s="79"/>
-      <c r="C4" s="79"/>
-      <c r="D4" s="79"/>
-      <c r="E4" s="79"/>
-      <c r="F4" s="79"/>
-      <c r="G4" s="79"/>
-      <c r="H4" s="79"/>
-      <c r="I4" s="79"/>
+      <c r="B4" s="86"/>
+      <c r="C4" s="86"/>
+      <c r="D4" s="86"/>
+      <c r="E4" s="86"/>
+      <c r="F4" s="86"/>
+      <c r="G4" s="86"/>
+      <c r="H4" s="86"/>
+      <c r="I4" s="86"/>
       <c r="J4" s="49"/>
       <c r="K4" s="56"/>
       <c r="L4" s="56"/>
@@ -5794,10 +5803,10 @@
       <c r="B6" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="76" t="s">
+      <c r="C6" s="75" t="s">
         <v>67</v>
       </c>
-      <c r="D6" s="76" t="s">
+      <c r="D6" s="75" t="s">
         <v>68</v>
       </c>
       <c r="E6" s="11">
@@ -5835,8 +5844,8 @@
       <c r="B7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="76"/>
-      <c r="D7" s="76"/>
+      <c r="C7" s="75"/>
+      <c r="D7" s="75"/>
       <c r="E7" s="11">
         <v>6.9727237799999994E-2</v>
       </c>
@@ -5872,8 +5881,8 @@
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="76"/>
-      <c r="D8" s="76"/>
+      <c r="C8" s="75"/>
+      <c r="D8" s="75"/>
       <c r="E8" s="11">
         <v>2.8812910000000001E-4</v>
       </c>
@@ -5909,10 +5918,10 @@
       <c r="B10" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C10" s="76" t="s">
+      <c r="C10" s="75" t="s">
         <v>69</v>
       </c>
-      <c r="D10" s="76" t="s">
+      <c r="D10" s="75" t="s">
         <v>70</v>
       </c>
       <c r="E10" s="11">
@@ -5950,8 +5959,8 @@
       <c r="B11" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C11" s="76"/>
-      <c r="D11" s="76"/>
+      <c r="C11" s="75"/>
+      <c r="D11" s="75"/>
       <c r="E11" s="11">
         <v>2.4010757000000001E-3</v>
       </c>
@@ -5987,8 +5996,8 @@
       <c r="B12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C12" s="76"/>
-      <c r="D12" s="76"/>
+      <c r="C12" s="75"/>
+      <c r="D12" s="75"/>
       <c r="E12" s="11">
         <v>0</v>
       </c>
@@ -6024,10 +6033,10 @@
       <c r="B14" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C14" s="76" t="s">
+      <c r="C14" s="75" t="s">
         <v>74</v>
       </c>
-      <c r="D14" s="76" t="s">
+      <c r="D14" s="75" t="s">
         <v>81</v>
       </c>
       <c r="E14" s="11">
@@ -6065,8 +6074,8 @@
       <c r="B15" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C15" s="76"/>
-      <c r="D15" s="76"/>
+      <c r="C15" s="75"/>
+      <c r="D15" s="75"/>
       <c r="E15" s="11">
         <v>3.5474592999999999E-3</v>
       </c>
@@ -6102,8 +6111,8 @@
       <c r="B16" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C16" s="76"/>
-      <c r="D16" s="76"/>
+      <c r="C16" s="75"/>
+      <c r="D16" s="75"/>
       <c r="E16" s="11">
         <v>3.8350910000000001E-4</v>
       </c>
@@ -6139,10 +6148,10 @@
       <c r="B18" s="63" t="s">
         <v>5</v>
       </c>
-      <c r="C18" s="76" t="s">
+      <c r="C18" s="75" t="s">
         <v>80</v>
       </c>
-      <c r="D18" s="76" t="s">
+      <c r="D18" s="75" t="s">
         <v>79</v>
       </c>
       <c r="E18" s="64">
@@ -6180,8 +6189,8 @@
       <c r="B19" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C19" s="76"/>
-      <c r="D19" s="76"/>
+      <c r="C19" s="75"/>
+      <c r="D19" s="75"/>
       <c r="E19" s="11">
         <v>3.0680729000000001E-3</v>
       </c>
@@ -6217,8 +6226,8 @@
       <c r="B20" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C20" s="76"/>
-      <c r="D20" s="76"/>
+      <c r="C20" s="75"/>
+      <c r="D20" s="75"/>
       <c r="E20" s="11">
         <v>2.876318E-4</v>
       </c>
@@ -6257,10 +6266,10 @@
       <c r="B22" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C22" s="76" t="s">
+      <c r="C22" s="75" t="s">
         <v>72</v>
       </c>
-      <c r="D22" s="76" t="s">
+      <c r="D22" s="75" t="s">
         <v>73</v>
       </c>
       <c r="E22" s="11">
@@ -6298,8 +6307,8 @@
       <c r="B23" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C23" s="76"/>
-      <c r="D23" s="76"/>
+      <c r="C23" s="75"/>
+      <c r="D23" s="75"/>
       <c r="E23" s="11">
         <v>3.1639501E-3</v>
       </c>
@@ -6335,8 +6344,8 @@
       <c r="B24" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C24" s="76"/>
-      <c r="D24" s="76"/>
+      <c r="C24" s="75"/>
+      <c r="D24" s="75"/>
       <c r="E24" s="11">
         <v>1.917546E-4</v>
       </c>
@@ -6372,10 +6381,10 @@
       <c r="B26" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C26" s="76" t="s">
+      <c r="C26" s="75" t="s">
         <v>77</v>
       </c>
-      <c r="D26" s="76" t="s">
+      <c r="D26" s="75" t="s">
         <v>75</v>
       </c>
       <c r="E26" s="11">
@@ -6413,8 +6422,8 @@
       <c r="B27" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C27" s="76"/>
-      <c r="D27" s="76"/>
+      <c r="C27" s="75"/>
+      <c r="D27" s="75"/>
       <c r="E27" s="11">
         <v>1.70661553E-2</v>
       </c>
@@ -6450,8 +6459,8 @@
       <c r="B28" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C28" s="76"/>
-      <c r="D28" s="76"/>
+      <c r="C28" s="75"/>
+      <c r="D28" s="75"/>
       <c r="E28" s="11">
         <v>6.7114089999999996E-4</v>
       </c>
@@ -6487,10 +6496,10 @@
       <c r="B30" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C30" s="76" t="s">
+      <c r="C30" s="75" t="s">
         <v>78</v>
       </c>
-      <c r="D30" s="76" t="s">
+      <c r="D30" s="75" t="s">
         <v>76</v>
       </c>
       <c r="E30" s="11">
@@ -6528,8 +6537,8 @@
       <c r="B31" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C31" s="76"/>
-      <c r="D31" s="76"/>
+      <c r="C31" s="75"/>
+      <c r="D31" s="75"/>
       <c r="E31" s="11">
         <v>7.2866731000000001E-3</v>
       </c>
@@ -6565,8 +6574,8 @@
       <c r="B32" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C32" s="76"/>
-      <c r="D32" s="76"/>
+      <c r="C32" s="75"/>
+      <c r="D32" s="75"/>
       <c r="E32" s="11">
         <v>0</v>
       </c>
@@ -6596,12 +6605,12 @@
       </c>
     </row>
     <row r="35" spans="1:14" s="14" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="77" t="s">
+      <c r="A35" s="88" t="s">
         <v>59</v>
       </c>
-      <c r="B35" s="77"/>
-      <c r="C35" s="77"/>
-      <c r="D35" s="77"/>
+      <c r="B35" s="88"/>
+      <c r="C35" s="88"/>
+      <c r="D35" s="88"/>
       <c r="E35" s="16">
         <f t="shared" ref="E35:L35" si="0">MAX(E5:E33)</f>
         <v>8.2742090099999999E-2</v>
@@ -6638,12 +6647,12 @@
       <c r="N35" s="17"/>
     </row>
     <row r="36" spans="1:14" s="52" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="82" t="s">
+      <c r="A36" s="83" t="s">
         <v>60</v>
       </c>
-      <c r="B36" s="82"/>
-      <c r="C36" s="82"/>
-      <c r="D36" s="82"/>
+      <c r="B36" s="83"/>
+      <c r="C36" s="83"/>
+      <c r="D36" s="83"/>
       <c r="E36" s="29">
         <f t="shared" ref="E36:L36" si="1">AVERAGE(E6:E33)</f>
         <v>2.0975477057142849E-2</v>
@@ -6680,17 +6689,17 @@
       <c r="N36" s="58"/>
     </row>
     <row r="38" spans="1:14" s="47" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="79" t="s">
+      <c r="A38" s="86" t="s">
         <v>86</v>
       </c>
-      <c r="B38" s="79"/>
-      <c r="C38" s="79"/>
-      <c r="D38" s="79"/>
-      <c r="E38" s="79"/>
-      <c r="F38" s="79"/>
-      <c r="G38" s="79"/>
-      <c r="H38" s="79"/>
-      <c r="I38" s="79"/>
+      <c r="B38" s="86"/>
+      <c r="C38" s="86"/>
+      <c r="D38" s="86"/>
+      <c r="E38" s="86"/>
+      <c r="F38" s="86"/>
+      <c r="G38" s="86"/>
+      <c r="H38" s="86"/>
+      <c r="I38" s="86"/>
       <c r="J38" s="49"/>
       <c r="K38" s="56"/>
       <c r="L38" s="56"/>
@@ -6716,10 +6725,10 @@
       <c r="B40" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C40" s="76" t="s">
+      <c r="C40" s="75" t="s">
         <v>87</v>
       </c>
-      <c r="D40" s="76" t="s">
+      <c r="D40" s="75" t="s">
         <v>68</v>
       </c>
       <c r="E40" s="11">
@@ -6757,8 +6766,8 @@
       <c r="B41" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C41" s="76"/>
-      <c r="D41" s="76"/>
+      <c r="C41" s="75"/>
+      <c r="D41" s="75"/>
       <c r="E41" s="11">
         <v>1.42857143E-2</v>
       </c>
@@ -6794,8 +6803,8 @@
       <c r="B42" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C42" s="76"/>
-      <c r="D42" s="76"/>
+      <c r="C42" s="75"/>
+      <c r="D42" s="75"/>
       <c r="E42" s="11">
         <v>3.8350910000000001E-4</v>
       </c>
@@ -6831,10 +6840,10 @@
       <c r="B44" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C44" s="76" t="s">
+      <c r="C44" s="75" t="s">
         <v>88</v>
       </c>
-      <c r="D44" s="76" t="s">
+      <c r="D44" s="75" t="s">
         <v>70</v>
       </c>
       <c r="E44" s="11">
@@ -6872,8 +6881,8 @@
       <c r="B45" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C45" s="76"/>
-      <c r="D45" s="76"/>
+      <c r="C45" s="75"/>
+      <c r="D45" s="75"/>
       <c r="E45" s="11">
         <v>2.8475551299999999E-2</v>
       </c>
@@ -6909,8 +6918,8 @@
       <c r="B46" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C46" s="76"/>
-      <c r="D46" s="76"/>
+      <c r="C46" s="75"/>
+      <c r="D46" s="75"/>
       <c r="E46" s="11">
         <v>1.917546E-4</v>
       </c>
@@ -6946,10 +6955,10 @@
       <c r="B48" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C48" s="76" t="s">
+      <c r="C48" s="75" t="s">
         <v>89</v>
       </c>
-      <c r="D48" s="76" t="s">
+      <c r="D48" s="75" t="s">
         <v>81</v>
       </c>
       <c r="E48" s="11">
@@ -6987,8 +6996,8 @@
       <c r="B49" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C49" s="76"/>
-      <c r="D49" s="76"/>
+      <c r="C49" s="75"/>
+      <c r="D49" s="75"/>
       <c r="E49" s="11">
         <v>6.3279002999999997E-3</v>
       </c>
@@ -7024,8 +7033,8 @@
       <c r="B50" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C50" s="76"/>
-      <c r="D50" s="76"/>
+      <c r="C50" s="75"/>
+      <c r="D50" s="75"/>
       <c r="E50" s="11">
         <v>2.876318E-4</v>
       </c>
@@ -7061,10 +7070,10 @@
       <c r="B52" s="63" t="s">
         <v>5</v>
       </c>
-      <c r="C52" s="76" t="s">
+      <c r="C52" s="75" t="s">
         <v>90</v>
       </c>
-      <c r="D52" s="76" t="s">
+      <c r="D52" s="75" t="s">
         <v>79</v>
       </c>
       <c r="E52" s="64">
@@ -7102,8 +7111,8 @@
       <c r="B53" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C53" s="76"/>
-      <c r="D53" s="76"/>
+      <c r="C53" s="75"/>
+      <c r="D53" s="75"/>
       <c r="E53" s="11">
         <v>2.0134227999999998E-3</v>
       </c>
@@ -7139,8 +7148,8 @@
       <c r="B54" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C54" s="76"/>
-      <c r="D54" s="76"/>
+      <c r="C54" s="75"/>
+      <c r="D54" s="75"/>
       <c r="E54" s="11">
         <v>1.917546E-4</v>
       </c>
@@ -7179,10 +7188,10 @@
       <c r="B56" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C56" s="76" t="s">
+      <c r="C56" s="75" t="s">
         <v>91</v>
       </c>
-      <c r="D56" s="76" t="s">
+      <c r="D56" s="75" t="s">
         <v>73</v>
       </c>
       <c r="E56" s="11">
@@ -7220,8 +7229,8 @@
       <c r="B57" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C57" s="76"/>
-      <c r="D57" s="76"/>
+      <c r="C57" s="75"/>
+      <c r="D57" s="75"/>
       <c r="E57" s="11">
         <v>1.9558964500000001E-2</v>
       </c>
@@ -7257,8 +7266,8 @@
       <c r="B58" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C58" s="76"/>
-      <c r="D58" s="76"/>
+      <c r="C58" s="75"/>
+      <c r="D58" s="75"/>
       <c r="E58" s="11">
         <v>0</v>
       </c>
@@ -7294,10 +7303,10 @@
       <c r="B60" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C60" s="76" t="s">
+      <c r="C60" s="75" t="s">
         <v>92</v>
       </c>
-      <c r="D60" s="76" t="s">
+      <c r="D60" s="75" t="s">
         <v>75</v>
       </c>
       <c r="E60" s="11">
@@ -7335,8 +7344,8 @@
       <c r="B61" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C61" s="76"/>
-      <c r="D61" s="76"/>
+      <c r="C61" s="75"/>
+      <c r="D61" s="75"/>
       <c r="E61" s="11">
         <v>4.4103546999999998E-3</v>
       </c>
@@ -7372,8 +7381,8 @@
       <c r="B62" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C62" s="76"/>
-      <c r="D62" s="76"/>
+      <c r="C62" s="75"/>
+      <c r="D62" s="75"/>
       <c r="E62" s="11">
         <v>2.8763183000000002E-3</v>
       </c>
@@ -7409,10 +7418,10 @@
       <c r="B64" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C64" s="76" t="s">
+      <c r="C64" s="75" t="s">
         <v>93</v>
       </c>
-      <c r="D64" s="76" t="s">
+      <c r="D64" s="75" t="s">
         <v>76</v>
       </c>
       <c r="E64" s="11">
@@ -7450,8 +7459,8 @@
       <c r="B65" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C65" s="76"/>
-      <c r="D65" s="76"/>
+      <c r="C65" s="75"/>
+      <c r="D65" s="75"/>
       <c r="E65" s="11">
         <v>8.6289548999999993E-3</v>
       </c>
@@ -7487,8 +7496,8 @@
       <c r="B66" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C66" s="76"/>
-      <c r="D66" s="76"/>
+      <c r="C66" s="75"/>
+      <c r="D66" s="75"/>
       <c r="E66" s="11">
         <v>1.9175455000000001E-3</v>
       </c>
@@ -7518,12 +7527,12 @@
       </c>
     </row>
     <row r="69" spans="1:14" s="14" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="77" t="s">
+      <c r="A69" s="88" t="s">
         <v>59</v>
       </c>
-      <c r="B69" s="77"/>
-      <c r="C69" s="77"/>
-      <c r="D69" s="77"/>
+      <c r="B69" s="88"/>
+      <c r="C69" s="88"/>
+      <c r="D69" s="88"/>
       <c r="E69" s="16">
         <f t="shared" ref="E69:L69" si="2">MAX(E39:E67)</f>
         <v>9.0220517700000002E-2</v>
@@ -7560,12 +7569,12 @@
       <c r="N69" s="17"/>
     </row>
     <row r="70" spans="1:14" s="52" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A70" s="82" t="s">
+      <c r="A70" s="83" t="s">
         <v>60</v>
       </c>
-      <c r="B70" s="82"/>
-      <c r="C70" s="82"/>
-      <c r="D70" s="82"/>
+      <c r="B70" s="83"/>
+      <c r="C70" s="83"/>
+      <c r="D70" s="83"/>
       <c r="E70" s="29">
         <f t="shared" ref="E70:L70" si="3">AVERAGE(E40:E67)</f>
         <v>1.7271606619047621E-2</v>
@@ -7602,17 +7611,17 @@
       <c r="N70" s="58"/>
     </row>
     <row r="72" spans="1:14" s="47" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="79" t="s">
+      <c r="A72" s="86" t="s">
         <v>94</v>
       </c>
-      <c r="B72" s="79"/>
-      <c r="C72" s="79"/>
-      <c r="D72" s="79"/>
-      <c r="E72" s="79"/>
-      <c r="F72" s="79"/>
-      <c r="G72" s="79"/>
-      <c r="H72" s="79"/>
-      <c r="I72" s="79"/>
+      <c r="B72" s="86"/>
+      <c r="C72" s="86"/>
+      <c r="D72" s="86"/>
+      <c r="E72" s="86"/>
+      <c r="F72" s="86"/>
+      <c r="G72" s="86"/>
+      <c r="H72" s="86"/>
+      <c r="I72" s="86"/>
       <c r="J72" s="49"/>
       <c r="K72" s="56"/>
       <c r="L72" s="56"/>
@@ -7638,10 +7647,10 @@
       <c r="B74" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C74" s="76" t="s">
+      <c r="C74" s="75" t="s">
         <v>95</v>
       </c>
-      <c r="D74" s="76" t="s">
+      <c r="D74" s="75" t="s">
         <v>68</v>
       </c>
       <c r="E74" s="11">
@@ -7679,8 +7688,8 @@
       <c r="B75" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C75" s="76"/>
-      <c r="D75" s="76"/>
+      <c r="C75" s="75"/>
+      <c r="D75" s="75"/>
       <c r="E75" s="11">
         <v>8.8139489999999997E-3</v>
       </c>
@@ -7716,8 +7725,8 @@
       <c r="B76" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C76" s="76"/>
-      <c r="D76" s="76"/>
+      <c r="C76" s="75"/>
+      <c r="D76" s="75"/>
       <c r="E76" s="11">
         <v>1.9160760000000001E-4</v>
       </c>
@@ -7753,10 +7762,10 @@
       <c r="B78" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C78" s="76" t="s">
+      <c r="C78" s="75" t="s">
         <v>96</v>
       </c>
-      <c r="D78" s="76" t="s">
+      <c r="D78" s="75" t="s">
         <v>70</v>
       </c>
       <c r="E78" s="11">
@@ -7794,8 +7803,8 @@
       <c r="B79" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C79" s="76"/>
-      <c r="D79" s="76"/>
+      <c r="C79" s="75"/>
+      <c r="D79" s="75"/>
       <c r="E79" s="11">
         <v>3.4489365999999999E-3</v>
       </c>
@@ -7831,8 +7840,8 @@
       <c r="B80" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C80" s="76"/>
-      <c r="D80" s="76"/>
+      <c r="C80" s="75"/>
+      <c r="D80" s="75"/>
       <c r="E80" s="62">
         <v>4.7901900000000002E-4</v>
       </c>
@@ -7868,10 +7877,10 @@
       <c r="B82" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C82" s="76" t="s">
+      <c r="C82" s="75" t="s">
         <v>97</v>
       </c>
-      <c r="D82" s="76" t="s">
+      <c r="D82" s="75" t="s">
         <v>81</v>
       </c>
       <c r="E82" s="11">
@@ -7909,8 +7918,8 @@
       <c r="B83" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C83" s="76"/>
-      <c r="D83" s="76"/>
+      <c r="C83" s="75"/>
+      <c r="D83" s="75"/>
       <c r="E83" s="11">
         <v>4.3111707000000003E-3</v>
       </c>
@@ -7946,8 +7955,8 @@
       <c r="B84" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C84" s="76"/>
-      <c r="D84" s="76"/>
+      <c r="C84" s="75"/>
+      <c r="D84" s="75"/>
       <c r="E84" s="11">
         <v>2.1076835000000001E-3</v>
       </c>
@@ -7983,10 +7992,10 @@
       <c r="B86" s="42" t="s">
         <v>5</v>
       </c>
-      <c r="C86" s="76" t="s">
+      <c r="C86" s="75" t="s">
         <v>98</v>
       </c>
-      <c r="D86" s="76" t="s">
+      <c r="D86" s="75" t="s">
         <v>79</v>
       </c>
       <c r="E86" s="67">
@@ -8024,8 +8033,8 @@
       <c r="B87" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C87" s="76"/>
-      <c r="D87" s="76"/>
+      <c r="C87" s="75"/>
+      <c r="D87" s="75"/>
       <c r="E87" s="11">
         <v>8.6223409999999995E-4</v>
       </c>
@@ -8061,8 +8070,8 @@
       <c r="B88" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C88" s="76"/>
-      <c r="D88" s="76"/>
+      <c r="C88" s="75"/>
+      <c r="D88" s="75"/>
       <c r="E88" s="11">
         <v>3.8321520000000002E-4</v>
       </c>
@@ -8101,10 +8110,10 @@
       <c r="B90" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C90" s="76" t="s">
+      <c r="C90" s="75" t="s">
         <v>99</v>
       </c>
-      <c r="D90" s="76" t="s">
+      <c r="D90" s="75" t="s">
         <v>73</v>
       </c>
       <c r="E90" s="11">
@@ -8142,8 +8151,8 @@
       <c r="B91" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C91" s="76"/>
-      <c r="D91" s="76"/>
+      <c r="C91" s="75"/>
+      <c r="D91" s="75"/>
       <c r="E91" s="11">
         <v>1.59034298E-2</v>
       </c>
@@ -8179,8 +8188,8 @@
       <c r="B92" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C92" s="76"/>
-      <c r="D92" s="76"/>
+      <c r="C92" s="75"/>
+      <c r="D92" s="75"/>
       <c r="E92" s="11">
         <v>0</v>
       </c>
@@ -8216,10 +8225,10 @@
       <c r="B94" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C94" s="76" t="s">
+      <c r="C94" s="75" t="s">
         <v>100</v>
       </c>
-      <c r="D94" s="76" t="s">
+      <c r="D94" s="75" t="s">
         <v>75</v>
       </c>
       <c r="E94" s="11">
@@ -8257,8 +8266,8 @@
       <c r="B95" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C95" s="76"/>
-      <c r="D95" s="76"/>
+      <c r="C95" s="75"/>
+      <c r="D95" s="75"/>
       <c r="E95" s="11">
         <v>9.4845755999999996E-3</v>
       </c>
@@ -8294,8 +8303,8 @@
       <c r="B96" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C96" s="76"/>
-      <c r="D96" s="76"/>
+      <c r="C96" s="75"/>
+      <c r="D96" s="75"/>
       <c r="E96" s="11">
         <v>1.9160760000000001E-4</v>
       </c>
@@ -8331,10 +8340,10 @@
       <c r="B98" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C98" s="76" t="s">
+      <c r="C98" s="75" t="s">
         <v>101</v>
       </c>
-      <c r="D98" s="76" t="s">
+      <c r="D98" s="75" t="s">
         <v>76</v>
       </c>
       <c r="E98" s="11">
@@ -8372,8 +8381,8 @@
       <c r="B99" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C99" s="76"/>
-      <c r="D99" s="76"/>
+      <c r="C99" s="75"/>
+      <c r="D99" s="75"/>
       <c r="E99" s="11">
         <v>8.9097528000000002E-3</v>
       </c>
@@ -8409,8 +8418,8 @@
       <c r="B100" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C100" s="76"/>
-      <c r="D100" s="76"/>
+      <c r="C100" s="75"/>
+      <c r="D100" s="75"/>
       <c r="E100" s="11">
         <v>1.6286645000000001E-3</v>
       </c>
@@ -8440,12 +8449,12 @@
       </c>
     </row>
     <row r="103" spans="1:14" s="14" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A103" s="77" t="s">
+      <c r="A103" s="88" t="s">
         <v>59</v>
       </c>
-      <c r="B103" s="77"/>
-      <c r="C103" s="77"/>
-      <c r="D103" s="77"/>
+      <c r="B103" s="88"/>
+      <c r="C103" s="88"/>
+      <c r="D103" s="88"/>
       <c r="E103" s="16">
         <f t="shared" ref="E103:L103" si="4">MAX(E73:E101)</f>
         <v>4.4165548999999998E-2</v>
@@ -8482,12 +8491,12 @@
       <c r="N103" s="17"/>
     </row>
     <row r="104" spans="1:14" s="52" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A104" s="82" t="s">
+      <c r="A104" s="83" t="s">
         <v>60</v>
       </c>
-      <c r="B104" s="82"/>
-      <c r="C104" s="82"/>
-      <c r="D104" s="82"/>
+      <c r="B104" s="83"/>
+      <c r="C104" s="83"/>
+      <c r="D104" s="83"/>
       <c r="E104" s="29">
         <f t="shared" ref="E104:L104" si="5">AVERAGE(E74:E101)</f>
         <v>1.0789332023809524E-2</v>
@@ -8525,6 +8534,42 @@
     </row>
   </sheetData>
   <mergeCells count="52">
+    <mergeCell ref="A4:I4"/>
+    <mergeCell ref="C22:C24"/>
+    <mergeCell ref="D22:D24"/>
+    <mergeCell ref="C26:C28"/>
+    <mergeCell ref="D26:D28"/>
+    <mergeCell ref="D6:D8"/>
+    <mergeCell ref="D10:D12"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="C10:C12"/>
+    <mergeCell ref="D18:D20"/>
+    <mergeCell ref="C18:C20"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A36:D36"/>
+    <mergeCell ref="C14:C16"/>
+    <mergeCell ref="D14:D16"/>
+    <mergeCell ref="C30:C32"/>
+    <mergeCell ref="D30:D32"/>
+    <mergeCell ref="A38:I38"/>
+    <mergeCell ref="C40:C42"/>
+    <mergeCell ref="D40:D42"/>
+    <mergeCell ref="C44:C46"/>
+    <mergeCell ref="D44:D46"/>
+    <mergeCell ref="C48:C50"/>
+    <mergeCell ref="D48:D50"/>
+    <mergeCell ref="C52:C54"/>
+    <mergeCell ref="D52:D54"/>
+    <mergeCell ref="C56:C58"/>
+    <mergeCell ref="D56:D58"/>
+    <mergeCell ref="D74:D76"/>
+    <mergeCell ref="C78:C80"/>
+    <mergeCell ref="D78:D80"/>
+    <mergeCell ref="C60:C62"/>
+    <mergeCell ref="D60:D62"/>
+    <mergeCell ref="C64:C66"/>
+    <mergeCell ref="D64:D66"/>
+    <mergeCell ref="A69:D69"/>
     <mergeCell ref="A1:XFD1"/>
     <mergeCell ref="A104:D104"/>
     <mergeCell ref="C94:C96"/>
@@ -8541,42 +8586,6 @@
     <mergeCell ref="A70:D70"/>
     <mergeCell ref="A72:I72"/>
     <mergeCell ref="C74:C76"/>
-    <mergeCell ref="D74:D76"/>
-    <mergeCell ref="C78:C80"/>
-    <mergeCell ref="D78:D80"/>
-    <mergeCell ref="C60:C62"/>
-    <mergeCell ref="D60:D62"/>
-    <mergeCell ref="C64:C66"/>
-    <mergeCell ref="D64:D66"/>
-    <mergeCell ref="A69:D69"/>
-    <mergeCell ref="C48:C50"/>
-    <mergeCell ref="D48:D50"/>
-    <mergeCell ref="C52:C54"/>
-    <mergeCell ref="D52:D54"/>
-    <mergeCell ref="C56:C58"/>
-    <mergeCell ref="D56:D58"/>
-    <mergeCell ref="A38:I38"/>
-    <mergeCell ref="C40:C42"/>
-    <mergeCell ref="D40:D42"/>
-    <mergeCell ref="C44:C46"/>
-    <mergeCell ref="D44:D46"/>
-    <mergeCell ref="A35:D35"/>
-    <mergeCell ref="A36:D36"/>
-    <mergeCell ref="C14:C16"/>
-    <mergeCell ref="D14:D16"/>
-    <mergeCell ref="C30:C32"/>
-    <mergeCell ref="D30:D32"/>
-    <mergeCell ref="A4:I4"/>
-    <mergeCell ref="C22:C24"/>
-    <mergeCell ref="D22:D24"/>
-    <mergeCell ref="C26:C28"/>
-    <mergeCell ref="D26:D28"/>
-    <mergeCell ref="D6:D8"/>
-    <mergeCell ref="D10:D12"/>
-    <mergeCell ref="C6:C8"/>
-    <mergeCell ref="C10:C12"/>
-    <mergeCell ref="D18:D20"/>
-    <mergeCell ref="C18:C20"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -8597,8 +8606,8 @@
     <col min="11" max="16384" width="22.6640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="89" customFormat="1" ht="27" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="89" t="s">
+    <row r="1" spans="1:10" s="71" customFormat="1" ht="27" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="71" t="s">
         <v>119</v>
       </c>
     </row>
@@ -8641,10 +8650,10 @@
       <c r="B4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="76" t="s">
+      <c r="C4" s="75" t="s">
         <v>107</v>
       </c>
-      <c r="D4" s="76" t="s">
+      <c r="D4" s="75" t="s">
         <v>109</v>
       </c>
       <c r="E4" s="1">
@@ -8674,8 +8683,8 @@
       <c r="B5" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="76"/>
-      <c r="D5" s="76"/>
+      <c r="C5" s="75"/>
+      <c r="D5" s="75"/>
       <c r="E5" s="1">
         <v>0.51505273250000005</v>
       </c>
@@ -8703,8 +8712,8 @@
       <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="76"/>
-      <c r="D6" s="76"/>
+      <c r="C6" s="75"/>
+      <c r="D6" s="75"/>
       <c r="E6" s="1">
         <v>3.79674017E-2</v>
       </c>
@@ -8732,10 +8741,10 @@
       <c r="B8" s="42" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="85" t="s">
+      <c r="C8" s="89" t="s">
         <v>110</v>
       </c>
-      <c r="D8" s="76" t="s">
+      <c r="D8" s="75" t="s">
         <v>111</v>
       </c>
       <c r="E8" s="42">
@@ -8754,7 +8763,7 @@
         <v>0.14285714290000001</v>
       </c>
       <c r="J8" s="66">
-        <f t="shared" si="0"/>
+        <f>G8*1/3+H8*1/3+I8*1/3</f>
         <v>0.41626844496666671</v>
       </c>
     </row>
@@ -8765,8 +8774,8 @@
       <c r="B9" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="85"/>
-      <c r="D9" s="76"/>
+      <c r="C9" s="89"/>
+      <c r="D9" s="75"/>
       <c r="E9" s="1">
         <v>0.27823585810000001</v>
       </c>
@@ -8794,8 +8803,8 @@
       <c r="B10" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C10" s="85"/>
-      <c r="D10" s="76"/>
+      <c r="C10" s="89"/>
+      <c r="D10" s="75"/>
       <c r="E10" s="1">
         <v>2.9146692200000001E-2</v>
       </c>
@@ -8823,10 +8832,10 @@
       <c r="B12" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C12" s="76" t="s">
+      <c r="C12" s="75" t="s">
         <v>112</v>
       </c>
-      <c r="D12" s="76" t="s">
+      <c r="D12" s="75" t="s">
         <v>113</v>
       </c>
       <c r="E12" s="1">
@@ -8856,8 +8865,8 @@
       <c r="B13" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C13" s="76"/>
-      <c r="D13" s="76"/>
+      <c r="C13" s="75"/>
+      <c r="D13" s="75"/>
       <c r="E13" s="1">
         <v>0.42057865490000002</v>
       </c>
@@ -8885,8 +8894,8 @@
       <c r="B14" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C14" s="76"/>
-      <c r="D14" s="76"/>
+      <c r="C14" s="75"/>
+      <c r="D14" s="75"/>
       <c r="E14" s="1">
         <v>0.78884843839999996</v>
       </c>
@@ -8923,7 +8932,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E8BFB43-1DD7-8F42-9661-D6416FFA154E}">
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:L14"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="22.6640625" defaultRowHeight="21" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="34.5" style="1" customWidth="1"/>
@@ -8933,15 +8942,17 @@
     <col min="5" max="6" width="26.1640625" style="1" customWidth="1"/>
     <col min="7" max="9" width="22.6640625" style="1"/>
     <col min="10" max="10" width="27.1640625" style="1" customWidth="1"/>
-    <col min="11" max="16384" width="22.6640625" style="1"/>
+    <col min="11" max="11" width="22.6640625" style="1"/>
+    <col min="12" max="12" width="41.6640625" style="1" customWidth="1"/>
+    <col min="13" max="16384" width="22.6640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="89" customFormat="1" ht="27" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="89" t="s">
+    <row r="1" spans="1:12" s="71" customFormat="1" ht="27" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="71" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="2" spans="1:11" s="7" customFormat="1" ht="66" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:12" s="7" customFormat="1" ht="66" x14ac:dyDescent="0.2">
       <c r="A2" s="7" t="s">
         <v>0</v>
       </c>
@@ -8976,141 +8987,235 @@
         <v>121</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="69" t="s">
+    <row r="4" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="77" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="76" t="s">
+      <c r="C4" s="75" t="s">
         <v>47</v>
       </c>
-      <c r="D4" s="76" t="s">
+      <c r="D4" s="75" t="s">
         <v>109</v>
       </c>
-      <c r="G4" s="11"/>
-      <c r="H4" s="11"/>
-      <c r="I4" s="11"/>
+      <c r="E4" s="1">
+        <v>0.62550335570000004</v>
+      </c>
+      <c r="F4" s="1">
+        <v>0.85330776610000003</v>
+      </c>
+      <c r="G4" s="11">
+        <v>0.68249189440000002</v>
+      </c>
+      <c r="H4" s="11">
+        <v>0.40575916229999998</v>
+      </c>
+      <c r="I4" s="11">
+        <v>3.7593985000000003E-2</v>
+      </c>
+      <c r="J4" s="1">
+        <v>0.73139733309999999</v>
+      </c>
       <c r="K4" s="1">
-        <f>G4*1/3+H4*1/3+I4*1/3</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A5" s="69"/>
+        <f>(G4*1/3)+(H4*1/3)+(I4*1/3)</f>
+        <v>0.37528168056666661</v>
+      </c>
+      <c r="L4" s="90" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A5" s="77"/>
       <c r="B5" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="C5" s="76"/>
-      <c r="D5" s="76"/>
-      <c r="G5" s="11"/>
-      <c r="H5" s="11"/>
-      <c r="I5" s="11"/>
+      <c r="C5" s="75"/>
+      <c r="D5" s="75"/>
+      <c r="E5" s="1">
+        <v>0.82301054650000005</v>
+      </c>
+      <c r="F5" s="1">
+        <v>0.97066155320000003</v>
+      </c>
+      <c r="G5" s="11">
+        <v>0.97568318669999998</v>
+      </c>
+      <c r="H5" s="11">
+        <v>0.1020942408</v>
+      </c>
+      <c r="I5" s="11">
+        <v>7.5187969999999998E-3</v>
+      </c>
+      <c r="J5" s="1">
+        <v>0.83872653870000002</v>
+      </c>
       <c r="K5" s="1">
-        <f>G5*1/3+H5*1/3+I5*1/3</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A6" s="69"/>
+        <f>(G5*1/3)+(H5*1/3)+(I5*1/3)</f>
+        <v>0.36176540816666669</v>
+      </c>
+      <c r="L5" s="90"/>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A6" s="77"/>
       <c r="B6" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="C6" s="76"/>
-      <c r="D6" s="76"/>
+      <c r="C6" s="75"/>
+      <c r="D6" s="75"/>
       <c r="G6" s="11"/>
       <c r="H6" s="11"/>
       <c r="I6" s="11"/>
       <c r="K6" s="1">
-        <f>G6*1/3+H6*1/3+I6*1/3</f>
+        <f>(G6*1/3)+(H6*1/3)+(I6*1/3)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C7" s="76"/>
-      <c r="D7" s="76"/>
-    </row>
-    <row r="8" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="69" t="s">
+    <row r="7" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C7" s="75"/>
+      <c r="D7" s="75"/>
+    </row>
+    <row r="8" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="77" t="s">
         <v>124</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="C8" s="76"/>
-      <c r="D8" s="76"/>
+      <c r="C8" s="75"/>
+      <c r="D8" s="75"/>
+      <c r="E8" s="1">
+        <v>0.27497603069999998</v>
+      </c>
+      <c r="F8" s="1">
+        <v>0.69434324069999998</v>
+      </c>
+      <c r="G8" s="1">
+        <v>0.26401111630000001</v>
+      </c>
+      <c r="H8" s="1">
+        <v>0.31544502619999998</v>
+      </c>
+      <c r="I8" s="1">
+        <v>0.3984962406</v>
+      </c>
+      <c r="J8" s="1">
+        <v>0.46539974550000002</v>
+      </c>
       <c r="K8" s="1">
-        <f>G8*1/3+H8*1/3+I8*1/3</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A9" s="69"/>
+        <f>(G8*1/3)+(H8*1/3)+(I8*1/3)</f>
+        <v>0.32598412770000001</v>
+      </c>
+      <c r="L8" s="90" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A9" s="77"/>
       <c r="B9" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="C9" s="76"/>
-      <c r="D9" s="76"/>
+      <c r="C9" s="75"/>
+      <c r="D9" s="75"/>
+      <c r="E9" s="1">
+        <v>0.4669223394</v>
+      </c>
+      <c r="F9" s="1">
+        <v>0.77890699900000004</v>
+      </c>
+      <c r="G9" s="1">
+        <v>0.48286243629999998</v>
+      </c>
+      <c r="H9" s="1">
+        <v>0.38481675389999997</v>
+      </c>
+      <c r="I9" s="1">
+        <v>0.4210526316</v>
+      </c>
+      <c r="J9" s="1">
+        <v>0.56444247859999996</v>
+      </c>
       <c r="K9" s="1">
-        <f>G9*1/3+H9*1/3+I9*1/3</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="69"/>
+        <f>(G9*1/3)+(H9*1/3)+(I9*1/3)</f>
+        <v>0.42957727393333334</v>
+      </c>
+      <c r="L9" s="90"/>
+    </row>
+    <row r="10" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="77"/>
       <c r="B10" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="C10" s="76"/>
-      <c r="D10" s="76"/>
+      <c r="C10" s="75"/>
+      <c r="D10" s="75"/>
+      <c r="E10" s="1">
+        <v>0.57679769889999999</v>
+      </c>
+      <c r="F10" s="1">
+        <v>0.81054650049999999</v>
+      </c>
+      <c r="G10" s="1">
+        <v>0.62459471980000003</v>
+      </c>
+      <c r="H10" s="1">
+        <v>0.35078534030000003</v>
+      </c>
+      <c r="I10" s="1">
+        <v>0.32330827070000001</v>
+      </c>
+      <c r="J10" s="1">
+        <v>0.64231125950000001</v>
+      </c>
       <c r="K10" s="1">
-        <f>G10*1/3+H10*1/3+I10*1/3</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="C11" s="76"/>
-      <c r="D11" s="76"/>
-    </row>
-    <row r="12" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="69" t="s">
+        <f>(G10*1/3)+(H10*1/3)+(I10*1/3)</f>
+        <v>0.43289611026666669</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="C11" s="75"/>
+      <c r="D11" s="75"/>
+    </row>
+    <row r="12" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="77" t="s">
         <v>125</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="C12" s="76"/>
-      <c r="D12" s="76"/>
+      <c r="C12" s="75"/>
+      <c r="D12" s="75"/>
       <c r="K12" s="1">
-        <f>G12*1/3+H12*1/3+I12*1/3</f>
+        <f>(G12*1/3)+(H12*1/3)+(I12*1/3)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="69"/>
+    <row r="13" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="77"/>
       <c r="B13" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="C13" s="76"/>
-      <c r="D13" s="76"/>
+      <c r="C13" s="75"/>
+      <c r="D13" s="75"/>
       <c r="K13" s="1">
-        <f>G13*1/3+H13*1/3+I13*1/3</f>
+        <f>(G13*1/3)+(H13*1/3)+(I13*1/3)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C14" s="50"/>
       <c r="D14" s="50"/>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="8">
     <mergeCell ref="A8:A10"/>
     <mergeCell ref="A12:A13"/>
     <mergeCell ref="C4:C13"/>
     <mergeCell ref="D4:D13"/>
     <mergeCell ref="A1:XFD1"/>
     <mergeCell ref="A4:A6"/>
+    <mergeCell ref="L8:L9"/>
+    <mergeCell ref="L4:L5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/benchmarking/results/results.xlsx
+++ b/benchmarking/results/results.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11210"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10114"/>
   <workbookPr hidePivotFieldList="1" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/deborahdore/Documents/political-debates-graph-analysis/benchmarking/results/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B9E7A9B-A0E9-D64A-B40F-D53CC5E4DD04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B74AEAA0-B811-604F-84CD-0AD866031F06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="51200" windowHeight="28800" activeTab="5" xr2:uid="{E2EDC037-19C4-FE46-A599-BB595128A04F}"/>
+    <workbookView xWindow="4280" yWindow="500" windowWidth="46920" windowHeight="26600" activeTab="5" xr2:uid="{E2EDC037-19C4-FE46-A599-BB595128A04F}"/>
   </bookViews>
   <sheets>
     <sheet name="Basic" sheetId="1" r:id="rId1"/>
@@ -434,15 +434,9 @@
     <t>DO MODELS IN A FAMILY OF MODELS BEHAVE THE SAME?</t>
   </si>
   <si>
-    <t xml:space="preserve">WEIGHTED RELATION PREDICTION </t>
-  </si>
-  <si>
     <t>TransH</t>
   </si>
   <si>
-    <t>BoxE</t>
-  </si>
-  <si>
     <t xml:space="preserve">Semantic Matching </t>
   </si>
   <si>
@@ -468,6 +462,12 @@
   </si>
   <si>
     <t>GIVES MORE IMPORTANCE TO THE EQUIVALENT RELATION</t>
+  </si>
+  <si>
+    <t>TransD</t>
+  </si>
+  <si>
+    <t>WEIGHTED AVERAGE</t>
   </si>
 </sst>
 </file>
@@ -8984,7 +8984,7 @@
         <v>57</v>
       </c>
       <c r="K2" s="7" t="s">
-        <v>121</v>
+        <v>132</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.2">
@@ -9019,17 +9019,17 @@
         <v>0.73139733309999999</v>
       </c>
       <c r="K4" s="1">
-        <f>(G4*1/3)+(H4*1/3)+(I4*1/3)</f>
-        <v>0.37528168056666661</v>
+        <f>E4*1/5+G4*1/5+H4*1/5+I4*1/5+J4*1/5</f>
+        <v>0.49654914610000001</v>
       </c>
       <c r="L4" s="90" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="77"/>
       <c r="B5" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C5" s="75"/>
       <c r="D5" s="75"/>
@@ -9052,24 +9052,39 @@
         <v>0.83872653870000002</v>
       </c>
       <c r="K5" s="1">
-        <f>(G5*1/3)+(H5*1/3)+(I5*1/3)</f>
-        <v>0.36176540816666669</v>
+        <f>E5*1/5+G5*1/5+H5*1/5+I5*1/5+J5*1/5</f>
+        <v>0.5494066619400001</v>
       </c>
       <c r="L5" s="90"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" s="77"/>
       <c r="B6" s="1" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="C6" s="75"/>
       <c r="D6" s="75"/>
-      <c r="G6" s="11"/>
-      <c r="H6" s="11"/>
-      <c r="I6" s="11"/>
+      <c r="E6" s="1">
+        <v>0.52540747840000002</v>
+      </c>
+      <c r="F6" s="1">
+        <v>0.71831255989999998</v>
+      </c>
+      <c r="G6" s="11">
+        <v>0.54585456229999996</v>
+      </c>
+      <c r="H6" s="11">
+        <v>0.44502617799999999</v>
+      </c>
+      <c r="I6" s="11">
+        <v>0.32330827070000001</v>
+      </c>
+      <c r="J6" s="1">
+        <v>0.46895855479999998</v>
+      </c>
       <c r="K6" s="1">
-        <f>(G6*1/3)+(H6*1/3)+(I6*1/3)</f>
-        <v>0</v>
+        <f>E6*1/5+G6*1/5+H6*1/5+I6*1/5+J6*1/5</f>
+        <v>0.46171100883999999</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.2">
@@ -9078,10 +9093,10 @@
     </row>
     <row r="8" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="77" t="s">
+        <v>122</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>124</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>126</v>
       </c>
       <c r="C8" s="75"/>
       <c r="D8" s="75"/>
@@ -9104,17 +9119,17 @@
         <v>0.46539974550000002</v>
       </c>
       <c r="K8" s="1">
-        <f>(G8*1/3)+(H8*1/3)+(I8*1/3)</f>
-        <v>0.32598412770000001</v>
+        <f>E8*1/5+G8*1/5+H8*1/5+I8*1/5+J8*1/5</f>
+        <v>0.34366563185999999</v>
       </c>
       <c r="L8" s="90" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A9" s="77"/>
       <c r="B9" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C9" s="75"/>
       <c r="D9" s="75"/>
@@ -9137,15 +9152,15 @@
         <v>0.56444247859999996</v>
       </c>
       <c r="K9" s="1">
-        <f>(G9*1/3)+(H9*1/3)+(I9*1/3)</f>
-        <v>0.42957727393333334</v>
+        <f>E9*1/5+G9*1/5+H9*1/5+I9*1/5+J9*1/5</f>
+        <v>0.46401932795999995</v>
       </c>
       <c r="L9" s="90"/>
     </row>
     <row r="10" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="77"/>
       <c r="B10" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C10" s="75"/>
       <c r="D10" s="75"/>
@@ -9168,8 +9183,8 @@
         <v>0.64231125950000001</v>
       </c>
       <c r="K10" s="1">
-        <f>(G10*1/3)+(H10*1/3)+(I10*1/3)</f>
-        <v>0.43289611026666669</v>
+        <f>E10*1/5+G10*1/5+H10*1/5+I10*1/5+J10*1/5</f>
+        <v>0.50355945784</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
@@ -9178,27 +9193,45 @@
     </row>
     <row r="12" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="77" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C12" s="75"/>
       <c r="D12" s="75"/>
+      <c r="E12" s="1">
+        <v>0.15627996159999999</v>
+      </c>
+      <c r="F12" s="1">
+        <v>0.82396931929999995</v>
+      </c>
+      <c r="G12" s="1">
+        <v>1.5979620199999999E-2</v>
+      </c>
+      <c r="H12" s="1">
+        <v>0.96596858640000005</v>
+      </c>
+      <c r="I12" s="1">
+        <v>6.0150375899999997E-2</v>
+      </c>
+      <c r="J12" s="1">
+        <v>0.53981483360000004</v>
+      </c>
       <c r="K12" s="1">
-        <f>(G12*1/3)+(H12*1/3)+(I12*1/3)</f>
-        <v>0</v>
+        <f>E12*1/5+G12*1/5+H12*1/5+I12*1/5+J12*1/5</f>
+        <v>0.34763867554</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="77"/>
       <c r="B13" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C13" s="75"/>
       <c r="D13" s="75"/>
       <c r="K13" s="1">
-        <f>(G13*1/3)+(H13*1/3)+(I13*1/3)</f>
+        <f>E13*1/5+G13*1/5+H13*1/5+I13*1/5+J13*1/5</f>
         <v>0</v>
       </c>
     </row>

--- a/benchmarking/results/results.xlsx
+++ b/benchmarking/results/results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/deborahdore/Documents/political-debates-graph-analysis/benchmarking/results/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B74AEAA0-B811-604F-84CD-0AD866031F06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A7BCD03-7035-CC46-AE8B-94D33FA4ABAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4280" yWindow="500" windowWidth="46920" windowHeight="26600" activeTab="5" xr2:uid="{E2EDC037-19C4-FE46-A599-BB595128A04F}"/>
+    <workbookView xWindow="4280" yWindow="500" windowWidth="46920" windowHeight="26600" activeTab="3" xr2:uid="{E2EDC037-19C4-FE46-A599-BB595128A04F}"/>
   </bookViews>
   <sheets>
     <sheet name="Basic" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="654" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="652" uniqueCount="130">
   <si>
     <t>MODEL'S TYPE</t>
   </si>
@@ -233,15 +233,6 @@
   </si>
   <si>
     <t>WEIGHTED SUM OF ALL</t>
-  </si>
-  <si>
-    <t>1) WEIGHTED MEAN OF MAX LP, LD, TC:</t>
-  </si>
-  <si>
-    <t>2) WEIGHTED MEAN OF MAX RP, RC:</t>
-  </si>
-  <si>
-    <t>3 ) WEIGHTED MEAN OF MAX OF ALL:</t>
   </si>
   <si>
     <t>special/text_speaker_year</t>
@@ -458,24 +449,25 @@
     <t>ConvKB</t>
   </si>
   <si>
-    <t>BIASED TOWARDS SUPPORT</t>
-  </si>
-  <si>
-    <t>GIVES MORE IMPORTANCE TO THE EQUIVALENT RELATION</t>
-  </si>
-  <si>
     <t>TransD</t>
   </si>
   <si>
     <t>WEIGHTED AVERAGE</t>
+  </si>
+  <si>
+    <t>STANDARD DEVIATION</t>
+  </si>
+  <si>
+    <t>MIN:</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.0000000000"/>
+    <numFmt numFmtId="165" formatCode="0.0000"/>
   </numFmts>
   <fonts count="7" x14ac:knownFonts="1">
     <font>
@@ -532,7 +524,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -560,18 +552,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.14999847407452621"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -664,7 +644,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="91">
+  <cellXfs count="85">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -729,14 +709,11 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -747,16 +724,13 @@
     <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -765,43 +739,16 @@
     <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -840,31 +787,28 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -876,14 +820,29 @@
     <xf numFmtId="164" fontId="1" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -891,50 +850,53 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -944,9 +906,9 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
-      <color rgb="FFFFE699"/>
       <color rgb="FFE3EFDB"/>
       <color rgb="FFBED7EE"/>
+      <color rgb="FFFFE699"/>
     </mruColors>
   </colors>
   <extLst>
@@ -1274,46 +1236,46 @@
     <col min="12" max="16384" width="51.33203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="71" customFormat="1" ht="27" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="71" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" s="68" customFormat="1" ht="66" x14ac:dyDescent="0.2">
-      <c r="A2" s="68" t="s">
+    <row r="1" spans="1:12" s="65" customFormat="1" ht="27" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="65" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" s="56" customFormat="1" ht="66" x14ac:dyDescent="0.2">
+      <c r="A2" s="56" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="68" t="s">
+      <c r="B2" s="56" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="69" t="s">
+      <c r="C2" s="57" t="s">
         <v>40</v>
       </c>
-      <c r="D2" s="69" t="s">
+      <c r="D2" s="57" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="69" t="s">
+      <c r="E2" s="57" t="s">
         <v>12</v>
       </c>
-      <c r="F2" s="70" t="s">
+      <c r="F2" s="58" t="s">
         <v>53</v>
       </c>
-      <c r="G2" s="70" t="s">
+      <c r="G2" s="58" t="s">
         <v>54</v>
       </c>
-      <c r="H2" s="70" t="s">
+      <c r="H2" s="58" t="s">
         <v>55</v>
       </c>
-      <c r="I2" s="70" t="s">
+      <c r="I2" s="58" t="s">
         <v>56</v>
       </c>
-      <c r="J2" s="70" t="s">
-        <v>82</v>
-      </c>
-      <c r="K2" s="69" t="s">
+      <c r="J2" s="58" t="s">
+        <v>79</v>
+      </c>
+      <c r="K2" s="57" t="s">
         <v>14</v>
       </c>
-      <c r="L2" s="69"/>
+      <c r="L2" s="57"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
@@ -1322,13 +1284,13 @@
       <c r="B3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="79" t="s">
+      <c r="C3" s="64" t="s">
         <v>41</v>
       </c>
-      <c r="D3" s="76" t="s">
+      <c r="D3" s="63" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="76" t="s">
+      <c r="E3" s="63" t="s">
         <v>13</v>
       </c>
       <c r="F3" s="11">
@@ -1346,7 +1308,7 @@
       <c r="J3" s="11">
         <v>0.52440008120000003</v>
       </c>
-      <c r="K3" s="74" t="s">
+      <c r="K3" s="67" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1357,9 +1319,9 @@
       <c r="B4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="77"/>
-      <c r="D4" s="73"/>
-      <c r="E4" s="73"/>
+      <c r="C4" s="60"/>
+      <c r="D4" s="61"/>
+      <c r="E4" s="61"/>
       <c r="F4" s="11">
         <v>3.9117929099999997E-2</v>
       </c>
@@ -1375,7 +1337,7 @@
       <c r="J4" s="11">
         <v>0.4957882649</v>
       </c>
-      <c r="K4" s="75"/>
+      <c r="K4" s="68"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
@@ -1384,9 +1346,9 @@
       <c r="B5" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="77"/>
-      <c r="D5" s="73"/>
-      <c r="E5" s="73"/>
+      <c r="C5" s="60"/>
+      <c r="D5" s="61"/>
+      <c r="E5" s="61"/>
       <c r="F5" s="11">
         <v>2.1093001000000002E-3</v>
       </c>
@@ -1402,7 +1364,7 @@
       <c r="J5" s="11">
         <v>0.4776301698</v>
       </c>
-      <c r="K5" s="75"/>
+      <c r="K5" s="68"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
@@ -1411,13 +1373,13 @@
       <c r="B7" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="77" t="s">
+      <c r="C7" s="60" t="s">
         <v>42</v>
       </c>
-      <c r="D7" s="73" t="s">
+      <c r="D7" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="E7" s="73" t="s">
+      <c r="E7" s="61" t="s">
         <v>13</v>
       </c>
       <c r="F7" s="11">
@@ -1435,7 +1397,7 @@
       <c r="J7" s="11">
         <v>0.51801477490000003</v>
       </c>
-      <c r="K7" s="75" t="s">
+      <c r="K7" s="68" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1446,9 +1408,9 @@
       <c r="B8" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="77"/>
-      <c r="D8" s="73"/>
-      <c r="E8" s="73"/>
+      <c r="C8" s="60"/>
+      <c r="D8" s="61"/>
+      <c r="E8" s="61"/>
       <c r="F8" s="11">
         <v>3.2094270899999999E-2</v>
       </c>
@@ -1464,7 +1426,7 @@
       <c r="J8" s="11">
         <v>0.50083099880000004</v>
       </c>
-      <c r="K8" s="75"/>
+      <c r="K8" s="68"/>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
@@ -1473,9 +1435,9 @@
       <c r="B9" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="77"/>
-      <c r="D9" s="73"/>
-      <c r="E9" s="73"/>
+      <c r="C9" s="60"/>
+      <c r="D9" s="61"/>
+      <c r="E9" s="61"/>
       <c r="F9" s="11">
         <v>2.8741139999999998E-4</v>
       </c>
@@ -1491,22 +1453,22 @@
       <c r="J9" s="11">
         <v>0.4887305689</v>
       </c>
-      <c r="K9" s="75"/>
-    </row>
-    <row r="11" spans="1:12" s="59" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="78" t="s">
+      <c r="K9" s="68"/>
+    </row>
+    <row r="11" spans="1:12" s="48" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="62" t="s">
         <v>37</v>
       </c>
-      <c r="B11" s="78"/>
-      <c r="C11" s="78"/>
-      <c r="D11" s="78"/>
-      <c r="E11" s="60"/>
-      <c r="F11" s="61"/>
-      <c r="G11" s="61"/>
-      <c r="H11" s="61"/>
-      <c r="I11" s="61"/>
-      <c r="J11" s="61"/>
-      <c r="K11" s="60"/>
+      <c r="B11" s="62"/>
+      <c r="C11" s="62"/>
+      <c r="D11" s="62"/>
+      <c r="E11" s="49"/>
+      <c r="F11" s="50"/>
+      <c r="G11" s="50"/>
+      <c r="H11" s="50"/>
+      <c r="I11" s="50"/>
+      <c r="J11" s="50"/>
+      <c r="K11" s="49"/>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
@@ -1515,13 +1477,13 @@
       <c r="B13" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C13" s="77" t="s">
+      <c r="C13" s="60" t="s">
         <v>43</v>
       </c>
-      <c r="D13" s="73" t="s">
+      <c r="D13" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="E13" s="73" t="s">
+      <c r="E13" s="61" t="s">
         <v>17</v>
       </c>
       <c r="F13" s="11">
@@ -1539,7 +1501,7 @@
       <c r="J13" s="11">
         <v>0.65087326729999995</v>
       </c>
-      <c r="K13" s="75" t="s">
+      <c r="K13" s="68" t="s">
         <v>18</v>
       </c>
     </row>
@@ -1550,9 +1512,9 @@
       <c r="B14" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C14" s="77"/>
-      <c r="D14" s="73"/>
-      <c r="E14" s="73"/>
+      <c r="C14" s="60"/>
+      <c r="D14" s="61"/>
+      <c r="E14" s="61"/>
       <c r="F14" s="11">
         <v>1.0937623800000001E-2</v>
       </c>
@@ -1568,7 +1530,7 @@
       <c r="J14" s="11">
         <v>0.48031703009999999</v>
       </c>
-      <c r="K14" s="75"/>
+      <c r="K14" s="68"/>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
@@ -1577,9 +1539,9 @@
       <c r="B15" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C15" s="77"/>
-      <c r="D15" s="73"/>
-      <c r="E15" s="73"/>
+      <c r="C15" s="60"/>
+      <c r="D15" s="61"/>
+      <c r="E15" s="61"/>
       <c r="F15" s="11">
         <v>2.377744E-4</v>
       </c>
@@ -1595,7 +1557,7 @@
       <c r="J15" s="11">
         <v>0.49770047779999999</v>
       </c>
-      <c r="K15" s="75"/>
+      <c r="K15" s="68"/>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
@@ -1604,13 +1566,13 @@
       <c r="B17" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C17" s="77" t="s">
+      <c r="C17" s="60" t="s">
         <v>44</v>
       </c>
-      <c r="D17" s="73" t="s">
+      <c r="D17" s="61" t="s">
         <v>19</v>
       </c>
-      <c r="E17" s="73" t="s">
+      <c r="E17" s="61" t="s">
         <v>27</v>
       </c>
       <c r="F17" s="11">
@@ -1628,7 +1590,7 @@
       <c r="J17" s="11">
         <v>0.44106115289999998</v>
       </c>
-      <c r="K17" s="75" t="s">
+      <c r="K17" s="68" t="s">
         <v>36</v>
       </c>
     </row>
@@ -1639,9 +1601,9 @@
       <c r="B18" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C18" s="77"/>
-      <c r="D18" s="73"/>
-      <c r="E18" s="73"/>
+      <c r="C18" s="60"/>
+      <c r="D18" s="61"/>
+      <c r="E18" s="61"/>
       <c r="F18" s="11">
         <v>6.6187922000000001E-3</v>
       </c>
@@ -1657,7 +1619,7 @@
       <c r="J18" s="11">
         <v>0.48203358359999998</v>
       </c>
-      <c r="K18" s="75"/>
+      <c r="K18" s="68"/>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
@@ -1666,9 +1628,9 @@
       <c r="B19" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C19" s="77"/>
-      <c r="D19" s="73"/>
-      <c r="E19" s="73"/>
+      <c r="C19" s="60"/>
+      <c r="D19" s="61"/>
+      <c r="E19" s="61"/>
       <c r="F19" s="11">
         <v>1.9467035999999999E-3</v>
       </c>
@@ -1684,7 +1646,7 @@
       <c r="J19" s="11">
         <v>0.31319458500000003</v>
       </c>
-      <c r="K19" s="75"/>
+      <c r="K19" s="68"/>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
@@ -1693,13 +1655,13 @@
       <c r="B21" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C21" s="77" t="s">
+      <c r="C21" s="60" t="s">
         <v>45</v>
       </c>
-      <c r="D21" s="73" t="s">
+      <c r="D21" s="61" t="s">
         <v>20</v>
       </c>
-      <c r="E21" s="73" t="s">
+      <c r="E21" s="61" t="s">
         <v>28</v>
       </c>
       <c r="F21" s="11">
@@ -1717,7 +1679,7 @@
       <c r="J21" s="11">
         <v>0.42558258160000001</v>
       </c>
-      <c r="K21" s="75" t="s">
+      <c r="K21" s="68" t="s">
         <v>35</v>
       </c>
     </row>
@@ -1728,9 +1690,9 @@
       <c r="B22" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C22" s="77"/>
-      <c r="D22" s="73"/>
-      <c r="E22" s="73"/>
+      <c r="C22" s="60"/>
+      <c r="D22" s="61"/>
+      <c r="E22" s="61"/>
       <c r="F22" s="11">
         <v>0.36964094320000002</v>
       </c>
@@ -1746,7 +1708,7 @@
       <c r="J22" s="11">
         <v>0.71370811339999995</v>
       </c>
-      <c r="K22" s="75"/>
+      <c r="K22" s="68"/>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
@@ -1755,9 +1717,9 @@
       <c r="B23" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C23" s="77"/>
-      <c r="D23" s="73"/>
-      <c r="E23" s="73"/>
+      <c r="C23" s="60"/>
+      <c r="D23" s="61"/>
+      <c r="E23" s="61"/>
       <c r="F23" s="11">
         <v>1.786352E-4</v>
       </c>
@@ -1773,7 +1735,7 @@
       <c r="J23" s="11">
         <v>0.35677707139999998</v>
       </c>
-      <c r="K23" s="75"/>
+      <c r="K23" s="68"/>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
@@ -1782,13 +1744,13 @@
       <c r="B25" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C25" s="77" t="s">
+      <c r="C25" s="60" t="s">
         <v>46</v>
       </c>
-      <c r="D25" s="73" t="s">
+      <c r="D25" s="61" t="s">
         <v>21</v>
       </c>
-      <c r="E25" s="73" t="s">
+      <c r="E25" s="61" t="s">
         <v>32</v>
       </c>
       <c r="F25" s="11">
@@ -1814,9 +1776,9 @@
       <c r="B26" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C26" s="77"/>
-      <c r="D26" s="73"/>
-      <c r="E26" s="73"/>
+      <c r="C26" s="60"/>
+      <c r="D26" s="61"/>
+      <c r="E26" s="61"/>
       <c r="F26" s="11">
         <v>2.2257384000000002E-2</v>
       </c>
@@ -1840,9 +1802,9 @@
       <c r="B27" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C27" s="77"/>
-      <c r="D27" s="73"/>
-      <c r="E27" s="73"/>
+      <c r="C27" s="60"/>
+      <c r="D27" s="61"/>
+      <c r="E27" s="61"/>
       <c r="F27" s="11">
         <v>3.9556960000000001E-4</v>
       </c>
@@ -1866,13 +1828,13 @@
       <c r="B29" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C29" s="77" t="s">
+      <c r="C29" s="60" t="s">
         <v>47</v>
       </c>
-      <c r="D29" s="73" t="s">
+      <c r="D29" s="61" t="s">
         <v>22</v>
       </c>
-      <c r="E29" s="73" t="s">
+      <c r="E29" s="61" t="s">
         <v>33</v>
       </c>
       <c r="F29" s="11">
@@ -1898,9 +1860,9 @@
       <c r="B30" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C30" s="77"/>
-      <c r="D30" s="73"/>
-      <c r="E30" s="73"/>
+      <c r="C30" s="60"/>
+      <c r="D30" s="61"/>
+      <c r="E30" s="61"/>
       <c r="F30" s="11">
         <v>1.8442843300000001E-2</v>
       </c>
@@ -1924,9 +1886,9 @@
       <c r="B31" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C31" s="77"/>
-      <c r="D31" s="73"/>
-      <c r="E31" s="73"/>
+      <c r="C31" s="60"/>
+      <c r="D31" s="61"/>
+      <c r="E31" s="61"/>
       <c r="F31" s="11">
         <v>6.9899990000000004E-4</v>
       </c>
@@ -1950,13 +1912,13 @@
       <c r="B33" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C33" s="77" t="s">
+      <c r="C33" s="60" t="s">
         <v>48</v>
       </c>
-      <c r="D33" s="73" t="s">
+      <c r="D33" s="61" t="s">
         <v>23</v>
       </c>
-      <c r="E33" s="73" t="s">
+      <c r="E33" s="61" t="s">
         <v>29</v>
       </c>
       <c r="F33" s="11">
@@ -1982,9 +1944,9 @@
       <c r="B34" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C34" s="77"/>
-      <c r="D34" s="73"/>
-      <c r="E34" s="73"/>
+      <c r="C34" s="60"/>
+      <c r="D34" s="61"/>
+      <c r="E34" s="61"/>
       <c r="F34" s="11">
         <v>4.8571429999999999E-4</v>
       </c>
@@ -2008,9 +1970,9 @@
       <c r="B35" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C35" s="77"/>
-      <c r="D35" s="73"/>
-      <c r="E35" s="73"/>
+      <c r="C35" s="60"/>
+      <c r="D35" s="61"/>
+      <c r="E35" s="61"/>
       <c r="F35" s="11">
         <v>8.5714299999999993E-5</v>
       </c>
@@ -2034,13 +1996,13 @@
       <c r="B37" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C37" s="77" t="s">
+      <c r="C37" s="60" t="s">
         <v>49</v>
       </c>
-      <c r="D37" s="73" t="s">
+      <c r="D37" s="61" t="s">
         <v>24</v>
       </c>
-      <c r="E37" s="73" t="s">
+      <c r="E37" s="61" t="s">
         <v>34</v>
       </c>
       <c r="F37" s="11">
@@ -2066,9 +2028,9 @@
       <c r="B38" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C38" s="77"/>
-      <c r="D38" s="73"/>
-      <c r="E38" s="73"/>
+      <c r="C38" s="60"/>
+      <c r="D38" s="61"/>
+      <c r="E38" s="61"/>
       <c r="F38" s="11">
         <v>0.12567659680000001</v>
       </c>
@@ -2092,9 +2054,9 @@
       <c r="B39" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C39" s="77"/>
-      <c r="D39" s="73"/>
-      <c r="E39" s="73"/>
+      <c r="C39" s="60"/>
+      <c r="D39" s="61"/>
+      <c r="E39" s="61"/>
       <c r="F39" s="11">
         <v>5.4127739999999998E-4</v>
       </c>
@@ -2111,20 +2073,20 @@
         <v>0.24669741079999999</v>
       </c>
     </row>
-    <row r="41" spans="1:11" s="59" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="78" t="s">
+    <row r="41" spans="1:11" s="48" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="62" t="s">
         <v>38</v>
       </c>
-      <c r="B41" s="78"/>
-      <c r="C41" s="78"/>
-      <c r="D41" s="78"/>
-      <c r="E41" s="60"/>
-      <c r="F41" s="61"/>
-      <c r="G41" s="61"/>
-      <c r="H41" s="61"/>
-      <c r="I41" s="61"/>
-      <c r="J41" s="61"/>
-      <c r="K41" s="60"/>
+      <c r="B41" s="62"/>
+      <c r="C41" s="62"/>
+      <c r="D41" s="62"/>
+      <c r="E41" s="49"/>
+      <c r="F41" s="50"/>
+      <c r="G41" s="50"/>
+      <c r="H41" s="50"/>
+      <c r="I41" s="50"/>
+      <c r="J41" s="50"/>
+      <c r="K41" s="49"/>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
@@ -2133,13 +2095,13 @@
       <c r="B43" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C43" s="77" t="s">
+      <c r="C43" s="60" t="s">
         <v>50</v>
       </c>
-      <c r="D43" s="73" t="s">
+      <c r="D43" s="61" t="s">
         <v>25</v>
       </c>
-      <c r="E43" s="73" t="s">
+      <c r="E43" s="61" t="s">
         <v>27</v>
       </c>
       <c r="F43" s="11">
@@ -2157,7 +2119,7 @@
       <c r="J43" s="11">
         <v>0.47978398890000001</v>
       </c>
-      <c r="K43" s="75" t="s">
+      <c r="K43" s="68" t="s">
         <v>30</v>
       </c>
     </row>
@@ -2168,9 +2130,9 @@
       <c r="B44" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C44" s="77"/>
-      <c r="D44" s="73"/>
-      <c r="E44" s="73"/>
+      <c r="C44" s="60"/>
+      <c r="D44" s="61"/>
+      <c r="E44" s="61"/>
       <c r="F44" s="11">
         <v>0.15768715</v>
       </c>
@@ -2186,7 +2148,7 @@
       <c r="J44" s="11">
         <v>0.64265883619999997</v>
       </c>
-      <c r="K44" s="75"/>
+      <c r="K44" s="68"/>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
@@ -2195,9 +2157,9 @@
       <c r="B45" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C45" s="77"/>
-      <c r="D45" s="73"/>
-      <c r="E45" s="73"/>
+      <c r="C45" s="60"/>
+      <c r="D45" s="61"/>
+      <c r="E45" s="61"/>
       <c r="F45" s="11">
         <v>1.5776599999999999E-4</v>
       </c>
@@ -2213,7 +2175,7 @@
       <c r="J45" s="11">
         <v>0.33957444949999999</v>
       </c>
-      <c r="K45" s="75"/>
+      <c r="K45" s="68"/>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A47" s="1" t="s">
@@ -2222,13 +2184,13 @@
       <c r="B47" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C47" s="77" t="s">
+      <c r="C47" s="60" t="s">
         <v>51</v>
       </c>
-      <c r="D47" s="73" t="s">
+      <c r="D47" s="61" t="s">
         <v>26</v>
       </c>
-      <c r="E47" s="73" t="s">
+      <c r="E47" s="61" t="s">
         <v>28</v>
       </c>
       <c r="F47" s="11">
@@ -2246,7 +2208,7 @@
       <c r="J47" s="11">
         <v>0.43650638670000003</v>
       </c>
-      <c r="K47" s="75" t="s">
+      <c r="K47" s="68" t="s">
         <v>31</v>
       </c>
     </row>
@@ -2257,9 +2219,9 @@
       <c r="B48" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C48" s="77"/>
-      <c r="D48" s="73"/>
-      <c r="E48" s="73"/>
+      <c r="C48" s="60"/>
+      <c r="D48" s="61"/>
+      <c r="E48" s="61"/>
       <c r="F48" s="11">
         <v>0.28846457310000001</v>
       </c>
@@ -2275,7 +2237,7 @@
       <c r="J48" s="11">
         <v>0.62979789600000002</v>
       </c>
-      <c r="K48" s="75"/>
+      <c r="K48" s="68"/>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A49" s="1" t="s">
@@ -2284,9 +2246,9 @@
       <c r="B49" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C49" s="77"/>
-      <c r="D49" s="73"/>
-      <c r="E49" s="73"/>
+      <c r="C49" s="60"/>
+      <c r="D49" s="61"/>
+      <c r="E49" s="61"/>
       <c r="F49" s="11">
         <v>2.7615590000000002E-4</v>
       </c>
@@ -2302,7 +2264,7 @@
       <c r="J49" s="11">
         <v>0.39453545410000002</v>
       </c>
-      <c r="K49" s="75"/>
+      <c r="K49" s="68"/>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A51" s="1" t="s">
@@ -2311,13 +2273,13 @@
       <c r="B51" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C51" s="77" t="s">
+      <c r="C51" s="60" t="s">
         <v>52</v>
       </c>
-      <c r="D51" s="73" t="s">
+      <c r="D51" s="61" t="s">
         <v>39</v>
       </c>
-      <c r="E51" s="73" t="s">
+      <c r="E51" s="61" t="s">
         <v>29</v>
       </c>
       <c r="F51" s="11">
@@ -2343,9 +2305,9 @@
       <c r="B52" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C52" s="77"/>
-      <c r="D52" s="73"/>
-      <c r="E52" s="73"/>
+      <c r="C52" s="60"/>
+      <c r="D52" s="61"/>
+      <c r="E52" s="61"/>
       <c r="F52" s="11">
         <v>3.5391416699999997E-2</v>
       </c>
@@ -2369,9 +2331,9 @@
       <c r="B53" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C53" s="77"/>
-      <c r="D53" s="73"/>
-      <c r="E53" s="73"/>
+      <c r="C53" s="60"/>
+      <c r="D53" s="61"/>
+      <c r="E53" s="61"/>
       <c r="F53" s="11">
         <v>9.9344299999999997E-5</v>
       </c>
@@ -2388,68 +2350,100 @@
         <v>0.49504548949999999</v>
       </c>
     </row>
-    <row r="56" spans="1:11" s="42" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="80" t="s">
+    <row r="56" spans="1:11" s="31" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A56" s="59" t="s">
         <v>59</v>
       </c>
-      <c r="B56" s="80"/>
-      <c r="C56" s="80"/>
-      <c r="D56" s="80"/>
-      <c r="E56" s="39"/>
-      <c r="F56" s="40">
+      <c r="B56" s="59"/>
+      <c r="C56" s="59"/>
+      <c r="D56" s="59"/>
+      <c r="E56" s="28"/>
+      <c r="F56" s="29">
         <f>MAX(F3:F53)</f>
         <v>0.39523043940000002</v>
       </c>
-      <c r="G56" s="40">
+      <c r="G56" s="29">
         <f>MAX(G3:G53)</f>
         <v>0.24390032880000001</v>
       </c>
-      <c r="H56" s="40">
+      <c r="H56" s="29">
         <f>MAX(H3:H53)</f>
         <v>1</v>
       </c>
-      <c r="I56" s="40">
+      <c r="I56" s="29">
         <f>MAX(I3:I53)</f>
         <v>0.87609028769999997</v>
       </c>
-      <c r="J56" s="40">
+      <c r="J56" s="29">
         <f>MAX(J3:J53)</f>
         <v>0.71370811339999995</v>
       </c>
-      <c r="K56" s="41"/>
-    </row>
-    <row r="57" spans="1:11" s="46" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="72" t="s">
+      <c r="K56" s="30"/>
+    </row>
+    <row r="57" spans="1:11" s="35" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A57" s="66" t="s">
         <v>60</v>
       </c>
-      <c r="B57" s="72"/>
-      <c r="C57" s="72"/>
-      <c r="D57" s="72"/>
-      <c r="E57" s="43"/>
-      <c r="F57" s="44">
+      <c r="B57" s="66"/>
+      <c r="C57" s="66"/>
+      <c r="D57" s="66"/>
+      <c r="E57" s="32"/>
+      <c r="F57" s="33">
         <f>AVERAGE(F3:F53)</f>
         <v>0.11288026050555554</v>
       </c>
-      <c r="G57" s="44">
+      <c r="G57" s="33">
         <f>AVERAGE(G3:G53)</f>
         <v>4.7862085486111108E-2</v>
       </c>
-      <c r="H57" s="44">
+      <c r="H57" s="33">
         <f>AVERAGE(H3:H53)</f>
         <v>0.54284128776111118</v>
       </c>
-      <c r="I57" s="44">
+      <c r="I57" s="33">
         <f>AVERAGE(I3:I53)</f>
         <v>0.66250185551944452</v>
       </c>
-      <c r="J57" s="44">
+      <c r="J57" s="33">
         <f>AVERAGE(J3:J53)</f>
         <v>0.48710133090555563</v>
       </c>
-      <c r="K57" s="45"/>
+      <c r="K57" s="34"/>
     </row>
   </sheetData>
   <mergeCells count="48">
+    <mergeCell ref="A1:XFD1"/>
+    <mergeCell ref="A57:D57"/>
+    <mergeCell ref="E51:E53"/>
+    <mergeCell ref="K3:K5"/>
+    <mergeCell ref="K7:K9"/>
+    <mergeCell ref="K13:K15"/>
+    <mergeCell ref="K17:K19"/>
+    <mergeCell ref="K21:K23"/>
+    <mergeCell ref="K43:K45"/>
+    <mergeCell ref="K47:K49"/>
+    <mergeCell ref="E25:E27"/>
+    <mergeCell ref="E29:E31"/>
+    <mergeCell ref="E33:E35"/>
+    <mergeCell ref="E37:E39"/>
+    <mergeCell ref="E43:E45"/>
+    <mergeCell ref="E3:E5"/>
+    <mergeCell ref="C29:C31"/>
+    <mergeCell ref="C33:C35"/>
+    <mergeCell ref="C37:C39"/>
+    <mergeCell ref="E47:E49"/>
+    <mergeCell ref="E7:E9"/>
+    <mergeCell ref="E13:E15"/>
+    <mergeCell ref="E17:E19"/>
+    <mergeCell ref="E21:E23"/>
+    <mergeCell ref="C43:C45"/>
+    <mergeCell ref="D3:D5"/>
+    <mergeCell ref="D7:D9"/>
+    <mergeCell ref="D13:D15"/>
+    <mergeCell ref="D17:D19"/>
+    <mergeCell ref="D21:D23"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="C3:C5"/>
     <mergeCell ref="A56:D56"/>
     <mergeCell ref="C7:C9"/>
     <mergeCell ref="C13:C15"/>
@@ -2466,38 +2460,6 @@
     <mergeCell ref="D51:D53"/>
     <mergeCell ref="A41:D41"/>
     <mergeCell ref="C47:C49"/>
-    <mergeCell ref="D3:D5"/>
-    <mergeCell ref="D7:D9"/>
-    <mergeCell ref="D13:D15"/>
-    <mergeCell ref="D17:D19"/>
-    <mergeCell ref="D21:D23"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="C3:C5"/>
-    <mergeCell ref="C29:C31"/>
-    <mergeCell ref="C33:C35"/>
-    <mergeCell ref="C37:C39"/>
-    <mergeCell ref="E47:E49"/>
-    <mergeCell ref="E7:E9"/>
-    <mergeCell ref="E13:E15"/>
-    <mergeCell ref="E17:E19"/>
-    <mergeCell ref="E21:E23"/>
-    <mergeCell ref="C43:C45"/>
-    <mergeCell ref="A1:XFD1"/>
-    <mergeCell ref="A57:D57"/>
-    <mergeCell ref="E51:E53"/>
-    <mergeCell ref="K3:K5"/>
-    <mergeCell ref="K7:K9"/>
-    <mergeCell ref="K13:K15"/>
-    <mergeCell ref="K17:K19"/>
-    <mergeCell ref="K21:K23"/>
-    <mergeCell ref="K43:K45"/>
-    <mergeCell ref="K47:K49"/>
-    <mergeCell ref="E25:E27"/>
-    <mergeCell ref="E29:E31"/>
-    <mergeCell ref="E33:E35"/>
-    <mergeCell ref="E37:E39"/>
-    <mergeCell ref="E43:E45"/>
-    <mergeCell ref="E3:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2522,9 +2484,9 @@
     <col min="12" max="16384" width="51.33203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="71" customFormat="1" ht="27" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="71" t="s">
-        <v>116</v>
+    <row r="1" spans="1:12" s="65" customFormat="1" ht="27" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="65" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="2" spans="1:12" s="6" customFormat="1" ht="66" x14ac:dyDescent="0.2">
@@ -2570,13 +2532,13 @@
       <c r="B3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="79" t="s">
+      <c r="C3" s="64" t="s">
         <v>41</v>
       </c>
-      <c r="D3" s="76" t="s">
+      <c r="D3" s="63" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="76" t="s">
+      <c r="E3" s="63" t="s">
         <v>13</v>
       </c>
       <c r="F3" s="11">
@@ -2594,7 +2556,7 @@
       <c r="J3" s="11">
         <v>0.5008326072</v>
       </c>
-      <c r="K3" s="74" t="s">
+      <c r="K3" s="67" t="s">
         <v>15</v>
       </c>
     </row>
@@ -2605,9 +2567,9 @@
       <c r="B4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="77"/>
-      <c r="D4" s="73"/>
-      <c r="E4" s="73"/>
+      <c r="C4" s="60"/>
+      <c r="D4" s="61"/>
+      <c r="E4" s="61"/>
       <c r="F4" s="11">
         <v>2.8763183099999999E-2</v>
       </c>
@@ -2623,7 +2585,7 @@
       <c r="J4" s="11">
         <v>0.49456959480000001</v>
       </c>
-      <c r="K4" s="75"/>
+      <c r="K4" s="68"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
@@ -2632,9 +2594,9 @@
       <c r="B5" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="77"/>
-      <c r="D5" s="73"/>
-      <c r="E5" s="73"/>
+      <c r="C5" s="60"/>
+      <c r="D5" s="61"/>
+      <c r="E5" s="61"/>
       <c r="F5" s="11">
         <v>5.7526370000000003E-4</v>
       </c>
@@ -2650,7 +2612,7 @@
       <c r="J5" s="11">
         <v>0.46208879800000002</v>
       </c>
-      <c r="K5" s="75"/>
+      <c r="K5" s="68"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="G6" s="11"/>
@@ -2665,13 +2627,13 @@
       <c r="B7" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="77" t="s">
+      <c r="C7" s="60" t="s">
         <v>42</v>
       </c>
-      <c r="D7" s="73" t="s">
+      <c r="D7" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="E7" s="73" t="s">
+      <c r="E7" s="61" t="s">
         <v>13</v>
       </c>
       <c r="F7" s="11">
@@ -2689,7 +2651,7 @@
       <c r="J7" s="11">
         <v>0.50993042769999997</v>
       </c>
-      <c r="K7" s="75" t="s">
+      <c r="K7" s="68" t="s">
         <v>16</v>
       </c>
     </row>
@@ -2700,9 +2662,9 @@
       <c r="B8" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="77"/>
-      <c r="D8" s="73"/>
-      <c r="E8" s="73"/>
+      <c r="C8" s="60"/>
+      <c r="D8" s="61"/>
+      <c r="E8" s="61"/>
       <c r="F8" s="11">
         <v>3.3435524000000001E-2</v>
       </c>
@@ -2718,7 +2680,7 @@
       <c r="J8" s="11">
         <v>0.50392556320000004</v>
       </c>
-      <c r="K8" s="75"/>
+      <c r="K8" s="68"/>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
@@ -2727,9 +2689,9 @@
       <c r="B9" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="77"/>
-      <c r="D9" s="73"/>
-      <c r="E9" s="73"/>
+      <c r="C9" s="60"/>
+      <c r="D9" s="61"/>
+      <c r="E9" s="61"/>
       <c r="F9" s="11">
         <v>3.8321520000000002E-4</v>
       </c>
@@ -2745,7 +2707,7 @@
       <c r="J9" s="11">
         <v>0.47738500210000001</v>
       </c>
-      <c r="K9" s="75"/>
+      <c r="K9" s="68"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="G10" s="11"/>
@@ -2753,20 +2715,20 @@
       <c r="I10" s="11"/>
       <c r="J10" s="11"/>
     </row>
-    <row r="11" spans="1:12" s="59" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="78" t="s">
+    <row r="11" spans="1:12" s="48" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="62" t="s">
         <v>37</v>
       </c>
-      <c r="B11" s="78"/>
-      <c r="C11" s="78"/>
-      <c r="D11" s="78"/>
-      <c r="E11" s="60"/>
-      <c r="F11" s="61"/>
-      <c r="G11" s="61"/>
-      <c r="H11" s="61"/>
-      <c r="I11" s="61"/>
-      <c r="J11" s="61"/>
-      <c r="K11" s="60"/>
+      <c r="B11" s="62"/>
+      <c r="C11" s="62"/>
+      <c r="D11" s="62"/>
+      <c r="E11" s="49"/>
+      <c r="F11" s="50"/>
+      <c r="G11" s="50"/>
+      <c r="H11" s="50"/>
+      <c r="I11" s="50"/>
+      <c r="J11" s="50"/>
+      <c r="K11" s="49"/>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="G12" s="11"/>
@@ -2781,13 +2743,13 @@
       <c r="B13" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C13" s="77" t="s">
+      <c r="C13" s="60" t="s">
         <v>43</v>
       </c>
-      <c r="D13" s="73" t="s">
+      <c r="D13" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="E13" s="73" t="s">
+      <c r="E13" s="61" t="s">
         <v>17</v>
       </c>
       <c r="F13" s="11">
@@ -2805,7 +2767,7 @@
       <c r="J13" s="11">
         <v>0.4966675035</v>
       </c>
-      <c r="K13" s="75" t="s">
+      <c r="K13" s="68" t="s">
         <v>18</v>
       </c>
     </row>
@@ -2816,9 +2778,9 @@
       <c r="B14" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C14" s="77"/>
-      <c r="D14" s="73"/>
-      <c r="E14" s="73"/>
+      <c r="C14" s="60"/>
+      <c r="D14" s="61"/>
+      <c r="E14" s="61"/>
       <c r="F14" s="11">
         <v>2.876318E-4</v>
       </c>
@@ -2834,7 +2796,7 @@
       <c r="J14" s="11">
         <v>0.48225264400000001</v>
       </c>
-      <c r="K14" s="75"/>
+      <c r="K14" s="68"/>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
@@ -2843,9 +2805,9 @@
       <c r="B15" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C15" s="77"/>
-      <c r="D15" s="73"/>
-      <c r="E15" s="73"/>
+      <c r="C15" s="60"/>
+      <c r="D15" s="61"/>
+      <c r="E15" s="61"/>
       <c r="F15" s="11">
         <v>6.7114089999999996E-4</v>
       </c>
@@ -2861,7 +2823,7 @@
       <c r="J15" s="11">
         <v>0.43776818420000002</v>
       </c>
-      <c r="K15" s="75"/>
+      <c r="K15" s="68"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="G16" s="11"/>
@@ -2876,13 +2838,13 @@
       <c r="B17" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C17" s="77" t="s">
+      <c r="C17" s="60" t="s">
         <v>44</v>
       </c>
-      <c r="D17" s="73" t="s">
+      <c r="D17" s="61" t="s">
         <v>19</v>
       </c>
-      <c r="E17" s="73" t="s">
+      <c r="E17" s="61" t="s">
         <v>27</v>
       </c>
       <c r="F17" s="11">
@@ -2900,7 +2862,7 @@
       <c r="J17" s="11">
         <v>0.44130707470000002</v>
       </c>
-      <c r="K17" s="75" t="s">
+      <c r="K17" s="68" t="s">
         <v>36</v>
       </c>
     </row>
@@ -2911,9 +2873,9 @@
       <c r="B18" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C18" s="77"/>
-      <c r="D18" s="73"/>
-      <c r="E18" s="73"/>
+      <c r="C18" s="60"/>
+      <c r="D18" s="61"/>
+      <c r="E18" s="61"/>
       <c r="F18" s="11">
         <v>7.7660593999999998E-3</v>
       </c>
@@ -2929,7 +2891,7 @@
       <c r="J18" s="11">
         <v>0.46778393010000002</v>
       </c>
-      <c r="K18" s="75"/>
+      <c r="K18" s="68"/>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
@@ -2938,9 +2900,9 @@
       <c r="B19" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C19" s="77"/>
-      <c r="D19" s="73"/>
-      <c r="E19" s="73"/>
+      <c r="C19" s="60"/>
+      <c r="D19" s="61"/>
+      <c r="E19" s="61"/>
       <c r="F19" s="11">
         <v>2.876318E-4</v>
       </c>
@@ -2956,7 +2918,7 @@
       <c r="J19" s="11">
         <v>0.46815617929999997</v>
       </c>
-      <c r="K19" s="75"/>
+      <c r="K19" s="68"/>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.2">
       <c r="G20" s="11"/>
@@ -2971,13 +2933,13 @@
       <c r="B21" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C21" s="77" t="s">
+      <c r="C21" s="60" t="s">
         <v>45</v>
       </c>
-      <c r="D21" s="73" t="s">
+      <c r="D21" s="61" t="s">
         <v>20</v>
       </c>
-      <c r="E21" s="73" t="s">
+      <c r="E21" s="61" t="s">
         <v>28</v>
       </c>
       <c r="F21" s="11">
@@ -2995,7 +2957,7 @@
       <c r="J21" s="11">
         <v>0.4434595543</v>
       </c>
-      <c r="K21" s="75" t="s">
+      <c r="K21" s="68" t="s">
         <v>35</v>
       </c>
     </row>
@@ -3006,9 +2968,9 @@
       <c r="B22" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C22" s="77"/>
-      <c r="D22" s="73"/>
-      <c r="E22" s="73"/>
+      <c r="C22" s="60"/>
+      <c r="D22" s="61"/>
+      <c r="E22" s="61"/>
       <c r="F22" s="11">
         <v>5.11025887E-2</v>
       </c>
@@ -3024,7 +2986,7 @@
       <c r="J22" s="11">
         <v>0.46092753450000001</v>
       </c>
-      <c r="K22" s="75"/>
+      <c r="K22" s="68"/>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
@@ -3033,9 +2995,9 @@
       <c r="B23" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C23" s="77"/>
-      <c r="D23" s="73"/>
-      <c r="E23" s="73"/>
+      <c r="C23" s="60"/>
+      <c r="D23" s="61"/>
+      <c r="E23" s="61"/>
       <c r="F23" s="11">
         <v>0</v>
       </c>
@@ -3051,7 +3013,7 @@
       <c r="J23" s="11">
         <v>0.4740446935</v>
       </c>
-      <c r="K23" s="75"/>
+      <c r="K23" s="68"/>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.2">
       <c r="G24" s="11"/>
@@ -3066,13 +3028,13 @@
       <c r="B25" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C25" s="77" t="s">
+      <c r="C25" s="60" t="s">
         <v>46</v>
       </c>
-      <c r="D25" s="73" t="s">
+      <c r="D25" s="61" t="s">
         <v>21</v>
       </c>
-      <c r="E25" s="73" t="s">
+      <c r="E25" s="61" t="s">
         <v>32</v>
       </c>
       <c r="F25" s="11">
@@ -3098,9 +3060,9 @@
       <c r="B26" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C26" s="77"/>
-      <c r="D26" s="73"/>
-      <c r="E26" s="73"/>
+      <c r="C26" s="60"/>
+      <c r="D26" s="61"/>
+      <c r="E26" s="61"/>
       <c r="F26" s="11">
         <v>3.0584851400000002E-2</v>
       </c>
@@ -3124,9 +3086,9 @@
       <c r="B27" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C27" s="77"/>
-      <c r="D27" s="73"/>
-      <c r="E27" s="73"/>
+      <c r="C27" s="60"/>
+      <c r="D27" s="61"/>
+      <c r="E27" s="61"/>
       <c r="F27" s="11">
         <v>6.7114089999999996E-4</v>
       </c>
@@ -3156,13 +3118,13 @@
       <c r="B29" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C29" s="77" t="s">
+      <c r="C29" s="60" t="s">
         <v>47</v>
       </c>
-      <c r="D29" s="73" t="s">
+      <c r="D29" s="61" t="s">
         <v>22</v>
       </c>
-      <c r="E29" s="73" t="s">
+      <c r="E29" s="61" t="s">
         <v>33</v>
       </c>
       <c r="F29" s="11">
@@ -3188,9 +3150,9 @@
       <c r="B30" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C30" s="77"/>
-      <c r="D30" s="73"/>
-      <c r="E30" s="73"/>
+      <c r="C30" s="60"/>
+      <c r="D30" s="61"/>
+      <c r="E30" s="61"/>
       <c r="F30" s="11">
         <v>1.42857143E-2</v>
       </c>
@@ -3214,9 +3176,9 @@
       <c r="B31" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C31" s="77"/>
-      <c r="D31" s="73"/>
-      <c r="E31" s="73"/>
+      <c r="C31" s="60"/>
+      <c r="D31" s="61"/>
+      <c r="E31" s="61"/>
       <c r="F31" s="11">
         <v>3.8350910000000001E-4</v>
       </c>
@@ -3246,13 +3208,13 @@
       <c r="B33" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C33" s="77" t="s">
+      <c r="C33" s="60" t="s">
         <v>48</v>
       </c>
-      <c r="D33" s="73" t="s">
+      <c r="D33" s="61" t="s">
         <v>23</v>
       </c>
-      <c r="E33" s="73" t="s">
+      <c r="E33" s="61" t="s">
         <v>29</v>
       </c>
       <c r="F33" s="11">
@@ -3278,9 +3240,9 @@
       <c r="B34" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C34" s="77"/>
-      <c r="D34" s="73"/>
-      <c r="E34" s="73"/>
+      <c r="C34" s="60"/>
+      <c r="D34" s="61"/>
+      <c r="E34" s="61"/>
       <c r="F34" s="11">
         <v>6.9727237799999994E-2</v>
       </c>
@@ -3304,9 +3266,9 @@
       <c r="B35" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C35" s="77"/>
-      <c r="D35" s="73"/>
-      <c r="E35" s="73"/>
+      <c r="C35" s="60"/>
+      <c r="D35" s="61"/>
+      <c r="E35" s="61"/>
       <c r="F35" s="11">
         <v>2.8812910000000001E-4</v>
       </c>
@@ -3336,13 +3298,13 @@
       <c r="B37" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C37" s="77" t="s">
+      <c r="C37" s="60" t="s">
         <v>49</v>
       </c>
-      <c r="D37" s="73" t="s">
+      <c r="D37" s="61" t="s">
         <v>24</v>
       </c>
-      <c r="E37" s="73" t="s">
+      <c r="E37" s="61" t="s">
         <v>34</v>
       </c>
       <c r="F37" s="11">
@@ -3368,9 +3330,9 @@
       <c r="B38" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C38" s="77"/>
-      <c r="D38" s="73"/>
-      <c r="E38" s="73"/>
+      <c r="C38" s="60"/>
+      <c r="D38" s="61"/>
+      <c r="E38" s="61"/>
       <c r="F38" s="11">
         <v>1.4189837E-2</v>
       </c>
@@ -3394,9 +3356,9 @@
       <c r="B39" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C39" s="77"/>
-      <c r="D39" s="73"/>
-      <c r="E39" s="73"/>
+      <c r="C39" s="60"/>
+      <c r="D39" s="61"/>
+      <c r="E39" s="61"/>
       <c r="F39" s="11">
         <v>2.876318E-4</v>
       </c>
@@ -3419,20 +3381,20 @@
       <c r="I40" s="11"/>
       <c r="J40" s="11"/>
     </row>
-    <row r="41" spans="1:11" s="59" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="78" t="s">
+    <row r="41" spans="1:11" s="48" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="62" t="s">
         <v>38</v>
       </c>
-      <c r="B41" s="78"/>
-      <c r="C41" s="78"/>
-      <c r="D41" s="78"/>
-      <c r="E41" s="60"/>
-      <c r="F41" s="61"/>
-      <c r="G41" s="61"/>
-      <c r="H41" s="61"/>
-      <c r="I41" s="61"/>
-      <c r="J41" s="61"/>
-      <c r="K41" s="60"/>
+      <c r="B41" s="62"/>
+      <c r="C41" s="62"/>
+      <c r="D41" s="62"/>
+      <c r="E41" s="49"/>
+      <c r="F41" s="50"/>
+      <c r="G41" s="50"/>
+      <c r="H41" s="50"/>
+      <c r="I41" s="50"/>
+      <c r="J41" s="50"/>
+      <c r="K41" s="49"/>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.2">
       <c r="G42" s="11"/>
@@ -3447,13 +3409,13 @@
       <c r="B43" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C43" s="77" t="s">
+      <c r="C43" s="60" t="s">
         <v>50</v>
       </c>
-      <c r="D43" s="73" t="s">
+      <c r="D43" s="61" t="s">
         <v>25</v>
       </c>
-      <c r="E43" s="73" t="s">
+      <c r="E43" s="61" t="s">
         <v>27</v>
       </c>
       <c r="F43" s="11">
@@ -3471,7 +3433,7 @@
       <c r="J43" s="11">
         <v>0.4587482034</v>
       </c>
-      <c r="K43" s="75" t="s">
+      <c r="K43" s="68" t="s">
         <v>30</v>
       </c>
     </row>
@@ -3482,9 +3444,9 @@
       <c r="B44" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C44" s="77"/>
-      <c r="D44" s="73"/>
-      <c r="E44" s="73"/>
+      <c r="C44" s="60"/>
+      <c r="D44" s="61"/>
+      <c r="E44" s="61"/>
       <c r="F44" s="11">
         <v>1.34125311E-2</v>
       </c>
@@ -3500,7 +3462,7 @@
       <c r="J44" s="11">
         <v>0.46907909489999999</v>
       </c>
-      <c r="K44" s="75"/>
+      <c r="K44" s="68"/>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
@@ -3509,9 +3471,9 @@
       <c r="B45" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C45" s="77"/>
-      <c r="D45" s="73"/>
-      <c r="E45" s="73"/>
+      <c r="C45" s="60"/>
+      <c r="D45" s="61"/>
+      <c r="E45" s="61"/>
       <c r="F45" s="11">
         <v>8.6223409999999995E-4</v>
       </c>
@@ -3527,7 +3489,7 @@
       <c r="J45" s="11">
         <v>0.49390839069999998</v>
       </c>
-      <c r="K45" s="75"/>
+      <c r="K45" s="68"/>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.2">
       <c r="G46" s="11"/>
@@ -3542,13 +3504,13 @@
       <c r="B47" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C47" s="77" t="s">
+      <c r="C47" s="60" t="s">
         <v>51</v>
       </c>
-      <c r="D47" s="73" t="s">
+      <c r="D47" s="61" t="s">
         <v>26</v>
       </c>
-      <c r="E47" s="73" t="s">
+      <c r="E47" s="61" t="s">
         <v>28</v>
       </c>
       <c r="F47" s="11">
@@ -3566,7 +3528,7 @@
       <c r="J47" s="11">
         <v>0.45388746419999998</v>
       </c>
-      <c r="K47" s="75" t="s">
+      <c r="K47" s="68" t="s">
         <v>31</v>
       </c>
     </row>
@@ -3577,9 +3539,9 @@
       <c r="B48" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C48" s="77"/>
-      <c r="D48" s="73"/>
-      <c r="E48" s="73"/>
+      <c r="C48" s="60"/>
+      <c r="D48" s="61"/>
+      <c r="E48" s="61"/>
       <c r="F48" s="11">
         <v>4.3303314799999999E-2</v>
       </c>
@@ -3595,7 +3557,7 @@
       <c r="J48" s="11">
         <v>0.45908136910000003</v>
       </c>
-      <c r="K48" s="75"/>
+      <c r="K48" s="68"/>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A49" s="1" t="s">
@@ -3604,9 +3566,9 @@
       <c r="B49" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C49" s="77"/>
-      <c r="D49" s="73"/>
-      <c r="E49" s="73"/>
+      <c r="C49" s="60"/>
+      <c r="D49" s="61"/>
+      <c r="E49" s="61"/>
       <c r="F49" s="11">
         <v>9.5803800000000006E-5</v>
       </c>
@@ -3622,7 +3584,7 @@
       <c r="J49" s="11">
         <v>0.478579698</v>
       </c>
-      <c r="K49" s="75"/>
+      <c r="K49" s="68"/>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.2">
       <c r="G50" s="11"/>
@@ -3637,13 +3599,13 @@
       <c r="B51" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C51" s="77" t="s">
+      <c r="C51" s="60" t="s">
         <v>52</v>
       </c>
-      <c r="D51" s="73" t="s">
+      <c r="D51" s="61" t="s">
         <v>39</v>
       </c>
-      <c r="E51" s="73" t="s">
+      <c r="E51" s="61" t="s">
         <v>29</v>
       </c>
       <c r="F51" s="11">
@@ -3669,9 +3631,9 @@
       <c r="B52" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C52" s="77"/>
-      <c r="D52" s="73"/>
-      <c r="E52" s="73"/>
+      <c r="C52" s="60"/>
+      <c r="D52" s="61"/>
+      <c r="E52" s="61"/>
       <c r="F52" s="11">
         <v>8.8139489999999997E-3</v>
       </c>
@@ -3695,9 +3657,9 @@
       <c r="B53" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C53" s="77"/>
-      <c r="D53" s="73"/>
-      <c r="E53" s="73"/>
+      <c r="C53" s="60"/>
+      <c r="D53" s="61"/>
+      <c r="E53" s="61"/>
       <c r="F53" s="11">
         <v>1.9160760000000001E-4</v>
       </c>
@@ -3726,100 +3688,68 @@
       <c r="I55" s="11"/>
       <c r="J55" s="11"/>
     </row>
-    <row r="56" spans="1:11" s="42" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="80" t="s">
+    <row r="56" spans="1:11" s="31" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A56" s="59" t="s">
         <v>59</v>
       </c>
-      <c r="B56" s="80"/>
-      <c r="C56" s="80"/>
-      <c r="D56" s="80"/>
-      <c r="E56" s="39"/>
-      <c r="F56" s="40">
+      <c r="B56" s="59"/>
+      <c r="C56" s="59"/>
+      <c r="D56" s="59"/>
+      <c r="E56" s="28"/>
+      <c r="F56" s="29">
         <f>MAX(F3:F53)</f>
         <v>7.4400767000000007E-2</v>
       </c>
-      <c r="G56" s="40">
+      <c r="G56" s="29">
         <f>MAX(G3:G53)</f>
         <v>1.9367209900000001E-2</v>
       </c>
-      <c r="H56" s="40">
+      <c r="H56" s="29">
         <f>MAX(H3:H53)</f>
         <v>1</v>
       </c>
-      <c r="I56" s="40">
+      <c r="I56" s="29">
         <f>MAX(I3:I53)</f>
         <v>0.89029599260000003</v>
       </c>
-      <c r="J56" s="40">
+      <c r="J56" s="29">
         <f>MAX(J3:J53)</f>
         <v>0.50993042769999997</v>
       </c>
-      <c r="K56" s="41"/>
-    </row>
-    <row r="57" spans="1:11" s="46" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="72" t="s">
+      <c r="K56" s="30"/>
+    </row>
+    <row r="57" spans="1:11" s="35" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A57" s="66" t="s">
         <v>60</v>
       </c>
-      <c r="B57" s="72"/>
-      <c r="C57" s="72"/>
-      <c r="D57" s="72"/>
-      <c r="E57" s="43"/>
-      <c r="F57" s="44">
+      <c r="B57" s="66"/>
+      <c r="C57" s="66"/>
+      <c r="D57" s="66"/>
+      <c r="E57" s="32"/>
+      <c r="F57" s="33">
         <f>AVERAGE(F3:F53)</f>
         <v>2.2625756961111115E-2</v>
       </c>
-      <c r="G57" s="44">
+      <c r="G57" s="33">
         <f>AVERAGE(G3:G53)</f>
         <v>4.1386779447222218E-3</v>
       </c>
-      <c r="H57" s="44">
+      <c r="H57" s="33">
         <f>AVERAGE(H3:H53)</f>
         <v>0.36452921899722224</v>
       </c>
-      <c r="I57" s="44">
+      <c r="I57" s="33">
         <f>AVERAGE(I3:I53)</f>
         <v>0.63549272388055567</v>
       </c>
-      <c r="J57" s="44">
+      <c r="J57" s="33">
         <f>AVERAGE(J3:J53)</f>
         <v>0.45735612999444442</v>
       </c>
-      <c r="K57" s="45"/>
+      <c r="K57" s="34"/>
     </row>
   </sheetData>
   <mergeCells count="48">
-    <mergeCell ref="A56:D56"/>
-    <mergeCell ref="E51:E53"/>
-    <mergeCell ref="D51:D53"/>
-    <mergeCell ref="K43:K45"/>
-    <mergeCell ref="C47:C49"/>
-    <mergeCell ref="D47:D49"/>
-    <mergeCell ref="E47:E49"/>
-    <mergeCell ref="K47:K49"/>
-    <mergeCell ref="C37:C39"/>
-    <mergeCell ref="D37:D39"/>
-    <mergeCell ref="E37:E39"/>
-    <mergeCell ref="A41:D41"/>
-    <mergeCell ref="C43:C45"/>
-    <mergeCell ref="D43:D45"/>
-    <mergeCell ref="E43:E45"/>
-    <mergeCell ref="C3:C5"/>
-    <mergeCell ref="D3:D5"/>
-    <mergeCell ref="E3:E5"/>
-    <mergeCell ref="K3:K5"/>
-    <mergeCell ref="C7:C9"/>
-    <mergeCell ref="D7:D9"/>
-    <mergeCell ref="E7:E9"/>
-    <mergeCell ref="K7:K9"/>
-    <mergeCell ref="K13:K15"/>
-    <mergeCell ref="C21:C23"/>
-    <mergeCell ref="D21:D23"/>
-    <mergeCell ref="E21:E23"/>
-    <mergeCell ref="K21:K23"/>
-    <mergeCell ref="C17:C19"/>
-    <mergeCell ref="D17:D19"/>
-    <mergeCell ref="E17:E19"/>
-    <mergeCell ref="K17:K19"/>
     <mergeCell ref="A1:XFD1"/>
     <mergeCell ref="A57:D57"/>
     <mergeCell ref="A11:D11"/>
@@ -3836,6 +3766,38 @@
     <mergeCell ref="D33:D35"/>
     <mergeCell ref="E33:E35"/>
     <mergeCell ref="C51:C53"/>
+    <mergeCell ref="K13:K15"/>
+    <mergeCell ref="C21:C23"/>
+    <mergeCell ref="D21:D23"/>
+    <mergeCell ref="E21:E23"/>
+    <mergeCell ref="K21:K23"/>
+    <mergeCell ref="C17:C19"/>
+    <mergeCell ref="D17:D19"/>
+    <mergeCell ref="E17:E19"/>
+    <mergeCell ref="K17:K19"/>
+    <mergeCell ref="C3:C5"/>
+    <mergeCell ref="D3:D5"/>
+    <mergeCell ref="E3:E5"/>
+    <mergeCell ref="K3:K5"/>
+    <mergeCell ref="C7:C9"/>
+    <mergeCell ref="D7:D9"/>
+    <mergeCell ref="E7:E9"/>
+    <mergeCell ref="K7:K9"/>
+    <mergeCell ref="C37:C39"/>
+    <mergeCell ref="D37:D39"/>
+    <mergeCell ref="E37:E39"/>
+    <mergeCell ref="A41:D41"/>
+    <mergeCell ref="C43:C45"/>
+    <mergeCell ref="D43:D45"/>
+    <mergeCell ref="E43:E45"/>
+    <mergeCell ref="A56:D56"/>
+    <mergeCell ref="E51:E53"/>
+    <mergeCell ref="D51:D53"/>
+    <mergeCell ref="K43:K45"/>
+    <mergeCell ref="C47:C49"/>
+    <mergeCell ref="D47:D49"/>
+    <mergeCell ref="E47:E49"/>
+    <mergeCell ref="K47:K49"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -3844,7 +3806,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34A06E9C-6A0D-1745-934A-9CD3EA122E2E}">
-  <dimension ref="A1:O65"/>
+  <dimension ref="A1:O62"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="51.33203125" defaultRowHeight="21" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="26.1640625" style="1" customWidth="1"/>
@@ -3864,9 +3826,9 @@
     <col min="15" max="16384" width="51.33203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" s="71" customFormat="1" ht="27" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="71" t="s">
-        <v>117</v>
+    <row r="1" spans="1:15" s="65" customFormat="1" ht="27" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="65" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="2" spans="1:15" s="6" customFormat="1" ht="66" x14ac:dyDescent="0.2">
@@ -3921,13 +3883,13 @@
       <c r="B3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="79" t="s">
+      <c r="C3" s="64" t="s">
         <v>41</v>
       </c>
-      <c r="D3" s="76" t="s">
+      <c r="D3" s="63" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="76" t="s">
+      <c r="E3" s="63" t="s">
         <v>13</v>
       </c>
       <c r="F3" s="11">
@@ -3957,7 +3919,7 @@
         <f>SUM(F3*1/5,G3*1/5,H3*1/5,I3*1/5,J3*1/5)</f>
         <v>0.29130368856</v>
       </c>
-      <c r="N3" s="74" t="s">
+      <c r="N3" s="67" t="s">
         <v>15</v>
       </c>
     </row>
@@ -3968,9 +3930,9 @@
       <c r="B4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="77"/>
-      <c r="D4" s="73"/>
-      <c r="E4" s="73"/>
+      <c r="C4" s="60"/>
+      <c r="D4" s="61"/>
+      <c r="E4" s="61"/>
       <c r="F4" s="11">
         <v>2.3969319E-3</v>
       </c>
@@ -3998,7 +3960,7 @@
         <f>SUM(F4*1/5,G4*1/5,H4*1/5,I4*1/5,J4*1/5)</f>
         <v>0.26225518991999996</v>
       </c>
-      <c r="N4" s="75"/>
+      <c r="N4" s="68"/>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
@@ -4007,9 +3969,9 @@
       <c r="B5" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="77"/>
-      <c r="D5" s="73"/>
-      <c r="E5" s="73"/>
+      <c r="C5" s="60"/>
+      <c r="D5" s="61"/>
+      <c r="E5" s="61"/>
       <c r="F5" s="11">
         <v>6.5867689399999999E-2</v>
       </c>
@@ -4037,7 +3999,7 @@
         <f>SUM(F5*1/5,G5*1/5,H5*1/5,I5*1/5,J5*1/5)</f>
         <v>0.29107094631999997</v>
       </c>
-      <c r="N5" s="75"/>
+      <c r="N5" s="68"/>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
@@ -4046,13 +4008,13 @@
       <c r="B7" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="77" t="s">
+      <c r="C7" s="60" t="s">
         <v>42</v>
       </c>
-      <c r="D7" s="73" t="s">
+      <c r="D7" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="E7" s="73" t="s">
+      <c r="E7" s="61" t="s">
         <v>13</v>
       </c>
       <c r="F7" s="11">
@@ -4082,7 +4044,7 @@
         <f>SUM(F7*1/5,G7*1/5,H7*1/5,I7*1/5,J7*1/5)</f>
         <v>0.29438649154000002</v>
       </c>
-      <c r="N7" s="75" t="s">
+      <c r="N7" s="68" t="s">
         <v>16</v>
       </c>
     </row>
@@ -4093,9 +4055,9 @@
       <c r="B8" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="77"/>
-      <c r="D8" s="73"/>
-      <c r="E8" s="73"/>
+      <c r="C8" s="60"/>
+      <c r="D8" s="61"/>
+      <c r="E8" s="61"/>
       <c r="F8" s="11">
         <v>1.3604138700000001E-2</v>
       </c>
@@ -4123,7 +4085,7 @@
         <f>SUM(F8*1/5,G8*1/5,H8*1/5,I8*1/5,J8*1/5)</f>
         <v>0.27579129901999999</v>
       </c>
-      <c r="N8" s="75"/>
+      <c r="N8" s="68"/>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
@@ -4132,9 +4094,9 @@
       <c r="B9" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="77"/>
-      <c r="D9" s="73"/>
-      <c r="E9" s="73"/>
+      <c r="C9" s="60"/>
+      <c r="D9" s="61"/>
+      <c r="E9" s="61"/>
       <c r="F9" s="11">
         <v>3.8321517499999999E-2</v>
       </c>
@@ -4162,15 +4124,15 @@
         <f>SUM(F9*1/5,G9*1/5,H9*1/5,I9*1/5,J9*1/5)</f>
         <v>0.2717815321</v>
       </c>
-      <c r="N9" s="75"/>
+      <c r="N9" s="68"/>
     </row>
     <row r="11" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="87" t="s">
+      <c r="A11" s="70" t="s">
         <v>37</v>
       </c>
-      <c r="B11" s="87"/>
-      <c r="C11" s="87"/>
-      <c r="D11" s="87"/>
+      <c r="B11" s="70"/>
+      <c r="C11" s="70"/>
+      <c r="D11" s="70"/>
       <c r="E11" s="5"/>
       <c r="F11" s="13"/>
       <c r="G11" s="13"/>
@@ -4189,13 +4151,13 @@
       <c r="B13" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C13" s="77" t="s">
+      <c r="C13" s="60" t="s">
         <v>43</v>
       </c>
-      <c r="D13" s="73" t="s">
+      <c r="D13" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="E13" s="73" t="s">
+      <c r="E13" s="61" t="s">
         <v>17</v>
       </c>
       <c r="F13" s="11">
@@ -4225,7 +4187,7 @@
         <f>SUM(F13*1/5,G13*1/5,H13*1/5,I13*1/5,J13*1/5)</f>
         <v>0.33641501256</v>
       </c>
-      <c r="N13" s="75" t="s">
+      <c r="N13" s="68" t="s">
         <v>18</v>
       </c>
     </row>
@@ -4236,9 +4198,9 @@
       <c r="B14" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C14" s="77"/>
-      <c r="D14" s="73"/>
-      <c r="E14" s="73"/>
+      <c r="C14" s="60"/>
+      <c r="D14" s="61"/>
+      <c r="E14" s="61"/>
       <c r="F14" s="11">
         <v>7.9194630899999993E-2</v>
       </c>
@@ -4266,7 +4228,7 @@
         <f>SUM(F14*1/5,G14*1/5,H14*1/5,I14*1/5,J14*1/5)</f>
         <v>0.26691102733999994</v>
       </c>
-      <c r="N14" s="75"/>
+      <c r="N14" s="68"/>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
@@ -4275,9 +4237,9 @@
       <c r="B15" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C15" s="77"/>
-      <c r="D15" s="73"/>
-      <c r="E15" s="73"/>
+      <c r="C15" s="60"/>
+      <c r="D15" s="61"/>
+      <c r="E15" s="61"/>
       <c r="F15" s="11">
         <v>3.8350910000000001E-4</v>
       </c>
@@ -4305,7 +4267,7 @@
         <f>SUM(F15*1/5,G15*1/5,H15*1/5,I15*1/5,J15*1/5)</f>
         <v>0.22330577798000001</v>
       </c>
-      <c r="N15" s="75"/>
+      <c r="N15" s="68"/>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
@@ -4314,13 +4276,13 @@
       <c r="B17" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C17" s="77" t="s">
+      <c r="C17" s="60" t="s">
         <v>44</v>
       </c>
-      <c r="D17" s="73" t="s">
+      <c r="D17" s="61" t="s">
         <v>19</v>
       </c>
-      <c r="E17" s="73" t="s">
+      <c r="E17" s="61" t="s">
         <v>27</v>
       </c>
       <c r="F17" s="11">
@@ -4350,7 +4312,7 @@
         <f>SUM(F17*1/5,G17*1/5,H17*1/5,I17*1/5,J17*1/5)</f>
         <v>0.34767161497999999</v>
       </c>
-      <c r="N17" s="75" t="s">
+      <c r="N17" s="68" t="s">
         <v>36</v>
       </c>
     </row>
@@ -4361,9 +4323,9 @@
       <c r="B18" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C18" s="77"/>
-      <c r="D18" s="73"/>
-      <c r="E18" s="73"/>
+      <c r="C18" s="60"/>
+      <c r="D18" s="61"/>
+      <c r="E18" s="61"/>
       <c r="F18" s="11">
         <v>3.7296260800000001E-2</v>
       </c>
@@ -4391,7 +4353,7 @@
         <f>SUM(F18*1/5,G18*1/5,H18*1/5,I18*1/5,J18*1/5)</f>
         <v>0.33628517706000005</v>
       </c>
-      <c r="N18" s="75"/>
+      <c r="N18" s="68"/>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
@@ -4400,9 +4362,9 @@
       <c r="B19" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C19" s="77"/>
-      <c r="D19" s="73"/>
-      <c r="E19" s="73"/>
+      <c r="C19" s="60"/>
+      <c r="D19" s="61"/>
+      <c r="E19" s="61"/>
       <c r="F19" s="11">
         <v>1.0546500000000001E-3</v>
       </c>
@@ -4430,7 +4392,7 @@
         <f>SUM(F19*1/5,G19*1/5,H19*1/5,I19*1/5,J19*1/5)</f>
         <v>0.20704430204000002</v>
       </c>
-      <c r="N19" s="75"/>
+      <c r="N19" s="68"/>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
@@ -4439,13 +4401,13 @@
       <c r="B21" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C21" s="77" t="s">
+      <c r="C21" s="60" t="s">
         <v>45</v>
       </c>
-      <c r="D21" s="73" t="s">
+      <c r="D21" s="61" t="s">
         <v>20</v>
       </c>
-      <c r="E21" s="73" t="s">
+      <c r="E21" s="61" t="s">
         <v>28</v>
       </c>
       <c r="F21" s="11">
@@ -4475,7 +4437,7 @@
         <f>SUM(F21*1/5,G21*1/5,H21*1/5,I21*1/5,J21*1/5)</f>
         <v>0.31181358595999997</v>
       </c>
-      <c r="N21" s="75" t="s">
+      <c r="N21" s="68" t="s">
         <v>35</v>
       </c>
     </row>
@@ -4486,9 +4448,9 @@
       <c r="B22" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C22" s="77"/>
-      <c r="D22" s="73"/>
-      <c r="E22" s="73"/>
+      <c r="C22" s="60"/>
+      <c r="D22" s="61"/>
+      <c r="E22" s="61"/>
       <c r="F22" s="11">
         <v>1.05465005E-2</v>
       </c>
@@ -4516,7 +4478,7 @@
         <f>SUM(F22*1/5,G22*1/5,H22*1/5,I22*1/5,J22*1/5)</f>
         <v>0.29879759264</v>
       </c>
-      <c r="N22" s="75"/>
+      <c r="N22" s="68"/>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
@@ -4525,9 +4487,9 @@
       <c r="B23" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C23" s="77"/>
-      <c r="D23" s="73"/>
-      <c r="E23" s="73"/>
+      <c r="C23" s="60"/>
+      <c r="D23" s="61"/>
+      <c r="E23" s="61"/>
       <c r="F23" s="11">
         <v>0</v>
       </c>
@@ -4555,7 +4517,7 @@
         <f>SUM(F23*1/5,G23*1/5,H23*1/5,I23*1/5,J23*1/5)</f>
         <v>0.22541820497999998</v>
       </c>
-      <c r="N23" s="75"/>
+      <c r="N23" s="68"/>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
@@ -4564,13 +4526,13 @@
       <c r="B25" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C25" s="77" t="s">
+      <c r="C25" s="60" t="s">
         <v>46</v>
       </c>
-      <c r="D25" s="73" t="s">
+      <c r="D25" s="61" t="s">
         <v>21</v>
       </c>
-      <c r="E25" s="73" t="s">
+      <c r="E25" s="61" t="s">
         <v>32</v>
       </c>
       <c r="F25" s="11">
@@ -4608,9 +4570,9 @@
       <c r="B26" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C26" s="77"/>
-      <c r="D26" s="73"/>
-      <c r="E26" s="73"/>
+      <c r="C26" s="60"/>
+      <c r="D26" s="61"/>
+      <c r="E26" s="61"/>
       <c r="F26" s="11">
         <v>2.7229146700000002E-2</v>
       </c>
@@ -4646,9 +4608,9 @@
       <c r="B27" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C27" s="77"/>
-      <c r="D27" s="73"/>
-      <c r="E27" s="73"/>
+      <c r="C27" s="60"/>
+      <c r="D27" s="61"/>
+      <c r="E27" s="61"/>
       <c r="F27" s="11">
         <v>3.8350910000000001E-4</v>
       </c>
@@ -4684,13 +4646,13 @@
       <c r="B29" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C29" s="77" t="s">
+      <c r="C29" s="60" t="s">
         <v>47</v>
       </c>
-      <c r="D29" s="73" t="s">
+      <c r="D29" s="61" t="s">
         <v>22</v>
       </c>
-      <c r="E29" s="73" t="s">
+      <c r="E29" s="61" t="s">
         <v>33</v>
       </c>
       <c r="F29" s="11">
@@ -4728,9 +4690,9 @@
       <c r="B30" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C30" s="77"/>
-      <c r="D30" s="73"/>
-      <c r="E30" s="73"/>
+      <c r="C30" s="60"/>
+      <c r="D30" s="61"/>
+      <c r="E30" s="61"/>
       <c r="F30" s="11">
         <v>2.8475551299999999E-2</v>
       </c>
@@ -4766,9 +4728,9 @@
       <c r="B31" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C31" s="77"/>
-      <c r="D31" s="73"/>
-      <c r="E31" s="73"/>
+      <c r="C31" s="60"/>
+      <c r="D31" s="61"/>
+      <c r="E31" s="61"/>
       <c r="F31" s="11">
         <v>1.917546E-4</v>
       </c>
@@ -4788,7 +4750,7 @@
         <f>SUM(F31*1/3,G31*1/3,I31*1/3)</f>
         <v>0.16992359133333332</v>
       </c>
-      <c r="L31" s="54">
+      <c r="L31" s="43">
         <f>SUM(H31*1/2,J31*1/2)</f>
         <v>0.64708675169999996</v>
       </c>
@@ -4804,13 +4766,13 @@
       <c r="B33" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C33" s="77" t="s">
+      <c r="C33" s="60" t="s">
         <v>48</v>
       </c>
-      <c r="D33" s="73" t="s">
+      <c r="D33" s="61" t="s">
         <v>23</v>
       </c>
-      <c r="E33" s="73" t="s">
+      <c r="E33" s="61" t="s">
         <v>29</v>
       </c>
       <c r="F33" s="11">
@@ -4828,7 +4790,7 @@
       <c r="J33" s="11">
         <v>0.39221498240000002</v>
       </c>
-      <c r="K33" s="54">
+      <c r="K33" s="43">
         <f>SUM(F33*1/3,G33*1/3,I33*1/3)</f>
         <v>0.31817600136666668</v>
       </c>
@@ -4848,9 +4810,9 @@
       <c r="B34" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C34" s="77"/>
-      <c r="D34" s="73"/>
-      <c r="E34" s="73"/>
+      <c r="C34" s="60"/>
+      <c r="D34" s="61"/>
+      <c r="E34" s="61"/>
       <c r="F34" s="11">
         <v>2.4010757000000001E-3</v>
       </c>
@@ -4886,9 +4848,9 @@
       <c r="B35" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C35" s="77"/>
-      <c r="D35" s="73"/>
-      <c r="E35" s="73"/>
+      <c r="C35" s="60"/>
+      <c r="D35" s="61"/>
+      <c r="E35" s="61"/>
       <c r="F35" s="11">
         <v>0</v>
       </c>
@@ -4924,13 +4886,13 @@
       <c r="B37" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C37" s="77" t="s">
+      <c r="C37" s="60" t="s">
         <v>49</v>
       </c>
-      <c r="D37" s="73" t="s">
+      <c r="D37" s="61" t="s">
         <v>24</v>
       </c>
-      <c r="E37" s="73" t="s">
+      <c r="E37" s="61" t="s">
         <v>34</v>
       </c>
       <c r="F37" s="11">
@@ -4968,9 +4930,9 @@
       <c r="B38" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C38" s="77"/>
-      <c r="D38" s="73"/>
-      <c r="E38" s="73"/>
+      <c r="C38" s="60"/>
+      <c r="D38" s="61"/>
+      <c r="E38" s="61"/>
       <c r="F38" s="11">
         <v>5.9443912000000003E-3</v>
       </c>
@@ -5006,9 +4968,9 @@
       <c r="B39" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C39" s="77"/>
-      <c r="D39" s="73"/>
-      <c r="E39" s="73"/>
+      <c r="C39" s="60"/>
+      <c r="D39" s="61"/>
+      <c r="E39" s="61"/>
       <c r="F39" s="11">
         <v>1.917546E-4</v>
       </c>
@@ -5038,12 +5000,12 @@
       </c>
     </row>
     <row r="41" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="87" t="s">
+      <c r="A41" s="70" t="s">
         <v>38</v>
       </c>
-      <c r="B41" s="87"/>
-      <c r="C41" s="87"/>
-      <c r="D41" s="87"/>
+      <c r="B41" s="70"/>
+      <c r="C41" s="70"/>
+      <c r="D41" s="70"/>
       <c r="E41" s="5"/>
       <c r="F41" s="13"/>
       <c r="G41" s="13"/>
@@ -5062,13 +5024,13 @@
       <c r="B43" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C43" s="77" t="s">
+      <c r="C43" s="60" t="s">
         <v>50</v>
       </c>
-      <c r="D43" s="73" t="s">
+      <c r="D43" s="61" t="s">
         <v>25</v>
       </c>
-      <c r="E43" s="73" t="s">
+      <c r="E43" s="61" t="s">
         <v>27</v>
       </c>
       <c r="F43" s="11">
@@ -5098,7 +5060,7 @@
         <f>SUM(F43*1/5,G43*1/5,H43*1/5,I43*1/5,J43*1/5)</f>
         <v>0.32911788728000002</v>
       </c>
-      <c r="N43" s="75" t="s">
+      <c r="N43" s="68" t="s">
         <v>30</v>
       </c>
     </row>
@@ -5109,9 +5071,9 @@
       <c r="B44" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C44" s="77"/>
-      <c r="D44" s="73"/>
-      <c r="E44" s="73"/>
+      <c r="C44" s="60"/>
+      <c r="D44" s="61"/>
+      <c r="E44" s="61"/>
       <c r="F44" s="11">
         <v>1.59034298E-2</v>
       </c>
@@ -5139,7 +5101,7 @@
         <f>SUM(F44*1/5,G44*1/5,H44*1/5,I44*1/5,J44*1/5)</f>
         <v>0.33481998118</v>
       </c>
-      <c r="N44" s="75"/>
+      <c r="N44" s="68"/>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
@@ -5148,10 +5110,10 @@
       <c r="B45" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C45" s="77"/>
-      <c r="D45" s="73"/>
-      <c r="E45" s="73"/>
-      <c r="F45" s="62">
+      <c r="C45" s="60"/>
+      <c r="D45" s="61"/>
+      <c r="E45" s="61"/>
+      <c r="F45" s="51">
         <v>0</v>
       </c>
       <c r="G45" s="11">
@@ -5178,7 +5140,7 @@
         <f>SUM(F45*1/5,G45*1/5,H45*1/5,I45*1/5,J45*1/5)</f>
         <v>0.23017129817999998</v>
       </c>
-      <c r="N45" s="75"/>
+      <c r="N45" s="68"/>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A47" s="1" t="s">
@@ -5187,13 +5149,13 @@
       <c r="B47" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C47" s="77" t="s">
+      <c r="C47" s="60" t="s">
         <v>51</v>
       </c>
-      <c r="D47" s="73" t="s">
+      <c r="D47" s="61" t="s">
         <v>26</v>
       </c>
-      <c r="E47" s="73" t="s">
+      <c r="E47" s="61" t="s">
         <v>28</v>
       </c>
       <c r="F47" s="11">
@@ -5223,7 +5185,7 @@
         <f>SUM(F47*1/5,G47*1/5,H47*1/5,I47*1/5,J47*1/5)</f>
         <v>0.28403192430000002</v>
       </c>
-      <c r="N47" s="75" t="s">
+      <c r="N47" s="68" t="s">
         <v>31</v>
       </c>
     </row>
@@ -5234,9 +5196,9 @@
       <c r="B48" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C48" s="77"/>
-      <c r="D48" s="73"/>
-      <c r="E48" s="73"/>
+      <c r="C48" s="60"/>
+      <c r="D48" s="61"/>
+      <c r="E48" s="61"/>
       <c r="F48" s="11">
         <v>2.90285495E-2</v>
       </c>
@@ -5264,7 +5226,7 @@
         <f>SUM(F48*1/5,G48*1/5,H48*1/5,I48*1/5,J48*1/5)</f>
         <v>0.35089340806000002</v>
       </c>
-      <c r="N48" s="75"/>
+      <c r="N48" s="68"/>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A49" s="1" t="s">
@@ -5273,9 +5235,9 @@
       <c r="B49" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C49" s="77"/>
-      <c r="D49" s="73"/>
-      <c r="E49" s="73"/>
+      <c r="C49" s="60"/>
+      <c r="D49" s="61"/>
+      <c r="E49" s="61"/>
       <c r="F49" s="11">
         <v>1.9160760000000001E-4</v>
       </c>
@@ -5303,7 +5265,7 @@
         <f>SUM(F49*1/5,G49*1/5,H49*1/5,I49*1/5,J49*1/5)</f>
         <v>0.34178323869999999</v>
       </c>
-      <c r="N49" s="75"/>
+      <c r="N49" s="68"/>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A51" s="1" t="s">
@@ -5312,13 +5274,13 @@
       <c r="B51" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C51" s="77" t="s">
+      <c r="C51" s="60" t="s">
         <v>52</v>
       </c>
-      <c r="D51" s="73" t="s">
+      <c r="D51" s="61" t="s">
         <v>39</v>
       </c>
-      <c r="E51" s="73" t="s">
+      <c r="E51" s="61" t="s">
         <v>29</v>
       </c>
       <c r="F51" s="11">
@@ -5344,7 +5306,7 @@
         <f>SUM(H51*1/2,J51*1/2)</f>
         <v>0.54001762715000001</v>
       </c>
-      <c r="M51" s="54">
+      <c r="M51" s="43">
         <f>SUM(F51*1/5,G51*1/5,H51*1/5,I51*1/5,J51*1/5)</f>
         <v>0.39645458486000001</v>
       </c>
@@ -5356,9 +5318,9 @@
       <c r="B52" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C52" s="77"/>
-      <c r="D52" s="73"/>
-      <c r="E52" s="73"/>
+      <c r="C52" s="60"/>
+      <c r="D52" s="61"/>
+      <c r="E52" s="61"/>
       <c r="F52" s="11">
         <v>3.4489365999999999E-3</v>
       </c>
@@ -5394,10 +5356,10 @@
       <c r="B53" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C53" s="77"/>
-      <c r="D53" s="73"/>
-      <c r="E53" s="73"/>
-      <c r="F53" s="62">
+      <c r="C53" s="60"/>
+      <c r="D53" s="61"/>
+      <c r="E53" s="61"/>
+      <c r="F53" s="51">
         <v>4.7901900000000002E-4</v>
       </c>
       <c r="G53" s="11">
@@ -5426,12 +5388,12 @@
       </c>
     </row>
     <row r="56" spans="1:14" s="14" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="88" t="s">
+      <c r="A56" s="69" t="s">
         <v>59</v>
       </c>
-      <c r="B56" s="88"/>
-      <c r="C56" s="88"/>
-      <c r="D56" s="88"/>
+      <c r="B56" s="69"/>
+      <c r="C56" s="69"/>
+      <c r="D56" s="69"/>
       <c r="E56" s="15"/>
       <c r="F56" s="16">
         <f t="shared" ref="F56:M56" si="0">MAX(F3:F53)</f>
@@ -5468,12 +5430,12 @@
       <c r="N56" s="17"/>
     </row>
     <row r="57" spans="1:14" s="18" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="86" t="s">
+      <c r="A57" s="74" t="s">
         <v>60</v>
       </c>
-      <c r="B57" s="86"/>
-      <c r="C57" s="86"/>
-      <c r="D57" s="86"/>
+      <c r="B57" s="74"/>
+      <c r="C57" s="74"/>
+      <c r="D57" s="74"/>
       <c r="E57" s="19"/>
       <c r="F57" s="20">
         <f t="shared" ref="F57:M57" si="1">AVERAGE(F3:F53)</f>
@@ -5509,125 +5471,104 @@
       </c>
       <c r="N57" s="21"/>
     </row>
-    <row r="59" spans="1:14" s="22" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="83" t="s">
-        <v>64</v>
-      </c>
-      <c r="B59" s="83"/>
-      <c r="C59" s="83"/>
-      <c r="D59" s="83"/>
-      <c r="E59" s="83"/>
-      <c r="F59" s="29">
-        <f>SUM(F56*(1/3),  G56*(1/3), I56*(1/3))</f>
-        <v>0.33744571563333331</v>
-      </c>
-      <c r="G59" s="23"/>
-      <c r="H59" s="23"/>
-      <c r="I59" s="23"/>
-      <c r="J59" s="23"/>
-      <c r="K59" s="23"/>
-      <c r="L59" s="23"/>
-      <c r="M59" s="23"/>
-      <c r="N59" s="24"/>
-    </row>
-    <row r="60" spans="1:14" s="27" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="84" t="s">
-        <v>65</v>
-      </c>
-      <c r="B60" s="84"/>
-      <c r="C60" s="84"/>
-      <c r="D60" s="84"/>
-      <c r="E60" s="84"/>
-      <c r="F60" s="28">
-        <f>SUM(H56*(1/2),  J56*(1/2))</f>
-        <v>0.67529401794999999</v>
-      </c>
-      <c r="G60" s="25"/>
-      <c r="H60" s="25"/>
-      <c r="I60" s="25"/>
-      <c r="J60" s="25"/>
-      <c r="K60" s="25"/>
-      <c r="L60" s="25"/>
-      <c r="M60" s="25"/>
-      <c r="N60" s="26"/>
-    </row>
-    <row r="61" spans="1:14" s="33" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="85" t="s">
-        <v>66</v>
-      </c>
-      <c r="B61" s="85"/>
-      <c r="C61" s="85"/>
-      <c r="D61" s="85"/>
-      <c r="E61" s="85"/>
-      <c r="F61" s="30">
-        <f>SUM(F56*1/5, G56*1/5, H56*1/5, I56*1/5,J56*1/5)</f>
-        <v>0.47258503656</v>
-      </c>
-      <c r="G61" s="31"/>
-      <c r="H61" s="31"/>
-      <c r="I61" s="31"/>
-      <c r="J61" s="31"/>
-      <c r="K61" s="31"/>
-      <c r="L61" s="31"/>
-      <c r="M61" s="31"/>
-      <c r="N61" s="32"/>
-    </row>
-    <row r="63" spans="1:14" s="37" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A63" s="81" t="s">
-        <v>83</v>
-      </c>
-      <c r="B63" s="81"/>
-      <c r="C63" s="81"/>
-      <c r="D63" s="81"/>
-      <c r="E63" s="34"/>
-      <c r="F63" s="35"/>
-      <c r="G63" s="35"/>
-      <c r="H63" s="35"/>
-      <c r="I63" s="35"/>
-      <c r="J63" s="35"/>
-      <c r="K63" s="35"/>
-      <c r="L63" s="35"/>
-      <c r="M63" s="35"/>
-      <c r="N63" s="36"/>
-    </row>
-    <row r="64" spans="1:14" s="37" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="81" t="s">
-        <v>84</v>
-      </c>
-      <c r="B64" s="82"/>
-      <c r="C64" s="82"/>
-      <c r="D64" s="82"/>
-      <c r="E64" s="38"/>
-      <c r="F64" s="35"/>
-      <c r="G64" s="35"/>
-      <c r="H64" s="35"/>
-      <c r="I64" s="35"/>
-      <c r="J64" s="35"/>
-      <c r="K64" s="35"/>
-      <c r="L64" s="35"/>
-      <c r="M64" s="35"/>
-      <c r="N64" s="36"/>
-    </row>
-    <row r="65" spans="1:14" s="37" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="81" t="s">
-        <v>85</v>
-      </c>
-      <c r="B65" s="82"/>
-      <c r="C65" s="82"/>
-      <c r="D65" s="82"/>
-      <c r="E65" s="38"/>
-      <c r="F65" s="35"/>
-      <c r="G65" s="35"/>
-      <c r="H65" s="35"/>
-      <c r="I65" s="35"/>
-      <c r="J65" s="35"/>
-      <c r="K65" s="35"/>
-      <c r="L65" s="35"/>
-      <c r="M65" s="35"/>
-      <c r="N65" s="36"/>
+    <row r="60" spans="1:14" s="26" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A60" s="71" t="s">
+        <v>80</v>
+      </c>
+      <c r="B60" s="71"/>
+      <c r="C60" s="71"/>
+      <c r="D60" s="71"/>
+      <c r="E60" s="23"/>
+      <c r="F60" s="24"/>
+      <c r="G60" s="24"/>
+      <c r="H60" s="24"/>
+      <c r="I60" s="24"/>
+      <c r="J60" s="24"/>
+      <c r="K60" s="24"/>
+      <c r="L60" s="24"/>
+      <c r="M60" s="24"/>
+      <c r="N60" s="25"/>
+    </row>
+    <row r="61" spans="1:14" s="26" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A61" s="71" t="s">
+        <v>81</v>
+      </c>
+      <c r="B61" s="72"/>
+      <c r="C61" s="72"/>
+      <c r="D61" s="72"/>
+      <c r="E61" s="27"/>
+      <c r="F61" s="24"/>
+      <c r="G61" s="24"/>
+      <c r="H61" s="24"/>
+      <c r="I61" s="24"/>
+      <c r="J61" s="24"/>
+      <c r="K61" s="24"/>
+      <c r="L61" s="24"/>
+      <c r="M61" s="24"/>
+      <c r="N61" s="25"/>
+    </row>
+    <row r="62" spans="1:14" s="26" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A62" s="71" t="s">
+        <v>82</v>
+      </c>
+      <c r="B62" s="72"/>
+      <c r="C62" s="72"/>
+      <c r="D62" s="72"/>
+      <c r="E62" s="27"/>
+      <c r="F62" s="24"/>
+      <c r="G62" s="24"/>
+      <c r="H62" s="24"/>
+      <c r="I62" s="24"/>
+      <c r="J62" s="24"/>
+      <c r="K62" s="24"/>
+      <c r="L62" s="24"/>
+      <c r="M62" s="24"/>
+      <c r="N62" s="25"/>
     </row>
   </sheetData>
-  <mergeCells count="54">
+  <mergeCells count="51">
+    <mergeCell ref="A1:XFD1"/>
+    <mergeCell ref="A61:D61"/>
+    <mergeCell ref="A62:D62"/>
+    <mergeCell ref="A60:D60"/>
+    <mergeCell ref="A57:D57"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="C13:C15"/>
+    <mergeCell ref="D13:D15"/>
+    <mergeCell ref="E13:E15"/>
+    <mergeCell ref="C25:C27"/>
+    <mergeCell ref="D25:D27"/>
+    <mergeCell ref="E25:E27"/>
+    <mergeCell ref="C29:C31"/>
+    <mergeCell ref="D29:D31"/>
+    <mergeCell ref="E29:E31"/>
+    <mergeCell ref="C33:C35"/>
+    <mergeCell ref="D33:D35"/>
+    <mergeCell ref="E33:E35"/>
+    <mergeCell ref="C37:C39"/>
+    <mergeCell ref="D37:D39"/>
+    <mergeCell ref="E37:E39"/>
+    <mergeCell ref="A41:D41"/>
+    <mergeCell ref="C43:C45"/>
+    <mergeCell ref="D43:D45"/>
+    <mergeCell ref="E43:E45"/>
+    <mergeCell ref="N3:N5"/>
+    <mergeCell ref="C7:C9"/>
+    <mergeCell ref="D7:D9"/>
+    <mergeCell ref="E7:E9"/>
+    <mergeCell ref="N7:N9"/>
+    <mergeCell ref="C3:C5"/>
+    <mergeCell ref="D3:D5"/>
+    <mergeCell ref="E3:E5"/>
+    <mergeCell ref="N13:N15"/>
+    <mergeCell ref="C21:C23"/>
+    <mergeCell ref="D21:D23"/>
+    <mergeCell ref="E21:E23"/>
+    <mergeCell ref="N21:N23"/>
+    <mergeCell ref="C17:C19"/>
+    <mergeCell ref="D17:D19"/>
+    <mergeCell ref="E17:E19"/>
+    <mergeCell ref="N17:N19"/>
     <mergeCell ref="A56:D56"/>
     <mergeCell ref="N43:N45"/>
     <mergeCell ref="C47:C49"/>
@@ -5637,51 +5578,6 @@
     <mergeCell ref="E51:E53"/>
     <mergeCell ref="C51:C53"/>
     <mergeCell ref="D51:D53"/>
-    <mergeCell ref="N13:N15"/>
-    <mergeCell ref="C21:C23"/>
-    <mergeCell ref="D21:D23"/>
-    <mergeCell ref="E21:E23"/>
-    <mergeCell ref="N21:N23"/>
-    <mergeCell ref="C17:C19"/>
-    <mergeCell ref="D17:D19"/>
-    <mergeCell ref="E17:E19"/>
-    <mergeCell ref="N17:N19"/>
-    <mergeCell ref="N3:N5"/>
-    <mergeCell ref="C7:C9"/>
-    <mergeCell ref="D7:D9"/>
-    <mergeCell ref="E7:E9"/>
-    <mergeCell ref="N7:N9"/>
-    <mergeCell ref="C3:C5"/>
-    <mergeCell ref="D3:D5"/>
-    <mergeCell ref="E3:E5"/>
-    <mergeCell ref="C37:C39"/>
-    <mergeCell ref="D37:D39"/>
-    <mergeCell ref="E37:E39"/>
-    <mergeCell ref="A41:D41"/>
-    <mergeCell ref="C43:C45"/>
-    <mergeCell ref="D43:D45"/>
-    <mergeCell ref="E43:E45"/>
-    <mergeCell ref="D29:D31"/>
-    <mergeCell ref="E29:E31"/>
-    <mergeCell ref="C33:C35"/>
-    <mergeCell ref="D33:D35"/>
-    <mergeCell ref="E33:E35"/>
-    <mergeCell ref="A1:XFD1"/>
-    <mergeCell ref="A64:D64"/>
-    <mergeCell ref="A65:D65"/>
-    <mergeCell ref="A59:E59"/>
-    <mergeCell ref="A60:E60"/>
-    <mergeCell ref="A61:E61"/>
-    <mergeCell ref="A63:D63"/>
-    <mergeCell ref="A57:D57"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="C13:C15"/>
-    <mergeCell ref="D13:D15"/>
-    <mergeCell ref="E13:E15"/>
-    <mergeCell ref="C25:C27"/>
-    <mergeCell ref="D25:D27"/>
-    <mergeCell ref="E25:E27"/>
-    <mergeCell ref="C29:C31"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5707,9 +5603,9 @@
     <col min="13" max="16384" width="51.33203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="71" customFormat="1" ht="27" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="71" t="s">
-        <v>118</v>
+    <row r="1" spans="1:14" s="65" customFormat="1" ht="27" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="65" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="2" spans="1:14" s="6" customFormat="1" ht="66" x14ac:dyDescent="0.2">
@@ -5755,46 +5651,46 @@
       <c r="B3" s="9"/>
       <c r="C3" s="10"/>
       <c r="D3" s="10"/>
-      <c r="E3" s="53"/>
-      <c r="F3" s="53"/>
-      <c r="G3" s="53"/>
-      <c r="H3" s="53"/>
-      <c r="I3" s="53"/>
-      <c r="J3" s="53"/>
-      <c r="K3" s="55"/>
-      <c r="L3" s="55"/>
+      <c r="E3" s="42"/>
+      <c r="F3" s="42"/>
+      <c r="G3" s="42"/>
+      <c r="H3" s="42"/>
+      <c r="I3" s="42"/>
+      <c r="J3" s="42"/>
+      <c r="K3" s="44"/>
+      <c r="L3" s="44"/>
       <c r="M3" s="9"/>
       <c r="N3" s="9"/>
     </row>
-    <row r="4" spans="1:14" s="47" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="86" t="s">
-        <v>71</v>
-      </c>
-      <c r="B4" s="86"/>
-      <c r="C4" s="86"/>
-      <c r="D4" s="86"/>
-      <c r="E4" s="86"/>
-      <c r="F4" s="86"/>
-      <c r="G4" s="86"/>
-      <c r="H4" s="86"/>
-      <c r="I4" s="86"/>
-      <c r="J4" s="49"/>
-      <c r="K4" s="56"/>
-      <c r="L4" s="56"/>
-    </row>
-    <row r="5" spans="1:14" s="48" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:14" s="36" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="74" t="s">
+        <v>68</v>
+      </c>
+      <c r="B4" s="74"/>
+      <c r="C4" s="74"/>
+      <c r="D4" s="74"/>
+      <c r="E4" s="74"/>
+      <c r="F4" s="74"/>
+      <c r="G4" s="74"/>
+      <c r="H4" s="74"/>
+      <c r="I4" s="74"/>
+      <c r="J4" s="38"/>
+      <c r="K4" s="45"/>
+      <c r="L4" s="45"/>
+    </row>
+    <row r="5" spans="1:14" s="37" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A5" s="8"/>
       <c r="B5" s="8"/>
       <c r="C5" s="8"/>
-      <c r="D5" s="51"/>
-      <c r="E5" s="54"/>
-      <c r="F5" s="54"/>
-      <c r="G5" s="54"/>
-      <c r="H5" s="54"/>
-      <c r="I5" s="54"/>
-      <c r="J5" s="57"/>
-      <c r="K5" s="57"/>
-      <c r="L5" s="57"/>
+      <c r="D5" s="40"/>
+      <c r="E5" s="43"/>
+      <c r="F5" s="43"/>
+      <c r="G5" s="43"/>
+      <c r="H5" s="43"/>
+      <c r="I5" s="43"/>
+      <c r="J5" s="46"/>
+      <c r="K5" s="46"/>
+      <c r="L5" s="46"/>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
@@ -5803,11 +5699,11 @@
       <c r="B6" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="75" t="s">
-        <v>67</v>
-      </c>
-      <c r="D6" s="75" t="s">
-        <v>68</v>
+      <c r="C6" s="68" t="s">
+        <v>64</v>
+      </c>
+      <c r="D6" s="68" t="s">
+        <v>65</v>
       </c>
       <c r="E6" s="11">
         <v>5.7529773300000003E-2</v>
@@ -5844,8 +5740,8 @@
       <c r="B7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="75"/>
-      <c r="D7" s="75"/>
+      <c r="C7" s="68"/>
+      <c r="D7" s="68"/>
       <c r="E7" s="11">
         <v>6.9727237799999994E-2</v>
       </c>
@@ -5881,8 +5777,8 @@
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="75"/>
-      <c r="D8" s="75"/>
+      <c r="C8" s="68"/>
+      <c r="D8" s="68"/>
       <c r="E8" s="11">
         <v>2.8812910000000001E-4</v>
       </c>
@@ -5918,11 +5814,11 @@
       <c r="B10" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C10" s="75" t="s">
-        <v>69</v>
-      </c>
-      <c r="D10" s="75" t="s">
-        <v>70</v>
+      <c r="C10" s="68" t="s">
+        <v>66</v>
+      </c>
+      <c r="D10" s="68" t="s">
+        <v>67</v>
       </c>
       <c r="E10" s="11">
         <v>5.1094890499999997E-2</v>
@@ -5933,7 +5829,7 @@
       <c r="G10" s="11">
         <v>0.4692662313</v>
       </c>
-      <c r="H10" s="54">
+      <c r="H10" s="43">
         <v>0.89344463880000002</v>
       </c>
       <c r="I10" s="11">
@@ -5959,8 +5855,8 @@
       <c r="B11" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C11" s="75"/>
-      <c r="D11" s="75"/>
+      <c r="C11" s="68"/>
+      <c r="D11" s="68"/>
       <c r="E11" s="11">
         <v>2.4010757000000001E-3</v>
       </c>
@@ -5996,8 +5892,8 @@
       <c r="B12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C12" s="75"/>
-      <c r="D12" s="75"/>
+      <c r="C12" s="68"/>
+      <c r="D12" s="68"/>
       <c r="E12" s="11">
         <v>0</v>
       </c>
@@ -6033,11 +5929,11 @@
       <c r="B14" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C14" s="75" t="s">
-        <v>74</v>
-      </c>
-      <c r="D14" s="75" t="s">
-        <v>81</v>
+      <c r="C14" s="68" t="s">
+        <v>71</v>
+      </c>
+      <c r="D14" s="68" t="s">
+        <v>78</v>
       </c>
       <c r="E14" s="11">
         <v>2.40651965E-2</v>
@@ -6074,8 +5970,8 @@
       <c r="B15" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C15" s="75"/>
-      <c r="D15" s="75"/>
+      <c r="C15" s="68"/>
+      <c r="D15" s="68"/>
       <c r="E15" s="11">
         <v>3.5474592999999999E-3</v>
       </c>
@@ -6111,8 +6007,8 @@
       <c r="B16" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C16" s="75"/>
-      <c r="D16" s="75"/>
+      <c r="C16" s="68"/>
+      <c r="D16" s="68"/>
       <c r="E16" s="11">
         <v>3.8350910000000001E-4</v>
       </c>
@@ -6141,43 +6037,43 @@
         <v>0.35585434523999993</v>
       </c>
     </row>
-    <row r="18" spans="1:12" s="63" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="63" t="s">
+    <row r="18" spans="1:12" s="52" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="52" t="s">
         <v>2</v>
       </c>
-      <c r="B18" s="63" t="s">
+      <c r="B18" s="52" t="s">
         <v>5</v>
       </c>
-      <c r="C18" s="75" t="s">
-        <v>80</v>
-      </c>
-      <c r="D18" s="75" t="s">
-        <v>79</v>
-      </c>
-      <c r="E18" s="64">
+      <c r="C18" s="68" t="s">
+        <v>77</v>
+      </c>
+      <c r="D18" s="68" t="s">
+        <v>76</v>
+      </c>
+      <c r="E18" s="53">
         <v>3.5474592999999999E-3</v>
       </c>
-      <c r="F18" s="64">
+      <c r="F18" s="53">
         <v>2.3969319E-3</v>
       </c>
-      <c r="G18" s="64">
+      <c r="G18" s="53">
         <v>0.68648130389999995</v>
       </c>
-      <c r="H18" s="64">
+      <c r="H18" s="53">
         <v>0.73279006160000004</v>
       </c>
-      <c r="I18" s="65">
+      <c r="I18" s="54">
         <v>0.70502058919999999</v>
       </c>
-      <c r="J18" s="64">
+      <c r="J18" s="53">
         <f>SUM(E18*1/3,F18*1/3,H18*1/3)</f>
         <v>0.2462448176</v>
       </c>
-      <c r="K18" s="64">
+      <c r="K18" s="53">
         <f>SUM(G18*1/2,I18*1/2)</f>
         <v>0.69575094655000003</v>
       </c>
-      <c r="L18" s="64">
+      <c r="L18" s="53">
         <f>SUM(E18*1/5,F18*1/5,G18*1/5,H18*1/5,I18*1/5)</f>
         <v>0.42604726918000002</v>
       </c>
@@ -6189,8 +6085,8 @@
       <c r="B19" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C19" s="75"/>
-      <c r="D19" s="75"/>
+      <c r="C19" s="68"/>
+      <c r="D19" s="68"/>
       <c r="E19" s="11">
         <v>3.0680729000000001E-3</v>
       </c>
@@ -6226,8 +6122,8 @@
       <c r="B20" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C20" s="75"/>
-      <c r="D20" s="75"/>
+      <c r="C20" s="68"/>
+      <c r="D20" s="68"/>
       <c r="E20" s="11">
         <v>2.876318E-4</v>
       </c>
@@ -6257,7 +6153,7 @@
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="C21" s="50"/>
+      <c r="C21" s="39"/>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
@@ -6266,11 +6162,11 @@
       <c r="B22" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C22" s="75" t="s">
-        <v>72</v>
-      </c>
-      <c r="D22" s="75" t="s">
-        <v>73</v>
+      <c r="C22" s="68" t="s">
+        <v>69</v>
+      </c>
+      <c r="D22" s="68" t="s">
+        <v>70</v>
       </c>
       <c r="E22" s="11">
         <v>8.2742090099999999E-2</v>
@@ -6307,8 +6203,8 @@
       <c r="B23" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C23" s="75"/>
-      <c r="D23" s="75"/>
+      <c r="C23" s="68"/>
+      <c r="D23" s="68"/>
       <c r="E23" s="11">
         <v>3.1639501E-3</v>
       </c>
@@ -6344,15 +6240,15 @@
       <c r="B24" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C24" s="75"/>
-      <c r="D24" s="75"/>
+      <c r="C24" s="68"/>
+      <c r="D24" s="68"/>
       <c r="E24" s="11">
         <v>1.917546E-4</v>
       </c>
       <c r="F24" s="11">
         <v>4.5062319999999998E-3</v>
       </c>
-      <c r="G24" s="54">
+      <c r="G24" s="43">
         <v>0.79884947269999995</v>
       </c>
       <c r="H24" s="11">
@@ -6381,11 +6277,11 @@
       <c r="B26" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C26" s="75" t="s">
-        <v>77</v>
-      </c>
-      <c r="D26" s="75" t="s">
-        <v>75</v>
+      <c r="C26" s="68" t="s">
+        <v>74</v>
+      </c>
+      <c r="D26" s="68" t="s">
+        <v>72</v>
       </c>
       <c r="E26" s="11">
         <v>4.0172579100000001E-2</v>
@@ -6422,8 +6318,8 @@
       <c r="B27" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C27" s="75"/>
-      <c r="D27" s="75"/>
+      <c r="C27" s="68"/>
+      <c r="D27" s="68"/>
       <c r="E27" s="11">
         <v>1.70661553E-2</v>
       </c>
@@ -6459,8 +6355,8 @@
       <c r="B28" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C28" s="75"/>
-      <c r="D28" s="75"/>
+      <c r="C28" s="68"/>
+      <c r="D28" s="68"/>
       <c r="E28" s="11">
         <v>6.7114089999999996E-4</v>
       </c>
@@ -6496,11 +6392,11 @@
       <c r="B30" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C30" s="75" t="s">
-        <v>78</v>
-      </c>
-      <c r="D30" s="75" t="s">
-        <v>76</v>
+      <c r="C30" s="68" t="s">
+        <v>75</v>
+      </c>
+      <c r="D30" s="68" t="s">
+        <v>73</v>
       </c>
       <c r="E30" s="11">
         <v>7.3250239699999997E-2</v>
@@ -6537,8 +6433,8 @@
       <c r="B31" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C31" s="75"/>
-      <c r="D31" s="75"/>
+      <c r="C31" s="68"/>
+      <c r="D31" s="68"/>
       <c r="E31" s="11">
         <v>7.2866731000000001E-3</v>
       </c>
@@ -6574,8 +6470,8 @@
       <c r="B32" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C32" s="75"/>
-      <c r="D32" s="75"/>
+      <c r="C32" s="68"/>
+      <c r="D32" s="68"/>
       <c r="E32" s="11">
         <v>0</v>
       </c>
@@ -6605,12 +6501,12 @@
       </c>
     </row>
     <row r="35" spans="1:14" s="14" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="88" t="s">
+      <c r="A35" s="69" t="s">
         <v>59</v>
       </c>
-      <c r="B35" s="88"/>
-      <c r="C35" s="88"/>
-      <c r="D35" s="88"/>
+      <c r="B35" s="69"/>
+      <c r="C35" s="69"/>
+      <c r="D35" s="69"/>
       <c r="E35" s="16">
         <f t="shared" ref="E35:L35" si="0">MAX(E5:E33)</f>
         <v>8.2742090099999999E-2</v>
@@ -6646,77 +6542,77 @@
       <c r="M35" s="16"/>
       <c r="N35" s="17"/>
     </row>
-    <row r="36" spans="1:14" s="52" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="83" t="s">
+    <row r="36" spans="1:14" s="41" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="73" t="s">
         <v>60</v>
       </c>
-      <c r="B36" s="83"/>
-      <c r="C36" s="83"/>
-      <c r="D36" s="83"/>
-      <c r="E36" s="29">
+      <c r="B36" s="73"/>
+      <c r="C36" s="73"/>
+      <c r="D36" s="73"/>
+      <c r="E36" s="22">
         <f t="shared" ref="E36:L36" si="1">AVERAGE(E6:E33)</f>
         <v>2.0975477057142849E-2</v>
       </c>
-      <c r="F36" s="29">
+      <c r="F36" s="22">
         <f t="shared" si="1"/>
         <v>4.2395303095238103E-3</v>
       </c>
-      <c r="G36" s="29">
+      <c r="G36" s="22">
         <f t="shared" si="1"/>
         <v>0.36637347650000002</v>
       </c>
-      <c r="H36" s="29">
+      <c r="H36" s="22">
         <f t="shared" si="1"/>
         <v>0.60164974021428563</v>
       </c>
-      <c r="I36" s="29">
+      <c r="I36" s="22">
         <f t="shared" si="1"/>
         <v>0.47145003103333344</v>
       </c>
-      <c r="J36" s="29">
+      <c r="J36" s="22">
         <f t="shared" si="1"/>
         <v>0.20895491586031745</v>
       </c>
-      <c r="K36" s="29">
+      <c r="K36" s="22">
         <f t="shared" si="1"/>
         <v>0.41891175376666662</v>
       </c>
-      <c r="L36" s="29">
+      <c r="L36" s="22">
         <f t="shared" si="1"/>
         <v>0.29293765102285718</v>
       </c>
-      <c r="M36" s="29"/>
-      <c r="N36" s="58"/>
-    </row>
-    <row r="38" spans="1:14" s="47" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="86" t="s">
-        <v>86</v>
-      </c>
-      <c r="B38" s="86"/>
-      <c r="C38" s="86"/>
-      <c r="D38" s="86"/>
-      <c r="E38" s="86"/>
-      <c r="F38" s="86"/>
-      <c r="G38" s="86"/>
-      <c r="H38" s="86"/>
-      <c r="I38" s="86"/>
-      <c r="J38" s="49"/>
-      <c r="K38" s="56"/>
-      <c r="L38" s="56"/>
-    </row>
-    <row r="39" spans="1:14" s="48" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="M36" s="22"/>
+      <c r="N36" s="47"/>
+    </row>
+    <row r="38" spans="1:14" s="36" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="74" t="s">
+        <v>83</v>
+      </c>
+      <c r="B38" s="74"/>
+      <c r="C38" s="74"/>
+      <c r="D38" s="74"/>
+      <c r="E38" s="74"/>
+      <c r="F38" s="74"/>
+      <c r="G38" s="74"/>
+      <c r="H38" s="74"/>
+      <c r="I38" s="74"/>
+      <c r="J38" s="38"/>
+      <c r="K38" s="45"/>
+      <c r="L38" s="45"/>
+    </row>
+    <row r="39" spans="1:14" s="37" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A39" s="8"/>
       <c r="B39" s="8"/>
       <c r="C39" s="8"/>
-      <c r="D39" s="51"/>
-      <c r="E39" s="54"/>
-      <c r="F39" s="54"/>
-      <c r="G39" s="54"/>
-      <c r="H39" s="54"/>
-      <c r="I39" s="54"/>
-      <c r="J39" s="57"/>
-      <c r="K39" s="57"/>
-      <c r="L39" s="57"/>
+      <c r="D39" s="40"/>
+      <c r="E39" s="43"/>
+      <c r="F39" s="43"/>
+      <c r="G39" s="43"/>
+      <c r="H39" s="43"/>
+      <c r="I39" s="43"/>
+      <c r="J39" s="46"/>
+      <c r="K39" s="46"/>
+      <c r="L39" s="46"/>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
@@ -6725,11 +6621,11 @@
       <c r="B40" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C40" s="75" t="s">
-        <v>87</v>
-      </c>
-      <c r="D40" s="75" t="s">
-        <v>68</v>
+      <c r="C40" s="68" t="s">
+        <v>84</v>
+      </c>
+      <c r="D40" s="68" t="s">
+        <v>65</v>
       </c>
       <c r="E40" s="11">
         <v>3.2885905999999999E-2</v>
@@ -6766,8 +6662,8 @@
       <c r="B41" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C41" s="75"/>
-      <c r="D41" s="75"/>
+      <c r="C41" s="68"/>
+      <c r="D41" s="68"/>
       <c r="E41" s="11">
         <v>1.42857143E-2</v>
       </c>
@@ -6803,8 +6699,8 @@
       <c r="B42" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C42" s="75"/>
-      <c r="D42" s="75"/>
+      <c r="C42" s="68"/>
+      <c r="D42" s="68"/>
       <c r="E42" s="11">
         <v>3.8350910000000001E-4</v>
       </c>
@@ -6840,11 +6736,11 @@
       <c r="B44" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C44" s="75" t="s">
-        <v>88</v>
-      </c>
-      <c r="D44" s="75" t="s">
-        <v>70</v>
+      <c r="C44" s="68" t="s">
+        <v>85</v>
+      </c>
+      <c r="D44" s="68" t="s">
+        <v>67</v>
       </c>
       <c r="E44" s="11">
         <v>4.0364333699999998E-2</v>
@@ -6881,8 +6777,8 @@
       <c r="B45" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C45" s="75"/>
-      <c r="D45" s="75"/>
+      <c r="C45" s="68"/>
+      <c r="D45" s="68"/>
       <c r="E45" s="11">
         <v>2.8475551299999999E-2</v>
       </c>
@@ -6892,13 +6788,13 @@
       <c r="G45" s="11">
         <v>0.5637583893</v>
       </c>
-      <c r="H45" s="54">
+      <c r="H45" s="43">
         <v>0.85501700719999996</v>
       </c>
       <c r="I45" s="11">
         <v>0.43641871859999998</v>
       </c>
-      <c r="J45" s="54">
+      <c r="J45" s="43">
         <f>SUM(E45*1/3,F45*1/3,H45*1/3)</f>
         <v>0.29484906953333329</v>
       </c>
@@ -6918,8 +6814,8 @@
       <c r="B46" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C46" s="75"/>
-      <c r="D46" s="75"/>
+      <c r="C46" s="68"/>
+      <c r="D46" s="68"/>
       <c r="E46" s="11">
         <v>1.917546E-4</v>
       </c>
@@ -6955,11 +6851,11 @@
       <c r="B48" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C48" s="75" t="s">
-        <v>89</v>
-      </c>
-      <c r="D48" s="75" t="s">
-        <v>81</v>
+      <c r="C48" s="68" t="s">
+        <v>86</v>
+      </c>
+      <c r="D48" s="68" t="s">
+        <v>78</v>
       </c>
       <c r="E48" s="11">
         <v>2.1572387299999999E-2</v>
@@ -6996,8 +6892,8 @@
       <c r="B49" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C49" s="75"/>
-      <c r="D49" s="75"/>
+      <c r="C49" s="68"/>
+      <c r="D49" s="68"/>
       <c r="E49" s="11">
         <v>6.3279002999999997E-3</v>
       </c>
@@ -7033,8 +6929,8 @@
       <c r="B50" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C50" s="75"/>
-      <c r="D50" s="75"/>
+      <c r="C50" s="68"/>
+      <c r="D50" s="68"/>
       <c r="E50" s="11">
         <v>2.876318E-4</v>
       </c>
@@ -7063,43 +6959,43 @@
         <v>0.33726077935999998</v>
       </c>
     </row>
-    <row r="52" spans="1:12" s="63" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="63" t="s">
+    <row r="52" spans="1:12" s="52" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A52" s="52" t="s">
         <v>2</v>
       </c>
-      <c r="B52" s="63" t="s">
+      <c r="B52" s="52" t="s">
         <v>5</v>
       </c>
-      <c r="C52" s="75" t="s">
-        <v>90</v>
-      </c>
-      <c r="D52" s="75" t="s">
-        <v>79</v>
-      </c>
-      <c r="E52" s="64">
+      <c r="C52" s="68" t="s">
+        <v>87</v>
+      </c>
+      <c r="D52" s="68" t="s">
+        <v>76</v>
+      </c>
+      <c r="E52" s="53">
         <v>1.23681687E-2</v>
       </c>
-      <c r="F52" s="64">
+      <c r="F52" s="53">
         <v>2.6845637999999999E-3</v>
       </c>
-      <c r="G52" s="64">
+      <c r="G52" s="53">
         <v>0.70795781400000002</v>
       </c>
-      <c r="H52" s="64">
+      <c r="H52" s="53">
         <v>0.71314872139999996</v>
       </c>
-      <c r="I52" s="65">
+      <c r="I52" s="54">
         <v>0.64805542540000005</v>
       </c>
-      <c r="J52" s="64">
+      <c r="J52" s="53">
         <f>SUM(E52*1/3,F52*1/3,H52*1/3)</f>
         <v>0.24273381796666665</v>
       </c>
-      <c r="K52" s="65">
+      <c r="K52" s="54">
         <f>SUM(G52*1/2,I52*1/2)</f>
         <v>0.67800661970000009</v>
       </c>
-      <c r="L52" s="65">
+      <c r="L52" s="54">
         <f>SUM(E52*1/5,F52*1/5,G52*1/5,H52*1/5,I52*1/5)</f>
         <v>0.41684293866000005</v>
       </c>
@@ -7111,8 +7007,8 @@
       <c r="B53" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C53" s="75"/>
-      <c r="D53" s="75"/>
+      <c r="C53" s="68"/>
+      <c r="D53" s="68"/>
       <c r="E53" s="11">
         <v>2.0134227999999998E-3</v>
       </c>
@@ -7148,8 +7044,8 @@
       <c r="B54" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C54" s="75"/>
-      <c r="D54" s="75"/>
+      <c r="C54" s="68"/>
+      <c r="D54" s="68"/>
       <c r="E54" s="11">
         <v>1.917546E-4</v>
       </c>
@@ -7179,7 +7075,7 @@
       </c>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="C55" s="50"/>
+      <c r="C55" s="39"/>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A56" s="1" t="s">
@@ -7188,11 +7084,11 @@
       <c r="B56" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C56" s="75" t="s">
-        <v>91</v>
-      </c>
-      <c r="D56" s="75" t="s">
-        <v>73</v>
+      <c r="C56" s="68" t="s">
+        <v>88</v>
+      </c>
+      <c r="D56" s="68" t="s">
+        <v>70</v>
       </c>
       <c r="E56" s="11">
         <v>9.0220517700000002E-2</v>
@@ -7229,8 +7125,8 @@
       <c r="B57" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C57" s="75"/>
-      <c r="D57" s="75"/>
+      <c r="C57" s="68"/>
+      <c r="D57" s="68"/>
       <c r="E57" s="11">
         <v>1.9558964500000001E-2</v>
       </c>
@@ -7266,15 +7162,15 @@
       <c r="B58" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C58" s="75"/>
-      <c r="D58" s="75"/>
+      <c r="C58" s="68"/>
+      <c r="D58" s="68"/>
       <c r="E58" s="11">
         <v>0</v>
       </c>
       <c r="F58" s="11">
         <v>2.8763183999999998E-3</v>
       </c>
-      <c r="G58" s="54">
+      <c r="G58" s="43">
         <v>0.81802492810000005</v>
       </c>
       <c r="H58" s="11">
@@ -7303,11 +7199,11 @@
       <c r="B60" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C60" s="75" t="s">
-        <v>92</v>
-      </c>
-      <c r="D60" s="75" t="s">
-        <v>75</v>
+      <c r="C60" s="68" t="s">
+        <v>89</v>
+      </c>
+      <c r="D60" s="68" t="s">
+        <v>72</v>
       </c>
       <c r="E60" s="11">
         <v>2.47363375E-2</v>
@@ -7344,8 +7240,8 @@
       <c r="B61" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C61" s="75"/>
-      <c r="D61" s="75"/>
+      <c r="C61" s="68"/>
+      <c r="D61" s="68"/>
       <c r="E61" s="11">
         <v>4.4103546999999998E-3</v>
       </c>
@@ -7381,8 +7277,8 @@
       <c r="B62" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C62" s="75"/>
-      <c r="D62" s="75"/>
+      <c r="C62" s="68"/>
+      <c r="D62" s="68"/>
       <c r="E62" s="11">
         <v>2.8763183000000002E-3</v>
       </c>
@@ -7418,11 +7314,11 @@
       <c r="B64" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C64" s="75" t="s">
-        <v>93</v>
-      </c>
-      <c r="D64" s="75" t="s">
-        <v>76</v>
+      <c r="C64" s="68" t="s">
+        <v>90</v>
+      </c>
+      <c r="D64" s="68" t="s">
+        <v>73</v>
       </c>
       <c r="E64" s="11">
         <v>5.1006711400000002E-2</v>
@@ -7459,8 +7355,8 @@
       <c r="B65" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C65" s="75"/>
-      <c r="D65" s="75"/>
+      <c r="C65" s="68"/>
+      <c r="D65" s="68"/>
       <c r="E65" s="11">
         <v>8.6289548999999993E-3</v>
       </c>
@@ -7496,8 +7392,8 @@
       <c r="B66" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C66" s="75"/>
-      <c r="D66" s="75"/>
+      <c r="C66" s="68"/>
+      <c r="D66" s="68"/>
       <c r="E66" s="11">
         <v>1.9175455000000001E-3</v>
       </c>
@@ -7527,12 +7423,12 @@
       </c>
     </row>
     <row r="69" spans="1:14" s="14" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="88" t="s">
+      <c r="A69" s="69" t="s">
         <v>59</v>
       </c>
-      <c r="B69" s="88"/>
-      <c r="C69" s="88"/>
-      <c r="D69" s="88"/>
+      <c r="B69" s="69"/>
+      <c r="C69" s="69"/>
+      <c r="D69" s="69"/>
       <c r="E69" s="16">
         <f t="shared" ref="E69:L69" si="2">MAX(E39:E67)</f>
         <v>9.0220517700000002E-2</v>
@@ -7568,77 +7464,77 @@
       <c r="M69" s="16"/>
       <c r="N69" s="17"/>
     </row>
-    <row r="70" spans="1:14" s="52" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A70" s="83" t="s">
+    <row r="70" spans="1:14" s="41" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A70" s="73" t="s">
         <v>60</v>
       </c>
-      <c r="B70" s="83"/>
-      <c r="C70" s="83"/>
-      <c r="D70" s="83"/>
-      <c r="E70" s="29">
+      <c r="B70" s="73"/>
+      <c r="C70" s="73"/>
+      <c r="D70" s="73"/>
+      <c r="E70" s="22">
         <f t="shared" ref="E70:L70" si="3">AVERAGE(E40:E67)</f>
         <v>1.7271606619047621E-2</v>
       </c>
-      <c r="F70" s="29">
+      <c r="F70" s="22">
         <f t="shared" si="3"/>
         <v>3.9948865666666663E-3</v>
       </c>
-      <c r="G70" s="29">
+      <c r="G70" s="22">
         <f t="shared" si="3"/>
         <v>0.41313975254285717</v>
       </c>
-      <c r="H70" s="29">
+      <c r="H70" s="22">
         <f t="shared" si="3"/>
         <v>0.5907288973095236</v>
       </c>
-      <c r="I70" s="29">
+      <c r="I70" s="22">
         <f t="shared" si="3"/>
         <v>0.47859011843809524</v>
       </c>
-      <c r="J70" s="29">
+      <c r="J70" s="22">
         <f t="shared" si="3"/>
         <v>0.20399846349841269</v>
       </c>
-      <c r="K70" s="29">
+      <c r="K70" s="22">
         <f t="shared" si="3"/>
         <v>0.44586493549047612</v>
       </c>
-      <c r="L70" s="29">
+      <c r="L70" s="22">
         <f t="shared" si="3"/>
         <v>0.30074505229523812</v>
       </c>
-      <c r="M70" s="29"/>
-      <c r="N70" s="58"/>
-    </row>
-    <row r="72" spans="1:14" s="47" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="86" t="s">
-        <v>94</v>
-      </c>
-      <c r="B72" s="86"/>
-      <c r="C72" s="86"/>
-      <c r="D72" s="86"/>
-      <c r="E72" s="86"/>
-      <c r="F72" s="86"/>
-      <c r="G72" s="86"/>
-      <c r="H72" s="86"/>
-      <c r="I72" s="86"/>
-      <c r="J72" s="49"/>
-      <c r="K72" s="56"/>
-      <c r="L72" s="56"/>
-    </row>
-    <row r="73" spans="1:14" s="48" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="M70" s="22"/>
+      <c r="N70" s="47"/>
+    </row>
+    <row r="72" spans="1:14" s="36" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A72" s="74" t="s">
+        <v>91</v>
+      </c>
+      <c r="B72" s="74"/>
+      <c r="C72" s="74"/>
+      <c r="D72" s="74"/>
+      <c r="E72" s="74"/>
+      <c r="F72" s="74"/>
+      <c r="G72" s="74"/>
+      <c r="H72" s="74"/>
+      <c r="I72" s="74"/>
+      <c r="J72" s="38"/>
+      <c r="K72" s="45"/>
+      <c r="L72" s="45"/>
+    </row>
+    <row r="73" spans="1:14" s="37" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A73" s="8"/>
       <c r="B73" s="8"/>
       <c r="C73" s="8"/>
-      <c r="D73" s="51"/>
-      <c r="E73" s="54"/>
-      <c r="F73" s="54"/>
-      <c r="G73" s="54"/>
-      <c r="H73" s="54"/>
-      <c r="I73" s="54"/>
-      <c r="J73" s="57"/>
-      <c r="K73" s="57"/>
-      <c r="L73" s="57"/>
+      <c r="D73" s="40"/>
+      <c r="E73" s="43"/>
+      <c r="F73" s="43"/>
+      <c r="G73" s="43"/>
+      <c r="H73" s="43"/>
+      <c r="I73" s="43"/>
+      <c r="J73" s="46"/>
+      <c r="K73" s="46"/>
+      <c r="L73" s="46"/>
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A74" s="1" t="s">
@@ -7647,11 +7543,11 @@
       <c r="B74" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C74" s="75" t="s">
-        <v>95</v>
-      </c>
-      <c r="D74" s="75" t="s">
-        <v>68</v>
+      <c r="C74" s="68" t="s">
+        <v>92</v>
+      </c>
+      <c r="D74" s="68" t="s">
+        <v>65</v>
       </c>
       <c r="E74" s="11">
         <v>3.1423644399999999E-2</v>
@@ -7662,13 +7558,13 @@
       <c r="G74" s="11">
         <v>0.31423644379999999</v>
       </c>
-      <c r="H74" s="54">
+      <c r="H74" s="43">
         <v>0.87912838900000001</v>
       </c>
       <c r="I74" s="11">
         <v>0.37861748220000002</v>
       </c>
-      <c r="J74" s="54">
+      <c r="J74" s="43">
         <f>SUM(E74*1/3,F74*1/3,H74*1/3)</f>
         <v>0.30501827056666669</v>
       </c>
@@ -7688,8 +7584,8 @@
       <c r="B75" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C75" s="75"/>
-      <c r="D75" s="75"/>
+      <c r="C75" s="68"/>
+      <c r="D75" s="68"/>
       <c r="E75" s="11">
         <v>8.8139489999999997E-3</v>
       </c>
@@ -7725,8 +7621,8 @@
       <c r="B76" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C76" s="75"/>
-      <c r="D76" s="75"/>
+      <c r="C76" s="68"/>
+      <c r="D76" s="68"/>
       <c r="E76" s="11">
         <v>1.9160760000000001E-4</v>
       </c>
@@ -7762,11 +7658,11 @@
       <c r="B78" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C78" s="75" t="s">
-        <v>96</v>
-      </c>
-      <c r="D78" s="75" t="s">
-        <v>70</v>
+      <c r="C78" s="68" t="s">
+        <v>93</v>
+      </c>
+      <c r="D78" s="68" t="s">
+        <v>67</v>
       </c>
       <c r="E78" s="11">
         <v>2.7399884999999999E-2</v>
@@ -7803,8 +7699,8 @@
       <c r="B79" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C79" s="75"/>
-      <c r="D79" s="75"/>
+      <c r="C79" s="68"/>
+      <c r="D79" s="68"/>
       <c r="E79" s="11">
         <v>3.4489365999999999E-3</v>
       </c>
@@ -7840,9 +7736,9 @@
       <c r="B80" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C80" s="75"/>
-      <c r="D80" s="75"/>
-      <c r="E80" s="62">
+      <c r="C80" s="68"/>
+      <c r="D80" s="68"/>
+      <c r="E80" s="51">
         <v>4.7901900000000002E-4</v>
       </c>
       <c r="F80" s="11">
@@ -7877,11 +7773,11 @@
       <c r="B82" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C82" s="75" t="s">
-        <v>97</v>
-      </c>
-      <c r="D82" s="75" t="s">
-        <v>81</v>
+      <c r="C82" s="68" t="s">
+        <v>94</v>
+      </c>
+      <c r="D82" s="68" t="s">
+        <v>78</v>
       </c>
       <c r="E82" s="11">
         <v>1.41789615E-2</v>
@@ -7918,8 +7814,8 @@
       <c r="B83" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C83" s="75"/>
-      <c r="D83" s="75"/>
+      <c r="C83" s="68"/>
+      <c r="D83" s="68"/>
       <c r="E83" s="11">
         <v>4.3111707000000003E-3</v>
       </c>
@@ -7955,8 +7851,8 @@
       <c r="B84" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C84" s="75"/>
-      <c r="D84" s="75"/>
+      <c r="C84" s="68"/>
+      <c r="D84" s="68"/>
       <c r="E84" s="11">
         <v>2.1076835000000001E-3</v>
       </c>
@@ -7985,43 +7881,43 @@
         <v>0.28440324</v>
       </c>
     </row>
-    <row r="86" spans="1:12" s="42" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A86" s="42" t="s">
+    <row r="86" spans="1:12" s="31" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A86" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="B86" s="42" t="s">
+      <c r="B86" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="C86" s="75" t="s">
-        <v>98</v>
-      </c>
-      <c r="D86" s="75" t="s">
-        <v>79</v>
-      </c>
-      <c r="E86" s="67">
+      <c r="C86" s="68" t="s">
+        <v>95</v>
+      </c>
+      <c r="D86" s="68" t="s">
+        <v>76</v>
+      </c>
+      <c r="E86" s="55">
         <v>1.9543973900000001E-2</v>
       </c>
-      <c r="F86" s="67">
+      <c r="F86" s="55">
         <v>8.0475187000000007E-3</v>
       </c>
-      <c r="G86" s="67">
+      <c r="G86" s="55">
         <v>0.7549338954</v>
       </c>
-      <c r="H86" s="67">
+      <c r="H86" s="55">
         <v>0.80678453409999995</v>
       </c>
-      <c r="I86" s="40">
+      <c r="I86" s="29">
         <v>0.68024081950000004</v>
       </c>
-      <c r="J86" s="67">
+      <c r="J86" s="55">
         <f>SUM(E86*1/3,F86*1/3,H86*1/3)</f>
         <v>0.27812534223333329</v>
       </c>
-      <c r="K86" s="67">
+      <c r="K86" s="55">
         <f>SUM(G86*1/2,I86*1/2)</f>
         <v>0.71758735745000002</v>
       </c>
-      <c r="L86" s="67">
+      <c r="L86" s="55">
         <f>SUM(E86*1/5,F86*1/5,G86*1/5,H86*1/5,I86*1/5)</f>
         <v>0.45391014831999998</v>
       </c>
@@ -8033,8 +7929,8 @@
       <c r="B87" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C87" s="75"/>
-      <c r="D87" s="75"/>
+      <c r="C87" s="68"/>
+      <c r="D87" s="68"/>
       <c r="E87" s="11">
         <v>8.6223409999999995E-4</v>
       </c>
@@ -8058,7 +7954,7 @@
         <f>SUM(G87*1/2,I87*1/2)</f>
         <v>0.45788973504999997</v>
       </c>
-      <c r="L87" s="54">
+      <c r="L87" s="43">
         <f>SUM(E87*1/5,F87*1/5,G87*1/5,H87*1/5,I87*1/5)</f>
         <v>0.29463758565999998</v>
       </c>
@@ -8070,15 +7966,15 @@
       <c r="B88" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C88" s="75"/>
-      <c r="D88" s="75"/>
+      <c r="C88" s="68"/>
+      <c r="D88" s="68"/>
       <c r="E88" s="11">
         <v>3.8321520000000002E-4</v>
       </c>
       <c r="F88" s="11">
         <v>2.1076835000000001E-3</v>
       </c>
-      <c r="G88" s="54">
+      <c r="G88" s="43">
         <v>0.78884843839999996</v>
       </c>
       <c r="H88" s="11">
@@ -8091,7 +7987,7 @@
         <f>SUM(E88*1/3,F88*1/3,H88*1/3)</f>
         <v>0.20858465213333333</v>
       </c>
-      <c r="K88" s="54">
+      <c r="K88" s="43">
         <f>SUM(G88*1/2,I88*1/2)</f>
         <v>0.718753631</v>
       </c>
@@ -8101,7 +7997,7 @@
       </c>
     </row>
     <row r="89" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="C89" s="50"/>
+      <c r="C89" s="39"/>
     </row>
     <row r="90" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A90" s="1" t="s">
@@ -8110,11 +8006,11 @@
       <c r="B90" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C90" s="75" t="s">
-        <v>99</v>
-      </c>
-      <c r="D90" s="75" t="s">
-        <v>73</v>
+      <c r="C90" s="68" t="s">
+        <v>96</v>
+      </c>
+      <c r="D90" s="68" t="s">
+        <v>70</v>
       </c>
       <c r="E90" s="11">
         <v>4.4165548999999998E-2</v>
@@ -8151,8 +8047,8 @@
       <c r="B91" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C91" s="75"/>
-      <c r="D91" s="75"/>
+      <c r="C91" s="68"/>
+      <c r="D91" s="68"/>
       <c r="E91" s="11">
         <v>1.59034298E-2</v>
       </c>
@@ -8188,8 +8084,8 @@
       <c r="B92" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C92" s="75"/>
-      <c r="D92" s="75"/>
+      <c r="C92" s="68"/>
+      <c r="D92" s="68"/>
       <c r="E92" s="11">
         <v>0</v>
       </c>
@@ -8225,11 +8121,11 @@
       <c r="B94" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C94" s="75" t="s">
-        <v>100</v>
-      </c>
-      <c r="D94" s="75" t="s">
-        <v>75</v>
+      <c r="C94" s="68" t="s">
+        <v>97</v>
+      </c>
+      <c r="D94" s="68" t="s">
+        <v>72</v>
       </c>
       <c r="E94" s="11">
         <v>2.6537650900000001E-2</v>
@@ -8266,8 +8162,8 @@
       <c r="B95" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C95" s="75"/>
-      <c r="D95" s="75"/>
+      <c r="C95" s="68"/>
+      <c r="D95" s="68"/>
       <c r="E95" s="11">
         <v>9.4845755999999996E-3</v>
       </c>
@@ -8303,8 +8199,8 @@
       <c r="B96" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C96" s="75"/>
-      <c r="D96" s="75"/>
+      <c r="C96" s="68"/>
+      <c r="D96" s="68"/>
       <c r="E96" s="11">
         <v>1.9160760000000001E-4</v>
       </c>
@@ -8340,11 +8236,11 @@
       <c r="B98" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C98" s="75" t="s">
-        <v>101</v>
-      </c>
-      <c r="D98" s="75" t="s">
-        <v>76</v>
+      <c r="C98" s="68" t="s">
+        <v>98</v>
+      </c>
+      <c r="D98" s="68" t="s">
+        <v>73</v>
       </c>
       <c r="E98" s="11">
         <v>6.6104618E-3</v>
@@ -8381,8 +8277,8 @@
       <c r="B99" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C99" s="75"/>
-      <c r="D99" s="75"/>
+      <c r="C99" s="68"/>
+      <c r="D99" s="68"/>
       <c r="E99" s="11">
         <v>8.9097528000000002E-3</v>
       </c>
@@ -8418,8 +8314,8 @@
       <c r="B100" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C100" s="75"/>
-      <c r="D100" s="75"/>
+      <c r="C100" s="68"/>
+      <c r="D100" s="68"/>
       <c r="E100" s="11">
         <v>1.6286645000000001E-3</v>
       </c>
@@ -8449,12 +8345,12 @@
       </c>
     </row>
     <row r="103" spans="1:14" s="14" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A103" s="88" t="s">
+      <c r="A103" s="69" t="s">
         <v>59</v>
       </c>
-      <c r="B103" s="88"/>
-      <c r="C103" s="88"/>
-      <c r="D103" s="88"/>
+      <c r="B103" s="69"/>
+      <c r="C103" s="69"/>
+      <c r="D103" s="69"/>
       <c r="E103" s="16">
         <f t="shared" ref="E103:L103" si="4">MAX(E73:E101)</f>
         <v>4.4165548999999998E-2</v>
@@ -8490,86 +8386,50 @@
       <c r="M103" s="16"/>
       <c r="N103" s="17"/>
     </row>
-    <row r="104" spans="1:14" s="52" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A104" s="83" t="s">
+    <row r="104" spans="1:14" s="41" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A104" s="73" t="s">
         <v>60</v>
       </c>
-      <c r="B104" s="83"/>
-      <c r="C104" s="83"/>
-      <c r="D104" s="83"/>
-      <c r="E104" s="29">
+      <c r="B104" s="73"/>
+      <c r="C104" s="73"/>
+      <c r="D104" s="73"/>
+      <c r="E104" s="22">
         <f t="shared" ref="E104:L104" si="5">AVERAGE(E74:E101)</f>
         <v>1.0789332023809524E-2</v>
       </c>
-      <c r="F104" s="29">
+      <c r="F104" s="22">
         <f t="shared" si="5"/>
         <v>6.1223186428571424E-3</v>
       </c>
-      <c r="G104" s="29">
+      <c r="G104" s="22">
         <f t="shared" si="5"/>
         <v>0.38850719441428572</v>
       </c>
-      <c r="H104" s="29">
+      <c r="H104" s="22">
         <f t="shared" si="5"/>
         <v>0.59446806516190465</v>
       </c>
-      <c r="I104" s="29">
+      <c r="I104" s="22">
         <f t="shared" si="5"/>
         <v>0.481445747004762</v>
       </c>
-      <c r="J104" s="29">
+      <c r="J104" s="22">
         <f t="shared" si="5"/>
         <v>0.20379323860952378</v>
       </c>
-      <c r="K104" s="29">
+      <c r="K104" s="22">
         <f t="shared" si="5"/>
         <v>0.43497647070952389</v>
       </c>
-      <c r="L104" s="29">
+      <c r="L104" s="22">
         <f t="shared" si="5"/>
         <v>0.29626653144952381</v>
       </c>
-      <c r="M104" s="29"/>
-      <c r="N104" s="58"/>
+      <c r="M104" s="22"/>
+      <c r="N104" s="47"/>
     </row>
   </sheetData>
   <mergeCells count="52">
-    <mergeCell ref="A4:I4"/>
-    <mergeCell ref="C22:C24"/>
-    <mergeCell ref="D22:D24"/>
-    <mergeCell ref="C26:C28"/>
-    <mergeCell ref="D26:D28"/>
-    <mergeCell ref="D6:D8"/>
-    <mergeCell ref="D10:D12"/>
-    <mergeCell ref="C6:C8"/>
-    <mergeCell ref="C10:C12"/>
-    <mergeCell ref="D18:D20"/>
-    <mergeCell ref="C18:C20"/>
-    <mergeCell ref="A35:D35"/>
-    <mergeCell ref="A36:D36"/>
-    <mergeCell ref="C14:C16"/>
-    <mergeCell ref="D14:D16"/>
-    <mergeCell ref="C30:C32"/>
-    <mergeCell ref="D30:D32"/>
-    <mergeCell ref="A38:I38"/>
-    <mergeCell ref="C40:C42"/>
-    <mergeCell ref="D40:D42"/>
-    <mergeCell ref="C44:C46"/>
-    <mergeCell ref="D44:D46"/>
-    <mergeCell ref="C48:C50"/>
-    <mergeCell ref="D48:D50"/>
-    <mergeCell ref="C52:C54"/>
-    <mergeCell ref="D52:D54"/>
-    <mergeCell ref="C56:C58"/>
-    <mergeCell ref="D56:D58"/>
-    <mergeCell ref="D74:D76"/>
-    <mergeCell ref="C78:C80"/>
-    <mergeCell ref="D78:D80"/>
-    <mergeCell ref="C60:C62"/>
-    <mergeCell ref="D60:D62"/>
-    <mergeCell ref="C64:C66"/>
-    <mergeCell ref="D64:D66"/>
-    <mergeCell ref="A69:D69"/>
     <mergeCell ref="A1:XFD1"/>
     <mergeCell ref="A104:D104"/>
     <mergeCell ref="C94:C96"/>
@@ -8586,6 +8446,42 @@
     <mergeCell ref="A70:D70"/>
     <mergeCell ref="A72:I72"/>
     <mergeCell ref="C74:C76"/>
+    <mergeCell ref="D74:D76"/>
+    <mergeCell ref="C78:C80"/>
+    <mergeCell ref="D78:D80"/>
+    <mergeCell ref="C60:C62"/>
+    <mergeCell ref="D60:D62"/>
+    <mergeCell ref="C64:C66"/>
+    <mergeCell ref="D64:D66"/>
+    <mergeCell ref="A69:D69"/>
+    <mergeCell ref="C48:C50"/>
+    <mergeCell ref="D48:D50"/>
+    <mergeCell ref="C52:C54"/>
+    <mergeCell ref="D52:D54"/>
+    <mergeCell ref="C56:C58"/>
+    <mergeCell ref="D56:D58"/>
+    <mergeCell ref="A38:I38"/>
+    <mergeCell ref="C40:C42"/>
+    <mergeCell ref="D40:D42"/>
+    <mergeCell ref="C44:C46"/>
+    <mergeCell ref="D44:D46"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A36:D36"/>
+    <mergeCell ref="C14:C16"/>
+    <mergeCell ref="D14:D16"/>
+    <mergeCell ref="C30:C32"/>
+    <mergeCell ref="D30:D32"/>
+    <mergeCell ref="A4:I4"/>
+    <mergeCell ref="C22:C24"/>
+    <mergeCell ref="D22:D24"/>
+    <mergeCell ref="C26:C28"/>
+    <mergeCell ref="D26:D28"/>
+    <mergeCell ref="D6:D8"/>
+    <mergeCell ref="D10:D12"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="C10:C12"/>
+    <mergeCell ref="D18:D20"/>
+    <mergeCell ref="C18:C20"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -8593,7 +8489,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B868A83-228E-4B46-AAFD-22D8E7035CA7}">
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:K18"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="22.6640625" defaultRowHeight="21" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="34.5" style="1" customWidth="1"/>
@@ -8603,15 +8499,16 @@
     <col min="5" max="6" width="26.1640625" style="1" customWidth="1"/>
     <col min="7" max="9" width="22.6640625" style="1"/>
     <col min="10" max="10" width="31.1640625" style="1" customWidth="1"/>
-    <col min="11" max="16384" width="22.6640625" style="1"/>
+    <col min="11" max="11" width="16.83203125" style="80" customWidth="1"/>
+    <col min="12" max="16384" width="22.6640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="71" customFormat="1" ht="27" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="71" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" s="6" customFormat="1" ht="66" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11" s="65" customFormat="1" ht="27" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="65" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" s="6" customFormat="1" ht="66" x14ac:dyDescent="0.2">
       <c r="A2" s="6" t="s">
         <v>0</v>
       </c>
@@ -8619,42 +8516,45 @@
         <v>1</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="E2" s="7" t="s">
         <v>55</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="G2" s="12" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="H2" s="12" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="I2" s="12" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="J2" s="7" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+        <v>111</v>
+      </c>
+      <c r="K2" s="79" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="75" t="s">
-        <v>107</v>
-      </c>
-      <c r="D4" s="75" t="s">
-        <v>109</v>
+      <c r="C4" s="68" t="s">
+        <v>104</v>
+      </c>
+      <c r="D4" s="68" t="s">
+        <v>106</v>
       </c>
       <c r="E4" s="1">
         <v>0.68648130389999995</v>
@@ -8675,16 +8575,20 @@
         <f>G4*1/3+H4*1/3+I4*1/3</f>
         <v>0.38645857859999999</v>
       </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K4" s="80">
+        <f>STDEV(J4,G4:I4)</f>
+        <v>0.29558263577738919</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="75"/>
-      <c r="D5" s="75"/>
+      <c r="C5" s="68"/>
+      <c r="D5" s="68"/>
       <c r="E5" s="1">
         <v>0.51505273250000005</v>
       </c>
@@ -8704,16 +8608,20 @@
         <f t="shared" ref="J5:J14" si="0">G5*1/3+H5*1/3+I5*1/3</f>
         <v>0.34069669856666668</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K5" s="80">
+        <f>STDEV(J5,G5:I5)</f>
+        <v>0.19232818047053601</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="75"/>
-      <c r="D6" s="75"/>
+      <c r="C6" s="68"/>
+      <c r="D6" s="68"/>
       <c r="E6" s="1">
         <v>3.79674017E-2</v>
       </c>
@@ -8733,110 +8641,129 @@
         <f t="shared" si="0"/>
         <v>0.33626065166666669</v>
       </c>
-    </row>
-    <row r="8" spans="1:10" s="42" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="42" t="s">
+      <c r="K6" s="80">
+        <f>STDEV(J6,G6:I6)</f>
+        <v>0.44288803485512168</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" s="76" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="76" t="s">
         <v>2</v>
       </c>
-      <c r="B8" s="42" t="s">
+      <c r="B8" s="76" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="89" t="s">
-        <v>110</v>
-      </c>
-      <c r="D8" s="75" t="s">
-        <v>111</v>
-      </c>
-      <c r="E8" s="42">
+      <c r="C8" s="77" t="s">
+        <v>107</v>
+      </c>
+      <c r="D8" s="77" t="s">
+        <v>108</v>
+      </c>
+      <c r="E8" s="76">
         <v>0.70795781400000002</v>
       </c>
-      <c r="F8" s="42">
+      <c r="F8" s="76">
         <v>0.89434324070000004</v>
       </c>
-      <c r="G8" s="67">
+      <c r="G8" s="78">
         <v>0.79573876789999998</v>
       </c>
-      <c r="H8" s="67">
+      <c r="H8" s="78">
         <v>0.31020942410000002</v>
       </c>
-      <c r="I8" s="67">
+      <c r="I8" s="78">
         <v>0.14285714290000001</v>
       </c>
-      <c r="J8" s="66">
+      <c r="J8" s="76">
         <f>G8*1/3+H8*1/3+I8*1/3</f>
         <v>0.41626844496666671</v>
       </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A9" s="1" t="s">
+      <c r="K8" s="81">
+        <f>STDEV(J8,G8:I8)</f>
+        <v>0.27688745125779551</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" s="76" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="76" t="s">
         <v>3</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" s="76" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="89"/>
-      <c r="D9" s="75"/>
-      <c r="E9" s="1">
+      <c r="C9" s="77"/>
+      <c r="D9" s="77"/>
+      <c r="E9" s="76">
         <v>0.27823585810000001</v>
       </c>
-      <c r="F9" s="1">
+      <c r="F9" s="76">
         <v>0.69242569509999996</v>
       </c>
-      <c r="G9" s="11">
+      <c r="G9" s="78">
         <v>0.26146364059999999</v>
       </c>
-      <c r="H9" s="11">
+      <c r="H9" s="78">
         <v>0.33900523560000001</v>
       </c>
-      <c r="I9" s="11">
+      <c r="I9" s="78">
         <v>0.47368421049999998</v>
       </c>
-      <c r="J9" s="1">
+      <c r="J9" s="76">
         <f t="shared" si="0"/>
         <v>0.35805102890000001</v>
       </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A10" s="1" t="s">
+      <c r="K9" s="81">
+        <f>STDEV(J9,G9:I9)</f>
+        <v>8.7679147098915777E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" s="76" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="76" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B10" s="76" t="s">
         <v>7</v>
       </c>
-      <c r="C10" s="89"/>
-      <c r="D10" s="75"/>
-      <c r="E10" s="1">
+      <c r="C10" s="77"/>
+      <c r="D10" s="77"/>
+      <c r="E10" s="76">
         <v>2.9146692200000001E-2</v>
       </c>
-      <c r="F10" s="1">
+      <c r="F10" s="76">
         <v>0.1883029722</v>
       </c>
-      <c r="G10" s="11">
+      <c r="G10" s="78">
         <v>6.9476610000000002E-4</v>
       </c>
-      <c r="H10" s="11">
+      <c r="H10" s="78">
         <v>2.4869109899999998E-2</v>
       </c>
-      <c r="I10" s="11">
+      <c r="I10" s="78">
         <v>0.97744360900000005</v>
       </c>
-      <c r="J10" s="1">
+      <c r="J10" s="76">
         <f t="shared" si="0"/>
         <v>0.33433582833333336</v>
       </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K10" s="81">
+        <f>STDEV(J10,G10:I10)</f>
+        <v>0.45485295271478982</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" s="76" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="K11" s="81"/>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C12" s="75" t="s">
-        <v>112</v>
-      </c>
-      <c r="D12" s="75" t="s">
-        <v>113</v>
+      <c r="C12" s="68" t="s">
+        <v>109</v>
+      </c>
+      <c r="D12" s="68" t="s">
+        <v>110</v>
       </c>
       <c r="E12" s="1">
         <v>0.7549338954</v>
@@ -8857,45 +8784,53 @@
         <f t="shared" si="0"/>
         <v>0.40264688770000001</v>
       </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A13" s="1" t="s">
+      <c r="K12" s="80">
+        <f>STDEV(J12,G12:I12)</f>
+        <v>0.34092242455712579</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" s="31" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="31" t="s">
         <v>3</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="B13" s="31" t="s">
         <v>6</v>
       </c>
-      <c r="C13" s="75"/>
-      <c r="D13" s="75"/>
-      <c r="E13" s="1">
+      <c r="C13" s="68"/>
+      <c r="D13" s="68"/>
+      <c r="E13" s="31">
         <v>0.42057865490000002</v>
       </c>
-      <c r="F13" s="1">
+      <c r="F13" s="31">
         <v>0.64073577309999996</v>
       </c>
-      <c r="G13" s="1">
+      <c r="G13" s="31">
         <v>0.45162037040000003</v>
       </c>
-      <c r="H13" s="1">
+      <c r="H13" s="31">
         <v>0.25130890049999999</v>
       </c>
-      <c r="I13" s="1">
+      <c r="I13" s="31">
         <v>0.3851851852</v>
       </c>
-      <c r="J13" s="1">
+      <c r="J13" s="31">
         <f t="shared" si="0"/>
         <v>0.36270481870000004</v>
       </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K13" s="82">
+        <f>STDEV(J13,G13:I13)</f>
+        <v>8.3307448253864089E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C14" s="75"/>
-      <c r="D14" s="75"/>
+      <c r="C14" s="68"/>
+      <c r="D14" s="68"/>
       <c r="E14" s="1">
         <v>0.78884843839999996</v>
       </c>
@@ -8914,6 +8849,49 @@
       <c r="J14" s="1">
         <f t="shared" si="0"/>
         <v>0.32867421303333333</v>
+      </c>
+      <c r="K14" s="80">
+        <f>STDEV(J14,G14:I14)</f>
+        <v>0.44027473437700593</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" s="83" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="I16" s="48" t="s">
+        <v>59</v>
+      </c>
+      <c r="J16" s="83">
+        <f>MAX(J4:J14)</f>
+        <v>0.41626844496666671</v>
+      </c>
+      <c r="K16" s="84">
+        <f>MAX(K4:K14)</f>
+        <v>0.45485295271478982</v>
+      </c>
+    </row>
+    <row r="17" spans="9:11" s="83" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="I17" s="48" t="s">
+        <v>129</v>
+      </c>
+      <c r="J17" s="83">
+        <f>MIN(J4:J14)</f>
+        <v>0.32867421303333333</v>
+      </c>
+      <c r="K17" s="84">
+        <f>MIN(K4:K14)</f>
+        <v>8.3307448253864089E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="9:11" s="83" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="I18" s="48" t="s">
+        <v>60</v>
+      </c>
+      <c r="J18" s="83">
+        <f>AVERAGE(J4:J14)</f>
+        <v>0.36289968338518519</v>
+      </c>
+      <c r="K18" s="84">
+        <f>AVERAGE(K4:K14)</f>
+        <v>0.29052477881806044</v>
       </c>
     </row>
   </sheetData>
@@ -8927,6 +8905,9 @@
     <mergeCell ref="D8:D10"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ignoredErrors>
+    <ignoredError sqref="K4:K6 K8:K10 K12:K14" formulaRange="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
@@ -8947,9 +8928,9 @@
     <col min="13" max="16384" width="22.6640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="71" customFormat="1" ht="27" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="71" t="s">
-        <v>120</v>
+    <row r="1" spans="1:12" s="65" customFormat="1" ht="27" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="65" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="2" spans="1:12" s="7" customFormat="1" ht="66" x14ac:dyDescent="0.2">
@@ -8960,284 +8941,129 @@
         <v>1</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="E2" s="7" t="s">
         <v>55</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="G2" s="12" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="H2" s="12" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="I2" s="12" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="J2" s="7" t="s">
         <v>57</v>
       </c>
       <c r="K2" s="7" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="77" t="s">
+      <c r="A4" s="60" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="75" t="s">
-        <v>47</v>
-      </c>
-      <c r="D4" s="75" t="s">
+      <c r="C4" s="68" t="s">
         <v>109</v>
       </c>
-      <c r="E4" s="1">
-        <v>0.62550335570000004</v>
-      </c>
-      <c r="F4" s="1">
-        <v>0.85330776610000003</v>
-      </c>
-      <c r="G4" s="11">
-        <v>0.68249189440000002</v>
-      </c>
-      <c r="H4" s="11">
-        <v>0.40575916229999998</v>
-      </c>
-      <c r="I4" s="11">
-        <v>3.7593985000000003E-2</v>
-      </c>
-      <c r="J4" s="1">
-        <v>0.73139733309999999</v>
-      </c>
-      <c r="K4" s="1">
-        <f>E4*1/5+G4*1/5+H4*1/5+I4*1/5+J4*1/5</f>
-        <v>0.49654914610000001</v>
-      </c>
-      <c r="L4" s="90" t="s">
-        <v>129</v>
-      </c>
+      <c r="D4" s="68"/>
+      <c r="G4" s="11"/>
+      <c r="H4" s="11"/>
+      <c r="I4" s="11"/>
+      <c r="L4" s="75"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A5" s="77"/>
+      <c r="A5" s="60"/>
       <c r="B5" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="C5" s="68"/>
+      <c r="D5" s="68"/>
+      <c r="G5" s="11"/>
+      <c r="H5" s="11"/>
+      <c r="I5" s="11"/>
+      <c r="L5" s="75"/>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A6" s="60"/>
+      <c r="B6" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="C6" s="68"/>
+      <c r="D6" s="68"/>
+      <c r="G6" s="11"/>
+      <c r="H6" s="11"/>
+      <c r="I6" s="11"/>
+    </row>
+    <row r="7" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C7" s="68"/>
+      <c r="D7" s="68"/>
+    </row>
+    <row r="8" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="60" t="s">
+        <v>119</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="C5" s="75"/>
-      <c r="D5" s="75"/>
-      <c r="E5" s="1">
-        <v>0.82301054650000005</v>
-      </c>
-      <c r="F5" s="1">
-        <v>0.97066155320000003</v>
-      </c>
-      <c r="G5" s="11">
-        <v>0.97568318669999998</v>
-      </c>
-      <c r="H5" s="11">
-        <v>0.1020942408</v>
-      </c>
-      <c r="I5" s="11">
-        <v>7.5187969999999998E-3</v>
-      </c>
-      <c r="J5" s="1">
-        <v>0.83872653870000002</v>
-      </c>
-      <c r="K5" s="1">
-        <f>E5*1/5+G5*1/5+H5*1/5+I5*1/5+J5*1/5</f>
-        <v>0.5494066619400001</v>
-      </c>
-      <c r="L5" s="90"/>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A6" s="77"/>
-      <c r="B6" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="C6" s="75"/>
-      <c r="D6" s="75"/>
-      <c r="E6" s="1">
-        <v>0.52540747840000002</v>
-      </c>
-      <c r="F6" s="1">
-        <v>0.71831255989999998</v>
-      </c>
-      <c r="G6" s="11">
-        <v>0.54585456229999996</v>
-      </c>
-      <c r="H6" s="11">
-        <v>0.44502617799999999</v>
-      </c>
-      <c r="I6" s="11">
-        <v>0.32330827070000001</v>
-      </c>
-      <c r="J6" s="1">
-        <v>0.46895855479999998</v>
-      </c>
-      <c r="K6" s="1">
-        <f>E6*1/5+G6*1/5+H6*1/5+I6*1/5+J6*1/5</f>
-        <v>0.46171100883999999</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C7" s="75"/>
-      <c r="D7" s="75"/>
-    </row>
-    <row r="8" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="77" t="s">
+      <c r="C8" s="68"/>
+      <c r="D8" s="68"/>
+      <c r="L8" s="75"/>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A9" s="60"/>
+      <c r="B9" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="C9" s="68"/>
+      <c r="D9" s="68"/>
+      <c r="L9" s="75"/>
+    </row>
+    <row r="10" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="60"/>
+      <c r="B10" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="C10" s="68"/>
+      <c r="D10" s="68"/>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="C11" s="68"/>
+      <c r="D11" s="68"/>
+    </row>
+    <row r="12" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="60" t="s">
+        <v>120</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="C8" s="75"/>
-      <c r="D8" s="75"/>
-      <c r="E8" s="1">
-        <v>0.27497603069999998</v>
-      </c>
-      <c r="F8" s="1">
-        <v>0.69434324069999998</v>
-      </c>
-      <c r="G8" s="1">
-        <v>0.26401111630000001</v>
-      </c>
-      <c r="H8" s="1">
-        <v>0.31544502619999998</v>
-      </c>
-      <c r="I8" s="1">
-        <v>0.3984962406</v>
-      </c>
-      <c r="J8" s="1">
-        <v>0.46539974550000002</v>
-      </c>
-      <c r="K8" s="1">
-        <f>E8*1/5+G8*1/5+H8*1/5+I8*1/5+J8*1/5</f>
-        <v>0.34366563185999999</v>
-      </c>
-      <c r="L8" s="90" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A9" s="77"/>
-      <c r="B9" s="1" t="s">
+      <c r="C12" s="68"/>
+      <c r="D12" s="68"/>
+    </row>
+    <row r="13" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="60"/>
+      <c r="B13" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="C9" s="75"/>
-      <c r="D9" s="75"/>
-      <c r="E9" s="1">
-        <v>0.4669223394</v>
-      </c>
-      <c r="F9" s="1">
-        <v>0.77890699900000004</v>
-      </c>
-      <c r="G9" s="1">
-        <v>0.48286243629999998</v>
-      </c>
-      <c r="H9" s="1">
-        <v>0.38481675389999997</v>
-      </c>
-      <c r="I9" s="1">
-        <v>0.4210526316</v>
-      </c>
-      <c r="J9" s="1">
-        <v>0.56444247859999996</v>
-      </c>
-      <c r="K9" s="1">
-        <f>E9*1/5+G9*1/5+H9*1/5+I9*1/5+J9*1/5</f>
-        <v>0.46401932795999995</v>
-      </c>
-      <c r="L9" s="90"/>
-    </row>
-    <row r="10" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="77"/>
-      <c r="B10" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="C10" s="75"/>
-      <c r="D10" s="75"/>
-      <c r="E10" s="1">
-        <v>0.57679769889999999</v>
-      </c>
-      <c r="F10" s="1">
-        <v>0.81054650049999999</v>
-      </c>
-      <c r="G10" s="1">
-        <v>0.62459471980000003</v>
-      </c>
-      <c r="H10" s="1">
-        <v>0.35078534030000003</v>
-      </c>
-      <c r="I10" s="1">
-        <v>0.32330827070000001</v>
-      </c>
-      <c r="J10" s="1">
-        <v>0.64231125950000001</v>
-      </c>
-      <c r="K10" s="1">
-        <f>E10*1/5+G10*1/5+H10*1/5+I10*1/5+J10*1/5</f>
-        <v>0.50355945784</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="C11" s="75"/>
-      <c r="D11" s="75"/>
-    </row>
-    <row r="12" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="77" t="s">
-        <v>123</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="C12" s="75"/>
-      <c r="D12" s="75"/>
-      <c r="E12" s="1">
-        <v>0.15627996159999999</v>
-      </c>
-      <c r="F12" s="1">
-        <v>0.82396931929999995</v>
-      </c>
-      <c r="G12" s="1">
-        <v>1.5979620199999999E-2</v>
-      </c>
-      <c r="H12" s="1">
-        <v>0.96596858640000005</v>
-      </c>
-      <c r="I12" s="1">
-        <v>6.0150375899999997E-2</v>
-      </c>
-      <c r="J12" s="1">
-        <v>0.53981483360000004</v>
-      </c>
-      <c r="K12" s="1">
-        <f>E12*1/5+G12*1/5+H12*1/5+I12*1/5+J12*1/5</f>
-        <v>0.34763867554</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="77"/>
-      <c r="B13" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="C13" s="75"/>
-      <c r="D13" s="75"/>
-      <c r="K13" s="1">
-        <f>E13*1/5+G13*1/5+H13*1/5+I13*1/5+J13*1/5</f>
-        <v>0</v>
-      </c>
+      <c r="C13" s="68"/>
+      <c r="D13" s="68"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="C14" s="50"/>
-      <c r="D14" s="50"/>
+      <c r="C14" s="39"/>
+      <c r="D14" s="39"/>
     </row>
   </sheetData>
   <mergeCells count="8">

--- a/benchmarking/results/results.xlsx
+++ b/benchmarking/results/results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/deborahdore/Documents/political-debates-graph-analysis/benchmarking/results/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22DF4EF7-AFF3-014D-9137-8BBEE1B6AB83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43F1B055-937D-A54F-AC30-6862DD7C71E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4280" yWindow="500" windowWidth="46920" windowHeight="26600" activeTab="5" xr2:uid="{E2EDC037-19C4-FE46-A599-BB595128A04F}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="51200" windowHeight="28800" activeTab="5" xr2:uid="{E2EDC037-19C4-FE46-A599-BB595128A04F}"/>
   </bookViews>
   <sheets>
     <sheet name="Basic" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,8 @@
     <sheet name="Pretrained-Special" sheetId="6" r:id="rId3"/>
     <sheet name="Improving Results" sheetId="7" r:id="rId4"/>
     <sheet name="Checking Bias" sheetId="8" r:id="rId5"/>
-    <sheet name="Other Models" sheetId="10" r:id="rId6"/>
+    <sheet name="Noise" sheetId="11" r:id="rId6"/>
+    <sheet name="Other Models" sheetId="10" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="685" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="758" uniqueCount="144">
   <si>
     <t>MODEL'S TYPE</t>
   </si>
@@ -496,6 +497,12 @@
   </si>
   <si>
     <t>BIASED TOWARDS EQUIVALENT</t>
+  </si>
+  <si>
+    <t>ARE MODEL ROBUST TO NOISE?</t>
+  </si>
+  <si>
+    <t>NOISE</t>
   </si>
 </sst>
 </file>
@@ -991,6 +998,9 @@
     <xf numFmtId="166" fontId="1" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1067,9 +1077,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1097,9 +1104,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - Tema 2022">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema di Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1137,7 +1144,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1243,7 +1250,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1385,7 +1392,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1410,8 +1417,8 @@
     <col min="12" max="16384" width="51.33203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="86" customFormat="1" ht="27" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="86" t="s">
+    <row r="1" spans="1:12" s="87" customFormat="1" ht="27" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="87" t="s">
         <v>109</v>
       </c>
     </row>
@@ -1458,13 +1465,13 @@
       <c r="B3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="94" t="s">
+      <c r="C3" s="95" t="s">
         <v>41</v>
       </c>
-      <c r="D3" s="91" t="s">
+      <c r="D3" s="92" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="91" t="s">
+      <c r="E3" s="92" t="s">
         <v>13</v>
       </c>
       <c r="F3" s="58">
@@ -1482,7 +1489,7 @@
       <c r="J3" s="58">
         <v>0.52440008120000003</v>
       </c>
-      <c r="K3" s="89" t="s">
+      <c r="K3" s="90" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1493,9 +1500,9 @@
       <c r="B4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="92"/>
-      <c r="D4" s="88"/>
-      <c r="E4" s="88"/>
+      <c r="C4" s="93"/>
+      <c r="D4" s="89"/>
+      <c r="E4" s="89"/>
       <c r="F4" s="58">
         <v>3.9117929099999997E-2</v>
       </c>
@@ -1511,7 +1518,7 @@
       <c r="J4" s="58">
         <v>0.4957882649</v>
       </c>
-      <c r="K4" s="90"/>
+      <c r="K4" s="91"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
@@ -1520,9 +1527,9 @@
       <c r="B5" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="92"/>
-      <c r="D5" s="88"/>
-      <c r="E5" s="88"/>
+      <c r="C5" s="93"/>
+      <c r="D5" s="89"/>
+      <c r="E5" s="89"/>
       <c r="F5" s="58">
         <v>2.1093001000000002E-3</v>
       </c>
@@ -1538,7 +1545,7 @@
       <c r="J5" s="58">
         <v>0.4776301698</v>
       </c>
-      <c r="K5" s="90"/>
+      <c r="K5" s="91"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
@@ -1547,13 +1554,13 @@
       <c r="B7" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="92" t="s">
+      <c r="C7" s="93" t="s">
         <v>42</v>
       </c>
-      <c r="D7" s="88" t="s">
+      <c r="D7" s="89" t="s">
         <v>10</v>
       </c>
-      <c r="E7" s="88" t="s">
+      <c r="E7" s="89" t="s">
         <v>13</v>
       </c>
       <c r="F7" s="58">
@@ -1571,7 +1578,7 @@
       <c r="J7" s="58">
         <v>0.51801477490000003</v>
       </c>
-      <c r="K7" s="90" t="s">
+      <c r="K7" s="91" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1582,9 +1589,9 @@
       <c r="B8" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="92"/>
-      <c r="D8" s="88"/>
-      <c r="E8" s="88"/>
+      <c r="C8" s="93"/>
+      <c r="D8" s="89"/>
+      <c r="E8" s="89"/>
       <c r="F8" s="58">
         <v>3.2094270899999999E-2</v>
       </c>
@@ -1600,7 +1607,7 @@
       <c r="J8" s="58">
         <v>0.50083099880000004</v>
       </c>
-      <c r="K8" s="90"/>
+      <c r="K8" s="91"/>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
@@ -1609,9 +1616,9 @@
       <c r="B9" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="92"/>
-      <c r="D9" s="88"/>
-      <c r="E9" s="88"/>
+      <c r="C9" s="93"/>
+      <c r="D9" s="89"/>
+      <c r="E9" s="89"/>
       <c r="F9" s="58">
         <v>2.8741139999999998E-4</v>
       </c>
@@ -1627,15 +1634,15 @@
       <c r="J9" s="58">
         <v>0.4887305689</v>
       </c>
-      <c r="K9" s="90"/>
+      <c r="K9" s="91"/>
     </row>
     <row r="11" spans="1:12" s="35" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="93" t="s">
+      <c r="A11" s="94" t="s">
         <v>37</v>
       </c>
-      <c r="B11" s="93"/>
-      <c r="C11" s="93"/>
-      <c r="D11" s="93"/>
+      <c r="B11" s="94"/>
+      <c r="C11" s="94"/>
+      <c r="D11" s="94"/>
       <c r="E11" s="36"/>
       <c r="F11" s="61"/>
       <c r="G11" s="61"/>
@@ -1651,13 +1658,13 @@
       <c r="B13" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C13" s="92" t="s">
+      <c r="C13" s="93" t="s">
         <v>43</v>
       </c>
-      <c r="D13" s="88" t="s">
+      <c r="D13" s="89" t="s">
         <v>11</v>
       </c>
-      <c r="E13" s="88" t="s">
+      <c r="E13" s="89" t="s">
         <v>17</v>
       </c>
       <c r="F13" s="58">
@@ -1675,7 +1682,7 @@
       <c r="J13" s="58">
         <v>0.65087326729999995</v>
       </c>
-      <c r="K13" s="90" t="s">
+      <c r="K13" s="91" t="s">
         <v>18</v>
       </c>
     </row>
@@ -1686,9 +1693,9 @@
       <c r="B14" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C14" s="92"/>
-      <c r="D14" s="88"/>
-      <c r="E14" s="88"/>
+      <c r="C14" s="93"/>
+      <c r="D14" s="89"/>
+      <c r="E14" s="89"/>
       <c r="F14" s="58">
         <v>1.0937623800000001E-2</v>
       </c>
@@ -1704,7 +1711,7 @@
       <c r="J14" s="58">
         <v>0.48031703009999999</v>
       </c>
-      <c r="K14" s="90"/>
+      <c r="K14" s="91"/>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
@@ -1713,9 +1720,9 @@
       <c r="B15" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C15" s="92"/>
-      <c r="D15" s="88"/>
-      <c r="E15" s="88"/>
+      <c r="C15" s="93"/>
+      <c r="D15" s="89"/>
+      <c r="E15" s="89"/>
       <c r="F15" s="58">
         <v>2.377744E-4</v>
       </c>
@@ -1731,7 +1738,7 @@
       <c r="J15" s="58">
         <v>0.49770047779999999</v>
       </c>
-      <c r="K15" s="90"/>
+      <c r="K15" s="91"/>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
@@ -1740,13 +1747,13 @@
       <c r="B17" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C17" s="92" t="s">
+      <c r="C17" s="93" t="s">
         <v>44</v>
       </c>
-      <c r="D17" s="88" t="s">
+      <c r="D17" s="89" t="s">
         <v>19</v>
       </c>
-      <c r="E17" s="88" t="s">
+      <c r="E17" s="89" t="s">
         <v>27</v>
       </c>
       <c r="F17" s="58">
@@ -1764,7 +1771,7 @@
       <c r="J17" s="58">
         <v>0.44106115289999998</v>
       </c>
-      <c r="K17" s="90" t="s">
+      <c r="K17" s="91" t="s">
         <v>36</v>
       </c>
     </row>
@@ -1775,9 +1782,9 @@
       <c r="B18" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C18" s="92"/>
-      <c r="D18" s="88"/>
-      <c r="E18" s="88"/>
+      <c r="C18" s="93"/>
+      <c r="D18" s="89"/>
+      <c r="E18" s="89"/>
       <c r="F18" s="58">
         <v>6.6187922000000001E-3</v>
       </c>
@@ -1793,7 +1800,7 @@
       <c r="J18" s="58">
         <v>0.48203358359999998</v>
       </c>
-      <c r="K18" s="90"/>
+      <c r="K18" s="91"/>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
@@ -1802,9 +1809,9 @@
       <c r="B19" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C19" s="92"/>
-      <c r="D19" s="88"/>
-      <c r="E19" s="88"/>
+      <c r="C19" s="93"/>
+      <c r="D19" s="89"/>
+      <c r="E19" s="89"/>
       <c r="F19" s="58">
         <v>1.9467035999999999E-3</v>
       </c>
@@ -1820,7 +1827,7 @@
       <c r="J19" s="58">
         <v>0.31319458500000003</v>
       </c>
-      <c r="K19" s="90"/>
+      <c r="K19" s="91"/>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
@@ -1829,13 +1836,13 @@
       <c r="B21" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C21" s="92" t="s">
+      <c r="C21" s="93" t="s">
         <v>45</v>
       </c>
-      <c r="D21" s="88" t="s">
+      <c r="D21" s="89" t="s">
         <v>20</v>
       </c>
-      <c r="E21" s="88" t="s">
+      <c r="E21" s="89" t="s">
         <v>28</v>
       </c>
       <c r="F21" s="58">
@@ -1853,7 +1860,7 @@
       <c r="J21" s="58">
         <v>0.42558258160000001</v>
       </c>
-      <c r="K21" s="90" t="s">
+      <c r="K21" s="91" t="s">
         <v>35</v>
       </c>
     </row>
@@ -1864,9 +1871,9 @@
       <c r="B22" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C22" s="92"/>
-      <c r="D22" s="88"/>
-      <c r="E22" s="88"/>
+      <c r="C22" s="93"/>
+      <c r="D22" s="89"/>
+      <c r="E22" s="89"/>
       <c r="F22" s="58">
         <v>0.36964094320000002</v>
       </c>
@@ -1882,7 +1889,7 @@
       <c r="J22" s="58">
         <v>0.71370811339999995</v>
       </c>
-      <c r="K22" s="90"/>
+      <c r="K22" s="91"/>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
@@ -1891,9 +1898,9 @@
       <c r="B23" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C23" s="92"/>
-      <c r="D23" s="88"/>
-      <c r="E23" s="88"/>
+      <c r="C23" s="93"/>
+      <c r="D23" s="89"/>
+      <c r="E23" s="89"/>
       <c r="F23" s="58">
         <v>1.786352E-4</v>
       </c>
@@ -1909,7 +1916,7 @@
       <c r="J23" s="58">
         <v>0.35677707139999998</v>
       </c>
-      <c r="K23" s="90"/>
+      <c r="K23" s="91"/>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
@@ -1918,13 +1925,13 @@
       <c r="B25" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C25" s="92" t="s">
+      <c r="C25" s="93" t="s">
         <v>46</v>
       </c>
-      <c r="D25" s="88" t="s">
+      <c r="D25" s="89" t="s">
         <v>21</v>
       </c>
-      <c r="E25" s="88" t="s">
+      <c r="E25" s="89" t="s">
         <v>32</v>
       </c>
       <c r="F25" s="58">
@@ -1950,9 +1957,9 @@
       <c r="B26" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C26" s="92"/>
-      <c r="D26" s="88"/>
-      <c r="E26" s="88"/>
+      <c r="C26" s="93"/>
+      <c r="D26" s="89"/>
+      <c r="E26" s="89"/>
       <c r="F26" s="58">
         <v>2.2257384000000002E-2</v>
       </c>
@@ -1976,9 +1983,9 @@
       <c r="B27" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C27" s="92"/>
-      <c r="D27" s="88"/>
-      <c r="E27" s="88"/>
+      <c r="C27" s="93"/>
+      <c r="D27" s="89"/>
+      <c r="E27" s="89"/>
       <c r="F27" s="58">
         <v>3.9556960000000001E-4</v>
       </c>
@@ -2002,13 +2009,13 @@
       <c r="B29" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C29" s="92" t="s">
+      <c r="C29" s="93" t="s">
         <v>47</v>
       </c>
-      <c r="D29" s="88" t="s">
+      <c r="D29" s="89" t="s">
         <v>22</v>
       </c>
-      <c r="E29" s="88" t="s">
+      <c r="E29" s="89" t="s">
         <v>33</v>
       </c>
       <c r="F29" s="58">
@@ -2034,9 +2041,9 @@
       <c r="B30" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C30" s="92"/>
-      <c r="D30" s="88"/>
-      <c r="E30" s="88"/>
+      <c r="C30" s="93"/>
+      <c r="D30" s="89"/>
+      <c r="E30" s="89"/>
       <c r="F30" s="58">
         <v>1.8442843300000001E-2</v>
       </c>
@@ -2060,9 +2067,9 @@
       <c r="B31" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C31" s="92"/>
-      <c r="D31" s="88"/>
-      <c r="E31" s="88"/>
+      <c r="C31" s="93"/>
+      <c r="D31" s="89"/>
+      <c r="E31" s="89"/>
       <c r="F31" s="58">
         <v>6.9899990000000004E-4</v>
       </c>
@@ -2086,13 +2093,13 @@
       <c r="B33" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C33" s="92" t="s">
+      <c r="C33" s="93" t="s">
         <v>48</v>
       </c>
-      <c r="D33" s="88" t="s">
+      <c r="D33" s="89" t="s">
         <v>23</v>
       </c>
-      <c r="E33" s="88" t="s">
+      <c r="E33" s="89" t="s">
         <v>29</v>
       </c>
       <c r="F33" s="58">
@@ -2118,9 +2125,9 @@
       <c r="B34" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C34" s="92"/>
-      <c r="D34" s="88"/>
-      <c r="E34" s="88"/>
+      <c r="C34" s="93"/>
+      <c r="D34" s="89"/>
+      <c r="E34" s="89"/>
       <c r="F34" s="58">
         <v>4.8571429999999999E-4</v>
       </c>
@@ -2144,9 +2151,9 @@
       <c r="B35" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C35" s="92"/>
-      <c r="D35" s="88"/>
-      <c r="E35" s="88"/>
+      <c r="C35" s="93"/>
+      <c r="D35" s="89"/>
+      <c r="E35" s="89"/>
       <c r="F35" s="58">
         <v>8.5714299999999993E-5</v>
       </c>
@@ -2170,13 +2177,13 @@
       <c r="B37" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C37" s="92" t="s">
+      <c r="C37" s="93" t="s">
         <v>49</v>
       </c>
-      <c r="D37" s="88" t="s">
+      <c r="D37" s="89" t="s">
         <v>24</v>
       </c>
-      <c r="E37" s="88" t="s">
+      <c r="E37" s="89" t="s">
         <v>34</v>
       </c>
       <c r="F37" s="58">
@@ -2202,9 +2209,9 @@
       <c r="B38" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C38" s="92"/>
-      <c r="D38" s="88"/>
-      <c r="E38" s="88"/>
+      <c r="C38" s="93"/>
+      <c r="D38" s="89"/>
+      <c r="E38" s="89"/>
       <c r="F38" s="58">
         <v>0.12567659680000001</v>
       </c>
@@ -2228,9 +2235,9 @@
       <c r="B39" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C39" s="92"/>
-      <c r="D39" s="88"/>
-      <c r="E39" s="88"/>
+      <c r="C39" s="93"/>
+      <c r="D39" s="89"/>
+      <c r="E39" s="89"/>
       <c r="F39" s="58">
         <v>5.4127739999999998E-4</v>
       </c>
@@ -2248,12 +2255,12 @@
       </c>
     </row>
     <row r="41" spans="1:11" s="35" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="93" t="s">
+      <c r="A41" s="94" t="s">
         <v>38</v>
       </c>
-      <c r="B41" s="93"/>
-      <c r="C41" s="93"/>
-      <c r="D41" s="93"/>
+      <c r="B41" s="94"/>
+      <c r="C41" s="94"/>
+      <c r="D41" s="94"/>
       <c r="E41" s="36"/>
       <c r="F41" s="61"/>
       <c r="G41" s="61"/>
@@ -2269,13 +2276,13 @@
       <c r="B43" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C43" s="92" t="s">
+      <c r="C43" s="93" t="s">
         <v>50</v>
       </c>
-      <c r="D43" s="88" t="s">
+      <c r="D43" s="89" t="s">
         <v>25</v>
       </c>
-      <c r="E43" s="88" t="s">
+      <c r="E43" s="89" t="s">
         <v>27</v>
       </c>
       <c r="F43" s="58">
@@ -2293,7 +2300,7 @@
       <c r="J43" s="58">
         <v>0.47978398890000001</v>
       </c>
-      <c r="K43" s="90" t="s">
+      <c r="K43" s="91" t="s">
         <v>30</v>
       </c>
     </row>
@@ -2304,9 +2311,9 @@
       <c r="B44" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C44" s="92"/>
-      <c r="D44" s="88"/>
-      <c r="E44" s="88"/>
+      <c r="C44" s="93"/>
+      <c r="D44" s="89"/>
+      <c r="E44" s="89"/>
       <c r="F44" s="58">
         <v>0.15768715</v>
       </c>
@@ -2322,7 +2329,7 @@
       <c r="J44" s="58">
         <v>0.64265883619999997</v>
       </c>
-      <c r="K44" s="90"/>
+      <c r="K44" s="91"/>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
@@ -2331,9 +2338,9 @@
       <c r="B45" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C45" s="92"/>
-      <c r="D45" s="88"/>
-      <c r="E45" s="88"/>
+      <c r="C45" s="93"/>
+      <c r="D45" s="89"/>
+      <c r="E45" s="89"/>
       <c r="F45" s="58">
         <v>1.5776599999999999E-4</v>
       </c>
@@ -2349,7 +2356,7 @@
       <c r="J45" s="58">
         <v>0.33957444949999999</v>
       </c>
-      <c r="K45" s="90"/>
+      <c r="K45" s="91"/>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A47" s="1" t="s">
@@ -2358,13 +2365,13 @@
       <c r="B47" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C47" s="92" t="s">
+      <c r="C47" s="93" t="s">
         <v>51</v>
       </c>
-      <c r="D47" s="88" t="s">
+      <c r="D47" s="89" t="s">
         <v>26</v>
       </c>
-      <c r="E47" s="88" t="s">
+      <c r="E47" s="89" t="s">
         <v>28</v>
       </c>
       <c r="F47" s="58">
@@ -2382,7 +2389,7 @@
       <c r="J47" s="58">
         <v>0.43650638670000003</v>
       </c>
-      <c r="K47" s="90" t="s">
+      <c r="K47" s="91" t="s">
         <v>31</v>
       </c>
     </row>
@@ -2393,9 +2400,9 @@
       <c r="B48" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C48" s="92"/>
-      <c r="D48" s="88"/>
-      <c r="E48" s="88"/>
+      <c r="C48" s="93"/>
+      <c r="D48" s="89"/>
+      <c r="E48" s="89"/>
       <c r="F48" s="58">
         <v>0.28846457310000001</v>
       </c>
@@ -2411,7 +2418,7 @@
       <c r="J48" s="58">
         <v>0.62979789600000002</v>
       </c>
-      <c r="K48" s="90"/>
+      <c r="K48" s="91"/>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A49" s="1" t="s">
@@ -2420,9 +2427,9 @@
       <c r="B49" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C49" s="92"/>
-      <c r="D49" s="88"/>
-      <c r="E49" s="88"/>
+      <c r="C49" s="93"/>
+      <c r="D49" s="89"/>
+      <c r="E49" s="89"/>
       <c r="F49" s="58">
         <v>2.7615590000000002E-4</v>
       </c>
@@ -2438,7 +2445,7 @@
       <c r="J49" s="58">
         <v>0.39453545410000002</v>
       </c>
-      <c r="K49" s="90"/>
+      <c r="K49" s="91"/>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A51" s="1" t="s">
@@ -2447,13 +2454,13 @@
       <c r="B51" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C51" s="92" t="s">
+      <c r="C51" s="93" t="s">
         <v>52</v>
       </c>
-      <c r="D51" s="88" t="s">
+      <c r="D51" s="89" t="s">
         <v>39</v>
       </c>
-      <c r="E51" s="88" t="s">
+      <c r="E51" s="89" t="s">
         <v>29</v>
       </c>
       <c r="F51" s="58">
@@ -2479,9 +2486,9 @@
       <c r="B52" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C52" s="92"/>
-      <c r="D52" s="88"/>
-      <c r="E52" s="88"/>
+      <c r="C52" s="93"/>
+      <c r="D52" s="89"/>
+      <c r="E52" s="89"/>
       <c r="F52" s="58">
         <v>3.5391416699999997E-2</v>
       </c>
@@ -2505,9 +2512,9 @@
       <c r="B53" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C53" s="92"/>
-      <c r="D53" s="88"/>
-      <c r="E53" s="88"/>
+      <c r="C53" s="93"/>
+      <c r="D53" s="89"/>
+      <c r="E53" s="89"/>
       <c r="F53" s="58">
         <v>9.9344299999999997E-5</v>
       </c>
@@ -2525,12 +2532,12 @@
       </c>
     </row>
     <row r="56" spans="1:11" s="25" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="95" t="s">
+      <c r="A56" s="96" t="s">
         <v>59</v>
       </c>
-      <c r="B56" s="95"/>
-      <c r="C56" s="95"/>
-      <c r="D56" s="95"/>
+      <c r="B56" s="96"/>
+      <c r="C56" s="96"/>
+      <c r="D56" s="96"/>
       <c r="E56" s="23"/>
       <c r="F56" s="83">
         <f>MAX(F3:F53)</f>
@@ -2555,12 +2562,12 @@
       <c r="K56" s="24"/>
     </row>
     <row r="57" spans="1:11" s="28" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="87" t="s">
+      <c r="A57" s="88" t="s">
         <v>60</v>
       </c>
-      <c r="B57" s="87"/>
-      <c r="C57" s="87"/>
-      <c r="D57" s="87"/>
+      <c r="B57" s="88"/>
+      <c r="C57" s="88"/>
+      <c r="D57" s="88"/>
       <c r="E57" s="26"/>
       <c r="F57" s="84">
         <f>AVERAGE(F3:F53)</f>
@@ -2658,8 +2665,8 @@
     <col min="12" max="16384" width="51.33203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="86" customFormat="1" ht="27" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="86" t="s">
+    <row r="1" spans="1:12" s="87" customFormat="1" ht="27" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="87" t="s">
         <v>110</v>
       </c>
     </row>
@@ -2706,13 +2713,13 @@
       <c r="B3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="94" t="s">
+      <c r="C3" s="95" t="s">
         <v>41</v>
       </c>
-      <c r="D3" s="91" t="s">
+      <c r="D3" s="92" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="91" t="s">
+      <c r="E3" s="92" t="s">
         <v>13</v>
       </c>
       <c r="F3" s="58">
@@ -2730,7 +2737,7 @@
       <c r="J3" s="58">
         <v>0.5008326072</v>
       </c>
-      <c r="K3" s="89" t="s">
+      <c r="K3" s="90" t="s">
         <v>15</v>
       </c>
     </row>
@@ -2741,9 +2748,9 @@
       <c r="B4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="92"/>
-      <c r="D4" s="88"/>
-      <c r="E4" s="88"/>
+      <c r="C4" s="93"/>
+      <c r="D4" s="89"/>
+      <c r="E4" s="89"/>
       <c r="F4" s="58">
         <v>2.8763183099999999E-2</v>
       </c>
@@ -2759,7 +2766,7 @@
       <c r="J4" s="58">
         <v>0.49456959480000001</v>
       </c>
-      <c r="K4" s="90"/>
+      <c r="K4" s="91"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
@@ -2768,9 +2775,9 @@
       <c r="B5" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="92"/>
-      <c r="D5" s="88"/>
-      <c r="E5" s="88"/>
+      <c r="C5" s="93"/>
+      <c r="D5" s="89"/>
+      <c r="E5" s="89"/>
       <c r="F5" s="58">
         <v>5.7526370000000003E-4</v>
       </c>
@@ -2786,7 +2793,7 @@
       <c r="J5" s="58">
         <v>0.46208879800000002</v>
       </c>
-      <c r="K5" s="90"/>
+      <c r="K5" s="91"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
@@ -2795,13 +2802,13 @@
       <c r="B7" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="92" t="s">
+      <c r="C7" s="93" t="s">
         <v>42</v>
       </c>
-      <c r="D7" s="88" t="s">
+      <c r="D7" s="89" t="s">
         <v>10</v>
       </c>
-      <c r="E7" s="88" t="s">
+      <c r="E7" s="89" t="s">
         <v>13</v>
       </c>
       <c r="F7" s="58">
@@ -2819,7 +2826,7 @@
       <c r="J7" s="58">
         <v>0.50993042769999997</v>
       </c>
-      <c r="K7" s="90" t="s">
+      <c r="K7" s="91" t="s">
         <v>16</v>
       </c>
     </row>
@@ -2830,9 +2837,9 @@
       <c r="B8" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="92"/>
-      <c r="D8" s="88"/>
-      <c r="E8" s="88"/>
+      <c r="C8" s="93"/>
+      <c r="D8" s="89"/>
+      <c r="E8" s="89"/>
       <c r="F8" s="58">
         <v>3.3435524000000001E-2</v>
       </c>
@@ -2848,7 +2855,7 @@
       <c r="J8" s="58">
         <v>0.50392556320000004</v>
       </c>
-      <c r="K8" s="90"/>
+      <c r="K8" s="91"/>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
@@ -2857,9 +2864,9 @@
       <c r="B9" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="92"/>
-      <c r="D9" s="88"/>
-      <c r="E9" s="88"/>
+      <c r="C9" s="93"/>
+      <c r="D9" s="89"/>
+      <c r="E9" s="89"/>
       <c r="F9" s="58">
         <v>3.8321520000000002E-4</v>
       </c>
@@ -2875,15 +2882,15 @@
       <c r="J9" s="58">
         <v>0.47738500210000001</v>
       </c>
-      <c r="K9" s="90"/>
+      <c r="K9" s="91"/>
     </row>
     <row r="11" spans="1:12" s="35" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="93" t="s">
+      <c r="A11" s="94" t="s">
         <v>37</v>
       </c>
-      <c r="B11" s="93"/>
-      <c r="C11" s="93"/>
-      <c r="D11" s="93"/>
+      <c r="B11" s="94"/>
+      <c r="C11" s="94"/>
+      <c r="D11" s="94"/>
       <c r="E11" s="36"/>
       <c r="F11" s="61"/>
       <c r="G11" s="61"/>
@@ -2899,13 +2906,13 @@
       <c r="B13" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C13" s="92" t="s">
+      <c r="C13" s="93" t="s">
         <v>43</v>
       </c>
-      <c r="D13" s="88" t="s">
+      <c r="D13" s="89" t="s">
         <v>11</v>
       </c>
-      <c r="E13" s="88" t="s">
+      <c r="E13" s="89" t="s">
         <v>17</v>
       </c>
       <c r="F13" s="58">
@@ -2923,7 +2930,7 @@
       <c r="J13" s="58">
         <v>0.4966675035</v>
       </c>
-      <c r="K13" s="90" t="s">
+      <c r="K13" s="91" t="s">
         <v>18</v>
       </c>
     </row>
@@ -2934,9 +2941,9 @@
       <c r="B14" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C14" s="92"/>
-      <c r="D14" s="88"/>
-      <c r="E14" s="88"/>
+      <c r="C14" s="93"/>
+      <c r="D14" s="89"/>
+      <c r="E14" s="89"/>
       <c r="F14" s="58">
         <v>2.876318E-4</v>
       </c>
@@ -2952,7 +2959,7 @@
       <c r="J14" s="58">
         <v>0.48225264400000001</v>
       </c>
-      <c r="K14" s="90"/>
+      <c r="K14" s="91"/>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
@@ -2961,9 +2968,9 @@
       <c r="B15" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C15" s="92"/>
-      <c r="D15" s="88"/>
-      <c r="E15" s="88"/>
+      <c r="C15" s="93"/>
+      <c r="D15" s="89"/>
+      <c r="E15" s="89"/>
       <c r="F15" s="58">
         <v>6.7114089999999996E-4</v>
       </c>
@@ -2979,7 +2986,7 @@
       <c r="J15" s="58">
         <v>0.43776818420000002</v>
       </c>
-      <c r="K15" s="90"/>
+      <c r="K15" s="91"/>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
@@ -2988,13 +2995,13 @@
       <c r="B17" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C17" s="92" t="s">
+      <c r="C17" s="93" t="s">
         <v>44</v>
       </c>
-      <c r="D17" s="88" t="s">
+      <c r="D17" s="89" t="s">
         <v>19</v>
       </c>
-      <c r="E17" s="88" t="s">
+      <c r="E17" s="89" t="s">
         <v>27</v>
       </c>
       <c r="F17" s="58">
@@ -3012,7 +3019,7 @@
       <c r="J17" s="58">
         <v>0.44130707470000002</v>
       </c>
-      <c r="K17" s="90" t="s">
+      <c r="K17" s="91" t="s">
         <v>36</v>
       </c>
     </row>
@@ -3023,9 +3030,9 @@
       <c r="B18" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C18" s="92"/>
-      <c r="D18" s="88"/>
-      <c r="E18" s="88"/>
+      <c r="C18" s="93"/>
+      <c r="D18" s="89"/>
+      <c r="E18" s="89"/>
       <c r="F18" s="58">
         <v>7.7660593999999998E-3</v>
       </c>
@@ -3041,7 +3048,7 @@
       <c r="J18" s="58">
         <v>0.46778393010000002</v>
       </c>
-      <c r="K18" s="90"/>
+      <c r="K18" s="91"/>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
@@ -3050,9 +3057,9 @@
       <c r="B19" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C19" s="92"/>
-      <c r="D19" s="88"/>
-      <c r="E19" s="88"/>
+      <c r="C19" s="93"/>
+      <c r="D19" s="89"/>
+      <c r="E19" s="89"/>
       <c r="F19" s="58">
         <v>2.876318E-4</v>
       </c>
@@ -3068,7 +3075,7 @@
       <c r="J19" s="58">
         <v>0.46815617929999997</v>
       </c>
-      <c r="K19" s="90"/>
+      <c r="K19" s="91"/>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
@@ -3077,13 +3084,13 @@
       <c r="B21" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C21" s="92" t="s">
+      <c r="C21" s="93" t="s">
         <v>45</v>
       </c>
-      <c r="D21" s="88" t="s">
+      <c r="D21" s="89" t="s">
         <v>20</v>
       </c>
-      <c r="E21" s="88" t="s">
+      <c r="E21" s="89" t="s">
         <v>28</v>
       </c>
       <c r="F21" s="58">
@@ -3101,7 +3108,7 @@
       <c r="J21" s="58">
         <v>0.4434595543</v>
       </c>
-      <c r="K21" s="90" t="s">
+      <c r="K21" s="91" t="s">
         <v>35</v>
       </c>
     </row>
@@ -3112,9 +3119,9 @@
       <c r="B22" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C22" s="92"/>
-      <c r="D22" s="88"/>
-      <c r="E22" s="88"/>
+      <c r="C22" s="93"/>
+      <c r="D22" s="89"/>
+      <c r="E22" s="89"/>
       <c r="F22" s="58">
         <v>5.11025887E-2</v>
       </c>
@@ -3130,7 +3137,7 @@
       <c r="J22" s="58">
         <v>0.46092753450000001</v>
       </c>
-      <c r="K22" s="90"/>
+      <c r="K22" s="91"/>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
@@ -3139,9 +3146,9 @@
       <c r="B23" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C23" s="92"/>
-      <c r="D23" s="88"/>
-      <c r="E23" s="88"/>
+      <c r="C23" s="93"/>
+      <c r="D23" s="89"/>
+      <c r="E23" s="89"/>
       <c r="F23" s="58">
         <v>0</v>
       </c>
@@ -3157,7 +3164,7 @@
       <c r="J23" s="58">
         <v>0.4740446935</v>
       </c>
-      <c r="K23" s="90"/>
+      <c r="K23" s="91"/>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
@@ -3166,13 +3173,13 @@
       <c r="B25" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C25" s="92" t="s">
+      <c r="C25" s="93" t="s">
         <v>46</v>
       </c>
-      <c r="D25" s="88" t="s">
+      <c r="D25" s="89" t="s">
         <v>21</v>
       </c>
-      <c r="E25" s="88" t="s">
+      <c r="E25" s="89" t="s">
         <v>32</v>
       </c>
       <c r="F25" s="58">
@@ -3198,9 +3205,9 @@
       <c r="B26" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C26" s="92"/>
-      <c r="D26" s="88"/>
-      <c r="E26" s="88"/>
+      <c r="C26" s="93"/>
+      <c r="D26" s="89"/>
+      <c r="E26" s="89"/>
       <c r="F26" s="58">
         <v>3.0584851400000002E-2</v>
       </c>
@@ -3224,9 +3231,9 @@
       <c r="B27" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C27" s="92"/>
-      <c r="D27" s="88"/>
-      <c r="E27" s="88"/>
+      <c r="C27" s="93"/>
+      <c r="D27" s="89"/>
+      <c r="E27" s="89"/>
       <c r="F27" s="58">
         <v>6.7114089999999996E-4</v>
       </c>
@@ -3250,13 +3257,13 @@
       <c r="B29" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C29" s="92" t="s">
+      <c r="C29" s="93" t="s">
         <v>47</v>
       </c>
-      <c r="D29" s="88" t="s">
+      <c r="D29" s="89" t="s">
         <v>22</v>
       </c>
-      <c r="E29" s="88" t="s">
+      <c r="E29" s="89" t="s">
         <v>33</v>
       </c>
       <c r="F29" s="58">
@@ -3282,9 +3289,9 @@
       <c r="B30" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C30" s="92"/>
-      <c r="D30" s="88"/>
-      <c r="E30" s="88"/>
+      <c r="C30" s="93"/>
+      <c r="D30" s="89"/>
+      <c r="E30" s="89"/>
       <c r="F30" s="58">
         <v>1.42857143E-2</v>
       </c>
@@ -3308,9 +3315,9 @@
       <c r="B31" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C31" s="92"/>
-      <c r="D31" s="88"/>
-      <c r="E31" s="88"/>
+      <c r="C31" s="93"/>
+      <c r="D31" s="89"/>
+      <c r="E31" s="89"/>
       <c r="F31" s="58">
         <v>3.8350910000000001E-4</v>
       </c>
@@ -3334,13 +3341,13 @@
       <c r="B33" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C33" s="92" t="s">
+      <c r="C33" s="93" t="s">
         <v>48</v>
       </c>
-      <c r="D33" s="88" t="s">
+      <c r="D33" s="89" t="s">
         <v>23</v>
       </c>
-      <c r="E33" s="88" t="s">
+      <c r="E33" s="89" t="s">
         <v>29</v>
       </c>
       <c r="F33" s="58">
@@ -3366,9 +3373,9 @@
       <c r="B34" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C34" s="92"/>
-      <c r="D34" s="88"/>
-      <c r="E34" s="88"/>
+      <c r="C34" s="93"/>
+      <c r="D34" s="89"/>
+      <c r="E34" s="89"/>
       <c r="F34" s="58">
         <v>6.9727237799999994E-2</v>
       </c>
@@ -3392,9 +3399,9 @@
       <c r="B35" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C35" s="92"/>
-      <c r="D35" s="88"/>
-      <c r="E35" s="88"/>
+      <c r="C35" s="93"/>
+      <c r="D35" s="89"/>
+      <c r="E35" s="89"/>
       <c r="F35" s="58">
         <v>2.8812910000000001E-4</v>
       </c>
@@ -3418,13 +3425,13 @@
       <c r="B37" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C37" s="92" t="s">
+      <c r="C37" s="93" t="s">
         <v>49</v>
       </c>
-      <c r="D37" s="88" t="s">
+      <c r="D37" s="89" t="s">
         <v>24</v>
       </c>
-      <c r="E37" s="88" t="s">
+      <c r="E37" s="89" t="s">
         <v>34</v>
       </c>
       <c r="F37" s="58">
@@ -3450,9 +3457,9 @@
       <c r="B38" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C38" s="92"/>
-      <c r="D38" s="88"/>
-      <c r="E38" s="88"/>
+      <c r="C38" s="93"/>
+      <c r="D38" s="89"/>
+      <c r="E38" s="89"/>
       <c r="F38" s="58">
         <v>1.4189837E-2</v>
       </c>
@@ -3476,9 +3483,9 @@
       <c r="B39" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C39" s="92"/>
-      <c r="D39" s="88"/>
-      <c r="E39" s="88"/>
+      <c r="C39" s="93"/>
+      <c r="D39" s="89"/>
+      <c r="E39" s="89"/>
       <c r="F39" s="58">
         <v>2.876318E-4</v>
       </c>
@@ -3496,12 +3503,12 @@
       </c>
     </row>
     <row r="41" spans="1:11" s="35" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="93" t="s">
+      <c r="A41" s="94" t="s">
         <v>38</v>
       </c>
-      <c r="B41" s="93"/>
-      <c r="C41" s="93"/>
-      <c r="D41" s="93"/>
+      <c r="B41" s="94"/>
+      <c r="C41" s="94"/>
+      <c r="D41" s="94"/>
       <c r="E41" s="36"/>
       <c r="F41" s="61"/>
       <c r="G41" s="61"/>
@@ -3517,13 +3524,13 @@
       <c r="B43" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C43" s="92" t="s">
+      <c r="C43" s="93" t="s">
         <v>50</v>
       </c>
-      <c r="D43" s="88" t="s">
+      <c r="D43" s="89" t="s">
         <v>25</v>
       </c>
-      <c r="E43" s="88" t="s">
+      <c r="E43" s="89" t="s">
         <v>27</v>
       </c>
       <c r="F43" s="58">
@@ -3541,7 +3548,7 @@
       <c r="J43" s="58">
         <v>0.4587482034</v>
       </c>
-      <c r="K43" s="90" t="s">
+      <c r="K43" s="91" t="s">
         <v>30</v>
       </c>
     </row>
@@ -3552,9 +3559,9 @@
       <c r="B44" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C44" s="92"/>
-      <c r="D44" s="88"/>
-      <c r="E44" s="88"/>
+      <c r="C44" s="93"/>
+      <c r="D44" s="89"/>
+      <c r="E44" s="89"/>
       <c r="F44" s="58">
         <v>1.34125311E-2</v>
       </c>
@@ -3570,7 +3577,7 @@
       <c r="J44" s="58">
         <v>0.46907909489999999</v>
       </c>
-      <c r="K44" s="90"/>
+      <c r="K44" s="91"/>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
@@ -3579,9 +3586,9 @@
       <c r="B45" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C45" s="92"/>
-      <c r="D45" s="88"/>
-      <c r="E45" s="88"/>
+      <c r="C45" s="93"/>
+      <c r="D45" s="89"/>
+      <c r="E45" s="89"/>
       <c r="F45" s="58">
         <v>8.6223409999999995E-4</v>
       </c>
@@ -3597,7 +3604,7 @@
       <c r="J45" s="58">
         <v>0.49390839069999998</v>
       </c>
-      <c r="K45" s="90"/>
+      <c r="K45" s="91"/>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A47" s="1" t="s">
@@ -3606,13 +3613,13 @@
       <c r="B47" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C47" s="92" t="s">
+      <c r="C47" s="93" t="s">
         <v>51</v>
       </c>
-      <c r="D47" s="88" t="s">
+      <c r="D47" s="89" t="s">
         <v>26</v>
       </c>
-      <c r="E47" s="88" t="s">
+      <c r="E47" s="89" t="s">
         <v>28</v>
       </c>
       <c r="F47" s="58">
@@ -3630,7 +3637,7 @@
       <c r="J47" s="58">
         <v>0.45388746419999998</v>
       </c>
-      <c r="K47" s="90" t="s">
+      <c r="K47" s="91" t="s">
         <v>31</v>
       </c>
     </row>
@@ -3641,9 +3648,9 @@
       <c r="B48" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C48" s="92"/>
-      <c r="D48" s="88"/>
-      <c r="E48" s="88"/>
+      <c r="C48" s="93"/>
+      <c r="D48" s="89"/>
+      <c r="E48" s="89"/>
       <c r="F48" s="58">
         <v>4.3303314799999999E-2</v>
       </c>
@@ -3659,7 +3666,7 @@
       <c r="J48" s="58">
         <v>0.45908136910000003</v>
       </c>
-      <c r="K48" s="90"/>
+      <c r="K48" s="91"/>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A49" s="1" t="s">
@@ -3668,9 +3675,9 @@
       <c r="B49" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C49" s="92"/>
-      <c r="D49" s="88"/>
-      <c r="E49" s="88"/>
+      <c r="C49" s="93"/>
+      <c r="D49" s="89"/>
+      <c r="E49" s="89"/>
       <c r="F49" s="58">
         <v>9.5803800000000006E-5</v>
       </c>
@@ -3686,7 +3693,7 @@
       <c r="J49" s="58">
         <v>0.478579698</v>
       </c>
-      <c r="K49" s="90"/>
+      <c r="K49" s="91"/>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A51" s="1" t="s">
@@ -3695,13 +3702,13 @@
       <c r="B51" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C51" s="92" t="s">
+      <c r="C51" s="93" t="s">
         <v>52</v>
       </c>
-      <c r="D51" s="88" t="s">
+      <c r="D51" s="89" t="s">
         <v>39</v>
       </c>
-      <c r="E51" s="88" t="s">
+      <c r="E51" s="89" t="s">
         <v>29</v>
       </c>
       <c r="F51" s="58">
@@ -3727,9 +3734,9 @@
       <c r="B52" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C52" s="92"/>
-      <c r="D52" s="88"/>
-      <c r="E52" s="88"/>
+      <c r="C52" s="93"/>
+      <c r="D52" s="89"/>
+      <c r="E52" s="89"/>
       <c r="F52" s="58">
         <v>8.8139489999999997E-3</v>
       </c>
@@ -3753,9 +3760,9 @@
       <c r="B53" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C53" s="92"/>
-      <c r="D53" s="88"/>
-      <c r="E53" s="88"/>
+      <c r="C53" s="93"/>
+      <c r="D53" s="89"/>
+      <c r="E53" s="89"/>
       <c r="F53" s="58">
         <v>1.9160760000000001E-4</v>
       </c>
@@ -3773,12 +3780,12 @@
       </c>
     </row>
     <row r="56" spans="1:11" s="25" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="95" t="s">
+      <c r="A56" s="96" t="s">
         <v>59</v>
       </c>
-      <c r="B56" s="95"/>
-      <c r="C56" s="95"/>
-      <c r="D56" s="95"/>
+      <c r="B56" s="96"/>
+      <c r="C56" s="96"/>
+      <c r="D56" s="96"/>
       <c r="E56" s="23"/>
       <c r="F56" s="83">
         <f>MAX(F3:F53)</f>
@@ -3803,12 +3810,12 @@
       <c r="K56" s="24"/>
     </row>
     <row r="57" spans="1:11" s="28" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="87" t="s">
+      <c r="A57" s="88" t="s">
         <v>60</v>
       </c>
-      <c r="B57" s="87"/>
-      <c r="C57" s="87"/>
-      <c r="D57" s="87"/>
+      <c r="B57" s="88"/>
+      <c r="C57" s="88"/>
+      <c r="D57" s="88"/>
       <c r="E57" s="26"/>
       <c r="F57" s="84">
         <f>AVERAGE(F3:F53)</f>
@@ -3911,18 +3918,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" s="43" customFormat="1" ht="27" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="99" t="s">
+      <c r="A1" s="100" t="s">
         <v>111</v>
       </c>
-      <c r="B1" s="100"/>
-      <c r="C1" s="100"/>
-      <c r="D1" s="100"/>
-      <c r="E1" s="100"/>
-      <c r="F1" s="100"/>
-      <c r="G1" s="100"/>
-      <c r="H1" s="100"/>
-      <c r="I1" s="100"/>
-      <c r="J1" s="101"/>
+      <c r="B1" s="101"/>
+      <c r="C1" s="101"/>
+      <c r="D1" s="101"/>
+      <c r="E1" s="101"/>
+      <c r="F1" s="101"/>
+      <c r="G1" s="101"/>
+      <c r="H1" s="101"/>
+      <c r="I1" s="101"/>
+      <c r="J1" s="102"/>
       <c r="K1" s="82"/>
       <c r="L1" s="82"/>
       <c r="M1" s="82"/>
@@ -3979,13 +3986,13 @@
       <c r="B3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="94" t="s">
+      <c r="C3" s="95" t="s">
         <v>41</v>
       </c>
-      <c r="D3" s="91" t="s">
+      <c r="D3" s="92" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="91" t="s">
+      <c r="E3" s="92" t="s">
         <v>13</v>
       </c>
       <c r="F3" s="58">
@@ -4015,7 +4022,7 @@
         <f>AVERAGE(F3:J3)</f>
         <v>0.29130368856000005</v>
       </c>
-      <c r="N3" s="89" t="s">
+      <c r="N3" s="90" t="s">
         <v>15</v>
       </c>
     </row>
@@ -4026,9 +4033,9 @@
       <c r="B4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="92"/>
-      <c r="D4" s="88"/>
-      <c r="E4" s="88"/>
+      <c r="C4" s="93"/>
+      <c r="D4" s="89"/>
+      <c r="E4" s="89"/>
       <c r="F4" s="58">
         <v>2.3969319E-3</v>
       </c>
@@ -4056,7 +4063,7 @@
         <f t="shared" ref="M4:M53" si="2">AVERAGE(F4:J4)</f>
         <v>0.26225518991999996</v>
       </c>
-      <c r="N4" s="90"/>
+      <c r="N4" s="91"/>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
@@ -4065,9 +4072,9 @@
       <c r="B5" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="92"/>
-      <c r="D5" s="88"/>
-      <c r="E5" s="88"/>
+      <c r="C5" s="93"/>
+      <c r="D5" s="89"/>
+      <c r="E5" s="89"/>
       <c r="F5" s="58">
         <v>6.5867689399999999E-2</v>
       </c>
@@ -4095,7 +4102,7 @@
         <f t="shared" si="2"/>
         <v>0.29107094631999997</v>
       </c>
-      <c r="N5" s="90"/>
+      <c r="N5" s="91"/>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
@@ -4104,13 +4111,13 @@
       <c r="B7" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="92" t="s">
+      <c r="C7" s="93" t="s">
         <v>42</v>
       </c>
-      <c r="D7" s="88" t="s">
+      <c r="D7" s="89" t="s">
         <v>10</v>
       </c>
-      <c r="E7" s="88" t="s">
+      <c r="E7" s="89" t="s">
         <v>13</v>
       </c>
       <c r="F7" s="58">
@@ -4140,7 +4147,7 @@
         <f t="shared" si="2"/>
         <v>0.29438649153999996</v>
       </c>
-      <c r="N7" s="90" t="s">
+      <c r="N7" s="91" t="s">
         <v>16</v>
       </c>
     </row>
@@ -4151,9 +4158,9 @@
       <c r="B8" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="92"/>
-      <c r="D8" s="88"/>
-      <c r="E8" s="88"/>
+      <c r="C8" s="93"/>
+      <c r="D8" s="89"/>
+      <c r="E8" s="89"/>
       <c r="F8" s="58">
         <v>1.3604138700000001E-2</v>
       </c>
@@ -4181,7 +4188,7 @@
         <f t="shared" si="2"/>
         <v>0.27579129901999999</v>
       </c>
-      <c r="N8" s="90"/>
+      <c r="N8" s="91"/>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
@@ -4190,9 +4197,9 @@
       <c r="B9" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="92"/>
-      <c r="D9" s="88"/>
-      <c r="E9" s="88"/>
+      <c r="C9" s="93"/>
+      <c r="D9" s="89"/>
+      <c r="E9" s="89"/>
       <c r="F9" s="58">
         <v>3.8321517499999999E-2</v>
       </c>
@@ -4220,15 +4227,15 @@
         <f t="shared" si="2"/>
         <v>0.2717815321</v>
       </c>
-      <c r="N9" s="90"/>
+      <c r="N9" s="91"/>
     </row>
     <row r="11" spans="1:15" s="35" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="93" t="s">
+      <c r="A11" s="94" t="s">
         <v>37</v>
       </c>
-      <c r="B11" s="93"/>
-      <c r="C11" s="93"/>
-      <c r="D11" s="93"/>
+      <c r="B11" s="94"/>
+      <c r="C11" s="94"/>
+      <c r="D11" s="94"/>
       <c r="E11" s="36"/>
       <c r="F11" s="61"/>
       <c r="G11" s="61"/>
@@ -4247,13 +4254,13 @@
       <c r="B13" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C13" s="92" t="s">
+      <c r="C13" s="93" t="s">
         <v>43</v>
       </c>
-      <c r="D13" s="88" t="s">
+      <c r="D13" s="89" t="s">
         <v>11</v>
       </c>
-      <c r="E13" s="88" t="s">
+      <c r="E13" s="89" t="s">
         <v>17</v>
       </c>
       <c r="F13" s="58">
@@ -4283,7 +4290,7 @@
         <f t="shared" si="2"/>
         <v>0.33641501256</v>
       </c>
-      <c r="N13" s="90" t="s">
+      <c r="N13" s="91" t="s">
         <v>18</v>
       </c>
     </row>
@@ -4294,9 +4301,9 @@
       <c r="B14" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C14" s="92"/>
-      <c r="D14" s="88"/>
-      <c r="E14" s="88"/>
+      <c r="C14" s="93"/>
+      <c r="D14" s="89"/>
+      <c r="E14" s="89"/>
       <c r="F14" s="58">
         <v>7.9194630899999993E-2</v>
       </c>
@@ -4324,7 +4331,7 @@
         <f t="shared" si="2"/>
         <v>0.26691102734</v>
       </c>
-      <c r="N14" s="90"/>
+      <c r="N14" s="91"/>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
@@ -4333,9 +4340,9 @@
       <c r="B15" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C15" s="92"/>
-      <c r="D15" s="88"/>
-      <c r="E15" s="88"/>
+      <c r="C15" s="93"/>
+      <c r="D15" s="89"/>
+      <c r="E15" s="89"/>
       <c r="F15" s="58">
         <v>3.8350910000000001E-4</v>
       </c>
@@ -4363,7 +4370,7 @@
         <f t="shared" si="2"/>
         <v>0.22330577798000001</v>
       </c>
-      <c r="N15" s="90"/>
+      <c r="N15" s="91"/>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
@@ -4372,13 +4379,13 @@
       <c r="B17" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C17" s="92" t="s">
+      <c r="C17" s="93" t="s">
         <v>44</v>
       </c>
-      <c r="D17" s="88" t="s">
+      <c r="D17" s="89" t="s">
         <v>19</v>
       </c>
-      <c r="E17" s="88" t="s">
+      <c r="E17" s="89" t="s">
         <v>27</v>
       </c>
       <c r="F17" s="58">
@@ -4408,7 +4415,7 @@
         <f t="shared" si="2"/>
         <v>0.34767161497999999</v>
       </c>
-      <c r="N17" s="90" t="s">
+      <c r="N17" s="91" t="s">
         <v>36</v>
       </c>
     </row>
@@ -4419,9 +4426,9 @@
       <c r="B18" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C18" s="92"/>
-      <c r="D18" s="88"/>
-      <c r="E18" s="88"/>
+      <c r="C18" s="93"/>
+      <c r="D18" s="89"/>
+      <c r="E18" s="89"/>
       <c r="F18" s="58">
         <v>3.7296260800000001E-2</v>
       </c>
@@ -4449,7 +4456,7 @@
         <f t="shared" si="2"/>
         <v>0.33628517706</v>
       </c>
-      <c r="N18" s="90"/>
+      <c r="N18" s="91"/>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
@@ -4458,9 +4465,9 @@
       <c r="B19" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C19" s="92"/>
-      <c r="D19" s="88"/>
-      <c r="E19" s="88"/>
+      <c r="C19" s="93"/>
+      <c r="D19" s="89"/>
+      <c r="E19" s="89"/>
       <c r="F19" s="58">
         <v>1.0546500000000001E-3</v>
       </c>
@@ -4488,7 +4495,7 @@
         <f t="shared" si="2"/>
         <v>0.20704430203999999</v>
       </c>
-      <c r="N19" s="90"/>
+      <c r="N19" s="91"/>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
@@ -4497,13 +4504,13 @@
       <c r="B21" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C21" s="92" t="s">
+      <c r="C21" s="93" t="s">
         <v>45</v>
       </c>
-      <c r="D21" s="88" t="s">
+      <c r="D21" s="89" t="s">
         <v>20</v>
       </c>
-      <c r="E21" s="88" t="s">
+      <c r="E21" s="89" t="s">
         <v>28</v>
       </c>
       <c r="F21" s="58">
@@ -4533,7 +4540,7 @@
         <f t="shared" si="2"/>
         <v>0.31181358596000003</v>
       </c>
-      <c r="N21" s="90" t="s">
+      <c r="N21" s="91" t="s">
         <v>35</v>
       </c>
     </row>
@@ -4544,9 +4551,9 @@
       <c r="B22" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C22" s="92"/>
-      <c r="D22" s="88"/>
-      <c r="E22" s="88"/>
+      <c r="C22" s="93"/>
+      <c r="D22" s="89"/>
+      <c r="E22" s="89"/>
       <c r="F22" s="58">
         <v>1.05465005E-2</v>
       </c>
@@ -4574,7 +4581,7 @@
         <f t="shared" si="2"/>
         <v>0.29879759264</v>
       </c>
-      <c r="N22" s="90"/>
+      <c r="N22" s="91"/>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
@@ -4583,9 +4590,9 @@
       <c r="B23" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C23" s="92"/>
-      <c r="D23" s="88"/>
-      <c r="E23" s="88"/>
+      <c r="C23" s="93"/>
+      <c r="D23" s="89"/>
+      <c r="E23" s="89"/>
       <c r="F23" s="58">
         <v>0</v>
       </c>
@@ -4613,7 +4620,7 @@
         <f t="shared" si="2"/>
         <v>0.22541820497999998</v>
       </c>
-      <c r="N23" s="90"/>
+      <c r="N23" s="91"/>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
@@ -4622,13 +4629,13 @@
       <c r="B25" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C25" s="92" t="s">
+      <c r="C25" s="93" t="s">
         <v>46</v>
       </c>
-      <c r="D25" s="88" t="s">
+      <c r="D25" s="89" t="s">
         <v>21</v>
       </c>
-      <c r="E25" s="88" t="s">
+      <c r="E25" s="89" t="s">
         <v>32</v>
       </c>
       <c r="F25" s="58">
@@ -4666,9 +4673,9 @@
       <c r="B26" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C26" s="92"/>
-      <c r="D26" s="88"/>
-      <c r="E26" s="88"/>
+      <c r="C26" s="93"/>
+      <c r="D26" s="89"/>
+      <c r="E26" s="89"/>
       <c r="F26" s="58">
         <v>2.7229146700000002E-2</v>
       </c>
@@ -4704,9 +4711,9 @@
       <c r="B27" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C27" s="92"/>
-      <c r="D27" s="88"/>
-      <c r="E27" s="88"/>
+      <c r="C27" s="93"/>
+      <c r="D27" s="89"/>
+      <c r="E27" s="89"/>
       <c r="F27" s="58">
         <v>3.8350910000000001E-4</v>
       </c>
@@ -4742,13 +4749,13 @@
       <c r="B29" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C29" s="92" t="s">
+      <c r="C29" s="93" t="s">
         <v>47</v>
       </c>
-      <c r="D29" s="88" t="s">
+      <c r="D29" s="89" t="s">
         <v>22</v>
       </c>
-      <c r="E29" s="88" t="s">
+      <c r="E29" s="89" t="s">
         <v>33</v>
       </c>
       <c r="F29" s="58">
@@ -4786,9 +4793,9 @@
       <c r="B30" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C30" s="92"/>
-      <c r="D30" s="88"/>
-      <c r="E30" s="88"/>
+      <c r="C30" s="93"/>
+      <c r="D30" s="89"/>
+      <c r="E30" s="89"/>
       <c r="F30" s="58">
         <v>2.8475551299999999E-2</v>
       </c>
@@ -4824,9 +4831,9 @@
       <c r="B31" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C31" s="92"/>
-      <c r="D31" s="88"/>
-      <c r="E31" s="88"/>
+      <c r="C31" s="93"/>
+      <c r="D31" s="89"/>
+      <c r="E31" s="89"/>
       <c r="F31" s="58">
         <v>1.917546E-4</v>
       </c>
@@ -4862,13 +4869,13 @@
       <c r="B33" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C33" s="92" t="s">
+      <c r="C33" s="93" t="s">
         <v>48</v>
       </c>
-      <c r="D33" s="88" t="s">
+      <c r="D33" s="89" t="s">
         <v>23</v>
       </c>
-      <c r="E33" s="88" t="s">
+      <c r="E33" s="89" t="s">
         <v>29</v>
       </c>
       <c r="F33" s="58">
@@ -4906,9 +4913,9 @@
       <c r="B34" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C34" s="92"/>
-      <c r="D34" s="88"/>
-      <c r="E34" s="88"/>
+      <c r="C34" s="93"/>
+      <c r="D34" s="89"/>
+      <c r="E34" s="89"/>
       <c r="F34" s="58">
         <v>2.4010757000000001E-3</v>
       </c>
@@ -4944,9 +4951,9 @@
       <c r="B35" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C35" s="92"/>
-      <c r="D35" s="88"/>
-      <c r="E35" s="88"/>
+      <c r="C35" s="93"/>
+      <c r="D35" s="89"/>
+      <c r="E35" s="89"/>
       <c r="F35" s="58">
         <v>0</v>
       </c>
@@ -4982,13 +4989,13 @@
       <c r="B37" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C37" s="92" t="s">
+      <c r="C37" s="93" t="s">
         <v>49</v>
       </c>
-      <c r="D37" s="88" t="s">
+      <c r="D37" s="89" t="s">
         <v>24</v>
       </c>
-      <c r="E37" s="88" t="s">
+      <c r="E37" s="89" t="s">
         <v>34</v>
       </c>
       <c r="F37" s="58">
@@ -5026,9 +5033,9 @@
       <c r="B38" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C38" s="92"/>
-      <c r="D38" s="88"/>
-      <c r="E38" s="88"/>
+      <c r="C38" s="93"/>
+      <c r="D38" s="89"/>
+      <c r="E38" s="89"/>
       <c r="F38" s="58">
         <v>5.9443912000000003E-3</v>
       </c>
@@ -5064,9 +5071,9 @@
       <c r="B39" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C39" s="92"/>
-      <c r="D39" s="88"/>
-      <c r="E39" s="88"/>
+      <c r="C39" s="93"/>
+      <c r="D39" s="89"/>
+      <c r="E39" s="89"/>
       <c r="F39" s="58">
         <v>1.917546E-4</v>
       </c>
@@ -5096,12 +5103,12 @@
       </c>
     </row>
     <row r="41" spans="1:14" s="35" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="93" t="s">
+      <c r="A41" s="94" t="s">
         <v>38</v>
       </c>
-      <c r="B41" s="93"/>
-      <c r="C41" s="93"/>
-      <c r="D41" s="93"/>
+      <c r="B41" s="94"/>
+      <c r="C41" s="94"/>
+      <c r="D41" s="94"/>
       <c r="E41" s="36"/>
       <c r="F41" s="61"/>
       <c r="G41" s="61"/>
@@ -5120,13 +5127,13 @@
       <c r="B43" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C43" s="92" t="s">
+      <c r="C43" s="93" t="s">
         <v>50</v>
       </c>
-      <c r="D43" s="88" t="s">
+      <c r="D43" s="89" t="s">
         <v>25</v>
       </c>
-      <c r="E43" s="88" t="s">
+      <c r="E43" s="89" t="s">
         <v>27</v>
       </c>
       <c r="F43" s="58">
@@ -5156,7 +5163,7 @@
         <f t="shared" si="2"/>
         <v>0.32911788728000002</v>
       </c>
-      <c r="N43" s="90" t="s">
+      <c r="N43" s="91" t="s">
         <v>30</v>
       </c>
     </row>
@@ -5167,9 +5174,9 @@
       <c r="B44" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C44" s="92"/>
-      <c r="D44" s="88"/>
-      <c r="E44" s="88"/>
+      <c r="C44" s="93"/>
+      <c r="D44" s="89"/>
+      <c r="E44" s="89"/>
       <c r="F44" s="58">
         <v>1.59034298E-2</v>
       </c>
@@ -5197,7 +5204,7 @@
         <f t="shared" si="2"/>
         <v>0.33481998118</v>
       </c>
-      <c r="N44" s="90"/>
+      <c r="N44" s="91"/>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
@@ -5206,9 +5213,9 @@
       <c r="B45" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C45" s="92"/>
-      <c r="D45" s="88"/>
-      <c r="E45" s="88"/>
+      <c r="C45" s="93"/>
+      <c r="D45" s="89"/>
+      <c r="E45" s="89"/>
       <c r="F45" s="73">
         <v>0</v>
       </c>
@@ -5236,7 +5243,7 @@
         <f t="shared" si="2"/>
         <v>0.23017129818000001</v>
       </c>
-      <c r="N45" s="90"/>
+      <c r="N45" s="91"/>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A47" s="1" t="s">
@@ -5245,13 +5252,13 @@
       <c r="B47" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C47" s="92" t="s">
+      <c r="C47" s="93" t="s">
         <v>51</v>
       </c>
-      <c r="D47" s="88" t="s">
+      <c r="D47" s="89" t="s">
         <v>26</v>
       </c>
-      <c r="E47" s="88" t="s">
+      <c r="E47" s="89" t="s">
         <v>28</v>
       </c>
       <c r="F47" s="58">
@@ -5281,7 +5288,7 @@
         <f t="shared" si="2"/>
         <v>0.28403192430000002</v>
       </c>
-      <c r="N47" s="90" t="s">
+      <c r="N47" s="91" t="s">
         <v>31</v>
       </c>
     </row>
@@ -5292,9 +5299,9 @@
       <c r="B48" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C48" s="92"/>
-      <c r="D48" s="88"/>
-      <c r="E48" s="88"/>
+      <c r="C48" s="93"/>
+      <c r="D48" s="89"/>
+      <c r="E48" s="89"/>
       <c r="F48" s="58">
         <v>2.90285495E-2</v>
       </c>
@@ -5322,7 +5329,7 @@
         <f t="shared" si="2"/>
         <v>0.35089340806000002</v>
       </c>
-      <c r="N48" s="90"/>
+      <c r="N48" s="91"/>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A49" s="1" t="s">
@@ -5331,9 +5338,9 @@
       <c r="B49" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C49" s="92"/>
-      <c r="D49" s="88"/>
-      <c r="E49" s="88"/>
+      <c r="C49" s="93"/>
+      <c r="D49" s="89"/>
+      <c r="E49" s="89"/>
       <c r="F49" s="58">
         <v>1.9160760000000001E-4</v>
       </c>
@@ -5361,7 +5368,7 @@
         <f t="shared" si="2"/>
         <v>0.34178323869999999</v>
       </c>
-      <c r="N49" s="90"/>
+      <c r="N49" s="91"/>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A51" s="1" t="s">
@@ -5370,13 +5377,13 @@
       <c r="B51" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C51" s="92" t="s">
+      <c r="C51" s="93" t="s">
         <v>52</v>
       </c>
-      <c r="D51" s="88" t="s">
+      <c r="D51" s="89" t="s">
         <v>39</v>
       </c>
-      <c r="E51" s="88" t="s">
+      <c r="E51" s="89" t="s">
         <v>29</v>
       </c>
       <c r="F51" s="58">
@@ -5414,9 +5421,9 @@
       <c r="B52" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C52" s="92"/>
-      <c r="D52" s="88"/>
-      <c r="E52" s="88"/>
+      <c r="C52" s="93"/>
+      <c r="D52" s="89"/>
+      <c r="E52" s="89"/>
       <c r="F52" s="58">
         <v>3.4489365999999999E-3</v>
       </c>
@@ -5452,9 +5459,9 @@
       <c r="B53" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C53" s="92"/>
-      <c r="D53" s="88"/>
-      <c r="E53" s="88"/>
+      <c r="C53" s="93"/>
+      <c r="D53" s="89"/>
+      <c r="E53" s="89"/>
       <c r="F53" s="73">
         <v>4.7901900000000002E-4</v>
       </c>
@@ -5484,12 +5491,12 @@
       </c>
     </row>
     <row r="56" spans="1:14" s="11" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="102" t="s">
+      <c r="A56" s="103" t="s">
         <v>59</v>
       </c>
-      <c r="B56" s="102"/>
-      <c r="C56" s="102"/>
-      <c r="D56" s="102"/>
+      <c r="B56" s="103"/>
+      <c r="C56" s="103"/>
+      <c r="D56" s="103"/>
       <c r="E56" s="12"/>
       <c r="F56" s="71">
         <f t="shared" ref="F56:M56" si="3">MAX(F3:F53)</f>
@@ -5526,12 +5533,12 @@
       <c r="N56" s="14"/>
     </row>
     <row r="57" spans="1:14" s="15" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="98" t="s">
+      <c r="A57" s="99" t="s">
         <v>60</v>
       </c>
-      <c r="B57" s="98"/>
-      <c r="C57" s="98"/>
-      <c r="D57" s="98"/>
+      <c r="B57" s="99"/>
+      <c r="C57" s="99"/>
+      <c r="D57" s="99"/>
       <c r="E57" s="16"/>
       <c r="F57" s="80">
         <f t="shared" ref="F57:M57" si="4">AVERAGE(F3:F53)</f>
@@ -5568,12 +5575,12 @@
       <c r="N57" s="17"/>
     </row>
     <row r="60" spans="1:14" s="21" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="96" t="s">
+      <c r="A60" s="97" t="s">
         <v>77</v>
       </c>
-      <c r="B60" s="96"/>
-      <c r="C60" s="96"/>
-      <c r="D60" s="96"/>
+      <c r="B60" s="97"/>
+      <c r="C60" s="97"/>
+      <c r="D60" s="97"/>
       <c r="E60" s="19"/>
       <c r="F60" s="81"/>
       <c r="G60" s="81"/>
@@ -5586,12 +5593,12 @@
       <c r="N60" s="20"/>
     </row>
     <row r="61" spans="1:14" s="21" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="96" t="s">
+      <c r="A61" s="97" t="s">
         <v>78</v>
       </c>
-      <c r="B61" s="97"/>
-      <c r="C61" s="97"/>
-      <c r="D61" s="97"/>
+      <c r="B61" s="98"/>
+      <c r="C61" s="98"/>
+      <c r="D61" s="98"/>
       <c r="E61" s="22"/>
       <c r="F61" s="81"/>
       <c r="G61" s="81"/>
@@ -5604,12 +5611,12 @@
       <c r="N61" s="20"/>
     </row>
     <row r="62" spans="1:14" s="21" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="96" t="s">
+      <c r="A62" s="97" t="s">
         <v>79</v>
       </c>
-      <c r="B62" s="97"/>
-      <c r="C62" s="97"/>
-      <c r="D62" s="97"/>
+      <c r="B62" s="98"/>
+      <c r="C62" s="98"/>
+      <c r="D62" s="98"/>
       <c r="E62" s="22"/>
       <c r="F62" s="81"/>
       <c r="G62" s="81"/>
@@ -5699,23 +5706,23 @@
     <col min="13" max="16384" width="51.33203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="106" customFormat="1" ht="27" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="103" t="s">
+    <row r="1" spans="1:14" s="107" customFormat="1" ht="27" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="104" t="s">
         <v>112</v>
       </c>
-      <c r="B1" s="104"/>
-      <c r="C1" s="104"/>
-      <c r="D1" s="104"/>
-      <c r="E1" s="104"/>
-      <c r="F1" s="104"/>
-      <c r="G1" s="104"/>
-      <c r="H1" s="104"/>
-      <c r="I1" s="104"/>
-      <c r="J1" s="104"/>
-      <c r="K1" s="104"/>
-      <c r="L1" s="104"/>
-      <c r="M1" s="104"/>
-      <c r="N1" s="105"/>
+      <c r="B1" s="105"/>
+      <c r="C1" s="105"/>
+      <c r="D1" s="105"/>
+      <c r="E1" s="105"/>
+      <c r="F1" s="105"/>
+      <c r="G1" s="105"/>
+      <c r="H1" s="105"/>
+      <c r="I1" s="105"/>
+      <c r="J1" s="105"/>
+      <c r="K1" s="105"/>
+      <c r="L1" s="105"/>
+      <c r="M1" s="105"/>
+      <c r="N1" s="106"/>
     </row>
     <row r="2" spans="1:14" s="4" customFormat="1" ht="66" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
@@ -5772,17 +5779,17 @@
       <c r="N3" s="7"/>
     </row>
     <row r="4" spans="1:14" s="29" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="98" t="s">
+      <c r="A4" s="99" t="s">
         <v>65</v>
       </c>
-      <c r="B4" s="98"/>
-      <c r="C4" s="98"/>
-      <c r="D4" s="98"/>
-      <c r="E4" s="98"/>
-      <c r="F4" s="98"/>
-      <c r="G4" s="98"/>
-      <c r="H4" s="98"/>
-      <c r="I4" s="98"/>
+      <c r="B4" s="99"/>
+      <c r="C4" s="99"/>
+      <c r="D4" s="99"/>
+      <c r="E4" s="99"/>
+      <c r="F4" s="99"/>
+      <c r="G4" s="99"/>
+      <c r="H4" s="99"/>
+      <c r="I4" s="99"/>
       <c r="J4" s="76"/>
       <c r="K4" s="79"/>
       <c r="L4" s="79"/>
@@ -5808,10 +5815,10 @@
       <c r="B6" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="90" t="s">
+      <c r="C6" s="91" t="s">
         <v>61</v>
       </c>
-      <c r="D6" s="90" t="s">
+      <c r="D6" s="91" t="s">
         <v>62</v>
       </c>
       <c r="E6" s="58">
@@ -5849,8 +5856,8 @@
       <c r="B7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="90"/>
-      <c r="D7" s="90"/>
+      <c r="C7" s="91"/>
+      <c r="D7" s="91"/>
       <c r="E7" s="58">
         <v>6.9727237799999994E-2</v>
       </c>
@@ -5886,8 +5893,8 @@
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="90"/>
-      <c r="D8" s="90"/>
+      <c r="C8" s="91"/>
+      <c r="D8" s="91"/>
       <c r="E8" s="58">
         <v>2.8812910000000001E-4</v>
       </c>
@@ -5923,10 +5930,10 @@
       <c r="B10" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C10" s="90" t="s">
+      <c r="C10" s="91" t="s">
         <v>63</v>
       </c>
-      <c r="D10" s="90" t="s">
+      <c r="D10" s="91" t="s">
         <v>64</v>
       </c>
       <c r="E10" s="58">
@@ -5964,8 +5971,8 @@
       <c r="B11" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C11" s="90"/>
-      <c r="D11" s="90"/>
+      <c r="C11" s="91"/>
+      <c r="D11" s="91"/>
       <c r="E11" s="58">
         <v>2.4010757000000001E-3</v>
       </c>
@@ -6001,8 +6008,8 @@
       <c r="B12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C12" s="90"/>
-      <c r="D12" s="90"/>
+      <c r="C12" s="91"/>
+      <c r="D12" s="91"/>
       <c r="E12" s="58">
         <v>0</v>
       </c>
@@ -6038,10 +6045,10 @@
       <c r="B14" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C14" s="90" t="s">
+      <c r="C14" s="91" t="s">
         <v>68</v>
       </c>
-      <c r="D14" s="90" t="s">
+      <c r="D14" s="91" t="s">
         <v>75</v>
       </c>
       <c r="E14" s="58">
@@ -6079,8 +6086,8 @@
       <c r="B15" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C15" s="90"/>
-      <c r="D15" s="90"/>
+      <c r="C15" s="91"/>
+      <c r="D15" s="91"/>
       <c r="E15" s="58">
         <v>3.5474592999999999E-3</v>
       </c>
@@ -6116,8 +6123,8 @@
       <c r="B16" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C16" s="90"/>
-      <c r="D16" s="90"/>
+      <c r="C16" s="91"/>
+      <c r="D16" s="91"/>
       <c r="E16" s="58">
         <v>3.8350910000000001E-4</v>
       </c>
@@ -6153,10 +6160,10 @@
       <c r="B18" s="49" t="s">
         <v>5</v>
       </c>
-      <c r="C18" s="90" t="s">
+      <c r="C18" s="91" t="s">
         <v>74</v>
       </c>
-      <c r="D18" s="90" t="s">
+      <c r="D18" s="91" t="s">
         <v>73</v>
       </c>
       <c r="E18" s="70">
@@ -6194,8 +6201,8 @@
       <c r="B19" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C19" s="90"/>
-      <c r="D19" s="90"/>
+      <c r="C19" s="91"/>
+      <c r="D19" s="91"/>
       <c r="E19" s="58">
         <v>3.0680729000000001E-3</v>
       </c>
@@ -6231,8 +6238,8 @@
       <c r="B20" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C20" s="90"/>
-      <c r="D20" s="90"/>
+      <c r="C20" s="91"/>
+      <c r="D20" s="91"/>
       <c r="E20" s="58">
         <v>2.876318E-4</v>
       </c>
@@ -6271,10 +6278,10 @@
       <c r="B22" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C22" s="90" t="s">
+      <c r="C22" s="91" t="s">
         <v>66</v>
       </c>
-      <c r="D22" s="90" t="s">
+      <c r="D22" s="91" t="s">
         <v>67</v>
       </c>
       <c r="E22" s="58">
@@ -6312,8 +6319,8 @@
       <c r="B23" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C23" s="90"/>
-      <c r="D23" s="90"/>
+      <c r="C23" s="91"/>
+      <c r="D23" s="91"/>
       <c r="E23" s="58">
         <v>3.1639501E-3</v>
       </c>
@@ -6349,8 +6356,8 @@
       <c r="B24" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C24" s="90"/>
-      <c r="D24" s="90"/>
+      <c r="C24" s="91"/>
+      <c r="D24" s="91"/>
       <c r="E24" s="58">
         <v>1.917546E-4</v>
       </c>
@@ -6386,10 +6393,10 @@
       <c r="B26" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C26" s="90" t="s">
+      <c r="C26" s="91" t="s">
         <v>71</v>
       </c>
-      <c r="D26" s="90" t="s">
+      <c r="D26" s="91" t="s">
         <v>69</v>
       </c>
       <c r="E26" s="58">
@@ -6427,8 +6434,8 @@
       <c r="B27" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C27" s="90"/>
-      <c r="D27" s="90"/>
+      <c r="C27" s="91"/>
+      <c r="D27" s="91"/>
       <c r="E27" s="58">
         <v>1.70661553E-2</v>
       </c>
@@ -6464,8 +6471,8 @@
       <c r="B28" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C28" s="90"/>
-      <c r="D28" s="90"/>
+      <c r="C28" s="91"/>
+      <c r="D28" s="91"/>
       <c r="E28" s="58">
         <v>6.7114089999999996E-4</v>
       </c>
@@ -6501,10 +6508,10 @@
       <c r="B30" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C30" s="90" t="s">
+      <c r="C30" s="91" t="s">
         <v>72</v>
       </c>
-      <c r="D30" s="90" t="s">
+      <c r="D30" s="91" t="s">
         <v>70</v>
       </c>
       <c r="E30" s="58">
@@ -6542,8 +6549,8 @@
       <c r="B31" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C31" s="90"/>
-      <c r="D31" s="90"/>
+      <c r="C31" s="91"/>
+      <c r="D31" s="91"/>
       <c r="E31" s="58">
         <v>7.2866731000000001E-3</v>
       </c>
@@ -6579,8 +6586,8 @@
       <c r="B32" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C32" s="90"/>
-      <c r="D32" s="90"/>
+      <c r="C32" s="91"/>
+      <c r="D32" s="91"/>
       <c r="E32" s="58">
         <v>0</v>
       </c>
@@ -6610,12 +6617,12 @@
       </c>
     </row>
     <row r="35" spans="1:14" s="11" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="102" t="s">
+      <c r="A35" s="103" t="s">
         <v>59</v>
       </c>
-      <c r="B35" s="102"/>
-      <c r="C35" s="102"/>
-      <c r="D35" s="102"/>
+      <c r="B35" s="103"/>
+      <c r="C35" s="103"/>
+      <c r="D35" s="103"/>
       <c r="E35" s="71">
         <f t="shared" ref="E35:L35" si="3">MAX(E5:E33)</f>
         <v>8.2742090099999999E-2</v>
@@ -6652,12 +6659,12 @@
       <c r="N35" s="14"/>
     </row>
     <row r="36" spans="1:14" s="33" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="107" t="s">
+      <c r="A36" s="108" t="s">
         <v>60</v>
       </c>
-      <c r="B36" s="107"/>
-      <c r="C36" s="107"/>
-      <c r="D36" s="107"/>
+      <c r="B36" s="108"/>
+      <c r="C36" s="108"/>
+      <c r="D36" s="108"/>
       <c r="E36" s="72">
         <f t="shared" ref="E36:L36" si="4">AVERAGE(E6:E33)</f>
         <v>2.0975477057142849E-2</v>
@@ -6694,17 +6701,17 @@
       <c r="N36" s="34"/>
     </row>
     <row r="38" spans="1:14" s="29" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="98" t="s">
+      <c r="A38" s="99" t="s">
         <v>80</v>
       </c>
-      <c r="B38" s="98"/>
-      <c r="C38" s="98"/>
-      <c r="D38" s="98"/>
-      <c r="E38" s="98"/>
-      <c r="F38" s="98"/>
-      <c r="G38" s="98"/>
-      <c r="H38" s="98"/>
-      <c r="I38" s="98"/>
+      <c r="B38" s="99"/>
+      <c r="C38" s="99"/>
+      <c r="D38" s="99"/>
+      <c r="E38" s="99"/>
+      <c r="F38" s="99"/>
+      <c r="G38" s="99"/>
+      <c r="H38" s="99"/>
+      <c r="I38" s="99"/>
       <c r="J38" s="76"/>
       <c r="K38" s="79"/>
       <c r="L38" s="79"/>
@@ -6730,10 +6737,10 @@
       <c r="B40" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C40" s="90" t="s">
+      <c r="C40" s="91" t="s">
         <v>81</v>
       </c>
-      <c r="D40" s="90" t="s">
+      <c r="D40" s="91" t="s">
         <v>62</v>
       </c>
       <c r="E40" s="58">
@@ -6771,8 +6778,8 @@
       <c r="B41" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C41" s="90"/>
-      <c r="D41" s="90"/>
+      <c r="C41" s="91"/>
+      <c r="D41" s="91"/>
       <c r="E41" s="58">
         <v>1.42857143E-2</v>
       </c>
@@ -6808,8 +6815,8 @@
       <c r="B42" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C42" s="90"/>
-      <c r="D42" s="90"/>
+      <c r="C42" s="91"/>
+      <c r="D42" s="91"/>
       <c r="E42" s="58">
         <v>3.8350910000000001E-4</v>
       </c>
@@ -6845,10 +6852,10 @@
       <c r="B44" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C44" s="90" t="s">
+      <c r="C44" s="91" t="s">
         <v>82</v>
       </c>
-      <c r="D44" s="90" t="s">
+      <c r="D44" s="91" t="s">
         <v>64</v>
       </c>
       <c r="E44" s="58">
@@ -6886,8 +6893,8 @@
       <c r="B45" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C45" s="90"/>
-      <c r="D45" s="90"/>
+      <c r="C45" s="91"/>
+      <c r="D45" s="91"/>
       <c r="E45" s="58">
         <v>2.8475551299999999E-2</v>
       </c>
@@ -6923,8 +6930,8 @@
       <c r="B46" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C46" s="90"/>
-      <c r="D46" s="90"/>
+      <c r="C46" s="91"/>
+      <c r="D46" s="91"/>
       <c r="E46" s="58">
         <v>1.917546E-4</v>
       </c>
@@ -6960,10 +6967,10 @@
       <c r="B48" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C48" s="90" t="s">
+      <c r="C48" s="91" t="s">
         <v>83</v>
       </c>
-      <c r="D48" s="90" t="s">
+      <c r="D48" s="91" t="s">
         <v>75</v>
       </c>
       <c r="E48" s="58">
@@ -7001,8 +7008,8 @@
       <c r="B49" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C49" s="90"/>
-      <c r="D49" s="90"/>
+      <c r="C49" s="91"/>
+      <c r="D49" s="91"/>
       <c r="E49" s="58">
         <v>6.3279002999999997E-3</v>
       </c>
@@ -7038,8 +7045,8 @@
       <c r="B50" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C50" s="90"/>
-      <c r="D50" s="90"/>
+      <c r="C50" s="91"/>
+      <c r="D50" s="91"/>
       <c r="E50" s="58">
         <v>2.876318E-4</v>
       </c>
@@ -7075,10 +7082,10 @@
       <c r="B52" s="49" t="s">
         <v>5</v>
       </c>
-      <c r="C52" s="90" t="s">
+      <c r="C52" s="91" t="s">
         <v>84</v>
       </c>
-      <c r="D52" s="90" t="s">
+      <c r="D52" s="91" t="s">
         <v>73</v>
       </c>
       <c r="E52" s="70">
@@ -7116,8 +7123,8 @@
       <c r="B53" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C53" s="90"/>
-      <c r="D53" s="90"/>
+      <c r="C53" s="91"/>
+      <c r="D53" s="91"/>
       <c r="E53" s="58">
         <v>2.0134227999999998E-3</v>
       </c>
@@ -7153,8 +7160,8 @@
       <c r="B54" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C54" s="90"/>
-      <c r="D54" s="90"/>
+      <c r="C54" s="91"/>
+      <c r="D54" s="91"/>
       <c r="E54" s="58">
         <v>1.917546E-4</v>
       </c>
@@ -7193,10 +7200,10 @@
       <c r="B56" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C56" s="90" t="s">
+      <c r="C56" s="91" t="s">
         <v>85</v>
       </c>
-      <c r="D56" s="90" t="s">
+      <c r="D56" s="91" t="s">
         <v>67</v>
       </c>
       <c r="E56" s="58">
@@ -7234,8 +7241,8 @@
       <c r="B57" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C57" s="90"/>
-      <c r="D57" s="90"/>
+      <c r="C57" s="91"/>
+      <c r="D57" s="91"/>
       <c r="E57" s="58">
         <v>1.9558964500000001E-2</v>
       </c>
@@ -7271,8 +7278,8 @@
       <c r="B58" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C58" s="90"/>
-      <c r="D58" s="90"/>
+      <c r="C58" s="91"/>
+      <c r="D58" s="91"/>
       <c r="E58" s="58">
         <v>0</v>
       </c>
@@ -7308,10 +7315,10 @@
       <c r="B60" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C60" s="90" t="s">
+      <c r="C60" s="91" t="s">
         <v>86</v>
       </c>
-      <c r="D60" s="90" t="s">
+      <c r="D60" s="91" t="s">
         <v>69</v>
       </c>
       <c r="E60" s="58">
@@ -7349,8 +7356,8 @@
       <c r="B61" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C61" s="90"/>
-      <c r="D61" s="90"/>
+      <c r="C61" s="91"/>
+      <c r="D61" s="91"/>
       <c r="E61" s="58">
         <v>4.4103546999999998E-3</v>
       </c>
@@ -7386,8 +7393,8 @@
       <c r="B62" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C62" s="90"/>
-      <c r="D62" s="90"/>
+      <c r="C62" s="91"/>
+      <c r="D62" s="91"/>
       <c r="E62" s="58">
         <v>2.8763183000000002E-3</v>
       </c>
@@ -7423,10 +7430,10 @@
       <c r="B64" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C64" s="90" t="s">
+      <c r="C64" s="91" t="s">
         <v>87</v>
       </c>
-      <c r="D64" s="90" t="s">
+      <c r="D64" s="91" t="s">
         <v>70</v>
       </c>
       <c r="E64" s="58">
@@ -7464,8 +7471,8 @@
       <c r="B65" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C65" s="90"/>
-      <c r="D65" s="90"/>
+      <c r="C65" s="91"/>
+      <c r="D65" s="91"/>
       <c r="E65" s="58">
         <v>8.6289548999999993E-3</v>
       </c>
@@ -7501,8 +7508,8 @@
       <c r="B66" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C66" s="90"/>
-      <c r="D66" s="90"/>
+      <c r="C66" s="91"/>
+      <c r="D66" s="91"/>
       <c r="E66" s="58">
         <v>1.9175455000000001E-3</v>
       </c>
@@ -7532,12 +7539,12 @@
       </c>
     </row>
     <row r="69" spans="1:14" s="11" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="102" t="s">
+      <c r="A69" s="103" t="s">
         <v>59</v>
       </c>
-      <c r="B69" s="102"/>
-      <c r="C69" s="102"/>
-      <c r="D69" s="102"/>
+      <c r="B69" s="103"/>
+      <c r="C69" s="103"/>
+      <c r="D69" s="103"/>
       <c r="E69" s="71">
         <f t="shared" ref="E69:L69" si="26">MAX(E39:E67)</f>
         <v>9.0220517700000002E-2</v>
@@ -7574,12 +7581,12 @@
       <c r="N69" s="14"/>
     </row>
     <row r="70" spans="1:14" s="33" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A70" s="107" t="s">
+      <c r="A70" s="108" t="s">
         <v>60</v>
       </c>
-      <c r="B70" s="107"/>
-      <c r="C70" s="107"/>
-      <c r="D70" s="107"/>
+      <c r="B70" s="108"/>
+      <c r="C70" s="108"/>
+      <c r="D70" s="108"/>
       <c r="E70" s="72">
         <f t="shared" ref="E70:L70" si="27">AVERAGE(E40:E67)</f>
         <v>1.7271606619047621E-2</v>
@@ -7616,17 +7623,17 @@
       <c r="N70" s="34"/>
     </row>
     <row r="72" spans="1:14" s="29" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="98" t="s">
+      <c r="A72" s="99" t="s">
         <v>88</v>
       </c>
-      <c r="B72" s="98"/>
-      <c r="C72" s="98"/>
-      <c r="D72" s="98"/>
-      <c r="E72" s="98"/>
-      <c r="F72" s="98"/>
-      <c r="G72" s="98"/>
-      <c r="H72" s="98"/>
-      <c r="I72" s="98"/>
+      <c r="B72" s="99"/>
+      <c r="C72" s="99"/>
+      <c r="D72" s="99"/>
+      <c r="E72" s="99"/>
+      <c r="F72" s="99"/>
+      <c r="G72" s="99"/>
+      <c r="H72" s="99"/>
+      <c r="I72" s="99"/>
       <c r="J72" s="76"/>
       <c r="K72" s="79"/>
       <c r="L72" s="79"/>
@@ -7652,10 +7659,10 @@
       <c r="B74" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C74" s="90" t="s">
+      <c r="C74" s="91" t="s">
         <v>89</v>
       </c>
-      <c r="D74" s="90" t="s">
+      <c r="D74" s="91" t="s">
         <v>62</v>
       </c>
       <c r="E74" s="58">
@@ -7693,8 +7700,8 @@
       <c r="B75" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C75" s="90"/>
-      <c r="D75" s="90"/>
+      <c r="C75" s="91"/>
+      <c r="D75" s="91"/>
       <c r="E75" s="58">
         <v>8.8139489999999997E-3</v>
       </c>
@@ -7730,8 +7737,8 @@
       <c r="B76" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C76" s="90"/>
-      <c r="D76" s="90"/>
+      <c r="C76" s="91"/>
+      <c r="D76" s="91"/>
       <c r="E76" s="58">
         <v>1.9160760000000001E-4</v>
       </c>
@@ -7767,10 +7774,10 @@
       <c r="B78" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C78" s="90" t="s">
+      <c r="C78" s="91" t="s">
         <v>90</v>
       </c>
-      <c r="D78" s="90" t="s">
+      <c r="D78" s="91" t="s">
         <v>64</v>
       </c>
       <c r="E78" s="58">
@@ -7808,8 +7815,8 @@
       <c r="B79" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C79" s="90"/>
-      <c r="D79" s="90"/>
+      <c r="C79" s="91"/>
+      <c r="D79" s="91"/>
       <c r="E79" s="58">
         <v>3.4489365999999999E-3</v>
       </c>
@@ -7845,8 +7852,8 @@
       <c r="B80" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C80" s="90"/>
-      <c r="D80" s="90"/>
+      <c r="C80" s="91"/>
+      <c r="D80" s="91"/>
       <c r="E80" s="73">
         <v>4.7901900000000002E-4</v>
       </c>
@@ -7882,10 +7889,10 @@
       <c r="B82" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C82" s="90" t="s">
+      <c r="C82" s="91" t="s">
         <v>91</v>
       </c>
-      <c r="D82" s="90" t="s">
+      <c r="D82" s="91" t="s">
         <v>75</v>
       </c>
       <c r="E82" s="58">
@@ -7923,8 +7930,8 @@
       <c r="B83" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C83" s="90"/>
-      <c r="D83" s="90"/>
+      <c r="C83" s="91"/>
+      <c r="D83" s="91"/>
       <c r="E83" s="58">
         <v>4.3111707000000003E-3</v>
       </c>
@@ -7960,8 +7967,8 @@
       <c r="B84" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C84" s="90"/>
-      <c r="D84" s="90"/>
+      <c r="C84" s="91"/>
+      <c r="D84" s="91"/>
       <c r="E84" s="58">
         <v>2.1076835000000001E-3</v>
       </c>
@@ -7997,10 +8004,10 @@
       <c r="B86" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="C86" s="90" t="s">
+      <c r="C86" s="91" t="s">
         <v>92</v>
       </c>
-      <c r="D86" s="90" t="s">
+      <c r="D86" s="91" t="s">
         <v>73</v>
       </c>
       <c r="E86" s="60">
@@ -8038,8 +8045,8 @@
       <c r="B87" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C87" s="90"/>
-      <c r="D87" s="90"/>
+      <c r="C87" s="91"/>
+      <c r="D87" s="91"/>
       <c r="E87" s="58">
         <v>8.6223409999999995E-4</v>
       </c>
@@ -8075,8 +8082,8 @@
       <c r="B88" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C88" s="90"/>
-      <c r="D88" s="90"/>
+      <c r="C88" s="91"/>
+      <c r="D88" s="91"/>
       <c r="E88" s="58">
         <v>3.8321520000000002E-4</v>
       </c>
@@ -8115,10 +8122,10 @@
       <c r="B90" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C90" s="90" t="s">
+      <c r="C90" s="91" t="s">
         <v>93</v>
       </c>
-      <c r="D90" s="90" t="s">
+      <c r="D90" s="91" t="s">
         <v>67</v>
       </c>
       <c r="E90" s="58">
@@ -8156,8 +8163,8 @@
       <c r="B91" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C91" s="90"/>
-      <c r="D91" s="90"/>
+      <c r="C91" s="91"/>
+      <c r="D91" s="91"/>
       <c r="E91" s="58">
         <v>1.59034298E-2</v>
       </c>
@@ -8193,8 +8200,8 @@
       <c r="B92" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C92" s="90"/>
-      <c r="D92" s="90"/>
+      <c r="C92" s="91"/>
+      <c r="D92" s="91"/>
       <c r="E92" s="58">
         <v>0</v>
       </c>
@@ -8230,10 +8237,10 @@
       <c r="B94" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C94" s="90" t="s">
+      <c r="C94" s="91" t="s">
         <v>94</v>
       </c>
-      <c r="D94" s="90" t="s">
+      <c r="D94" s="91" t="s">
         <v>69</v>
       </c>
       <c r="E94" s="58">
@@ -8271,8 +8278,8 @@
       <c r="B95" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C95" s="90"/>
-      <c r="D95" s="90"/>
+      <c r="C95" s="91"/>
+      <c r="D95" s="91"/>
       <c r="E95" s="58">
         <v>9.4845755999999996E-3</v>
       </c>
@@ -8308,8 +8315,8 @@
       <c r="B96" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C96" s="90"/>
-      <c r="D96" s="90"/>
+      <c r="C96" s="91"/>
+      <c r="D96" s="91"/>
       <c r="E96" s="58">
         <v>1.9160760000000001E-4</v>
       </c>
@@ -8345,10 +8352,10 @@
       <c r="B98" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C98" s="90" t="s">
+      <c r="C98" s="91" t="s">
         <v>95</v>
       </c>
-      <c r="D98" s="90" t="s">
+      <c r="D98" s="91" t="s">
         <v>70</v>
       </c>
       <c r="E98" s="58">
@@ -8386,8 +8393,8 @@
       <c r="B99" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C99" s="90"/>
-      <c r="D99" s="90"/>
+      <c r="C99" s="91"/>
+      <c r="D99" s="91"/>
       <c r="E99" s="58">
         <v>8.9097528000000002E-3</v>
       </c>
@@ -8423,8 +8430,8 @@
       <c r="B100" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C100" s="90"/>
-      <c r="D100" s="90"/>
+      <c r="C100" s="91"/>
+      <c r="D100" s="91"/>
       <c r="E100" s="58">
         <v>1.6286645000000001E-3</v>
       </c>
@@ -8454,12 +8461,12 @@
       </c>
     </row>
     <row r="103" spans="1:14" s="11" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A103" s="102" t="s">
+      <c r="A103" s="103" t="s">
         <v>59</v>
       </c>
-      <c r="B103" s="102"/>
-      <c r="C103" s="102"/>
-      <c r="D103" s="102"/>
+      <c r="B103" s="103"/>
+      <c r="C103" s="103"/>
+      <c r="D103" s="103"/>
       <c r="E103" s="71">
         <f t="shared" ref="E103:L103" si="49">MAX(E73:E101)</f>
         <v>4.4165548999999998E-2</v>
@@ -8496,12 +8503,12 @@
       <c r="N103" s="14"/>
     </row>
     <row r="104" spans="1:14" s="33" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A104" s="107" t="s">
+      <c r="A104" s="108" t="s">
         <v>60</v>
       </c>
-      <c r="B104" s="107"/>
-      <c r="C104" s="107"/>
-      <c r="D104" s="107"/>
+      <c r="B104" s="108"/>
+      <c r="C104" s="108"/>
+      <c r="D104" s="108"/>
       <c r="E104" s="72">
         <f t="shared" ref="E104:L104" si="50">AVERAGE(E74:E101)</f>
         <v>1.0789332023809524E-2</v>
@@ -8618,11 +8625,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" s="44" customFormat="1" ht="27" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="99" t="s">
+      <c r="A1" s="100" t="s">
         <v>113</v>
       </c>
-      <c r="B1" s="100"/>
-      <c r="C1" s="101"/>
+      <c r="B1" s="101"/>
+      <c r="C1" s="102"/>
       <c r="E1" s="55"/>
       <c r="F1" s="55"/>
       <c r="G1" s="55"/>
@@ -8683,10 +8690,10 @@
       <c r="B4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="90" t="s">
+      <c r="C4" s="91" t="s">
         <v>101</v>
       </c>
-      <c r="D4" s="90" t="s">
+      <c r="D4" s="91" t="s">
         <v>103</v>
       </c>
       <c r="E4" s="57">
@@ -8719,7 +8726,7 @@
         <f>SUMPRODUCT(H4:J4,$F$21:$H$21)/SUM($F$21:$H$21)</f>
         <v>0.11303680448376624</v>
       </c>
-      <c r="N4" s="109">
+      <c r="N4" s="110">
         <f>AVERAGE(M4:M6)</f>
         <v>0.39531696738290045</v>
       </c>
@@ -8732,8 +8739,8 @@
       <c r="B5" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="90"/>
-      <c r="D5" s="90"/>
+      <c r="C5" s="91"/>
+      <c r="D5" s="91"/>
       <c r="E5" s="57">
         <v>0.52140253719999996</v>
       </c>
@@ -8764,7 +8771,7 @@
         <f>SUMPRODUCT(H5:J5,$F$21:$H$21)/SUM($F$21:$H$21)</f>
         <v>0.28553819413441561</v>
       </c>
-      <c r="N5" s="109"/>
+      <c r="N5" s="110"/>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
@@ -8773,8 +8780,8 @@
       <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="90"/>
-      <c r="D6" s="90"/>
+      <c r="C6" s="91"/>
+      <c r="D6" s="91"/>
       <c r="E6" s="57">
         <v>0.43752120239999998</v>
       </c>
@@ -8805,7 +8812,7 @@
         <f>SUMPRODUCT(H6:J6,$F$21:$H$21)/SUM($F$21:$H$21)</f>
         <v>0.78737590353051945</v>
       </c>
-      <c r="N6" s="109"/>
+      <c r="N6" s="110"/>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="E7" s="58"/>
@@ -8825,10 +8832,10 @@
       <c r="B8" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="90" t="s">
+      <c r="C8" s="91" t="s">
         <v>104</v>
       </c>
-      <c r="D8" s="90" t="s">
+      <c r="D8" s="91" t="s">
         <v>105</v>
       </c>
       <c r="E8" s="57">
@@ -8861,7 +8868,7 @@
         <f>SUMPRODUCT(H8:J8,$F$24:$H$24)/SUM($F$24:$H$24)</f>
         <v>0.18299197745155707</v>
       </c>
-      <c r="N8" s="108">
+      <c r="N8" s="109">
         <f>AVERAGE(M8:M10)</f>
         <v>0.48243735815617073</v>
       </c>
@@ -8873,8 +8880,8 @@
       <c r="B9" s="50" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="90"/>
-      <c r="D9" s="90"/>
+      <c r="C9" s="91"/>
+      <c r="D9" s="91"/>
       <c r="E9" s="59">
         <v>0.47961395620000002</v>
       </c>
@@ -8905,7 +8912,7 @@
         <f>SUMPRODUCT(H9:J9,$F$24:$H$24)/SUM($F$24:$H$24)</f>
         <v>0.44897119688373704</v>
       </c>
-      <c r="N9" s="108"/>
+      <c r="N9" s="109"/>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
@@ -8914,8 +8921,8 @@
       <c r="B10" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C10" s="90"/>
-      <c r="D10" s="90"/>
+      <c r="C10" s="91"/>
+      <c r="D10" s="91"/>
       <c r="E10" s="57">
         <v>0.31939047450000002</v>
       </c>
@@ -8946,7 +8953,7 @@
         <f>SUMPRODUCT(H10:J10,$F$24:$H$24)/SUM($F$24:$H$24)</f>
         <v>0.81534890013321804</v>
       </c>
-      <c r="N10" s="108"/>
+      <c r="N10" s="109"/>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="E11" s="58"/>
@@ -8966,10 +8973,10 @@
       <c r="B12" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C12" s="90" t="s">
+      <c r="C12" s="91" t="s">
         <v>106</v>
       </c>
-      <c r="D12" s="90" t="s">
+      <c r="D12" s="91" t="s">
         <v>107</v>
       </c>
       <c r="E12" s="57">
@@ -9002,7 +9009,7 @@
         <f>SUMPRODUCT(H12:J12, $F$27:$H$27)/SUM( $F$27:$H$27)</f>
         <v>9.5083615811034486E-2</v>
       </c>
-      <c r="N12" s="108">
+      <c r="N12" s="109">
         <f>AVERAGE(M12:M14)</f>
         <v>0.17141022467678158</v>
       </c>
@@ -9014,8 +9021,8 @@
       <c r="B13" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C13" s="90"/>
-      <c r="D13" s="90"/>
+      <c r="C13" s="91"/>
+      <c r="D13" s="91"/>
       <c r="E13" s="57">
         <v>0.49520081519999998</v>
       </c>
@@ -9046,7 +9053,7 @@
         <f>SUMPRODUCT(H13:J13, $F$27:$H$27)/SUM( $F$27:$H$27)</f>
         <v>0.36762890080068961</v>
       </c>
-      <c r="N13" s="108"/>
+      <c r="N13" s="109"/>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
@@ -9055,8 +9062,8 @@
       <c r="B14" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C14" s="90"/>
-      <c r="D14" s="90"/>
+      <c r="C14" s="91"/>
+      <c r="D14" s="91"/>
       <c r="E14" s="57">
         <v>0.64865882360000005</v>
       </c>
@@ -9087,7 +9094,7 @@
         <f>SUMPRODUCT(H14:J14, $F$27:$H$27)/SUM( $F$27:$H$27)</f>
         <v>5.1518157418620682E-2</v>
       </c>
-      <c r="N14" s="108"/>
+      <c r="N14" s="109"/>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="E15" s="58"/>
@@ -9280,6 +9287,971 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27F8C4AA-89AD-F044-80D9-1C4AE445CCE9}">
+  <dimension ref="A1:N35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="22.6640625" defaultRowHeight="21" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="25.1640625" style="1" customWidth="1"/>
+    <col min="2" max="3" width="15" style="1" customWidth="1"/>
+    <col min="4" max="4" width="41.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="36.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="21" style="9" customWidth="1"/>
+    <col min="7" max="7" width="22.6640625" style="9"/>
+    <col min="8" max="8" width="21" style="9" customWidth="1"/>
+    <col min="9" max="9" width="19" style="9" customWidth="1"/>
+    <col min="10" max="11" width="16.6640625" style="9" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="24.5" style="9" customWidth="1"/>
+    <col min="13" max="13" width="13.83203125" style="41" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="25.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="22.6640625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" s="44" customFormat="1" ht="27" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="100" t="s">
+        <v>142</v>
+      </c>
+      <c r="B1" s="101"/>
+      <c r="C1" s="101"/>
+      <c r="D1" s="102"/>
+      <c r="F1" s="55"/>
+      <c r="G1" s="55"/>
+      <c r="H1" s="55"/>
+      <c r="I1" s="55"/>
+      <c r="J1" s="55"/>
+      <c r="K1" s="55"/>
+      <c r="L1" s="55"/>
+      <c r="M1" s="63"/>
+    </row>
+    <row r="2" spans="1:14" s="4" customFormat="1" ht="66" x14ac:dyDescent="0.2">
+      <c r="A2" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F2" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="G2" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="H2" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="I2" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="J2" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="K2" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="L2" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="M2" s="40" t="s">
+        <v>124</v>
+      </c>
+      <c r="N2" s="5" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A4" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="93">
+        <v>0</v>
+      </c>
+      <c r="D4" s="91" t="s">
+        <v>104</v>
+      </c>
+      <c r="E4" s="91" t="s">
+        <v>105</v>
+      </c>
+      <c r="F4" s="57">
+        <v>0.64805542540000005</v>
+      </c>
+      <c r="G4" s="58">
+        <v>0.70795781400000002</v>
+      </c>
+      <c r="H4" s="58">
+        <v>0.89434324070000004</v>
+      </c>
+      <c r="I4" s="58">
+        <v>0.79573876789999998</v>
+      </c>
+      <c r="J4" s="58">
+        <v>0.31020942410000002</v>
+      </c>
+      <c r="K4" s="58">
+        <v>0.14285714290000001</v>
+      </c>
+      <c r="L4" s="58">
+        <f>I4*1/3+J4*1/3+K4*1/3</f>
+        <v>0.41626844496666671</v>
+      </c>
+      <c r="M4" s="41">
+        <f>STDEV(I4:K4)</f>
+        <v>0.33911648588067361</v>
+      </c>
+      <c r="N4" s="58">
+        <f>SUMPRODUCT(I4:K4,$G$32:$I$32)/SUM($G$32:$I$32)</f>
+        <v>0.18299197745155707</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="93"/>
+      <c r="D5" s="91"/>
+      <c r="E5" s="91"/>
+      <c r="F5" s="57">
+        <v>0.47961395620000002</v>
+      </c>
+      <c r="G5" s="58">
+        <v>0.27823585810000001</v>
+      </c>
+      <c r="H5" s="58">
+        <v>0.69242569509999996</v>
+      </c>
+      <c r="I5" s="58">
+        <v>0.26146364059999999</v>
+      </c>
+      <c r="J5" s="58">
+        <v>0.33900523560000001</v>
+      </c>
+      <c r="K5" s="58">
+        <v>0.47368421049999998</v>
+      </c>
+      <c r="L5" s="58">
+        <f t="shared" ref="L5:L6" si="0">I5*1/3+J5*1/3+K5*1/3</f>
+        <v>0.35805102890000001</v>
+      </c>
+      <c r="M5" s="41">
+        <f>STDEV(I5:K5)</f>
+        <v>0.1073845857373857</v>
+      </c>
+      <c r="N5" s="58">
+        <f>SUMPRODUCT(I5:K5,$G$32:$I$32)/SUM($G$32:$I$32)</f>
+        <v>0.44897119688373704</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="93"/>
+      <c r="D6" s="91"/>
+      <c r="E6" s="91"/>
+      <c r="F6" s="57">
+        <v>0.31939047450000002</v>
+      </c>
+      <c r="G6" s="58">
+        <v>2.9146692200000001E-2</v>
+      </c>
+      <c r="H6" s="58">
+        <v>0.1883029722</v>
+      </c>
+      <c r="I6" s="58">
+        <v>6.9476610000000002E-4</v>
+      </c>
+      <c r="J6" s="58">
+        <v>2.4869109899999998E-2</v>
+      </c>
+      <c r="K6" s="58">
+        <v>0.97744360900000005</v>
+      </c>
+      <c r="L6" s="58">
+        <f t="shared" si="0"/>
+        <v>0.33433582833333336</v>
+      </c>
+      <c r="M6" s="41">
+        <f>STDEV(I6:K6)</f>
+        <v>0.55707882107475981</v>
+      </c>
+      <c r="N6" s="58">
+        <f>SUMPRODUCT(I6:K6,$G$32:$I$32)/SUM($G$32:$I$32)</f>
+        <v>0.81534890013321804</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="57"/>
+      <c r="G7" s="58"/>
+      <c r="H7" s="58"/>
+      <c r="I7" s="58"/>
+      <c r="J7" s="58"/>
+      <c r="K7" s="58"/>
+      <c r="L7" s="58"/>
+      <c r="N7" s="58"/>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A8" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="93">
+        <v>10</v>
+      </c>
+      <c r="D8" s="91" t="s">
+        <v>104</v>
+      </c>
+      <c r="E8" s="91" t="s">
+        <v>105</v>
+      </c>
+      <c r="F8" s="57">
+        <v>0.65405767370000001</v>
+      </c>
+      <c r="G8" s="58">
+        <v>0.61514860979999997</v>
+      </c>
+      <c r="H8" s="58">
+        <v>0.91965484180000001</v>
+      </c>
+      <c r="I8" s="58">
+        <v>0.65979620189999999</v>
+      </c>
+      <c r="J8" s="58">
+        <v>0.46204188480000002</v>
+      </c>
+      <c r="K8" s="58">
+        <v>4.5112781999999997E-2</v>
+      </c>
+      <c r="L8" s="58">
+        <f>I8*1/3+J8*1/3+K8*1/3</f>
+        <v>0.38898362289999999</v>
+      </c>
+      <c r="M8" s="41">
+        <f>STDEV(I8:K8)</f>
+        <v>0.31378664550754348</v>
+      </c>
+      <c r="N8" s="58">
+        <f>SUMPRODUCT(I8:K8,$G$32:$I$32)/SUM($G$32:$I$32)</f>
+        <v>0.12059308046678201</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9" s="93"/>
+      <c r="D9" s="91"/>
+      <c r="E9" s="91"/>
+      <c r="F9" s="57">
+        <v>0.49123318589999998</v>
+      </c>
+      <c r="G9" s="58">
+        <v>0.29626078620000001</v>
+      </c>
+      <c r="H9" s="58">
+        <v>0.72732502399999999</v>
+      </c>
+      <c r="I9" s="58">
+        <v>0.28855951829999998</v>
+      </c>
+      <c r="J9" s="58">
+        <v>0.32591623040000001</v>
+      </c>
+      <c r="K9" s="58">
+        <v>0.37593984959999999</v>
+      </c>
+      <c r="L9" s="58">
+        <f t="shared" ref="L9:L10" si="1">I9*1/3+J9*1/3+K9*1/3</f>
+        <v>0.33013853276666666</v>
+      </c>
+      <c r="M9" s="41">
+        <f>STDEV(I9:K9)</f>
+        <v>4.3842917928453309E-2</v>
+      </c>
+      <c r="N9" s="58">
+        <f>SUMPRODUCT(I9:K9,$G$32:$I$32)/SUM($G$32:$I$32)</f>
+        <v>0.36655350245294122</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A10" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" s="93"/>
+      <c r="D10" s="91"/>
+      <c r="E10" s="91"/>
+      <c r="F10" s="57">
+        <v>0.4400081542</v>
+      </c>
+      <c r="G10" s="58">
+        <v>0.18791946309999999</v>
+      </c>
+      <c r="H10" s="58">
+        <v>0.56529242570000005</v>
+      </c>
+      <c r="I10" s="58">
+        <v>0.1727651691</v>
+      </c>
+      <c r="J10" s="58">
+        <v>0.2015706806</v>
+      </c>
+      <c r="K10" s="58">
+        <v>0.6015037594</v>
+      </c>
+      <c r="L10" s="58">
+        <f t="shared" si="1"/>
+        <v>0.3252798697</v>
+      </c>
+      <c r="M10" s="41">
+        <f>STDEV(I10:K10)</f>
+        <v>0.23965009347785046</v>
+      </c>
+      <c r="N10" s="58">
+        <f>SUMPRODUCT(I10:K10,$G$32:$I$32)/SUM($G$32:$I$32)</f>
+        <v>0.53299732534567468</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="57"/>
+      <c r="G11" s="58"/>
+      <c r="H11" s="58"/>
+      <c r="I11" s="58"/>
+      <c r="J11" s="58"/>
+      <c r="K11" s="58"/>
+      <c r="L11" s="58"/>
+      <c r="N11" s="58"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A12" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C12" s="93">
+        <v>20</v>
+      </c>
+      <c r="D12" s="91" t="s">
+        <v>104</v>
+      </c>
+      <c r="E12" s="91" t="s">
+        <v>105</v>
+      </c>
+      <c r="F12" s="57">
+        <v>0.60802313109999995</v>
+      </c>
+      <c r="G12" s="58">
+        <v>0.53978906999999998</v>
+      </c>
+      <c r="H12" s="58">
+        <v>0.86136145730000002</v>
+      </c>
+      <c r="I12" s="58">
+        <v>0.57989810100000005</v>
+      </c>
+      <c r="J12" s="58">
+        <v>0.39005235599999999</v>
+      </c>
+      <c r="K12" s="58">
+        <v>9.7744360899999994E-2</v>
+      </c>
+      <c r="L12" s="58">
+        <f>I12*1/3+J12*1/3+K12*1/3</f>
+        <v>0.35589827263333335</v>
+      </c>
+      <c r="M12" s="41">
+        <f>STDEV(I12:K12)</f>
+        <v>0.24288460908642909</v>
+      </c>
+      <c r="N12" s="58">
+        <f>SUMPRODUCT(I12:K12,$G$32:$I$32)/SUM($G$32:$I$32)</f>
+        <v>0.15190357188581313</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A13" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C13" s="93"/>
+      <c r="D13" s="91"/>
+      <c r="E13" s="91"/>
+      <c r="F13" s="57">
+        <v>0.48156989849999998</v>
+      </c>
+      <c r="G13" s="58">
+        <v>0.27957813999999998</v>
+      </c>
+      <c r="H13" s="58">
+        <v>0.70584851390000003</v>
+      </c>
+      <c r="I13" s="58">
+        <v>0.27674849470000001</v>
+      </c>
+      <c r="J13" s="58">
+        <v>0.2565445026</v>
+      </c>
+      <c r="K13" s="58">
+        <v>0.50375939849999996</v>
+      </c>
+      <c r="L13" s="58">
+        <f t="shared" ref="L13:L14" si="2">I13*1/3+J13*1/3+K13*1/3</f>
+        <v>0.34568413193333336</v>
+      </c>
+      <c r="M13" s="41">
+        <f>STDEV(I13:K13)</f>
+        <v>0.13726941665675668</v>
+      </c>
+      <c r="N13" s="58">
+        <f>SUMPRODUCT(I13:K13,$G$32:$I$32)/SUM($G$32:$I$32)</f>
+        <v>0.46233344018027672</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A14" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C14" s="93"/>
+      <c r="D14" s="91"/>
+      <c r="E14" s="91"/>
+      <c r="F14" s="57">
+        <v>0.53785895859999999</v>
+      </c>
+      <c r="G14" s="58">
+        <v>0.69338446789999997</v>
+      </c>
+      <c r="H14" s="58">
+        <v>0.83739213810000002</v>
+      </c>
+      <c r="I14" s="58">
+        <v>0.81194997680000003</v>
+      </c>
+      <c r="J14" s="58">
+        <v>0.14005235599999999</v>
+      </c>
+      <c r="K14" s="58">
+        <v>2.2556390999999999E-2</v>
+      </c>
+      <c r="L14" s="58">
+        <f t="shared" si="2"/>
+        <v>0.32485290793333338</v>
+      </c>
+      <c r="M14" s="41">
+        <f>STDEV(I14:K14)</f>
+        <v>0.42590960463658717</v>
+      </c>
+      <c r="N14" s="58">
+        <f>SUMPRODUCT(I14:K14,$G$32:$I$32)/SUM($G$32:$I$32)</f>
+        <v>5.8752189029757776E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="57"/>
+      <c r="G15" s="58"/>
+      <c r="H15" s="58"/>
+      <c r="I15" s="58"/>
+      <c r="J15" s="58"/>
+      <c r="K15" s="58"/>
+      <c r="L15" s="58"/>
+      <c r="N15" s="58"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A16" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C16" s="93">
+        <v>30</v>
+      </c>
+      <c r="D16" s="91" t="s">
+        <v>104</v>
+      </c>
+      <c r="E16" s="91" t="s">
+        <v>105</v>
+      </c>
+      <c r="F16" s="57">
+        <v>0.59880876279999995</v>
+      </c>
+      <c r="G16" s="58">
+        <v>0.51505273250000005</v>
+      </c>
+      <c r="H16" s="58">
+        <v>0.83873441989999997</v>
+      </c>
+      <c r="I16" s="58">
+        <v>0.56855025469999998</v>
+      </c>
+      <c r="J16" s="58">
+        <v>0.2643979058</v>
+      </c>
+      <c r="K16" s="58">
+        <v>0.2180451128</v>
+      </c>
+      <c r="L16" s="58">
+        <f>I16*1/3+J16*1/3+K16*1/3</f>
+        <v>0.35033109109999999</v>
+      </c>
+      <c r="M16" s="41">
+        <f>STDEV(I16:K16)</f>
+        <v>0.19039918034602427</v>
+      </c>
+      <c r="N16" s="58">
+        <f>SUMPRODUCT(I16:K16,$G$32:$I$32)/SUM($G$32:$I$32)</f>
+        <v>0.23327124878373701</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A17" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C17" s="93"/>
+      <c r="D17" s="91"/>
+      <c r="E17" s="91"/>
+      <c r="F17" s="57">
+        <v>0.48391429850000001</v>
+      </c>
+      <c r="G17" s="58">
+        <v>0.2834132311</v>
+      </c>
+      <c r="H17" s="58">
+        <v>0.70278044100000003</v>
+      </c>
+      <c r="I17" s="58">
+        <v>0.27211672069999998</v>
+      </c>
+      <c r="J17" s="58">
+        <v>0.34424083770000002</v>
+      </c>
+      <c r="K17" s="58">
+        <v>0.3007518797</v>
+      </c>
+      <c r="L17" s="58">
+        <f t="shared" ref="L17:L18" si="3">I17*1/3+J17*1/3+K17*1/3</f>
+        <v>0.30570314603333332</v>
+      </c>
+      <c r="M17" s="41">
+        <f>STDEV(I17:K17)</f>
+        <v>3.6316089299167714E-2</v>
+      </c>
+      <c r="N17" s="58">
+        <f>SUMPRODUCT(I17:K17,$G$32:$I$32)/SUM($G$32:$I$32)</f>
+        <v>0.30637848912214527</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A18" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C18" s="93"/>
+      <c r="D18" s="91"/>
+      <c r="E18" s="91"/>
+      <c r="F18" s="57">
+        <v>0.4437803837</v>
+      </c>
+      <c r="G18" s="58">
+        <v>6.9798657700000002E-2</v>
+      </c>
+      <c r="H18" s="58">
+        <v>0.19194630870000001</v>
+      </c>
+      <c r="I18" s="58">
+        <v>1.1579434899999999E-2</v>
+      </c>
+      <c r="J18" s="58">
+        <v>0.27879581149999999</v>
+      </c>
+      <c r="K18" s="58">
+        <v>0.75939849619999999</v>
+      </c>
+      <c r="L18" s="58">
+        <f t="shared" si="3"/>
+        <v>0.34992458086666667</v>
+      </c>
+      <c r="M18" s="41">
+        <f>STDEV(I18:K18)</f>
+        <v>0.37894961866271298</v>
+      </c>
+      <c r="N18" s="58">
+        <f>SUMPRODUCT(I18:K18,$G$32:$I$32)/SUM($G$32:$I$32)</f>
+        <v>0.67143985887647051</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="D19" s="2"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="57"/>
+      <c r="G19" s="58"/>
+      <c r="H19" s="58"/>
+      <c r="I19" s="58"/>
+      <c r="J19" s="58"/>
+      <c r="K19" s="58"/>
+      <c r="L19" s="58"/>
+      <c r="N19" s="58"/>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A20" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C20" s="93">
+        <v>50</v>
+      </c>
+      <c r="D20" s="91" t="s">
+        <v>104</v>
+      </c>
+      <c r="E20" s="91" t="s">
+        <v>105</v>
+      </c>
+      <c r="F20" s="57">
+        <v>0.53963160349999995</v>
+      </c>
+      <c r="G20" s="58">
+        <v>0.4343240652</v>
+      </c>
+      <c r="H20" s="58">
+        <v>0.77162032599999997</v>
+      </c>
+      <c r="I20" s="58">
+        <v>0.46132468739999999</v>
+      </c>
+      <c r="J20" s="58">
+        <v>0.29057591620000001</v>
+      </c>
+      <c r="K20" s="58">
+        <v>0.38345864660000001</v>
+      </c>
+      <c r="L20" s="58">
+        <f>I20*1/3+J20*1/3+K20*1/3</f>
+        <v>0.37845308340000006</v>
+      </c>
+      <c r="M20" s="41">
+        <f>STDEV(I20:K20)</f>
+        <v>8.5484369704580204E-2</v>
+      </c>
+      <c r="N20" s="58">
+        <f>SUMPRODUCT(I20:K20,$G$32:$I$32)/SUM($G$32:$I$32)</f>
+        <v>0.37184614697647056</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A21" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C21" s="93"/>
+      <c r="D21" s="91"/>
+      <c r="E21" s="91"/>
+      <c r="F21" s="57">
+        <v>0.49039566899999998</v>
+      </c>
+      <c r="G21" s="58">
+        <v>0.31716203259999998</v>
+      </c>
+      <c r="H21" s="58">
+        <v>0.68034515819999997</v>
+      </c>
+      <c r="I21" s="58">
+        <v>0.30477072719999998</v>
+      </c>
+      <c r="J21" s="58">
+        <v>0.37172774870000003</v>
+      </c>
+      <c r="K21" s="58">
+        <v>0.40601503760000002</v>
+      </c>
+      <c r="L21" s="58">
+        <f t="shared" ref="L21:L22" si="4">I21*1/3+J21*1/3+K21*1/3</f>
+        <v>0.36083783783333334</v>
+      </c>
+      <c r="M21" s="41">
+        <f>STDEV(I21:K21)</f>
+        <v>5.1493156983291363E-2</v>
+      </c>
+      <c r="N21" s="58">
+        <f>SUMPRODUCT(I21:K21,$G$32:$I$32)/SUM($G$32:$I$32)</f>
+        <v>0.398579825466436</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A22" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C22" s="93"/>
+      <c r="D22" s="91"/>
+      <c r="E22" s="91"/>
+      <c r="F22" s="57">
+        <v>0.35765062860000002</v>
+      </c>
+      <c r="G22" s="58">
+        <v>0.15417066160000001</v>
+      </c>
+      <c r="H22" s="58">
+        <v>0.33940556090000001</v>
+      </c>
+      <c r="I22" s="58">
+        <v>1.4590087999999999E-2</v>
+      </c>
+      <c r="J22" s="58">
+        <v>0.96596858640000005</v>
+      </c>
+      <c r="K22" s="58">
+        <v>2.2556390999999999E-2</v>
+      </c>
+      <c r="L22" s="58">
+        <f t="shared" si="4"/>
+        <v>0.33437168846666671</v>
+      </c>
+      <c r="M22" s="41">
+        <f>STDEV(I22:K22)</f>
+        <v>0.5469934612087507</v>
+      </c>
+      <c r="N22" s="58">
+        <f>SUMPRODUCT(I22:K22,$G$32:$I$32)/SUM($G$32:$I$32)</f>
+        <v>0.15946832209273357</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="F23" s="58"/>
+      <c r="G23" s="58"/>
+      <c r="H23" s="58"/>
+      <c r="I23" s="58"/>
+      <c r="J23" s="58"/>
+      <c r="K23" s="58"/>
+      <c r="L23" s="58"/>
+      <c r="N23" s="58"/>
+    </row>
+    <row r="24" spans="1:14" s="42" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="F24" s="61"/>
+      <c r="G24" s="61"/>
+      <c r="H24" s="61"/>
+      <c r="I24" s="61"/>
+      <c r="J24" s="61"/>
+      <c r="K24" s="62" t="s">
+        <v>59</v>
+      </c>
+      <c r="L24" s="61">
+        <f>MAX(L4:L23)</f>
+        <v>0.41626844496666671</v>
+      </c>
+      <c r="M24" s="65">
+        <f>MAX(M4:M23)</f>
+        <v>0.55707882107475981</v>
+      </c>
+      <c r="N24" s="61">
+        <f>MAX(N4:N23)</f>
+        <v>0.81534890013321804</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" s="42" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="F25" s="61"/>
+      <c r="G25" s="61"/>
+      <c r="H25" s="61"/>
+      <c r="I25" s="61"/>
+      <c r="J25" s="61"/>
+      <c r="K25" s="62" t="s">
+        <v>125</v>
+      </c>
+      <c r="L25" s="61">
+        <f>MIN(L4:L23)</f>
+        <v>0.30570314603333332</v>
+      </c>
+      <c r="M25" s="65">
+        <f>MIN(M4:M23)</f>
+        <v>3.6316089299167714E-2</v>
+      </c>
+      <c r="N25" s="61">
+        <f>MIN(N4:N23)</f>
+        <v>5.8752189029757776E-2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" s="42" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="F26" s="61"/>
+      <c r="G26" s="61"/>
+      <c r="H26" s="61"/>
+      <c r="I26" s="61"/>
+      <c r="J26" s="61"/>
+      <c r="K26" s="62" t="s">
+        <v>60</v>
+      </c>
+      <c r="L26" s="61">
+        <f>AVERAGE(L4:L23)</f>
+        <v>0.35060760451777784</v>
+      </c>
+      <c r="M26" s="65">
+        <f>AVERAGE(M4:M23)</f>
+        <v>0.24643727041273114</v>
+      </c>
+      <c r="N26" s="61">
+        <f>AVERAGE(N4:N23)</f>
+        <v>0.35209527167651677</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="F28" s="54" t="s">
+        <v>136</v>
+      </c>
+      <c r="G28" s="53" t="s">
+        <v>133</v>
+      </c>
+      <c r="H28" s="53" t="s">
+        <v>134</v>
+      </c>
+      <c r="I28" s="53" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="F29" s="53" t="s">
+        <v>128</v>
+      </c>
+      <c r="G29" s="52">
+        <f>1/25</f>
+        <v>0.04</v>
+      </c>
+      <c r="H29" s="52">
+        <f>1/4</f>
+        <v>0.25</v>
+      </c>
+      <c r="I29" s="52">
+        <f>1/0.8</f>
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="F31" s="54" t="s">
+        <v>137</v>
+      </c>
+      <c r="G31" s="53" t="s">
+        <v>133</v>
+      </c>
+      <c r="H31" s="53" t="s">
+        <v>134</v>
+      </c>
+      <c r="I31" s="53" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="F32" s="53" t="s">
+        <v>128</v>
+      </c>
+      <c r="G32" s="52">
+        <f>1/24</f>
+        <v>4.1666666666666664E-2</v>
+      </c>
+      <c r="H32" s="52">
+        <f>1/4</f>
+        <v>0.25</v>
+      </c>
+      <c r="I32" s="52">
+        <f>1/0.7</f>
+        <v>1.4285714285714286</v>
+      </c>
+    </row>
+    <row r="34" spans="6:9" x14ac:dyDescent="0.2">
+      <c r="F34" s="54" t="s">
+        <v>138</v>
+      </c>
+      <c r="G34" s="53" t="s">
+        <v>133</v>
+      </c>
+      <c r="H34" s="53" t="s">
+        <v>134</v>
+      </c>
+      <c r="I34" s="53" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="35" spans="6:9" x14ac:dyDescent="0.2">
+      <c r="F35" s="53" t="s">
+        <v>128</v>
+      </c>
+      <c r="G35" s="52">
+        <f>1/21</f>
+        <v>4.7619047619047616E-2</v>
+      </c>
+      <c r="H35" s="51">
+        <f>1/4</f>
+        <v>0.25</v>
+      </c>
+      <c r="I35" s="51">
+        <f>1/0.7</f>
+        <v>1.4285714285714286</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="16">
+    <mergeCell ref="C8:C10"/>
+    <mergeCell ref="D8:D10"/>
+    <mergeCell ref="E8:E10"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="C4:C6"/>
+    <mergeCell ref="D4:D6"/>
+    <mergeCell ref="E4:E6"/>
+    <mergeCell ref="C20:C22"/>
+    <mergeCell ref="D20:D22"/>
+    <mergeCell ref="E20:E22"/>
+    <mergeCell ref="C12:C14"/>
+    <mergeCell ref="D12:D14"/>
+    <mergeCell ref="E12:E14"/>
+    <mergeCell ref="C16:C18"/>
+    <mergeCell ref="D16:D18"/>
+    <mergeCell ref="E16:E18"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E8BFB43-1DD7-8F42-9661-D6416FFA154E}">
   <dimension ref="A1:N24"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="22.6640625" defaultRowHeight="21" x14ac:dyDescent="0.2"/>
@@ -9302,14 +10274,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" s="43" customFormat="1" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="99" t="s">
+      <c r="A1" s="100" t="s">
         <v>114</v>
       </c>
-      <c r="B1" s="100"/>
-      <c r="C1" s="100"/>
-      <c r="D1" s="100"/>
-      <c r="E1" s="100"/>
-      <c r="F1" s="101"/>
+      <c r="B1" s="101"/>
+      <c r="C1" s="101"/>
+      <c r="D1" s="101"/>
+      <c r="E1" s="101"/>
+      <c r="F1" s="102"/>
       <c r="G1" s="45"/>
       <c r="H1" s="45"/>
       <c r="I1" s="45"/>
@@ -9361,16 +10333,16 @@
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A4" s="92" t="s">
+      <c r="A4" s="93" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="111" t="s">
+      <c r="C4" s="112" t="s">
         <v>140</v>
       </c>
-      <c r="D4" s="90" t="s">
+      <c r="D4" s="91" t="s">
         <v>105</v>
       </c>
       <c r="E4" s="57">
@@ -9403,17 +10375,17 @@
         <f>SUMPRODUCT(H4:J4,$C$21:$E$21)/SUM($C$21:$E$21)</f>
         <v>0.18299197745155707</v>
       </c>
-      <c r="N4" s="110" t="s">
+      <c r="N4" s="111" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A5" s="92"/>
+      <c r="A5" s="93"/>
       <c r="B5" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="C5" s="111"/>
-      <c r="D5" s="90"/>
+      <c r="C5" s="112"/>
+      <c r="D5" s="91"/>
       <c r="E5" s="57">
         <v>0.86840317560000002</v>
       </c>
@@ -9444,15 +10416,15 @@
         <f>SUMPRODUCT(H5:J5,$C$21:$E$21)/SUM($C$21:$E$21)</f>
         <v>2.4221453287197228E-2</v>
       </c>
-      <c r="N5" s="90"/>
+      <c r="N5" s="91"/>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A6" s="92"/>
+      <c r="A6" s="93"/>
       <c r="B6" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="C6" s="111"/>
-      <c r="D6" s="90"/>
+      <c r="C6" s="112"/>
+      <c r="D6" s="91"/>
       <c r="E6" s="57">
         <v>0.51856609070000004</v>
       </c>
@@ -9483,11 +10455,11 @@
         <f>SUMPRODUCT(H6:J6,$C$21:$E$21)/SUM($C$21:$E$21)</f>
         <v>0.12131813426885814</v>
       </c>
-      <c r="N6" s="90"/>
+      <c r="N6" s="91"/>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C7" s="111"/>
-      <c r="D7" s="90"/>
+      <c r="C7" s="112"/>
+      <c r="D7" s="91"/>
       <c r="E7" s="57"/>
       <c r="F7" s="58"/>
       <c r="G7" s="58"/>
@@ -9498,14 +10470,14 @@
       <c r="M7" s="58"/>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A8" s="92" t="s">
+      <c r="A8" s="93" t="s">
         <v>116</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="C8" s="111"/>
-      <c r="D8" s="90"/>
+      <c r="C8" s="112"/>
+      <c r="D8" s="91"/>
       <c r="E8" s="57">
         <v>0.47961395620000002</v>
       </c>
@@ -9536,17 +10508,17 @@
         <f>SUMPRODUCT(H8:J8,$C$21:$E$21)/SUM($C$21:$E$21)</f>
         <v>0.44897119688373704</v>
       </c>
-      <c r="N8" s="110" t="s">
+      <c r="N8" s="111" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A9" s="92"/>
+      <c r="A9" s="93"/>
       <c r="B9" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="C9" s="111"/>
-      <c r="D9" s="90"/>
+      <c r="C9" s="112"/>
+      <c r="D9" s="91"/>
       <c r="E9" s="57">
         <v>0.51324470619999996</v>
       </c>
@@ -9577,15 +10549,15 @@
         <f>SUMPRODUCT(H9:J9,$C$21:$E$21)/SUM($C$21:$E$21)</f>
         <v>0.34063268984359857</v>
       </c>
-      <c r="N9" s="90"/>
+      <c r="N9" s="91"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A10" s="92"/>
+      <c r="A10" s="93"/>
       <c r="B10" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="C10" s="111"/>
-      <c r="D10" s="90"/>
+      <c r="C10" s="112"/>
+      <c r="D10" s="91"/>
       <c r="E10" s="57">
         <v>0.62861262309999999</v>
       </c>
@@ -9616,11 +10588,11 @@
         <f>SUMPRODUCT(H10:J10,$C$21:$E$21)/SUM($C$21:$E$21)</f>
         <v>0.28493143419515571</v>
       </c>
-      <c r="N10" s="90"/>
+      <c r="N10" s="91"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C11" s="111"/>
-      <c r="D11" s="90"/>
+      <c r="C11" s="112"/>
+      <c r="D11" s="91"/>
       <c r="E11" s="57"/>
       <c r="F11" s="58"/>
       <c r="G11" s="58"/>
@@ -9631,14 +10603,14 @@
       <c r="M11" s="58"/>
     </row>
     <row r="12" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="92" t="s">
+      <c r="A12" s="93" t="s">
         <v>117</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="C12" s="111"/>
-      <c r="D12" s="90"/>
+      <c r="C12" s="112"/>
+      <c r="D12" s="91"/>
       <c r="E12" s="57">
         <v>0.31939047450000002</v>
       </c>
@@ -9669,17 +10641,17 @@
         <f>SUMPRODUCT(H12:J12,$C$21:$E$21)/SUM($C$21:$E$21)</f>
         <v>0.81534890013321804</v>
       </c>
-      <c r="N12" s="112" t="s">
+      <c r="N12" s="86" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="22" x14ac:dyDescent="0.2">
-      <c r="A13" s="92"/>
+      <c r="A13" s="93"/>
       <c r="B13" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="C13" s="111"/>
-      <c r="D13" s="90"/>
+      <c r="C13" s="112"/>
+      <c r="D13" s="91"/>
       <c r="E13" s="57"/>
       <c r="F13" s="58">
         <v>0.65522531159999997</v>
